--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{,}</t>
+    <t>list&lt;list&lt;int&gt;{_}&gt;{,}</t>
   </si>
   <si>
     <t>id</t>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -1380,7 +1380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,6 +1392,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2025,7 +2028,7 @@
       <c r="J2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2046,19 +2049,19 @@
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2069,11 +2072,11 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" customHeight="1" spans="1:11">
       <c r="A5" s="3">
@@ -2095,15 +2098,15 @@
       <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="8">
-        <v>60</v>
-      </c>
-      <c r="K5" s="9" t="s">
+      <c r="G5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="9">
+        <v>60</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2127,17 +2130,17 @@
       <c r="F6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
+      <c r="G6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="8">
-        <v>60</v>
-      </c>
-      <c r="K6" s="9" t="s">
+      <c r="J6" s="9">
+        <v>60</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2161,17 +2164,17 @@
       <c r="F7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6" t="s">
+      <c r="G7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="8">
-        <v>60</v>
-      </c>
-      <c r="K7" s="9" t="s">
+      <c r="J7" s="9">
+        <v>60</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2195,17 +2198,17 @@
       <c r="F8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="s">
+      <c r="G8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="8">
-        <v>60</v>
-      </c>
-      <c r="K8" s="9" t="s">
+      <c r="J8" s="9">
+        <v>60</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2229,17 +2232,17 @@
       <c r="F9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
+      <c r="G9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="8">
-        <v>60</v>
-      </c>
-      <c r="K9" s="9" t="s">
+      <c r="J9" s="9">
+        <v>60</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2263,17 +2266,17 @@
       <c r="F10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
+      <c r="G10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="8">
-        <v>60</v>
-      </c>
-      <c r="K10" s="9" t="s">
+      <c r="J10" s="9">
+        <v>60</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2297,17 +2300,17 @@
       <c r="F11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
+      <c r="G11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="8">
-        <v>60</v>
-      </c>
-      <c r="K11" s="9" t="s">
+      <c r="J11" s="9">
+        <v>60</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2331,17 +2334,17 @@
       <c r="F12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="s">
+      <c r="G12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="8">
-        <v>60</v>
-      </c>
-      <c r="K12" s="9" t="s">
+      <c r="J12" s="9">
+        <v>60</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2356,26 +2359,26 @@
       <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>9</v>
       </c>
       <c r="E13" s="3">
         <v>8</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="6" t="s">
+      <c r="F13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="8">
-        <v>60</v>
-      </c>
-      <c r="K13" s="9" t="s">
+      <c r="J13" s="9">
+        <v>60</v>
+      </c>
+      <c r="K13" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2399,17 +2402,17 @@
       <c r="F14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
+      <c r="G14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="8">
-        <v>60</v>
-      </c>
-      <c r="K14" s="9" t="s">
+      <c r="J14" s="9">
+        <v>60</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2433,15 +2436,15 @@
       <c r="F15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="8">
-        <v>60</v>
-      </c>
-      <c r="K15" s="9" t="s">
+      <c r="G15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="9">
+        <v>60</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2465,17 +2468,17 @@
       <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="s">
+      <c r="G16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="8">
-        <v>60</v>
-      </c>
-      <c r="K16" s="9" t="s">
+      <c r="J16" s="9">
+        <v>60</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2499,17 +2502,17 @@
       <c r="F17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="s">
+      <c r="G17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="8">
-        <v>60</v>
-      </c>
-      <c r="K17" s="9" t="s">
+      <c r="J17" s="9">
+        <v>60</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2533,17 +2536,17 @@
       <c r="F18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="s">
+      <c r="G18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="8">
-        <v>60</v>
-      </c>
-      <c r="K18" s="9" t="s">
+      <c r="J18" s="9">
+        <v>60</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2567,17 +2570,17 @@
       <c r="F19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="s">
+      <c r="G19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="8">
-        <v>60</v>
-      </c>
-      <c r="K19" s="9" t="s">
+      <c r="J19" s="9">
+        <v>60</v>
+      </c>
+      <c r="K19" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2601,17 +2604,17 @@
       <c r="F20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
+      <c r="G20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="8">
-        <v>60</v>
-      </c>
-      <c r="K20" s="9" t="s">
+      <c r="J20" s="9">
+        <v>60</v>
+      </c>
+      <c r="K20" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2635,17 +2638,17 @@
       <c r="F21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6" t="s">
+      <c r="G21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="8">
-        <v>60</v>
-      </c>
-      <c r="K21" s="9" t="s">
+      <c r="J21" s="9">
+        <v>60</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2669,17 +2672,17 @@
       <c r="F22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6" t="s">
+      <c r="G22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="8">
-        <v>60</v>
-      </c>
-      <c r="K22" s="9" t="s">
+      <c r="J22" s="9">
+        <v>60</v>
+      </c>
+      <c r="K22" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2694,26 +2697,26 @@
       <c r="C23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="11">
         <v>9</v>
       </c>
       <c r="E23" s="3">
         <v>8</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="6" t="s">
+      <c r="F23" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="8">
-        <v>60</v>
-      </c>
-      <c r="K23" s="9" t="s">
+      <c r="J23" s="9">
+        <v>60</v>
+      </c>
+      <c r="K23" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2737,17 +2740,17 @@
       <c r="F24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6" t="s">
+      <c r="G24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J24" s="8">
-        <v>60</v>
-      </c>
-      <c r="K24" s="9" t="s">
+      <c r="J24" s="9">
+        <v>60</v>
+      </c>
+      <c r="K24" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2771,15 +2774,15 @@
       <c r="F25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="8">
-        <v>60</v>
-      </c>
-      <c r="K25" s="9" t="s">
+      <c r="G25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="9">
+        <v>60</v>
+      </c>
+      <c r="K25" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2803,17 +2806,17 @@
       <c r="F26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6" t="s">
+      <c r="G26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J26" s="8">
-        <v>60</v>
-      </c>
-      <c r="K26" s="9" t="s">
+      <c r="J26" s="9">
+        <v>60</v>
+      </c>
+      <c r="K26" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2837,17 +2840,17 @@
       <c r="F27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6" t="s">
+      <c r="G27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J27" s="8">
-        <v>60</v>
-      </c>
-      <c r="K27" s="9" t="s">
+      <c r="J27" s="9">
+        <v>60</v>
+      </c>
+      <c r="K27" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2871,17 +2874,17 @@
       <c r="F28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6" t="s">
+      <c r="G28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J28" s="8">
-        <v>60</v>
-      </c>
-      <c r="K28" s="9" t="s">
+      <c r="J28" s="9">
+        <v>60</v>
+      </c>
+      <c r="K28" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2905,17 +2908,17 @@
       <c r="F29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6" t="s">
+      <c r="G29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="8">
-        <v>60</v>
-      </c>
-      <c r="K29" s="9" t="s">
+      <c r="J29" s="9">
+        <v>60</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2939,17 +2942,17 @@
       <c r="F30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6" t="s">
+      <c r="G30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="8">
-        <v>60</v>
-      </c>
-      <c r="K30" s="9" t="s">
+      <c r="J30" s="9">
+        <v>60</v>
+      </c>
+      <c r="K30" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2973,17 +2976,17 @@
       <c r="F31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6" t="s">
+      <c r="G31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J31" s="8">
-        <v>60</v>
-      </c>
-      <c r="K31" s="9" t="s">
+      <c r="J31" s="9">
+        <v>60</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3007,17 +3010,17 @@
       <c r="F32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6" t="s">
+      <c r="G32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J32" s="8">
-        <v>60</v>
-      </c>
-      <c r="K32" s="9" t="s">
+      <c r="J32" s="9">
+        <v>60</v>
+      </c>
+      <c r="K32" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3032,26 +3035,26 @@
       <c r="C33" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="11">
         <v>9</v>
       </c>
       <c r="E33" s="3">
         <v>8</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="6" t="s">
+      <c r="F33" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J33" s="8">
-        <v>60</v>
-      </c>
-      <c r="K33" s="9" t="s">
+      <c r="J33" s="9">
+        <v>60</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3075,17 +3078,17 @@
       <c r="F34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6" t="s">
+      <c r="G34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J34" s="8">
-        <v>60</v>
-      </c>
-      <c r="K34" s="9" t="s">
+      <c r="J34" s="9">
+        <v>60</v>
+      </c>
+      <c r="K34" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3109,15 +3112,15 @@
       <c r="F35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="8">
-        <v>60</v>
-      </c>
-      <c r="K35" s="9" t="s">
+      <c r="G35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="9">
+        <v>60</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3141,17 +3144,17 @@
       <c r="F36" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6" t="s">
+      <c r="G36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J36" s="8">
-        <v>60</v>
-      </c>
-      <c r="K36" s="9" t="s">
+      <c r="J36" s="9">
+        <v>60</v>
+      </c>
+      <c r="K36" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3175,17 +3178,17 @@
       <c r="F37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J37" s="8">
-        <v>60</v>
-      </c>
-      <c r="K37" s="9" t="s">
+      <c r="G37" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J37" s="9">
+        <v>60</v>
+      </c>
+      <c r="K37" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3209,17 +3212,17 @@
       <c r="F38" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6" t="s">
+      <c r="G38" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="8">
-        <v>60</v>
-      </c>
-      <c r="K38" s="9" t="s">
+      <c r="J38" s="9">
+        <v>60</v>
+      </c>
+      <c r="K38" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3243,17 +3246,17 @@
       <c r="F39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6" t="s">
+      <c r="G39" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J39" s="8">
-        <v>60</v>
-      </c>
-      <c r="K39" s="9" t="s">
+      <c r="J39" s="9">
+        <v>60</v>
+      </c>
+      <c r="K39" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3277,17 +3280,17 @@
       <c r="F40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6" t="s">
+      <c r="G40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J40" s="8">
-        <v>60</v>
-      </c>
-      <c r="K40" s="9" t="s">
+      <c r="J40" s="9">
+        <v>60</v>
+      </c>
+      <c r="K40" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3311,17 +3314,17 @@
       <c r="F41" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6" t="s">
+      <c r="G41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J41" s="8">
-        <v>60</v>
-      </c>
-      <c r="K41" s="9" t="s">
+      <c r="J41" s="9">
+        <v>60</v>
+      </c>
+      <c r="K41" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3345,17 +3348,17 @@
       <c r="F42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6" t="s">
+      <c r="G42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J42" s="8">
-        <v>60</v>
-      </c>
-      <c r="K42" s="9" t="s">
+      <c r="J42" s="9">
+        <v>60</v>
+      </c>
+      <c r="K42" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3370,26 +3373,26 @@
       <c r="C43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="11">
         <v>9</v>
       </c>
       <c r="E43" s="3">
         <v>8</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H43" s="11"/>
-      <c r="I43" s="6" t="s">
+      <c r="F43" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H43" s="12"/>
+      <c r="I43" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J43" s="8">
-        <v>60</v>
-      </c>
-      <c r="K43" s="9" t="s">
+      <c r="J43" s="9">
+        <v>60</v>
+      </c>
+      <c r="K43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3413,17 +3416,17 @@
       <c r="F44" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6" t="s">
+      <c r="G44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J44" s="8">
-        <v>60</v>
-      </c>
-      <c r="K44" s="9" t="s">
+      <c r="J44" s="9">
+        <v>60</v>
+      </c>
+      <c r="K44" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3447,15 +3450,15 @@
       <c r="F45" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="8">
-        <v>60</v>
-      </c>
-      <c r="K45" s="9" t="s">
+      <c r="G45" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="9">
+        <v>60</v>
+      </c>
+      <c r="K45" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3479,17 +3482,17 @@
       <c r="F46" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6" t="s">
+      <c r="G46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="8">
-        <v>60</v>
-      </c>
-      <c r="K46" s="9" t="s">
+      <c r="J46" s="9">
+        <v>60</v>
+      </c>
+      <c r="K46" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3513,17 +3516,17 @@
       <c r="F47" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6" t="s">
+      <c r="G47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J47" s="8">
-        <v>60</v>
-      </c>
-      <c r="K47" s="9" t="s">
+      <c r="J47" s="9">
+        <v>60</v>
+      </c>
+      <c r="K47" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3547,17 +3550,17 @@
       <c r="F48" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6" t="s">
+      <c r="G48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J48" s="8">
-        <v>60</v>
-      </c>
-      <c r="K48" s="9" t="s">
+      <c r="J48" s="9">
+        <v>60</v>
+      </c>
+      <c r="K48" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3581,17 +3584,17 @@
       <c r="F49" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6" t="s">
+      <c r="G49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J49" s="8">
-        <v>60</v>
-      </c>
-      <c r="K49" s="9" t="s">
+      <c r="J49" s="9">
+        <v>60</v>
+      </c>
+      <c r="K49" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3615,17 +3618,17 @@
       <c r="F50" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6" t="s">
+      <c r="G50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J50" s="8">
-        <v>60</v>
-      </c>
-      <c r="K50" s="9" t="s">
+      <c r="J50" s="9">
+        <v>60</v>
+      </c>
+      <c r="K50" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3649,17 +3652,17 @@
       <c r="F51" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6" t="s">
+      <c r="G51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J51" s="8">
-        <v>60</v>
-      </c>
-      <c r="K51" s="9" t="s">
+      <c r="J51" s="9">
+        <v>60</v>
+      </c>
+      <c r="K51" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3683,17 +3686,17 @@
       <c r="F52" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6" t="s">
+      <c r="G52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J52" s="8">
-        <v>60</v>
-      </c>
-      <c r="K52" s="9" t="s">
+      <c r="J52" s="9">
+        <v>60</v>
+      </c>
+      <c r="K52" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3708,26 +3711,26 @@
       <c r="C53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="11">
         <v>9</v>
       </c>
       <c r="E53" s="3">
         <v>8</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H53" s="11"/>
-      <c r="I53" s="6" t="s">
+      <c r="F53" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="12"/>
+      <c r="I53" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="J53" s="8">
-        <v>60</v>
-      </c>
-      <c r="K53" s="9" t="s">
+      <c r="J53" s="9">
+        <v>60</v>
+      </c>
+      <c r="K53" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3751,17 +3754,17 @@
       <c r="F54" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6" t="s">
+      <c r="G54" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J54" s="8">
-        <v>60</v>
-      </c>
-      <c r="K54" s="9" t="s">
+      <c r="J54" s="9">
+        <v>60</v>
+      </c>
+      <c r="K54" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3785,15 +3788,15 @@
       <c r="F55" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="8">
-        <v>60</v>
-      </c>
-      <c r="K55" s="9" t="s">
+      <c r="G55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="9">
+        <v>60</v>
+      </c>
+      <c r="K55" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3817,17 +3820,17 @@
       <c r="F56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6" t="s">
+      <c r="G56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J56" s="8">
-        <v>60</v>
-      </c>
-      <c r="K56" s="9" t="s">
+      <c r="J56" s="9">
+        <v>60</v>
+      </c>
+      <c r="K56" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3851,17 +3854,17 @@
       <c r="F57" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6" t="s">
+      <c r="G57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="8">
-        <v>60</v>
-      </c>
-      <c r="K57" s="9" t="s">
+      <c r="J57" s="9">
+        <v>60</v>
+      </c>
+      <c r="K57" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3885,17 +3888,17 @@
       <c r="F58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6" t="s">
+      <c r="G58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J58" s="8">
-        <v>60</v>
-      </c>
-      <c r="K58" s="9" t="s">
+      <c r="J58" s="9">
+        <v>60</v>
+      </c>
+      <c r="K58" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3919,17 +3922,17 @@
       <c r="F59" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6" t="s">
+      <c r="G59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J59" s="8">
-        <v>60</v>
-      </c>
-      <c r="K59" s="9" t="s">
+      <c r="J59" s="9">
+        <v>60</v>
+      </c>
+      <c r="K59" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3953,17 +3956,17 @@
       <c r="F60" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6" t="s">
+      <c r="G60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J60" s="8">
-        <v>60</v>
-      </c>
-      <c r="K60" s="9" t="s">
+      <c r="J60" s="9">
+        <v>60</v>
+      </c>
+      <c r="K60" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3987,17 +3990,17 @@
       <c r="F61" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6" t="s">
+      <c r="G61" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J61" s="8">
-        <v>60</v>
-      </c>
-      <c r="K61" s="9" t="s">
+      <c r="J61" s="9">
+        <v>60</v>
+      </c>
+      <c r="K61" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4021,17 +4024,17 @@
       <c r="F62" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6" t="s">
+      <c r="G62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J62" s="8">
-        <v>60</v>
-      </c>
-      <c r="K62" s="9" t="s">
+      <c r="J62" s="9">
+        <v>60</v>
+      </c>
+      <c r="K62" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4046,26 +4049,26 @@
       <c r="C63" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="11">
         <v>9</v>
       </c>
       <c r="E63" s="3">
         <v>8</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H63" s="11"/>
-      <c r="I63" s="6" t="s">
+      <c r="F63" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="12"/>
+      <c r="I63" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="J63" s="8">
-        <v>60</v>
-      </c>
-      <c r="K63" s="9" t="s">
+      <c r="J63" s="9">
+        <v>60</v>
+      </c>
+      <c r="K63" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4089,17 +4092,17 @@
       <c r="F64" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6" t="s">
+      <c r="G64" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="J64" s="8">
-        <v>60</v>
-      </c>
-      <c r="K64" s="9" t="s">
+      <c r="J64" s="9">
+        <v>60</v>
+      </c>
+      <c r="K64" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4123,15 +4126,15 @@
       <c r="F65" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="8">
-        <v>60</v>
-      </c>
-      <c r="K65" s="9" t="s">
+      <c r="G65" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="9">
+        <v>60</v>
+      </c>
+      <c r="K65" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4155,17 +4158,17 @@
       <c r="F66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6" t="s">
+      <c r="G66" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J66" s="8">
-        <v>60</v>
-      </c>
-      <c r="K66" s="9" t="s">
+      <c r="J66" s="9">
+        <v>60</v>
+      </c>
+      <c r="K66" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4189,17 +4192,17 @@
       <c r="F67" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G67" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6" t="s">
+      <c r="G67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="J67" s="8">
-        <v>60</v>
-      </c>
-      <c r="K67" s="9" t="s">
+      <c r="J67" s="9">
+        <v>60</v>
+      </c>
+      <c r="K67" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4223,17 +4226,17 @@
       <c r="F68" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6" t="s">
+      <c r="G68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J68" s="8">
-        <v>60</v>
-      </c>
-      <c r="K68" s="9" t="s">
+      <c r="J68" s="9">
+        <v>60</v>
+      </c>
+      <c r="K68" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4257,17 +4260,17 @@
       <c r="F69" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G69" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6" t="s">
+      <c r="G69" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J69" s="8">
-        <v>60</v>
-      </c>
-      <c r="K69" s="9" t="s">
+      <c r="J69" s="9">
+        <v>60</v>
+      </c>
+      <c r="K69" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4291,17 +4294,17 @@
       <c r="F70" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6" t="s">
+      <c r="G70" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="J70" s="8">
-        <v>60</v>
-      </c>
-      <c r="K70" s="9" t="s">
+      <c r="J70" s="9">
+        <v>60</v>
+      </c>
+      <c r="K70" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4325,17 +4328,17 @@
       <c r="F71" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6" t="s">
+      <c r="G71" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J71" s="8">
-        <v>60</v>
-      </c>
-      <c r="K71" s="9" t="s">
+      <c r="J71" s="9">
+        <v>60</v>
+      </c>
+      <c r="K71" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4359,17 +4362,17 @@
       <c r="F72" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G72" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6" t="s">
+      <c r="G72" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J72" s="8">
-        <v>60</v>
-      </c>
-      <c r="K72" s="9" t="s">
+      <c r="J72" s="9">
+        <v>60</v>
+      </c>
+      <c r="K72" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4384,26 +4387,26 @@
       <c r="C73" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="11">
         <v>9</v>
       </c>
       <c r="E73" s="3">
         <v>8</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H73" s="11"/>
-      <c r="I73" s="6" t="s">
+      <c r="F73" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" s="12"/>
+      <c r="I73" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J73" s="8">
-        <v>60</v>
-      </c>
-      <c r="K73" s="9" t="s">
+      <c r="J73" s="9">
+        <v>60</v>
+      </c>
+      <c r="K73" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4427,17 +4430,17 @@
       <c r="F74" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G74" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6" t="s">
+      <c r="G74" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J74" s="8">
-        <v>60</v>
-      </c>
-      <c r="K74" s="9" t="s">
+      <c r="J74" s="9">
+        <v>60</v>
+      </c>
+      <c r="K74" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4461,15 +4464,15 @@
       <c r="F75" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G75" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="8">
-        <v>60</v>
-      </c>
-      <c r="K75" s="9" t="s">
+      <c r="G75" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="9">
+        <v>60</v>
+      </c>
+      <c r="K75" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4493,17 +4496,17 @@
       <c r="F76" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G76" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6" t="s">
+      <c r="G76" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J76" s="8">
-        <v>60</v>
-      </c>
-      <c r="K76" s="9" t="s">
+      <c r="J76" s="9">
+        <v>60</v>
+      </c>
+      <c r="K76" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4527,17 +4530,17 @@
       <c r="F77" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6" t="s">
+      <c r="G77" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J77" s="8">
-        <v>60</v>
-      </c>
-      <c r="K77" s="9" t="s">
+      <c r="J77" s="9">
+        <v>60</v>
+      </c>
+      <c r="K77" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4561,17 +4564,17 @@
       <c r="F78" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6" t="s">
+      <c r="G78" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J78" s="8">
-        <v>60</v>
-      </c>
-      <c r="K78" s="9" t="s">
+      <c r="J78" s="9">
+        <v>60</v>
+      </c>
+      <c r="K78" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4595,17 +4598,17 @@
       <c r="F79" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G79" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6" t="s">
+      <c r="G79" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J79" s="8">
-        <v>60</v>
-      </c>
-      <c r="K79" s="9" t="s">
+      <c r="J79" s="9">
+        <v>60</v>
+      </c>
+      <c r="K79" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4629,17 +4632,17 @@
       <c r="F80" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G80" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6" t="s">
+      <c r="G80" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J80" s="8">
-        <v>60</v>
-      </c>
-      <c r="K80" s="9" t="s">
+      <c r="J80" s="9">
+        <v>60</v>
+      </c>
+      <c r="K80" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4663,17 +4666,17 @@
       <c r="F81" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6" t="s">
+      <c r="G81" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J81" s="8">
-        <v>60</v>
-      </c>
-      <c r="K81" s="9" t="s">
+      <c r="J81" s="9">
+        <v>60</v>
+      </c>
+      <c r="K81" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4697,17 +4700,17 @@
       <c r="F82" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6" t="s">
+      <c r="G82" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="J82" s="8">
-        <v>60</v>
-      </c>
-      <c r="K82" s="9" t="s">
+      <c r="J82" s="9">
+        <v>60</v>
+      </c>
+      <c r="K82" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4722,26 +4725,26 @@
       <c r="C83" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="11">
         <v>9</v>
       </c>
       <c r="E83" s="3">
         <v>8</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H83" s="11"/>
-      <c r="I83" s="6" t="s">
+      <c r="F83" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" s="12"/>
+      <c r="I83" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J83" s="8">
-        <v>60</v>
-      </c>
-      <c r="K83" s="9" t="s">
+      <c r="J83" s="9">
+        <v>60</v>
+      </c>
+      <c r="K83" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4765,17 +4768,17 @@
       <c r="F84" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G84" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6" t="s">
+      <c r="G84" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="J84" s="8">
-        <v>60</v>
-      </c>
-      <c r="K84" s="9" t="s">
+      <c r="J84" s="9">
+        <v>60</v>
+      </c>
+      <c r="K84" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4799,15 +4802,15 @@
       <c r="F85" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="8">
-        <v>60</v>
-      </c>
-      <c r="K85" s="9" t="s">
+      <c r="G85" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="9">
+        <v>60</v>
+      </c>
+      <c r="K85" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4831,17 +4834,17 @@
       <c r="F86" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6" t="s">
+      <c r="G86" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J86" s="8">
-        <v>60</v>
-      </c>
-      <c r="K86" s="9" t="s">
+      <c r="J86" s="9">
+        <v>60</v>
+      </c>
+      <c r="K86" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4865,17 +4868,17 @@
       <c r="F87" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6" t="s">
+      <c r="G87" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J87" s="8">
-        <v>60</v>
-      </c>
-      <c r="K87" s="9" t="s">
+      <c r="J87" s="9">
+        <v>60</v>
+      </c>
+      <c r="K87" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4899,17 +4902,17 @@
       <c r="F88" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G88" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6" t="s">
+      <c r="G88" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J88" s="8">
-        <v>60</v>
-      </c>
-      <c r="K88" s="9" t="s">
+      <c r="J88" s="9">
+        <v>60</v>
+      </c>
+      <c r="K88" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4933,17 +4936,17 @@
       <c r="F89" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G89" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6" t="s">
+      <c r="G89" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J89" s="8">
-        <v>60</v>
-      </c>
-      <c r="K89" s="9" t="s">
+      <c r="J89" s="9">
+        <v>60</v>
+      </c>
+      <c r="K89" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4967,17 +4970,17 @@
       <c r="F90" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G90" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6" t="s">
+      <c r="G90" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J90" s="8">
-        <v>60</v>
-      </c>
-      <c r="K90" s="9" t="s">
+      <c r="J90" s="9">
+        <v>60</v>
+      </c>
+      <c r="K90" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5001,17 +5004,17 @@
       <c r="F91" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6" t="s">
+      <c r="G91" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J91" s="8">
-        <v>60</v>
-      </c>
-      <c r="K91" s="9" t="s">
+      <c r="J91" s="9">
+        <v>60</v>
+      </c>
+      <c r="K91" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5035,17 +5038,17 @@
       <c r="F92" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6" t="s">
+      <c r="G92" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J92" s="8">
-        <v>60</v>
-      </c>
-      <c r="K92" s="9" t="s">
+      <c r="J92" s="9">
+        <v>60</v>
+      </c>
+      <c r="K92" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5060,26 +5063,26 @@
       <c r="C93" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D93" s="10">
+      <c r="D93" s="11">
         <v>9</v>
       </c>
       <c r="E93" s="3">
         <v>8</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H93" s="11"/>
-      <c r="I93" s="6" t="s">
+      <c r="F93" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="12"/>
+      <c r="I93" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J93" s="8">
-        <v>60</v>
-      </c>
-      <c r="K93" s="9" t="s">
+      <c r="J93" s="9">
+        <v>60</v>
+      </c>
+      <c r="K93" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5103,17 +5106,17 @@
       <c r="F94" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6" t="s">
+      <c r="G94" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J94" s="8">
-        <v>60</v>
-      </c>
-      <c r="K94" s="9" t="s">
+      <c r="J94" s="9">
+        <v>60</v>
+      </c>
+      <c r="K94" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5137,15 +5140,15 @@
       <c r="F95" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G95" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="8">
-        <v>60</v>
-      </c>
-      <c r="K95" s="9" t="s">
+      <c r="G95" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="9">
+        <v>60</v>
+      </c>
+      <c r="K95" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5169,17 +5172,17 @@
       <c r="F96" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G96" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6" t="s">
+      <c r="G96" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="J96" s="8">
-        <v>60</v>
-      </c>
-      <c r="K96" s="9" t="s">
+      <c r="J96" s="9">
+        <v>60</v>
+      </c>
+      <c r="K96" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5203,17 +5206,17 @@
       <c r="F97" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G97" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6" t="s">
+      <c r="G97" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="J97" s="8">
-        <v>60</v>
-      </c>
-      <c r="K97" s="9" t="s">
+      <c r="J97" s="9">
+        <v>60</v>
+      </c>
+      <c r="K97" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5237,17 +5240,17 @@
       <c r="F98" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G98" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6" t="s">
+      <c r="G98" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="J98" s="8">
-        <v>60</v>
-      </c>
-      <c r="K98" s="9" t="s">
+      <c r="J98" s="9">
+        <v>60</v>
+      </c>
+      <c r="K98" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5271,17 +5274,17 @@
       <c r="F99" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G99" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6" t="s">
+      <c r="G99" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="J99" s="8">
-        <v>60</v>
-      </c>
-      <c r="K99" s="9" t="s">
+      <c r="J99" s="9">
+        <v>60</v>
+      </c>
+      <c r="K99" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5305,17 +5308,17 @@
       <c r="F100" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G100" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6" t="s">
+      <c r="G100" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J100" s="8">
-        <v>60</v>
-      </c>
-      <c r="K100" s="9" t="s">
+      <c r="J100" s="9">
+        <v>60</v>
+      </c>
+      <c r="K100" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5339,17 +5342,17 @@
       <c r="F101" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6" t="s">
+      <c r="G101" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="J101" s="8">
-        <v>60</v>
-      </c>
-      <c r="K101" s="9" t="s">
+      <c r="J101" s="9">
+        <v>60</v>
+      </c>
+      <c r="K101" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5373,17 +5376,17 @@
       <c r="F102" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G102" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6" t="s">
+      <c r="G102" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J102" s="8">
-        <v>60</v>
-      </c>
-      <c r="K102" s="9" t="s">
+      <c r="J102" s="9">
+        <v>60</v>
+      </c>
+      <c r="K102" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5398,26 +5401,26 @@
       <c r="C103" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D103" s="10">
+      <c r="D103" s="11">
         <v>9</v>
       </c>
       <c r="E103" s="3">
         <v>8</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H103" s="11"/>
-      <c r="I103" s="6" t="s">
+      <c r="F103" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" s="12"/>
+      <c r="I103" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J103" s="8">
-        <v>60</v>
-      </c>
-      <c r="K103" s="9" t="s">
+      <c r="J103" s="9">
+        <v>60</v>
+      </c>
+      <c r="K103" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5441,17 +5444,17 @@
       <c r="F104" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G104" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6" t="s">
+      <c r="G104" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="J104" s="8">
-        <v>60</v>
-      </c>
-      <c r="K104" s="9" t="s">
+      <c r="J104" s="9">
+        <v>60</v>
+      </c>
+      <c r="K104" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5475,15 +5478,15 @@
       <c r="F105" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="8">
-        <v>60</v>
-      </c>
-      <c r="K105" s="9" t="s">
+      <c r="G105" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="9">
+        <v>60</v>
+      </c>
+      <c r="K105" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5507,17 +5510,17 @@
       <c r="F106" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G106" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6" t="s">
+      <c r="G106" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J106" s="8">
-        <v>60</v>
-      </c>
-      <c r="K106" s="9" t="s">
+      <c r="J106" s="9">
+        <v>60</v>
+      </c>
+      <c r="K106" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5541,17 +5544,17 @@
       <c r="F107" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G107" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6" t="s">
+      <c r="G107" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="7"/>
+      <c r="I107" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J107" s="8">
-        <v>60</v>
-      </c>
-      <c r="K107" s="9" t="s">
+      <c r="J107" s="9">
+        <v>60</v>
+      </c>
+      <c r="K107" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5575,17 +5578,17 @@
       <c r="F108" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G108" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6" t="s">
+      <c r="G108" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J108" s="8">
-        <v>60</v>
-      </c>
-      <c r="K108" s="9" t="s">
+      <c r="J108" s="9">
+        <v>60</v>
+      </c>
+      <c r="K108" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5609,17 +5612,17 @@
       <c r="F109" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G109" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6" t="s">
+      <c r="G109" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="J109" s="8">
-        <v>60</v>
-      </c>
-      <c r="K109" s="9" t="s">
+      <c r="J109" s="9">
+        <v>60</v>
+      </c>
+      <c r="K109" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5643,17 +5646,17 @@
       <c r="F110" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6" t="s">
+      <c r="G110" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" s="7"/>
+      <c r="I110" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J110" s="8">
-        <v>60</v>
-      </c>
-      <c r="K110" s="9" t="s">
+      <c r="J110" s="9">
+        <v>60</v>
+      </c>
+      <c r="K110" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5677,17 +5680,17 @@
       <c r="F111" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G111" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6" t="s">
+      <c r="G111" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="J111" s="8">
-        <v>60</v>
-      </c>
-      <c r="K111" s="9" t="s">
+      <c r="J111" s="9">
+        <v>60</v>
+      </c>
+      <c r="K111" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5711,17 +5714,17 @@
       <c r="F112" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G112" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6" t="s">
+      <c r="G112" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J112" s="8">
-        <v>60</v>
-      </c>
-      <c r="K112" s="9" t="s">
+      <c r="J112" s="9">
+        <v>60</v>
+      </c>
+      <c r="K112" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5736,26 +5739,26 @@
       <c r="C113" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D113" s="10">
+      <c r="D113" s="11">
         <v>9</v>
       </c>
       <c r="E113" s="3">
         <v>8</v>
       </c>
-      <c r="F113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H113" s="11"/>
-      <c r="I113" s="6" t="s">
+      <c r="F113" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" s="12"/>
+      <c r="I113" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J113" s="8">
-        <v>60</v>
-      </c>
-      <c r="K113" s="9" t="s">
+      <c r="J113" s="9">
+        <v>60</v>
+      </c>
+      <c r="K113" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5779,17 +5782,17 @@
       <c r="F114" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G114" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6" t="s">
+      <c r="G114" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="J114" s="8">
-        <v>60</v>
-      </c>
-      <c r="K114" s="9" t="s">
+      <c r="J114" s="9">
+        <v>60</v>
+      </c>
+      <c r="K114" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5813,15 +5816,15 @@
       <c r="F115" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G115" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="8">
-        <v>60</v>
-      </c>
-      <c r="K115" s="9" t="s">
+      <c r="G115" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="9">
+        <v>60</v>
+      </c>
+      <c r="K115" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5845,17 +5848,17 @@
       <c r="F116" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G116" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6" t="s">
+      <c r="G116" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J116" s="8">
-        <v>60</v>
-      </c>
-      <c r="K116" s="9" t="s">
+      <c r="J116" s="9">
+        <v>60</v>
+      </c>
+      <c r="K116" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5879,17 +5882,17 @@
       <c r="F117" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G117" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6" t="s">
+      <c r="G117" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J117" s="8">
-        <v>60</v>
-      </c>
-      <c r="K117" s="9" t="s">
+      <c r="J117" s="9">
+        <v>60</v>
+      </c>
+      <c r="K117" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5913,17 +5916,17 @@
       <c r="F118" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G118" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6" t="s">
+      <c r="G118" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J118" s="8">
-        <v>60</v>
-      </c>
-      <c r="K118" s="9" t="s">
+      <c r="J118" s="9">
+        <v>60</v>
+      </c>
+      <c r="K118" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5947,17 +5950,17 @@
       <c r="F119" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6" t="s">
+      <c r="G119" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="J119" s="8">
-        <v>60</v>
-      </c>
-      <c r="K119" s="9" t="s">
+      <c r="J119" s="9">
+        <v>60</v>
+      </c>
+      <c r="K119" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5981,17 +5984,17 @@
       <c r="F120" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G120" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6" t="s">
+      <c r="G120" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J120" s="8">
-        <v>60</v>
-      </c>
-      <c r="K120" s="9" t="s">
+      <c r="J120" s="9">
+        <v>60</v>
+      </c>
+      <c r="K120" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6015,17 +6018,17 @@
       <c r="F121" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G121" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6" t="s">
+      <c r="G121" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J121" s="8">
-        <v>60</v>
-      </c>
-      <c r="K121" s="9" t="s">
+      <c r="J121" s="9">
+        <v>60</v>
+      </c>
+      <c r="K121" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6049,17 +6052,17 @@
       <c r="F122" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G122" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6" t="s">
+      <c r="G122" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="J122" s="8">
-        <v>60</v>
-      </c>
-      <c r="K122" s="9" t="s">
+      <c r="J122" s="9">
+        <v>60</v>
+      </c>
+      <c r="K122" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6074,26 +6077,26 @@
       <c r="C123" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D123" s="10">
+      <c r="D123" s="11">
         <v>9</v>
       </c>
       <c r="E123" s="3">
         <v>8</v>
       </c>
-      <c r="F123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G123" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H123" s="11"/>
-      <c r="I123" s="6" t="s">
+      <c r="F123" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" s="12"/>
+      <c r="I123" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="J123" s="8">
-        <v>60</v>
-      </c>
-      <c r="K123" s="9" t="s">
+      <c r="J123" s="9">
+        <v>60</v>
+      </c>
+      <c r="K123" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6117,17 +6120,17 @@
       <c r="F124" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G124" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6" t="s">
+      <c r="G124" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" s="7"/>
+      <c r="I124" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J124" s="8">
-        <v>60</v>
-      </c>
-      <c r="K124" s="9" t="s">
+      <c r="J124" s="9">
+        <v>60</v>
+      </c>
+      <c r="K124" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6151,15 +6154,15 @@
       <c r="F125" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G125" s="6" t="s">
+      <c r="G125" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="8">
-        <v>60</v>
-      </c>
-      <c r="K125" s="9" t="s">
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="9">
+        <v>60</v>
+      </c>
+      <c r="K125" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6183,17 +6186,17 @@
       <c r="F126" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G126" s="6" t="s">
+      <c r="G126" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6" t="s">
+      <c r="H126" s="7"/>
+      <c r="I126" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="J126" s="8">
-        <v>60</v>
-      </c>
-      <c r="K126" s="9" t="s">
+      <c r="J126" s="9">
+        <v>60</v>
+      </c>
+      <c r="K126" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6217,17 +6220,17 @@
       <c r="F127" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G127" s="6" t="s">
+      <c r="G127" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6" t="s">
+      <c r="H127" s="7"/>
+      <c r="I127" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J127" s="8">
-        <v>60</v>
-      </c>
-      <c r="K127" s="9" t="s">
+      <c r="J127" s="9">
+        <v>60</v>
+      </c>
+      <c r="K127" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6251,17 +6254,17 @@
       <c r="F128" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="6" t="s">
+      <c r="G128" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6" t="s">
+      <c r="H128" s="7"/>
+      <c r="I128" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J128" s="8">
-        <v>60</v>
-      </c>
-      <c r="K128" s="9" t="s">
+      <c r="J128" s="9">
+        <v>60</v>
+      </c>
+      <c r="K128" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6285,17 +6288,17 @@
       <c r="F129" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="G129" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6" t="s">
+      <c r="H129" s="7"/>
+      <c r="I129" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J129" s="8">
-        <v>60</v>
-      </c>
-      <c r="K129" s="9" t="s">
+      <c r="J129" s="9">
+        <v>60</v>
+      </c>
+      <c r="K129" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6319,17 +6322,17 @@
       <c r="F130" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G130" s="6" t="s">
+      <c r="G130" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6" t="s">
+      <c r="H130" s="7"/>
+      <c r="I130" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="J130" s="8">
-        <v>60</v>
-      </c>
-      <c r="K130" s="9" t="s">
+      <c r="J130" s="9">
+        <v>60</v>
+      </c>
+      <c r="K130" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6353,17 +6356,17 @@
       <c r="F131" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G131" s="6" t="s">
+      <c r="G131" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6" t="s">
+      <c r="H131" s="7"/>
+      <c r="I131" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J131" s="8">
-        <v>60</v>
-      </c>
-      <c r="K131" s="9" t="s">
+      <c r="J131" s="9">
+        <v>60</v>
+      </c>
+      <c r="K131" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6387,17 +6390,17 @@
       <c r="F132" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="6" t="s">
+      <c r="G132" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6" t="s">
+      <c r="H132" s="7"/>
+      <c r="I132" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="J132" s="8">
-        <v>60</v>
-      </c>
-      <c r="K132" s="9" t="s">
+      <c r="J132" s="9">
+        <v>60</v>
+      </c>
+      <c r="K132" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6412,26 +6415,26 @@
       <c r="C133" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D133" s="10">
+      <c r="D133" s="11">
         <v>9</v>
       </c>
       <c r="E133" s="3">
         <v>8</v>
       </c>
-      <c r="F133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G133" s="11" t="s">
+      <c r="F133" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="H133" s="11"/>
-      <c r="I133" s="6" t="s">
+      <c r="H133" s="12"/>
+      <c r="I133" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="J133" s="8">
-        <v>60</v>
-      </c>
-      <c r="K133" s="9" t="s">
+      <c r="J133" s="9">
+        <v>60</v>
+      </c>
+      <c r="K133" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6455,17 +6458,17 @@
       <c r="F134" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G134" s="6" t="s">
+      <c r="G134" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6" t="s">
+      <c r="H134" s="7"/>
+      <c r="I134" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="J134" s="8">
-        <v>60</v>
-      </c>
-      <c r="K134" s="9" t="s">
+      <c r="J134" s="9">
+        <v>60</v>
+      </c>
+      <c r="K134" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6489,15 +6492,15 @@
       <c r="F135" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G135" s="6" t="s">
+      <c r="G135" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="8">
-        <v>60</v>
-      </c>
-      <c r="K135" s="9" t="s">
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="9">
+        <v>60</v>
+      </c>
+      <c r="K135" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6521,17 +6524,17 @@
       <c r="F136" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G136" s="6" t="s">
+      <c r="G136" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6" t="s">
+      <c r="H136" s="7"/>
+      <c r="I136" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="J136" s="8">
-        <v>60</v>
-      </c>
-      <c r="K136" s="9" t="s">
+      <c r="J136" s="9">
+        <v>60</v>
+      </c>
+      <c r="K136" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6555,17 +6558,17 @@
       <c r="F137" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G137" s="6" t="s">
+      <c r="G137" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6" t="s">
+      <c r="H137" s="7"/>
+      <c r="I137" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J137" s="8">
-        <v>60</v>
-      </c>
-      <c r="K137" s="9" t="s">
+      <c r="J137" s="9">
+        <v>60</v>
+      </c>
+      <c r="K137" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6589,17 +6592,17 @@
       <c r="F138" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G138" s="6" t="s">
+      <c r="G138" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6" t="s">
+      <c r="H138" s="7"/>
+      <c r="I138" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="J138" s="8">
-        <v>60</v>
-      </c>
-      <c r="K138" s="9" t="s">
+      <c r="J138" s="9">
+        <v>60</v>
+      </c>
+      <c r="K138" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6623,17 +6626,17 @@
       <c r="F139" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G139" s="6" t="s">
+      <c r="G139" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6" t="s">
+      <c r="H139" s="7"/>
+      <c r="I139" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="J139" s="8">
-        <v>60</v>
-      </c>
-      <c r="K139" s="9" t="s">
+      <c r="J139" s="9">
+        <v>60</v>
+      </c>
+      <c r="K139" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6657,17 +6660,17 @@
       <c r="F140" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G140" s="6" t="s">
+      <c r="G140" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6" t="s">
+      <c r="H140" s="7"/>
+      <c r="I140" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="J140" s="8">
-        <v>60</v>
-      </c>
-      <c r="K140" s="9" t="s">
+      <c r="J140" s="9">
+        <v>60</v>
+      </c>
+      <c r="K140" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6691,17 +6694,17 @@
       <c r="F141" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G141" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6" t="s">
+      <c r="H141" s="7"/>
+      <c r="I141" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J141" s="8">
-        <v>60</v>
-      </c>
-      <c r="K141" s="9" t="s">
+      <c r="J141" s="9">
+        <v>60</v>
+      </c>
+      <c r="K141" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6725,17 +6728,17 @@
       <c r="F142" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G142" s="6" t="s">
+      <c r="G142" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6" t="s">
+      <c r="H142" s="7"/>
+      <c r="I142" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J142" s="8">
-        <v>60</v>
-      </c>
-      <c r="K142" s="9" t="s">
+      <c r="J142" s="9">
+        <v>60</v>
+      </c>
+      <c r="K142" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6750,26 +6753,26 @@
       <c r="C143" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D143" s="10">
+      <c r="D143" s="11">
         <v>9</v>
       </c>
       <c r="E143" s="3">
         <v>8</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="11" t="s">
+      <c r="F143" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="H143" s="11"/>
-      <c r="I143" s="6" t="s">
+      <c r="H143" s="12"/>
+      <c r="I143" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="J143" s="8">
-        <v>60</v>
-      </c>
-      <c r="K143" s="9" t="s">
+      <c r="J143" s="9">
+        <v>60</v>
+      </c>
+      <c r="K143" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6793,17 +6796,17 @@
       <c r="F144" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G144" s="6" t="s">
+      <c r="G144" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6" t="s">
+      <c r="H144" s="7"/>
+      <c r="I144" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="J144" s="8">
-        <v>60</v>
-      </c>
-      <c r="K144" s="9" t="s">
+      <c r="J144" s="9">
+        <v>60</v>
+      </c>
+      <c r="K144" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6821,19 +6824,19 @@
       <c r="D145" s="3">
         <v>1</v>
       </c>
-      <c r="E145" s="12"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G145" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H145" s="12"/>
-      <c r="I145" s="12"/>
-      <c r="J145" s="8">
-        <v>60</v>
-      </c>
-      <c r="K145" s="9" t="s">
+      <c r="H145" s="13"/>
+      <c r="I145" s="13"/>
+      <c r="J145" s="9">
+        <v>60</v>
+      </c>
+      <c r="K145" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6851,19 +6854,19 @@
       <c r="D146" s="3">
         <v>2</v>
       </c>
-      <c r="E146" s="12"/>
+      <c r="E146" s="13"/>
       <c r="F146" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G146" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H146" s="12"/>
-      <c r="I146" s="12"/>
-      <c r="J146" s="8">
-        <v>60</v>
-      </c>
-      <c r="K146" s="9" t="s">
+      <c r="H146" s="13"/>
+      <c r="I146" s="13"/>
+      <c r="J146" s="9">
+        <v>60</v>
+      </c>
+      <c r="K146" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6881,19 +6884,19 @@
       <c r="D147" s="3">
         <v>3</v>
       </c>
-      <c r="E147" s="12"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G147" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H147" s="12"/>
-      <c r="I147" s="12"/>
-      <c r="J147" s="8">
-        <v>60</v>
-      </c>
-      <c r="K147" s="9" t="s">
+      <c r="H147" s="13"/>
+      <c r="I147" s="13"/>
+      <c r="J147" s="9">
+        <v>60</v>
+      </c>
+      <c r="K147" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6911,19 +6914,19 @@
       <c r="D148" s="3">
         <v>4</v>
       </c>
-      <c r="E148" s="12"/>
+      <c r="E148" s="13"/>
       <c r="F148" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G148" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H148" s="12"/>
-      <c r="I148" s="12"/>
-      <c r="J148" s="8">
-        <v>60</v>
-      </c>
-      <c r="K148" s="9" t="s">
+      <c r="H148" s="13"/>
+      <c r="I148" s="13"/>
+      <c r="J148" s="9">
+        <v>60</v>
+      </c>
+      <c r="K148" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6941,19 +6944,19 @@
       <c r="D149" s="3">
         <v>5</v>
       </c>
-      <c r="E149" s="12"/>
+      <c r="E149" s="13"/>
       <c r="F149" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="G149" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H149" s="12"/>
-      <c r="I149" s="12"/>
-      <c r="J149" s="8">
-        <v>60</v>
-      </c>
-      <c r="K149" s="9" t="s">
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="9">
+        <v>60</v>
+      </c>
+      <c r="K149" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6971,19 +6974,19 @@
       <c r="D150" s="3">
         <v>6</v>
       </c>
-      <c r="E150" s="12"/>
+      <c r="E150" s="13"/>
       <c r="F150" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G150" s="6" t="s">
+      <c r="G150" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H150" s="12"/>
-      <c r="I150" s="12"/>
-      <c r="J150" s="8">
-        <v>60</v>
-      </c>
-      <c r="K150" s="9" t="s">
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="9">
+        <v>60</v>
+      </c>
+      <c r="K150" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7001,19 +7004,19 @@
       <c r="D151" s="3">
         <v>7</v>
       </c>
-      <c r="E151" s="12"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G151" s="6" t="s">
+      <c r="G151" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H151" s="12"/>
-      <c r="I151" s="12"/>
-      <c r="J151" s="8">
-        <v>60</v>
-      </c>
-      <c r="K151" s="9" t="s">
+      <c r="H151" s="13"/>
+      <c r="I151" s="13"/>
+      <c r="J151" s="9">
+        <v>60</v>
+      </c>
+      <c r="K151" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7031,19 +7034,19 @@
       <c r="D152" s="3">
         <v>8</v>
       </c>
-      <c r="E152" s="12"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G152" s="6" t="s">
+      <c r="G152" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H152" s="12"/>
-      <c r="I152" s="12"/>
-      <c r="J152" s="8">
-        <v>60</v>
-      </c>
-      <c r="K152" s="9" t="s">
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="9">
+        <v>60</v>
+      </c>
+      <c r="K152" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7058,22 +7061,22 @@
       <c r="C153" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D153" s="10">
+      <c r="D153" s="11">
         <v>9</v>
       </c>
-      <c r="E153" s="12"/>
+      <c r="E153" s="13"/>
       <c r="F153" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G153" s="6" t="s">
+      <c r="G153" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H153" s="12"/>
-      <c r="I153" s="12"/>
-      <c r="J153" s="8">
-        <v>60</v>
-      </c>
-      <c r="K153" s="9" t="s">
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="9">
+        <v>60</v>
+      </c>
+      <c r="K153" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7091,19 +7094,19 @@
       <c r="D154" s="3">
         <v>10</v>
       </c>
-      <c r="E154" s="12"/>
+      <c r="E154" s="13"/>
       <c r="F154" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G154" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H154" s="12"/>
-      <c r="I154" s="12"/>
-      <c r="J154" s="8">
-        <v>60</v>
-      </c>
-      <c r="K154" s="9" t="s">
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+      <c r="J154" s="9">
+        <v>60</v>
+      </c>
+      <c r="K154" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7121,21 +7124,21 @@
       <c r="D155" s="3">
         <v>1</v>
       </c>
-      <c r="E155" s="12"/>
+      <c r="E155" s="13"/>
       <c r="F155" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G155" s="6"/>
-      <c r="H155" s="13">
+      <c r="G155" s="7"/>
+      <c r="H155" s="14">
         <v>4030001</v>
       </c>
-      <c r="I155" s="6">
+      <c r="I155" s="7">
         <v>100300</v>
       </c>
-      <c r="J155" s="8">
-        <v>60</v>
-      </c>
-      <c r="K155" s="9" t="s">
+      <c r="J155" s="9">
+        <v>60</v>
+      </c>
+      <c r="K155" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7153,21 +7156,21 @@
       <c r="D156" s="3">
         <v>2</v>
       </c>
-      <c r="E156" s="12"/>
+      <c r="E156" s="13"/>
       <c r="F156" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G156" s="6"/>
-      <c r="H156" s="13">
+      <c r="G156" s="7"/>
+      <c r="H156" s="14">
         <v>4030002</v>
       </c>
-      <c r="I156" s="6">
+      <c r="I156" s="7">
         <v>103400</v>
       </c>
-      <c r="J156" s="8">
-        <v>60</v>
-      </c>
-      <c r="K156" s="9" t="s">
+      <c r="J156" s="9">
+        <v>60</v>
+      </c>
+      <c r="K156" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7185,21 +7188,21 @@
       <c r="D157" s="3">
         <v>3</v>
       </c>
-      <c r="E157" s="12"/>
+      <c r="E157" s="13"/>
       <c r="F157" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G157" s="6"/>
-      <c r="H157" s="13">
+      <c r="G157" s="7"/>
+      <c r="H157" s="14">
         <v>4030003</v>
       </c>
-      <c r="I157" s="6">
+      <c r="I157" s="7">
         <v>103500</v>
       </c>
-      <c r="J157" s="8">
-        <v>60</v>
-      </c>
-      <c r="K157" s="9" t="s">
+      <c r="J157" s="9">
+        <v>60</v>
+      </c>
+      <c r="K157" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7217,21 +7220,21 @@
       <c r="D158" s="3">
         <v>4</v>
       </c>
-      <c r="E158" s="12"/>
+      <c r="E158" s="13"/>
       <c r="F158" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G158" s="6"/>
-      <c r="H158" s="13">
+      <c r="G158" s="7"/>
+      <c r="H158" s="14">
         <v>4030004</v>
       </c>
-      <c r="I158" s="6">
+      <c r="I158" s="7">
         <v>103500</v>
       </c>
-      <c r="J158" s="8">
-        <v>60</v>
-      </c>
-      <c r="K158" s="9" t="s">
+      <c r="J158" s="9">
+        <v>60</v>
+      </c>
+      <c r="K158" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7249,21 +7252,21 @@
       <c r="D159" s="3">
         <v>5</v>
       </c>
-      <c r="E159" s="12"/>
+      <c r="E159" s="13"/>
       <c r="F159" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="6"/>
-      <c r="H159" s="13">
+      <c r="G159" s="7"/>
+      <c r="H159" s="14">
         <v>4030005</v>
       </c>
-      <c r="I159" s="6">
+      <c r="I159" s="7">
         <v>103500</v>
       </c>
-      <c r="J159" s="8">
-        <v>60</v>
-      </c>
-      <c r="K159" s="9" t="s">
+      <c r="J159" s="9">
+        <v>60</v>
+      </c>
+      <c r="K159" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7281,21 +7284,21 @@
       <c r="D160" s="3">
         <v>6</v>
       </c>
-      <c r="E160" s="12"/>
+      <c r="E160" s="13"/>
       <c r="F160" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G160" s="6"/>
-      <c r="H160" s="13">
+      <c r="G160" s="7"/>
+      <c r="H160" s="14">
         <v>4030006</v>
       </c>
-      <c r="I160" s="6">
+      <c r="I160" s="7">
         <v>103500</v>
       </c>
-      <c r="J160" s="8">
-        <v>60</v>
-      </c>
-      <c r="K160" s="9" t="s">
+      <c r="J160" s="9">
+        <v>60</v>
+      </c>
+      <c r="K160" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7313,21 +7316,21 @@
       <c r="D161" s="3">
         <v>7</v>
       </c>
-      <c r="E161" s="12"/>
+      <c r="E161" s="13"/>
       <c r="F161" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G161" s="6"/>
-      <c r="H161" s="13">
+      <c r="G161" s="7"/>
+      <c r="H161" s="14">
         <v>4030007</v>
       </c>
-      <c r="I161" s="6">
+      <c r="I161" s="7">
         <v>103500</v>
       </c>
-      <c r="J161" s="8">
-        <v>60</v>
-      </c>
-      <c r="K161" s="9" t="s">
+      <c r="J161" s="9">
+        <v>60</v>
+      </c>
+      <c r="K161" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7345,21 +7348,21 @@
       <c r="D162" s="3">
         <v>8</v>
       </c>
-      <c r="E162" s="12"/>
+      <c r="E162" s="13"/>
       <c r="F162" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G162" s="6"/>
-      <c r="H162" s="13">
+      <c r="G162" s="7"/>
+      <c r="H162" s="14">
         <v>4030008</v>
       </c>
-      <c r="I162" s="6">
+      <c r="I162" s="7">
         <v>103500</v>
       </c>
-      <c r="J162" s="8">
-        <v>60</v>
-      </c>
-      <c r="K162" s="9" t="s">
+      <c r="J162" s="9">
+        <v>60</v>
+      </c>
+      <c r="K162" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7374,24 +7377,24 @@
       <c r="C163" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D163" s="10">
+      <c r="D163" s="11">
         <v>9</v>
       </c>
-      <c r="E163" s="12"/>
+      <c r="E163" s="13"/>
       <c r="F163" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G163" s="6"/>
-      <c r="H163" s="13">
+      <c r="G163" s="7"/>
+      <c r="H163" s="14">
         <v>4030009</v>
       </c>
-      <c r="I163" s="6">
+      <c r="I163" s="7">
         <v>103500</v>
       </c>
-      <c r="J163" s="8">
-        <v>60</v>
-      </c>
-      <c r="K163" s="9" t="s">
+      <c r="J163" s="9">
+        <v>60</v>
+      </c>
+      <c r="K163" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7409,21 +7412,21 @@
       <c r="D164" s="3">
         <v>10</v>
       </c>
-      <c r="E164" s="12"/>
+      <c r="E164" s="13"/>
       <c r="F164" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G164" s="6"/>
-      <c r="H164" s="13">
+      <c r="G164" s="7"/>
+      <c r="H164" s="14">
         <v>4030010</v>
       </c>
-      <c r="I164" s="6">
+      <c r="I164" s="7">
         <v>103500</v>
       </c>
-      <c r="J164" s="8">
-        <v>60</v>
-      </c>
-      <c r="K164" s="9" t="s">
+      <c r="J164" s="9">
+        <v>60</v>
+      </c>
+      <c r="K164" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7441,19 +7444,19 @@
       <c r="D165" s="3">
         <v>1</v>
       </c>
-      <c r="E165" s="12"/>
+      <c r="E165" s="13"/>
       <c r="F165" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G165" s="6" t="s">
+      <c r="G165" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="H165" s="12"/>
-      <c r="I165" s="12"/>
-      <c r="J165" s="8">
-        <v>60</v>
-      </c>
-      <c r="K165" s="9" t="s">
+      <c r="H165" s="13"/>
+      <c r="I165" s="13"/>
+      <c r="J165" s="9">
+        <v>60</v>
+      </c>
+      <c r="K165" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7471,19 +7474,19 @@
       <c r="D166" s="3">
         <v>2</v>
       </c>
-      <c r="E166" s="12"/>
+      <c r="E166" s="13"/>
       <c r="F166" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G166" s="6" t="s">
+      <c r="G166" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H166" s="12"/>
-      <c r="I166" s="12"/>
-      <c r="J166" s="8">
-        <v>60</v>
-      </c>
-      <c r="K166" s="9" t="s">
+      <c r="H166" s="13"/>
+      <c r="I166" s="13"/>
+      <c r="J166" s="9">
+        <v>60</v>
+      </c>
+      <c r="K166" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7501,19 +7504,19 @@
       <c r="D167" s="3">
         <v>3</v>
       </c>
-      <c r="E167" s="12"/>
+      <c r="E167" s="13"/>
       <c r="F167" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G167" s="6" t="s">
+      <c r="G167" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="H167" s="12"/>
-      <c r="I167" s="12"/>
-      <c r="J167" s="8">
-        <v>60</v>
-      </c>
-      <c r="K167" s="9" t="s">
+      <c r="H167" s="13"/>
+      <c r="I167" s="13"/>
+      <c r="J167" s="9">
+        <v>60</v>
+      </c>
+      <c r="K167" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7531,19 +7534,19 @@
       <c r="D168" s="3">
         <v>4</v>
       </c>
-      <c r="E168" s="12"/>
+      <c r="E168" s="13"/>
       <c r="F168" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G168" s="6" t="s">
+      <c r="G168" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="H168" s="12"/>
-      <c r="I168" s="12"/>
-      <c r="J168" s="8">
-        <v>60</v>
-      </c>
-      <c r="K168" s="9" t="s">
+      <c r="H168" s="13"/>
+      <c r="I168" s="13"/>
+      <c r="J168" s="9">
+        <v>60</v>
+      </c>
+      <c r="K168" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7561,19 +7564,19 @@
       <c r="D169" s="3">
         <v>5</v>
       </c>
-      <c r="E169" s="12"/>
+      <c r="E169" s="13"/>
       <c r="F169" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G169" s="6" t="s">
+      <c r="G169" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="H169" s="12"/>
-      <c r="I169" s="12"/>
-      <c r="J169" s="8">
-        <v>60</v>
-      </c>
-      <c r="K169" s="9" t="s">
+      <c r="H169" s="13"/>
+      <c r="I169" s="13"/>
+      <c r="J169" s="9">
+        <v>60</v>
+      </c>
+      <c r="K169" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7591,19 +7594,19 @@
       <c r="D170" s="3">
         <v>6</v>
       </c>
-      <c r="E170" s="12"/>
+      <c r="E170" s="13"/>
       <c r="F170" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G170" s="6" t="s">
+      <c r="G170" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="H170" s="12"/>
-      <c r="I170" s="12"/>
-      <c r="J170" s="8">
-        <v>60</v>
-      </c>
-      <c r="K170" s="9" t="s">
+      <c r="H170" s="13"/>
+      <c r="I170" s="13"/>
+      <c r="J170" s="9">
+        <v>60</v>
+      </c>
+      <c r="K170" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7621,19 +7624,19 @@
       <c r="D171" s="3">
         <v>7</v>
       </c>
-      <c r="E171" s="12"/>
+      <c r="E171" s="13"/>
       <c r="F171" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G171" s="6" t="s">
+      <c r="G171" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H171" s="12"/>
-      <c r="I171" s="12"/>
-      <c r="J171" s="8">
-        <v>60</v>
-      </c>
-      <c r="K171" s="9" t="s">
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="9">
+        <v>60</v>
+      </c>
+      <c r="K171" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7651,19 +7654,19 @@
       <c r="D172" s="3">
         <v>8</v>
       </c>
-      <c r="E172" s="12"/>
+      <c r="E172" s="13"/>
       <c r="F172" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G172" s="6" t="s">
+      <c r="G172" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="H172" s="12"/>
-      <c r="I172" s="12"/>
-      <c r="J172" s="8">
-        <v>60</v>
-      </c>
-      <c r="K172" s="9" t="s">
+      <c r="H172" s="13"/>
+      <c r="I172" s="13"/>
+      <c r="J172" s="9">
+        <v>60</v>
+      </c>
+      <c r="K172" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7678,22 +7681,22 @@
       <c r="C173" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D173" s="10">
+      <c r="D173" s="11">
         <v>9</v>
       </c>
-      <c r="E173" s="12"/>
+      <c r="E173" s="13"/>
       <c r="F173" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G173" s="6" t="s">
+      <c r="G173" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="H173" s="12"/>
-      <c r="I173" s="12"/>
-      <c r="J173" s="8">
-        <v>60</v>
-      </c>
-      <c r="K173" s="9" t="s">
+      <c r="H173" s="13"/>
+      <c r="I173" s="13"/>
+      <c r="J173" s="9">
+        <v>60</v>
+      </c>
+      <c r="K173" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7711,19 +7714,19 @@
       <c r="D174" s="3">
         <v>10</v>
       </c>
-      <c r="E174" s="12"/>
+      <c r="E174" s="13"/>
       <c r="F174" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G174" s="6" t="s">
+      <c r="G174" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H174" s="12"/>
-      <c r="I174" s="12"/>
-      <c r="J174" s="8">
-        <v>60</v>
-      </c>
-      <c r="K174" s="9" t="s">
+      <c r="H174" s="13"/>
+      <c r="I174" s="13"/>
+      <c r="J174" s="9">
+        <v>60</v>
+      </c>
+      <c r="K174" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7741,19 +7744,19 @@
       <c r="D175" s="3">
         <v>1</v>
       </c>
-      <c r="E175" s="12"/>
+      <c r="E175" s="13"/>
       <c r="F175" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G175" s="6" t="s">
+      <c r="G175" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="H175" s="12"/>
-      <c r="I175" s="12"/>
-      <c r="J175" s="8">
-        <v>60</v>
-      </c>
-      <c r="K175" s="9" t="s">
+      <c r="H175" s="13"/>
+      <c r="I175" s="13"/>
+      <c r="J175" s="9">
+        <v>60</v>
+      </c>
+      <c r="K175" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7771,19 +7774,19 @@
       <c r="D176" s="3">
         <v>2</v>
       </c>
-      <c r="E176" s="12"/>
+      <c r="E176" s="13"/>
       <c r="F176" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G176" s="6" t="s">
+      <c r="G176" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H176" s="12"/>
-      <c r="I176" s="12"/>
-      <c r="J176" s="8">
-        <v>60</v>
-      </c>
-      <c r="K176" s="9" t="s">
+      <c r="H176" s="13"/>
+      <c r="I176" s="13"/>
+      <c r="J176" s="9">
+        <v>60</v>
+      </c>
+      <c r="K176" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7801,19 +7804,19 @@
       <c r="D177" s="3">
         <v>3</v>
       </c>
-      <c r="E177" s="12"/>
+      <c r="E177" s="13"/>
       <c r="F177" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G177" s="6" t="s">
+      <c r="G177" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="H177" s="12"/>
-      <c r="I177" s="12"/>
-      <c r="J177" s="8">
-        <v>60</v>
-      </c>
-      <c r="K177" s="9" t="s">
+      <c r="H177" s="13"/>
+      <c r="I177" s="13"/>
+      <c r="J177" s="9">
+        <v>60</v>
+      </c>
+      <c r="K177" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7831,19 +7834,19 @@
       <c r="D178" s="3">
         <v>4</v>
       </c>
-      <c r="E178" s="12"/>
+      <c r="E178" s="13"/>
       <c r="F178" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G178" s="6" t="s">
+      <c r="G178" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H178" s="12"/>
-      <c r="I178" s="12"/>
-      <c r="J178" s="8">
-        <v>60</v>
-      </c>
-      <c r="K178" s="9" t="s">
+      <c r="H178" s="13"/>
+      <c r="I178" s="13"/>
+      <c r="J178" s="9">
+        <v>60</v>
+      </c>
+      <c r="K178" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7861,19 +7864,19 @@
       <c r="D179" s="3">
         <v>5</v>
       </c>
-      <c r="E179" s="12"/>
+      <c r="E179" s="13"/>
       <c r="F179" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G179" s="6" t="s">
+      <c r="G179" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="H179" s="12"/>
-      <c r="I179" s="12"/>
-      <c r="J179" s="8">
-        <v>60</v>
-      </c>
-      <c r="K179" s="9" t="s">
+      <c r="H179" s="13"/>
+      <c r="I179" s="13"/>
+      <c r="J179" s="9">
+        <v>60</v>
+      </c>
+      <c r="K179" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7891,19 +7894,19 @@
       <c r="D180" s="3">
         <v>6</v>
       </c>
-      <c r="E180" s="12"/>
+      <c r="E180" s="13"/>
       <c r="F180" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G180" s="6" t="s">
+      <c r="G180" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="H180" s="12"/>
-      <c r="I180" s="12"/>
-      <c r="J180" s="8">
-        <v>60</v>
-      </c>
-      <c r="K180" s="9" t="s">
+      <c r="H180" s="13"/>
+      <c r="I180" s="13"/>
+      <c r="J180" s="9">
+        <v>60</v>
+      </c>
+      <c r="K180" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7921,19 +7924,19 @@
       <c r="D181" s="3">
         <v>7</v>
       </c>
-      <c r="E181" s="12"/>
+      <c r="E181" s="13"/>
       <c r="F181" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G181" s="6" t="s">
+      <c r="G181" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="H181" s="12"/>
-      <c r="I181" s="12"/>
-      <c r="J181" s="8">
-        <v>60</v>
-      </c>
-      <c r="K181" s="9" t="s">
+      <c r="H181" s="13"/>
+      <c r="I181" s="13"/>
+      <c r="J181" s="9">
+        <v>60</v>
+      </c>
+      <c r="K181" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7951,19 +7954,19 @@
       <c r="D182" s="3">
         <v>8</v>
       </c>
-      <c r="E182" s="12"/>
+      <c r="E182" s="13"/>
       <c r="F182" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G182" s="6" t="s">
+      <c r="G182" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H182" s="12"/>
-      <c r="I182" s="12"/>
-      <c r="J182" s="8">
-        <v>60</v>
-      </c>
-      <c r="K182" s="9" t="s">
+      <c r="H182" s="13"/>
+      <c r="I182" s="13"/>
+      <c r="J182" s="9">
+        <v>60</v>
+      </c>
+      <c r="K182" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7978,22 +7981,22 @@
       <c r="C183" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D183" s="10">
+      <c r="D183" s="11">
         <v>9</v>
       </c>
-      <c r="E183" s="12"/>
+      <c r="E183" s="13"/>
       <c r="F183" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G183" s="6" t="s">
+      <c r="G183" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="H183" s="12"/>
-      <c r="I183" s="12"/>
-      <c r="J183" s="8">
-        <v>60</v>
-      </c>
-      <c r="K183" s="9" t="s">
+      <c r="H183" s="13"/>
+      <c r="I183" s="13"/>
+      <c r="J183" s="9">
+        <v>60</v>
+      </c>
+      <c r="K183" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -8011,19 +8014,19 @@
       <c r="D184" s="3">
         <v>10</v>
       </c>
-      <c r="E184" s="12"/>
+      <c r="E184" s="13"/>
       <c r="F184" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G184" s="6" t="s">
+      <c r="G184" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="H184" s="12"/>
-      <c r="I184" s="12"/>
-      <c r="J184" s="8">
-        <v>60</v>
-      </c>
-      <c r="K184" s="9" t="s">
+      <c r="H184" s="13"/>
+      <c r="I184" s="13"/>
+      <c r="J184" s="9">
+        <v>60</v>
+      </c>
+      <c r="K184" s="10" t="s">
         <v>28</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -209,7 +209,7 @@
     <t>富贵厅</t>
   </si>
   <si>
-    <t>1970000_10000</t>
+    <t>1980000_10000</t>
   </si>
   <si>
     <t>1990000_1000</t>
@@ -1380,7 +1380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,9 +1392,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2028,7 +2025,7 @@
       <c r="J2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2049,19 +2046,19 @@
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2072,11 +2069,11 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" customHeight="1" spans="1:11">
       <c r="A5" s="3">
@@ -2098,15 +2095,15 @@
       <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="9">
-        <v>60</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="G5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="8">
+        <v>60</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2130,17 +2127,17 @@
       <c r="F6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
+      <c r="G6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="9">
-        <v>60</v>
-      </c>
-      <c r="K6" s="10" t="s">
+      <c r="J6" s="8">
+        <v>60</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2164,17 +2161,17 @@
       <c r="F7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
+      <c r="G7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="9">
-        <v>60</v>
-      </c>
-      <c r="K7" s="10" t="s">
+      <c r="J7" s="8">
+        <v>60</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2198,17 +2195,17 @@
       <c r="F8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
+      <c r="G8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="9">
-        <v>60</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="J8" s="8">
+        <v>60</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2232,17 +2229,17 @@
       <c r="F9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7" t="s">
+      <c r="G9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="9">
-        <v>60</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="J9" s="8">
+        <v>60</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2266,17 +2263,17 @@
       <c r="F10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7" t="s">
+      <c r="G10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="9">
-        <v>60</v>
-      </c>
-      <c r="K10" s="10" t="s">
+      <c r="J10" s="8">
+        <v>60</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2300,17 +2297,17 @@
       <c r="F11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7" t="s">
+      <c r="G11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="9">
-        <v>60</v>
-      </c>
-      <c r="K11" s="10" t="s">
+      <c r="J11" s="8">
+        <v>60</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2334,17 +2331,17 @@
       <c r="F12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7" t="s">
+      <c r="G12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="9">
-        <v>60</v>
-      </c>
-      <c r="K12" s="10" t="s">
+      <c r="J12" s="8">
+        <v>60</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2359,26 +2356,26 @@
       <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>9</v>
       </c>
       <c r="E13" s="3">
         <v>8</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="7" t="s">
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="9">
-        <v>60</v>
-      </c>
-      <c r="K13" s="10" t="s">
+      <c r="J13" s="8">
+        <v>60</v>
+      </c>
+      <c r="K13" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2402,17 +2399,17 @@
       <c r="F14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7" t="s">
+      <c r="G14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="9">
-        <v>60</v>
-      </c>
-      <c r="K14" s="10" t="s">
+      <c r="J14" s="8">
+        <v>60</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2436,15 +2433,15 @@
       <c r="F15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="9">
-        <v>60</v>
-      </c>
-      <c r="K15" s="10" t="s">
+      <c r="G15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="8">
+        <v>60</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2468,17 +2465,17 @@
       <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7" t="s">
+      <c r="G16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="9">
-        <v>60</v>
-      </c>
-      <c r="K16" s="10" t="s">
+      <c r="J16" s="8">
+        <v>60</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2502,17 +2499,17 @@
       <c r="F17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7" t="s">
+      <c r="G17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="9">
-        <v>60</v>
-      </c>
-      <c r="K17" s="10" t="s">
+      <c r="J17" s="8">
+        <v>60</v>
+      </c>
+      <c r="K17" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2536,17 +2533,17 @@
       <c r="F18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7" t="s">
+      <c r="G18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="9">
-        <v>60</v>
-      </c>
-      <c r="K18" s="10" t="s">
+      <c r="J18" s="8">
+        <v>60</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2570,17 +2567,17 @@
       <c r="F19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7" t="s">
+      <c r="G19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="9">
-        <v>60</v>
-      </c>
-      <c r="K19" s="10" t="s">
+      <c r="J19" s="8">
+        <v>60</v>
+      </c>
+      <c r="K19" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2604,17 +2601,17 @@
       <c r="F20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7" t="s">
+      <c r="G20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="9">
-        <v>60</v>
-      </c>
-      <c r="K20" s="10" t="s">
+      <c r="J20" s="8">
+        <v>60</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2638,17 +2635,17 @@
       <c r="F21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7" t="s">
+      <c r="G21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="9">
-        <v>60</v>
-      </c>
-      <c r="K21" s="10" t="s">
+      <c r="J21" s="8">
+        <v>60</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2672,17 +2669,17 @@
       <c r="F22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7" t="s">
+      <c r="G22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="9">
-        <v>60</v>
-      </c>
-      <c r="K22" s="10" t="s">
+      <c r="J22" s="8">
+        <v>60</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2697,26 +2694,26 @@
       <c r="C23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>9</v>
       </c>
       <c r="E23" s="3">
         <v>8</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="7" t="s">
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="9">
-        <v>60</v>
-      </c>
-      <c r="K23" s="10" t="s">
+      <c r="J23" s="8">
+        <v>60</v>
+      </c>
+      <c r="K23" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2740,17 +2737,17 @@
       <c r="F24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7" t="s">
+      <c r="G24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J24" s="9">
-        <v>60</v>
-      </c>
-      <c r="K24" s="10" t="s">
+      <c r="J24" s="8">
+        <v>60</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2774,15 +2771,15 @@
       <c r="F25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="9">
-        <v>60</v>
-      </c>
-      <c r="K25" s="10" t="s">
+      <c r="G25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="8">
+        <v>60</v>
+      </c>
+      <c r="K25" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2806,17 +2803,17 @@
       <c r="F26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7" t="s">
+      <c r="G26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J26" s="9">
-        <v>60</v>
-      </c>
-      <c r="K26" s="10" t="s">
+      <c r="J26" s="8">
+        <v>60</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2840,17 +2837,17 @@
       <c r="F27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7" t="s">
+      <c r="G27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J27" s="9">
-        <v>60</v>
-      </c>
-      <c r="K27" s="10" t="s">
+      <c r="J27" s="8">
+        <v>60</v>
+      </c>
+      <c r="K27" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2874,17 +2871,17 @@
       <c r="F28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7" t="s">
+      <c r="G28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J28" s="9">
-        <v>60</v>
-      </c>
-      <c r="K28" s="10" t="s">
+      <c r="J28" s="8">
+        <v>60</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2908,17 +2905,17 @@
       <c r="F29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7" t="s">
+      <c r="G29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="9">
-        <v>60</v>
-      </c>
-      <c r="K29" s="10" t="s">
+      <c r="J29" s="8">
+        <v>60</v>
+      </c>
+      <c r="K29" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2942,17 +2939,17 @@
       <c r="F30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7" t="s">
+      <c r="G30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="9">
-        <v>60</v>
-      </c>
-      <c r="K30" s="10" t="s">
+      <c r="J30" s="8">
+        <v>60</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2976,17 +2973,17 @@
       <c r="F31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7" t="s">
+      <c r="G31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J31" s="9">
-        <v>60</v>
-      </c>
-      <c r="K31" s="10" t="s">
+      <c r="J31" s="8">
+        <v>60</v>
+      </c>
+      <c r="K31" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3010,17 +3007,17 @@
       <c r="F32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7" t="s">
+      <c r="G32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J32" s="9">
-        <v>60</v>
-      </c>
-      <c r="K32" s="10" t="s">
+      <c r="J32" s="8">
+        <v>60</v>
+      </c>
+      <c r="K32" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3035,26 +3032,26 @@
       <c r="C33" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>9</v>
       </c>
       <c r="E33" s="3">
         <v>8</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="7" t="s">
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="11"/>
+      <c r="I33" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J33" s="9">
-        <v>60</v>
-      </c>
-      <c r="K33" s="10" t="s">
+      <c r="J33" s="8">
+        <v>60</v>
+      </c>
+      <c r="K33" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3078,17 +3075,17 @@
       <c r="F34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7" t="s">
+      <c r="G34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J34" s="9">
-        <v>60</v>
-      </c>
-      <c r="K34" s="10" t="s">
+      <c r="J34" s="8">
+        <v>60</v>
+      </c>
+      <c r="K34" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3112,15 +3109,15 @@
       <c r="F35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="9">
-        <v>60</v>
-      </c>
-      <c r="K35" s="10" t="s">
+      <c r="G35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="8">
+        <v>60</v>
+      </c>
+      <c r="K35" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3144,17 +3141,17 @@
       <c r="F36" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7" t="s">
+      <c r="G36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J36" s="9">
-        <v>60</v>
-      </c>
-      <c r="K36" s="10" t="s">
+      <c r="J36" s="8">
+        <v>60</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3178,17 +3175,17 @@
       <c r="F37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J37" s="9">
-        <v>60</v>
-      </c>
-      <c r="K37" s="10" t="s">
+      <c r="G37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J37" s="8">
+        <v>60</v>
+      </c>
+      <c r="K37" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3212,17 +3209,17 @@
       <c r="F38" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
+      <c r="G38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="9">
-        <v>60</v>
-      </c>
-      <c r="K38" s="10" t="s">
+      <c r="J38" s="8">
+        <v>60</v>
+      </c>
+      <c r="K38" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3246,17 +3243,17 @@
       <c r="F39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7" t="s">
+      <c r="G39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J39" s="9">
-        <v>60</v>
-      </c>
-      <c r="K39" s="10" t="s">
+      <c r="J39" s="8">
+        <v>60</v>
+      </c>
+      <c r="K39" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3280,17 +3277,17 @@
       <c r="F40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7" t="s">
+      <c r="G40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J40" s="9">
-        <v>60</v>
-      </c>
-      <c r="K40" s="10" t="s">
+      <c r="J40" s="8">
+        <v>60</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3314,17 +3311,17 @@
       <c r="F41" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7" t="s">
+      <c r="G41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J41" s="9">
-        <v>60</v>
-      </c>
-      <c r="K41" s="10" t="s">
+      <c r="J41" s="8">
+        <v>60</v>
+      </c>
+      <c r="K41" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3348,17 +3345,17 @@
       <c r="F42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7" t="s">
+      <c r="G42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J42" s="9">
-        <v>60</v>
-      </c>
-      <c r="K42" s="10" t="s">
+      <c r="J42" s="8">
+        <v>60</v>
+      </c>
+      <c r="K42" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3373,26 +3370,26 @@
       <c r="C43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>9</v>
       </c>
       <c r="E43" s="3">
         <v>8</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H43" s="12"/>
-      <c r="I43" s="7" t="s">
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H43" s="11"/>
+      <c r="I43" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="J43" s="9">
-        <v>60</v>
-      </c>
-      <c r="K43" s="10" t="s">
+      <c r="J43" s="8">
+        <v>60</v>
+      </c>
+      <c r="K43" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3416,17 +3413,17 @@
       <c r="F44" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7" t="s">
+      <c r="G44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J44" s="9">
-        <v>60</v>
-      </c>
-      <c r="K44" s="10" t="s">
+      <c r="J44" s="8">
+        <v>60</v>
+      </c>
+      <c r="K44" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3450,15 +3447,15 @@
       <c r="F45" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="9">
-        <v>60</v>
-      </c>
-      <c r="K45" s="10" t="s">
+      <c r="G45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="8">
+        <v>60</v>
+      </c>
+      <c r="K45" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3482,17 +3479,17 @@
       <c r="F46" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
+      <c r="G46" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="9">
-        <v>60</v>
-      </c>
-      <c r="K46" s="10" t="s">
+      <c r="J46" s="8">
+        <v>60</v>
+      </c>
+      <c r="K46" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3516,17 +3513,17 @@
       <c r="F47" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7" t="s">
+      <c r="G47" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J47" s="9">
-        <v>60</v>
-      </c>
-      <c r="K47" s="10" t="s">
+      <c r="J47" s="8">
+        <v>60</v>
+      </c>
+      <c r="K47" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3550,17 +3547,17 @@
       <c r="F48" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7" t="s">
+      <c r="G48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J48" s="9">
-        <v>60</v>
-      </c>
-      <c r="K48" s="10" t="s">
+      <c r="J48" s="8">
+        <v>60</v>
+      </c>
+      <c r="K48" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3584,17 +3581,17 @@
       <c r="F49" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7" t="s">
+      <c r="G49" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J49" s="9">
-        <v>60</v>
-      </c>
-      <c r="K49" s="10" t="s">
+      <c r="J49" s="8">
+        <v>60</v>
+      </c>
+      <c r="K49" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3618,17 +3615,17 @@
       <c r="F50" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G50" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7" t="s">
+      <c r="G50" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="J50" s="9">
-        <v>60</v>
-      </c>
-      <c r="K50" s="10" t="s">
+      <c r="J50" s="8">
+        <v>60</v>
+      </c>
+      <c r="K50" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3652,17 +3649,17 @@
       <c r="F51" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7" t="s">
+      <c r="G51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J51" s="9">
-        <v>60</v>
-      </c>
-      <c r="K51" s="10" t="s">
+      <c r="J51" s="8">
+        <v>60</v>
+      </c>
+      <c r="K51" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3686,17 +3683,17 @@
       <c r="F52" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7" t="s">
+      <c r="G52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J52" s="9">
-        <v>60</v>
-      </c>
-      <c r="K52" s="10" t="s">
+      <c r="J52" s="8">
+        <v>60</v>
+      </c>
+      <c r="K52" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3711,26 +3708,26 @@
       <c r="C53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>9</v>
       </c>
       <c r="E53" s="3">
         <v>8</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H53" s="12"/>
-      <c r="I53" s="7" t="s">
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="11"/>
+      <c r="I53" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="J53" s="9">
-        <v>60</v>
-      </c>
-      <c r="K53" s="10" t="s">
+      <c r="J53" s="8">
+        <v>60</v>
+      </c>
+      <c r="K53" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3754,17 +3751,17 @@
       <c r="F54" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7" t="s">
+      <c r="G54" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J54" s="9">
-        <v>60</v>
-      </c>
-      <c r="K54" s="10" t="s">
+      <c r="J54" s="8">
+        <v>60</v>
+      </c>
+      <c r="K54" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3788,15 +3785,15 @@
       <c r="F55" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G55" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="9">
-        <v>60</v>
-      </c>
-      <c r="K55" s="10" t="s">
+      <c r="G55" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="8">
+        <v>60</v>
+      </c>
+      <c r="K55" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3820,17 +3817,17 @@
       <c r="F56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7" t="s">
+      <c r="G56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="J56" s="9">
-        <v>60</v>
-      </c>
-      <c r="K56" s="10" t="s">
+      <c r="J56" s="8">
+        <v>60</v>
+      </c>
+      <c r="K56" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3854,17 +3851,17 @@
       <c r="F57" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7" t="s">
+      <c r="G57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J57" s="9">
-        <v>60</v>
-      </c>
-      <c r="K57" s="10" t="s">
+      <c r="J57" s="8">
+        <v>60</v>
+      </c>
+      <c r="K57" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3888,17 +3885,17 @@
       <c r="F58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G58" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7" t="s">
+      <c r="G58" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J58" s="9">
-        <v>60</v>
-      </c>
-      <c r="K58" s="10" t="s">
+      <c r="J58" s="8">
+        <v>60</v>
+      </c>
+      <c r="K58" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3922,17 +3919,17 @@
       <c r="F59" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7" t="s">
+      <c r="G59" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="J59" s="9">
-        <v>60</v>
-      </c>
-      <c r="K59" s="10" t="s">
+      <c r="J59" s="8">
+        <v>60</v>
+      </c>
+      <c r="K59" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3956,17 +3953,17 @@
       <c r="F60" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G60" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7" t="s">
+      <c r="G60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="J60" s="9">
-        <v>60</v>
-      </c>
-      <c r="K60" s="10" t="s">
+      <c r="J60" s="8">
+        <v>60</v>
+      </c>
+      <c r="K60" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3990,17 +3987,17 @@
       <c r="F61" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7" t="s">
+      <c r="G61" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="J61" s="9">
-        <v>60</v>
-      </c>
-      <c r="K61" s="10" t="s">
+      <c r="J61" s="8">
+        <v>60</v>
+      </c>
+      <c r="K61" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4024,17 +4021,17 @@
       <c r="F62" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G62" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7" t="s">
+      <c r="G62" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J62" s="9">
-        <v>60</v>
-      </c>
-      <c r="K62" s="10" t="s">
+      <c r="J62" s="8">
+        <v>60</v>
+      </c>
+      <c r="K62" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4049,26 +4046,26 @@
       <c r="C63" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <v>9</v>
       </c>
       <c r="E63" s="3">
         <v>8</v>
       </c>
-      <c r="F63" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H63" s="12"/>
-      <c r="I63" s="7" t="s">
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="11"/>
+      <c r="I63" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="J63" s="9">
-        <v>60</v>
-      </c>
-      <c r="K63" s="10" t="s">
+      <c r="J63" s="8">
+        <v>60</v>
+      </c>
+      <c r="K63" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4092,17 +4089,17 @@
       <c r="F64" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G64" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7" t="s">
+      <c r="G64" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="J64" s="9">
-        <v>60</v>
-      </c>
-      <c r="K64" s="10" t="s">
+      <c r="J64" s="8">
+        <v>60</v>
+      </c>
+      <c r="K64" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4126,15 +4123,15 @@
       <c r="F65" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="9">
-        <v>60</v>
-      </c>
-      <c r="K65" s="10" t="s">
+      <c r="G65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="8">
+        <v>60</v>
+      </c>
+      <c r="K65" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4158,17 +4155,17 @@
       <c r="F66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7" t="s">
+      <c r="G66" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="J66" s="9">
-        <v>60</v>
-      </c>
-      <c r="K66" s="10" t="s">
+      <c r="J66" s="8">
+        <v>60</v>
+      </c>
+      <c r="K66" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4192,17 +4189,17 @@
       <c r="F67" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7" t="s">
+      <c r="G67" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="J67" s="9">
-        <v>60</v>
-      </c>
-      <c r="K67" s="10" t="s">
+      <c r="J67" s="8">
+        <v>60</v>
+      </c>
+      <c r="K67" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4226,17 +4223,17 @@
       <c r="F68" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7" t="s">
+      <c r="G68" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J68" s="9">
-        <v>60</v>
-      </c>
-      <c r="K68" s="10" t="s">
+      <c r="J68" s="8">
+        <v>60</v>
+      </c>
+      <c r="K68" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4260,17 +4257,17 @@
       <c r="F69" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G69" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7" t="s">
+      <c r="G69" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J69" s="9">
-        <v>60</v>
-      </c>
-      <c r="K69" s="10" t="s">
+      <c r="J69" s="8">
+        <v>60</v>
+      </c>
+      <c r="K69" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4294,17 +4291,17 @@
       <c r="F70" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7" t="s">
+      <c r="G70" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="J70" s="9">
-        <v>60</v>
-      </c>
-      <c r="K70" s="10" t="s">
+      <c r="J70" s="8">
+        <v>60</v>
+      </c>
+      <c r="K70" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4328,17 +4325,17 @@
       <c r="F71" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7" t="s">
+      <c r="G71" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="J71" s="9">
-        <v>60</v>
-      </c>
-      <c r="K71" s="10" t="s">
+      <c r="J71" s="8">
+        <v>60</v>
+      </c>
+      <c r="K71" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4362,17 +4359,17 @@
       <c r="F72" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7" t="s">
+      <c r="G72" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="J72" s="9">
-        <v>60</v>
-      </c>
-      <c r="K72" s="10" t="s">
+      <c r="J72" s="8">
+        <v>60</v>
+      </c>
+      <c r="K72" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4387,26 +4384,26 @@
       <c r="C73" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <v>9</v>
       </c>
       <c r="E73" s="3">
         <v>8</v>
       </c>
-      <c r="F73" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="7" t="s">
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" s="11"/>
+      <c r="I73" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J73" s="9">
-        <v>60</v>
-      </c>
-      <c r="K73" s="10" t="s">
+      <c r="J73" s="8">
+        <v>60</v>
+      </c>
+      <c r="K73" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4430,17 +4427,17 @@
       <c r="F74" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7" t="s">
+      <c r="G74" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J74" s="9">
-        <v>60</v>
-      </c>
-      <c r="K74" s="10" t="s">
+      <c r="J74" s="8">
+        <v>60</v>
+      </c>
+      <c r="K74" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4464,15 +4461,15 @@
       <c r="F75" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G75" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="9">
-        <v>60</v>
-      </c>
-      <c r="K75" s="10" t="s">
+      <c r="G75" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="8">
+        <v>60</v>
+      </c>
+      <c r="K75" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4496,17 +4493,17 @@
       <c r="F76" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7" t="s">
+      <c r="G76" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J76" s="9">
-        <v>60</v>
-      </c>
-      <c r="K76" s="10" t="s">
+      <c r="J76" s="8">
+        <v>60</v>
+      </c>
+      <c r="K76" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4530,17 +4527,17 @@
       <c r="F77" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7" t="s">
+      <c r="G77" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="J77" s="9">
-        <v>60</v>
-      </c>
-      <c r="K77" s="10" t="s">
+      <c r="J77" s="8">
+        <v>60</v>
+      </c>
+      <c r="K77" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4564,17 +4561,17 @@
       <c r="F78" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7" t="s">
+      <c r="G78" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="J78" s="9">
-        <v>60</v>
-      </c>
-      <c r="K78" s="10" t="s">
+      <c r="J78" s="8">
+        <v>60</v>
+      </c>
+      <c r="K78" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4598,17 +4595,17 @@
       <c r="F79" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7" t="s">
+      <c r="G79" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="J79" s="9">
-        <v>60</v>
-      </c>
-      <c r="K79" s="10" t="s">
+      <c r="J79" s="8">
+        <v>60</v>
+      </c>
+      <c r="K79" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4632,17 +4629,17 @@
       <c r="F80" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G80" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7" t="s">
+      <c r="G80" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J80" s="9">
-        <v>60</v>
-      </c>
-      <c r="K80" s="10" t="s">
+      <c r="J80" s="8">
+        <v>60</v>
+      </c>
+      <c r="K80" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4666,17 +4663,17 @@
       <c r="F81" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G81" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7" t="s">
+      <c r="G81" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="J81" s="9">
-        <v>60</v>
-      </c>
-      <c r="K81" s="10" t="s">
+      <c r="J81" s="8">
+        <v>60</v>
+      </c>
+      <c r="K81" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4700,17 +4697,17 @@
       <c r="F82" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7" t="s">
+      <c r="G82" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="J82" s="9">
-        <v>60</v>
-      </c>
-      <c r="K82" s="10" t="s">
+      <c r="J82" s="8">
+        <v>60</v>
+      </c>
+      <c r="K82" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4725,26 +4722,26 @@
       <c r="C83" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <v>9</v>
       </c>
       <c r="E83" s="3">
         <v>8</v>
       </c>
-      <c r="F83" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H83" s="12"/>
-      <c r="I83" s="7" t="s">
+      <c r="F83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="J83" s="9">
-        <v>60</v>
-      </c>
-      <c r="K83" s="10" t="s">
+      <c r="J83" s="8">
+        <v>60</v>
+      </c>
+      <c r="K83" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4768,17 +4765,17 @@
       <c r="F84" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G84" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7" t="s">
+      <c r="G84" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="J84" s="9">
-        <v>60</v>
-      </c>
-      <c r="K84" s="10" t="s">
+      <c r="J84" s="8">
+        <v>60</v>
+      </c>
+      <c r="K84" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4802,15 +4799,15 @@
       <c r="F85" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="9">
-        <v>60</v>
-      </c>
-      <c r="K85" s="10" t="s">
+      <c r="G85" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="8">
+        <v>60</v>
+      </c>
+      <c r="K85" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4834,17 +4831,17 @@
       <c r="F86" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7" t="s">
+      <c r="G86" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J86" s="9">
-        <v>60</v>
-      </c>
-      <c r="K86" s="10" t="s">
+      <c r="J86" s="8">
+        <v>60</v>
+      </c>
+      <c r="K86" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4868,17 +4865,17 @@
       <c r="F87" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7" t="s">
+      <c r="G87" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J87" s="9">
-        <v>60</v>
-      </c>
-      <c r="K87" s="10" t="s">
+      <c r="J87" s="8">
+        <v>60</v>
+      </c>
+      <c r="K87" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4902,17 +4899,17 @@
       <c r="F88" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7" t="s">
+      <c r="G88" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J88" s="9">
-        <v>60</v>
-      </c>
-      <c r="K88" s="10" t="s">
+      <c r="J88" s="8">
+        <v>60</v>
+      </c>
+      <c r="K88" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4936,17 +4933,17 @@
       <c r="F89" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G89" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7" t="s">
+      <c r="G89" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J89" s="9">
-        <v>60</v>
-      </c>
-      <c r="K89" s="10" t="s">
+      <c r="J89" s="8">
+        <v>60</v>
+      </c>
+      <c r="K89" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4970,17 +4967,17 @@
       <c r="F90" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G90" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7" t="s">
+      <c r="G90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="J90" s="9">
-        <v>60</v>
-      </c>
-      <c r="K90" s="10" t="s">
+      <c r="J90" s="8">
+        <v>60</v>
+      </c>
+      <c r="K90" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5004,17 +5001,17 @@
       <c r="F91" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G91" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7" t="s">
+      <c r="G91" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="J91" s="9">
-        <v>60</v>
-      </c>
-      <c r="K91" s="10" t="s">
+      <c r="J91" s="8">
+        <v>60</v>
+      </c>
+      <c r="K91" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5038,17 +5035,17 @@
       <c r="F92" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7" t="s">
+      <c r="G92" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="J92" s="9">
-        <v>60</v>
-      </c>
-      <c r="K92" s="10" t="s">
+      <c r="J92" s="8">
+        <v>60</v>
+      </c>
+      <c r="K92" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5063,26 +5060,26 @@
       <c r="C93" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <v>9</v>
       </c>
       <c r="E93" s="3">
         <v>8</v>
       </c>
-      <c r="F93" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="7" t="s">
+      <c r="F93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="11"/>
+      <c r="I93" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J93" s="9">
-        <v>60</v>
-      </c>
-      <c r="K93" s="10" t="s">
+      <c r="J93" s="8">
+        <v>60</v>
+      </c>
+      <c r="K93" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5106,17 +5103,17 @@
       <c r="F94" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G94" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7" t="s">
+      <c r="G94" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="J94" s="9">
-        <v>60</v>
-      </c>
-      <c r="K94" s="10" t="s">
+      <c r="J94" s="8">
+        <v>60</v>
+      </c>
+      <c r="K94" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5140,15 +5137,15 @@
       <c r="F95" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G95" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="9">
-        <v>60</v>
-      </c>
-      <c r="K95" s="10" t="s">
+      <c r="G95" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="8">
+        <v>60</v>
+      </c>
+      <c r="K95" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5172,17 +5169,17 @@
       <c r="F96" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G96" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7" t="s">
+      <c r="G96" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="J96" s="9">
-        <v>60</v>
-      </c>
-      <c r="K96" s="10" t="s">
+      <c r="J96" s="8">
+        <v>60</v>
+      </c>
+      <c r="K96" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5206,17 +5203,17 @@
       <c r="F97" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G97" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7" t="s">
+      <c r="G97" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="J97" s="9">
-        <v>60</v>
-      </c>
-      <c r="K97" s="10" t="s">
+      <c r="J97" s="8">
+        <v>60</v>
+      </c>
+      <c r="K97" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5240,17 +5237,17 @@
       <c r="F98" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7" t="s">
+      <c r="G98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="J98" s="9">
-        <v>60</v>
-      </c>
-      <c r="K98" s="10" t="s">
+      <c r="J98" s="8">
+        <v>60</v>
+      </c>
+      <c r="K98" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5274,17 +5271,17 @@
       <c r="F99" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G99" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7" t="s">
+      <c r="G99" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J99" s="9">
-        <v>60</v>
-      </c>
-      <c r="K99" s="10" t="s">
+      <c r="J99" s="8">
+        <v>60</v>
+      </c>
+      <c r="K99" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5308,17 +5305,17 @@
       <c r="F100" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G100" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7" t="s">
+      <c r="G100" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J100" s="9">
-        <v>60</v>
-      </c>
-      <c r="K100" s="10" t="s">
+      <c r="J100" s="8">
+        <v>60</v>
+      </c>
+      <c r="K100" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5342,17 +5339,17 @@
       <c r="F101" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7" t="s">
+      <c r="G101" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J101" s="9">
-        <v>60</v>
-      </c>
-      <c r="K101" s="10" t="s">
+      <c r="J101" s="8">
+        <v>60</v>
+      </c>
+      <c r="K101" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5376,17 +5373,17 @@
       <c r="F102" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7" t="s">
+      <c r="G102" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="J102" s="9">
-        <v>60</v>
-      </c>
-      <c r="K102" s="10" t="s">
+      <c r="J102" s="8">
+        <v>60</v>
+      </c>
+      <c r="K102" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5401,26 +5398,26 @@
       <c r="C103" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <v>9</v>
       </c>
       <c r="E103" s="3">
         <v>8</v>
       </c>
-      <c r="F103" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H103" s="12"/>
-      <c r="I103" s="7" t="s">
+      <c r="F103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" s="11"/>
+      <c r="I103" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J103" s="9">
-        <v>60</v>
-      </c>
-      <c r="K103" s="10" t="s">
+      <c r="J103" s="8">
+        <v>60</v>
+      </c>
+      <c r="K103" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5444,17 +5441,17 @@
       <c r="F104" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G104" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H104" s="7"/>
-      <c r="I104" s="7" t="s">
+      <c r="G104" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="J104" s="9">
-        <v>60</v>
-      </c>
-      <c r="K104" s="10" t="s">
+      <c r="J104" s="8">
+        <v>60</v>
+      </c>
+      <c r="K104" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5478,15 +5475,15 @@
       <c r="F105" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="9">
-        <v>60</v>
-      </c>
-      <c r="K105" s="10" t="s">
+      <c r="G105" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="8">
+        <v>60</v>
+      </c>
+      <c r="K105" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5510,17 +5507,17 @@
       <c r="F106" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G106" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7" t="s">
+      <c r="G106" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="J106" s="9">
-        <v>60</v>
-      </c>
-      <c r="K106" s="10" t="s">
+      <c r="J106" s="8">
+        <v>60</v>
+      </c>
+      <c r="K106" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5544,17 +5541,17 @@
       <c r="F107" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G107" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7" t="s">
+      <c r="G107" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J107" s="9">
-        <v>60</v>
-      </c>
-      <c r="K107" s="10" t="s">
+      <c r="J107" s="8">
+        <v>60</v>
+      </c>
+      <c r="K107" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5578,17 +5575,17 @@
       <c r="F108" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G108" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7" t="s">
+      <c r="G108" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J108" s="9">
-        <v>60</v>
-      </c>
-      <c r="K108" s="10" t="s">
+      <c r="J108" s="8">
+        <v>60</v>
+      </c>
+      <c r="K108" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5612,17 +5609,17 @@
       <c r="F109" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G109" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7" t="s">
+      <c r="G109" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J109" s="9">
-        <v>60</v>
-      </c>
-      <c r="K109" s="10" t="s">
+      <c r="J109" s="8">
+        <v>60</v>
+      </c>
+      <c r="K109" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5646,17 +5643,17 @@
       <c r="F110" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7" t="s">
+      <c r="G110" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J110" s="9">
-        <v>60</v>
-      </c>
-      <c r="K110" s="10" t="s">
+      <c r="J110" s="8">
+        <v>60</v>
+      </c>
+      <c r="K110" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5680,17 +5677,17 @@
       <c r="F111" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G111" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7" t="s">
+      <c r="G111" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="J111" s="9">
-        <v>60</v>
-      </c>
-      <c r="K111" s="10" t="s">
+      <c r="J111" s="8">
+        <v>60</v>
+      </c>
+      <c r="K111" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5714,17 +5711,17 @@
       <c r="F112" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G112" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7" t="s">
+      <c r="G112" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J112" s="9">
-        <v>60</v>
-      </c>
-      <c r="K112" s="10" t="s">
+      <c r="J112" s="8">
+        <v>60</v>
+      </c>
+      <c r="K112" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5739,26 +5736,26 @@
       <c r="C113" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <v>9</v>
       </c>
       <c r="E113" s="3">
         <v>8</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G113" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H113" s="12"/>
-      <c r="I113" s="7" t="s">
+      <c r="F113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G113" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" s="11"/>
+      <c r="I113" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J113" s="9">
-        <v>60</v>
-      </c>
-      <c r="K113" s="10" t="s">
+      <c r="J113" s="8">
+        <v>60</v>
+      </c>
+      <c r="K113" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5782,17 +5779,17 @@
       <c r="F114" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7" t="s">
+      <c r="G114" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="J114" s="9">
-        <v>60</v>
-      </c>
-      <c r="K114" s="10" t="s">
+      <c r="J114" s="8">
+        <v>60</v>
+      </c>
+      <c r="K114" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5816,15 +5813,15 @@
       <c r="F115" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="9">
-        <v>60</v>
-      </c>
-      <c r="K115" s="10" t="s">
+      <c r="G115" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="8">
+        <v>60</v>
+      </c>
+      <c r="K115" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5848,17 +5845,17 @@
       <c r="F116" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G116" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7" t="s">
+      <c r="G116" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="J116" s="9">
-        <v>60</v>
-      </c>
-      <c r="K116" s="10" t="s">
+      <c r="J116" s="8">
+        <v>60</v>
+      </c>
+      <c r="K116" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5882,17 +5879,17 @@
       <c r="F117" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G117" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7" t="s">
+      <c r="G117" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J117" s="9">
-        <v>60</v>
-      </c>
-      <c r="K117" s="10" t="s">
+      <c r="J117" s="8">
+        <v>60</v>
+      </c>
+      <c r="K117" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5916,17 +5913,17 @@
       <c r="F118" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G118" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7" t="s">
+      <c r="G118" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="J118" s="9">
-        <v>60</v>
-      </c>
-      <c r="K118" s="10" t="s">
+      <c r="J118" s="8">
+        <v>60</v>
+      </c>
+      <c r="K118" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5950,17 +5947,17 @@
       <c r="F119" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7" t="s">
+      <c r="G119" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="J119" s="9">
-        <v>60</v>
-      </c>
-      <c r="K119" s="10" t="s">
+      <c r="J119" s="8">
+        <v>60</v>
+      </c>
+      <c r="K119" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5984,17 +5981,17 @@
       <c r="F120" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G120" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7" t="s">
+      <c r="G120" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="J120" s="9">
-        <v>60</v>
-      </c>
-      <c r="K120" s="10" t="s">
+      <c r="J120" s="8">
+        <v>60</v>
+      </c>
+      <c r="K120" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6018,17 +6015,17 @@
       <c r="F121" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G121" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7" t="s">
+      <c r="G121" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="J121" s="9">
-        <v>60</v>
-      </c>
-      <c r="K121" s="10" t="s">
+      <c r="J121" s="8">
+        <v>60</v>
+      </c>
+      <c r="K121" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6052,17 +6049,17 @@
       <c r="F122" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G122" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7" t="s">
+      <c r="G122" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J122" s="9">
-        <v>60</v>
-      </c>
-      <c r="K122" s="10" t="s">
+      <c r="J122" s="8">
+        <v>60</v>
+      </c>
+      <c r="K122" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6077,26 +6074,26 @@
       <c r="C123" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <v>9</v>
       </c>
       <c r="E123" s="3">
         <v>8</v>
       </c>
-      <c r="F123" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G123" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H123" s="12"/>
-      <c r="I123" s="7" t="s">
+      <c r="F123" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" s="11"/>
+      <c r="I123" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J123" s="9">
-        <v>60</v>
-      </c>
-      <c r="K123" s="10" t="s">
+      <c r="J123" s="8">
+        <v>60</v>
+      </c>
+      <c r="K123" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6120,17 +6117,17 @@
       <c r="F124" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G124" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7" t="s">
+      <c r="G124" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" s="6"/>
+      <c r="I124" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="J124" s="9">
-        <v>60</v>
-      </c>
-      <c r="K124" s="10" t="s">
+      <c r="J124" s="8">
+        <v>60</v>
+      </c>
+      <c r="K124" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6154,15 +6151,15 @@
       <c r="F125" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G125" s="7" t="s">
+      <c r="G125" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="9">
-        <v>60</v>
-      </c>
-      <c r="K125" s="10" t="s">
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="8">
+        <v>60</v>
+      </c>
+      <c r="K125" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6186,17 +6183,17 @@
       <c r="F126" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7" t="s">
+      <c r="H126" s="6"/>
+      <c r="I126" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="J126" s="9">
-        <v>60</v>
-      </c>
-      <c r="K126" s="10" t="s">
+      <c r="J126" s="8">
+        <v>60</v>
+      </c>
+      <c r="K126" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6220,17 +6217,17 @@
       <c r="F127" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="G127" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7" t="s">
+      <c r="H127" s="6"/>
+      <c r="I127" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="J127" s="9">
-        <v>60</v>
-      </c>
-      <c r="K127" s="10" t="s">
+      <c r="J127" s="8">
+        <v>60</v>
+      </c>
+      <c r="K127" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6254,17 +6251,17 @@
       <c r="F128" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="7" t="s">
+      <c r="G128" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7" t="s">
+      <c r="H128" s="6"/>
+      <c r="I128" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="J128" s="9">
-        <v>60</v>
-      </c>
-      <c r="K128" s="10" t="s">
+      <c r="J128" s="8">
+        <v>60</v>
+      </c>
+      <c r="K128" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6288,17 +6285,17 @@
       <c r="F129" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G129" s="7" t="s">
+      <c r="G129" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7" t="s">
+      <c r="H129" s="6"/>
+      <c r="I129" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J129" s="9">
-        <v>60</v>
-      </c>
-      <c r="K129" s="10" t="s">
+      <c r="J129" s="8">
+        <v>60</v>
+      </c>
+      <c r="K129" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6322,17 +6319,17 @@
       <c r="F130" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G130" s="7" t="s">
+      <c r="G130" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7" t="s">
+      <c r="H130" s="6"/>
+      <c r="I130" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="J130" s="9">
-        <v>60</v>
-      </c>
-      <c r="K130" s="10" t="s">
+      <c r="J130" s="8">
+        <v>60</v>
+      </c>
+      <c r="K130" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6356,17 +6353,17 @@
       <c r="F131" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G131" s="7" t="s">
+      <c r="G131" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7" t="s">
+      <c r="H131" s="6"/>
+      <c r="I131" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="J131" s="9">
-        <v>60</v>
-      </c>
-      <c r="K131" s="10" t="s">
+      <c r="J131" s="8">
+        <v>60</v>
+      </c>
+      <c r="K131" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6390,17 +6387,17 @@
       <c r="F132" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="7" t="s">
+      <c r="G132" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7" t="s">
+      <c r="H132" s="6"/>
+      <c r="I132" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="J132" s="9">
-        <v>60</v>
-      </c>
-      <c r="K132" s="10" t="s">
+      <c r="J132" s="8">
+        <v>60</v>
+      </c>
+      <c r="K132" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6415,26 +6412,26 @@
       <c r="C133" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <v>9</v>
       </c>
       <c r="E133" s="3">
         <v>8</v>
       </c>
-      <c r="F133" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G133" s="12" t="s">
+      <c r="F133" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="H133" s="12"/>
-      <c r="I133" s="7" t="s">
+      <c r="H133" s="11"/>
+      <c r="I133" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="J133" s="9">
-        <v>60</v>
-      </c>
-      <c r="K133" s="10" t="s">
+      <c r="J133" s="8">
+        <v>60</v>
+      </c>
+      <c r="K133" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6458,17 +6455,17 @@
       <c r="F134" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G134" s="7" t="s">
+      <c r="G134" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7" t="s">
+      <c r="H134" s="6"/>
+      <c r="I134" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J134" s="9">
-        <v>60</v>
-      </c>
-      <c r="K134" s="10" t="s">
+      <c r="J134" s="8">
+        <v>60</v>
+      </c>
+      <c r="K134" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6492,15 +6489,15 @@
       <c r="F135" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G135" s="7" t="s">
+      <c r="G135" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="9">
-        <v>60</v>
-      </c>
-      <c r="K135" s="10" t="s">
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="8">
+        <v>60</v>
+      </c>
+      <c r="K135" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6524,17 +6521,17 @@
       <c r="F136" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G136" s="7" t="s">
+      <c r="G136" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7" t="s">
+      <c r="H136" s="6"/>
+      <c r="I136" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="J136" s="9">
-        <v>60</v>
-      </c>
-      <c r="K136" s="10" t="s">
+      <c r="J136" s="8">
+        <v>60</v>
+      </c>
+      <c r="K136" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6558,17 +6555,17 @@
       <c r="F137" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="G137" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7" t="s">
+      <c r="H137" s="6"/>
+      <c r="I137" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="J137" s="9">
-        <v>60</v>
-      </c>
-      <c r="K137" s="10" t="s">
+      <c r="J137" s="8">
+        <v>60</v>
+      </c>
+      <c r="K137" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6592,17 +6589,17 @@
       <c r="F138" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G138" s="7" t="s">
+      <c r="G138" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7" t="s">
+      <c r="H138" s="6"/>
+      <c r="I138" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="J138" s="9">
-        <v>60</v>
-      </c>
-      <c r="K138" s="10" t="s">
+      <c r="J138" s="8">
+        <v>60</v>
+      </c>
+      <c r="K138" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6626,17 +6623,17 @@
       <c r="F139" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G139" s="7" t="s">
+      <c r="G139" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H139" s="7"/>
-      <c r="I139" s="7" t="s">
+      <c r="H139" s="6"/>
+      <c r="I139" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="J139" s="9">
-        <v>60</v>
-      </c>
-      <c r="K139" s="10" t="s">
+      <c r="J139" s="8">
+        <v>60</v>
+      </c>
+      <c r="K139" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6660,17 +6657,17 @@
       <c r="F140" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G140" s="7" t="s">
+      <c r="G140" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7" t="s">
+      <c r="H140" s="6"/>
+      <c r="I140" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="J140" s="9">
-        <v>60</v>
-      </c>
-      <c r="K140" s="10" t="s">
+      <c r="J140" s="8">
+        <v>60</v>
+      </c>
+      <c r="K140" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6694,17 +6691,17 @@
       <c r="F141" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G141" s="7" t="s">
+      <c r="G141" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H141" s="7"/>
-      <c r="I141" s="7" t="s">
+      <c r="H141" s="6"/>
+      <c r="I141" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J141" s="9">
-        <v>60</v>
-      </c>
-      <c r="K141" s="10" t="s">
+      <c r="J141" s="8">
+        <v>60</v>
+      </c>
+      <c r="K141" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6728,17 +6725,17 @@
       <c r="F142" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G142" s="7" t="s">
+      <c r="G142" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H142" s="7"/>
-      <c r="I142" s="7" t="s">
+      <c r="H142" s="6"/>
+      <c r="I142" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J142" s="9">
-        <v>60</v>
-      </c>
-      <c r="K142" s="10" t="s">
+      <c r="J142" s="8">
+        <v>60</v>
+      </c>
+      <c r="K142" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6753,26 +6750,26 @@
       <c r="C143" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <v>9</v>
       </c>
       <c r="E143" s="3">
         <v>8</v>
       </c>
-      <c r="F143" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="12" t="s">
+      <c r="F143" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="H143" s="12"/>
-      <c r="I143" s="7" t="s">
+      <c r="H143" s="11"/>
+      <c r="I143" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J143" s="9">
-        <v>60</v>
-      </c>
-      <c r="K143" s="10" t="s">
+      <c r="J143" s="8">
+        <v>60</v>
+      </c>
+      <c r="K143" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6796,17 +6793,17 @@
       <c r="F144" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G144" s="7" t="s">
+      <c r="G144" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H144" s="7"/>
-      <c r="I144" s="7" t="s">
+      <c r="H144" s="6"/>
+      <c r="I144" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J144" s="9">
-        <v>60</v>
-      </c>
-      <c r="K144" s="10" t="s">
+      <c r="J144" s="8">
+        <v>60</v>
+      </c>
+      <c r="K144" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6824,19 +6821,19 @@
       <c r="D145" s="3">
         <v>1</v>
       </c>
-      <c r="E145" s="13"/>
+      <c r="E145" s="12"/>
       <c r="F145" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G145" s="7" t="s">
+      <c r="G145" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H145" s="13"/>
-      <c r="I145" s="13"/>
-      <c r="J145" s="9">
-        <v>60</v>
-      </c>
-      <c r="K145" s="10" t="s">
+      <c r="H145" s="12"/>
+      <c r="I145" s="12"/>
+      <c r="J145" s="8">
+        <v>60</v>
+      </c>
+      <c r="K145" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6854,19 +6851,19 @@
       <c r="D146" s="3">
         <v>2</v>
       </c>
-      <c r="E146" s="13"/>
+      <c r="E146" s="12"/>
       <c r="F146" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G146" s="7" t="s">
+      <c r="G146" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
-      <c r="J146" s="9">
-        <v>60</v>
-      </c>
-      <c r="K146" s="10" t="s">
+      <c r="H146" s="12"/>
+      <c r="I146" s="12"/>
+      <c r="J146" s="8">
+        <v>60</v>
+      </c>
+      <c r="K146" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6884,19 +6881,19 @@
       <c r="D147" s="3">
         <v>3</v>
       </c>
-      <c r="E147" s="13"/>
+      <c r="E147" s="12"/>
       <c r="F147" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G147" s="7" t="s">
+      <c r="G147" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H147" s="13"/>
-      <c r="I147" s="13"/>
-      <c r="J147" s="9">
-        <v>60</v>
-      </c>
-      <c r="K147" s="10" t="s">
+      <c r="H147" s="12"/>
+      <c r="I147" s="12"/>
+      <c r="J147" s="8">
+        <v>60</v>
+      </c>
+      <c r="K147" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6914,19 +6911,19 @@
       <c r="D148" s="3">
         <v>4</v>
       </c>
-      <c r="E148" s="13"/>
+      <c r="E148" s="12"/>
       <c r="F148" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G148" s="7" t="s">
+      <c r="G148" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
-      <c r="J148" s="9">
-        <v>60</v>
-      </c>
-      <c r="K148" s="10" t="s">
+      <c r="H148" s="12"/>
+      <c r="I148" s="12"/>
+      <c r="J148" s="8">
+        <v>60</v>
+      </c>
+      <c r="K148" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6944,19 +6941,19 @@
       <c r="D149" s="3">
         <v>5</v>
       </c>
-      <c r="E149" s="13"/>
+      <c r="E149" s="12"/>
       <c r="F149" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G149" s="7" t="s">
+      <c r="G149" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="9">
-        <v>60</v>
-      </c>
-      <c r="K149" s="10" t="s">
+      <c r="H149" s="12"/>
+      <c r="I149" s="12"/>
+      <c r="J149" s="8">
+        <v>60</v>
+      </c>
+      <c r="K149" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6974,19 +6971,19 @@
       <c r="D150" s="3">
         <v>6</v>
       </c>
-      <c r="E150" s="13"/>
+      <c r="E150" s="12"/>
       <c r="F150" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G150" s="7" t="s">
+      <c r="G150" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-      <c r="J150" s="9">
-        <v>60</v>
-      </c>
-      <c r="K150" s="10" t="s">
+      <c r="H150" s="12"/>
+      <c r="I150" s="12"/>
+      <c r="J150" s="8">
+        <v>60</v>
+      </c>
+      <c r="K150" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7004,19 +7001,19 @@
       <c r="D151" s="3">
         <v>7</v>
       </c>
-      <c r="E151" s="13"/>
+      <c r="E151" s="12"/>
       <c r="F151" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G151" s="7" t="s">
+      <c r="G151" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
-      <c r="J151" s="9">
-        <v>60</v>
-      </c>
-      <c r="K151" s="10" t="s">
+      <c r="H151" s="12"/>
+      <c r="I151" s="12"/>
+      <c r="J151" s="8">
+        <v>60</v>
+      </c>
+      <c r="K151" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7034,19 +7031,19 @@
       <c r="D152" s="3">
         <v>8</v>
       </c>
-      <c r="E152" s="13"/>
+      <c r="E152" s="12"/>
       <c r="F152" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G152" s="7" t="s">
+      <c r="G152" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-      <c r="J152" s="9">
-        <v>60</v>
-      </c>
-      <c r="K152" s="10" t="s">
+      <c r="H152" s="12"/>
+      <c r="I152" s="12"/>
+      <c r="J152" s="8">
+        <v>60</v>
+      </c>
+      <c r="K152" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7061,22 +7058,22 @@
       <c r="C153" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="10">
         <v>9</v>
       </c>
-      <c r="E153" s="13"/>
+      <c r="E153" s="12"/>
       <c r="F153" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G153" s="7" t="s">
+      <c r="G153" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H153" s="13"/>
-      <c r="I153" s="13"/>
-      <c r="J153" s="9">
-        <v>60</v>
-      </c>
-      <c r="K153" s="10" t="s">
+      <c r="H153" s="12"/>
+      <c r="I153" s="12"/>
+      <c r="J153" s="8">
+        <v>60</v>
+      </c>
+      <c r="K153" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7094,19 +7091,19 @@
       <c r="D154" s="3">
         <v>10</v>
       </c>
-      <c r="E154" s="13"/>
+      <c r="E154" s="12"/>
       <c r="F154" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G154" s="7" t="s">
+      <c r="G154" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H154" s="13"/>
-      <c r="I154" s="13"/>
-      <c r="J154" s="9">
-        <v>60</v>
-      </c>
-      <c r="K154" s="10" t="s">
+      <c r="H154" s="12"/>
+      <c r="I154" s="12"/>
+      <c r="J154" s="8">
+        <v>60</v>
+      </c>
+      <c r="K154" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7124,21 +7121,21 @@
       <c r="D155" s="3">
         <v>1</v>
       </c>
-      <c r="E155" s="13"/>
+      <c r="E155" s="12"/>
       <c r="F155" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G155" s="7"/>
-      <c r="H155" s="14">
+      <c r="G155" s="6"/>
+      <c r="H155" s="13">
         <v>4030001</v>
       </c>
-      <c r="I155" s="7">
+      <c r="I155" s="6">
         <v>100300</v>
       </c>
-      <c r="J155" s="9">
-        <v>60</v>
-      </c>
-      <c r="K155" s="10" t="s">
+      <c r="J155" s="8">
+        <v>60</v>
+      </c>
+      <c r="K155" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7156,21 +7153,21 @@
       <c r="D156" s="3">
         <v>2</v>
       </c>
-      <c r="E156" s="13"/>
+      <c r="E156" s="12"/>
       <c r="F156" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G156" s="7"/>
-      <c r="H156" s="14">
+      <c r="G156" s="6"/>
+      <c r="H156" s="13">
         <v>4030002</v>
       </c>
-      <c r="I156" s="7">
+      <c r="I156" s="6">
         <v>103400</v>
       </c>
-      <c r="J156" s="9">
-        <v>60</v>
-      </c>
-      <c r="K156" s="10" t="s">
+      <c r="J156" s="8">
+        <v>60</v>
+      </c>
+      <c r="K156" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7188,21 +7185,21 @@
       <c r="D157" s="3">
         <v>3</v>
       </c>
-      <c r="E157" s="13"/>
+      <c r="E157" s="12"/>
       <c r="F157" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G157" s="7"/>
-      <c r="H157" s="14">
+      <c r="G157" s="6"/>
+      <c r="H157" s="13">
         <v>4030003</v>
       </c>
-      <c r="I157" s="7">
+      <c r="I157" s="6">
         <v>103500</v>
       </c>
-      <c r="J157" s="9">
-        <v>60</v>
-      </c>
-      <c r="K157" s="10" t="s">
+      <c r="J157" s="8">
+        <v>60</v>
+      </c>
+      <c r="K157" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7220,21 +7217,21 @@
       <c r="D158" s="3">
         <v>4</v>
       </c>
-      <c r="E158" s="13"/>
+      <c r="E158" s="12"/>
       <c r="F158" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G158" s="7"/>
-      <c r="H158" s="14">
+      <c r="G158" s="6"/>
+      <c r="H158" s="13">
         <v>4030004</v>
       </c>
-      <c r="I158" s="7">
+      <c r="I158" s="6">
         <v>103500</v>
       </c>
-      <c r="J158" s="9">
-        <v>60</v>
-      </c>
-      <c r="K158" s="10" t="s">
+      <c r="J158" s="8">
+        <v>60</v>
+      </c>
+      <c r="K158" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7252,21 +7249,21 @@
       <c r="D159" s="3">
         <v>5</v>
       </c>
-      <c r="E159" s="13"/>
+      <c r="E159" s="12"/>
       <c r="F159" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G159" s="7"/>
-      <c r="H159" s="14">
+      <c r="G159" s="6"/>
+      <c r="H159" s="13">
         <v>4030005</v>
       </c>
-      <c r="I159" s="7">
+      <c r="I159" s="6">
         <v>103500</v>
       </c>
-      <c r="J159" s="9">
-        <v>60</v>
-      </c>
-      <c r="K159" s="10" t="s">
+      <c r="J159" s="8">
+        <v>60</v>
+      </c>
+      <c r="K159" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7284,21 +7281,21 @@
       <c r="D160" s="3">
         <v>6</v>
       </c>
-      <c r="E160" s="13"/>
+      <c r="E160" s="12"/>
       <c r="F160" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G160" s="7"/>
-      <c r="H160" s="14">
+      <c r="G160" s="6"/>
+      <c r="H160" s="13">
         <v>4030006</v>
       </c>
-      <c r="I160" s="7">
+      <c r="I160" s="6">
         <v>103500</v>
       </c>
-      <c r="J160" s="9">
-        <v>60</v>
-      </c>
-      <c r="K160" s="10" t="s">
+      <c r="J160" s="8">
+        <v>60</v>
+      </c>
+      <c r="K160" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7316,21 +7313,21 @@
       <c r="D161" s="3">
         <v>7</v>
       </c>
-      <c r="E161" s="13"/>
+      <c r="E161" s="12"/>
       <c r="F161" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G161" s="7"/>
-      <c r="H161" s="14">
+      <c r="G161" s="6"/>
+      <c r="H161" s="13">
         <v>4030007</v>
       </c>
-      <c r="I161" s="7">
+      <c r="I161" s="6">
         <v>103500</v>
       </c>
-      <c r="J161" s="9">
-        <v>60</v>
-      </c>
-      <c r="K161" s="10" t="s">
+      <c r="J161" s="8">
+        <v>60</v>
+      </c>
+      <c r="K161" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7348,21 +7345,21 @@
       <c r="D162" s="3">
         <v>8</v>
       </c>
-      <c r="E162" s="13"/>
+      <c r="E162" s="12"/>
       <c r="F162" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G162" s="7"/>
-      <c r="H162" s="14">
+      <c r="G162" s="6"/>
+      <c r="H162" s="13">
         <v>4030008</v>
       </c>
-      <c r="I162" s="7">
+      <c r="I162" s="6">
         <v>103500</v>
       </c>
-      <c r="J162" s="9">
-        <v>60</v>
-      </c>
-      <c r="K162" s="10" t="s">
+      <c r="J162" s="8">
+        <v>60</v>
+      </c>
+      <c r="K162" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7377,24 +7374,24 @@
       <c r="C163" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="10">
         <v>9</v>
       </c>
-      <c r="E163" s="13"/>
+      <c r="E163" s="12"/>
       <c r="F163" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G163" s="7"/>
-      <c r="H163" s="14">
+      <c r="G163" s="6"/>
+      <c r="H163" s="13">
         <v>4030009</v>
       </c>
-      <c r="I163" s="7">
+      <c r="I163" s="6">
         <v>103500</v>
       </c>
-      <c r="J163" s="9">
-        <v>60</v>
-      </c>
-      <c r="K163" s="10" t="s">
+      <c r="J163" s="8">
+        <v>60</v>
+      </c>
+      <c r="K163" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7412,21 +7409,21 @@
       <c r="D164" s="3">
         <v>10</v>
       </c>
-      <c r="E164" s="13"/>
+      <c r="E164" s="12"/>
       <c r="F164" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G164" s="7"/>
-      <c r="H164" s="14">
+      <c r="G164" s="6"/>
+      <c r="H164" s="13">
         <v>4030010</v>
       </c>
-      <c r="I164" s="7">
+      <c r="I164" s="6">
         <v>103500</v>
       </c>
-      <c r="J164" s="9">
-        <v>60</v>
-      </c>
-      <c r="K164" s="10" t="s">
+      <c r="J164" s="8">
+        <v>60</v>
+      </c>
+      <c r="K164" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7444,19 +7441,19 @@
       <c r="D165" s="3">
         <v>1</v>
       </c>
-      <c r="E165" s="13"/>
+      <c r="E165" s="12"/>
       <c r="F165" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G165" s="7" t="s">
+      <c r="G165" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H165" s="13"/>
-      <c r="I165" s="13"/>
-      <c r="J165" s="9">
-        <v>60</v>
-      </c>
-      <c r="K165" s="10" t="s">
+      <c r="H165" s="12"/>
+      <c r="I165" s="12"/>
+      <c r="J165" s="8">
+        <v>60</v>
+      </c>
+      <c r="K165" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7474,19 +7471,19 @@
       <c r="D166" s="3">
         <v>2</v>
       </c>
-      <c r="E166" s="13"/>
+      <c r="E166" s="12"/>
       <c r="F166" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G166" s="7" t="s">
+      <c r="G166" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H166" s="13"/>
-      <c r="I166" s="13"/>
-      <c r="J166" s="9">
-        <v>60</v>
-      </c>
-      <c r="K166" s="10" t="s">
+      <c r="H166" s="12"/>
+      <c r="I166" s="12"/>
+      <c r="J166" s="8">
+        <v>60</v>
+      </c>
+      <c r="K166" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7504,19 +7501,19 @@
       <c r="D167" s="3">
         <v>3</v>
       </c>
-      <c r="E167" s="13"/>
+      <c r="E167" s="12"/>
       <c r="F167" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G167" s="7" t="s">
+      <c r="G167" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H167" s="13"/>
-      <c r="I167" s="13"/>
-      <c r="J167" s="9">
-        <v>60</v>
-      </c>
-      <c r="K167" s="10" t="s">
+      <c r="H167" s="12"/>
+      <c r="I167" s="12"/>
+      <c r="J167" s="8">
+        <v>60</v>
+      </c>
+      <c r="K167" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7534,19 +7531,19 @@
       <c r="D168" s="3">
         <v>4</v>
       </c>
-      <c r="E168" s="13"/>
+      <c r="E168" s="12"/>
       <c r="F168" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G168" s="7" t="s">
+      <c r="G168" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H168" s="13"/>
-      <c r="I168" s="13"/>
-      <c r="J168" s="9">
-        <v>60</v>
-      </c>
-      <c r="K168" s="10" t="s">
+      <c r="H168" s="12"/>
+      <c r="I168" s="12"/>
+      <c r="J168" s="8">
+        <v>60</v>
+      </c>
+      <c r="K168" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7564,19 +7561,19 @@
       <c r="D169" s="3">
         <v>5</v>
       </c>
-      <c r="E169" s="13"/>
+      <c r="E169" s="12"/>
       <c r="F169" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G169" s="7" t="s">
+      <c r="G169" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="H169" s="13"/>
-      <c r="I169" s="13"/>
-      <c r="J169" s="9">
-        <v>60</v>
-      </c>
-      <c r="K169" s="10" t="s">
+      <c r="H169" s="12"/>
+      <c r="I169" s="12"/>
+      <c r="J169" s="8">
+        <v>60</v>
+      </c>
+      <c r="K169" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7594,19 +7591,19 @@
       <c r="D170" s="3">
         <v>6</v>
       </c>
-      <c r="E170" s="13"/>
+      <c r="E170" s="12"/>
       <c r="F170" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G170" s="7" t="s">
+      <c r="G170" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H170" s="13"/>
-      <c r="I170" s="13"/>
-      <c r="J170" s="9">
-        <v>60</v>
-      </c>
-      <c r="K170" s="10" t="s">
+      <c r="H170" s="12"/>
+      <c r="I170" s="12"/>
+      <c r="J170" s="8">
+        <v>60</v>
+      </c>
+      <c r="K170" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7624,19 +7621,19 @@
       <c r="D171" s="3">
         <v>7</v>
       </c>
-      <c r="E171" s="13"/>
+      <c r="E171" s="12"/>
       <c r="F171" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G171" s="7" t="s">
+      <c r="G171" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="H171" s="13"/>
-      <c r="I171" s="13"/>
-      <c r="J171" s="9">
-        <v>60</v>
-      </c>
-      <c r="K171" s="10" t="s">
+      <c r="H171" s="12"/>
+      <c r="I171" s="12"/>
+      <c r="J171" s="8">
+        <v>60</v>
+      </c>
+      <c r="K171" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7654,19 +7651,19 @@
       <c r="D172" s="3">
         <v>8</v>
       </c>
-      <c r="E172" s="13"/>
+      <c r="E172" s="12"/>
       <c r="F172" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G172" s="7" t="s">
+      <c r="G172" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="H172" s="13"/>
-      <c r="I172" s="13"/>
-      <c r="J172" s="9">
-        <v>60</v>
-      </c>
-      <c r="K172" s="10" t="s">
+      <c r="H172" s="12"/>
+      <c r="I172" s="12"/>
+      <c r="J172" s="8">
+        <v>60</v>
+      </c>
+      <c r="K172" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7681,22 +7678,22 @@
       <c r="C173" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D173" s="10">
         <v>9</v>
       </c>
-      <c r="E173" s="13"/>
+      <c r="E173" s="12"/>
       <c r="F173" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G173" s="7" t="s">
+      <c r="G173" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H173" s="13"/>
-      <c r="I173" s="13"/>
-      <c r="J173" s="9">
-        <v>60</v>
-      </c>
-      <c r="K173" s="10" t="s">
+      <c r="H173" s="12"/>
+      <c r="I173" s="12"/>
+      <c r="J173" s="8">
+        <v>60</v>
+      </c>
+      <c r="K173" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7714,19 +7711,19 @@
       <c r="D174" s="3">
         <v>10</v>
       </c>
-      <c r="E174" s="13"/>
+      <c r="E174" s="12"/>
       <c r="F174" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G174" s="7" t="s">
+      <c r="G174" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="H174" s="13"/>
-      <c r="I174" s="13"/>
-      <c r="J174" s="9">
-        <v>60</v>
-      </c>
-      <c r="K174" s="10" t="s">
+      <c r="H174" s="12"/>
+      <c r="I174" s="12"/>
+      <c r="J174" s="8">
+        <v>60</v>
+      </c>
+      <c r="K174" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7744,19 +7741,19 @@
       <c r="D175" s="3">
         <v>1</v>
       </c>
-      <c r="E175" s="13"/>
+      <c r="E175" s="12"/>
       <c r="F175" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G175" s="7" t="s">
+      <c r="G175" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="H175" s="13"/>
-      <c r="I175" s="13"/>
-      <c r="J175" s="9">
-        <v>60</v>
-      </c>
-      <c r="K175" s="10" t="s">
+      <c r="H175" s="12"/>
+      <c r="I175" s="12"/>
+      <c r="J175" s="8">
+        <v>60</v>
+      </c>
+      <c r="K175" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7774,19 +7771,19 @@
       <c r="D176" s="3">
         <v>2</v>
       </c>
-      <c r="E176" s="13"/>
+      <c r="E176" s="12"/>
       <c r="F176" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G176" s="7" t="s">
+      <c r="G176" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="H176" s="13"/>
-      <c r="I176" s="13"/>
-      <c r="J176" s="9">
-        <v>60</v>
-      </c>
-      <c r="K176" s="10" t="s">
+      <c r="H176" s="12"/>
+      <c r="I176" s="12"/>
+      <c r="J176" s="8">
+        <v>60</v>
+      </c>
+      <c r="K176" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7804,19 +7801,19 @@
       <c r="D177" s="3">
         <v>3</v>
       </c>
-      <c r="E177" s="13"/>
+      <c r="E177" s="12"/>
       <c r="F177" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G177" s="7" t="s">
+      <c r="G177" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="H177" s="13"/>
-      <c r="I177" s="13"/>
-      <c r="J177" s="9">
-        <v>60</v>
-      </c>
-      <c r="K177" s="10" t="s">
+      <c r="H177" s="12"/>
+      <c r="I177" s="12"/>
+      <c r="J177" s="8">
+        <v>60</v>
+      </c>
+      <c r="K177" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7834,19 +7831,19 @@
       <c r="D178" s="3">
         <v>4</v>
       </c>
-      <c r="E178" s="13"/>
+      <c r="E178" s="12"/>
       <c r="F178" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G178" s="7" t="s">
+      <c r="G178" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H178" s="13"/>
-      <c r="I178" s="13"/>
-      <c r="J178" s="9">
-        <v>60</v>
-      </c>
-      <c r="K178" s="10" t="s">
+      <c r="H178" s="12"/>
+      <c r="I178" s="12"/>
+      <c r="J178" s="8">
+        <v>60</v>
+      </c>
+      <c r="K178" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7864,19 +7861,19 @@
       <c r="D179" s="3">
         <v>5</v>
       </c>
-      <c r="E179" s="13"/>
+      <c r="E179" s="12"/>
       <c r="F179" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G179" s="7" t="s">
+      <c r="G179" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="H179" s="13"/>
-      <c r="I179" s="13"/>
-      <c r="J179" s="9">
-        <v>60</v>
-      </c>
-      <c r="K179" s="10" t="s">
+      <c r="H179" s="12"/>
+      <c r="I179" s="12"/>
+      <c r="J179" s="8">
+        <v>60</v>
+      </c>
+      <c r="K179" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7894,19 +7891,19 @@
       <c r="D180" s="3">
         <v>6</v>
       </c>
-      <c r="E180" s="13"/>
+      <c r="E180" s="12"/>
       <c r="F180" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G180" s="7" t="s">
+      <c r="G180" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="H180" s="13"/>
-      <c r="I180" s="13"/>
-      <c r="J180" s="9">
-        <v>60</v>
-      </c>
-      <c r="K180" s="10" t="s">
+      <c r="H180" s="12"/>
+      <c r="I180" s="12"/>
+      <c r="J180" s="8">
+        <v>60</v>
+      </c>
+      <c r="K180" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7924,19 +7921,19 @@
       <c r="D181" s="3">
         <v>7</v>
       </c>
-      <c r="E181" s="13"/>
+      <c r="E181" s="12"/>
       <c r="F181" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G181" s="7" t="s">
+      <c r="G181" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H181" s="13"/>
-      <c r="I181" s="13"/>
-      <c r="J181" s="9">
-        <v>60</v>
-      </c>
-      <c r="K181" s="10" t="s">
+      <c r="H181" s="12"/>
+      <c r="I181" s="12"/>
+      <c r="J181" s="8">
+        <v>60</v>
+      </c>
+      <c r="K181" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7954,19 +7951,19 @@
       <c r="D182" s="3">
         <v>8</v>
       </c>
-      <c r="E182" s="13"/>
+      <c r="E182" s="12"/>
       <c r="F182" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G182" s="7" t="s">
+      <c r="G182" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H182" s="13"/>
-      <c r="I182" s="13"/>
-      <c r="J182" s="9">
-        <v>60</v>
-      </c>
-      <c r="K182" s="10" t="s">
+      <c r="H182" s="12"/>
+      <c r="I182" s="12"/>
+      <c r="J182" s="8">
+        <v>60</v>
+      </c>
+      <c r="K182" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7981,22 +7978,22 @@
       <c r="C183" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="10">
         <v>9</v>
       </c>
-      <c r="E183" s="13"/>
+      <c r="E183" s="12"/>
       <c r="F183" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G183" s="7" t="s">
+      <c r="G183" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H183" s="13"/>
-      <c r="I183" s="13"/>
-      <c r="J183" s="9">
-        <v>60</v>
-      </c>
-      <c r="K183" s="10" t="s">
+      <c r="H183" s="12"/>
+      <c r="I183" s="12"/>
+      <c r="J183" s="8">
+        <v>60</v>
+      </c>
+      <c r="K183" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -8014,19 +8011,19 @@
       <c r="D184" s="3">
         <v>10</v>
       </c>
-      <c r="E184" s="13"/>
+      <c r="E184" s="12"/>
       <c r="F184" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G184" s="7" t="s">
+      <c r="G184" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H184" s="13"/>
-      <c r="I184" s="13"/>
-      <c r="J184" s="9">
-        <v>60</v>
-      </c>
-      <c r="K184" s="10" t="s">
+      <c r="H184" s="12"/>
+      <c r="I184" s="12"/>
+      <c r="J184" s="8">
+        <v>60</v>
+      </c>
+      <c r="K184" s="9" t="s">
         <v>28</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -1341,11 +1341,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1372,12 +1369,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1389,21 +1380,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1936,6080 +1912,6092 @@
   <dimension ref="A1:K184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="14.875" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.625" style="2" customWidth="1"/>
-    <col min="8" max="9" width="20.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="24" style="2" customWidth="1"/>
-    <col min="11" max="11" width="32" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="14.875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A5" s="10">
+      <c r="A5" s="4">
         <f>B5*1000+D5</f>
         <v>1101001</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="4">
         <v>1101</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="7">
         <v>1000</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12">
-        <v>60</v>
-      </c>
-      <c r="K5" s="13" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="9">
+        <v>60</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A6" s="10">
+      <c r="A6" s="4">
         <f t="shared" ref="A6:A69" si="0">B6*1000+D6</f>
         <v>1101002</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="4">
         <v>1101</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="4">
         <v>2</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="4">
         <v>4</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="7">
         <v>1100</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="12">
-        <v>60</v>
-      </c>
-      <c r="K6" s="13" t="s">
+      <c r="J6" s="9">
+        <v>60</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A7" s="10">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1101003</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="4">
         <v>1101</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="4">
         <v>6</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="7">
         <v>2000</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="12">
-        <v>60</v>
-      </c>
-      <c r="K7" s="13" t="s">
+      <c r="J7" s="9">
+        <v>60</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A8" s="10">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1101004</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="4">
         <v>1101</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="4">
         <v>4</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="4">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="7">
         <v>3000</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="12">
-        <v>60</v>
-      </c>
-      <c r="K8" s="13" t="s">
+      <c r="J8" s="9">
+        <v>60</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A9" s="10">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1101005</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="4">
         <v>1101</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="4">
         <v>5</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="4">
         <v>10</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="7">
         <v>4500</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11" t="s">
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="12">
-        <v>60</v>
-      </c>
-      <c r="K9" s="13" t="s">
+      <c r="J9" s="9">
+        <v>60</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A10" s="10">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1101006</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="4">
         <v>1101</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="4">
         <v>6</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="4">
         <v>12</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="7">
         <v>6000</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11" t="s">
+      <c r="H10" s="7"/>
+      <c r="I10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="12">
-        <v>60</v>
-      </c>
-      <c r="K10" s="13" t="s">
+      <c r="J10" s="9">
+        <v>60</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A11" s="10">
+      <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1101007</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="4">
         <v>1101</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="4">
         <v>7</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="4">
         <v>14</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="7">
         <v>9000</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11" t="s">
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="12">
-        <v>60</v>
-      </c>
-      <c r="K11" s="13" t="s">
+      <c r="J11" s="9">
+        <v>60</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A12" s="10">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1101008</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="4">
         <v>1101</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="4">
         <v>8</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="4">
         <v>16</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="7">
         <v>15000</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11" t="s">
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="12">
-        <v>60</v>
-      </c>
-      <c r="K12" s="13" t="s">
+      <c r="J12" s="9">
+        <v>60</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A13" s="10">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1101009</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="4">
         <v>1101</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="11">
         <v>9</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="4">
         <v>18</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="7">
         <v>30000</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="11" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="12">
-        <v>60</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="J13" s="9">
+        <v>60</v>
+      </c>
+      <c r="K13" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A14" s="10">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1101010</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="4">
         <v>1101</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="4">
         <v>10</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="4">
         <v>20</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="7">
         <v>10000</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11" t="s">
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="12">
-        <v>60</v>
-      </c>
-      <c r="K14" s="13" t="s">
+      <c r="J14" s="9">
+        <v>60</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1102001</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>1102</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="7">
         <v>1000</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="16">
-        <v>60</v>
-      </c>
-      <c r="K15" s="17" t="s">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="9">
+        <v>60</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1102002</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>1102</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="4">
         <v>4</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="7">
         <v>1100</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="16">
-        <v>60</v>
-      </c>
-      <c r="K16" s="17" t="s">
+      <c r="J16" s="9">
+        <v>60</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1102003</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>1102</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>3</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="4">
         <v>6</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="7">
         <v>2000</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="16">
-        <v>60</v>
-      </c>
-      <c r="K17" s="17" t="s">
+      <c r="J17" s="9">
+        <v>60</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1102004</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>1102</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>4</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="4">
         <v>8</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="7">
         <v>3000</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="16">
-        <v>60</v>
-      </c>
-      <c r="K18" s="17" t="s">
+      <c r="J18" s="9">
+        <v>60</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:11">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1102005</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>1102</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>5</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="4">
         <v>10</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="7">
         <v>4500</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J19" s="16">
-        <v>60</v>
-      </c>
-      <c r="K19" s="17" t="s">
+      <c r="J19" s="9">
+        <v>60</v>
+      </c>
+      <c r="K19" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1102006</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>1102</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>6</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="4">
         <v>12</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="7">
         <v>6000</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8" t="s">
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="16">
-        <v>60</v>
-      </c>
-      <c r="K20" s="17" t="s">
+      <c r="J20" s="9">
+        <v>60</v>
+      </c>
+      <c r="K20" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1102007</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>1102</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>7</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="4">
         <v>14</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="7">
         <v>9000</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="16">
-        <v>60</v>
-      </c>
-      <c r="K21" s="17" t="s">
+      <c r="J21" s="9">
+        <v>60</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>1102008</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>1102</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>8</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="4">
         <v>16</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="7">
         <v>15000</v>
       </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="s">
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="16">
-        <v>60</v>
-      </c>
-      <c r="K22" s="17" t="s">
+      <c r="J22" s="9">
+        <v>60</v>
+      </c>
+      <c r="K22" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>1102009</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>1102</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="11">
         <v>9</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="4">
         <v>18</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="7">
         <v>30000</v>
       </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="12"/>
+      <c r="I23" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="16">
-        <v>60</v>
-      </c>
-      <c r="K23" s="17" t="s">
+      <c r="J23" s="9">
+        <v>60</v>
+      </c>
+      <c r="K23" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>1102010</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>1102</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>10</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="4">
         <v>20</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="7">
         <v>10000</v>
       </c>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8" t="s">
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J24" s="16">
-        <v>60</v>
-      </c>
-      <c r="K24" s="17" t="s">
+      <c r="J24" s="9">
+        <v>60</v>
+      </c>
+      <c r="K24" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:11">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>1103001</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>1103</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="7">
         <v>1000</v>
       </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="16">
-        <v>60</v>
-      </c>
-      <c r="K25" s="17" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="9">
+        <v>60</v>
+      </c>
+      <c r="K25" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:11">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>1103002</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>1103</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>2</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="4">
         <v>4</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="7">
         <v>1100</v>
       </c>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8" t="s">
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J26" s="16">
-        <v>60</v>
-      </c>
-      <c r="K26" s="17" t="s">
+      <c r="J26" s="9">
+        <v>60</v>
+      </c>
+      <c r="K26" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>1103003</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>1103</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>3</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="4">
         <v>6</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="7">
         <v>2000</v>
       </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8" t="s">
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="16">
-        <v>60</v>
-      </c>
-      <c r="K27" s="17" t="s">
+      <c r="J27" s="9">
+        <v>60</v>
+      </c>
+      <c r="K27" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>1103004</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>1103</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>4</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="4">
         <v>8</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="7">
         <v>3000</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J28" s="16">
-        <v>60</v>
-      </c>
-      <c r="K28" s="17" t="s">
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J28" s="9">
+        <v>60</v>
+      </c>
+      <c r="K28" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>1103005</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>1103</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>5</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="4">
         <v>10</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="7">
         <v>4500</v>
       </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="s">
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J29" s="16">
-        <v>60</v>
-      </c>
-      <c r="K29" s="17" t="s">
+      <c r="J29" s="9">
+        <v>60</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>1103006</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>1103</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>6</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="4">
         <v>12</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="7">
         <v>6000</v>
       </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8" t="s">
+      <c r="H30" s="7"/>
+      <c r="I30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J30" s="16">
-        <v>60</v>
-      </c>
-      <c r="K30" s="17" t="s">
+      <c r="J30" s="9">
+        <v>60</v>
+      </c>
+      <c r="K30" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:11">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>1103007</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>1103</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>7</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="4">
         <v>14</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="7">
         <v>9000</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8" t="s">
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J31" s="16">
-        <v>60</v>
-      </c>
-      <c r="K31" s="17" t="s">
+      <c r="J31" s="9">
+        <v>60</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:11">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>1103008</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>1103</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>8</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="4">
         <v>16</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="7">
         <v>15000</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8" t="s">
+      <c r="H32" s="7"/>
+      <c r="I32" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="16">
-        <v>60</v>
-      </c>
-      <c r="K32" s="17" t="s">
+      <c r="J32" s="9">
+        <v>60</v>
+      </c>
+      <c r="K32" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:11">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>1103009</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>1103</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="11">
         <v>9</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="4">
         <v>18</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="7">
         <v>30000</v>
       </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="8" t="s">
+      <c r="H33" s="12"/>
+      <c r="I33" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J33" s="16">
-        <v>60</v>
-      </c>
-      <c r="K33" s="17" t="s">
+      <c r="J33" s="9">
+        <v>60</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:11">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>1103010</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>1103</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>10</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="4">
         <v>20</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="7">
         <v>10000</v>
       </c>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8" t="s">
+      <c r="H34" s="7"/>
+      <c r="I34" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J34" s="16">
-        <v>60</v>
-      </c>
-      <c r="K34" s="17" t="s">
+      <c r="J34" s="9">
+        <v>60</v>
+      </c>
+      <c r="K34" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:11">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <f t="shared" si="0"/>
         <v>1104001</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>1104</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="4">
         <v>2</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="7">
         <v>1000</v>
       </c>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="16">
-        <v>60</v>
-      </c>
-      <c r="K35" s="17" t="s">
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="9">
+        <v>60</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:11">
-      <c r="A36" s="5">
+      <c r="A36" s="4">
         <f t="shared" si="0"/>
         <v>1104002</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>1104</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="4">
         <v>2</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="4">
         <v>4</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="7">
         <v>1100</v>
       </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8" t="s">
+      <c r="H36" s="7"/>
+      <c r="I36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J36" s="16">
-        <v>60</v>
-      </c>
-      <c r="K36" s="17" t="s">
+      <c r="J36" s="9">
+        <v>60</v>
+      </c>
+      <c r="K36" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:11">
-      <c r="A37" s="5">
+      <c r="A37" s="4">
         <f t="shared" si="0"/>
         <v>1104003</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>1104</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="4">
         <v>3</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="4">
         <v>6</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="7">
         <v>2000</v>
       </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8" t="s">
+      <c r="H37" s="7"/>
+      <c r="I37" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J37" s="16">
-        <v>60</v>
-      </c>
-      <c r="K37" s="17" t="s">
+      <c r="J37" s="9">
+        <v>60</v>
+      </c>
+      <c r="K37" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:11">
-      <c r="A38" s="5">
+      <c r="A38" s="4">
         <f t="shared" si="0"/>
         <v>1104004</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="4">
         <v>1104</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="4">
         <v>4</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="4">
         <v>8</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="7">
         <v>3000</v>
       </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8" t="s">
+      <c r="H38" s="7"/>
+      <c r="I38" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="16">
-        <v>60</v>
-      </c>
-      <c r="K38" s="17" t="s">
+      <c r="J38" s="9">
+        <v>60</v>
+      </c>
+      <c r="K38" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:11">
-      <c r="A39" s="5">
+      <c r="A39" s="4">
         <f t="shared" si="0"/>
         <v>1104005</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>1104</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="4">
         <v>5</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="4">
         <v>10</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="7">
         <v>4500</v>
       </c>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8" t="s">
+      <c r="H39" s="7"/>
+      <c r="I39" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="16">
-        <v>60</v>
-      </c>
-      <c r="K39" s="17" t="s">
+      <c r="J39" s="9">
+        <v>60</v>
+      </c>
+      <c r="K39" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:11">
-      <c r="A40" s="5">
+      <c r="A40" s="4">
         <f t="shared" si="0"/>
         <v>1104006</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>1104</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="4">
         <v>6</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="4">
         <v>12</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="7">
         <v>6000</v>
       </c>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8" t="s">
+      <c r="H40" s="7"/>
+      <c r="I40" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J40" s="16">
-        <v>60</v>
-      </c>
-      <c r="K40" s="17" t="s">
+      <c r="J40" s="9">
+        <v>60</v>
+      </c>
+      <c r="K40" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:11">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <f t="shared" si="0"/>
         <v>1104007</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <v>1104</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="4">
         <v>7</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="4">
         <v>14</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="7">
         <v>9000</v>
       </c>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8" t="s">
+      <c r="H41" s="7"/>
+      <c r="I41" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J41" s="16">
-        <v>60</v>
-      </c>
-      <c r="K41" s="17" t="s">
+      <c r="J41" s="9">
+        <v>60</v>
+      </c>
+      <c r="K41" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:11">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <f t="shared" si="0"/>
         <v>1104008</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <v>1104</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="4">
         <v>8</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="4">
         <v>16</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="7">
         <v>15000</v>
       </c>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8" t="s">
+      <c r="H42" s="7"/>
+      <c r="I42" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J42" s="16">
-        <v>60</v>
-      </c>
-      <c r="K42" s="17" t="s">
+      <c r="J42" s="9">
+        <v>60</v>
+      </c>
+      <c r="K42" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:11">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <f t="shared" si="0"/>
         <v>1104009</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="4">
         <v>1104</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="11">
         <v>9</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="4">
         <v>18</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="7">
         <v>30000</v>
       </c>
-      <c r="H43" s="19"/>
-      <c r="I43" s="8" t="s">
+      <c r="H43" s="12"/>
+      <c r="I43" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J43" s="16">
-        <v>60</v>
-      </c>
-      <c r="K43" s="17" t="s">
+      <c r="J43" s="9">
+        <v>60</v>
+      </c>
+      <c r="K43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:11">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <f t="shared" si="0"/>
         <v>1104010</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <v>1104</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="4">
         <v>10</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="4">
         <v>20</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="7">
         <v>10000</v>
       </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8" t="s">
+      <c r="H44" s="7"/>
+      <c r="I44" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="J44" s="16">
-        <v>60</v>
-      </c>
-      <c r="K44" s="17" t="s">
+      <c r="J44" s="9">
+        <v>60</v>
+      </c>
+      <c r="K44" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:11">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <f t="shared" si="0"/>
         <v>1105001</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <v>1105</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="4">
         <v>2</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="7">
         <v>1000</v>
       </c>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="16">
-        <v>60</v>
-      </c>
-      <c r="K45" s="17" t="s">
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="9">
+        <v>60</v>
+      </c>
+      <c r="K45" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:11">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <f t="shared" si="0"/>
         <v>1105002</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="4">
         <v>1105</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="4">
         <v>2</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="4">
         <v>4</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="7">
         <v>1100</v>
       </c>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8" t="s">
+      <c r="H46" s="7"/>
+      <c r="I46" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J46" s="16">
-        <v>60</v>
-      </c>
-      <c r="K46" s="17" t="s">
+      <c r="J46" s="9">
+        <v>60</v>
+      </c>
+      <c r="K46" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:11">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <f t="shared" si="0"/>
         <v>1105003</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="4">
         <v>1105</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="4">
         <v>3</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="4">
         <v>6</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="7">
         <v>2000</v>
       </c>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8" t="s">
+      <c r="H47" s="7"/>
+      <c r="I47" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J47" s="16">
-        <v>60</v>
-      </c>
-      <c r="K47" s="17" t="s">
+      <c r="J47" s="9">
+        <v>60</v>
+      </c>
+      <c r="K47" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:11">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <f t="shared" si="0"/>
         <v>1105004</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="4">
         <v>1105</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="4">
         <v>4</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="4">
         <v>8</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="7">
         <v>3000</v>
       </c>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8" t="s">
+      <c r="H48" s="7"/>
+      <c r="I48" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J48" s="16">
-        <v>60</v>
-      </c>
-      <c r="K48" s="17" t="s">
+      <c r="J48" s="9">
+        <v>60</v>
+      </c>
+      <c r="K48" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:11">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <f t="shared" si="0"/>
         <v>1105005</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="4">
         <v>1105</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="4">
         <v>5</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="4">
         <v>10</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="7">
         <v>4500</v>
       </c>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8" t="s">
+      <c r="H49" s="7"/>
+      <c r="I49" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="16">
-        <v>60</v>
-      </c>
-      <c r="K49" s="17" t="s">
+      <c r="J49" s="9">
+        <v>60</v>
+      </c>
+      <c r="K49" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:11">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <f t="shared" si="0"/>
         <v>1105006</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="4">
         <v>1105</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="4">
         <v>6</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="4">
         <v>12</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="7">
         <v>6000</v>
       </c>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8" t="s">
+      <c r="H50" s="7"/>
+      <c r="I50" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J50" s="16">
-        <v>60</v>
-      </c>
-      <c r="K50" s="17" t="s">
+      <c r="J50" s="9">
+        <v>60</v>
+      </c>
+      <c r="K50" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:11">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <f t="shared" si="0"/>
         <v>1105007</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="4">
         <v>1105</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="4">
         <v>7</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="4">
         <v>14</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="7">
         <v>9000</v>
       </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8" t="s">
+      <c r="H51" s="7"/>
+      <c r="I51" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J51" s="16">
-        <v>60</v>
-      </c>
-      <c r="K51" s="17" t="s">
+      <c r="J51" s="9">
+        <v>60</v>
+      </c>
+      <c r="K51" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:11">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <f t="shared" si="0"/>
         <v>1105008</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="4">
         <v>1105</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="4">
         <v>8</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="4">
         <v>16</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="7">
         <v>15000</v>
       </c>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8" t="s">
+      <c r="H52" s="7"/>
+      <c r="I52" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J52" s="16">
-        <v>60</v>
-      </c>
-      <c r="K52" s="17" t="s">
+      <c r="J52" s="9">
+        <v>60</v>
+      </c>
+      <c r="K52" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:11">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <f t="shared" si="0"/>
         <v>1105009</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="4">
         <v>1105</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="18">
+      <c r="D53" s="11">
         <v>9</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="4">
         <v>18</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="7">
         <v>30000</v>
       </c>
-      <c r="H53" s="19"/>
-      <c r="I53" s="8" t="s">
+      <c r="H53" s="12"/>
+      <c r="I53" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J53" s="16">
-        <v>60</v>
-      </c>
-      <c r="K53" s="17" t="s">
+      <c r="J53" s="9">
+        <v>60</v>
+      </c>
+      <c r="K53" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:11">
-      <c r="A54" s="5">
+      <c r="A54" s="4">
         <f t="shared" si="0"/>
         <v>1105010</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="4">
         <v>1105</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="4">
         <v>10</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="4">
         <v>20</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="7">
         <v>10000</v>
       </c>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8" t="s">
+      <c r="H54" s="7"/>
+      <c r="I54" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="J54" s="16">
-        <v>60</v>
-      </c>
-      <c r="K54" s="17" t="s">
+      <c r="J54" s="9">
+        <v>60</v>
+      </c>
+      <c r="K54" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:11">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <f t="shared" si="0"/>
         <v>1106001</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="4">
         <v>1106</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="4">
         <v>2</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="7">
         <v>1000</v>
       </c>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="16">
-        <v>60</v>
-      </c>
-      <c r="K55" s="17" t="s">
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="9">
+        <v>60</v>
+      </c>
+      <c r="K55" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:11">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <f t="shared" si="0"/>
         <v>1106002</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="4">
         <v>1106</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="4">
         <v>2</v>
       </c>
-      <c r="E56" s="10">
+      <c r="E56" s="4">
         <v>4</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="7">
         <v>1100</v>
       </c>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8" t="s">
+      <c r="H56" s="7"/>
+      <c r="I56" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J56" s="16">
-        <v>60</v>
-      </c>
-      <c r="K56" s="17" t="s">
+      <c r="J56" s="9">
+        <v>60</v>
+      </c>
+      <c r="K56" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:11">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <f t="shared" si="0"/>
         <v>1106003</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="4">
         <v>1106</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="4">
         <v>3</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="4">
         <v>6</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="7">
         <v>2000</v>
       </c>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8" t="s">
+      <c r="H57" s="7"/>
+      <c r="I57" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J57" s="16">
-        <v>60</v>
-      </c>
-      <c r="K57" s="17" t="s">
+      <c r="J57" s="9">
+        <v>60</v>
+      </c>
+      <c r="K57" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <f t="shared" si="0"/>
         <v>1106004</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="4">
         <v>1106</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="4">
         <v>4</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="4">
         <v>8</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G58" s="11">
+      <c r="G58" s="7">
         <v>3000</v>
       </c>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8" t="s">
+      <c r="H58" s="7"/>
+      <c r="I58" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="J58" s="16">
-        <v>60</v>
-      </c>
-      <c r="K58" s="17" t="s">
+      <c r="J58" s="9">
+        <v>60</v>
+      </c>
+      <c r="K58" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <f t="shared" si="0"/>
         <v>1106005</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="4">
         <v>1106</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="4">
         <v>5</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E59" s="4">
         <v>10</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G59" s="11">
+      <c r="G59" s="7">
         <v>4500</v>
       </c>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8" t="s">
+      <c r="H59" s="7"/>
+      <c r="I59" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J59" s="16">
-        <v>60</v>
-      </c>
-      <c r="K59" s="17" t="s">
+      <c r="J59" s="9">
+        <v>60</v>
+      </c>
+      <c r="K59" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <f t="shared" si="0"/>
         <v>1106006</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="4">
         <v>1106</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="4">
         <v>6</v>
       </c>
-      <c r="E60" s="10">
+      <c r="E60" s="4">
         <v>12</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G60" s="11">
+      <c r="G60" s="7">
         <v>6000</v>
       </c>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8" t="s">
+      <c r="H60" s="7"/>
+      <c r="I60" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J60" s="16">
-        <v>60</v>
-      </c>
-      <c r="K60" s="17" t="s">
+      <c r="J60" s="9">
+        <v>60</v>
+      </c>
+      <c r="K60" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <f t="shared" si="0"/>
         <v>1106007</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="4">
         <v>1106</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="4">
         <v>7</v>
       </c>
-      <c r="E61" s="10">
+      <c r="E61" s="4">
         <v>14</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G61" s="11">
+      <c r="G61" s="7">
         <v>9000</v>
       </c>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8" t="s">
+      <c r="H61" s="7"/>
+      <c r="I61" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="J61" s="16">
-        <v>60</v>
-      </c>
-      <c r="K61" s="17" t="s">
+      <c r="J61" s="9">
+        <v>60</v>
+      </c>
+      <c r="K61" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <f t="shared" si="0"/>
         <v>1106008</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="4">
         <v>1106</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="4">
         <v>8</v>
       </c>
-      <c r="E62" s="10">
+      <c r="E62" s="4">
         <v>16</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="7">
         <v>15000</v>
       </c>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8" t="s">
+      <c r="H62" s="7"/>
+      <c r="I62" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J62" s="16">
-        <v>60</v>
-      </c>
-      <c r="K62" s="17" t="s">
+      <c r="J62" s="9">
+        <v>60</v>
+      </c>
+      <c r="K62" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <f t="shared" si="0"/>
         <v>1106009</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="4">
         <v>1106</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="11">
         <v>9</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="4">
         <v>18</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G63" s="11">
+      <c r="G63" s="7">
         <v>30000</v>
       </c>
-      <c r="H63" s="19"/>
-      <c r="I63" s="8" t="s">
+      <c r="H63" s="12"/>
+      <c r="I63" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J63" s="16">
-        <v>60</v>
-      </c>
-      <c r="K63" s="17" t="s">
+      <c r="J63" s="9">
+        <v>60</v>
+      </c>
+      <c r="K63" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <f t="shared" si="0"/>
         <v>1106010</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="4">
         <v>1106</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="4">
         <v>10</v>
       </c>
-      <c r="E64" s="10">
+      <c r="E64" s="4">
         <v>20</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="F64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="7">
         <v>10000</v>
       </c>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8" t="s">
+      <c r="H64" s="7"/>
+      <c r="I64" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J64" s="16">
-        <v>60</v>
-      </c>
-      <c r="K64" s="17" t="s">
+      <c r="J64" s="9">
+        <v>60</v>
+      </c>
+      <c r="K64" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:11">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <f t="shared" si="0"/>
         <v>1107001</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="4">
         <v>1107</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="10">
+      <c r="E65" s="4">
         <v>2</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G65" s="11">
+      <c r="G65" s="7">
         <v>1000</v>
       </c>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="16">
-        <v>60</v>
-      </c>
-      <c r="K65" s="17" t="s">
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="9">
+        <v>60</v>
+      </c>
+      <c r="K65" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:11">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <f t="shared" si="0"/>
         <v>1107002</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="4">
         <v>1107</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="4">
         <v>2</v>
       </c>
-      <c r="E66" s="10">
+      <c r="E66" s="4">
         <v>4</v>
       </c>
-      <c r="F66" s="10" t="s">
+      <c r="F66" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G66" s="7">
         <v>1100</v>
       </c>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8" t="s">
+      <c r="H66" s="7"/>
+      <c r="I66" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="J66" s="16">
-        <v>60</v>
-      </c>
-      <c r="K66" s="17" t="s">
+      <c r="J66" s="9">
+        <v>60</v>
+      </c>
+      <c r="K66" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <f t="shared" si="0"/>
         <v>1107003</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="4">
         <v>1107</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="4">
         <v>3</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E67" s="4">
         <v>6</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G67" s="7">
         <v>2000</v>
       </c>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8" t="s">
+      <c r="H67" s="7"/>
+      <c r="I67" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J67" s="16">
-        <v>60</v>
-      </c>
-      <c r="K67" s="17" t="s">
+      <c r="J67" s="9">
+        <v>60</v>
+      </c>
+      <c r="K67" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:11">
-      <c r="A68" s="5">
+      <c r="A68" s="4">
         <f t="shared" si="0"/>
         <v>1107004</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="4">
         <v>1107</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="4">
         <v>4</v>
       </c>
-      <c r="E68" s="10">
+      <c r="E68" s="4">
         <v>8</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="7">
         <v>3000</v>
       </c>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8" t="s">
+      <c r="H68" s="7"/>
+      <c r="I68" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J68" s="16">
-        <v>60</v>
-      </c>
-      <c r="K68" s="17" t="s">
+      <c r="J68" s="9">
+        <v>60</v>
+      </c>
+      <c r="K68" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:11">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <f t="shared" si="0"/>
         <v>1107005</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="4">
         <v>1107</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="4">
         <v>5</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="4">
         <v>10</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="7">
         <v>4500</v>
       </c>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8" t="s">
+      <c r="H69" s="7"/>
+      <c r="I69" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J69" s="16">
-        <v>60</v>
-      </c>
-      <c r="K69" s="17" t="s">
+      <c r="J69" s="9">
+        <v>60</v>
+      </c>
+      <c r="K69" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:11">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <f t="shared" ref="A70:A124" si="1">B70*1000+D70</f>
         <v>1107006</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70" s="4">
         <v>1107</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="4">
         <v>6</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="4">
         <v>12</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="7">
         <v>6000</v>
       </c>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8" t="s">
+      <c r="H70" s="7"/>
+      <c r="I70" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J70" s="16">
-        <v>60</v>
-      </c>
-      <c r="K70" s="17" t="s">
+      <c r="J70" s="9">
+        <v>60</v>
+      </c>
+      <c r="K70" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <f t="shared" si="1"/>
         <v>1107007</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="4">
         <v>1107</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="4">
         <v>7</v>
       </c>
-      <c r="E71" s="10">
+      <c r="E71" s="4">
         <v>14</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G71" s="7">
         <v>9000</v>
       </c>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8" t="s">
+      <c r="H71" s="7"/>
+      <c r="I71" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J71" s="16">
-        <v>60</v>
-      </c>
-      <c r="K71" s="17" t="s">
+      <c r="J71" s="9">
+        <v>60</v>
+      </c>
+      <c r="K71" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <f t="shared" si="1"/>
         <v>1107008</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="4">
         <v>1107</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="4">
         <v>8</v>
       </c>
-      <c r="E72" s="10">
+      <c r="E72" s="4">
         <v>16</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G72" s="11">
+      <c r="G72" s="7">
         <v>15000</v>
       </c>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8" t="s">
+      <c r="H72" s="7"/>
+      <c r="I72" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="16">
-        <v>60</v>
-      </c>
-      <c r="K72" s="17" t="s">
+      <c r="J72" s="9">
+        <v>60</v>
+      </c>
+      <c r="K72" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <f t="shared" si="1"/>
         <v>1107009</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="4">
         <v>1107</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="18">
+      <c r="D73" s="11">
         <v>9</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E73" s="4">
         <v>18</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="11">
+      <c r="G73" s="7">
         <v>30000</v>
       </c>
-      <c r="H73" s="19"/>
-      <c r="I73" s="8" t="s">
+      <c r="H73" s="12"/>
+      <c r="I73" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="J73" s="16">
-        <v>60</v>
-      </c>
-      <c r="K73" s="17" t="s">
+      <c r="J73" s="9">
+        <v>60</v>
+      </c>
+      <c r="K73" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
-      <c r="A74" s="5">
+      <c r="A74" s="4">
         <f t="shared" si="1"/>
         <v>1107010</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="4">
         <v>1107</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="4">
         <v>10</v>
       </c>
-      <c r="E74" s="10">
+      <c r="E74" s="4">
         <v>20</v>
       </c>
-      <c r="F74" s="10" t="s">
+      <c r="F74" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G74" s="11">
+      <c r="G74" s="7">
         <v>10000</v>
       </c>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8" t="s">
+      <c r="H74" s="7"/>
+      <c r="I74" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J74" s="16">
-        <v>60</v>
-      </c>
-      <c r="K74" s="17" t="s">
+      <c r="J74" s="9">
+        <v>60</v>
+      </c>
+      <c r="K74" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
-      <c r="A75" s="5">
+      <c r="A75" s="4">
         <f t="shared" si="1"/>
         <v>1108001</v>
       </c>
-      <c r="B75" s="5">
+      <c r="B75" s="4">
         <v>1108</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="10">
+      <c r="E75" s="4">
         <v>2</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="11">
+      <c r="G75" s="7">
         <v>1000</v>
       </c>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="16">
-        <v>60</v>
-      </c>
-      <c r="K75" s="17" t="s">
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="9">
+        <v>60</v>
+      </c>
+      <c r="K75" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
-      <c r="A76" s="5">
+      <c r="A76" s="4">
         <f t="shared" si="1"/>
         <v>1108002</v>
       </c>
-      <c r="B76" s="5">
+      <c r="B76" s="4">
         <v>1108</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="4">
         <v>2</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E76" s="4">
         <v>4</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G76" s="11">
+      <c r="G76" s="7">
         <v>1100</v>
       </c>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8" t="s">
+      <c r="H76" s="7"/>
+      <c r="I76" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J76" s="16">
-        <v>60</v>
-      </c>
-      <c r="K76" s="17" t="s">
+      <c r="J76" s="9">
+        <v>60</v>
+      </c>
+      <c r="K76" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:11">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <f t="shared" si="1"/>
         <v>1108003</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B77" s="4">
         <v>1108</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="4">
         <v>3</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E77" s="4">
         <v>6</v>
       </c>
-      <c r="F77" s="10" t="s">
+      <c r="F77" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G77" s="11">
+      <c r="G77" s="7">
         <v>2000</v>
       </c>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8" t="s">
+      <c r="H77" s="7"/>
+      <c r="I77" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J77" s="16">
-        <v>60</v>
-      </c>
-      <c r="K77" s="17" t="s">
+      <c r="J77" s="9">
+        <v>60</v>
+      </c>
+      <c r="K77" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:11">
-      <c r="A78" s="5">
+      <c r="A78" s="4">
         <f t="shared" si="1"/>
         <v>1108004</v>
       </c>
-      <c r="B78" s="5">
+      <c r="B78" s="4">
         <v>1108</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="4">
         <v>4</v>
       </c>
-      <c r="E78" s="10">
+      <c r="E78" s="4">
         <v>8</v>
       </c>
-      <c r="F78" s="10" t="s">
+      <c r="F78" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G78" s="11">
+      <c r="G78" s="7">
         <v>3000</v>
       </c>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8" t="s">
+      <c r="H78" s="7"/>
+      <c r="I78" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J78" s="16">
-        <v>60</v>
-      </c>
-      <c r="K78" s="17" t="s">
+      <c r="J78" s="9">
+        <v>60</v>
+      </c>
+      <c r="K78" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
-      <c r="A79" s="5">
+      <c r="A79" s="4">
         <f t="shared" si="1"/>
         <v>1108005</v>
       </c>
-      <c r="B79" s="5">
+      <c r="B79" s="4">
         <v>1108</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="4">
         <v>5</v>
       </c>
-      <c r="E79" s="10">
+      <c r="E79" s="4">
         <v>10</v>
       </c>
-      <c r="F79" s="10" t="s">
+      <c r="F79" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G79" s="11">
+      <c r="G79" s="7">
         <v>4500</v>
       </c>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8" t="s">
+      <c r="H79" s="7"/>
+      <c r="I79" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J79" s="16">
-        <v>60</v>
-      </c>
-      <c r="K79" s="17" t="s">
+      <c r="J79" s="9">
+        <v>60</v>
+      </c>
+      <c r="K79" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
-      <c r="A80" s="5">
+      <c r="A80" s="4">
         <f t="shared" si="1"/>
         <v>1108006</v>
       </c>
-      <c r="B80" s="5">
+      <c r="B80" s="4">
         <v>1108</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="4">
         <v>6</v>
       </c>
-      <c r="E80" s="10">
+      <c r="E80" s="4">
         <v>12</v>
       </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G80" s="7">
         <v>6000</v>
       </c>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8" t="s">
+      <c r="H80" s="7"/>
+      <c r="I80" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J80" s="16">
-        <v>60</v>
-      </c>
-      <c r="K80" s="17" t="s">
+      <c r="J80" s="9">
+        <v>60</v>
+      </c>
+      <c r="K80" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
-      <c r="A81" s="5">
+      <c r="A81" s="4">
         <f t="shared" si="1"/>
         <v>1108007</v>
       </c>
-      <c r="B81" s="5">
+      <c r="B81" s="4">
         <v>1108</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="4">
         <v>7</v>
       </c>
-      <c r="E81" s="10">
+      <c r="E81" s="4">
         <v>14</v>
       </c>
-      <c r="F81" s="10" t="s">
+      <c r="F81" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="11">
+      <c r="G81" s="7">
         <v>9000</v>
       </c>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8" t="s">
+      <c r="H81" s="7"/>
+      <c r="I81" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J81" s="16">
-        <v>60</v>
-      </c>
-      <c r="K81" s="17" t="s">
+      <c r="J81" s="9">
+        <v>60</v>
+      </c>
+      <c r="K81" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
-      <c r="A82" s="5">
+      <c r="A82" s="4">
         <f t="shared" si="1"/>
         <v>1108008</v>
       </c>
-      <c r="B82" s="5">
+      <c r="B82" s="4">
         <v>1108</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="4">
         <v>8</v>
       </c>
-      <c r="E82" s="10">
+      <c r="E82" s="4">
         <v>16</v>
       </c>
-      <c r="F82" s="10" t="s">
+      <c r="F82" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G82" s="11">
+      <c r="G82" s="7">
         <v>15000</v>
       </c>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8" t="s">
+      <c r="H82" s="7"/>
+      <c r="I82" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J82" s="16">
-        <v>60</v>
-      </c>
-      <c r="K82" s="17" t="s">
+      <c r="J82" s="9">
+        <v>60</v>
+      </c>
+      <c r="K82" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
-      <c r="A83" s="5">
+      <c r="A83" s="4">
         <f t="shared" si="1"/>
         <v>1108009</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B83" s="4">
         <v>1108</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="18">
+      <c r="D83" s="11">
         <v>9</v>
       </c>
-      <c r="E83" s="10">
+      <c r="E83" s="4">
         <v>18</v>
       </c>
-      <c r="F83" s="10" t="s">
+      <c r="F83" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G83" s="11">
+      <c r="G83" s="7">
         <v>30000</v>
       </c>
-      <c r="H83" s="19"/>
-      <c r="I83" s="8" t="s">
+      <c r="H83" s="12"/>
+      <c r="I83" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J83" s="16">
-        <v>60</v>
-      </c>
-      <c r="K83" s="17" t="s">
+      <c r="J83" s="9">
+        <v>60</v>
+      </c>
+      <c r="K83" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
-      <c r="A84" s="5">
+      <c r="A84" s="4">
         <f t="shared" si="1"/>
         <v>1108010</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B84" s="4">
         <v>1108</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="4">
         <v>10</v>
       </c>
-      <c r="E84" s="10">
+      <c r="E84" s="4">
         <v>20</v>
       </c>
-      <c r="F84" s="10" t="s">
+      <c r="F84" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G84" s="11">
+      <c r="G84" s="7">
         <v>10000</v>
       </c>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8" t="s">
+      <c r="H84" s="7"/>
+      <c r="I84" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="16">
-        <v>60</v>
-      </c>
-      <c r="K84" s="17" t="s">
+      <c r="J84" s="9">
+        <v>60</v>
+      </c>
+      <c r="K84" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <f t="shared" si="1"/>
         <v>1109001</v>
       </c>
-      <c r="B85" s="5">
+      <c r="B85" s="4">
         <v>1109</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="10">
+      <c r="E85" s="4">
         <v>2</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="F85" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G85" s="11">
+      <c r="G85" s="7">
         <v>1000</v>
       </c>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="16">
-        <v>60</v>
-      </c>
-      <c r="K85" s="17" t="s">
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="9">
+        <v>60</v>
+      </c>
+      <c r="K85" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
-      <c r="A86" s="5">
+      <c r="A86" s="4">
         <f t="shared" si="1"/>
         <v>1109002</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B86" s="4">
         <v>1109</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="4">
         <v>2</v>
       </c>
-      <c r="E86" s="10">
+      <c r="E86" s="4">
         <v>4</v>
       </c>
-      <c r="F86" s="10" t="s">
+      <c r="F86" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G86" s="11">
+      <c r="G86" s="7">
         <v>1100</v>
       </c>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8" t="s">
+      <c r="H86" s="7"/>
+      <c r="I86" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="J86" s="16">
-        <v>60</v>
-      </c>
-      <c r="K86" s="17" t="s">
+      <c r="J86" s="9">
+        <v>60</v>
+      </c>
+      <c r="K86" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <f t="shared" si="1"/>
         <v>1109003</v>
       </c>
-      <c r="B87" s="5">
+      <c r="B87" s="4">
         <v>1109</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="4">
         <v>3</v>
       </c>
-      <c r="E87" s="10">
+      <c r="E87" s="4">
         <v>6</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G87" s="11">
+      <c r="G87" s="7">
         <v>2000</v>
       </c>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8" t="s">
+      <c r="H87" s="7"/>
+      <c r="I87" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="J87" s="16">
-        <v>60</v>
-      </c>
-      <c r="K87" s="17" t="s">
+      <c r="J87" s="9">
+        <v>60</v>
+      </c>
+      <c r="K87" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
-      <c r="A88" s="5">
+      <c r="A88" s="4">
         <f t="shared" si="1"/>
         <v>1109004</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B88" s="4">
         <v>1109</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="4">
         <v>4</v>
       </c>
-      <c r="E88" s="10">
+      <c r="E88" s="4">
         <v>8</v>
       </c>
-      <c r="F88" s="10" t="s">
+      <c r="F88" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G88" s="11">
+      <c r="G88" s="7">
         <v>3000</v>
       </c>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8" t="s">
+      <c r="H88" s="7"/>
+      <c r="I88" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="J88" s="16">
-        <v>60</v>
-      </c>
-      <c r="K88" s="17" t="s">
+      <c r="J88" s="9">
+        <v>60</v>
+      </c>
+      <c r="K88" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:11">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <f t="shared" si="1"/>
         <v>1109005</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B89" s="4">
         <v>1109</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="4">
         <v>5</v>
       </c>
-      <c r="E89" s="10">
+      <c r="E89" s="4">
         <v>10</v>
       </c>
-      <c r="F89" s="10" t="s">
+      <c r="F89" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G89" s="11">
+      <c r="G89" s="7">
         <v>4500</v>
       </c>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8" t="s">
+      <c r="H89" s="7"/>
+      <c r="I89" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="J89" s="16">
-        <v>60</v>
-      </c>
-      <c r="K89" s="17" t="s">
+      <c r="J89" s="9">
+        <v>60</v>
+      </c>
+      <c r="K89" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:11">
-      <c r="A90" s="5">
+      <c r="A90" s="4">
         <f t="shared" si="1"/>
         <v>1109006</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B90" s="4">
         <v>1109</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="4">
         <v>6</v>
       </c>
-      <c r="E90" s="10">
+      <c r="E90" s="4">
         <v>12</v>
       </c>
-      <c r="F90" s="10" t="s">
+      <c r="F90" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G90" s="11">
+      <c r="G90" s="7">
         <v>6000</v>
       </c>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8" t="s">
+      <c r="H90" s="7"/>
+      <c r="I90" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="J90" s="16">
-        <v>60</v>
-      </c>
-      <c r="K90" s="17" t="s">
+      <c r="J90" s="9">
+        <v>60</v>
+      </c>
+      <c r="K90" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
-      <c r="A91" s="5">
+      <c r="A91" s="4">
         <f t="shared" si="1"/>
         <v>1109007</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B91" s="4">
         <v>1109</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="4">
         <v>7</v>
       </c>
-      <c r="E91" s="10">
+      <c r="E91" s="4">
         <v>14</v>
       </c>
-      <c r="F91" s="10" t="s">
+      <c r="F91" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="11">
+      <c r="G91" s="7">
         <v>9000</v>
       </c>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8" t="s">
+      <c r="H91" s="7"/>
+      <c r="I91" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J91" s="16">
-        <v>60</v>
-      </c>
-      <c r="K91" s="17" t="s">
+      <c r="J91" s="9">
+        <v>60</v>
+      </c>
+      <c r="K91" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
-      <c r="A92" s="5">
+      <c r="A92" s="4">
         <f t="shared" si="1"/>
         <v>1109008</v>
       </c>
-      <c r="B92" s="5">
+      <c r="B92" s="4">
         <v>1109</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="4">
         <v>8</v>
       </c>
-      <c r="E92" s="10">
+      <c r="E92" s="4">
         <v>16</v>
       </c>
-      <c r="F92" s="10" t="s">
+      <c r="F92" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G92" s="11">
+      <c r="G92" s="7">
         <v>15000</v>
       </c>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8" t="s">
+      <c r="H92" s="7"/>
+      <c r="I92" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="J92" s="16">
-        <v>60</v>
-      </c>
-      <c r="K92" s="17" t="s">
+      <c r="J92" s="9">
+        <v>60</v>
+      </c>
+      <c r="K92" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:11">
-      <c r="A93" s="5">
+      <c r="A93" s="4">
         <f t="shared" si="1"/>
         <v>1109009</v>
       </c>
-      <c r="B93" s="5">
+      <c r="B93" s="4">
         <v>1109</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D93" s="18">
+      <c r="D93" s="11">
         <v>9</v>
       </c>
-      <c r="E93" s="10">
+      <c r="E93" s="4">
         <v>18</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G93" s="11">
+      <c r="G93" s="7">
         <v>30000</v>
       </c>
-      <c r="H93" s="19"/>
-      <c r="I93" s="8" t="s">
+      <c r="H93" s="12"/>
+      <c r="I93" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J93" s="16">
-        <v>60</v>
-      </c>
-      <c r="K93" s="17" t="s">
+      <c r="J93" s="9">
+        <v>60</v>
+      </c>
+      <c r="K93" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:11">
-      <c r="A94" s="5">
+      <c r="A94" s="4">
         <f t="shared" si="1"/>
         <v>1109010</v>
       </c>
-      <c r="B94" s="5">
+      <c r="B94" s="4">
         <v>1109</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="4">
         <v>10</v>
       </c>
-      <c r="E94" s="10">
+      <c r="E94" s="4">
         <v>20</v>
       </c>
-      <c r="F94" s="10" t="s">
+      <c r="F94" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G94" s="11">
+      <c r="G94" s="7">
         <v>10000</v>
       </c>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8" t="s">
+      <c r="H94" s="7"/>
+      <c r="I94" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J94" s="16">
-        <v>60</v>
-      </c>
-      <c r="K94" s="17" t="s">
+      <c r="J94" s="9">
+        <v>60</v>
+      </c>
+      <c r="K94" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:11">
-      <c r="A95" s="5">
+      <c r="A95" s="4">
         <f t="shared" si="1"/>
         <v>1110001</v>
       </c>
-      <c r="B95" s="5">
+      <c r="B95" s="4">
         <v>1110</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="10">
+      <c r="E95" s="4">
         <v>2</v>
       </c>
-      <c r="F95" s="10" t="s">
+      <c r="F95" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G95" s="11">
+      <c r="G95" s="7">
         <v>1000</v>
       </c>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="16">
-        <v>60</v>
-      </c>
-      <c r="K95" s="17" t="s">
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="9">
+        <v>60</v>
+      </c>
+      <c r="K95" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:11">
-      <c r="A96" s="5">
+      <c r="A96" s="4">
         <f t="shared" si="1"/>
         <v>1110002</v>
       </c>
-      <c r="B96" s="5">
+      <c r="B96" s="4">
         <v>1110</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="4">
         <v>2</v>
       </c>
-      <c r="E96" s="10">
+      <c r="E96" s="4">
         <v>4</v>
       </c>
-      <c r="F96" s="10" t="s">
+      <c r="F96" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G96" s="11">
+      <c r="G96" s="7">
         <v>1100</v>
       </c>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8" t="s">
+      <c r="H96" s="7"/>
+      <c r="I96" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="J96" s="16">
-        <v>60</v>
-      </c>
-      <c r="K96" s="17" t="s">
+      <c r="J96" s="9">
+        <v>60</v>
+      </c>
+      <c r="K96" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:11">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <f t="shared" si="1"/>
         <v>1110003</v>
       </c>
-      <c r="B97" s="5">
+      <c r="B97" s="4">
         <v>1110</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="4">
         <v>3</v>
       </c>
-      <c r="E97" s="10">
+      <c r="E97" s="4">
         <v>6</v>
       </c>
-      <c r="F97" s="10" t="s">
+      <c r="F97" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G97" s="11">
+      <c r="G97" s="7">
         <v>2000</v>
       </c>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8" t="s">
+      <c r="H97" s="7"/>
+      <c r="I97" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J97" s="16">
-        <v>60</v>
-      </c>
-      <c r="K97" s="17" t="s">
+      <c r="J97" s="9">
+        <v>60</v>
+      </c>
+      <c r="K97" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:11">
-      <c r="A98" s="5">
+      <c r="A98" s="4">
         <f t="shared" si="1"/>
         <v>1110004</v>
       </c>
-      <c r="B98" s="5">
+      <c r="B98" s="4">
         <v>1110</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="4">
         <v>4</v>
       </c>
-      <c r="E98" s="10">
+      <c r="E98" s="4">
         <v>8</v>
       </c>
-      <c r="F98" s="10" t="s">
+      <c r="F98" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G98" s="11">
+      <c r="G98" s="7">
         <v>3000</v>
       </c>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8" t="s">
+      <c r="H98" s="7"/>
+      <c r="I98" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J98" s="16">
-        <v>60</v>
-      </c>
-      <c r="K98" s="17" t="s">
+      <c r="J98" s="9">
+        <v>60</v>
+      </c>
+      <c r="K98" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:11">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <f t="shared" si="1"/>
         <v>1110005</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B99" s="4">
         <v>1110</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C99" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="4">
         <v>5</v>
       </c>
-      <c r="E99" s="10">
+      <c r="E99" s="4">
         <v>10</v>
       </c>
-      <c r="F99" s="10" t="s">
+      <c r="F99" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G99" s="11">
+      <c r="G99" s="7">
         <v>4500</v>
       </c>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8" t="s">
+      <c r="H99" s="7"/>
+      <c r="I99" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J99" s="16">
-        <v>60</v>
-      </c>
-      <c r="K99" s="17" t="s">
+      <c r="J99" s="9">
+        <v>60</v>
+      </c>
+      <c r="K99" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:11">
-      <c r="A100" s="5">
+      <c r="A100" s="4">
         <f t="shared" si="1"/>
         <v>1110006</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B100" s="4">
         <v>1110</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C100" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="4">
         <v>6</v>
       </c>
-      <c r="E100" s="10">
+      <c r="E100" s="4">
         <v>12</v>
       </c>
-      <c r="F100" s="10" t="s">
+      <c r="F100" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G100" s="11">
+      <c r="G100" s="7">
         <v>6000</v>
       </c>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8" t="s">
+      <c r="H100" s="7"/>
+      <c r="I100" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="J100" s="16">
-        <v>60</v>
-      </c>
-      <c r="K100" s="17" t="s">
+      <c r="J100" s="9">
+        <v>60</v>
+      </c>
+      <c r="K100" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:11">
-      <c r="A101" s="5">
+      <c r="A101" s="4">
         <f t="shared" si="1"/>
         <v>1110007</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B101" s="4">
         <v>1110</v>
       </c>
-      <c r="C101" s="5" t="s">
+      <c r="C101" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="4">
         <v>7</v>
       </c>
-      <c r="E101" s="10">
+      <c r="E101" s="4">
         <v>14</v>
       </c>
-      <c r="F101" s="10" t="s">
+      <c r="F101" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G101" s="11">
+      <c r="G101" s="7">
         <v>9000</v>
       </c>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8" t="s">
+      <c r="H101" s="7"/>
+      <c r="I101" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J101" s="16">
-        <v>60</v>
-      </c>
-      <c r="K101" s="17" t="s">
+      <c r="J101" s="9">
+        <v>60</v>
+      </c>
+      <c r="K101" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:11">
-      <c r="A102" s="5">
+      <c r="A102" s="4">
         <f t="shared" si="1"/>
         <v>1110008</v>
       </c>
-      <c r="B102" s="5">
+      <c r="B102" s="4">
         <v>1110</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C102" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="4">
         <v>8</v>
       </c>
-      <c r="E102" s="10">
+      <c r="E102" s="4">
         <v>16</v>
       </c>
-      <c r="F102" s="10" t="s">
+      <c r="F102" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G102" s="11">
+      <c r="G102" s="7">
         <v>15000</v>
       </c>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8" t="s">
+      <c r="H102" s="7"/>
+      <c r="I102" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="J102" s="16">
-        <v>60</v>
-      </c>
-      <c r="K102" s="17" t="s">
+      <c r="J102" s="9">
+        <v>60</v>
+      </c>
+      <c r="K102" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:11">
-      <c r="A103" s="5">
+      <c r="A103" s="4">
         <f t="shared" si="1"/>
         <v>1110009</v>
       </c>
-      <c r="B103" s="5">
+      <c r="B103" s="4">
         <v>1110</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="C103" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D103" s="18">
+      <c r="D103" s="11">
         <v>9</v>
       </c>
-      <c r="E103" s="10">
+      <c r="E103" s="4">
         <v>18</v>
       </c>
-      <c r="F103" s="10" t="s">
+      <c r="F103" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G103" s="11">
+      <c r="G103" s="7">
         <v>30000</v>
       </c>
-      <c r="H103" s="19"/>
-      <c r="I103" s="8" t="s">
+      <c r="H103" s="12"/>
+      <c r="I103" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J103" s="16">
-        <v>60</v>
-      </c>
-      <c r="K103" s="17" t="s">
+      <c r="J103" s="9">
+        <v>60</v>
+      </c>
+      <c r="K103" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:11">
-      <c r="A104" s="5">
+      <c r="A104" s="4">
         <f t="shared" si="1"/>
         <v>1110010</v>
       </c>
-      <c r="B104" s="5">
+      <c r="B104" s="4">
         <v>1110</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C104" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="4">
         <v>10</v>
       </c>
-      <c r="E104" s="10">
+      <c r="E104" s="4">
         <v>20</v>
       </c>
-      <c r="F104" s="10" t="s">
+      <c r="F104" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G104" s="11">
+      <c r="G104" s="7">
         <v>10000</v>
       </c>
-      <c r="H104" s="8"/>
-      <c r="I104" s="8" t="s">
+      <c r="H104" s="7"/>
+      <c r="I104" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J104" s="16">
-        <v>60</v>
-      </c>
-      <c r="K104" s="17" t="s">
+      <c r="J104" s="9">
+        <v>60</v>
+      </c>
+      <c r="K104" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:11">
-      <c r="A105" s="5">
+      <c r="A105" s="4">
         <f t="shared" si="1"/>
         <v>1111001</v>
       </c>
-      <c r="B105" s="5">
+      <c r="B105" s="4">
         <v>1111</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C105" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="10">
+      <c r="E105" s="4">
         <v>2</v>
       </c>
-      <c r="F105" s="10" t="s">
+      <c r="F105" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G105" s="11">
+      <c r="G105" s="7">
         <v>1000</v>
       </c>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="16">
-        <v>60</v>
-      </c>
-      <c r="K105" s="17" t="s">
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="9">
+        <v>60</v>
+      </c>
+      <c r="K105" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:11">
-      <c r="A106" s="5">
+      <c r="A106" s="4">
         <f t="shared" si="1"/>
         <v>1111002</v>
       </c>
-      <c r="B106" s="5">
+      <c r="B106" s="4">
         <v>1111</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C106" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="4">
         <v>2</v>
       </c>
-      <c r="E106" s="10">
+      <c r="E106" s="4">
         <v>4</v>
       </c>
-      <c r="F106" s="10" t="s">
+      <c r="F106" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G106" s="11">
+      <c r="G106" s="7">
         <v>1100</v>
       </c>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8" t="s">
+      <c r="H106" s="7"/>
+      <c r="I106" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="J106" s="16">
-        <v>60</v>
-      </c>
-      <c r="K106" s="17" t="s">
+      <c r="J106" s="9">
+        <v>60</v>
+      </c>
+      <c r="K106" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:11">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <f t="shared" si="1"/>
         <v>1111003</v>
       </c>
-      <c r="B107" s="5">
+      <c r="B107" s="4">
         <v>1111</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="C107" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="4">
         <v>3</v>
       </c>
-      <c r="E107" s="10">
+      <c r="E107" s="4">
         <v>6</v>
       </c>
-      <c r="F107" s="10" t="s">
+      <c r="F107" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G107" s="11">
+      <c r="G107" s="7">
         <v>2000</v>
       </c>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8" t="s">
+      <c r="H107" s="7"/>
+      <c r="I107" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J107" s="16">
-        <v>60</v>
-      </c>
-      <c r="K107" s="17" t="s">
+      <c r="J107" s="9">
+        <v>60</v>
+      </c>
+      <c r="K107" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:11">
-      <c r="A108" s="5">
+      <c r="A108" s="4">
         <f t="shared" si="1"/>
         <v>1111004</v>
       </c>
-      <c r="B108" s="5">
+      <c r="B108" s="4">
         <v>1111</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C108" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="4">
         <v>4</v>
       </c>
-      <c r="E108" s="10">
+      <c r="E108" s="4">
         <v>8</v>
       </c>
-      <c r="F108" s="10" t="s">
+      <c r="F108" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G108" s="11">
+      <c r="G108" s="7">
         <v>3000</v>
       </c>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8" t="s">
+      <c r="H108" s="7"/>
+      <c r="I108" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J108" s="16">
-        <v>60</v>
-      </c>
-      <c r="K108" s="17" t="s">
+      <c r="J108" s="9">
+        <v>60</v>
+      </c>
+      <c r="K108" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:11">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <f t="shared" si="1"/>
         <v>1111005</v>
       </c>
-      <c r="B109" s="5">
+      <c r="B109" s="4">
         <v>1111</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="C109" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="4">
         <v>5</v>
       </c>
-      <c r="E109" s="10">
+      <c r="E109" s="4">
         <v>10</v>
       </c>
-      <c r="F109" s="10" t="s">
+      <c r="F109" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G109" s="11">
+      <c r="G109" s="7">
         <v>4500</v>
       </c>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8" t="s">
+      <c r="H109" s="7"/>
+      <c r="I109" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J109" s="16">
-        <v>60</v>
-      </c>
-      <c r="K109" s="17" t="s">
+      <c r="J109" s="9">
+        <v>60</v>
+      </c>
+      <c r="K109" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:11">
-      <c r="A110" s="5">
+      <c r="A110" s="4">
         <f t="shared" si="1"/>
         <v>1111006</v>
       </c>
-      <c r="B110" s="5">
+      <c r="B110" s="4">
         <v>1111</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C110" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D110" s="4">
         <v>6</v>
       </c>
-      <c r="E110" s="10">
+      <c r="E110" s="4">
         <v>12</v>
       </c>
-      <c r="F110" s="10" t="s">
+      <c r="F110" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G110" s="11">
+      <c r="G110" s="7">
         <v>6000</v>
       </c>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8" t="s">
+      <c r="H110" s="7"/>
+      <c r="I110" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="J110" s="16">
-        <v>60</v>
-      </c>
-      <c r="K110" s="17" t="s">
+      <c r="J110" s="9">
+        <v>60</v>
+      </c>
+      <c r="K110" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:11">
-      <c r="A111" s="5">
+      <c r="A111" s="4">
         <f t="shared" si="1"/>
         <v>1111007</v>
       </c>
-      <c r="B111" s="5">
+      <c r="B111" s="4">
         <v>1111</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="C111" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D111" s="5">
+      <c r="D111" s="4">
         <v>7</v>
       </c>
-      <c r="E111" s="10">
+      <c r="E111" s="4">
         <v>14</v>
       </c>
-      <c r="F111" s="10" t="s">
+      <c r="F111" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="11">
+      <c r="G111" s="7">
         <v>9000</v>
       </c>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8" t="s">
+      <c r="H111" s="7"/>
+      <c r="I111" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J111" s="16">
-        <v>60</v>
-      </c>
-      <c r="K111" s="17" t="s">
+      <c r="J111" s="9">
+        <v>60</v>
+      </c>
+      <c r="K111" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:11">
-      <c r="A112" s="5">
+      <c r="A112" s="4">
         <f t="shared" si="1"/>
         <v>1111008</v>
       </c>
-      <c r="B112" s="5">
+      <c r="B112" s="4">
         <v>1111</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C112" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="4">
         <v>8</v>
       </c>
-      <c r="E112" s="10">
+      <c r="E112" s="4">
         <v>16</v>
       </c>
-      <c r="F112" s="10" t="s">
+      <c r="F112" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G112" s="11">
+      <c r="G112" s="7">
         <v>15000</v>
       </c>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8" t="s">
+      <c r="H112" s="7"/>
+      <c r="I112" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J112" s="16">
-        <v>60</v>
-      </c>
-      <c r="K112" s="17" t="s">
+      <c r="J112" s="9">
+        <v>60</v>
+      </c>
+      <c r="K112" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:11">
-      <c r="A113" s="5">
+      <c r="A113" s="4">
         <f t="shared" si="1"/>
         <v>1111009</v>
       </c>
-      <c r="B113" s="5">
+      <c r="B113" s="4">
         <v>1111</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C113" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D113" s="18">
+      <c r="D113" s="11">
         <v>9</v>
       </c>
-      <c r="E113" s="10">
+      <c r="E113" s="4">
         <v>18</v>
       </c>
-      <c r="F113" s="10" t="s">
+      <c r="F113" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G113" s="11">
+      <c r="G113" s="7">
         <v>30000</v>
       </c>
-      <c r="H113" s="19"/>
-      <c r="I113" s="8" t="s">
+      <c r="H113" s="12"/>
+      <c r="I113" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="J113" s="16">
-        <v>60</v>
-      </c>
-      <c r="K113" s="17" t="s">
+      <c r="J113" s="9">
+        <v>60</v>
+      </c>
+      <c r="K113" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:11">
-      <c r="A114" s="5">
+      <c r="A114" s="4">
         <f t="shared" si="1"/>
         <v>1111010</v>
       </c>
-      <c r="B114" s="5">
+      <c r="B114" s="4">
         <v>1111</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D114" s="4">
         <v>10</v>
       </c>
-      <c r="E114" s="10">
+      <c r="E114" s="4">
         <v>20</v>
       </c>
-      <c r="F114" s="10" t="s">
+      <c r="F114" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G114" s="11">
+      <c r="G114" s="7">
         <v>10000</v>
       </c>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8" t="s">
+      <c r="H114" s="7"/>
+      <c r="I114" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="J114" s="16">
-        <v>60</v>
-      </c>
-      <c r="K114" s="17" t="s">
+      <c r="J114" s="9">
+        <v>60</v>
+      </c>
+      <c r="K114" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:11">
-      <c r="A115" s="5">
+      <c r="A115" s="4">
         <f t="shared" si="1"/>
         <v>1112001</v>
       </c>
-      <c r="B115" s="5">
+      <c r="B115" s="4">
         <v>1112</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C115" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D115" s="5">
+      <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="10">
+      <c r="E115" s="4">
         <v>2</v>
       </c>
-      <c r="F115" s="10" t="s">
+      <c r="F115" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G115" s="11">
+      <c r="G115" s="7">
         <v>1000</v>
       </c>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="16">
-        <v>60</v>
-      </c>
-      <c r="K115" s="17" t="s">
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="9">
+        <v>60</v>
+      </c>
+      <c r="K115" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:11">
-      <c r="A116" s="5">
+      <c r="A116" s="4">
         <f t="shared" si="1"/>
         <v>1112002</v>
       </c>
-      <c r="B116" s="5">
+      <c r="B116" s="4">
         <v>1112</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C116" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D116" s="4">
         <v>2</v>
       </c>
-      <c r="E116" s="10">
+      <c r="E116" s="4">
         <v>4</v>
       </c>
-      <c r="F116" s="10" t="s">
+      <c r="F116" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G116" s="11">
+      <c r="G116" s="7">
         <v>1100</v>
       </c>
-      <c r="H116" s="8"/>
-      <c r="I116" s="8" t="s">
+      <c r="H116" s="7"/>
+      <c r="I116" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="J116" s="16">
-        <v>60</v>
-      </c>
-      <c r="K116" s="17" t="s">
+      <c r="J116" s="9">
+        <v>60</v>
+      </c>
+      <c r="K116" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:11">
-      <c r="A117" s="5">
+      <c r="A117" s="4">
         <f t="shared" si="1"/>
         <v>1112003</v>
       </c>
-      <c r="B117" s="5">
+      <c r="B117" s="4">
         <v>1112</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C117" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D117" s="5">
+      <c r="D117" s="4">
         <v>3</v>
       </c>
-      <c r="E117" s="10">
+      <c r="E117" s="4">
         <v>6</v>
       </c>
-      <c r="F117" s="10" t="s">
+      <c r="F117" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G117" s="11">
+      <c r="G117" s="7">
         <v>2000</v>
       </c>
-      <c r="H117" s="8"/>
-      <c r="I117" s="8" t="s">
+      <c r="H117" s="7"/>
+      <c r="I117" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J117" s="16">
-        <v>60</v>
-      </c>
-      <c r="K117" s="17" t="s">
+      <c r="J117" s="9">
+        <v>60</v>
+      </c>
+      <c r="K117" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:11">
-      <c r="A118" s="5">
+      <c r="A118" s="4">
         <f t="shared" si="1"/>
         <v>1112004</v>
       </c>
-      <c r="B118" s="5">
+      <c r="B118" s="4">
         <v>1112</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C118" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="4">
         <v>4</v>
       </c>
-      <c r="E118" s="10">
+      <c r="E118" s="4">
         <v>8</v>
       </c>
-      <c r="F118" s="10" t="s">
+      <c r="F118" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G118" s="11">
+      <c r="G118" s="7">
         <v>3000</v>
       </c>
-      <c r="H118" s="8"/>
-      <c r="I118" s="8" t="s">
+      <c r="H118" s="7"/>
+      <c r="I118" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="J118" s="16">
-        <v>60</v>
-      </c>
-      <c r="K118" s="17" t="s">
+      <c r="J118" s="9">
+        <v>60</v>
+      </c>
+      <c r="K118" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:11">
-      <c r="A119" s="5">
+      <c r="A119" s="4">
         <f t="shared" si="1"/>
         <v>1112005</v>
       </c>
-      <c r="B119" s="5">
+      <c r="B119" s="4">
         <v>1112</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C119" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="4">
         <v>5</v>
       </c>
-      <c r="E119" s="10">
+      <c r="E119" s="4">
         <v>10</v>
       </c>
-      <c r="F119" s="10" t="s">
+      <c r="F119" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G119" s="11">
+      <c r="G119" s="7">
         <v>4500</v>
       </c>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8" t="s">
+      <c r="H119" s="7"/>
+      <c r="I119" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J119" s="16">
-        <v>60</v>
-      </c>
-      <c r="K119" s="17" t="s">
+      <c r="J119" s="9">
+        <v>60</v>
+      </c>
+      <c r="K119" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:11">
-      <c r="A120" s="5">
+      <c r="A120" s="4">
         <f t="shared" si="1"/>
         <v>1112006</v>
       </c>
-      <c r="B120" s="5">
+      <c r="B120" s="4">
         <v>1112</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C120" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D120" s="4">
         <v>6</v>
       </c>
-      <c r="E120" s="10">
+      <c r="E120" s="4">
         <v>12</v>
       </c>
-      <c r="F120" s="10" t="s">
+      <c r="F120" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G120" s="11">
+      <c r="G120" s="7">
         <v>6000</v>
       </c>
-      <c r="H120" s="8"/>
-      <c r="I120" s="8" t="s">
+      <c r="H120" s="7"/>
+      <c r="I120" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J120" s="16">
-        <v>60</v>
-      </c>
-      <c r="K120" s="17" t="s">
+      <c r="J120" s="9">
+        <v>60</v>
+      </c>
+      <c r="K120" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:11">
-      <c r="A121" s="5">
+      <c r="A121" s="4">
         <f t="shared" si="1"/>
         <v>1112007</v>
       </c>
-      <c r="B121" s="5">
+      <c r="B121" s="4">
         <v>1112</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="C121" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="4">
         <v>7</v>
       </c>
-      <c r="E121" s="10">
+      <c r="E121" s="4">
         <v>14</v>
       </c>
-      <c r="F121" s="10" t="s">
+      <c r="F121" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="11">
+      <c r="G121" s="7">
         <v>9000</v>
       </c>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8" t="s">
+      <c r="H121" s="7"/>
+      <c r="I121" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J121" s="16">
-        <v>60</v>
-      </c>
-      <c r="K121" s="17" t="s">
+      <c r="J121" s="9">
+        <v>60</v>
+      </c>
+      <c r="K121" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:11">
-      <c r="A122" s="5">
+      <c r="A122" s="4">
         <f t="shared" si="1"/>
         <v>1112008</v>
       </c>
-      <c r="B122" s="5">
+      <c r="B122" s="4">
         <v>1112</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C122" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D122" s="4">
         <v>8</v>
       </c>
-      <c r="E122" s="10">
+      <c r="E122" s="4">
         <v>16</v>
       </c>
-      <c r="F122" s="10" t="s">
+      <c r="F122" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G122" s="11">
+      <c r="G122" s="7">
         <v>15000</v>
       </c>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8" t="s">
+      <c r="H122" s="7"/>
+      <c r="I122" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="J122" s="16">
-        <v>60</v>
-      </c>
-      <c r="K122" s="17" t="s">
+      <c r="J122" s="9">
+        <v>60</v>
+      </c>
+      <c r="K122" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:11">
-      <c r="A123" s="5">
+      <c r="A123" s="4">
         <f t="shared" si="1"/>
         <v>1112009</v>
       </c>
-      <c r="B123" s="5">
+      <c r="B123" s="4">
         <v>1112</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C123" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D123" s="18">
+      <c r="D123" s="11">
         <v>9</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="4">
         <v>18</v>
       </c>
-      <c r="F123" s="10" t="s">
+      <c r="F123" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G123" s="11">
+      <c r="G123" s="7">
         <v>30000</v>
       </c>
-      <c r="H123" s="19"/>
-      <c r="I123" s="8" t="s">
+      <c r="H123" s="12"/>
+      <c r="I123" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J123" s="16">
-        <v>60</v>
-      </c>
-      <c r="K123" s="17" t="s">
+      <c r="J123" s="9">
+        <v>60</v>
+      </c>
+      <c r="K123" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:11">
-      <c r="A124" s="5">
+      <c r="A124" s="4">
         <f t="shared" si="1"/>
         <v>1112010</v>
       </c>
-      <c r="B124" s="5">
+      <c r="B124" s="4">
         <v>1112</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="C124" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D124" s="5">
+      <c r="D124" s="4">
         <v>10</v>
       </c>
-      <c r="E124" s="10">
+      <c r="E124" s="4">
         <v>20</v>
       </c>
-      <c r="F124" s="10" t="s">
+      <c r="F124" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G124" s="11">
+      <c r="G124" s="7">
         <v>10000</v>
       </c>
-      <c r="H124" s="8"/>
-      <c r="I124" s="8" t="s">
+      <c r="H124" s="7"/>
+      <c r="I124" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="J124" s="16">
-        <v>60</v>
-      </c>
-      <c r="K124" s="17" t="s">
+      <c r="J124" s="9">
+        <v>60</v>
+      </c>
+      <c r="K124" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:11">
-      <c r="A125" s="5">
+      <c r="A125" s="4">
         <f t="shared" ref="A125:A154" si="2">B125*1000+D125</f>
         <v>1201001</v>
       </c>
-      <c r="B125" s="5">
+      <c r="B125" s="4">
         <v>1201</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="C125" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D125" s="5">
+      <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="10">
+      <c r="E125" s="4">
         <v>2</v>
       </c>
-      <c r="F125" s="10" t="s">
+      <c r="F125" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G125" s="11">
+      <c r="G125" s="7">
         <v>1000</v>
       </c>
-      <c r="H125" s="8"/>
-      <c r="I125" s="8"/>
-      <c r="J125" s="16">
-        <v>60</v>
-      </c>
-      <c r="K125" s="17" t="s">
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="9">
+        <v>60</v>
+      </c>
+      <c r="K125" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:11">
-      <c r="A126" s="5">
+      <c r="A126" s="4">
         <f t="shared" si="2"/>
         <v>1201002</v>
       </c>
-      <c r="B126" s="5">
+      <c r="B126" s="4">
         <v>1201</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C126" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D126" s="4">
         <v>2</v>
       </c>
-      <c r="E126" s="10">
+      <c r="E126" s="4">
         <v>4</v>
       </c>
-      <c r="F126" s="10" t="s">
+      <c r="F126" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G126" s="11">
+      <c r="G126" s="7">
         <v>1100</v>
       </c>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8" t="s">
+      <c r="H126" s="7"/>
+      <c r="I126" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="J126" s="16">
-        <v>60</v>
-      </c>
-      <c r="K126" s="17" t="s">
+      <c r="J126" s="9">
+        <v>60</v>
+      </c>
+      <c r="K126" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:11">
-      <c r="A127" s="5">
+      <c r="A127" s="4">
         <f t="shared" si="2"/>
         <v>1201003</v>
       </c>
-      <c r="B127" s="5">
+      <c r="B127" s="4">
         <v>1201</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C127" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="4">
         <v>3</v>
       </c>
-      <c r="E127" s="10">
+      <c r="E127" s="4">
         <v>6</v>
       </c>
-      <c r="F127" s="10" t="s">
+      <c r="F127" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G127" s="11">
+      <c r="G127" s="7">
         <v>2000</v>
       </c>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8" t="s">
+      <c r="H127" s="7"/>
+      <c r="I127" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="J127" s="16">
-        <v>60</v>
-      </c>
-      <c r="K127" s="17" t="s">
+      <c r="J127" s="9">
+        <v>60</v>
+      </c>
+      <c r="K127" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:11">
-      <c r="A128" s="5">
+      <c r="A128" s="4">
         <f t="shared" si="2"/>
         <v>1201004</v>
       </c>
-      <c r="B128" s="5">
+      <c r="B128" s="4">
         <v>1201</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C128" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="4">
         <v>4</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="4">
         <v>8</v>
       </c>
-      <c r="F128" s="10" t="s">
+      <c r="F128" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G128" s="11">
+      <c r="G128" s="7">
         <v>3000</v>
       </c>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8" t="s">
+      <c r="H128" s="7"/>
+      <c r="I128" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="J128" s="16">
-        <v>60</v>
-      </c>
-      <c r="K128" s="17" t="s">
+      <c r="J128" s="9">
+        <v>60</v>
+      </c>
+      <c r="K128" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:11">
-      <c r="A129" s="5">
+      <c r="A129" s="4">
         <f t="shared" si="2"/>
         <v>1201005</v>
       </c>
-      <c r="B129" s="5">
+      <c r="B129" s="4">
         <v>1201</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="C129" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="4">
         <v>5</v>
       </c>
-      <c r="E129" s="10">
+      <c r="E129" s="4">
         <v>10</v>
       </c>
-      <c r="F129" s="10" t="s">
+      <c r="F129" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G129" s="11">
+      <c r="G129" s="7">
         <v>4500</v>
       </c>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8" t="s">
+      <c r="H129" s="7"/>
+      <c r="I129" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J129" s="16">
-        <v>60</v>
-      </c>
-      <c r="K129" s="17" t="s">
+      <c r="J129" s="9">
+        <v>60</v>
+      </c>
+      <c r="K129" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:11">
-      <c r="A130" s="5">
+      <c r="A130" s="4">
         <f t="shared" si="2"/>
         <v>1201006</v>
       </c>
-      <c r="B130" s="5">
+      <c r="B130" s="4">
         <v>1201</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C130" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D130" s="5">
+      <c r="D130" s="4">
         <v>6</v>
       </c>
-      <c r="E130" s="10">
+      <c r="E130" s="4">
         <v>12</v>
       </c>
-      <c r="F130" s="10" t="s">
+      <c r="F130" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G130" s="11">
+      <c r="G130" s="7">
         <v>6000</v>
       </c>
-      <c r="H130" s="8"/>
-      <c r="I130" s="8" t="s">
+      <c r="H130" s="7"/>
+      <c r="I130" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="J130" s="16">
-        <v>60</v>
-      </c>
-      <c r="K130" s="17" t="s">
+      <c r="J130" s="9">
+        <v>60</v>
+      </c>
+      <c r="K130" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:11">
-      <c r="A131" s="5">
+      <c r="A131" s="4">
         <f t="shared" si="2"/>
         <v>1201007</v>
       </c>
-      <c r="B131" s="5">
+      <c r="B131" s="4">
         <v>1201</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C131" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D131" s="5">
+      <c r="D131" s="4">
         <v>7</v>
       </c>
-      <c r="E131" s="10">
+      <c r="E131" s="4">
         <v>14</v>
       </c>
-      <c r="F131" s="10" t="s">
+      <c r="F131" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G131" s="11">
+      <c r="G131" s="7">
         <v>9000</v>
       </c>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8" t="s">
+      <c r="H131" s="7"/>
+      <c r="I131" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="J131" s="16">
-        <v>60</v>
-      </c>
-      <c r="K131" s="17" t="s">
+      <c r="J131" s="9">
+        <v>60</v>
+      </c>
+      <c r="K131" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:11">
-      <c r="A132" s="5">
+      <c r="A132" s="4">
         <f t="shared" si="2"/>
         <v>1201008</v>
       </c>
-      <c r="B132" s="5">
+      <c r="B132" s="4">
         <v>1201</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C132" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="4">
         <v>8</v>
       </c>
-      <c r="E132" s="10">
+      <c r="E132" s="4">
         <v>16</v>
       </c>
-      <c r="F132" s="10" t="s">
+      <c r="F132" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G132" s="11">
+      <c r="G132" s="7">
         <v>15000</v>
       </c>
-      <c r="H132" s="8"/>
-      <c r="I132" s="8" t="s">
+      <c r="H132" s="7"/>
+      <c r="I132" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="J132" s="16">
-        <v>60</v>
-      </c>
-      <c r="K132" s="17" t="s">
+      <c r="J132" s="9">
+        <v>60</v>
+      </c>
+      <c r="K132" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:11">
-      <c r="A133" s="5">
+      <c r="A133" s="4">
         <f t="shared" si="2"/>
         <v>1201009</v>
       </c>
-      <c r="B133" s="5">
+      <c r="B133" s="4">
         <v>1201</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C133" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D133" s="18">
+      <c r="D133" s="11">
         <v>9</v>
       </c>
-      <c r="E133" s="10">
+      <c r="E133" s="4">
         <v>18</v>
       </c>
-      <c r="F133" s="10" t="s">
+      <c r="F133" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G133" s="11">
+      <c r="G133" s="7">
         <v>30000</v>
       </c>
-      <c r="H133" s="19"/>
-      <c r="I133" s="8" t="s">
+      <c r="H133" s="12"/>
+      <c r="I133" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J133" s="16">
-        <v>60</v>
-      </c>
-      <c r="K133" s="17" t="s">
+      <c r="J133" s="9">
+        <v>60</v>
+      </c>
+      <c r="K133" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:11">
-      <c r="A134" s="5">
+      <c r="A134" s="4">
         <f t="shared" si="2"/>
         <v>1201010</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134" s="4">
         <v>1201</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C134" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="4">
         <v>10</v>
       </c>
-      <c r="E134" s="10">
+      <c r="E134" s="4">
         <v>20</v>
       </c>
-      <c r="F134" s="10" t="s">
+      <c r="F134" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G134" s="11">
+      <c r="G134" s="7">
         <v>10000</v>
       </c>
-      <c r="H134" s="8"/>
-      <c r="I134" s="8" t="s">
+      <c r="H134" s="7"/>
+      <c r="I134" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J134" s="16">
-        <v>60</v>
-      </c>
-      <c r="K134" s="17" t="s">
+      <c r="J134" s="9">
+        <v>60</v>
+      </c>
+      <c r="K134" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:11">
-      <c r="A135" s="5">
+      <c r="A135" s="4">
         <f t="shared" si="2"/>
         <v>1202001</v>
       </c>
-      <c r="B135" s="5">
+      <c r="B135" s="4">
         <v>1202</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="C135" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="10">
+      <c r="E135" s="4">
         <v>2</v>
       </c>
-      <c r="F135" s="10" t="s">
+      <c r="F135" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G135" s="8">
+      <c r="G135" s="7">
         <v>15</v>
       </c>
-      <c r="H135" s="8"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="16">
-        <v>60</v>
-      </c>
-      <c r="K135" s="17" t="s">
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="9">
+        <v>60</v>
+      </c>
+      <c r="K135" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:11">
-      <c r="A136" s="5">
+      <c r="A136" s="4">
         <f t="shared" si="2"/>
         <v>1202002</v>
       </c>
-      <c r="B136" s="5">
+      <c r="B136" s="4">
         <v>1202</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C136" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D136" s="4">
         <v>2</v>
       </c>
-      <c r="E136" s="10">
+      <c r="E136" s="4">
         <v>4</v>
       </c>
-      <c r="F136" s="10" t="s">
+      <c r="F136" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G136" s="8">
+      <c r="G136" s="7">
         <v>25</v>
       </c>
-      <c r="H136" s="8"/>
-      <c r="I136" s="8" t="s">
+      <c r="H136" s="7"/>
+      <c r="I136" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="J136" s="16">
-        <v>60</v>
-      </c>
-      <c r="K136" s="17" t="s">
+      <c r="J136" s="9">
+        <v>60</v>
+      </c>
+      <c r="K136" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:11">
-      <c r="A137" s="5">
+      <c r="A137" s="4">
         <f t="shared" si="2"/>
         <v>1202003</v>
       </c>
-      <c r="B137" s="5">
+      <c r="B137" s="4">
         <v>1202</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C137" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D137" s="4">
         <v>3</v>
       </c>
-      <c r="E137" s="10">
+      <c r="E137" s="4">
         <v>6</v>
       </c>
-      <c r="F137" s="10" t="s">
+      <c r="F137" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G137" s="8">
+      <c r="G137" s="7">
         <v>35</v>
       </c>
-      <c r="H137" s="8"/>
-      <c r="I137" s="8" t="s">
+      <c r="H137" s="7"/>
+      <c r="I137" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="J137" s="16">
-        <v>60</v>
-      </c>
-      <c r="K137" s="17" t="s">
+      <c r="J137" s="9">
+        <v>60</v>
+      </c>
+      <c r="K137" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:11">
-      <c r="A138" s="5">
+      <c r="A138" s="4">
         <f t="shared" si="2"/>
         <v>1202004</v>
       </c>
-      <c r="B138" s="5">
+      <c r="B138" s="4">
         <v>1202</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C138" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="4">
         <v>4</v>
       </c>
-      <c r="E138" s="10">
+      <c r="E138" s="4">
         <v>8</v>
       </c>
-      <c r="F138" s="10" t="s">
+      <c r="F138" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G138" s="8">
+      <c r="G138" s="7">
         <v>45</v>
       </c>
-      <c r="H138" s="8"/>
-      <c r="I138" s="8" t="s">
+      <c r="H138" s="7"/>
+      <c r="I138" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="J138" s="16">
-        <v>60</v>
-      </c>
-      <c r="K138" s="17" t="s">
+      <c r="J138" s="9">
+        <v>60</v>
+      </c>
+      <c r="K138" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:11">
-      <c r="A139" s="5">
+      <c r="A139" s="4">
         <f t="shared" si="2"/>
         <v>1202005</v>
       </c>
-      <c r="B139" s="5">
+      <c r="B139" s="4">
         <v>1202</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="C139" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="4">
         <v>5</v>
       </c>
-      <c r="E139" s="10">
+      <c r="E139" s="4">
         <v>10</v>
       </c>
-      <c r="F139" s="10" t="s">
+      <c r="F139" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G139" s="8">
+      <c r="G139" s="7">
         <v>55</v>
       </c>
-      <c r="H139" s="8"/>
-      <c r="I139" s="8" t="s">
+      <c r="H139" s="7"/>
+      <c r="I139" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="J139" s="16">
-        <v>60</v>
-      </c>
-      <c r="K139" s="17" t="s">
+      <c r="J139" s="9">
+        <v>60</v>
+      </c>
+      <c r="K139" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:11">
-      <c r="A140" s="5">
+      <c r="A140" s="4">
         <f t="shared" si="2"/>
         <v>1202006</v>
       </c>
-      <c r="B140" s="5">
+      <c r="B140" s="4">
         <v>1202</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C140" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140" s="4">
         <v>6</v>
       </c>
-      <c r="E140" s="10">
+      <c r="E140" s="4">
         <v>12</v>
       </c>
-      <c r="F140" s="10" t="s">
+      <c r="F140" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G140" s="8">
+      <c r="G140" s="7">
         <v>65</v>
       </c>
-      <c r="H140" s="8"/>
-      <c r="I140" s="8" t="s">
+      <c r="H140" s="7"/>
+      <c r="I140" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="J140" s="16">
-        <v>60</v>
-      </c>
-      <c r="K140" s="17" t="s">
+      <c r="J140" s="9">
+        <v>60</v>
+      </c>
+      <c r="K140" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:11">
-      <c r="A141" s="5">
+      <c r="A141" s="4">
         <f t="shared" si="2"/>
         <v>1202007</v>
       </c>
-      <c r="B141" s="5">
+      <c r="B141" s="4">
         <v>1202</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="C141" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D141" s="4">
         <v>7</v>
       </c>
-      <c r="E141" s="10">
+      <c r="E141" s="4">
         <v>14</v>
       </c>
-      <c r="F141" s="10" t="s">
+      <c r="F141" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G141" s="8">
+      <c r="G141" s="7">
         <v>75</v>
       </c>
-      <c r="H141" s="8"/>
-      <c r="I141" s="8" t="s">
+      <c r="H141" s="7"/>
+      <c r="I141" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="J141" s="16">
-        <v>60</v>
-      </c>
-      <c r="K141" s="17" t="s">
+      <c r="J141" s="9">
+        <v>60</v>
+      </c>
+      <c r="K141" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:11">
-      <c r="A142" s="5">
+      <c r="A142" s="4">
         <f t="shared" si="2"/>
         <v>1202008</v>
       </c>
-      <c r="B142" s="5">
+      <c r="B142" s="4">
         <v>1202</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142" s="4">
         <v>8</v>
       </c>
-      <c r="E142" s="10">
+      <c r="E142" s="4">
         <v>16</v>
       </c>
-      <c r="F142" s="10" t="s">
+      <c r="F142" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G142" s="8">
+      <c r="G142" s="7">
         <v>85</v>
       </c>
-      <c r="H142" s="8"/>
-      <c r="I142" s="8" t="s">
+      <c r="H142" s="7"/>
+      <c r="I142" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="J142" s="16">
-        <v>60</v>
-      </c>
-      <c r="K142" s="17" t="s">
+      <c r="J142" s="9">
+        <v>60</v>
+      </c>
+      <c r="K142" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="1:11">
-      <c r="A143" s="5">
+      <c r="A143" s="4">
         <f t="shared" si="2"/>
         <v>1202009</v>
       </c>
-      <c r="B143" s="5">
+      <c r="B143" s="4">
         <v>1202</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C143" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D143" s="18">
+      <c r="D143" s="11">
         <v>9</v>
       </c>
-      <c r="E143" s="10">
+      <c r="E143" s="4">
         <v>18</v>
       </c>
-      <c r="F143" s="10" t="s">
+      <c r="F143" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G143" s="8">
+      <c r="G143" s="7">
         <v>95</v>
       </c>
-      <c r="H143" s="19"/>
-      <c r="I143" s="8" t="s">
+      <c r="H143" s="12"/>
+      <c r="I143" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="J143" s="16">
-        <v>60</v>
-      </c>
-      <c r="K143" s="17" t="s">
+      <c r="J143" s="9">
+        <v>60</v>
+      </c>
+      <c r="K143" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:11">
-      <c r="A144" s="5">
+      <c r="A144" s="4">
         <f t="shared" si="2"/>
         <v>1202010</v>
       </c>
-      <c r="B144" s="5">
+      <c r="B144" s="4">
         <v>1202</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="C144" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="4">
         <v>10</v>
       </c>
-      <c r="E144" s="10">
+      <c r="E144" s="4">
         <v>20</v>
       </c>
-      <c r="F144" s="10" t="s">
+      <c r="F144" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G144" s="8">
+      <c r="G144" s="7">
         <v>105</v>
       </c>
-      <c r="H144" s="8"/>
-      <c r="I144" s="8" t="s">
+      <c r="H144" s="7"/>
+      <c r="I144" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="J144" s="16">
-        <v>60</v>
-      </c>
-      <c r="K144" s="17" t="s">
+      <c r="J144" s="9">
+        <v>60</v>
+      </c>
+      <c r="K144" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="1:11">
-      <c r="A145" s="5">
+      <c r="A145" s="4">
         <f t="shared" si="2"/>
         <v>1301001</v>
       </c>
-      <c r="B145" s="5">
+      <c r="B145" s="4">
         <v>1301</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C145" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="20"/>
-      <c r="F145" s="10" t="s">
+      <c r="E145" s="13"/>
+      <c r="F145" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G145" s="8">
+      <c r="G145" s="7">
         <v>1000</v>
       </c>
-      <c r="H145" s="20"/>
-      <c r="I145" s="20"/>
-      <c r="J145" s="16">
-        <v>60</v>
-      </c>
-      <c r="K145" s="17" t="s">
+      <c r="H145" s="13"/>
+      <c r="I145" s="13"/>
+      <c r="J145" s="9">
+        <v>60</v>
+      </c>
+      <c r="K145" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:11">
-      <c r="A146" s="5">
+      <c r="A146" s="4">
         <f t="shared" si="2"/>
         <v>1301002</v>
       </c>
-      <c r="B146" s="5">
+      <c r="B146" s="4">
         <v>1301</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C146" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D146" s="5">
+      <c r="D146" s="4">
         <v>2</v>
       </c>
-      <c r="E146" s="20"/>
-      <c r="F146" s="10" t="s">
+      <c r="E146" s="13"/>
+      <c r="F146" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G146" s="8">
+      <c r="G146" s="7">
         <v>2000</v>
       </c>
-      <c r="H146" s="20"/>
-      <c r="I146" s="20"/>
-      <c r="J146" s="16">
-        <v>60</v>
-      </c>
-      <c r="K146" s="17" t="s">
+      <c r="H146" s="13"/>
+      <c r="I146" s="13"/>
+      <c r="J146" s="9">
+        <v>60</v>
+      </c>
+      <c r="K146" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:11">
-      <c r="A147" s="5">
+      <c r="A147" s="4">
         <f t="shared" si="2"/>
         <v>1301003</v>
       </c>
-      <c r="B147" s="5">
+      <c r="B147" s="4">
         <v>1301</v>
       </c>
-      <c r="C147" s="5" t="s">
+      <c r="C147" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D147" s="5">
+      <c r="D147" s="4">
         <v>3</v>
       </c>
-      <c r="E147" s="20"/>
-      <c r="F147" s="10" t="s">
+      <c r="E147" s="13"/>
+      <c r="F147" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G147" s="8">
+      <c r="G147" s="7">
         <v>3000</v>
       </c>
-      <c r="H147" s="20"/>
-      <c r="I147" s="20"/>
-      <c r="J147" s="16">
-        <v>60</v>
-      </c>
-      <c r="K147" s="17" t="s">
+      <c r="H147" s="13"/>
+      <c r="I147" s="13"/>
+      <c r="J147" s="9">
+        <v>60</v>
+      </c>
+      <c r="K147" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:11">
-      <c r="A148" s="5">
+      <c r="A148" s="4">
         <f t="shared" si="2"/>
         <v>1301004</v>
       </c>
-      <c r="B148" s="5">
+      <c r="B148" s="4">
         <v>1301</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="C148" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D148" s="5">
+      <c r="D148" s="4">
         <v>4</v>
       </c>
-      <c r="E148" s="20"/>
-      <c r="F148" s="10" t="s">
+      <c r="E148" s="13"/>
+      <c r="F148" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G148" s="8">
+      <c r="G148" s="7">
         <v>4000</v>
       </c>
-      <c r="H148" s="20"/>
-      <c r="I148" s="20"/>
-      <c r="J148" s="16">
-        <v>60</v>
-      </c>
-      <c r="K148" s="17" t="s">
+      <c r="H148" s="13"/>
+      <c r="I148" s="13"/>
+      <c r="J148" s="9">
+        <v>60</v>
+      </c>
+      <c r="K148" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:11">
-      <c r="A149" s="5">
+      <c r="A149" s="4">
         <f t="shared" si="2"/>
         <v>1301005</v>
       </c>
-      <c r="B149" s="5">
+      <c r="B149" s="4">
         <v>1301</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="C149" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D149" s="4">
         <v>5</v>
       </c>
-      <c r="E149" s="20"/>
-      <c r="F149" s="10" t="s">
+      <c r="E149" s="13"/>
+      <c r="F149" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G149" s="8">
+      <c r="G149" s="7">
         <v>5000</v>
       </c>
-      <c r="H149" s="20"/>
-      <c r="I149" s="20"/>
-      <c r="J149" s="16">
-        <v>60</v>
-      </c>
-      <c r="K149" s="17" t="s">
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="9">
+        <v>60</v>
+      </c>
+      <c r="K149" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:11">
-      <c r="A150" s="5">
+      <c r="A150" s="4">
         <f t="shared" si="2"/>
         <v>1301006</v>
       </c>
-      <c r="B150" s="5">
+      <c r="B150" s="4">
         <v>1301</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C150" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D150" s="4">
         <v>6</v>
       </c>
-      <c r="E150" s="20"/>
-      <c r="F150" s="10" t="s">
+      <c r="E150" s="13"/>
+      <c r="F150" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G150" s="8">
+      <c r="G150" s="7">
         <v>6000</v>
       </c>
-      <c r="H150" s="20"/>
-      <c r="I150" s="20"/>
-      <c r="J150" s="16">
-        <v>60</v>
-      </c>
-      <c r="K150" s="17" t="s">
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="9">
+        <v>60</v>
+      </c>
+      <c r="K150" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:11">
-      <c r="A151" s="5">
+      <c r="A151" s="4">
         <f t="shared" si="2"/>
         <v>1301007</v>
       </c>
-      <c r="B151" s="5">
+      <c r="B151" s="4">
         <v>1301</v>
       </c>
-      <c r="C151" s="5" t="s">
+      <c r="C151" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D151" s="4">
         <v>7</v>
       </c>
-      <c r="E151" s="20"/>
-      <c r="F151" s="10" t="s">
+      <c r="E151" s="13"/>
+      <c r="F151" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G151" s="8">
+      <c r="G151" s="7">
         <v>7000</v>
       </c>
-      <c r="H151" s="20"/>
-      <c r="I151" s="20"/>
-      <c r="J151" s="16">
-        <v>60</v>
-      </c>
-      <c r="K151" s="17" t="s">
+      <c r="H151" s="13"/>
+      <c r="I151" s="13"/>
+      <c r="J151" s="9">
+        <v>60</v>
+      </c>
+      <c r="K151" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:11">
-      <c r="A152" s="5">
+      <c r="A152" s="4">
         <f t="shared" si="2"/>
         <v>1301008</v>
       </c>
-      <c r="B152" s="5">
+      <c r="B152" s="4">
         <v>1301</v>
       </c>
-      <c r="C152" s="5" t="s">
+      <c r="C152" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D152" s="4">
         <v>8</v>
       </c>
-      <c r="E152" s="20"/>
-      <c r="F152" s="10" t="s">
+      <c r="E152" s="13"/>
+      <c r="F152" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G152" s="8">
+      <c r="G152" s="7">
         <v>8000</v>
       </c>
-      <c r="H152" s="20"/>
-      <c r="I152" s="20"/>
-      <c r="J152" s="16">
-        <v>60</v>
-      </c>
-      <c r="K152" s="17" t="s">
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="9">
+        <v>60</v>
+      </c>
+      <c r="K152" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:11">
-      <c r="A153" s="5">
+      <c r="A153" s="4">
         <f t="shared" si="2"/>
         <v>1301009</v>
       </c>
-      <c r="B153" s="5">
+      <c r="B153" s="4">
         <v>1301</v>
       </c>
-      <c r="C153" s="5" t="s">
+      <c r="C153" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D153" s="18">
+      <c r="D153" s="11">
         <v>9</v>
       </c>
-      <c r="E153" s="20"/>
-      <c r="F153" s="10" t="s">
+      <c r="E153" s="13"/>
+      <c r="F153" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G153" s="8">
+      <c r="G153" s="7">
         <v>9000</v>
       </c>
-      <c r="H153" s="20"/>
-      <c r="I153" s="20"/>
-      <c r="J153" s="16">
-        <v>60</v>
-      </c>
-      <c r="K153" s="17" t="s">
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="9">
+        <v>60</v>
+      </c>
+      <c r="K153" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:11">
-      <c r="A154" s="5">
+      <c r="A154" s="4">
         <f t="shared" si="2"/>
         <v>1301010</v>
       </c>
-      <c r="B154" s="5">
+      <c r="B154" s="4">
         <v>1301</v>
       </c>
-      <c r="C154" s="5" t="s">
+      <c r="C154" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154" s="4">
         <v>10</v>
       </c>
-      <c r="E154" s="20"/>
-      <c r="F154" s="10" t="s">
+      <c r="E154" s="13"/>
+      <c r="F154" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G154" s="8">
+      <c r="G154" s="7">
         <v>10000</v>
       </c>
-      <c r="H154" s="20"/>
-      <c r="I154" s="20"/>
-      <c r="J154" s="16">
-        <v>60</v>
-      </c>
-      <c r="K154" s="17" t="s">
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+      <c r="J154" s="9">
+        <v>60</v>
+      </c>
+      <c r="K154" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A155" s="10">
+      <c r="A155" s="4">
         <f t="shared" ref="A155:A174" si="3">B155*1000+D155</f>
         <v>1302001</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B155" s="4">
         <v>1302</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C155" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D155" s="10">
+      <c r="D155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="21"/>
-      <c r="F155" s="10" t="s">
+      <c r="E155" s="13"/>
+      <c r="F155" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G155" s="11">
+      <c r="G155" s="7">
         <v>1</v>
       </c>
-      <c r="H155" s="11">
+      <c r="H155" s="7">
         <v>4030001</v>
       </c>
-      <c r="I155" s="11"/>
-      <c r="J155" s="12">
-        <v>60</v>
-      </c>
-      <c r="K155" s="13" t="s">
+      <c r="I155" s="7">
+        <v>100300</v>
+      </c>
+      <c r="J155" s="9">
+        <v>60</v>
+      </c>
+      <c r="K155" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A156" s="10">
+      <c r="A156" s="4">
         <f t="shared" si="3"/>
         <v>1302002</v>
       </c>
-      <c r="B156" s="10">
+      <c r="B156" s="4">
         <v>1302</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C156" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D156" s="10">
+      <c r="D156" s="4">
         <v>2</v>
       </c>
-      <c r="E156" s="21"/>
-      <c r="F156" s="10" t="s">
+      <c r="E156" s="13"/>
+      <c r="F156" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G156" s="11">
+      <c r="G156" s="7">
         <v>2</v>
       </c>
-      <c r="H156" s="11">
+      <c r="H156" s="7">
         <v>4030002</v>
       </c>
-      <c r="I156" s="21"/>
-      <c r="J156" s="12">
-        <v>60</v>
-      </c>
-      <c r="K156" s="13" t="s">
+      <c r="I156" s="13">
+        <v>103400</v>
+      </c>
+      <c r="J156" s="9">
+        <v>60</v>
+      </c>
+      <c r="K156" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A157" s="10">
+      <c r="A157" s="4">
         <f t="shared" si="3"/>
         <v>1302003</v>
       </c>
-      <c r="B157" s="10">
+      <c r="B157" s="4">
         <v>1302</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="C157" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D157" s="10">
+      <c r="D157" s="4">
         <v>3</v>
       </c>
-      <c r="E157" s="21"/>
-      <c r="F157" s="10" t="s">
+      <c r="E157" s="13"/>
+      <c r="F157" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G157" s="11">
+      <c r="G157" s="7">
         <v>3</v>
       </c>
-      <c r="H157" s="11">
+      <c r="H157" s="7">
         <v>4030003</v>
       </c>
-      <c r="I157" s="21"/>
-      <c r="J157" s="12">
-        <v>60</v>
-      </c>
-      <c r="K157" s="13" t="s">
+      <c r="I157" s="13">
+        <v>103500</v>
+      </c>
+      <c r="J157" s="9">
+        <v>60</v>
+      </c>
+      <c r="K157" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A158" s="10">
+      <c r="A158" s="4">
         <f t="shared" si="3"/>
         <v>1302004</v>
       </c>
-      <c r="B158" s="10">
+      <c r="B158" s="4">
         <v>1302</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="C158" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D158" s="10">
+      <c r="D158" s="4">
         <v>4</v>
       </c>
-      <c r="E158" s="21"/>
-      <c r="F158" s="10" t="s">
+      <c r="E158" s="13"/>
+      <c r="F158" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G158" s="11">
+      <c r="G158" s="7">
         <v>4</v>
       </c>
-      <c r="H158" s="11">
+      <c r="H158" s="7">
         <v>4030004</v>
       </c>
-      <c r="I158" s="21"/>
-      <c r="J158" s="12">
-        <v>60</v>
-      </c>
-      <c r="K158" s="13" t="s">
+      <c r="I158" s="13">
+        <v>101700</v>
+      </c>
+      <c r="J158" s="9">
+        <v>60</v>
+      </c>
+      <c r="K158" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A159" s="10">
+      <c r="A159" s="4">
         <f t="shared" si="3"/>
         <v>1302005</v>
       </c>
-      <c r="B159" s="10">
+      <c r="B159" s="4">
         <v>1302</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C159" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D159" s="10">
+      <c r="D159" s="4">
         <v>5</v>
       </c>
-      <c r="E159" s="21"/>
-      <c r="F159" s="10" t="s">
+      <c r="E159" s="13"/>
+      <c r="F159" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G159" s="11">
+      <c r="G159" s="7">
         <v>5</v>
       </c>
-      <c r="H159" s="11">
+      <c r="H159" s="7">
         <v>4030005</v>
       </c>
-      <c r="I159" s="21"/>
-      <c r="J159" s="12">
-        <v>60</v>
-      </c>
-      <c r="K159" s="13" t="s">
+      <c r="I159" s="13">
+        <v>101800</v>
+      </c>
+      <c r="J159" s="9">
+        <v>60</v>
+      </c>
+      <c r="K159" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A160" s="10">
+      <c r="A160" s="4">
         <f t="shared" si="3"/>
         <v>1302006</v>
       </c>
-      <c r="B160" s="10">
+      <c r="B160" s="4">
         <v>1302</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C160" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D160" s="10">
+      <c r="D160" s="4">
         <v>6</v>
       </c>
-      <c r="E160" s="21"/>
-      <c r="F160" s="10" t="s">
+      <c r="E160" s="13"/>
+      <c r="F160" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G160" s="11">
+      <c r="G160" s="7">
         <v>6</v>
       </c>
-      <c r="H160" s="11">
+      <c r="H160" s="7">
         <v>4030006</v>
       </c>
-      <c r="I160" s="21"/>
-      <c r="J160" s="12">
-        <v>60</v>
-      </c>
-      <c r="K160" s="13" t="s">
+      <c r="I160" s="13">
+        <v>102100</v>
+      </c>
+      <c r="J160" s="9">
+        <v>60</v>
+      </c>
+      <c r="K160" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A161" s="10">
+      <c r="A161" s="4">
         <f t="shared" si="3"/>
         <v>1302007</v>
       </c>
-      <c r="B161" s="10">
+      <c r="B161" s="4">
         <v>1302</v>
       </c>
-      <c r="C161" s="10" t="s">
+      <c r="C161" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D161" s="10">
+      <c r="D161" s="4">
         <v>7</v>
       </c>
-      <c r="E161" s="21"/>
-      <c r="F161" s="10" t="s">
+      <c r="E161" s="13"/>
+      <c r="F161" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G161" s="11">
+      <c r="G161" s="7">
         <v>7</v>
       </c>
-      <c r="H161" s="11">
+      <c r="H161" s="7">
         <v>4030007</v>
       </c>
-      <c r="I161" s="21"/>
-      <c r="J161" s="12">
-        <v>60</v>
-      </c>
-      <c r="K161" s="13" t="s">
+      <c r="I161" s="13"/>
+      <c r="J161" s="9">
+        <v>60</v>
+      </c>
+      <c r="K161" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A162" s="10">
+      <c r="A162" s="4">
         <f t="shared" si="3"/>
         <v>1302008</v>
       </c>
-      <c r="B162" s="10">
+      <c r="B162" s="4">
         <v>1302</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C162" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D162" s="10">
+      <c r="D162" s="4">
         <v>8</v>
       </c>
-      <c r="E162" s="21"/>
-      <c r="F162" s="10" t="s">
+      <c r="E162" s="13"/>
+      <c r="F162" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G162" s="11">
+      <c r="G162" s="7">
         <v>8</v>
       </c>
-      <c r="H162" s="11">
+      <c r="H162" s="7">
         <v>4030008</v>
       </c>
-      <c r="I162" s="21"/>
-      <c r="J162" s="12">
-        <v>60</v>
-      </c>
-      <c r="K162" s="13" t="s">
+      <c r="I162" s="13"/>
+      <c r="J162" s="9">
+        <v>60</v>
+      </c>
+      <c r="K162" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A163" s="10">
+      <c r="A163" s="4">
         <f t="shared" si="3"/>
         <v>1302009</v>
       </c>
-      <c r="B163" s="10">
+      <c r="B163" s="4">
         <v>1302</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D163" s="14">
+      <c r="D163" s="11">
         <v>9</v>
       </c>
-      <c r="E163" s="21"/>
-      <c r="F163" s="10" t="s">
+      <c r="E163" s="13"/>
+      <c r="F163" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G163" s="11">
+      <c r="G163" s="7">
         <v>9</v>
       </c>
-      <c r="H163" s="11">
+      <c r="H163" s="7">
         <v>4030009</v>
       </c>
-      <c r="I163" s="21"/>
-      <c r="J163" s="12">
-        <v>60</v>
-      </c>
-      <c r="K163" s="13" t="s">
+      <c r="I163" s="13"/>
+      <c r="J163" s="9">
+        <v>60</v>
+      </c>
+      <c r="K163" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A164" s="10">
+      <c r="A164" s="4">
         <f t="shared" si="3"/>
         <v>1302010</v>
       </c>
-      <c r="B164" s="10">
+      <c r="B164" s="4">
         <v>1302</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C164" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D164" s="10">
+      <c r="D164" s="4">
         <v>10</v>
       </c>
-      <c r="E164" s="21"/>
-      <c r="F164" s="10" t="s">
+      <c r="E164" s="13"/>
+      <c r="F164" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G164" s="11">
+      <c r="G164" s="7">
         <v>10</v>
       </c>
-      <c r="H164" s="11">
+      <c r="H164" s="7">
         <v>4030010</v>
       </c>
-      <c r="J164" s="12">
-        <v>60</v>
-      </c>
-      <c r="K164" s="13" t="s">
+      <c r="J164" s="9">
+        <v>60</v>
+      </c>
+      <c r="K164" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="165" customHeight="1" spans="1:11">
-      <c r="A165" s="5">
+      <c r="A165" s="4">
         <f t="shared" si="3"/>
         <v>1303001</v>
       </c>
-      <c r="B165" s="5">
+      <c r="B165" s="4">
         <v>1303</v>
       </c>
-      <c r="C165" s="5" t="s">
+      <c r="C165" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D165" s="5">
+      <c r="D165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="20"/>
-      <c r="F165" s="10" t="s">
+      <c r="E165" s="13"/>
+      <c r="F165" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G165" s="8">
+      <c r="G165" s="7">
         <v>100</v>
       </c>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
-      <c r="J165" s="16">
-        <v>60</v>
-      </c>
-      <c r="K165" s="17" t="s">
+      <c r="H165" s="13"/>
+      <c r="I165" s="13"/>
+      <c r="J165" s="9">
+        <v>60</v>
+      </c>
+      <c r="K165" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:11">
-      <c r="A166" s="5">
+      <c r="A166" s="4">
         <f t="shared" si="3"/>
         <v>1303002</v>
       </c>
-      <c r="B166" s="5">
+      <c r="B166" s="4">
         <v>1303</v>
       </c>
-      <c r="C166" s="5" t="s">
+      <c r="C166" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D166" s="5">
+      <c r="D166" s="4">
         <v>2</v>
       </c>
-      <c r="E166" s="20"/>
-      <c r="F166" s="10" t="s">
+      <c r="E166" s="13"/>
+      <c r="F166" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G166" s="8">
+      <c r="G166" s="7">
         <v>200</v>
       </c>
-      <c r="H166" s="20"/>
-      <c r="I166" s="20"/>
-      <c r="J166" s="16">
-        <v>60</v>
-      </c>
-      <c r="K166" s="17" t="s">
+      <c r="H166" s="13"/>
+      <c r="I166" s="13"/>
+      <c r="J166" s="9">
+        <v>60</v>
+      </c>
+      <c r="K166" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:11">
-      <c r="A167" s="5">
+      <c r="A167" s="4">
         <f t="shared" si="3"/>
         <v>1303003</v>
       </c>
-      <c r="B167" s="5">
+      <c r="B167" s="4">
         <v>1303</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="C167" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D167" s="5">
+      <c r="D167" s="4">
         <v>3</v>
       </c>
-      <c r="E167" s="20"/>
-      <c r="F167" s="10" t="s">
+      <c r="E167" s="13"/>
+      <c r="F167" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G167" s="8">
+      <c r="G167" s="7">
         <v>300</v>
       </c>
-      <c r="H167" s="20"/>
-      <c r="I167" s="20"/>
-      <c r="J167" s="16">
-        <v>60</v>
-      </c>
-      <c r="K167" s="17" t="s">
+      <c r="H167" s="13"/>
+      <c r="I167" s="13"/>
+      <c r="J167" s="9">
+        <v>60</v>
+      </c>
+      <c r="K167" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:11">
-      <c r="A168" s="5">
+      <c r="A168" s="4">
         <f t="shared" si="3"/>
         <v>1303004</v>
       </c>
-      <c r="B168" s="5">
+      <c r="B168" s="4">
         <v>1303</v>
       </c>
-      <c r="C168" s="5" t="s">
+      <c r="C168" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D168" s="5">
+      <c r="D168" s="4">
         <v>4</v>
       </c>
-      <c r="E168" s="20"/>
-      <c r="F168" s="10" t="s">
+      <c r="E168" s="13"/>
+      <c r="F168" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G168" s="8">
+      <c r="G168" s="7">
         <v>400</v>
       </c>
-      <c r="H168" s="20"/>
-      <c r="I168" s="20"/>
-      <c r="J168" s="16">
-        <v>60</v>
-      </c>
-      <c r="K168" s="17" t="s">
+      <c r="H168" s="13"/>
+      <c r="I168" s="13"/>
+      <c r="J168" s="9">
+        <v>60</v>
+      </c>
+      <c r="K168" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:11">
-      <c r="A169" s="5">
+      <c r="A169" s="4">
         <f t="shared" si="3"/>
         <v>1303005</v>
       </c>
-      <c r="B169" s="5">
+      <c r="B169" s="4">
         <v>1303</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="C169" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D169" s="5">
+      <c r="D169" s="4">
         <v>5</v>
       </c>
-      <c r="E169" s="20"/>
-      <c r="F169" s="10" t="s">
+      <c r="E169" s="13"/>
+      <c r="F169" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G169" s="8">
+      <c r="G169" s="7">
         <v>500</v>
       </c>
-      <c r="H169" s="20"/>
-      <c r="I169" s="20"/>
-      <c r="J169" s="16">
-        <v>60</v>
-      </c>
-      <c r="K169" s="17" t="s">
+      <c r="H169" s="13"/>
+      <c r="I169" s="13"/>
+      <c r="J169" s="9">
+        <v>60</v>
+      </c>
+      <c r="K169" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:11">
-      <c r="A170" s="5">
+      <c r="A170" s="4">
         <f t="shared" si="3"/>
         <v>1303006</v>
       </c>
-      <c r="B170" s="5">
+      <c r="B170" s="4">
         <v>1303</v>
       </c>
-      <c r="C170" s="5" t="s">
+      <c r="C170" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D170" s="5">
+      <c r="D170" s="4">
         <v>6</v>
       </c>
-      <c r="E170" s="20"/>
-      <c r="F170" s="10" t="s">
+      <c r="E170" s="13"/>
+      <c r="F170" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G170" s="8">
+      <c r="G170" s="7">
         <v>600</v>
       </c>
-      <c r="H170" s="20"/>
-      <c r="I170" s="20"/>
-      <c r="J170" s="16">
-        <v>60</v>
-      </c>
-      <c r="K170" s="17" t="s">
+      <c r="H170" s="13"/>
+      <c r="I170" s="13"/>
+      <c r="J170" s="9">
+        <v>60</v>
+      </c>
+      <c r="K170" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:11">
-      <c r="A171" s="5">
+      <c r="A171" s="4">
         <f t="shared" si="3"/>
         <v>1303007</v>
       </c>
-      <c r="B171" s="5">
+      <c r="B171" s="4">
         <v>1303</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C171" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D171" s="5">
+      <c r="D171" s="4">
         <v>7</v>
       </c>
-      <c r="E171" s="20"/>
-      <c r="F171" s="10" t="s">
+      <c r="E171" s="13"/>
+      <c r="F171" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G171" s="8">
+      <c r="G171" s="7">
         <v>700</v>
       </c>
-      <c r="H171" s="20"/>
-      <c r="I171" s="20"/>
-      <c r="J171" s="16">
-        <v>60</v>
-      </c>
-      <c r="K171" s="17" t="s">
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="9">
+        <v>60</v>
+      </c>
+      <c r="K171" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:11">
-      <c r="A172" s="5">
+      <c r="A172" s="4">
         <f t="shared" si="3"/>
         <v>1303008</v>
       </c>
-      <c r="B172" s="5">
+      <c r="B172" s="4">
         <v>1303</v>
       </c>
-      <c r="C172" s="5" t="s">
+      <c r="C172" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D172" s="5">
+      <c r="D172" s="4">
         <v>8</v>
       </c>
-      <c r="E172" s="20"/>
-      <c r="F172" s="10" t="s">
+      <c r="E172" s="13"/>
+      <c r="F172" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G172" s="8">
+      <c r="G172" s="7">
         <v>800</v>
       </c>
-      <c r="H172" s="20"/>
-      <c r="I172" s="20"/>
-      <c r="J172" s="16">
-        <v>60</v>
-      </c>
-      <c r="K172" s="17" t="s">
+      <c r="H172" s="13"/>
+      <c r="I172" s="13"/>
+      <c r="J172" s="9">
+        <v>60</v>
+      </c>
+      <c r="K172" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:11">
-      <c r="A173" s="5">
+      <c r="A173" s="4">
         <f t="shared" si="3"/>
         <v>1303009</v>
       </c>
-      <c r="B173" s="5">
+      <c r="B173" s="4">
         <v>1303</v>
       </c>
-      <c r="C173" s="5" t="s">
+      <c r="C173" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D173" s="18">
+      <c r="D173" s="11">
         <v>9</v>
       </c>
-      <c r="E173" s="20"/>
-      <c r="F173" s="10" t="s">
+      <c r="E173" s="13"/>
+      <c r="F173" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G173" s="8">
+      <c r="G173" s="7">
         <v>900</v>
       </c>
-      <c r="H173" s="20"/>
-      <c r="I173" s="20"/>
-      <c r="J173" s="16">
-        <v>60</v>
-      </c>
-      <c r="K173" s="17" t="s">
+      <c r="H173" s="13"/>
+      <c r="I173" s="13"/>
+      <c r="J173" s="9">
+        <v>60</v>
+      </c>
+      <c r="K173" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:11">
-      <c r="A174" s="5">
+      <c r="A174" s="4">
         <f t="shared" si="3"/>
         <v>1303010</v>
       </c>
-      <c r="B174" s="5">
+      <c r="B174" s="4">
         <v>1303</v>
       </c>
-      <c r="C174" s="5" t="s">
+      <c r="C174" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D174" s="5">
+      <c r="D174" s="4">
         <v>10</v>
       </c>
-      <c r="E174" s="20"/>
-      <c r="F174" s="10" t="s">
+      <c r="E174" s="13"/>
+      <c r="F174" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G174" s="8">
+      <c r="G174" s="7">
         <v>1000</v>
       </c>
-      <c r="H174" s="20"/>
-      <c r="I174" s="20"/>
-      <c r="J174" s="16">
-        <v>60</v>
-      </c>
-      <c r="K174" s="17" t="s">
+      <c r="H174" s="13"/>
+      <c r="I174" s="13"/>
+      <c r="J174" s="9">
+        <v>60</v>
+      </c>
+      <c r="K174" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:11">
-      <c r="A175" s="5">
+      <c r="A175" s="4">
         <f t="shared" ref="A175:A184" si="4">B175*1000+D175</f>
         <v>1304001</v>
       </c>
-      <c r="B175" s="5">
+      <c r="B175" s="4">
         <v>1304</v>
       </c>
-      <c r="C175" s="5" t="s">
+      <c r="C175" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D175" s="5">
+      <c r="D175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="20"/>
-      <c r="F175" s="10" t="s">
+      <c r="E175" s="13"/>
+      <c r="F175" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G175" s="8">
+      <c r="G175" s="7">
         <v>100</v>
       </c>
-      <c r="H175" s="20"/>
-      <c r="I175" s="20"/>
-      <c r="J175" s="16">
-        <v>60</v>
-      </c>
-      <c r="K175" s="17" t="s">
+      <c r="H175" s="13"/>
+      <c r="I175" s="13"/>
+      <c r="J175" s="9">
+        <v>60</v>
+      </c>
+      <c r="K175" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="176" customHeight="1" spans="1:11">
-      <c r="A176" s="5">
+      <c r="A176" s="4">
         <f t="shared" si="4"/>
         <v>1304002</v>
       </c>
-      <c r="B176" s="5">
+      <c r="B176" s="4">
         <v>1304</v>
       </c>
-      <c r="C176" s="5" t="s">
+      <c r="C176" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D176" s="5">
+      <c r="D176" s="4">
         <v>2</v>
       </c>
-      <c r="E176" s="20"/>
-      <c r="F176" s="10" t="s">
+      <c r="E176" s="13"/>
+      <c r="F176" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G176" s="8">
+      <c r="G176" s="7">
         <v>200</v>
       </c>
-      <c r="H176" s="20"/>
-      <c r="I176" s="20"/>
-      <c r="J176" s="16">
-        <v>60</v>
-      </c>
-      <c r="K176" s="17" t="s">
+      <c r="H176" s="13"/>
+      <c r="I176" s="13"/>
+      <c r="J176" s="9">
+        <v>60</v>
+      </c>
+      <c r="K176" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="177" customHeight="1" spans="1:11">
-      <c r="A177" s="5">
+      <c r="A177" s="4">
         <f t="shared" si="4"/>
         <v>1304003</v>
       </c>
-      <c r="B177" s="5">
+      <c r="B177" s="4">
         <v>1304</v>
       </c>
-      <c r="C177" s="5" t="s">
+      <c r="C177" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D177" s="5">
+      <c r="D177" s="4">
         <v>3</v>
       </c>
-      <c r="E177" s="20"/>
-      <c r="F177" s="10" t="s">
+      <c r="E177" s="13"/>
+      <c r="F177" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G177" s="8">
+      <c r="G177" s="7">
         <v>300</v>
       </c>
-      <c r="H177" s="20"/>
-      <c r="I177" s="20"/>
-      <c r="J177" s="16">
-        <v>60</v>
-      </c>
-      <c r="K177" s="17" t="s">
+      <c r="H177" s="13"/>
+      <c r="I177" s="13"/>
+      <c r="J177" s="9">
+        <v>60</v>
+      </c>
+      <c r="K177" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:11">
-      <c r="A178" s="5">
+      <c r="A178" s="4">
         <f t="shared" si="4"/>
         <v>1304004</v>
       </c>
-      <c r="B178" s="5">
+      <c r="B178" s="4">
         <v>1304</v>
       </c>
-      <c r="C178" s="5" t="s">
+      <c r="C178" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D178" s="5">
+      <c r="D178" s="4">
         <v>4</v>
       </c>
-      <c r="E178" s="20"/>
-      <c r="F178" s="10" t="s">
+      <c r="E178" s="13"/>
+      <c r="F178" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G178" s="8">
+      <c r="G178" s="7">
         <v>400</v>
       </c>
-      <c r="H178" s="20"/>
-      <c r="I178" s="20"/>
-      <c r="J178" s="16">
-        <v>60</v>
-      </c>
-      <c r="K178" s="17" t="s">
+      <c r="H178" s="13"/>
+      <c r="I178" s="13"/>
+      <c r="J178" s="9">
+        <v>60</v>
+      </c>
+      <c r="K178" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:11">
-      <c r="A179" s="5">
+      <c r="A179" s="4">
         <f t="shared" si="4"/>
         <v>1304005</v>
       </c>
-      <c r="B179" s="5">
+      <c r="B179" s="4">
         <v>1304</v>
       </c>
-      <c r="C179" s="5" t="s">
+      <c r="C179" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D179" s="5">
+      <c r="D179" s="4">
         <v>5</v>
       </c>
-      <c r="E179" s="20"/>
-      <c r="F179" s="10" t="s">
+      <c r="E179" s="13"/>
+      <c r="F179" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G179" s="8">
+      <c r="G179" s="7">
         <v>500</v>
       </c>
-      <c r="H179" s="20"/>
-      <c r="I179" s="20"/>
-      <c r="J179" s="16">
-        <v>60</v>
-      </c>
-      <c r="K179" s="17" t="s">
+      <c r="H179" s="13"/>
+      <c r="I179" s="13"/>
+      <c r="J179" s="9">
+        <v>60</v>
+      </c>
+      <c r="K179" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:11">
-      <c r="A180" s="5">
+      <c r="A180" s="4">
         <f t="shared" si="4"/>
         <v>1304006</v>
       </c>
-      <c r="B180" s="5">
+      <c r="B180" s="4">
         <v>1304</v>
       </c>
-      <c r="C180" s="5" t="s">
+      <c r="C180" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D180" s="5">
+      <c r="D180" s="4">
         <v>6</v>
       </c>
-      <c r="E180" s="20"/>
-      <c r="F180" s="10" t="s">
+      <c r="E180" s="13"/>
+      <c r="F180" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G180" s="8">
+      <c r="G180" s="7">
         <v>600</v>
       </c>
-      <c r="H180" s="20"/>
-      <c r="I180" s="20"/>
-      <c r="J180" s="16">
-        <v>60</v>
-      </c>
-      <c r="K180" s="17" t="s">
+      <c r="H180" s="13"/>
+      <c r="I180" s="13"/>
+      <c r="J180" s="9">
+        <v>60</v>
+      </c>
+      <c r="K180" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:11">
-      <c r="A181" s="5">
+      <c r="A181" s="4">
         <f t="shared" si="4"/>
         <v>1304007</v>
       </c>
-      <c r="B181" s="5">
+      <c r="B181" s="4">
         <v>1304</v>
       </c>
-      <c r="C181" s="5" t="s">
+      <c r="C181" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D181" s="5">
+      <c r="D181" s="4">
         <v>7</v>
       </c>
-      <c r="E181" s="20"/>
-      <c r="F181" s="10" t="s">
+      <c r="E181" s="13"/>
+      <c r="F181" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="8">
+      <c r="G181" s="7">
         <v>700</v>
       </c>
-      <c r="H181" s="20"/>
-      <c r="I181" s="20"/>
-      <c r="J181" s="16">
-        <v>60</v>
-      </c>
-      <c r="K181" s="17" t="s">
+      <c r="H181" s="13"/>
+      <c r="I181" s="13"/>
+      <c r="J181" s="9">
+        <v>60</v>
+      </c>
+      <c r="K181" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:11">
-      <c r="A182" s="5">
+      <c r="A182" s="4">
         <f t="shared" si="4"/>
         <v>1304008</v>
       </c>
-      <c r="B182" s="5">
+      <c r="B182" s="4">
         <v>1304</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C182" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D182" s="4">
         <v>8</v>
       </c>
-      <c r="E182" s="20"/>
-      <c r="F182" s="10" t="s">
+      <c r="E182" s="13"/>
+      <c r="F182" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G182" s="8">
+      <c r="G182" s="7">
         <v>800</v>
       </c>
-      <c r="H182" s="20"/>
-      <c r="I182" s="20"/>
-      <c r="J182" s="16">
-        <v>60</v>
-      </c>
-      <c r="K182" s="17" t="s">
+      <c r="H182" s="13"/>
+      <c r="I182" s="13"/>
+      <c r="J182" s="9">
+        <v>60</v>
+      </c>
+      <c r="K182" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:11">
-      <c r="A183" s="5">
+      <c r="A183" s="4">
         <f t="shared" si="4"/>
         <v>1304009</v>
       </c>
-      <c r="B183" s="5">
+      <c r="B183" s="4">
         <v>1304</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C183" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D183" s="18">
+      <c r="D183" s="11">
         <v>9</v>
       </c>
-      <c r="E183" s="20"/>
-      <c r="F183" s="10" t="s">
+      <c r="E183" s="13"/>
+      <c r="F183" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G183" s="8">
+      <c r="G183" s="7">
         <v>900</v>
       </c>
-      <c r="H183" s="20"/>
-      <c r="I183" s="20"/>
-      <c r="J183" s="16">
-        <v>60</v>
-      </c>
-      <c r="K183" s="17" t="s">
+      <c r="H183" s="13"/>
+      <c r="I183" s="13"/>
+      <c r="J183" s="9">
+        <v>60</v>
+      </c>
+      <c r="K183" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:11">
-      <c r="A184" s="5">
+      <c r="A184" s="4">
         <f t="shared" si="4"/>
         <v>1304010</v>
       </c>
-      <c r="B184" s="5">
+      <c r="B184" s="4">
         <v>1304</v>
       </c>
-      <c r="C184" s="5" t="s">
+      <c r="C184" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D184" s="5">
+      <c r="D184" s="4">
         <v>10</v>
       </c>
-      <c r="E184" s="20"/>
-      <c r="F184" s="10" t="s">
+      <c r="E184" s="13"/>
+      <c r="F184" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G184" s="8">
+      <c r="G184" s="7">
         <v>1000</v>
       </c>
-      <c r="H184" s="20"/>
-      <c r="I184" s="20"/>
-      <c r="J184" s="16">
-        <v>60</v>
-      </c>
-      <c r="K184" s="17" t="s">
+      <c r="H184" s="13"/>
+      <c r="I184" s="13"/>
+      <c r="J184" s="9">
+        <v>60</v>
+      </c>
+      <c r="K184" s="10" t="s">
         <v>28</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -1341,12 +1341,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1383,6 +1386,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1918,6086 +1924,6096 @@
     <col min="5" max="5" width="22.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="20.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="24" style="1" customWidth="1"/>
     <col min="11" max="11" width="32" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <f>B5*1000+D5</f>
         <v>1101001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>1101</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>1000</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="9">
-        <v>60</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="10">
+        <v>60</v>
+      </c>
+      <c r="K5" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <f t="shared" ref="A6:A69" si="0">B6*1000+D6</f>
         <v>1101002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>1101</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>1100</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="8"/>
+      <c r="I6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="9">
-        <v>60</v>
-      </c>
-      <c r="K6" s="10" t="s">
+      <c r="J6" s="10">
+        <v>60</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>1101003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>1101</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>2000</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="9">
-        <v>60</v>
-      </c>
-      <c r="K7" s="10" t="s">
+      <c r="J7" s="10">
+        <v>60</v>
+      </c>
+      <c r="K7" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>1101004</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>1101</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>4</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>8</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>3000</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="9">
-        <v>60</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="J8" s="10">
+        <v>60</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>1101005</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>1101</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>10</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>4500</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7" t="s">
+      <c r="H9" s="8"/>
+      <c r="I9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="9">
-        <v>60</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="J9" s="10">
+        <v>60</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>1101006</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>1101</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>6</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>12</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>6000</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="8"/>
+      <c r="I10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="9">
-        <v>60</v>
-      </c>
-      <c r="K10" s="10" t="s">
+      <c r="J10" s="10">
+        <v>60</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>1101007</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>1101</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>7</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>14</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>9000</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="9">
-        <v>60</v>
-      </c>
-      <c r="K11" s="10" t="s">
+      <c r="J11" s="10">
+        <v>60</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>1101008</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>1101</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>8</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>16</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>15000</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7" t="s">
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="9">
-        <v>60</v>
-      </c>
-      <c r="K12" s="10" t="s">
+      <c r="J12" s="10">
+        <v>60</v>
+      </c>
+      <c r="K12" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>1101009</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>1101</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <v>9</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>18</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <v>30000</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="7" t="s">
+      <c r="H13" s="13"/>
+      <c r="I13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="9">
-        <v>60</v>
-      </c>
-      <c r="K13" s="10" t="s">
+      <c r="J13" s="10">
+        <v>60</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>1101010</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>1101</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>10</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>20</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="8">
         <v>10000</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7" t="s">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="9">
-        <v>60</v>
-      </c>
-      <c r="K14" s="10" t="s">
+      <c r="J14" s="10">
+        <v>60</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>1102001</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>1102</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="8">
         <v>1000</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="9">
-        <v>60</v>
-      </c>
-      <c r="K15" s="10" t="s">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="10">
+        <v>60</v>
+      </c>
+      <c r="K15" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>1102002</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>1102</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>2</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>4</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>1100</v>
       </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7" t="s">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="9">
-        <v>60</v>
-      </c>
-      <c r="K16" s="10" t="s">
+      <c r="J16" s="10">
+        <v>60</v>
+      </c>
+      <c r="K16" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="4">
+      <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>1102003</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>1102</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>3</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>6</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>2000</v>
       </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7" t="s">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="9">
-        <v>60</v>
-      </c>
-      <c r="K17" s="10" t="s">
+      <c r="J17" s="10">
+        <v>60</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="4">
+      <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>1102004</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>1102</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>4</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>8</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>3000</v>
       </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="9">
-        <v>60</v>
-      </c>
-      <c r="K18" s="10" t="s">
+      <c r="J18" s="10">
+        <v>60</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:11">
-      <c r="A19" s="4">
+      <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>1102005</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>1102</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>5</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>10</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>4500</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7" t="s">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="J19" s="9">
-        <v>60</v>
-      </c>
-      <c r="K19" s="10" t="s">
+      <c r="J19" s="10">
+        <v>60</v>
+      </c>
+      <c r="K19" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="4">
+      <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>1102006</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>1102</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>6</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>12</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>6000</v>
       </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7" t="s">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="9">
-        <v>60</v>
-      </c>
-      <c r="K20" s="10" t="s">
+      <c r="J20" s="10">
+        <v>60</v>
+      </c>
+      <c r="K20" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="4">
+      <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>1102007</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <v>1102</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>7</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>14</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="8">
         <v>9000</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7" t="s">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="9">
-        <v>60</v>
-      </c>
-      <c r="K21" s="10" t="s">
+      <c r="J21" s="10">
+        <v>60</v>
+      </c>
+      <c r="K21" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="4">
+      <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>1102008</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>1102</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>8</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>16</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <v>15000</v>
       </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7" t="s">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="9">
-        <v>60</v>
-      </c>
-      <c r="K22" s="10" t="s">
+      <c r="J22" s="10">
+        <v>60</v>
+      </c>
+      <c r="K22" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="4">
+      <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>1102009</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="5">
         <v>1102</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="12">
         <v>9</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>18</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>30000</v>
       </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="7" t="s">
+      <c r="H23" s="13"/>
+      <c r="I23" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="9">
-        <v>60</v>
-      </c>
-      <c r="K23" s="10" t="s">
+      <c r="J23" s="10">
+        <v>60</v>
+      </c>
+      <c r="K23" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="4">
+      <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>1102010</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <v>1102</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>10</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>20</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="8">
         <v>10000</v>
       </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7" t="s">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J24" s="9">
-        <v>60</v>
-      </c>
-      <c r="K24" s="10" t="s">
+      <c r="J24" s="10">
+        <v>60</v>
+      </c>
+      <c r="K24" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:11">
-      <c r="A25" s="4">
+      <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>1103001</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <v>1103</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>1</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>2</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <v>1000</v>
       </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="9">
-        <v>60</v>
-      </c>
-      <c r="K25" s="10" t="s">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="10">
+        <v>60</v>
+      </c>
+      <c r="K25" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:11">
-      <c r="A26" s="4">
+      <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>1103002</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="5">
         <v>1103</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>2</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>4</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="8">
         <v>1100</v>
       </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7" t="s">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J26" s="9">
-        <v>60</v>
-      </c>
-      <c r="K26" s="10" t="s">
+      <c r="J26" s="10">
+        <v>60</v>
+      </c>
+      <c r="K26" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
-      <c r="A27" s="4">
+      <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>1103003</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="5">
         <v>1103</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>3</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>6</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="8">
         <v>2000</v>
       </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7" t="s">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="9">
-        <v>60</v>
-      </c>
-      <c r="K27" s="10" t="s">
+      <c r="J27" s="10">
+        <v>60</v>
+      </c>
+      <c r="K27" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
-      <c r="A28" s="4">
+      <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>1103004</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="5">
         <v>1103</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>4</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>8</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="8">
         <v>3000</v>
       </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J28" s="9">
-        <v>60</v>
-      </c>
-      <c r="K28" s="10" t="s">
+      <c r="H28" s="8"/>
+      <c r="I28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J28" s="10">
+        <v>60</v>
+      </c>
+      <c r="K28" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
-      <c r="A29" s="4">
+      <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>1103005</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <v>1103</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>5</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>10</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="8">
         <v>4500</v>
       </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7" t="s">
+      <c r="H29" s="8"/>
+      <c r="I29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J29" s="9">
-        <v>60</v>
-      </c>
-      <c r="K29" s="10" t="s">
+      <c r="J29" s="10">
+        <v>60</v>
+      </c>
+      <c r="K29" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
-      <c r="A30" s="4">
+      <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>1103006</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>1103</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>6</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>12</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="8">
         <v>6000</v>
       </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7" t="s">
+      <c r="H30" s="8"/>
+      <c r="I30" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J30" s="9">
-        <v>60</v>
-      </c>
-      <c r="K30" s="10" t="s">
+      <c r="J30" s="10">
+        <v>60</v>
+      </c>
+      <c r="K30" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:11">
-      <c r="A31" s="4">
+      <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>1103007</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>1103</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>7</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>14</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="8">
         <v>9000</v>
       </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7" t="s">
+      <c r="H31" s="8"/>
+      <c r="I31" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J31" s="9">
-        <v>60</v>
-      </c>
-      <c r="K31" s="10" t="s">
+      <c r="J31" s="10">
+        <v>60</v>
+      </c>
+      <c r="K31" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:11">
-      <c r="A32" s="4">
+      <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>1103008</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>1103</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="5">
         <v>8</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>16</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="8">
         <v>15000</v>
       </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7" t="s">
+      <c r="H32" s="8"/>
+      <c r="I32" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="9">
-        <v>60</v>
-      </c>
-      <c r="K32" s="10" t="s">
+      <c r="J32" s="10">
+        <v>60</v>
+      </c>
+      <c r="K32" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:11">
-      <c r="A33" s="4">
+      <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>1103009</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="5">
         <v>1103</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="12">
         <v>9</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="5">
         <v>18</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="8">
         <v>30000</v>
       </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="7" t="s">
+      <c r="H33" s="13"/>
+      <c r="I33" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J33" s="9">
-        <v>60</v>
-      </c>
-      <c r="K33" s="10" t="s">
+      <c r="J33" s="10">
+        <v>60</v>
+      </c>
+      <c r="K33" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:11">
-      <c r="A34" s="4">
+      <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>1103010</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>1103</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="5">
         <v>10</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="5">
         <v>20</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="8">
         <v>10000</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7" t="s">
+      <c r="H34" s="8"/>
+      <c r="I34" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J34" s="9">
-        <v>60</v>
-      </c>
-      <c r="K34" s="10" t="s">
+      <c r="J34" s="10">
+        <v>60</v>
+      </c>
+      <c r="K34" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:11">
-      <c r="A35" s="4">
+      <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>1104001</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>1104</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="5">
         <v>1</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="5">
         <v>2</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="8">
         <v>1000</v>
       </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="9">
-        <v>60</v>
-      </c>
-      <c r="K35" s="10" t="s">
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="10">
+        <v>60</v>
+      </c>
+      <c r="K35" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:11">
-      <c r="A36" s="4">
+      <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>1104002</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>1104</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="5">
         <v>2</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="5">
         <v>4</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="8">
         <v>1100</v>
       </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7" t="s">
+      <c r="H36" s="8"/>
+      <c r="I36" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J36" s="9">
-        <v>60</v>
-      </c>
-      <c r="K36" s="10" t="s">
+      <c r="J36" s="10">
+        <v>60</v>
+      </c>
+      <c r="K36" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:11">
-      <c r="A37" s="4">
+      <c r="A37" s="5">
         <f t="shared" si="0"/>
         <v>1104003</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>1104</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="5">
         <v>3</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="5">
         <v>6</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="8">
         <v>2000</v>
       </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7" t="s">
+      <c r="H37" s="8"/>
+      <c r="I37" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="J37" s="9">
-        <v>60</v>
-      </c>
-      <c r="K37" s="10" t="s">
+      <c r="J37" s="10">
+        <v>60</v>
+      </c>
+      <c r="K37" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:11">
-      <c r="A38" s="4">
+      <c r="A38" s="5">
         <f t="shared" si="0"/>
         <v>1104004</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="5">
         <v>1104</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="5">
         <v>4</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="5">
         <v>8</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="8">
         <v>3000</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
+      <c r="H38" s="8"/>
+      <c r="I38" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="9">
-        <v>60</v>
-      </c>
-      <c r="K38" s="10" t="s">
+      <c r="J38" s="10">
+        <v>60</v>
+      </c>
+      <c r="K38" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:11">
-      <c r="A39" s="4">
+      <c r="A39" s="5">
         <f t="shared" si="0"/>
         <v>1104005</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="5">
         <v>1104</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="5">
         <v>5</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="5">
         <v>10</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="8">
         <v>4500</v>
       </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7" t="s">
+      <c r="H39" s="8"/>
+      <c r="I39" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="9">
-        <v>60</v>
-      </c>
-      <c r="K39" s="10" t="s">
+      <c r="J39" s="10">
+        <v>60</v>
+      </c>
+      <c r="K39" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:11">
-      <c r="A40" s="4">
+      <c r="A40" s="5">
         <f t="shared" si="0"/>
         <v>1104006</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="5">
         <v>1104</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="5">
         <v>6</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="5">
         <v>12</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="8">
         <v>6000</v>
       </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7" t="s">
+      <c r="H40" s="8"/>
+      <c r="I40" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J40" s="9">
-        <v>60</v>
-      </c>
-      <c r="K40" s="10" t="s">
+      <c r="J40" s="10">
+        <v>60</v>
+      </c>
+      <c r="K40" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:11">
-      <c r="A41" s="4">
+      <c r="A41" s="5">
         <f t="shared" si="0"/>
         <v>1104007</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="5">
         <v>1104</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="5">
         <v>7</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="5">
         <v>14</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="8">
         <v>9000</v>
       </c>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7" t="s">
+      <c r="H41" s="8"/>
+      <c r="I41" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J41" s="9">
-        <v>60</v>
-      </c>
-      <c r="K41" s="10" t="s">
+      <c r="J41" s="10">
+        <v>60</v>
+      </c>
+      <c r="K41" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:11">
-      <c r="A42" s="4">
+      <c r="A42" s="5">
         <f t="shared" si="0"/>
         <v>1104008</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <v>1104</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="5">
         <v>8</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="5">
         <v>16</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="8">
         <v>15000</v>
       </c>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7" t="s">
+      <c r="H42" s="8"/>
+      <c r="I42" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J42" s="9">
-        <v>60</v>
-      </c>
-      <c r="K42" s="10" t="s">
+      <c r="J42" s="10">
+        <v>60</v>
+      </c>
+      <c r="K42" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:11">
-      <c r="A43" s="4">
+      <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>1104009</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <v>1104</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="12">
         <v>9</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="5">
         <v>18</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="8">
         <v>30000</v>
       </c>
-      <c r="H43" s="12"/>
-      <c r="I43" s="7" t="s">
+      <c r="H43" s="13"/>
+      <c r="I43" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J43" s="9">
-        <v>60</v>
-      </c>
-      <c r="K43" s="10" t="s">
+      <c r="J43" s="10">
+        <v>60</v>
+      </c>
+      <c r="K43" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:11">
-      <c r="A44" s="4">
+      <c r="A44" s="5">
         <f t="shared" si="0"/>
         <v>1104010</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <v>1104</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="5">
         <v>10</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="5">
         <v>20</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="8">
         <v>10000</v>
       </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7" t="s">
+      <c r="H44" s="8"/>
+      <c r="I44" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J44" s="9">
-        <v>60</v>
-      </c>
-      <c r="K44" s="10" t="s">
+      <c r="J44" s="10">
+        <v>60</v>
+      </c>
+      <c r="K44" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:11">
-      <c r="A45" s="4">
+      <c r="A45" s="5">
         <f t="shared" si="0"/>
         <v>1105001</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <v>1105</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="5">
         <v>1</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="5">
         <v>2</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="8">
         <v>1000</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="9">
-        <v>60</v>
-      </c>
-      <c r="K45" s="10" t="s">
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="10">
+        <v>60</v>
+      </c>
+      <c r="K45" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:11">
-      <c r="A46" s="4">
+      <c r="A46" s="5">
         <f t="shared" si="0"/>
         <v>1105002</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <v>1105</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="5">
         <v>2</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="5">
         <v>4</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="8">
         <v>1100</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
+      <c r="H46" s="8"/>
+      <c r="I46" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="J46" s="9">
-        <v>60</v>
-      </c>
-      <c r="K46" s="10" t="s">
+      <c r="J46" s="10">
+        <v>60</v>
+      </c>
+      <c r="K46" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:11">
-      <c r="A47" s="4">
+      <c r="A47" s="5">
         <f t="shared" si="0"/>
         <v>1105003</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <v>1105</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="5">
         <v>3</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="5">
         <v>6</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="8">
         <v>2000</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7" t="s">
+      <c r="H47" s="8"/>
+      <c r="I47" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J47" s="9">
-        <v>60</v>
-      </c>
-      <c r="K47" s="10" t="s">
+      <c r="J47" s="10">
+        <v>60</v>
+      </c>
+      <c r="K47" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:11">
-      <c r="A48" s="4">
+      <c r="A48" s="5">
         <f t="shared" si="0"/>
         <v>1105004</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="5">
         <v>1105</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="5">
         <v>4</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="5">
         <v>8</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="8">
         <v>3000</v>
       </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7" t="s">
+      <c r="H48" s="8"/>
+      <c r="I48" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="J48" s="9">
-        <v>60</v>
-      </c>
-      <c r="K48" s="10" t="s">
+      <c r="J48" s="10">
+        <v>60</v>
+      </c>
+      <c r="K48" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:11">
-      <c r="A49" s="4">
+      <c r="A49" s="5">
         <f t="shared" si="0"/>
         <v>1105005</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="5">
         <v>1105</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="5">
         <v>5</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="5">
         <v>10</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="8">
         <v>4500</v>
       </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7" t="s">
+      <c r="H49" s="8"/>
+      <c r="I49" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="9">
-        <v>60</v>
-      </c>
-      <c r="K49" s="10" t="s">
+      <c r="J49" s="10">
+        <v>60</v>
+      </c>
+      <c r="K49" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:11">
-      <c r="A50" s="4">
+      <c r="A50" s="5">
         <f t="shared" si="0"/>
         <v>1105006</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="5">
         <v>1105</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="5">
         <v>6</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="5">
         <v>12</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="8">
         <v>6000</v>
       </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7" t="s">
+      <c r="H50" s="8"/>
+      <c r="I50" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="J50" s="9">
-        <v>60</v>
-      </c>
-      <c r="K50" s="10" t="s">
+      <c r="J50" s="10">
+        <v>60</v>
+      </c>
+      <c r="K50" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:11">
-      <c r="A51" s="4">
+      <c r="A51" s="5">
         <f t="shared" si="0"/>
         <v>1105007</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="5">
         <v>1105</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>7</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="5">
         <v>14</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="8">
         <v>9000</v>
       </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7" t="s">
+      <c r="H51" s="8"/>
+      <c r="I51" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J51" s="9">
-        <v>60</v>
-      </c>
-      <c r="K51" s="10" t="s">
+      <c r="J51" s="10">
+        <v>60</v>
+      </c>
+      <c r="K51" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:11">
-      <c r="A52" s="4">
+      <c r="A52" s="5">
         <f t="shared" si="0"/>
         <v>1105008</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="5">
         <v>1105</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="5">
         <v>8</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="5">
         <v>16</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="8">
         <v>15000</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7" t="s">
+      <c r="H52" s="8"/>
+      <c r="I52" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="J52" s="9">
-        <v>60</v>
-      </c>
-      <c r="K52" s="10" t="s">
+      <c r="J52" s="10">
+        <v>60</v>
+      </c>
+      <c r="K52" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:11">
-      <c r="A53" s="4">
+      <c r="A53" s="5">
         <f t="shared" si="0"/>
         <v>1105009</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="5">
         <v>1105</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="12">
         <v>9</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="5">
         <v>18</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="8">
         <v>30000</v>
       </c>
-      <c r="H53" s="12"/>
-      <c r="I53" s="7" t="s">
+      <c r="H53" s="13"/>
+      <c r="I53" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J53" s="9">
-        <v>60</v>
-      </c>
-      <c r="K53" s="10" t="s">
+      <c r="J53" s="10">
+        <v>60</v>
+      </c>
+      <c r="K53" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:11">
-      <c r="A54" s="4">
+      <c r="A54" s="5">
         <f t="shared" si="0"/>
         <v>1105010</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="5">
         <v>1105</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="5">
         <v>10</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="5">
         <v>20</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="8">
         <v>10000</v>
       </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7" t="s">
+      <c r="H54" s="8"/>
+      <c r="I54" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J54" s="9">
-        <v>60</v>
-      </c>
-      <c r="K54" s="10" t="s">
+      <c r="J54" s="10">
+        <v>60</v>
+      </c>
+      <c r="K54" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:11">
-      <c r="A55" s="4">
+      <c r="A55" s="5">
         <f t="shared" si="0"/>
         <v>1106001</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="5">
         <v>1106</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="5">
         <v>1</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="5">
         <v>2</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="8">
         <v>1000</v>
       </c>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="9">
-        <v>60</v>
-      </c>
-      <c r="K55" s="10" t="s">
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="10">
+        <v>60</v>
+      </c>
+      <c r="K55" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:11">
-      <c r="A56" s="4">
+      <c r="A56" s="5">
         <f t="shared" si="0"/>
         <v>1106002</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="5">
         <v>1106</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="5">
         <v>2</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="5">
         <v>4</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="8">
         <v>1100</v>
       </c>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7" t="s">
+      <c r="H56" s="8"/>
+      <c r="I56" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="J56" s="9">
-        <v>60</v>
-      </c>
-      <c r="K56" s="10" t="s">
+      <c r="J56" s="10">
+        <v>60</v>
+      </c>
+      <c r="K56" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:11">
-      <c r="A57" s="4">
+      <c r="A57" s="5">
         <f t="shared" si="0"/>
         <v>1106003</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="5">
         <v>1106</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="5">
         <v>3</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="5">
         <v>6</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="8">
         <v>2000</v>
       </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7" t="s">
+      <c r="H57" s="8"/>
+      <c r="I57" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J57" s="9">
-        <v>60</v>
-      </c>
-      <c r="K57" s="10" t="s">
+      <c r="J57" s="10">
+        <v>60</v>
+      </c>
+      <c r="K57" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
-      <c r="A58" s="4">
+      <c r="A58" s="5">
         <f t="shared" si="0"/>
         <v>1106004</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="5">
         <v>1106</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="5">
         <v>4</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="5">
         <v>8</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="8">
         <v>3000</v>
       </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7" t="s">
+      <c r="H58" s="8"/>
+      <c r="I58" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="J58" s="9">
-        <v>60</v>
-      </c>
-      <c r="K58" s="10" t="s">
+      <c r="J58" s="10">
+        <v>60</v>
+      </c>
+      <c r="K58" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
-      <c r="A59" s="4">
+      <c r="A59" s="5">
         <f t="shared" si="0"/>
         <v>1106005</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="5">
         <v>1106</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="5">
         <v>5</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="5">
         <v>10</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="8">
         <v>4500</v>
       </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7" t="s">
+      <c r="H59" s="8"/>
+      <c r="I59" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="J59" s="9">
-        <v>60</v>
-      </c>
-      <c r="K59" s="10" t="s">
+      <c r="J59" s="10">
+        <v>60</v>
+      </c>
+      <c r="K59" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
-      <c r="A60" s="4">
+      <c r="A60" s="5">
         <f t="shared" si="0"/>
         <v>1106006</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="5">
         <v>1106</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="5">
         <v>6</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="5">
         <v>12</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="8">
         <v>6000</v>
       </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7" t="s">
+      <c r="H60" s="8"/>
+      <c r="I60" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="J60" s="9">
-        <v>60</v>
-      </c>
-      <c r="K60" s="10" t="s">
+      <c r="J60" s="10">
+        <v>60</v>
+      </c>
+      <c r="K60" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
-      <c r="A61" s="4">
+      <c r="A61" s="5">
         <f t="shared" si="0"/>
         <v>1106007</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="5">
         <v>1106</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="5">
         <v>7</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="5">
         <v>14</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="8">
         <v>9000</v>
       </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7" t="s">
+      <c r="H61" s="8"/>
+      <c r="I61" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="J61" s="9">
-        <v>60</v>
-      </c>
-      <c r="K61" s="10" t="s">
+      <c r="J61" s="10">
+        <v>60</v>
+      </c>
+      <c r="K61" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
-      <c r="A62" s="4">
+      <c r="A62" s="5">
         <f t="shared" si="0"/>
         <v>1106008</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="5">
         <v>1106</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="5">
         <v>8</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="5">
         <v>16</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="8">
         <v>15000</v>
       </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7" t="s">
+      <c r="H62" s="8"/>
+      <c r="I62" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="J62" s="9">
-        <v>60</v>
-      </c>
-      <c r="K62" s="10" t="s">
+      <c r="J62" s="10">
+        <v>60</v>
+      </c>
+      <c r="K62" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
-      <c r="A63" s="4">
+      <c r="A63" s="5">
         <f t="shared" si="0"/>
         <v>1106009</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="5">
         <v>1106</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="12">
         <v>9</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="5">
         <v>18</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="8">
         <v>30000</v>
       </c>
-      <c r="H63" s="12"/>
-      <c r="I63" s="7" t="s">
+      <c r="H63" s="13"/>
+      <c r="I63" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="J63" s="9">
-        <v>60</v>
-      </c>
-      <c r="K63" s="10" t="s">
+      <c r="J63" s="10">
+        <v>60</v>
+      </c>
+      <c r="K63" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
-      <c r="A64" s="4">
+      <c r="A64" s="5">
         <f t="shared" si="0"/>
         <v>1106010</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="5">
         <v>1106</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="5">
         <v>10</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="5">
         <v>20</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G64" s="7">
+      <c r="G64" s="8">
         <v>10000</v>
       </c>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7" t="s">
+      <c r="H64" s="8"/>
+      <c r="I64" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="J64" s="9">
-        <v>60</v>
-      </c>
-      <c r="K64" s="10" t="s">
+      <c r="J64" s="10">
+        <v>60</v>
+      </c>
+      <c r="K64" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:11">
-      <c r="A65" s="4">
+      <c r="A65" s="5">
         <f t="shared" si="0"/>
         <v>1107001</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="5">
         <v>1107</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="5">
         <v>1</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="5">
         <v>2</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G65" s="7">
+      <c r="G65" s="8">
         <v>1000</v>
       </c>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="9">
-        <v>60</v>
-      </c>
-      <c r="K65" s="10" t="s">
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="10">
+        <v>60</v>
+      </c>
+      <c r="K65" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:11">
-      <c r="A66" s="4">
+      <c r="A66" s="5">
         <f t="shared" si="0"/>
         <v>1107002</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="5">
         <v>1107</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="5">
         <v>2</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="5">
         <v>4</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G66" s="8">
         <v>1100</v>
       </c>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7" t="s">
+      <c r="H66" s="8"/>
+      <c r="I66" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="J66" s="9">
-        <v>60</v>
-      </c>
-      <c r="K66" s="10" t="s">
+      <c r="J66" s="10">
+        <v>60</v>
+      </c>
+      <c r="K66" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
-      <c r="A67" s="4">
+      <c r="A67" s="5">
         <f t="shared" si="0"/>
         <v>1107003</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="5">
         <v>1107</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="5">
         <v>3</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="5">
         <v>6</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="8">
         <v>2000</v>
       </c>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7" t="s">
+      <c r="H67" s="8"/>
+      <c r="I67" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J67" s="9">
-        <v>60</v>
-      </c>
-      <c r="K67" s="10" t="s">
+      <c r="J67" s="10">
+        <v>60</v>
+      </c>
+      <c r="K67" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:11">
-      <c r="A68" s="4">
+      <c r="A68" s="5">
         <f t="shared" si="0"/>
         <v>1107004</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="5">
         <v>1107</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="5">
         <v>4</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="5">
         <v>8</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G68" s="8">
         <v>3000</v>
       </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7" t="s">
+      <c r="H68" s="8"/>
+      <c r="I68" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J68" s="9">
-        <v>60</v>
-      </c>
-      <c r="K68" s="10" t="s">
+      <c r="J68" s="10">
+        <v>60</v>
+      </c>
+      <c r="K68" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:11">
-      <c r="A69" s="4">
+      <c r="A69" s="5">
         <f t="shared" si="0"/>
         <v>1107005</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="5">
         <v>1107</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="5">
         <v>5</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="5">
         <v>10</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="7">
+      <c r="G69" s="8">
         <v>4500</v>
       </c>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7" t="s">
+      <c r="H69" s="8"/>
+      <c r="I69" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J69" s="9">
-        <v>60</v>
-      </c>
-      <c r="K69" s="10" t="s">
+      <c r="J69" s="10">
+        <v>60</v>
+      </c>
+      <c r="K69" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:11">
-      <c r="A70" s="4">
+      <c r="A70" s="5">
         <f t="shared" ref="A70:A124" si="1">B70*1000+D70</f>
         <v>1107006</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="5">
         <v>1107</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="5">
         <v>6</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E70" s="5">
         <v>12</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G70" s="8">
         <v>6000</v>
       </c>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7" t="s">
+      <c r="H70" s="8"/>
+      <c r="I70" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J70" s="9">
-        <v>60</v>
-      </c>
-      <c r="K70" s="10" t="s">
+      <c r="J70" s="10">
+        <v>60</v>
+      </c>
+      <c r="K70" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
-      <c r="A71" s="4">
+      <c r="A71" s="5">
         <f t="shared" si="1"/>
         <v>1107007</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="5">
         <v>1107</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="5">
         <v>7</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="5">
         <v>14</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="8">
         <v>9000</v>
       </c>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7" t="s">
+      <c r="H71" s="8"/>
+      <c r="I71" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J71" s="9">
-        <v>60</v>
-      </c>
-      <c r="K71" s="10" t="s">
+      <c r="J71" s="10">
+        <v>60</v>
+      </c>
+      <c r="K71" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
-      <c r="A72" s="4">
+      <c r="A72" s="5">
         <f t="shared" si="1"/>
         <v>1107008</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="5">
         <v>1107</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="5">
         <v>8</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E72" s="5">
         <v>16</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G72" s="7">
+      <c r="G72" s="8">
         <v>15000</v>
       </c>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7" t="s">
+      <c r="H72" s="8"/>
+      <c r="I72" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="9">
-        <v>60</v>
-      </c>
-      <c r="K72" s="10" t="s">
+      <c r="J72" s="10">
+        <v>60</v>
+      </c>
+      <c r="K72" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
-      <c r="A73" s="4">
+      <c r="A73" s="5">
         <f t="shared" si="1"/>
         <v>1107009</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="5">
         <v>1107</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="12">
         <v>9</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E73" s="5">
         <v>18</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G73" s="8">
         <v>30000</v>
       </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="7" t="s">
+      <c r="H73" s="13"/>
+      <c r="I73" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J73" s="9">
-        <v>60</v>
-      </c>
-      <c r="K73" s="10" t="s">
+      <c r="J73" s="10">
+        <v>60</v>
+      </c>
+      <c r="K73" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
-      <c r="A74" s="4">
+      <c r="A74" s="5">
         <f t="shared" si="1"/>
         <v>1107010</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="5">
         <v>1107</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="5">
         <v>10</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="5">
         <v>20</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G74" s="8">
         <v>10000</v>
       </c>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7" t="s">
+      <c r="H74" s="8"/>
+      <c r="I74" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J74" s="9">
-        <v>60</v>
-      </c>
-      <c r="K74" s="10" t="s">
+      <c r="J74" s="10">
+        <v>60</v>
+      </c>
+      <c r="K74" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
-      <c r="A75" s="4">
+      <c r="A75" s="5">
         <f t="shared" si="1"/>
         <v>1108001</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="5">
         <v>1108</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="5">
         <v>1</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="5">
         <v>2</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="8">
         <v>1000</v>
       </c>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="9">
-        <v>60</v>
-      </c>
-      <c r="K75" s="10" t="s">
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="10">
+        <v>60</v>
+      </c>
+      <c r="K75" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
-      <c r="A76" s="4">
+      <c r="A76" s="5">
         <f t="shared" si="1"/>
         <v>1108002</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="5">
         <v>1108</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="5">
         <v>2</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E76" s="5">
         <v>4</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="8">
         <v>1100</v>
       </c>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7" t="s">
+      <c r="H76" s="8"/>
+      <c r="I76" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J76" s="9">
-        <v>60</v>
-      </c>
-      <c r="K76" s="10" t="s">
+      <c r="J76" s="10">
+        <v>60</v>
+      </c>
+      <c r="K76" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:11">
-      <c r="A77" s="4">
+      <c r="A77" s="5">
         <f t="shared" si="1"/>
         <v>1108003</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="5">
         <v>1108</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="5">
         <v>3</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="5">
         <v>6</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="8">
         <v>2000</v>
       </c>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7" t="s">
+      <c r="H77" s="8"/>
+      <c r="I77" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J77" s="9">
-        <v>60</v>
-      </c>
-      <c r="K77" s="10" t="s">
+      <c r="J77" s="10">
+        <v>60</v>
+      </c>
+      <c r="K77" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:11">
-      <c r="A78" s="4">
+      <c r="A78" s="5">
         <f t="shared" si="1"/>
         <v>1108004</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="5">
         <v>1108</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="5">
         <v>4</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="5">
         <v>8</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G78" s="8">
         <v>3000</v>
       </c>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7" t="s">
+      <c r="H78" s="8"/>
+      <c r="I78" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J78" s="9">
-        <v>60</v>
-      </c>
-      <c r="K78" s="10" t="s">
+      <c r="J78" s="10">
+        <v>60</v>
+      </c>
+      <c r="K78" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
-      <c r="A79" s="4">
+      <c r="A79" s="5">
         <f t="shared" si="1"/>
         <v>1108005</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="5">
         <v>1108</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="5">
         <v>5</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E79" s="5">
         <v>10</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G79" s="8">
         <v>4500</v>
       </c>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7" t="s">
+      <c r="H79" s="8"/>
+      <c r="I79" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J79" s="9">
-        <v>60</v>
-      </c>
-      <c r="K79" s="10" t="s">
+      <c r="J79" s="10">
+        <v>60</v>
+      </c>
+      <c r="K79" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
-      <c r="A80" s="4">
+      <c r="A80" s="5">
         <f t="shared" si="1"/>
         <v>1108006</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="5">
         <v>1108</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="5">
         <v>6</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E80" s="5">
         <v>12</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F80" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G80" s="7">
+      <c r="G80" s="8">
         <v>6000</v>
       </c>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7" t="s">
+      <c r="H80" s="8"/>
+      <c r="I80" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="J80" s="9">
-        <v>60</v>
-      </c>
-      <c r="K80" s="10" t="s">
+      <c r="J80" s="10">
+        <v>60</v>
+      </c>
+      <c r="K80" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
-      <c r="A81" s="4">
+      <c r="A81" s="5">
         <f t="shared" si="1"/>
         <v>1108007</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="5">
         <v>1108</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="5">
         <v>7</v>
       </c>
-      <c r="E81" s="4">
+      <c r="E81" s="5">
         <v>14</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G81" s="8">
         <v>9000</v>
       </c>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7" t="s">
+      <c r="H81" s="8"/>
+      <c r="I81" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J81" s="9">
-        <v>60</v>
-      </c>
-      <c r="K81" s="10" t="s">
+      <c r="J81" s="10">
+        <v>60</v>
+      </c>
+      <c r="K81" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
-      <c r="A82" s="4">
+      <c r="A82" s="5">
         <f t="shared" si="1"/>
         <v>1108008</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="5">
         <v>1108</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="5">
         <v>8</v>
       </c>
-      <c r="E82" s="4">
+      <c r="E82" s="5">
         <v>16</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G82" s="8">
         <v>15000</v>
       </c>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7" t="s">
+      <c r="H82" s="8"/>
+      <c r="I82" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J82" s="9">
-        <v>60</v>
-      </c>
-      <c r="K82" s="10" t="s">
+      <c r="J82" s="10">
+        <v>60</v>
+      </c>
+      <c r="K82" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
-      <c r="A83" s="4">
+      <c r="A83" s="5">
         <f t="shared" si="1"/>
         <v>1108009</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="5">
         <v>1108</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="12">
         <v>9</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="5">
         <v>18</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="8">
         <v>30000</v>
       </c>
-      <c r="H83" s="12"/>
-      <c r="I83" s="7" t="s">
+      <c r="H83" s="13"/>
+      <c r="I83" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J83" s="9">
-        <v>60</v>
-      </c>
-      <c r="K83" s="10" t="s">
+      <c r="J83" s="10">
+        <v>60</v>
+      </c>
+      <c r="K83" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
-      <c r="A84" s="4">
+      <c r="A84" s="5">
         <f t="shared" si="1"/>
         <v>1108010</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="5">
         <v>1108</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="5">
         <v>10</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="5">
         <v>20</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="8">
         <v>10000</v>
       </c>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7" t="s">
+      <c r="H84" s="8"/>
+      <c r="I84" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="9">
-        <v>60</v>
-      </c>
-      <c r="K84" s="10" t="s">
+      <c r="J84" s="10">
+        <v>60</v>
+      </c>
+      <c r="K84" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
-      <c r="A85" s="4">
+      <c r="A85" s="5">
         <f t="shared" si="1"/>
         <v>1109001</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="5">
         <v>1109</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="5">
         <v>1</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E85" s="5">
         <v>2</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G85" s="8">
         <v>1000</v>
       </c>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="9">
-        <v>60</v>
-      </c>
-      <c r="K85" s="10" t="s">
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="10">
+        <v>60</v>
+      </c>
+      <c r="K85" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
-      <c r="A86" s="4">
+      <c r="A86" s="5">
         <f t="shared" si="1"/>
         <v>1109002</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="5">
         <v>1109</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="5">
         <v>2</v>
       </c>
-      <c r="E86" s="4">
+      <c r="E86" s="5">
         <v>4</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G86" s="8">
         <v>1100</v>
       </c>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7" t="s">
+      <c r="H86" s="8"/>
+      <c r="I86" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J86" s="9">
-        <v>60</v>
-      </c>
-      <c r="K86" s="10" t="s">
+      <c r="J86" s="10">
+        <v>60</v>
+      </c>
+      <c r="K86" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
-      <c r="A87" s="4">
+      <c r="A87" s="5">
         <f t="shared" si="1"/>
         <v>1109003</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="5">
         <v>1109</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="5">
         <v>3</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E87" s="5">
         <v>6</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="8">
         <v>2000</v>
       </c>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7" t="s">
+      <c r="H87" s="8"/>
+      <c r="I87" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="J87" s="9">
-        <v>60</v>
-      </c>
-      <c r="K87" s="10" t="s">
+      <c r="J87" s="10">
+        <v>60</v>
+      </c>
+      <c r="K87" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
-      <c r="A88" s="4">
+      <c r="A88" s="5">
         <f t="shared" si="1"/>
         <v>1109004</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="5">
         <v>1109</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88" s="5">
         <v>4</v>
       </c>
-      <c r="E88" s="4">
+      <c r="E88" s="5">
         <v>8</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F88" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G88" s="8">
         <v>3000</v>
       </c>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7" t="s">
+      <c r="H88" s="8"/>
+      <c r="I88" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="J88" s="9">
-        <v>60</v>
-      </c>
-      <c r="K88" s="10" t="s">
+      <c r="J88" s="10">
+        <v>60</v>
+      </c>
+      <c r="K88" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:11">
-      <c r="A89" s="4">
+      <c r="A89" s="5">
         <f t="shared" si="1"/>
         <v>1109005</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="5">
         <v>1109</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89" s="5">
         <v>5</v>
       </c>
-      <c r="E89" s="4">
+      <c r="E89" s="5">
         <v>10</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G89" s="8">
         <v>4500</v>
       </c>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7" t="s">
+      <c r="H89" s="8"/>
+      <c r="I89" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="J89" s="9">
-        <v>60</v>
-      </c>
-      <c r="K89" s="10" t="s">
+      <c r="J89" s="10">
+        <v>60</v>
+      </c>
+      <c r="K89" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:11">
-      <c r="A90" s="4">
+      <c r="A90" s="5">
         <f t="shared" si="1"/>
         <v>1109006</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="5">
         <v>1109</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90" s="5">
         <v>6</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E90" s="5">
         <v>12</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G90" s="8">
         <v>6000</v>
       </c>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7" t="s">
+      <c r="H90" s="8"/>
+      <c r="I90" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="J90" s="9">
-        <v>60</v>
-      </c>
-      <c r="K90" s="10" t="s">
+      <c r="J90" s="10">
+        <v>60</v>
+      </c>
+      <c r="K90" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
-      <c r="A91" s="4">
+      <c r="A91" s="5">
         <f t="shared" si="1"/>
         <v>1109007</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="5">
         <v>1109</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="5">
         <v>7</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E91" s="5">
         <v>14</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G91" s="8">
         <v>9000</v>
       </c>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7" t="s">
+      <c r="H91" s="8"/>
+      <c r="I91" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J91" s="9">
-        <v>60</v>
-      </c>
-      <c r="K91" s="10" t="s">
+      <c r="J91" s="10">
+        <v>60</v>
+      </c>
+      <c r="K91" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
-      <c r="A92" s="4">
+      <c r="A92" s="5">
         <f t="shared" si="1"/>
         <v>1109008</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="5">
         <v>1109</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="5">
         <v>8</v>
       </c>
-      <c r="E92" s="4">
+      <c r="E92" s="5">
         <v>16</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F92" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G92" s="7">
+      <c r="G92" s="8">
         <v>15000</v>
       </c>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7" t="s">
+      <c r="H92" s="8"/>
+      <c r="I92" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="J92" s="9">
-        <v>60</v>
-      </c>
-      <c r="K92" s="10" t="s">
+      <c r="J92" s="10">
+        <v>60</v>
+      </c>
+      <c r="K92" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:11">
-      <c r="A93" s="4">
+      <c r="A93" s="5">
         <f t="shared" si="1"/>
         <v>1109009</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="5">
         <v>1109</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="12">
         <v>9</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E93" s="5">
         <v>18</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F93" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G93" s="7">
+      <c r="G93" s="8">
         <v>30000</v>
       </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="7" t="s">
+      <c r="H93" s="13"/>
+      <c r="I93" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J93" s="9">
-        <v>60</v>
-      </c>
-      <c r="K93" s="10" t="s">
+      <c r="J93" s="10">
+        <v>60</v>
+      </c>
+      <c r="K93" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:11">
-      <c r="A94" s="4">
+      <c r="A94" s="5">
         <f t="shared" si="1"/>
         <v>1109010</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="5">
         <v>1109</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="5">
         <v>10</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E94" s="5">
         <v>20</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F94" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G94" s="7">
+      <c r="G94" s="8">
         <v>10000</v>
       </c>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7" t="s">
+      <c r="H94" s="8"/>
+      <c r="I94" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="J94" s="9">
-        <v>60</v>
-      </c>
-      <c r="K94" s="10" t="s">
+      <c r="J94" s="10">
+        <v>60</v>
+      </c>
+      <c r="K94" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:11">
-      <c r="A95" s="4">
+      <c r="A95" s="5">
         <f t="shared" si="1"/>
         <v>1110001</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="5">
         <v>1110</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95" s="5">
         <v>1</v>
       </c>
-      <c r="E95" s="4">
+      <c r="E95" s="5">
         <v>2</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="F95" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G95" s="7">
+      <c r="G95" s="8">
         <v>1000</v>
       </c>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="9">
-        <v>60</v>
-      </c>
-      <c r="K95" s="10" t="s">
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="10">
+        <v>60</v>
+      </c>
+      <c r="K95" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:11">
-      <c r="A96" s="4">
+      <c r="A96" s="5">
         <f t="shared" si="1"/>
         <v>1110002</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="5">
         <v>1110</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="5">
         <v>2</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E96" s="5">
         <v>4</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F96" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G96" s="7">
+      <c r="G96" s="8">
         <v>1100</v>
       </c>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7" t="s">
+      <c r="H96" s="8"/>
+      <c r="I96" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="J96" s="9">
-        <v>60</v>
-      </c>
-      <c r="K96" s="10" t="s">
+      <c r="J96" s="10">
+        <v>60</v>
+      </c>
+      <c r="K96" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:11">
-      <c r="A97" s="4">
+      <c r="A97" s="5">
         <f t="shared" si="1"/>
         <v>1110003</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="5">
         <v>1110</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="5">
         <v>3</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E97" s="5">
         <v>6</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="F97" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G97" s="7">
+      <c r="G97" s="8">
         <v>2000</v>
       </c>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7" t="s">
+      <c r="H97" s="8"/>
+      <c r="I97" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="J97" s="9">
-        <v>60</v>
-      </c>
-      <c r="K97" s="10" t="s">
+      <c r="J97" s="10">
+        <v>60</v>
+      </c>
+      <c r="K97" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:11">
-      <c r="A98" s="4">
+      <c r="A98" s="5">
         <f t="shared" si="1"/>
         <v>1110004</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="5">
         <v>1110</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="5">
         <v>4</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="5">
         <v>8</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="F98" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G98" s="7">
+      <c r="G98" s="8">
         <v>3000</v>
       </c>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7" t="s">
+      <c r="H98" s="8"/>
+      <c r="I98" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="J98" s="9">
-        <v>60</v>
-      </c>
-      <c r="K98" s="10" t="s">
+      <c r="J98" s="10">
+        <v>60</v>
+      </c>
+      <c r="K98" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:11">
-      <c r="A99" s="4">
+      <c r="A99" s="5">
         <f t="shared" si="1"/>
         <v>1110005</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="5">
         <v>1110</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="5">
         <v>5</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E99" s="5">
         <v>10</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="F99" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G99" s="7">
+      <c r="G99" s="8">
         <v>4500</v>
       </c>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7" t="s">
+      <c r="H99" s="8"/>
+      <c r="I99" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="J99" s="9">
-        <v>60</v>
-      </c>
-      <c r="K99" s="10" t="s">
+      <c r="J99" s="10">
+        <v>60</v>
+      </c>
+      <c r="K99" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:11">
-      <c r="A100" s="4">
+      <c r="A100" s="5">
         <f t="shared" si="1"/>
         <v>1110006</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="5">
         <v>1110</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="5">
         <v>6</v>
       </c>
-      <c r="E100" s="4">
+      <c r="E100" s="5">
         <v>12</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G100" s="7">
+      <c r="G100" s="8">
         <v>6000</v>
       </c>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7" t="s">
+      <c r="H100" s="8"/>
+      <c r="I100" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="J100" s="9">
-        <v>60</v>
-      </c>
-      <c r="K100" s="10" t="s">
+      <c r="J100" s="10">
+        <v>60</v>
+      </c>
+      <c r="K100" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:11">
-      <c r="A101" s="4">
+      <c r="A101" s="5">
         <f t="shared" si="1"/>
         <v>1110007</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="5">
         <v>1110</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D101" s="4">
+      <c r="D101" s="5">
         <v>7</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E101" s="5">
         <v>14</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F101" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G101" s="7">
+      <c r="G101" s="8">
         <v>9000</v>
       </c>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7" t="s">
+      <c r="H101" s="8"/>
+      <c r="I101" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="J101" s="9">
-        <v>60</v>
-      </c>
-      <c r="K101" s="10" t="s">
+      <c r="J101" s="10">
+        <v>60</v>
+      </c>
+      <c r="K101" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:11">
-      <c r="A102" s="4">
+      <c r="A102" s="5">
         <f t="shared" si="1"/>
         <v>1110008</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="5">
         <v>1110</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102" s="5">
         <v>8</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="5">
         <v>16</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F102" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G102" s="7">
+      <c r="G102" s="8">
         <v>15000</v>
       </c>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7" t="s">
+      <c r="H102" s="8"/>
+      <c r="I102" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="J102" s="9">
-        <v>60</v>
-      </c>
-      <c r="K102" s="10" t="s">
+      <c r="J102" s="10">
+        <v>60</v>
+      </c>
+      <c r="K102" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:11">
-      <c r="A103" s="4">
+      <c r="A103" s="5">
         <f t="shared" si="1"/>
         <v>1110009</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="5">
         <v>1110</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="12">
         <v>9</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="5">
         <v>18</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="F103" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G103" s="8">
         <v>30000</v>
       </c>
-      <c r="H103" s="12"/>
-      <c r="I103" s="7" t="s">
+      <c r="H103" s="13"/>
+      <c r="I103" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="J103" s="9">
-        <v>60</v>
-      </c>
-      <c r="K103" s="10" t="s">
+      <c r="J103" s="10">
+        <v>60</v>
+      </c>
+      <c r="K103" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:11">
-      <c r="A104" s="4">
+      <c r="A104" s="5">
         <f t="shared" si="1"/>
         <v>1110010</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="5">
         <v>1110</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="5">
         <v>10</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="5">
         <v>20</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G104" s="7">
+      <c r="G104" s="8">
         <v>10000</v>
       </c>
-      <c r="H104" s="7"/>
-      <c r="I104" s="7" t="s">
+      <c r="H104" s="8"/>
+      <c r="I104" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J104" s="9">
-        <v>60</v>
-      </c>
-      <c r="K104" s="10" t="s">
+      <c r="J104" s="10">
+        <v>60</v>
+      </c>
+      <c r="K104" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:11">
-      <c r="A105" s="4">
+      <c r="A105" s="5">
         <f t="shared" si="1"/>
         <v>1111001</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="5">
         <v>1111</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="5">
         <v>1</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="5">
         <v>2</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F105" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G105" s="7">
+      <c r="G105" s="8">
         <v>1000</v>
       </c>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="9">
-        <v>60</v>
-      </c>
-      <c r="K105" s="10" t="s">
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="10">
+        <v>60</v>
+      </c>
+      <c r="K105" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:11">
-      <c r="A106" s="4">
+      <c r="A106" s="5">
         <f t="shared" si="1"/>
         <v>1111002</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="5">
         <v>1111</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="5">
         <v>2</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E106" s="5">
         <v>4</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F106" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G106" s="7">
+      <c r="G106" s="8">
         <v>1100</v>
       </c>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7" t="s">
+      <c r="H106" s="8"/>
+      <c r="I106" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="J106" s="9">
-        <v>60</v>
-      </c>
-      <c r="K106" s="10" t="s">
+      <c r="J106" s="10">
+        <v>60</v>
+      </c>
+      <c r="K106" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:11">
-      <c r="A107" s="4">
+      <c r="A107" s="5">
         <f t="shared" si="1"/>
         <v>1111003</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="5">
         <v>1111</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107" s="5">
         <v>3</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E107" s="5">
         <v>6</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="F107" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G107" s="7">
+      <c r="G107" s="8">
         <v>2000</v>
       </c>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7" t="s">
+      <c r="H107" s="8"/>
+      <c r="I107" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J107" s="9">
-        <v>60</v>
-      </c>
-      <c r="K107" s="10" t="s">
+      <c r="J107" s="10">
+        <v>60</v>
+      </c>
+      <c r="K107" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:11">
-      <c r="A108" s="4">
+      <c r="A108" s="5">
         <f t="shared" si="1"/>
         <v>1111004</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="5">
         <v>1111</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108" s="5">
         <v>4</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="5">
         <v>8</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G108" s="8">
         <v>3000</v>
       </c>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7" t="s">
+      <c r="H108" s="8"/>
+      <c r="I108" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="J108" s="9">
-        <v>60</v>
-      </c>
-      <c r="K108" s="10" t="s">
+      <c r="J108" s="10">
+        <v>60</v>
+      </c>
+      <c r="K108" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:11">
-      <c r="A109" s="4">
+      <c r="A109" s="5">
         <f t="shared" si="1"/>
         <v>1111005</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="5">
         <v>1111</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109" s="5">
         <v>5</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="5">
         <v>10</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F109" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G109" s="7">
+      <c r="G109" s="8">
         <v>4500</v>
       </c>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7" t="s">
+      <c r="H109" s="8"/>
+      <c r="I109" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="J109" s="9">
-        <v>60</v>
-      </c>
-      <c r="K109" s="10" t="s">
+      <c r="J109" s="10">
+        <v>60</v>
+      </c>
+      <c r="K109" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:11">
-      <c r="A110" s="4">
+      <c r="A110" s="5">
         <f t="shared" si="1"/>
         <v>1111006</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="5">
         <v>1111</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110" s="5">
         <v>6</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="5">
         <v>12</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G110" s="7">
+      <c r="G110" s="8">
         <v>6000</v>
       </c>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7" t="s">
+      <c r="H110" s="8"/>
+      <c r="I110" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="J110" s="9">
-        <v>60</v>
-      </c>
-      <c r="K110" s="10" t="s">
+      <c r="J110" s="10">
+        <v>60</v>
+      </c>
+      <c r="K110" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:11">
-      <c r="A111" s="4">
+      <c r="A111" s="5">
         <f t="shared" si="1"/>
         <v>1111007</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="5">
         <v>1111</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="5">
         <v>7</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="5">
         <v>14</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F111" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="7">
+      <c r="G111" s="8">
         <v>9000</v>
       </c>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7" t="s">
+      <c r="H111" s="8"/>
+      <c r="I111" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J111" s="9">
-        <v>60</v>
-      </c>
-      <c r="K111" s="10" t="s">
+      <c r="J111" s="10">
+        <v>60</v>
+      </c>
+      <c r="K111" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:11">
-      <c r="A112" s="4">
+      <c r="A112" s="5">
         <f t="shared" si="1"/>
         <v>1111008</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="5">
         <v>1111</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112" s="5">
         <v>8</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="5">
         <v>16</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F112" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G112" s="7">
+      <c r="G112" s="8">
         <v>15000</v>
       </c>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7" t="s">
+      <c r="H112" s="8"/>
+      <c r="I112" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J112" s="9">
-        <v>60</v>
-      </c>
-      <c r="K112" s="10" t="s">
+      <c r="J112" s="10">
+        <v>60</v>
+      </c>
+      <c r="K112" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:11">
-      <c r="A113" s="4">
+      <c r="A113" s="5">
         <f t="shared" si="1"/>
         <v>1111009</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="5">
         <v>1111</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="12">
         <v>9</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="5">
         <v>18</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F113" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G113" s="7">
+      <c r="G113" s="8">
         <v>30000</v>
       </c>
-      <c r="H113" s="12"/>
-      <c r="I113" s="7" t="s">
+      <c r="H113" s="13"/>
+      <c r="I113" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="J113" s="9">
-        <v>60</v>
-      </c>
-      <c r="K113" s="10" t="s">
+      <c r="J113" s="10">
+        <v>60</v>
+      </c>
+      <c r="K113" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:11">
-      <c r="A114" s="4">
+      <c r="A114" s="5">
         <f t="shared" si="1"/>
         <v>1111010</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="5">
         <v>1111</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D114" s="4">
+      <c r="D114" s="5">
         <v>10</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E114" s="5">
         <v>20</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G114" s="8">
         <v>10000</v>
       </c>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7" t="s">
+      <c r="H114" s="8"/>
+      <c r="I114" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J114" s="9">
-        <v>60</v>
-      </c>
-      <c r="K114" s="10" t="s">
+      <c r="J114" s="10">
+        <v>60</v>
+      </c>
+      <c r="K114" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:11">
-      <c r="A115" s="4">
+      <c r="A115" s="5">
         <f t="shared" si="1"/>
         <v>1112001</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="5">
         <v>1112</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D115" s="5">
         <v>1</v>
       </c>
-      <c r="E115" s="4">
+      <c r="E115" s="5">
         <v>2</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F115" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G115" s="7">
+      <c r="G115" s="8">
         <v>1000</v>
       </c>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="9">
-        <v>60</v>
-      </c>
-      <c r="K115" s="10" t="s">
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="10">
+        <v>60</v>
+      </c>
+      <c r="K115" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:11">
-      <c r="A116" s="4">
+      <c r="A116" s="5">
         <f t="shared" si="1"/>
         <v>1112002</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="5">
         <v>1112</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D116" s="4">
+      <c r="D116" s="5">
         <v>2</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E116" s="5">
         <v>4</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F116" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G116" s="7">
+      <c r="G116" s="8">
         <v>1100</v>
       </c>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7" t="s">
+      <c r="H116" s="8"/>
+      <c r="I116" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="J116" s="9">
-        <v>60</v>
-      </c>
-      <c r="K116" s="10" t="s">
+      <c r="J116" s="10">
+        <v>60</v>
+      </c>
+      <c r="K116" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:11">
-      <c r="A117" s="4">
+      <c r="A117" s="5">
         <f t="shared" si="1"/>
         <v>1112003</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="5">
         <v>1112</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D117" s="5">
         <v>3</v>
       </c>
-      <c r="E117" s="4">
+      <c r="E117" s="5">
         <v>6</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="F117" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G117" s="7">
+      <c r="G117" s="8">
         <v>2000</v>
       </c>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7" t="s">
+      <c r="H117" s="8"/>
+      <c r="I117" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J117" s="9">
-        <v>60</v>
-      </c>
-      <c r="K117" s="10" t="s">
+      <c r="J117" s="10">
+        <v>60</v>
+      </c>
+      <c r="K117" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:11">
-      <c r="A118" s="4">
+      <c r="A118" s="5">
         <f t="shared" si="1"/>
         <v>1112004</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="5">
         <v>1112</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118" s="5">
         <v>4</v>
       </c>
-      <c r="E118" s="4">
+      <c r="E118" s="5">
         <v>8</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F118" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G118" s="7">
+      <c r="G118" s="8">
         <v>3000</v>
       </c>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7" t="s">
+      <c r="H118" s="8"/>
+      <c r="I118" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="J118" s="9">
-        <v>60</v>
-      </c>
-      <c r="K118" s="10" t="s">
+      <c r="J118" s="10">
+        <v>60</v>
+      </c>
+      <c r="K118" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:11">
-      <c r="A119" s="4">
+      <c r="A119" s="5">
         <f t="shared" si="1"/>
         <v>1112005</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="5">
         <v>1112</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119" s="5">
         <v>5</v>
       </c>
-      <c r="E119" s="4">
+      <c r="E119" s="5">
         <v>10</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="F119" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G119" s="7">
+      <c r="G119" s="8">
         <v>4500</v>
       </c>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7" t="s">
+      <c r="H119" s="8"/>
+      <c r="I119" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="J119" s="9">
-        <v>60</v>
-      </c>
-      <c r="K119" s="10" t="s">
+      <c r="J119" s="10">
+        <v>60</v>
+      </c>
+      <c r="K119" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:11">
-      <c r="A120" s="4">
+      <c r="A120" s="5">
         <f t="shared" si="1"/>
         <v>1112006</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="5">
         <v>1112</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120" s="5">
         <v>6</v>
       </c>
-      <c r="E120" s="4">
+      <c r="E120" s="5">
         <v>12</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="F120" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G120" s="7">
+      <c r="G120" s="8">
         <v>6000</v>
       </c>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7" t="s">
+      <c r="H120" s="8"/>
+      <c r="I120" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J120" s="9">
-        <v>60</v>
-      </c>
-      <c r="K120" s="10" t="s">
+      <c r="J120" s="10">
+        <v>60</v>
+      </c>
+      <c r="K120" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:11">
-      <c r="A121" s="4">
+      <c r="A121" s="5">
         <f t="shared" si="1"/>
         <v>1112007</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="5">
         <v>1112</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D121" s="5">
         <v>7</v>
       </c>
-      <c r="E121" s="4">
+      <c r="E121" s="5">
         <v>14</v>
       </c>
-      <c r="F121" s="4" t="s">
+      <c r="F121" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="7">
+      <c r="G121" s="8">
         <v>9000</v>
       </c>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7" t="s">
+      <c r="H121" s="8"/>
+      <c r="I121" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J121" s="9">
-        <v>60</v>
-      </c>
-      <c r="K121" s="10" t="s">
+      <c r="J121" s="10">
+        <v>60</v>
+      </c>
+      <c r="K121" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:11">
-      <c r="A122" s="4">
+      <c r="A122" s="5">
         <f t="shared" si="1"/>
         <v>1112008</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="5">
         <v>1112</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122" s="5">
         <v>8</v>
       </c>
-      <c r="E122" s="4">
+      <c r="E122" s="5">
         <v>16</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F122" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G122" s="8">
         <v>15000</v>
       </c>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7" t="s">
+      <c r="H122" s="8"/>
+      <c r="I122" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="J122" s="9">
-        <v>60</v>
-      </c>
-      <c r="K122" s="10" t="s">
+      <c r="J122" s="10">
+        <v>60</v>
+      </c>
+      <c r="K122" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:11">
-      <c r="A123" s="4">
+      <c r="A123" s="5">
         <f t="shared" si="1"/>
         <v>1112009</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="5">
         <v>1112</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="12">
         <v>9</v>
       </c>
-      <c r="E123" s="4">
+      <c r="E123" s="5">
         <v>18</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="F123" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G123" s="8">
         <v>30000</v>
       </c>
-      <c r="H123" s="12"/>
-      <c r="I123" s="7" t="s">
+      <c r="H123" s="13"/>
+      <c r="I123" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J123" s="9">
-        <v>60</v>
-      </c>
-      <c r="K123" s="10" t="s">
+      <c r="J123" s="10">
+        <v>60</v>
+      </c>
+      <c r="K123" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:11">
-      <c r="A124" s="4">
+      <c r="A124" s="5">
         <f t="shared" si="1"/>
         <v>1112010</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="5">
         <v>1112</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D124" s="4">
+      <c r="D124" s="5">
         <v>10</v>
       </c>
-      <c r="E124" s="4">
+      <c r="E124" s="5">
         <v>20</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="F124" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G124" s="8">
         <v>10000</v>
       </c>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7" t="s">
+      <c r="H124" s="8"/>
+      <c r="I124" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="J124" s="9">
-        <v>60</v>
-      </c>
-      <c r="K124" s="10" t="s">
+      <c r="J124" s="10">
+        <v>60</v>
+      </c>
+      <c r="K124" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:11">
-      <c r="A125" s="4">
+      <c r="A125" s="5">
         <f t="shared" ref="A125:A154" si="2">B125*1000+D125</f>
         <v>1201001</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="5">
         <v>1201</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125" s="5">
         <v>1</v>
       </c>
-      <c r="E125" s="4">
+      <c r="E125" s="5">
         <v>2</v>
       </c>
-      <c r="F125" s="4" t="s">
+      <c r="F125" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G125" s="8">
         <v>1000</v>
       </c>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="9">
-        <v>60</v>
-      </c>
-      <c r="K125" s="10" t="s">
+      <c r="H125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="10">
+        <v>60</v>
+      </c>
+      <c r="K125" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:11">
-      <c r="A126" s="4">
+      <c r="A126" s="5">
         <f t="shared" si="2"/>
         <v>1201002</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="5">
         <v>1201</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126" s="5">
         <v>2</v>
       </c>
-      <c r="E126" s="4">
+      <c r="E126" s="5">
         <v>4</v>
       </c>
-      <c r="F126" s="4" t="s">
+      <c r="F126" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G126" s="7">
+      <c r="G126" s="8">
         <v>1100</v>
       </c>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7" t="s">
+      <c r="H126" s="8"/>
+      <c r="I126" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="J126" s="9">
-        <v>60</v>
-      </c>
-      <c r="K126" s="10" t="s">
+      <c r="J126" s="10">
+        <v>60</v>
+      </c>
+      <c r="K126" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:11">
-      <c r="A127" s="4">
+      <c r="A127" s="5">
         <f t="shared" si="2"/>
         <v>1201003</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="5">
         <v>1201</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D127" s="4">
+      <c r="D127" s="5">
         <v>3</v>
       </c>
-      <c r="E127" s="4">
+      <c r="E127" s="5">
         <v>6</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="F127" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G127" s="7">
+      <c r="G127" s="8">
         <v>2000</v>
       </c>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7" t="s">
+      <c r="H127" s="8"/>
+      <c r="I127" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J127" s="9">
-        <v>60</v>
-      </c>
-      <c r="K127" s="10" t="s">
+      <c r="J127" s="10">
+        <v>60</v>
+      </c>
+      <c r="K127" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:11">
-      <c r="A128" s="4">
+      <c r="A128" s="5">
         <f t="shared" si="2"/>
         <v>1201004</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="5">
         <v>1201</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128" s="5">
         <v>4</v>
       </c>
-      <c r="E128" s="4">
+      <c r="E128" s="5">
         <v>8</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="F128" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G128" s="7">
+      <c r="G128" s="8">
         <v>3000</v>
       </c>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7" t="s">
+      <c r="H128" s="8"/>
+      <c r="I128" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="J128" s="9">
-        <v>60</v>
-      </c>
-      <c r="K128" s="10" t="s">
+      <c r="J128" s="10">
+        <v>60</v>
+      </c>
+      <c r="K128" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:11">
-      <c r="A129" s="4">
+      <c r="A129" s="5">
         <f t="shared" si="2"/>
         <v>1201005</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="5">
         <v>1201</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D129" s="4">
+      <c r="D129" s="5">
         <v>5</v>
       </c>
-      <c r="E129" s="4">
+      <c r="E129" s="5">
         <v>10</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="F129" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G129" s="7">
+      <c r="G129" s="8">
         <v>4500</v>
       </c>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7" t="s">
+      <c r="H129" s="8"/>
+      <c r="I129" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="J129" s="9">
-        <v>60</v>
-      </c>
-      <c r="K129" s="10" t="s">
+      <c r="J129" s="10">
+        <v>60</v>
+      </c>
+      <c r="K129" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:11">
-      <c r="A130" s="4">
+      <c r="A130" s="5">
         <f t="shared" si="2"/>
         <v>1201006</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="5">
         <v>1201</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D130" s="4">
+      <c r="D130" s="5">
         <v>6</v>
       </c>
-      <c r="E130" s="4">
+      <c r="E130" s="5">
         <v>12</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="F130" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G130" s="7">
+      <c r="G130" s="8">
         <v>6000</v>
       </c>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7" t="s">
+      <c r="H130" s="8"/>
+      <c r="I130" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="J130" s="9">
-        <v>60</v>
-      </c>
-      <c r="K130" s="10" t="s">
+      <c r="J130" s="10">
+        <v>60</v>
+      </c>
+      <c r="K130" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:11">
-      <c r="A131" s="4">
+      <c r="A131" s="5">
         <f t="shared" si="2"/>
         <v>1201007</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="5">
         <v>1201</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D131" s="4">
+      <c r="D131" s="5">
         <v>7</v>
       </c>
-      <c r="E131" s="4">
+      <c r="E131" s="5">
         <v>14</v>
       </c>
-      <c r="F131" s="4" t="s">
+      <c r="F131" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G131" s="7">
+      <c r="G131" s="8">
         <v>9000</v>
       </c>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7" t="s">
+      <c r="H131" s="8"/>
+      <c r="I131" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="J131" s="9">
-        <v>60</v>
-      </c>
-      <c r="K131" s="10" t="s">
+      <c r="J131" s="10">
+        <v>60</v>
+      </c>
+      <c r="K131" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:11">
-      <c r="A132" s="4">
+      <c r="A132" s="5">
         <f t="shared" si="2"/>
         <v>1201008</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="5">
         <v>1201</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D132" s="4">
+      <c r="D132" s="5">
         <v>8</v>
       </c>
-      <c r="E132" s="4">
+      <c r="E132" s="5">
         <v>16</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="F132" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G132" s="7">
+      <c r="G132" s="8">
         <v>15000</v>
       </c>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7" t="s">
+      <c r="H132" s="8"/>
+      <c r="I132" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="J132" s="9">
-        <v>60</v>
-      </c>
-      <c r="K132" s="10" t="s">
+      <c r="J132" s="10">
+        <v>60</v>
+      </c>
+      <c r="K132" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:11">
-      <c r="A133" s="4">
+      <c r="A133" s="5">
         <f t="shared" si="2"/>
         <v>1201009</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="5">
         <v>1201</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="12">
         <v>9</v>
       </c>
-      <c r="E133" s="4">
+      <c r="E133" s="5">
         <v>18</v>
       </c>
-      <c r="F133" s="4" t="s">
+      <c r="F133" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G133" s="7">
+      <c r="G133" s="8">
         <v>30000</v>
       </c>
-      <c r="H133" s="12"/>
-      <c r="I133" s="7" t="s">
+      <c r="H133" s="13"/>
+      <c r="I133" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="J133" s="9">
-        <v>60</v>
-      </c>
-      <c r="K133" s="10" t="s">
+      <c r="J133" s="10">
+        <v>60</v>
+      </c>
+      <c r="K133" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:11">
-      <c r="A134" s="4">
+      <c r="A134" s="5">
         <f t="shared" si="2"/>
         <v>1201010</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="5">
         <v>1201</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D134" s="4">
+      <c r="D134" s="5">
         <v>10</v>
       </c>
-      <c r="E134" s="4">
+      <c r="E134" s="5">
         <v>20</v>
       </c>
-      <c r="F134" s="4" t="s">
+      <c r="F134" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G134" s="8">
         <v>10000</v>
       </c>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7" t="s">
+      <c r="H134" s="8"/>
+      <c r="I134" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="J134" s="9">
-        <v>60</v>
-      </c>
-      <c r="K134" s="10" t="s">
+      <c r="J134" s="10">
+        <v>60</v>
+      </c>
+      <c r="K134" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:11">
-      <c r="A135" s="4">
+      <c r="A135" s="5">
         <f t="shared" si="2"/>
         <v>1202001</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="5">
         <v>1202</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D135" s="4">
+      <c r="D135" s="5">
         <v>1</v>
       </c>
-      <c r="E135" s="4">
+      <c r="E135" s="5">
         <v>2</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="F135" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G135" s="7">
+      <c r="G135" s="8">
         <v>15</v>
       </c>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="9">
-        <v>60</v>
-      </c>
-      <c r="K135" s="10" t="s">
+      <c r="H135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="10">
+        <v>60</v>
+      </c>
+      <c r="K135" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:11">
-      <c r="A136" s="4">
+      <c r="A136" s="5">
         <f t="shared" si="2"/>
         <v>1202002</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="5">
         <v>1202</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D136" s="4">
+      <c r="D136" s="5">
         <v>2</v>
       </c>
-      <c r="E136" s="4">
+      <c r="E136" s="5">
         <v>4</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="F136" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G136" s="7">
+      <c r="G136" s="8">
         <v>25</v>
       </c>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7" t="s">
+      <c r="H136" s="8"/>
+      <c r="I136" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="J136" s="9">
-        <v>60</v>
-      </c>
-      <c r="K136" s="10" t="s">
+      <c r="J136" s="10">
+        <v>60</v>
+      </c>
+      <c r="K136" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:11">
-      <c r="A137" s="4">
+      <c r="A137" s="5">
         <f t="shared" si="2"/>
         <v>1202003</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="5">
         <v>1202</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D137" s="4">
+      <c r="D137" s="5">
         <v>3</v>
       </c>
-      <c r="E137" s="4">
+      <c r="E137" s="5">
         <v>6</v>
       </c>
-      <c r="F137" s="4" t="s">
+      <c r="F137" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G137" s="7">
+      <c r="G137" s="8">
         <v>35</v>
       </c>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7" t="s">
+      <c r="H137" s="8"/>
+      <c r="I137" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="J137" s="9">
-        <v>60</v>
-      </c>
-      <c r="K137" s="10" t="s">
+      <c r="J137" s="10">
+        <v>60</v>
+      </c>
+      <c r="K137" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:11">
-      <c r="A138" s="4">
+      <c r="A138" s="5">
         <f t="shared" si="2"/>
         <v>1202004</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="5">
         <v>1202</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D138" s="4">
+      <c r="D138" s="5">
         <v>4</v>
       </c>
-      <c r="E138" s="4">
+      <c r="E138" s="5">
         <v>8</v>
       </c>
-      <c r="F138" s="4" t="s">
+      <c r="F138" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G138" s="7">
+      <c r="G138" s="8">
         <v>45</v>
       </c>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7" t="s">
+      <c r="H138" s="8"/>
+      <c r="I138" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="J138" s="9">
-        <v>60</v>
-      </c>
-      <c r="K138" s="10" t="s">
+      <c r="J138" s="10">
+        <v>60</v>
+      </c>
+      <c r="K138" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:11">
-      <c r="A139" s="4">
+      <c r="A139" s="5">
         <f t="shared" si="2"/>
         <v>1202005</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="5">
         <v>1202</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D139" s="4">
+      <c r="D139" s="5">
         <v>5</v>
       </c>
-      <c r="E139" s="4">
+      <c r="E139" s="5">
         <v>10</v>
       </c>
-      <c r="F139" s="4" t="s">
+      <c r="F139" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G139" s="7">
+      <c r="G139" s="8">
         <v>55</v>
       </c>
-      <c r="H139" s="7"/>
-      <c r="I139" s="7" t="s">
+      <c r="H139" s="8"/>
+      <c r="I139" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="J139" s="9">
-        <v>60</v>
-      </c>
-      <c r="K139" s="10" t="s">
+      <c r="J139" s="10">
+        <v>60</v>
+      </c>
+      <c r="K139" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:11">
-      <c r="A140" s="4">
+      <c r="A140" s="5">
         <f t="shared" si="2"/>
         <v>1202006</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="5">
         <v>1202</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D140" s="4">
+      <c r="D140" s="5">
         <v>6</v>
       </c>
-      <c r="E140" s="4">
+      <c r="E140" s="5">
         <v>12</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F140" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G140" s="7">
+      <c r="G140" s="8">
         <v>65</v>
       </c>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7" t="s">
+      <c r="H140" s="8"/>
+      <c r="I140" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="J140" s="9">
-        <v>60</v>
-      </c>
-      <c r="K140" s="10" t="s">
+      <c r="J140" s="10">
+        <v>60</v>
+      </c>
+      <c r="K140" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:11">
-      <c r="A141" s="4">
+      <c r="A141" s="5">
         <f t="shared" si="2"/>
         <v>1202007</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="5">
         <v>1202</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D141" s="4">
+      <c r="D141" s="5">
         <v>7</v>
       </c>
-      <c r="E141" s="4">
+      <c r="E141" s="5">
         <v>14</v>
       </c>
-      <c r="F141" s="4" t="s">
+      <c r="F141" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G141" s="7">
+      <c r="G141" s="8">
         <v>75</v>
       </c>
-      <c r="H141" s="7"/>
-      <c r="I141" s="7" t="s">
+      <c r="H141" s="8"/>
+      <c r="I141" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J141" s="9">
-        <v>60</v>
-      </c>
-      <c r="K141" s="10" t="s">
+      <c r="J141" s="10">
+        <v>60</v>
+      </c>
+      <c r="K141" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:11">
-      <c r="A142" s="4">
+      <c r="A142" s="5">
         <f t="shared" si="2"/>
         <v>1202008</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="5">
         <v>1202</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D142" s="4">
+      <c r="D142" s="5">
         <v>8</v>
       </c>
-      <c r="E142" s="4">
+      <c r="E142" s="5">
         <v>16</v>
       </c>
-      <c r="F142" s="4" t="s">
+      <c r="F142" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G142" s="7">
+      <c r="G142" s="8">
         <v>85</v>
       </c>
-      <c r="H142" s="7"/>
-      <c r="I142" s="7" t="s">
+      <c r="H142" s="8"/>
+      <c r="I142" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="J142" s="9">
-        <v>60</v>
-      </c>
-      <c r="K142" s="10" t="s">
+      <c r="J142" s="10">
+        <v>60</v>
+      </c>
+      <c r="K142" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="1:11">
-      <c r="A143" s="4">
+      <c r="A143" s="5">
         <f t="shared" si="2"/>
         <v>1202009</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="5">
         <v>1202</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="12">
         <v>9</v>
       </c>
-      <c r="E143" s="4">
+      <c r="E143" s="5">
         <v>18</v>
       </c>
-      <c r="F143" s="4" t="s">
+      <c r="F143" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G143" s="7">
+      <c r="G143" s="8">
         <v>95</v>
       </c>
-      <c r="H143" s="12"/>
-      <c r="I143" s="7" t="s">
+      <c r="H143" s="13"/>
+      <c r="I143" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="J143" s="9">
-        <v>60</v>
-      </c>
-      <c r="K143" s="10" t="s">
+      <c r="J143" s="10">
+        <v>60</v>
+      </c>
+      <c r="K143" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:11">
-      <c r="A144" s="4">
+      <c r="A144" s="5">
         <f t="shared" si="2"/>
         <v>1202010</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="5">
         <v>1202</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D144" s="4">
+      <c r="D144" s="5">
         <v>10</v>
       </c>
-      <c r="E144" s="4">
+      <c r="E144" s="5">
         <v>20</v>
       </c>
-      <c r="F144" s="4" t="s">
+      <c r="F144" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G144" s="7">
+      <c r="G144" s="8">
         <v>105</v>
       </c>
-      <c r="H144" s="7"/>
-      <c r="I144" s="7" t="s">
+      <c r="H144" s="8"/>
+      <c r="I144" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="J144" s="9">
-        <v>60</v>
-      </c>
-      <c r="K144" s="10" t="s">
+      <c r="J144" s="10">
+        <v>60</v>
+      </c>
+      <c r="K144" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="1:11">
-      <c r="A145" s="4">
+      <c r="A145" s="5">
         <f t="shared" si="2"/>
         <v>1301001</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="5">
         <v>1301</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D145" s="4">
+      <c r="D145" s="5">
         <v>1</v>
       </c>
-      <c r="E145" s="13"/>
-      <c r="F145" s="4" t="s">
+      <c r="E145" s="14"/>
+      <c r="F145" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G145" s="7">
+      <c r="G145" s="8">
         <v>1000</v>
       </c>
-      <c r="H145" s="13"/>
-      <c r="I145" s="13"/>
-      <c r="J145" s="9">
-        <v>60</v>
-      </c>
-      <c r="K145" s="10" t="s">
+      <c r="H145" s="14"/>
+      <c r="I145" s="15"/>
+      <c r="J145" s="10">
+        <v>60</v>
+      </c>
+      <c r="K145" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:11">
-      <c r="A146" s="4">
+      <c r="A146" s="5">
         <f t="shared" si="2"/>
         <v>1301002</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="5">
         <v>1301</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D146" s="4">
+      <c r="D146" s="5">
         <v>2</v>
       </c>
-      <c r="E146" s="13"/>
-      <c r="F146" s="4" t="s">
+      <c r="E146" s="14"/>
+      <c r="F146" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G146" s="7">
+      <c r="G146" s="8">
         <v>2000</v>
       </c>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
-      <c r="J146" s="9">
-        <v>60</v>
-      </c>
-      <c r="K146" s="10" t="s">
+      <c r="H146" s="14"/>
+      <c r="I146" s="15"/>
+      <c r="J146" s="10">
+        <v>60</v>
+      </c>
+      <c r="K146" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:11">
-      <c r="A147" s="4">
+      <c r="A147" s="5">
         <f t="shared" si="2"/>
         <v>1301003</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="5">
         <v>1301</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D147" s="4">
+      <c r="D147" s="5">
         <v>3</v>
       </c>
-      <c r="E147" s="13"/>
-      <c r="F147" s="4" t="s">
+      <c r="E147" s="14"/>
+      <c r="F147" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G147" s="8">
         <v>3000</v>
       </c>
-      <c r="H147" s="13"/>
-      <c r="I147" s="13"/>
-      <c r="J147" s="9">
-        <v>60</v>
-      </c>
-      <c r="K147" s="10" t="s">
+      <c r="H147" s="14"/>
+      <c r="I147" s="15"/>
+      <c r="J147" s="10">
+        <v>60</v>
+      </c>
+      <c r="K147" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:11">
-      <c r="A148" s="4">
+      <c r="A148" s="5">
         <f t="shared" si="2"/>
         <v>1301004</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="5">
         <v>1301</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D148" s="4">
+      <c r="D148" s="5">
         <v>4</v>
       </c>
-      <c r="E148" s="13"/>
-      <c r="F148" s="4" t="s">
+      <c r="E148" s="14"/>
+      <c r="F148" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G148" s="7">
+      <c r="G148" s="8">
         <v>4000</v>
       </c>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
-      <c r="J148" s="9">
-        <v>60</v>
-      </c>
-      <c r="K148" s="10" t="s">
+      <c r="H148" s="14"/>
+      <c r="I148" s="15"/>
+      <c r="J148" s="10">
+        <v>60</v>
+      </c>
+      <c r="K148" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:11">
-      <c r="A149" s="4">
+      <c r="A149" s="5">
         <f t="shared" si="2"/>
         <v>1301005</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="5">
         <v>1301</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D149" s="4">
+      <c r="D149" s="5">
         <v>5</v>
       </c>
-      <c r="E149" s="13"/>
-      <c r="F149" s="4" t="s">
+      <c r="E149" s="14"/>
+      <c r="F149" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G149" s="7">
+      <c r="G149" s="8">
         <v>5000</v>
       </c>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="9">
-        <v>60</v>
-      </c>
-      <c r="K149" s="10" t="s">
+      <c r="H149" s="14"/>
+      <c r="I149" s="15"/>
+      <c r="J149" s="10">
+        <v>60</v>
+      </c>
+      <c r="K149" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:11">
-      <c r="A150" s="4">
+      <c r="A150" s="5">
         <f t="shared" si="2"/>
         <v>1301006</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="5">
         <v>1301</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150" s="5">
         <v>6</v>
       </c>
-      <c r="E150" s="13"/>
-      <c r="F150" s="4" t="s">
+      <c r="E150" s="14"/>
+      <c r="F150" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G150" s="7">
+      <c r="G150" s="8">
         <v>6000</v>
       </c>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-      <c r="J150" s="9">
-        <v>60</v>
-      </c>
-      <c r="K150" s="10" t="s">
+      <c r="H150" s="14"/>
+      <c r="I150" s="15"/>
+      <c r="J150" s="10">
+        <v>60</v>
+      </c>
+      <c r="K150" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:11">
-      <c r="A151" s="4">
+      <c r="A151" s="5">
         <f t="shared" si="2"/>
         <v>1301007</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="5">
         <v>1301</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151" s="5">
         <v>7</v>
       </c>
-      <c r="E151" s="13"/>
-      <c r="F151" s="4" t="s">
+      <c r="E151" s="14"/>
+      <c r="F151" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G151" s="7">
+      <c r="G151" s="8">
         <v>7000</v>
       </c>
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
-      <c r="J151" s="9">
-        <v>60</v>
-      </c>
-      <c r="K151" s="10" t="s">
+      <c r="H151" s="14"/>
+      <c r="I151" s="15"/>
+      <c r="J151" s="10">
+        <v>60</v>
+      </c>
+      <c r="K151" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:11">
-      <c r="A152" s="4">
+      <c r="A152" s="5">
         <f t="shared" si="2"/>
         <v>1301008</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="5">
         <v>1301</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152" s="5">
         <v>8</v>
       </c>
-      <c r="E152" s="13"/>
-      <c r="F152" s="4" t="s">
+      <c r="E152" s="14"/>
+      <c r="F152" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G152" s="7">
+      <c r="G152" s="8">
         <v>8000</v>
       </c>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-      <c r="J152" s="9">
-        <v>60</v>
-      </c>
-      <c r="K152" s="10" t="s">
+      <c r="H152" s="14"/>
+      <c r="I152" s="15"/>
+      <c r="J152" s="10">
+        <v>60</v>
+      </c>
+      <c r="K152" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:11">
-      <c r="A153" s="4">
+      <c r="A153" s="5">
         <f t="shared" si="2"/>
         <v>1301009</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="5">
         <v>1301</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="12">
         <v>9</v>
       </c>
-      <c r="E153" s="13"/>
-      <c r="F153" s="4" t="s">
+      <c r="E153" s="14"/>
+      <c r="F153" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="8">
         <v>9000</v>
       </c>
-      <c r="H153" s="13"/>
-      <c r="I153" s="13"/>
-      <c r="J153" s="9">
-        <v>60</v>
-      </c>
-      <c r="K153" s="10" t="s">
+      <c r="H153" s="14"/>
+      <c r="I153" s="15"/>
+      <c r="J153" s="10">
+        <v>60</v>
+      </c>
+      <c r="K153" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:11">
-      <c r="A154" s="4">
+      <c r="A154" s="5">
         <f t="shared" si="2"/>
         <v>1301010</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="5">
         <v>1301</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154" s="5">
         <v>10</v>
       </c>
-      <c r="E154" s="13"/>
-      <c r="F154" s="4" t="s">
+      <c r="E154" s="14"/>
+      <c r="F154" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G154" s="7">
+      <c r="G154" s="8">
         <v>10000</v>
       </c>
-      <c r="H154" s="13"/>
-      <c r="I154" s="13"/>
-      <c r="J154" s="9">
-        <v>60</v>
-      </c>
-      <c r="K154" s="10" t="s">
+      <c r="H154" s="14"/>
+      <c r="I154" s="15"/>
+      <c r="J154" s="10">
+        <v>60</v>
+      </c>
+      <c r="K154" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A155" s="4">
+      <c r="A155" s="5">
         <f t="shared" ref="A155:A174" si="3">B155*1000+D155</f>
         <v>1302001</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="5">
         <v>1302</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155" s="5">
         <v>1</v>
       </c>
-      <c r="E155" s="13"/>
-      <c r="F155" s="4" t="s">
+      <c r="E155" s="14"/>
+      <c r="F155" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G155" s="7">
+      <c r="G155" s="8">
         <v>1</v>
       </c>
-      <c r="H155" s="7">
+      <c r="H155" s="8">
         <v>4030001</v>
       </c>
-      <c r="I155" s="7">
+      <c r="I155" s="8">
         <v>100300</v>
       </c>
-      <c r="J155" s="9">
-        <v>60</v>
-      </c>
-      <c r="K155" s="10" t="s">
+      <c r="J155" s="10">
+        <v>5</v>
+      </c>
+      <c r="K155" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A156" s="4">
+      <c r="A156" s="5">
         <f t="shared" si="3"/>
         <v>1302002</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="5">
         <v>1302</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D156" s="4">
+      <c r="D156" s="5">
         <v>2</v>
       </c>
-      <c r="E156" s="13"/>
-      <c r="F156" s="4" t="s">
+      <c r="E156" s="14"/>
+      <c r="F156" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G156" s="7">
+      <c r="G156" s="8">
         <v>2</v>
       </c>
-      <c r="H156" s="7">
-        <v>4030002</v>
-      </c>
-      <c r="I156" s="13">
+      <c r="H156" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I156" s="15">
         <v>103400</v>
       </c>
-      <c r="J156" s="9">
-        <v>60</v>
-      </c>
-      <c r="K156" s="10" t="s">
+      <c r="J156" s="10">
+        <v>10</v>
+      </c>
+      <c r="K156" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A157" s="4">
+      <c r="A157" s="5">
         <f t="shared" si="3"/>
         <v>1302003</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="5">
         <v>1302</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D157" s="4">
+      <c r="D157" s="5">
         <v>3</v>
       </c>
-      <c r="E157" s="13"/>
-      <c r="F157" s="4" t="s">
+      <c r="E157" s="14"/>
+      <c r="F157" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G157" s="7">
+      <c r="G157" s="8">
         <v>3</v>
       </c>
-      <c r="H157" s="7">
-        <v>4030003</v>
-      </c>
-      <c r="I157" s="13">
+      <c r="H157" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I157" s="15">
         <v>103500</v>
       </c>
-      <c r="J157" s="9">
-        <v>60</v>
-      </c>
-      <c r="K157" s="10" t="s">
+      <c r="J157" s="10">
+        <v>20</v>
+      </c>
+      <c r="K157" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A158" s="4">
+      <c r="A158" s="5">
         <f t="shared" si="3"/>
         <v>1302004</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="5">
         <v>1302</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D158" s="4">
+      <c r="D158" s="5">
         <v>4</v>
       </c>
-      <c r="E158" s="13"/>
-      <c r="F158" s="4" t="s">
+      <c r="E158" s="14"/>
+      <c r="F158" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G158" s="7">
+      <c r="G158" s="8">
         <v>4</v>
       </c>
-      <c r="H158" s="7">
-        <v>4030004</v>
-      </c>
-      <c r="I158" s="13">
+      <c r="H158" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I158" s="15">
         <v>101700</v>
       </c>
-      <c r="J158" s="9">
-        <v>60</v>
-      </c>
-      <c r="K158" s="10" t="s">
+      <c r="J158" s="10">
+        <v>30</v>
+      </c>
+      <c r="K158" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A159" s="4">
+      <c r="A159" s="5">
         <f t="shared" si="3"/>
         <v>1302005</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="5">
         <v>1302</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D159" s="4">
+      <c r="D159" s="5">
         <v>5</v>
       </c>
-      <c r="E159" s="13"/>
-      <c r="F159" s="4" t="s">
+      <c r="E159" s="14"/>
+      <c r="F159" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G159" s="7">
+      <c r="G159" s="8">
         <v>5</v>
       </c>
-      <c r="H159" s="7">
-        <v>4030005</v>
-      </c>
-      <c r="I159" s="13">
+      <c r="H159" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I159" s="15">
         <v>101800</v>
       </c>
-      <c r="J159" s="9">
-        <v>60</v>
-      </c>
-      <c r="K159" s="10" t="s">
+      <c r="J159" s="10">
+        <v>60</v>
+      </c>
+      <c r="K159" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A160" s="4">
+      <c r="A160" s="5">
         <f t="shared" si="3"/>
         <v>1302006</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="5">
         <v>1302</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D160" s="4">
+      <c r="D160" s="5">
         <v>6</v>
       </c>
-      <c r="E160" s="13"/>
-      <c r="F160" s="4" t="s">
+      <c r="E160" s="14"/>
+      <c r="F160" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G160" s="7">
+      <c r="G160" s="8">
         <v>6</v>
       </c>
-      <c r="H160" s="7">
-        <v>4030006</v>
-      </c>
-      <c r="I160" s="13">
+      <c r="H160" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I160" s="15">
         <v>102100</v>
       </c>
-      <c r="J160" s="9">
-        <v>60</v>
-      </c>
-      <c r="K160" s="10" t="s">
+      <c r="J160" s="10">
+        <v>80</v>
+      </c>
+      <c r="K160" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A161" s="4">
+      <c r="A161" s="5">
         <f t="shared" si="3"/>
         <v>1302007</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="5">
         <v>1302</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161" s="5">
         <v>7</v>
       </c>
-      <c r="E161" s="13"/>
-      <c r="F161" s="4" t="s">
+      <c r="E161" s="14"/>
+      <c r="F161" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G161" s="7">
+      <c r="G161" s="8">
         <v>7</v>
       </c>
-      <c r="H161" s="7">
-        <v>4030007</v>
-      </c>
-      <c r="I161" s="13"/>
-      <c r="J161" s="9">
-        <v>60</v>
-      </c>
-      <c r="K161" s="10" t="s">
+      <c r="H161" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I161" s="15">
+        <v>100700</v>
+      </c>
+      <c r="J161" s="10">
+        <v>120</v>
+      </c>
+      <c r="K161" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A162" s="4">
+      <c r="A162" s="5">
         <f t="shared" si="3"/>
         <v>1302008</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="5">
         <v>1302</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D162" s="5">
         <v>8</v>
       </c>
-      <c r="E162" s="13"/>
-      <c r="F162" s="4" t="s">
+      <c r="E162" s="14"/>
+      <c r="F162" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G162" s="7">
+      <c r="G162" s="8">
         <v>8</v>
       </c>
-      <c r="H162" s="7">
-        <v>4030008</v>
-      </c>
-      <c r="I162" s="13"/>
-      <c r="J162" s="9">
-        <v>60</v>
-      </c>
-      <c r="K162" s="10" t="s">
+      <c r="H162" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I162" s="15">
+        <v>101200</v>
+      </c>
+      <c r="J162" s="10">
+        <v>150</v>
+      </c>
+      <c r="K162" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A163" s="4">
+      <c r="A163" s="5">
         <f t="shared" si="3"/>
         <v>1302009</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="5">
         <v>1302</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="12">
         <v>9</v>
       </c>
-      <c r="E163" s="13"/>
-      <c r="F163" s="4" t="s">
+      <c r="E163" s="14"/>
+      <c r="F163" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G163" s="7">
+      <c r="G163" s="8">
         <v>9</v>
       </c>
-      <c r="H163" s="7">
-        <v>4030009</v>
-      </c>
-      <c r="I163" s="13"/>
-      <c r="J163" s="9">
-        <v>60</v>
-      </c>
-      <c r="K163" s="10" t="s">
+      <c r="H163" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I163" s="15">
+        <v>101400</v>
+      </c>
+      <c r="J163" s="10">
+        <v>200</v>
+      </c>
+      <c r="K163" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A164" s="4">
+      <c r="A164" s="5">
         <f t="shared" si="3"/>
         <v>1302010</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="5">
         <v>1302</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D164" s="4">
+      <c r="D164" s="5">
         <v>10</v>
       </c>
-      <c r="E164" s="13"/>
-      <c r="F164" s="4" t="s">
+      <c r="E164" s="14"/>
+      <c r="F164" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G164" s="7">
+      <c r="G164" s="8">
         <v>10</v>
       </c>
-      <c r="H164" s="7">
-        <v>4030010</v>
-      </c>
-      <c r="J164" s="9">
-        <v>60</v>
-      </c>
-      <c r="K164" s="10" t="s">
+      <c r="H164" s="8">
+        <v>4030001</v>
+      </c>
+      <c r="I164" s="2">
+        <v>102300</v>
+      </c>
+      <c r="J164" s="10">
+        <v>300</v>
+      </c>
+      <c r="K164" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="165" customHeight="1" spans="1:11">
-      <c r="A165" s="4">
+      <c r="A165" s="5">
         <f t="shared" si="3"/>
         <v>1303001</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="5">
         <v>1303</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D165" s="4">
+      <c r="D165" s="5">
         <v>1</v>
       </c>
-      <c r="E165" s="13"/>
-      <c r="F165" s="4" t="s">
+      <c r="E165" s="14"/>
+      <c r="F165" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G165" s="7">
+      <c r="G165" s="8">
         <v>100</v>
       </c>
-      <c r="H165" s="13"/>
-      <c r="I165" s="13"/>
-      <c r="J165" s="9">
-        <v>60</v>
-      </c>
-      <c r="K165" s="10" t="s">
+      <c r="H165" s="14"/>
+      <c r="I165" s="15"/>
+      <c r="J165" s="10">
+        <v>60</v>
+      </c>
+      <c r="K165" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:11">
-      <c r="A166" s="4">
+      <c r="A166" s="5">
         <f t="shared" si="3"/>
         <v>1303002</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="5">
         <v>1303</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D166" s="4">
+      <c r="D166" s="5">
         <v>2</v>
       </c>
-      <c r="E166" s="13"/>
-      <c r="F166" s="4" t="s">
+      <c r="E166" s="14"/>
+      <c r="F166" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G166" s="7">
+      <c r="G166" s="8">
         <v>200</v>
       </c>
-      <c r="H166" s="13"/>
-      <c r="I166" s="13"/>
-      <c r="J166" s="9">
-        <v>60</v>
-      </c>
-      <c r="K166" s="10" t="s">
+      <c r="H166" s="14"/>
+      <c r="I166" s="15"/>
+      <c r="J166" s="10">
+        <v>60</v>
+      </c>
+      <c r="K166" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:11">
-      <c r="A167" s="4">
+      <c r="A167" s="5">
         <f t="shared" si="3"/>
         <v>1303003</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="5">
         <v>1303</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D167" s="4">
+      <c r="D167" s="5">
         <v>3</v>
       </c>
-      <c r="E167" s="13"/>
-      <c r="F167" s="4" t="s">
+      <c r="E167" s="14"/>
+      <c r="F167" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G167" s="7">
+      <c r="G167" s="8">
         <v>300</v>
       </c>
-      <c r="H167" s="13"/>
-      <c r="I167" s="13"/>
-      <c r="J167" s="9">
-        <v>60</v>
-      </c>
-      <c r="K167" s="10" t="s">
+      <c r="H167" s="14"/>
+      <c r="I167" s="15"/>
+      <c r="J167" s="10">
+        <v>60</v>
+      </c>
+      <c r="K167" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:11">
-      <c r="A168" s="4">
+      <c r="A168" s="5">
         <f t="shared" si="3"/>
         <v>1303004</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="5">
         <v>1303</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D168" s="4">
+      <c r="D168" s="5">
         <v>4</v>
       </c>
-      <c r="E168" s="13"/>
-      <c r="F168" s="4" t="s">
+      <c r="E168" s="14"/>
+      <c r="F168" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G168" s="7">
+      <c r="G168" s="8">
         <v>400</v>
       </c>
-      <c r="H168" s="13"/>
-      <c r="I168" s="13"/>
-      <c r="J168" s="9">
-        <v>60</v>
-      </c>
-      <c r="K168" s="10" t="s">
+      <c r="H168" s="14"/>
+      <c r="I168" s="15"/>
+      <c r="J168" s="10">
+        <v>60</v>
+      </c>
+      <c r="K168" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:11">
-      <c r="A169" s="4">
+      <c r="A169" s="5">
         <f t="shared" si="3"/>
         <v>1303005</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="5">
         <v>1303</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D169" s="4">
+      <c r="D169" s="5">
         <v>5</v>
       </c>
-      <c r="E169" s="13"/>
-      <c r="F169" s="4" t="s">
+      <c r="E169" s="14"/>
+      <c r="F169" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G169" s="7">
+      <c r="G169" s="8">
         <v>500</v>
       </c>
-      <c r="H169" s="13"/>
-      <c r="I169" s="13"/>
-      <c r="J169" s="9">
-        <v>60</v>
-      </c>
-      <c r="K169" s="10" t="s">
+      <c r="H169" s="14"/>
+      <c r="I169" s="15"/>
+      <c r="J169" s="10">
+        <v>60</v>
+      </c>
+      <c r="K169" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:11">
-      <c r="A170" s="4">
+      <c r="A170" s="5">
         <f t="shared" si="3"/>
         <v>1303006</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="5">
         <v>1303</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D170" s="4">
+      <c r="D170" s="5">
         <v>6</v>
       </c>
-      <c r="E170" s="13"/>
-      <c r="F170" s="4" t="s">
+      <c r="E170" s="14"/>
+      <c r="F170" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G170" s="7">
+      <c r="G170" s="8">
         <v>600</v>
       </c>
-      <c r="H170" s="13"/>
-      <c r="I170" s="13"/>
-      <c r="J170" s="9">
-        <v>60</v>
-      </c>
-      <c r="K170" s="10" t="s">
+      <c r="H170" s="14"/>
+      <c r="I170" s="15"/>
+      <c r="J170" s="10">
+        <v>60</v>
+      </c>
+      <c r="K170" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:11">
-      <c r="A171" s="4">
+      <c r="A171" s="5">
         <f t="shared" si="3"/>
         <v>1303007</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="5">
         <v>1303</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D171" s="4">
+      <c r="D171" s="5">
         <v>7</v>
       </c>
-      <c r="E171" s="13"/>
-      <c r="F171" s="4" t="s">
+      <c r="E171" s="14"/>
+      <c r="F171" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G171" s="7">
+      <c r="G171" s="8">
         <v>700</v>
       </c>
-      <c r="H171" s="13"/>
-      <c r="I171" s="13"/>
-      <c r="J171" s="9">
-        <v>60</v>
-      </c>
-      <c r="K171" s="10" t="s">
+      <c r="H171" s="14"/>
+      <c r="I171" s="15"/>
+      <c r="J171" s="10">
+        <v>60</v>
+      </c>
+      <c r="K171" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:11">
-      <c r="A172" s="4">
+      <c r="A172" s="5">
         <f t="shared" si="3"/>
         <v>1303008</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="5">
         <v>1303</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D172" s="4">
+      <c r="D172" s="5">
         <v>8</v>
       </c>
-      <c r="E172" s="13"/>
-      <c r="F172" s="4" t="s">
+      <c r="E172" s="14"/>
+      <c r="F172" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G172" s="7">
+      <c r="G172" s="8">
         <v>800</v>
       </c>
-      <c r="H172" s="13"/>
-      <c r="I172" s="13"/>
-      <c r="J172" s="9">
-        <v>60</v>
-      </c>
-      <c r="K172" s="10" t="s">
+      <c r="H172" s="14"/>
+      <c r="I172" s="15"/>
+      <c r="J172" s="10">
+        <v>60</v>
+      </c>
+      <c r="K172" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:11">
-      <c r="A173" s="4">
+      <c r="A173" s="5">
         <f t="shared" si="3"/>
         <v>1303009</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="5">
         <v>1303</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D173" s="12">
         <v>9</v>
       </c>
-      <c r="E173" s="13"/>
-      <c r="F173" s="4" t="s">
+      <c r="E173" s="14"/>
+      <c r="F173" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G173" s="7">
+      <c r="G173" s="8">
         <v>900</v>
       </c>
-      <c r="H173" s="13"/>
-      <c r="I173" s="13"/>
-      <c r="J173" s="9">
-        <v>60</v>
-      </c>
-      <c r="K173" s="10" t="s">
+      <c r="H173" s="14"/>
+      <c r="I173" s="15"/>
+      <c r="J173" s="10">
+        <v>60</v>
+      </c>
+      <c r="K173" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:11">
-      <c r="A174" s="4">
+      <c r="A174" s="5">
         <f t="shared" si="3"/>
         <v>1303010</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="5">
         <v>1303</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D174" s="4">
+      <c r="D174" s="5">
         <v>10</v>
       </c>
-      <c r="E174" s="13"/>
-      <c r="F174" s="4" t="s">
+      <c r="E174" s="14"/>
+      <c r="F174" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G174" s="7">
+      <c r="G174" s="8">
         <v>1000</v>
       </c>
-      <c r="H174" s="13"/>
-      <c r="I174" s="13"/>
-      <c r="J174" s="9">
-        <v>60</v>
-      </c>
-      <c r="K174" s="10" t="s">
+      <c r="H174" s="14"/>
+      <c r="I174" s="15"/>
+      <c r="J174" s="10">
+        <v>60</v>
+      </c>
+      <c r="K174" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:11">
-      <c r="A175" s="4">
+      <c r="A175" s="5">
         <f t="shared" ref="A175:A184" si="4">B175*1000+D175</f>
         <v>1304001</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="5">
         <v>1304</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D175" s="5">
         <v>1</v>
       </c>
-      <c r="E175" s="13"/>
-      <c r="F175" s="4" t="s">
+      <c r="E175" s="14"/>
+      <c r="F175" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G175" s="7">
+      <c r="G175" s="8">
         <v>100</v>
       </c>
-      <c r="H175" s="13"/>
-      <c r="I175" s="13"/>
-      <c r="J175" s="9">
-        <v>60</v>
-      </c>
-      <c r="K175" s="10" t="s">
+      <c r="H175" s="14"/>
+      <c r="I175" s="15"/>
+      <c r="J175" s="10">
+        <v>60</v>
+      </c>
+      <c r="K175" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="176" customHeight="1" spans="1:11">
-      <c r="A176" s="4">
+      <c r="A176" s="5">
         <f t="shared" si="4"/>
         <v>1304002</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="5">
         <v>1304</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D176" s="4">
+      <c r="D176" s="5">
         <v>2</v>
       </c>
-      <c r="E176" s="13"/>
-      <c r="F176" s="4" t="s">
+      <c r="E176" s="14"/>
+      <c r="F176" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G176" s="7">
+      <c r="G176" s="8">
         <v>200</v>
       </c>
-      <c r="H176" s="13"/>
-      <c r="I176" s="13"/>
-      <c r="J176" s="9">
-        <v>60</v>
-      </c>
-      <c r="K176" s="10" t="s">
+      <c r="H176" s="14"/>
+      <c r="I176" s="15"/>
+      <c r="J176" s="10">
+        <v>60</v>
+      </c>
+      <c r="K176" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="177" customHeight="1" spans="1:11">
-      <c r="A177" s="4">
+      <c r="A177" s="5">
         <f t="shared" si="4"/>
         <v>1304003</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="5">
         <v>1304</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D177" s="4">
+      <c r="D177" s="5">
         <v>3</v>
       </c>
-      <c r="E177" s="13"/>
-      <c r="F177" s="4" t="s">
+      <c r="E177" s="14"/>
+      <c r="F177" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G177" s="7">
+      <c r="G177" s="8">
         <v>300</v>
       </c>
-      <c r="H177" s="13"/>
-      <c r="I177" s="13"/>
-      <c r="J177" s="9">
-        <v>60</v>
-      </c>
-      <c r="K177" s="10" t="s">
+      <c r="H177" s="14"/>
+      <c r="I177" s="15"/>
+      <c r="J177" s="10">
+        <v>60</v>
+      </c>
+      <c r="K177" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:11">
-      <c r="A178" s="4">
+      <c r="A178" s="5">
         <f t="shared" si="4"/>
         <v>1304004</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="5">
         <v>1304</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D178" s="4">
+      <c r="D178" s="5">
         <v>4</v>
       </c>
-      <c r="E178" s="13"/>
-      <c r="F178" s="4" t="s">
+      <c r="E178" s="14"/>
+      <c r="F178" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G178" s="7">
+      <c r="G178" s="8">
         <v>400</v>
       </c>
-      <c r="H178" s="13"/>
-      <c r="I178" s="13"/>
-      <c r="J178" s="9">
-        <v>60</v>
-      </c>
-      <c r="K178" s="10" t="s">
+      <c r="H178" s="14"/>
+      <c r="I178" s="15"/>
+      <c r="J178" s="10">
+        <v>60</v>
+      </c>
+      <c r="K178" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:11">
-      <c r="A179" s="4">
+      <c r="A179" s="5">
         <f t="shared" si="4"/>
         <v>1304005</v>
       </c>
-      <c r="B179" s="4">
+      <c r="B179" s="5">
         <v>1304</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D179" s="4">
+      <c r="D179" s="5">
         <v>5</v>
       </c>
-      <c r="E179" s="13"/>
-      <c r="F179" s="4" t="s">
+      <c r="E179" s="14"/>
+      <c r="F179" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G179" s="7">
+      <c r="G179" s="8">
         <v>500</v>
       </c>
-      <c r="H179" s="13"/>
-      <c r="I179" s="13"/>
-      <c r="J179" s="9">
-        <v>60</v>
-      </c>
-      <c r="K179" s="10" t="s">
+      <c r="H179" s="14"/>
+      <c r="I179" s="15"/>
+      <c r="J179" s="10">
+        <v>60</v>
+      </c>
+      <c r="K179" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:11">
-      <c r="A180" s="4">
+      <c r="A180" s="5">
         <f t="shared" si="4"/>
         <v>1304006</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="5">
         <v>1304</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C180" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D180" s="4">
+      <c r="D180" s="5">
         <v>6</v>
       </c>
-      <c r="E180" s="13"/>
-      <c r="F180" s="4" t="s">
+      <c r="E180" s="14"/>
+      <c r="F180" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G180" s="7">
+      <c r="G180" s="8">
         <v>600</v>
       </c>
-      <c r="H180" s="13"/>
-      <c r="I180" s="13"/>
-      <c r="J180" s="9">
-        <v>60</v>
-      </c>
-      <c r="K180" s="10" t="s">
+      <c r="H180" s="14"/>
+      <c r="I180" s="15"/>
+      <c r="J180" s="10">
+        <v>60</v>
+      </c>
+      <c r="K180" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:11">
-      <c r="A181" s="4">
+      <c r="A181" s="5">
         <f t="shared" si="4"/>
         <v>1304007</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="5">
         <v>1304</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D181" s="4">
+      <c r="D181" s="5">
         <v>7</v>
       </c>
-      <c r="E181" s="13"/>
-      <c r="F181" s="4" t="s">
+      <c r="E181" s="14"/>
+      <c r="F181" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="7">
+      <c r="G181" s="8">
         <v>700</v>
       </c>
-      <c r="H181" s="13"/>
-      <c r="I181" s="13"/>
-      <c r="J181" s="9">
-        <v>60</v>
-      </c>
-      <c r="K181" s="10" t="s">
+      <c r="H181" s="14"/>
+      <c r="I181" s="15"/>
+      <c r="J181" s="10">
+        <v>60</v>
+      </c>
+      <c r="K181" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:11">
-      <c r="A182" s="4">
+      <c r="A182" s="5">
         <f t="shared" si="4"/>
         <v>1304008</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="5">
         <v>1304</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D182" s="4">
+      <c r="D182" s="5">
         <v>8</v>
       </c>
-      <c r="E182" s="13"/>
-      <c r="F182" s="4" t="s">
+      <c r="E182" s="14"/>
+      <c r="F182" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G182" s="7">
+      <c r="G182" s="8">
         <v>800</v>
       </c>
-      <c r="H182" s="13"/>
-      <c r="I182" s="13"/>
-      <c r="J182" s="9">
-        <v>60</v>
-      </c>
-      <c r="K182" s="10" t="s">
+      <c r="H182" s="14"/>
+      <c r="I182" s="15"/>
+      <c r="J182" s="10">
+        <v>60</v>
+      </c>
+      <c r="K182" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:11">
-      <c r="A183" s="4">
+      <c r="A183" s="5">
         <f t="shared" si="4"/>
         <v>1304009</v>
       </c>
-      <c r="B183" s="4">
+      <c r="B183" s="5">
         <v>1304</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="12">
         <v>9</v>
       </c>
-      <c r="E183" s="13"/>
-      <c r="F183" s="4" t="s">
+      <c r="E183" s="14"/>
+      <c r="F183" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G183" s="7">
+      <c r="G183" s="8">
         <v>900</v>
       </c>
-      <c r="H183" s="13"/>
-      <c r="I183" s="13"/>
-      <c r="J183" s="9">
-        <v>60</v>
-      </c>
-      <c r="K183" s="10" t="s">
+      <c r="H183" s="14"/>
+      <c r="I183" s="15"/>
+      <c r="J183" s="10">
+        <v>60</v>
+      </c>
+      <c r="K183" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:11">
-      <c r="A184" s="4">
+      <c r="A184" s="5">
         <f t="shared" si="4"/>
         <v>1304010</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="5">
         <v>1304</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D184" s="4">
+      <c r="D184" s="5">
         <v>10</v>
       </c>
-      <c r="E184" s="13"/>
-      <c r="F184" s="4" t="s">
+      <c r="E184" s="14"/>
+      <c r="F184" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G184" s="7">
+      <c r="G184" s="8">
         <v>1000</v>
       </c>
-      <c r="H184" s="13"/>
-      <c r="I184" s="13"/>
-      <c r="J184" s="9">
-        <v>60</v>
-      </c>
-      <c r="K184" s="10" t="s">
+      <c r="H184" s="14"/>
+      <c r="I184" s="15"/>
+      <c r="J184" s="10">
+        <v>60</v>
+      </c>
+      <c r="K184" s="11" t="s">
         <v>28</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -1341,7 +1341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1359,9 +1359,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1386,9 +1383,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1989,13 +1983,13 @@
       <c r="H2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2016,19 +2010,19 @@
       <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2039,11 +2033,11 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A5" s="5">
@@ -2065,15 +2059,15 @@
       <c r="F5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>1000</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="10">
-        <v>60</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="9">
+        <v>5</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2097,17 +2091,17 @@
       <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>1100</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="10">
-        <v>60</v>
-      </c>
-      <c r="K6" s="11" t="s">
+      <c r="J6" s="9">
+        <v>10</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2131,17 +2125,17 @@
       <c r="F7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>2000</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="10">
-        <v>60</v>
-      </c>
-      <c r="K7" s="11" t="s">
+      <c r="J7" s="9">
+        <v>20</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2165,17 +2159,17 @@
       <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>3000</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="10">
-        <v>60</v>
-      </c>
-      <c r="K8" s="11" t="s">
+      <c r="J8" s="9">
+        <v>30</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2199,17 +2193,17 @@
       <c r="F9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>4500</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>60</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2233,17 +2227,17 @@
       <c r="F10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>6000</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8" t="s">
+      <c r="H10" s="7"/>
+      <c r="I10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="10">
-        <v>60</v>
-      </c>
-      <c r="K10" s="11" t="s">
+      <c r="J10" s="9">
+        <v>80</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2267,17 +2261,17 @@
       <c r="F11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>9000</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="10">
-        <v>60</v>
-      </c>
-      <c r="K11" s="11" t="s">
+      <c r="J11" s="9">
+        <v>120</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2301,17 +2295,17 @@
       <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>15000</v>
       </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="s">
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="10">
-        <v>60</v>
-      </c>
-      <c r="K12" s="11" t="s">
+      <c r="J12" s="9">
+        <v>150</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2326,7 +2320,7 @@
       <c r="C13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>9</v>
       </c>
       <c r="E13" s="5">
@@ -2335,17 +2329,17 @@
       <c r="F13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>30000</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="8" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="10">
-        <v>60</v>
-      </c>
-      <c r="K13" s="11" t="s">
+      <c r="J13" s="9">
+        <v>200</v>
+      </c>
+      <c r="K13" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2369,17 +2363,17 @@
       <c r="F14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>10000</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="10">
-        <v>60</v>
-      </c>
-      <c r="K14" s="11" t="s">
+      <c r="J14" s="9">
+        <v>300</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2403,15 +2397,15 @@
       <c r="F15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <v>1000</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="10">
-        <v>60</v>
-      </c>
-      <c r="K15" s="11" t="s">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="9">
+        <v>5</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2435,17 +2429,17 @@
       <c r="F16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>1100</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="10">
-        <v>60</v>
-      </c>
-      <c r="K16" s="11" t="s">
+      <c r="J16" s="9">
+        <v>10</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2469,17 +2463,17 @@
       <c r="F17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>2000</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="10">
-        <v>60</v>
-      </c>
-      <c r="K17" s="11" t="s">
+      <c r="J17" s="9">
+        <v>20</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2503,17 +2497,17 @@
       <c r="F18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>3000</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="10">
-        <v>60</v>
-      </c>
-      <c r="K18" s="11" t="s">
+      <c r="J18" s="9">
+        <v>30</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2537,17 +2531,17 @@
       <c r="F19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>4500</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>60</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2571,17 +2565,17 @@
       <c r="F20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="7">
         <v>6000</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8" t="s">
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="10">
-        <v>60</v>
-      </c>
-      <c r="K20" s="11" t="s">
+      <c r="J20" s="9">
+        <v>80</v>
+      </c>
+      <c r="K20" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2605,17 +2599,17 @@
       <c r="F21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="7">
         <v>9000</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="10">
-        <v>60</v>
-      </c>
-      <c r="K21" s="11" t="s">
+      <c r="J21" s="9">
+        <v>120</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2639,17 +2633,17 @@
       <c r="F22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="7">
         <v>15000</v>
       </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="s">
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="10">
-        <v>60</v>
-      </c>
-      <c r="K22" s="11" t="s">
+      <c r="J22" s="9">
+        <v>150</v>
+      </c>
+      <c r="K22" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2664,7 +2658,7 @@
       <c r="C23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <v>9</v>
       </c>
       <c r="E23" s="5">
@@ -2673,17 +2667,17 @@
       <c r="F23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="7">
         <v>30000</v>
       </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="12"/>
+      <c r="I23" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="10">
-        <v>60</v>
-      </c>
-      <c r="K23" s="11" t="s">
+      <c r="J23" s="9">
+        <v>200</v>
+      </c>
+      <c r="K23" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2707,17 +2701,17 @@
       <c r="F24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="7">
         <v>10000</v>
       </c>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8" t="s">
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J24" s="10">
-        <v>60</v>
-      </c>
-      <c r="K24" s="11" t="s">
+      <c r="J24" s="9">
+        <v>300</v>
+      </c>
+      <c r="K24" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2741,15 +2735,15 @@
       <c r="F25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="7">
         <v>1000</v>
       </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="10">
-        <v>60</v>
-      </c>
-      <c r="K25" s="11" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="9">
+        <v>5</v>
+      </c>
+      <c r="K25" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2773,17 +2767,17 @@
       <c r="F26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="7">
         <v>1100</v>
       </c>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8" t="s">
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J26" s="10">
-        <v>60</v>
-      </c>
-      <c r="K26" s="11" t="s">
+      <c r="J26" s="9">
+        <v>10</v>
+      </c>
+      <c r="K26" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2807,17 +2801,17 @@
       <c r="F27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="7">
         <v>2000</v>
       </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8" t="s">
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="10">
-        <v>60</v>
-      </c>
-      <c r="K27" s="11" t="s">
+      <c r="J27" s="9">
+        <v>20</v>
+      </c>
+      <c r="K27" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2841,17 +2835,17 @@
       <c r="F28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="7">
         <v>3000</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8" t="s">
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J28" s="10">
-        <v>60</v>
-      </c>
-      <c r="K28" s="11" t="s">
+      <c r="J28" s="9">
+        <v>30</v>
+      </c>
+      <c r="K28" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2875,17 +2869,17 @@
       <c r="F29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="7">
         <v>4500</v>
       </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="s">
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="9">
         <v>60</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2909,17 +2903,17 @@
       <c r="F30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="7">
         <v>6000</v>
       </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8" t="s">
+      <c r="H30" s="7"/>
+      <c r="I30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J30" s="10">
-        <v>60</v>
-      </c>
-      <c r="K30" s="11" t="s">
+      <c r="J30" s="9">
+        <v>80</v>
+      </c>
+      <c r="K30" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2943,17 +2937,17 @@
       <c r="F31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="7">
         <v>9000</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8" t="s">
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J31" s="10">
-        <v>60</v>
-      </c>
-      <c r="K31" s="11" t="s">
+      <c r="J31" s="9">
+        <v>120</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2977,17 +2971,17 @@
       <c r="F32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="7">
         <v>15000</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8" t="s">
+      <c r="H32" s="7"/>
+      <c r="I32" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="10">
-        <v>60</v>
-      </c>
-      <c r="K32" s="11" t="s">
+      <c r="J32" s="9">
+        <v>150</v>
+      </c>
+      <c r="K32" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3002,7 +2996,7 @@
       <c r="C33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <v>9</v>
       </c>
       <c r="E33" s="5">
@@ -3011,17 +3005,17 @@
       <c r="F33" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="7">
         <v>30000</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="8" t="s">
+      <c r="H33" s="12"/>
+      <c r="I33" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J33" s="10">
-        <v>60</v>
-      </c>
-      <c r="K33" s="11" t="s">
+      <c r="J33" s="9">
+        <v>200</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3045,17 +3039,17 @@
       <c r="F34" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="7">
         <v>10000</v>
       </c>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8" t="s">
+      <c r="H34" s="7"/>
+      <c r="I34" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J34" s="10">
-        <v>60</v>
-      </c>
-      <c r="K34" s="11" t="s">
+      <c r="J34" s="9">
+        <v>300</v>
+      </c>
+      <c r="K34" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3079,15 +3073,15 @@
       <c r="F35" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="7">
         <v>1000</v>
       </c>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="10">
-        <v>60</v>
-      </c>
-      <c r="K35" s="11" t="s">
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="9">
+        <v>5</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3111,17 +3105,17 @@
       <c r="F36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="7">
         <v>1100</v>
       </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8" t="s">
+      <c r="H36" s="7"/>
+      <c r="I36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J36" s="10">
-        <v>60</v>
-      </c>
-      <c r="K36" s="11" t="s">
+      <c r="J36" s="9">
+        <v>10</v>
+      </c>
+      <c r="K36" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3145,17 +3139,17 @@
       <c r="F37" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="7">
         <v>2000</v>
       </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8" t="s">
+      <c r="H37" s="7"/>
+      <c r="I37" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J37" s="10">
-        <v>60</v>
-      </c>
-      <c r="K37" s="11" t="s">
+      <c r="J37" s="9">
+        <v>20</v>
+      </c>
+      <c r="K37" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3179,17 +3173,17 @@
       <c r="F38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="7">
         <v>3000</v>
       </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8" t="s">
+      <c r="H38" s="7"/>
+      <c r="I38" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="10">
-        <v>60</v>
-      </c>
-      <c r="K38" s="11" t="s">
+      <c r="J38" s="9">
+        <v>30</v>
+      </c>
+      <c r="K38" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3213,17 +3207,17 @@
       <c r="F39" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="7">
         <v>4500</v>
       </c>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8" t="s">
+      <c r="H39" s="7"/>
+      <c r="I39" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J39" s="9">
         <v>60</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K39" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3247,17 +3241,17 @@
       <c r="F40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="7">
         <v>6000</v>
       </c>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8" t="s">
+      <c r="H40" s="7"/>
+      <c r="I40" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J40" s="10">
-        <v>60</v>
-      </c>
-      <c r="K40" s="11" t="s">
+      <c r="J40" s="9">
+        <v>80</v>
+      </c>
+      <c r="K40" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3281,17 +3275,17 @@
       <c r="F41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="7">
         <v>9000</v>
       </c>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8" t="s">
+      <c r="H41" s="7"/>
+      <c r="I41" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J41" s="10">
-        <v>60</v>
-      </c>
-      <c r="K41" s="11" t="s">
+      <c r="J41" s="9">
+        <v>120</v>
+      </c>
+      <c r="K41" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3315,17 +3309,17 @@
       <c r="F42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="7">
         <v>15000</v>
       </c>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8" t="s">
+      <c r="H42" s="7"/>
+      <c r="I42" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J42" s="10">
-        <v>60</v>
-      </c>
-      <c r="K42" s="11" t="s">
+      <c r="J42" s="9">
+        <v>150</v>
+      </c>
+      <c r="K42" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3340,7 +3334,7 @@
       <c r="C43" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="11">
         <v>9</v>
       </c>
       <c r="E43" s="5">
@@ -3349,17 +3343,17 @@
       <c r="F43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="7">
         <v>30000</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="8" t="s">
+      <c r="H43" s="12"/>
+      <c r="I43" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J43" s="10">
-        <v>60</v>
-      </c>
-      <c r="K43" s="11" t="s">
+      <c r="J43" s="9">
+        <v>200</v>
+      </c>
+      <c r="K43" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3383,17 +3377,17 @@
       <c r="F44" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="7">
         <v>10000</v>
       </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8" t="s">
+      <c r="H44" s="7"/>
+      <c r="I44" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="J44" s="10">
-        <v>60</v>
-      </c>
-      <c r="K44" s="11" t="s">
+      <c r="J44" s="9">
+        <v>300</v>
+      </c>
+      <c r="K44" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3417,15 +3411,15 @@
       <c r="F45" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="7">
         <v>1000</v>
       </c>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="10">
-        <v>60</v>
-      </c>
-      <c r="K45" s="11" t="s">
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="9">
+        <v>5</v>
+      </c>
+      <c r="K45" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3449,17 +3443,17 @@
       <c r="F46" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="7">
         <v>1100</v>
       </c>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8" t="s">
+      <c r="H46" s="7"/>
+      <c r="I46" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J46" s="10">
-        <v>60</v>
-      </c>
-      <c r="K46" s="11" t="s">
+      <c r="J46" s="9">
+        <v>10</v>
+      </c>
+      <c r="K46" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3483,17 +3477,17 @@
       <c r="F47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="7">
         <v>2000</v>
       </c>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8" t="s">
+      <c r="H47" s="7"/>
+      <c r="I47" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J47" s="10">
-        <v>60</v>
-      </c>
-      <c r="K47" s="11" t="s">
+      <c r="J47" s="9">
+        <v>20</v>
+      </c>
+      <c r="K47" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3517,17 +3511,17 @@
       <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="7">
         <v>3000</v>
       </c>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8" t="s">
+      <c r="H48" s="7"/>
+      <c r="I48" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J48" s="10">
-        <v>60</v>
-      </c>
-      <c r="K48" s="11" t="s">
+      <c r="J48" s="9">
+        <v>30</v>
+      </c>
+      <c r="K48" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3551,17 +3545,17 @@
       <c r="F49" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="7">
         <v>4500</v>
       </c>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8" t="s">
+      <c r="H49" s="7"/>
+      <c r="I49" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="9">
         <v>60</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3585,17 +3579,17 @@
       <c r="F50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="7">
         <v>6000</v>
       </c>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8" t="s">
+      <c r="H50" s="7"/>
+      <c r="I50" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J50" s="10">
-        <v>60</v>
-      </c>
-      <c r="K50" s="11" t="s">
+      <c r="J50" s="9">
+        <v>80</v>
+      </c>
+      <c r="K50" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3619,17 +3613,17 @@
       <c r="F51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="7">
         <v>9000</v>
       </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8" t="s">
+      <c r="H51" s="7"/>
+      <c r="I51" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J51" s="10">
-        <v>60</v>
-      </c>
-      <c r="K51" s="11" t="s">
+      <c r="J51" s="9">
+        <v>120</v>
+      </c>
+      <c r="K51" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3653,17 +3647,17 @@
       <c r="F52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="7">
         <v>15000</v>
       </c>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8" t="s">
+      <c r="H52" s="7"/>
+      <c r="I52" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J52" s="10">
-        <v>60</v>
-      </c>
-      <c r="K52" s="11" t="s">
+      <c r="J52" s="9">
+        <v>150</v>
+      </c>
+      <c r="K52" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3678,7 +3672,7 @@
       <c r="C53" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="11">
         <v>9</v>
       </c>
       <c r="E53" s="5">
@@ -3687,17 +3681,17 @@
       <c r="F53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="7">
         <v>30000</v>
       </c>
-      <c r="H53" s="13"/>
-      <c r="I53" s="8" t="s">
+      <c r="H53" s="12"/>
+      <c r="I53" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J53" s="10">
-        <v>60</v>
-      </c>
-      <c r="K53" s="11" t="s">
+      <c r="J53" s="9">
+        <v>200</v>
+      </c>
+      <c r="K53" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3721,17 +3715,17 @@
       <c r="F54" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="7">
         <v>10000</v>
       </c>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8" t="s">
+      <c r="H54" s="7"/>
+      <c r="I54" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="J54" s="10">
-        <v>60</v>
-      </c>
-      <c r="K54" s="11" t="s">
+      <c r="J54" s="9">
+        <v>300</v>
+      </c>
+      <c r="K54" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3755,15 +3749,15 @@
       <c r="F55" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="7">
         <v>1000</v>
       </c>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="10">
-        <v>60</v>
-      </c>
-      <c r="K55" s="11" t="s">
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="9">
+        <v>5</v>
+      </c>
+      <c r="K55" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3787,17 +3781,17 @@
       <c r="F56" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="7">
         <v>1100</v>
       </c>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8" t="s">
+      <c r="H56" s="7"/>
+      <c r="I56" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J56" s="10">
-        <v>60</v>
-      </c>
-      <c r="K56" s="11" t="s">
+      <c r="J56" s="9">
+        <v>10</v>
+      </c>
+      <c r="K56" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3821,17 +3815,17 @@
       <c r="F57" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="7">
         <v>2000</v>
       </c>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8" t="s">
+      <c r="H57" s="7"/>
+      <c r="I57" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J57" s="10">
-        <v>60</v>
-      </c>
-      <c r="K57" s="11" t="s">
+      <c r="J57" s="9">
+        <v>20</v>
+      </c>
+      <c r="K57" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3855,17 +3849,17 @@
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="7">
         <v>3000</v>
       </c>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8" t="s">
+      <c r="H58" s="7"/>
+      <c r="I58" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="J58" s="10">
-        <v>60</v>
-      </c>
-      <c r="K58" s="11" t="s">
+      <c r="J58" s="9">
+        <v>30</v>
+      </c>
+      <c r="K58" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3889,17 +3883,17 @@
       <c r="F59" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="7">
         <v>4500</v>
       </c>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8" t="s">
+      <c r="H59" s="7"/>
+      <c r="I59" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J59" s="10">
+      <c r="J59" s="9">
         <v>60</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3923,17 +3917,17 @@
       <c r="F60" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="7">
         <v>6000</v>
       </c>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8" t="s">
+      <c r="H60" s="7"/>
+      <c r="I60" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J60" s="10">
-        <v>60</v>
-      </c>
-      <c r="K60" s="11" t="s">
+      <c r="J60" s="9">
+        <v>80</v>
+      </c>
+      <c r="K60" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3957,17 +3951,17 @@
       <c r="F61" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="7">
         <v>9000</v>
       </c>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8" t="s">
+      <c r="H61" s="7"/>
+      <c r="I61" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="J61" s="10">
-        <v>60</v>
-      </c>
-      <c r="K61" s="11" t="s">
+      <c r="J61" s="9">
+        <v>120</v>
+      </c>
+      <c r="K61" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3991,17 +3985,17 @@
       <c r="F62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="7">
         <v>15000</v>
       </c>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8" t="s">
+      <c r="H62" s="7"/>
+      <c r="I62" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J62" s="10">
-        <v>60</v>
-      </c>
-      <c r="K62" s="11" t="s">
+      <c r="J62" s="9">
+        <v>150</v>
+      </c>
+      <c r="K62" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4016,7 +4010,7 @@
       <c r="C63" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="11">
         <v>9</v>
       </c>
       <c r="E63" s="5">
@@ -4025,17 +4019,17 @@
       <c r="F63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="7">
         <v>30000</v>
       </c>
-      <c r="H63" s="13"/>
-      <c r="I63" s="8" t="s">
+      <c r="H63" s="12"/>
+      <c r="I63" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J63" s="10">
-        <v>60</v>
-      </c>
-      <c r="K63" s="11" t="s">
+      <c r="J63" s="9">
+        <v>200</v>
+      </c>
+      <c r="K63" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4059,17 +4053,17 @@
       <c r="F64" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="7">
         <v>10000</v>
       </c>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8" t="s">
+      <c r="H64" s="7"/>
+      <c r="I64" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J64" s="10">
-        <v>60</v>
-      </c>
-      <c r="K64" s="11" t="s">
+      <c r="J64" s="9">
+        <v>300</v>
+      </c>
+      <c r="K64" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4093,15 +4087,15 @@
       <c r="F65" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G65" s="8">
+      <c r="G65" s="7">
         <v>1000</v>
       </c>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="10">
-        <v>60</v>
-      </c>
-      <c r="K65" s="11" t="s">
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="9">
+        <v>5</v>
+      </c>
+      <c r="K65" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4125,17 +4119,17 @@
       <c r="F66" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="7">
         <v>1100</v>
       </c>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8" t="s">
+      <c r="H66" s="7"/>
+      <c r="I66" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="J66" s="10">
-        <v>60</v>
-      </c>
-      <c r="K66" s="11" t="s">
+      <c r="J66" s="9">
+        <v>10</v>
+      </c>
+      <c r="K66" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4159,17 +4153,17 @@
       <c r="F67" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="7">
         <v>2000</v>
       </c>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8" t="s">
+      <c r="H67" s="7"/>
+      <c r="I67" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J67" s="10">
-        <v>60</v>
-      </c>
-      <c r="K67" s="11" t="s">
+      <c r="J67" s="9">
+        <v>20</v>
+      </c>
+      <c r="K67" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4193,17 +4187,17 @@
       <c r="F68" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="7">
         <v>3000</v>
       </c>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8" t="s">
+      <c r="H68" s="7"/>
+      <c r="I68" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J68" s="10">
-        <v>60</v>
-      </c>
-      <c r="K68" s="11" t="s">
+      <c r="J68" s="9">
+        <v>30</v>
+      </c>
+      <c r="K68" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4227,17 +4221,17 @@
       <c r="F69" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="7">
         <v>4500</v>
       </c>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8" t="s">
+      <c r="H69" s="7"/>
+      <c r="I69" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J69" s="10">
+      <c r="J69" s="9">
         <v>60</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4261,17 +4255,17 @@
       <c r="F70" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="7">
         <v>6000</v>
       </c>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8" t="s">
+      <c r="H70" s="7"/>
+      <c r="I70" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J70" s="10">
-        <v>60</v>
-      </c>
-      <c r="K70" s="11" t="s">
+      <c r="J70" s="9">
+        <v>80</v>
+      </c>
+      <c r="K70" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4295,17 +4289,17 @@
       <c r="F71" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="7">
         <v>9000</v>
       </c>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8" t="s">
+      <c r="H71" s="7"/>
+      <c r="I71" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J71" s="10">
-        <v>60</v>
-      </c>
-      <c r="K71" s="11" t="s">
+      <c r="J71" s="9">
+        <v>120</v>
+      </c>
+      <c r="K71" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4329,17 +4323,17 @@
       <c r="F72" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="7">
         <v>15000</v>
       </c>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8" t="s">
+      <c r="H72" s="7"/>
+      <c r="I72" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="10">
-        <v>60</v>
-      </c>
-      <c r="K72" s="11" t="s">
+      <c r="J72" s="9">
+        <v>150</v>
+      </c>
+      <c r="K72" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4354,7 +4348,7 @@
       <c r="C73" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="11">
         <v>9</v>
       </c>
       <c r="E73" s="5">
@@ -4363,17 +4357,17 @@
       <c r="F73" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="7">
         <v>30000</v>
       </c>
-      <c r="H73" s="13"/>
-      <c r="I73" s="8" t="s">
+      <c r="H73" s="12"/>
+      <c r="I73" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="J73" s="10">
-        <v>60</v>
-      </c>
-      <c r="K73" s="11" t="s">
+      <c r="J73" s="9">
+        <v>200</v>
+      </c>
+      <c r="K73" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4397,17 +4391,17 @@
       <c r="F74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="7">
         <v>10000</v>
       </c>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8" t="s">
+      <c r="H74" s="7"/>
+      <c r="I74" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J74" s="10">
-        <v>60</v>
-      </c>
-      <c r="K74" s="11" t="s">
+      <c r="J74" s="9">
+        <v>300</v>
+      </c>
+      <c r="K74" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4431,15 +4425,15 @@
       <c r="F75" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="7">
         <v>1000</v>
       </c>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="10">
-        <v>60</v>
-      </c>
-      <c r="K75" s="11" t="s">
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="9">
+        <v>5</v>
+      </c>
+      <c r="K75" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4463,17 +4457,17 @@
       <c r="F76" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="7">
         <v>1100</v>
       </c>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8" t="s">
+      <c r="H76" s="7"/>
+      <c r="I76" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J76" s="10">
-        <v>60</v>
-      </c>
-      <c r="K76" s="11" t="s">
+      <c r="J76" s="9">
+        <v>10</v>
+      </c>
+      <c r="K76" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4497,17 +4491,17 @@
       <c r="F77" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="7">
         <v>2000</v>
       </c>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8" t="s">
+      <c r="H77" s="7"/>
+      <c r="I77" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J77" s="10">
-        <v>60</v>
-      </c>
-      <c r="K77" s="11" t="s">
+      <c r="J77" s="9">
+        <v>20</v>
+      </c>
+      <c r="K77" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4531,17 +4525,17 @@
       <c r="F78" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="7">
         <v>3000</v>
       </c>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8" t="s">
+      <c r="H78" s="7"/>
+      <c r="I78" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J78" s="10">
-        <v>60</v>
-      </c>
-      <c r="K78" s="11" t="s">
+      <c r="J78" s="9">
+        <v>30</v>
+      </c>
+      <c r="K78" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4565,17 +4559,17 @@
       <c r="F79" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="7">
         <v>4500</v>
       </c>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8" t="s">
+      <c r="H79" s="7"/>
+      <c r="I79" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J79" s="10">
+      <c r="J79" s="9">
         <v>60</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4599,17 +4593,17 @@
       <c r="F80" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="7">
         <v>6000</v>
       </c>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8" t="s">
+      <c r="H80" s="7"/>
+      <c r="I80" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J80" s="10">
-        <v>60</v>
-      </c>
-      <c r="K80" s="11" t="s">
+      <c r="J80" s="9">
+        <v>80</v>
+      </c>
+      <c r="K80" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4633,17 +4627,17 @@
       <c r="F81" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="7">
         <v>9000</v>
       </c>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8" t="s">
+      <c r="H81" s="7"/>
+      <c r="I81" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J81" s="10">
-        <v>60</v>
-      </c>
-      <c r="K81" s="11" t="s">
+      <c r="J81" s="9">
+        <v>120</v>
+      </c>
+      <c r="K81" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4667,17 +4661,17 @@
       <c r="F82" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="7">
         <v>15000</v>
       </c>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8" t="s">
+      <c r="H82" s="7"/>
+      <c r="I82" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J82" s="10">
-        <v>60</v>
-      </c>
-      <c r="K82" s="11" t="s">
+      <c r="J82" s="9">
+        <v>150</v>
+      </c>
+      <c r="K82" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4692,7 +4686,7 @@
       <c r="C83" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="11">
         <v>9</v>
       </c>
       <c r="E83" s="5">
@@ -4701,17 +4695,17 @@
       <c r="F83" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="7">
         <v>30000</v>
       </c>
-      <c r="H83" s="13"/>
-      <c r="I83" s="8" t="s">
+      <c r="H83" s="12"/>
+      <c r="I83" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J83" s="10">
-        <v>60</v>
-      </c>
-      <c r="K83" s="11" t="s">
+      <c r="J83" s="9">
+        <v>200</v>
+      </c>
+      <c r="K83" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4735,17 +4729,17 @@
       <c r="F84" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="7">
         <v>10000</v>
       </c>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8" t="s">
+      <c r="H84" s="7"/>
+      <c r="I84" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J84" s="10">
-        <v>60</v>
-      </c>
-      <c r="K84" s="11" t="s">
+      <c r="J84" s="9">
+        <v>300</v>
+      </c>
+      <c r="K84" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4769,15 +4763,15 @@
       <c r="F85" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="7">
         <v>1000</v>
       </c>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="10">
-        <v>60</v>
-      </c>
-      <c r="K85" s="11" t="s">
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="9">
+        <v>5</v>
+      </c>
+      <c r="K85" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4801,17 +4795,17 @@
       <c r="F86" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="7">
         <v>1100</v>
       </c>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8" t="s">
+      <c r="H86" s="7"/>
+      <c r="I86" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="J86" s="10">
-        <v>60</v>
-      </c>
-      <c r="K86" s="11" t="s">
+      <c r="J86" s="9">
+        <v>10</v>
+      </c>
+      <c r="K86" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4835,17 +4829,17 @@
       <c r="F87" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G87" s="8">
+      <c r="G87" s="7">
         <v>2000</v>
       </c>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8" t="s">
+      <c r="H87" s="7"/>
+      <c r="I87" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="J87" s="10">
-        <v>60</v>
-      </c>
-      <c r="K87" s="11" t="s">
+      <c r="J87" s="9">
+        <v>20</v>
+      </c>
+      <c r="K87" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4869,17 +4863,17 @@
       <c r="F88" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G88" s="8">
+      <c r="G88" s="7">
         <v>3000</v>
       </c>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8" t="s">
+      <c r="H88" s="7"/>
+      <c r="I88" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="J88" s="10">
-        <v>60</v>
-      </c>
-      <c r="K88" s="11" t="s">
+      <c r="J88" s="9">
+        <v>30</v>
+      </c>
+      <c r="K88" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4903,17 +4897,17 @@
       <c r="F89" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G89" s="8">
+      <c r="G89" s="7">
         <v>4500</v>
       </c>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8" t="s">
+      <c r="H89" s="7"/>
+      <c r="I89" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="J89" s="10">
+      <c r="J89" s="9">
         <v>60</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4937,17 +4931,17 @@
       <c r="F90" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G90" s="8">
+      <c r="G90" s="7">
         <v>6000</v>
       </c>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8" t="s">
+      <c r="H90" s="7"/>
+      <c r="I90" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="J90" s="10">
-        <v>60</v>
-      </c>
-      <c r="K90" s="11" t="s">
+      <c r="J90" s="9">
+        <v>80</v>
+      </c>
+      <c r="K90" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4971,17 +4965,17 @@
       <c r="F91" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="8">
+      <c r="G91" s="7">
         <v>9000</v>
       </c>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8" t="s">
+      <c r="H91" s="7"/>
+      <c r="I91" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J91" s="10">
-        <v>60</v>
-      </c>
-      <c r="K91" s="11" t="s">
+      <c r="J91" s="9">
+        <v>120</v>
+      </c>
+      <c r="K91" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5005,17 +4999,17 @@
       <c r="F92" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="7">
         <v>15000</v>
       </c>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8" t="s">
+      <c r="H92" s="7"/>
+      <c r="I92" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="J92" s="10">
-        <v>60</v>
-      </c>
-      <c r="K92" s="11" t="s">
+      <c r="J92" s="9">
+        <v>150</v>
+      </c>
+      <c r="K92" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5030,7 +5024,7 @@
       <c r="C93" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="11">
         <v>9</v>
       </c>
       <c r="E93" s="5">
@@ -5039,17 +5033,17 @@
       <c r="F93" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="7">
         <v>30000</v>
       </c>
-      <c r="H93" s="13"/>
-      <c r="I93" s="8" t="s">
+      <c r="H93" s="12"/>
+      <c r="I93" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J93" s="10">
-        <v>60</v>
-      </c>
-      <c r="K93" s="11" t="s">
+      <c r="J93" s="9">
+        <v>200</v>
+      </c>
+      <c r="K93" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5073,17 +5067,17 @@
       <c r="F94" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="7">
         <v>10000</v>
       </c>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8" t="s">
+      <c r="H94" s="7"/>
+      <c r="I94" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J94" s="10">
-        <v>60</v>
-      </c>
-      <c r="K94" s="11" t="s">
+      <c r="J94" s="9">
+        <v>300</v>
+      </c>
+      <c r="K94" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5107,15 +5101,15 @@
       <c r="F95" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G95" s="8">
+      <c r="G95" s="7">
         <v>1000</v>
       </c>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="10">
-        <v>60</v>
-      </c>
-      <c r="K95" s="11" t="s">
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="9">
+        <v>5</v>
+      </c>
+      <c r="K95" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5139,17 +5133,17 @@
       <c r="F96" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G96" s="8">
+      <c r="G96" s="7">
         <v>1100</v>
       </c>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8" t="s">
+      <c r="H96" s="7"/>
+      <c r="I96" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="J96" s="10">
-        <v>60</v>
-      </c>
-      <c r="K96" s="11" t="s">
+      <c r="J96" s="9">
+        <v>10</v>
+      </c>
+      <c r="K96" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5173,17 +5167,17 @@
       <c r="F97" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G97" s="8">
+      <c r="G97" s="7">
         <v>2000</v>
       </c>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8" t="s">
+      <c r="H97" s="7"/>
+      <c r="I97" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J97" s="10">
-        <v>60</v>
-      </c>
-      <c r="K97" s="11" t="s">
+      <c r="J97" s="9">
+        <v>20</v>
+      </c>
+      <c r="K97" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5207,17 +5201,17 @@
       <c r="F98" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G98" s="8">
+      <c r="G98" s="7">
         <v>3000</v>
       </c>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8" t="s">
+      <c r="H98" s="7"/>
+      <c r="I98" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J98" s="10">
-        <v>60</v>
-      </c>
-      <c r="K98" s="11" t="s">
+      <c r="J98" s="9">
+        <v>30</v>
+      </c>
+      <c r="K98" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5241,17 +5235,17 @@
       <c r="F99" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G99" s="8">
+      <c r="G99" s="7">
         <v>4500</v>
       </c>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8" t="s">
+      <c r="H99" s="7"/>
+      <c r="I99" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J99" s="10">
+      <c r="J99" s="9">
         <v>60</v>
       </c>
-      <c r="K99" s="11" t="s">
+      <c r="K99" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5275,17 +5269,17 @@
       <c r="F100" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G100" s="8">
+      <c r="G100" s="7">
         <v>6000</v>
       </c>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8" t="s">
+      <c r="H100" s="7"/>
+      <c r="I100" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="J100" s="10">
-        <v>60</v>
-      </c>
-      <c r="K100" s="11" t="s">
+      <c r="J100" s="9">
+        <v>80</v>
+      </c>
+      <c r="K100" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5309,17 +5303,17 @@
       <c r="F101" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G101" s="8">
+      <c r="G101" s="7">
         <v>9000</v>
       </c>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8" t="s">
+      <c r="H101" s="7"/>
+      <c r="I101" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J101" s="10">
-        <v>60</v>
-      </c>
-      <c r="K101" s="11" t="s">
+      <c r="J101" s="9">
+        <v>120</v>
+      </c>
+      <c r="K101" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5343,17 +5337,17 @@
       <c r="F102" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G102" s="8">
+      <c r="G102" s="7">
         <v>15000</v>
       </c>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8" t="s">
+      <c r="H102" s="7"/>
+      <c r="I102" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="J102" s="10">
-        <v>60</v>
-      </c>
-      <c r="K102" s="11" t="s">
+      <c r="J102" s="9">
+        <v>150</v>
+      </c>
+      <c r="K102" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5368,7 +5362,7 @@
       <c r="C103" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="11">
         <v>9</v>
       </c>
       <c r="E103" s="5">
@@ -5377,17 +5371,17 @@
       <c r="F103" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G103" s="8">
+      <c r="G103" s="7">
         <v>30000</v>
       </c>
-      <c r="H103" s="13"/>
-      <c r="I103" s="8" t="s">
+      <c r="H103" s="12"/>
+      <c r="I103" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J103" s="10">
-        <v>60</v>
-      </c>
-      <c r="K103" s="11" t="s">
+      <c r="J103" s="9">
+        <v>200</v>
+      </c>
+      <c r="K103" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5411,17 +5405,17 @@
       <c r="F104" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G104" s="8">
+      <c r="G104" s="7">
         <v>10000</v>
       </c>
-      <c r="H104" s="8"/>
-      <c r="I104" s="8" t="s">
+      <c r="H104" s="7"/>
+      <c r="I104" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J104" s="10">
-        <v>60</v>
-      </c>
-      <c r="K104" s="11" t="s">
+      <c r="J104" s="9">
+        <v>300</v>
+      </c>
+      <c r="K104" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5445,15 +5439,15 @@
       <c r="F105" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G105" s="8">
+      <c r="G105" s="7">
         <v>1000</v>
       </c>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="10">
-        <v>60</v>
-      </c>
-      <c r="K105" s="11" t="s">
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="9">
+        <v>5</v>
+      </c>
+      <c r="K105" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5477,17 +5471,17 @@
       <c r="F106" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G106" s="8">
+      <c r="G106" s="7">
         <v>1100</v>
       </c>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8" t="s">
+      <c r="H106" s="7"/>
+      <c r="I106" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="J106" s="10">
-        <v>60</v>
-      </c>
-      <c r="K106" s="11" t="s">
+      <c r="J106" s="9">
+        <v>10</v>
+      </c>
+      <c r="K106" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5511,17 +5505,17 @@
       <c r="F107" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G107" s="8">
+      <c r="G107" s="7">
         <v>2000</v>
       </c>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8" t="s">
+      <c r="H107" s="7"/>
+      <c r="I107" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J107" s="10">
-        <v>60</v>
-      </c>
-      <c r="K107" s="11" t="s">
+      <c r="J107" s="9">
+        <v>20</v>
+      </c>
+      <c r="K107" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5545,17 +5539,17 @@
       <c r="F108" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G108" s="8">
+      <c r="G108" s="7">
         <v>3000</v>
       </c>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8" t="s">
+      <c r="H108" s="7"/>
+      <c r="I108" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J108" s="10">
-        <v>60</v>
-      </c>
-      <c r="K108" s="11" t="s">
+      <c r="J108" s="9">
+        <v>30</v>
+      </c>
+      <c r="K108" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5579,17 +5573,17 @@
       <c r="F109" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G109" s="8">
+      <c r="G109" s="7">
         <v>4500</v>
       </c>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8" t="s">
+      <c r="H109" s="7"/>
+      <c r="I109" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J109" s="10">
+      <c r="J109" s="9">
         <v>60</v>
       </c>
-      <c r="K109" s="11" t="s">
+      <c r="K109" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5613,17 +5607,17 @@
       <c r="F110" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G110" s="8">
+      <c r="G110" s="7">
         <v>6000</v>
       </c>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8" t="s">
+      <c r="H110" s="7"/>
+      <c r="I110" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="J110" s="10">
-        <v>60</v>
-      </c>
-      <c r="K110" s="11" t="s">
+      <c r="J110" s="9">
+        <v>80</v>
+      </c>
+      <c r="K110" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5647,17 +5641,17 @@
       <c r="F111" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G111" s="8">
+      <c r="G111" s="7">
         <v>9000</v>
       </c>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8" t="s">
+      <c r="H111" s="7"/>
+      <c r="I111" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J111" s="10">
-        <v>60</v>
-      </c>
-      <c r="K111" s="11" t="s">
+      <c r="J111" s="9">
+        <v>120</v>
+      </c>
+      <c r="K111" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5681,17 +5675,17 @@
       <c r="F112" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G112" s="8">
+      <c r="G112" s="7">
         <v>15000</v>
       </c>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8" t="s">
+      <c r="H112" s="7"/>
+      <c r="I112" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J112" s="10">
-        <v>60</v>
-      </c>
-      <c r="K112" s="11" t="s">
+      <c r="J112" s="9">
+        <v>150</v>
+      </c>
+      <c r="K112" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5706,7 +5700,7 @@
       <c r="C113" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="11">
         <v>9</v>
       </c>
       <c r="E113" s="5">
@@ -5715,17 +5709,17 @@
       <c r="F113" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G113" s="8">
+      <c r="G113" s="7">
         <v>30000</v>
       </c>
-      <c r="H113" s="13"/>
-      <c r="I113" s="8" t="s">
+      <c r="H113" s="12"/>
+      <c r="I113" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="J113" s="10">
-        <v>60</v>
-      </c>
-      <c r="K113" s="11" t="s">
+      <c r="J113" s="9">
+        <v>200</v>
+      </c>
+      <c r="K113" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5749,17 +5743,17 @@
       <c r="F114" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G114" s="8">
+      <c r="G114" s="7">
         <v>10000</v>
       </c>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8" t="s">
+      <c r="H114" s="7"/>
+      <c r="I114" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="J114" s="10">
-        <v>60</v>
-      </c>
-      <c r="K114" s="11" t="s">
+      <c r="J114" s="9">
+        <v>300</v>
+      </c>
+      <c r="K114" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5783,15 +5777,15 @@
       <c r="F115" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G115" s="8">
+      <c r="G115" s="7">
         <v>1000</v>
       </c>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="10">
-        <v>60</v>
-      </c>
-      <c r="K115" s="11" t="s">
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="9">
+        <v>5</v>
+      </c>
+      <c r="K115" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5815,17 +5809,17 @@
       <c r="F116" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G116" s="8">
+      <c r="G116" s="7">
         <v>1100</v>
       </c>
-      <c r="H116" s="8"/>
-      <c r="I116" s="8" t="s">
+      <c r="H116" s="7"/>
+      <c r="I116" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="J116" s="10">
-        <v>60</v>
-      </c>
-      <c r="K116" s="11" t="s">
+      <c r="J116" s="9">
+        <v>10</v>
+      </c>
+      <c r="K116" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5849,17 +5843,17 @@
       <c r="F117" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G117" s="8">
+      <c r="G117" s="7">
         <v>2000</v>
       </c>
-      <c r="H117" s="8"/>
-      <c r="I117" s="8" t="s">
+      <c r="H117" s="7"/>
+      <c r="I117" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J117" s="10">
-        <v>60</v>
-      </c>
-      <c r="K117" s="11" t="s">
+      <c r="J117" s="9">
+        <v>20</v>
+      </c>
+      <c r="K117" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5883,17 +5877,17 @@
       <c r="F118" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G118" s="8">
+      <c r="G118" s="7">
         <v>3000</v>
       </c>
-      <c r="H118" s="8"/>
-      <c r="I118" s="8" t="s">
+      <c r="H118" s="7"/>
+      <c r="I118" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="J118" s="10">
-        <v>60</v>
-      </c>
-      <c r="K118" s="11" t="s">
+      <c r="J118" s="9">
+        <v>30</v>
+      </c>
+      <c r="K118" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5917,17 +5911,17 @@
       <c r="F119" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G119" s="8">
+      <c r="G119" s="7">
         <v>4500</v>
       </c>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8" t="s">
+      <c r="H119" s="7"/>
+      <c r="I119" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J119" s="10">
+      <c r="J119" s="9">
         <v>60</v>
       </c>
-      <c r="K119" s="11" t="s">
+      <c r="K119" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5951,17 +5945,17 @@
       <c r="F120" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G120" s="8">
+      <c r="G120" s="7">
         <v>6000</v>
       </c>
-      <c r="H120" s="8"/>
-      <c r="I120" s="8" t="s">
+      <c r="H120" s="7"/>
+      <c r="I120" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J120" s="10">
-        <v>60</v>
-      </c>
-      <c r="K120" s="11" t="s">
+      <c r="J120" s="9">
+        <v>80</v>
+      </c>
+      <c r="K120" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5985,17 +5979,17 @@
       <c r="F121" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G121" s="8">
+      <c r="G121" s="7">
         <v>9000</v>
       </c>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8" t="s">
+      <c r="H121" s="7"/>
+      <c r="I121" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J121" s="10">
-        <v>60</v>
-      </c>
-      <c r="K121" s="11" t="s">
+      <c r="J121" s="9">
+        <v>120</v>
+      </c>
+      <c r="K121" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6019,17 +6013,17 @@
       <c r="F122" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G122" s="8">
+      <c r="G122" s="7">
         <v>15000</v>
       </c>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8" t="s">
+      <c r="H122" s="7"/>
+      <c r="I122" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="J122" s="10">
-        <v>60</v>
-      </c>
-      <c r="K122" s="11" t="s">
+      <c r="J122" s="9">
+        <v>150</v>
+      </c>
+      <c r="K122" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6044,7 +6038,7 @@
       <c r="C123" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D123" s="12">
+      <c r="D123" s="11">
         <v>9</v>
       </c>
       <c r="E123" s="5">
@@ -6053,17 +6047,17 @@
       <c r="F123" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G123" s="8">
+      <c r="G123" s="7">
         <v>30000</v>
       </c>
-      <c r="H123" s="13"/>
-      <c r="I123" s="8" t="s">
+      <c r="H123" s="12"/>
+      <c r="I123" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J123" s="10">
-        <v>60</v>
-      </c>
-      <c r="K123" s="11" t="s">
+      <c r="J123" s="9">
+        <v>200</v>
+      </c>
+      <c r="K123" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6087,17 +6081,17 @@
       <c r="F124" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G124" s="8">
+      <c r="G124" s="7">
         <v>10000</v>
       </c>
-      <c r="H124" s="8"/>
-      <c r="I124" s="8" t="s">
+      <c r="H124" s="7"/>
+      <c r="I124" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="J124" s="10">
-        <v>60</v>
-      </c>
-      <c r="K124" s="11" t="s">
+      <c r="J124" s="9">
+        <v>300</v>
+      </c>
+      <c r="K124" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6121,15 +6115,15 @@
       <c r="F125" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G125" s="8">
+      <c r="G125" s="7">
         <v>1000</v>
       </c>
-      <c r="H125" s="8"/>
-      <c r="I125" s="8"/>
-      <c r="J125" s="10">
-        <v>60</v>
-      </c>
-      <c r="K125" s="11" t="s">
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="9">
+        <v>5</v>
+      </c>
+      <c r="K125" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6153,17 +6147,17 @@
       <c r="F126" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G126" s="8">
+      <c r="G126" s="7">
         <v>1100</v>
       </c>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8" t="s">
+      <c r="H126" s="7"/>
+      <c r="I126" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="J126" s="10">
-        <v>60</v>
-      </c>
-      <c r="K126" s="11" t="s">
+      <c r="J126" s="9">
+        <v>10</v>
+      </c>
+      <c r="K126" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6187,17 +6181,17 @@
       <c r="F127" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G127" s="8">
+      <c r="G127" s="7">
         <v>2000</v>
       </c>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8" t="s">
+      <c r="H127" s="7"/>
+      <c r="I127" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="J127" s="10">
-        <v>60</v>
-      </c>
-      <c r="K127" s="11" t="s">
+      <c r="J127" s="9">
+        <v>20</v>
+      </c>
+      <c r="K127" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6221,17 +6215,17 @@
       <c r="F128" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G128" s="8">
+      <c r="G128" s="7">
         <v>3000</v>
       </c>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8" t="s">
+      <c r="H128" s="7"/>
+      <c r="I128" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="J128" s="10">
-        <v>60</v>
-      </c>
-      <c r="K128" s="11" t="s">
+      <c r="J128" s="9">
+        <v>30</v>
+      </c>
+      <c r="K128" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6255,17 +6249,17 @@
       <c r="F129" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G129" s="8">
+      <c r="G129" s="7">
         <v>4500</v>
       </c>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8" t="s">
+      <c r="H129" s="7"/>
+      <c r="I129" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J129" s="10">
+      <c r="J129" s="9">
         <v>60</v>
       </c>
-      <c r="K129" s="11" t="s">
+      <c r="K129" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6289,17 +6283,17 @@
       <c r="F130" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G130" s="8">
+      <c r="G130" s="7">
         <v>6000</v>
       </c>
-      <c r="H130" s="8"/>
-      <c r="I130" s="8" t="s">
+      <c r="H130" s="7"/>
+      <c r="I130" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="J130" s="10">
-        <v>60</v>
-      </c>
-      <c r="K130" s="11" t="s">
+      <c r="J130" s="9">
+        <v>80</v>
+      </c>
+      <c r="K130" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6323,17 +6317,17 @@
       <c r="F131" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G131" s="8">
+      <c r="G131" s="7">
         <v>9000</v>
       </c>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8" t="s">
+      <c r="H131" s="7"/>
+      <c r="I131" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="J131" s="10">
-        <v>60</v>
-      </c>
-      <c r="K131" s="11" t="s">
+      <c r="J131" s="9">
+        <v>120</v>
+      </c>
+      <c r="K131" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6357,17 +6351,17 @@
       <c r="F132" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G132" s="8">
+      <c r="G132" s="7">
         <v>15000</v>
       </c>
-      <c r="H132" s="8"/>
-      <c r="I132" s="8" t="s">
+      <c r="H132" s="7"/>
+      <c r="I132" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="J132" s="10">
-        <v>60</v>
-      </c>
-      <c r="K132" s="11" t="s">
+      <c r="J132" s="9">
+        <v>150</v>
+      </c>
+      <c r="K132" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6382,7 +6376,7 @@
       <c r="C133" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D133" s="12">
+      <c r="D133" s="11">
         <v>9</v>
       </c>
       <c r="E133" s="5">
@@ -6391,17 +6385,17 @@
       <c r="F133" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G133" s="8">
+      <c r="G133" s="7">
         <v>30000</v>
       </c>
-      <c r="H133" s="13"/>
-      <c r="I133" s="8" t="s">
+      <c r="H133" s="12"/>
+      <c r="I133" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J133" s="10">
-        <v>60</v>
-      </c>
-      <c r="K133" s="11" t="s">
+      <c r="J133" s="9">
+        <v>200</v>
+      </c>
+      <c r="K133" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6425,17 +6419,17 @@
       <c r="F134" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G134" s="8">
+      <c r="G134" s="7">
         <v>10000</v>
       </c>
-      <c r="H134" s="8"/>
-      <c r="I134" s="8" t="s">
+      <c r="H134" s="7"/>
+      <c r="I134" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J134" s="10">
-        <v>60</v>
-      </c>
-      <c r="K134" s="11" t="s">
+      <c r="J134" s="9">
+        <v>300</v>
+      </c>
+      <c r="K134" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6459,15 +6453,15 @@
       <c r="F135" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G135" s="8">
+      <c r="G135" s="7">
         <v>15</v>
       </c>
-      <c r="H135" s="8"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="10">
-        <v>60</v>
-      </c>
-      <c r="K135" s="11" t="s">
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="9">
+        <v>5</v>
+      </c>
+      <c r="K135" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6491,17 +6485,17 @@
       <c r="F136" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G136" s="8">
+      <c r="G136" s="7">
         <v>25</v>
       </c>
-      <c r="H136" s="8"/>
-      <c r="I136" s="8" t="s">
+      <c r="H136" s="7"/>
+      <c r="I136" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="J136" s="10">
-        <v>60</v>
-      </c>
-      <c r="K136" s="11" t="s">
+      <c r="J136" s="9">
+        <v>10</v>
+      </c>
+      <c r="K136" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6525,17 +6519,17 @@
       <c r="F137" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G137" s="8">
+      <c r="G137" s="7">
         <v>35</v>
       </c>
-      <c r="H137" s="8"/>
-      <c r="I137" s="8" t="s">
+      <c r="H137" s="7"/>
+      <c r="I137" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="J137" s="10">
-        <v>60</v>
-      </c>
-      <c r="K137" s="11" t="s">
+      <c r="J137" s="9">
+        <v>20</v>
+      </c>
+      <c r="K137" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6559,17 +6553,17 @@
       <c r="F138" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G138" s="8">
+      <c r="G138" s="7">
         <v>45</v>
       </c>
-      <c r="H138" s="8"/>
-      <c r="I138" s="8" t="s">
+      <c r="H138" s="7"/>
+      <c r="I138" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="J138" s="10">
-        <v>60</v>
-      </c>
-      <c r="K138" s="11" t="s">
+      <c r="J138" s="9">
+        <v>30</v>
+      </c>
+      <c r="K138" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6593,17 +6587,17 @@
       <c r="F139" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G139" s="8">
+      <c r="G139" s="7">
         <v>55</v>
       </c>
-      <c r="H139" s="8"/>
-      <c r="I139" s="8" t="s">
+      <c r="H139" s="7"/>
+      <c r="I139" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="J139" s="10">
+      <c r="J139" s="9">
         <v>60</v>
       </c>
-      <c r="K139" s="11" t="s">
+      <c r="K139" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6627,17 +6621,17 @@
       <c r="F140" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G140" s="8">
+      <c r="G140" s="7">
         <v>65</v>
       </c>
-      <c r="H140" s="8"/>
-      <c r="I140" s="8" t="s">
+      <c r="H140" s="7"/>
+      <c r="I140" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="J140" s="10">
-        <v>60</v>
-      </c>
-      <c r="K140" s="11" t="s">
+      <c r="J140" s="9">
+        <v>80</v>
+      </c>
+      <c r="K140" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6661,17 +6655,17 @@
       <c r="F141" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G141" s="8">
+      <c r="G141" s="7">
         <v>75</v>
       </c>
-      <c r="H141" s="8"/>
-      <c r="I141" s="8" t="s">
+      <c r="H141" s="7"/>
+      <c r="I141" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="J141" s="10">
-        <v>60</v>
-      </c>
-      <c r="K141" s="11" t="s">
+      <c r="J141" s="9">
+        <v>120</v>
+      </c>
+      <c r="K141" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6695,17 +6689,17 @@
       <c r="F142" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G142" s="8">
+      <c r="G142" s="7">
         <v>85</v>
       </c>
-      <c r="H142" s="8"/>
-      <c r="I142" s="8" t="s">
+      <c r="H142" s="7"/>
+      <c r="I142" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="J142" s="10">
-        <v>60</v>
-      </c>
-      <c r="K142" s="11" t="s">
+      <c r="J142" s="9">
+        <v>150</v>
+      </c>
+      <c r="K142" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6720,7 +6714,7 @@
       <c r="C143" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D143" s="12">
+      <c r="D143" s="11">
         <v>9</v>
       </c>
       <c r="E143" s="5">
@@ -6729,17 +6723,17 @@
       <c r="F143" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G143" s="8">
+      <c r="G143" s="7">
         <v>95</v>
       </c>
-      <c r="H143" s="13"/>
-      <c r="I143" s="8" t="s">
+      <c r="H143" s="12"/>
+      <c r="I143" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="J143" s="10">
-        <v>60</v>
-      </c>
-      <c r="K143" s="11" t="s">
+      <c r="J143" s="9">
+        <v>200</v>
+      </c>
+      <c r="K143" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6763,17 +6757,17 @@
       <c r="F144" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G144" s="8">
+      <c r="G144" s="7">
         <v>105</v>
       </c>
-      <c r="H144" s="8"/>
-      <c r="I144" s="8" t="s">
+      <c r="H144" s="7"/>
+      <c r="I144" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="J144" s="10">
-        <v>60</v>
-      </c>
-      <c r="K144" s="11" t="s">
+      <c r="J144" s="9">
+        <v>300</v>
+      </c>
+      <c r="K144" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6791,19 +6785,19 @@
       <c r="D145" s="5">
         <v>1</v>
       </c>
-      <c r="E145" s="14"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G145" s="8">
+      <c r="G145" s="7">
         <v>1000</v>
       </c>
-      <c r="H145" s="14"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="10">
-        <v>60</v>
-      </c>
-      <c r="K145" s="11" t="s">
+      <c r="H145" s="13"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="9">
+        <v>5</v>
+      </c>
+      <c r="K145" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6821,19 +6815,19 @@
       <c r="D146" s="5">
         <v>2</v>
       </c>
-      <c r="E146" s="14"/>
+      <c r="E146" s="13"/>
       <c r="F146" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G146" s="8">
+      <c r="G146" s="7">
         <v>2000</v>
       </c>
-      <c r="H146" s="14"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="10">
-        <v>60</v>
-      </c>
-      <c r="K146" s="11" t="s">
+      <c r="H146" s="13"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="9">
+        <v>10</v>
+      </c>
+      <c r="K146" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6851,19 +6845,19 @@
       <c r="D147" s="5">
         <v>3</v>
       </c>
-      <c r="E147" s="14"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G147" s="8">
+      <c r="G147" s="7">
         <v>3000</v>
       </c>
-      <c r="H147" s="14"/>
-      <c r="I147" s="15"/>
-      <c r="J147" s="10">
-        <v>60</v>
-      </c>
-      <c r="K147" s="11" t="s">
+      <c r="H147" s="13"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="9">
+        <v>20</v>
+      </c>
+      <c r="K147" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6881,19 +6875,19 @@
       <c r="D148" s="5">
         <v>4</v>
       </c>
-      <c r="E148" s="14"/>
+      <c r="E148" s="13"/>
       <c r="F148" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G148" s="8">
+      <c r="G148" s="7">
         <v>4000</v>
       </c>
-      <c r="H148" s="14"/>
-      <c r="I148" s="15"/>
-      <c r="J148" s="10">
-        <v>60</v>
-      </c>
-      <c r="K148" s="11" t="s">
+      <c r="H148" s="13"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="9">
+        <v>30</v>
+      </c>
+      <c r="K148" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6911,19 +6905,19 @@
       <c r="D149" s="5">
         <v>5</v>
       </c>
-      <c r="E149" s="14"/>
+      <c r="E149" s="13"/>
       <c r="F149" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G149" s="8">
+      <c r="G149" s="7">
         <v>5000</v>
       </c>
-      <c r="H149" s="14"/>
-      <c r="I149" s="15"/>
-      <c r="J149" s="10">
+      <c r="H149" s="13"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="9">
         <v>60</v>
       </c>
-      <c r="K149" s="11" t="s">
+      <c r="K149" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6941,19 +6935,19 @@
       <c r="D150" s="5">
         <v>6</v>
       </c>
-      <c r="E150" s="14"/>
+      <c r="E150" s="13"/>
       <c r="F150" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G150" s="8">
+      <c r="G150" s="7">
         <v>6000</v>
       </c>
-      <c r="H150" s="14"/>
-      <c r="I150" s="15"/>
-      <c r="J150" s="10">
-        <v>60</v>
-      </c>
-      <c r="K150" s="11" t="s">
+      <c r="H150" s="13"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="9">
+        <v>80</v>
+      </c>
+      <c r="K150" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6971,19 +6965,19 @@
       <c r="D151" s="5">
         <v>7</v>
       </c>
-      <c r="E151" s="14"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G151" s="8">
+      <c r="G151" s="7">
         <v>7000</v>
       </c>
-      <c r="H151" s="14"/>
-      <c r="I151" s="15"/>
-      <c r="J151" s="10">
-        <v>60</v>
-      </c>
-      <c r="K151" s="11" t="s">
+      <c r="H151" s="13"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="9">
+        <v>120</v>
+      </c>
+      <c r="K151" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7001,19 +6995,19 @@
       <c r="D152" s="5">
         <v>8</v>
       </c>
-      <c r="E152" s="14"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G152" s="8">
+      <c r="G152" s="7">
         <v>8000</v>
       </c>
-      <c r="H152" s="14"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="10">
-        <v>60</v>
-      </c>
-      <c r="K152" s="11" t="s">
+      <c r="H152" s="13"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="9">
+        <v>150</v>
+      </c>
+      <c r="K152" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7028,22 +7022,22 @@
       <c r="C153" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D153" s="12">
+      <c r="D153" s="11">
         <v>9</v>
       </c>
-      <c r="E153" s="14"/>
+      <c r="E153" s="13"/>
       <c r="F153" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G153" s="8">
+      <c r="G153" s="7">
         <v>9000</v>
       </c>
-      <c r="H153" s="14"/>
-      <c r="I153" s="15"/>
-      <c r="J153" s="10">
-        <v>60</v>
-      </c>
-      <c r="K153" s="11" t="s">
+      <c r="H153" s="13"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="9">
+        <v>200</v>
+      </c>
+      <c r="K153" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7061,19 +7055,19 @@
       <c r="D154" s="5">
         <v>10</v>
       </c>
-      <c r="E154" s="14"/>
+      <c r="E154" s="13"/>
       <c r="F154" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G154" s="8">
+      <c r="G154" s="7">
         <v>10000</v>
       </c>
-      <c r="H154" s="14"/>
-      <c r="I154" s="15"/>
-      <c r="J154" s="10">
-        <v>60</v>
-      </c>
-      <c r="K154" s="11" t="s">
+      <c r="H154" s="13"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="9">
+        <v>300</v>
+      </c>
+      <c r="K154" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7091,23 +7085,23 @@
       <c r="D155" s="5">
         <v>1</v>
       </c>
-      <c r="E155" s="14"/>
+      <c r="E155" s="13"/>
       <c r="F155" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G155" s="8">
+      <c r="G155" s="7">
         <v>1</v>
       </c>
-      <c r="H155" s="8">
+      <c r="H155" s="7">
         <v>4030001</v>
       </c>
-      <c r="I155" s="8">
+      <c r="I155" s="7">
         <v>100300</v>
       </c>
-      <c r="J155" s="10">
+      <c r="J155" s="9">
         <v>5</v>
       </c>
-      <c r="K155" s="11" t="s">
+      <c r="K155" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7125,23 +7119,23 @@
       <c r="D156" s="5">
         <v>2</v>
       </c>
-      <c r="E156" s="14"/>
+      <c r="E156" s="13"/>
       <c r="F156" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G156" s="8">
+      <c r="G156" s="7">
         <v>2</v>
       </c>
-      <c r="H156" s="8">
+      <c r="H156" s="7">
         <v>4030001</v>
       </c>
-      <c r="I156" s="15">
+      <c r="I156" s="7">
         <v>103400</v>
       </c>
-      <c r="J156" s="10">
+      <c r="J156" s="9">
         <v>10</v>
       </c>
-      <c r="K156" s="11" t="s">
+      <c r="K156" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7159,23 +7153,23 @@
       <c r="D157" s="5">
         <v>3</v>
       </c>
-      <c r="E157" s="14"/>
+      <c r="E157" s="13"/>
       <c r="F157" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G157" s="8">
+      <c r="G157" s="7">
         <v>3</v>
       </c>
-      <c r="H157" s="8">
+      <c r="H157" s="7">
         <v>4030001</v>
       </c>
-      <c r="I157" s="15">
-        <v>103500</v>
-      </c>
-      <c r="J157" s="10">
+      <c r="I157" s="7">
+        <v>103401</v>
+      </c>
+      <c r="J157" s="9">
         <v>20</v>
       </c>
-      <c r="K157" s="11" t="s">
+      <c r="K157" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7193,23 +7187,23 @@
       <c r="D158" s="5">
         <v>4</v>
       </c>
-      <c r="E158" s="14"/>
+      <c r="E158" s="13"/>
       <c r="F158" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G158" s="8">
+      <c r="G158" s="7">
         <v>4</v>
       </c>
-      <c r="H158" s="8">
+      <c r="H158" s="7">
         <v>4030001</v>
       </c>
-      <c r="I158" s="15">
-        <v>101700</v>
-      </c>
-      <c r="J158" s="10">
+      <c r="I158" s="7">
+        <v>103500</v>
+      </c>
+      <c r="J158" s="9">
         <v>30</v>
       </c>
-      <c r="K158" s="11" t="s">
+      <c r="K158" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7227,23 +7221,23 @@
       <c r="D159" s="5">
         <v>5</v>
       </c>
-      <c r="E159" s="14"/>
+      <c r="E159" s="13"/>
       <c r="F159" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G159" s="8">
+      <c r="G159" s="7">
         <v>5</v>
       </c>
-      <c r="H159" s="8">
+      <c r="H159" s="7">
         <v>4030001</v>
       </c>
-      <c r="I159" s="15">
-        <v>101800</v>
-      </c>
-      <c r="J159" s="10">
+      <c r="I159" s="7">
+        <v>103501</v>
+      </c>
+      <c r="J159" s="9">
         <v>60</v>
       </c>
-      <c r="K159" s="11" t="s">
+      <c r="K159" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7261,23 +7255,23 @@
       <c r="D160" s="5">
         <v>6</v>
       </c>
-      <c r="E160" s="14"/>
+      <c r="E160" s="13"/>
       <c r="F160" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G160" s="8">
+      <c r="G160" s="7">
         <v>6</v>
       </c>
-      <c r="H160" s="8">
+      <c r="H160" s="7">
         <v>4030001</v>
       </c>
-      <c r="I160" s="15">
-        <v>102100</v>
-      </c>
-      <c r="J160" s="10">
+      <c r="I160" s="7">
+        <v>101400</v>
+      </c>
+      <c r="J160" s="9">
         <v>80</v>
       </c>
-      <c r="K160" s="11" t="s">
+      <c r="K160" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7295,23 +7289,23 @@
       <c r="D161" s="5">
         <v>7</v>
       </c>
-      <c r="E161" s="14"/>
+      <c r="E161" s="13"/>
       <c r="F161" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G161" s="8">
+      <c r="G161" s="7">
         <v>7</v>
       </c>
-      <c r="H161" s="8">
+      <c r="H161" s="7">
         <v>4030001</v>
       </c>
-      <c r="I161" s="15">
-        <v>100700</v>
-      </c>
-      <c r="J161" s="10">
+      <c r="I161" s="7">
+        <v>103700</v>
+      </c>
+      <c r="J161" s="9">
         <v>120</v>
       </c>
-      <c r="K161" s="11" t="s">
+      <c r="K161" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7329,23 +7323,23 @@
       <c r="D162" s="5">
         <v>8</v>
       </c>
-      <c r="E162" s="14"/>
+      <c r="E162" s="13"/>
       <c r="F162" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G162" s="8">
+      <c r="G162" s="7">
         <v>8</v>
       </c>
-      <c r="H162" s="8">
+      <c r="H162" s="7">
         <v>4030001</v>
       </c>
-      <c r="I162" s="15">
-        <v>101200</v>
-      </c>
-      <c r="J162" s="10">
+      <c r="I162" s="7">
+        <v>103600</v>
+      </c>
+      <c r="J162" s="9">
         <v>150</v>
       </c>
-      <c r="K162" s="11" t="s">
+      <c r="K162" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7360,26 +7354,26 @@
       <c r="C163" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D163" s="12">
+      <c r="D163" s="11">
         <v>9</v>
       </c>
-      <c r="E163" s="14"/>
+      <c r="E163" s="13"/>
       <c r="F163" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G163" s="8">
+      <c r="G163" s="7">
         <v>9</v>
       </c>
-      <c r="H163" s="8">
+      <c r="H163" s="7">
         <v>4030001</v>
       </c>
-      <c r="I163" s="15">
-        <v>101400</v>
-      </c>
-      <c r="J163" s="10">
+      <c r="I163" s="7">
+        <v>100700</v>
+      </c>
+      <c r="J163" s="9">
         <v>200</v>
       </c>
-      <c r="K163" s="11" t="s">
+      <c r="K163" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7397,23 +7391,23 @@
       <c r="D164" s="5">
         <v>10</v>
       </c>
-      <c r="E164" s="14"/>
+      <c r="E164" s="13"/>
       <c r="F164" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G164" s="8">
+      <c r="G164" s="7">
         <v>10</v>
       </c>
-      <c r="H164" s="8">
+      <c r="H164" s="7">
         <v>4030001</v>
       </c>
       <c r="I164" s="2">
-        <v>102300</v>
-      </c>
-      <c r="J164" s="10">
+        <v>101700</v>
+      </c>
+      <c r="J164" s="9">
         <v>300</v>
       </c>
-      <c r="K164" s="11" t="s">
+      <c r="K164" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7431,19 +7425,19 @@
       <c r="D165" s="5">
         <v>1</v>
       </c>
-      <c r="E165" s="14"/>
+      <c r="E165" s="13"/>
       <c r="F165" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G165" s="8">
+      <c r="G165" s="7">
         <v>100</v>
       </c>
-      <c r="H165" s="14"/>
-      <c r="I165" s="15"/>
-      <c r="J165" s="10">
-        <v>60</v>
-      </c>
-      <c r="K165" s="11" t="s">
+      <c r="H165" s="13"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="9">
+        <v>5</v>
+      </c>
+      <c r="K165" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7461,19 +7455,19 @@
       <c r="D166" s="5">
         <v>2</v>
       </c>
-      <c r="E166" s="14"/>
+      <c r="E166" s="13"/>
       <c r="F166" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G166" s="8">
+      <c r="G166" s="7">
         <v>200</v>
       </c>
-      <c r="H166" s="14"/>
-      <c r="I166" s="15"/>
-      <c r="J166" s="10">
-        <v>60</v>
-      </c>
-      <c r="K166" s="11" t="s">
+      <c r="H166" s="13"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="9">
+        <v>10</v>
+      </c>
+      <c r="K166" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7491,19 +7485,19 @@
       <c r="D167" s="5">
         <v>3</v>
       </c>
-      <c r="E167" s="14"/>
+      <c r="E167" s="13"/>
       <c r="F167" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G167" s="8">
+      <c r="G167" s="7">
         <v>300</v>
       </c>
-      <c r="H167" s="14"/>
-      <c r="I167" s="15"/>
-      <c r="J167" s="10">
-        <v>60</v>
-      </c>
-      <c r="K167" s="11" t="s">
+      <c r="H167" s="13"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="9">
+        <v>20</v>
+      </c>
+      <c r="K167" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7521,19 +7515,19 @@
       <c r="D168" s="5">
         <v>4</v>
       </c>
-      <c r="E168" s="14"/>
+      <c r="E168" s="13"/>
       <c r="F168" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G168" s="8">
+      <c r="G168" s="7">
         <v>400</v>
       </c>
-      <c r="H168" s="14"/>
-      <c r="I168" s="15"/>
-      <c r="J168" s="10">
-        <v>60</v>
-      </c>
-      <c r="K168" s="11" t="s">
+      <c r="H168" s="13"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="9">
+        <v>30</v>
+      </c>
+      <c r="K168" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7551,19 +7545,19 @@
       <c r="D169" s="5">
         <v>5</v>
       </c>
-      <c r="E169" s="14"/>
+      <c r="E169" s="13"/>
       <c r="F169" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G169" s="8">
+      <c r="G169" s="7">
         <v>500</v>
       </c>
-      <c r="H169" s="14"/>
-      <c r="I169" s="15"/>
-      <c r="J169" s="10">
+      <c r="H169" s="13"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="9">
         <v>60</v>
       </c>
-      <c r="K169" s="11" t="s">
+      <c r="K169" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7581,19 +7575,19 @@
       <c r="D170" s="5">
         <v>6</v>
       </c>
-      <c r="E170" s="14"/>
+      <c r="E170" s="13"/>
       <c r="F170" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G170" s="8">
+      <c r="G170" s="7">
         <v>600</v>
       </c>
-      <c r="H170" s="14"/>
-      <c r="I170" s="15"/>
-      <c r="J170" s="10">
-        <v>60</v>
-      </c>
-      <c r="K170" s="11" t="s">
+      <c r="H170" s="13"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="9">
+        <v>80</v>
+      </c>
+      <c r="K170" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7611,19 +7605,19 @@
       <c r="D171" s="5">
         <v>7</v>
       </c>
-      <c r="E171" s="14"/>
+      <c r="E171" s="13"/>
       <c r="F171" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G171" s="8">
+      <c r="G171" s="7">
         <v>700</v>
       </c>
-      <c r="H171" s="14"/>
-      <c r="I171" s="15"/>
-      <c r="J171" s="10">
-        <v>60</v>
-      </c>
-      <c r="K171" s="11" t="s">
+      <c r="H171" s="13"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="9">
+        <v>120</v>
+      </c>
+      <c r="K171" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7641,19 +7635,19 @@
       <c r="D172" s="5">
         <v>8</v>
       </c>
-      <c r="E172" s="14"/>
+      <c r="E172" s="13"/>
       <c r="F172" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G172" s="8">
+      <c r="G172" s="7">
         <v>800</v>
       </c>
-      <c r="H172" s="14"/>
-      <c r="I172" s="15"/>
-      <c r="J172" s="10">
-        <v>60</v>
-      </c>
-      <c r="K172" s="11" t="s">
+      <c r="H172" s="13"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="9">
+        <v>150</v>
+      </c>
+      <c r="K172" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7668,22 +7662,22 @@
       <c r="C173" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D173" s="12">
+      <c r="D173" s="11">
         <v>9</v>
       </c>
-      <c r="E173" s="14"/>
+      <c r="E173" s="13"/>
       <c r="F173" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G173" s="8">
+      <c r="G173" s="7">
         <v>900</v>
       </c>
-      <c r="H173" s="14"/>
-      <c r="I173" s="15"/>
-      <c r="J173" s="10">
-        <v>60</v>
-      </c>
-      <c r="K173" s="11" t="s">
+      <c r="H173" s="13"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="9">
+        <v>200</v>
+      </c>
+      <c r="K173" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7701,19 +7695,19 @@
       <c r="D174" s="5">
         <v>10</v>
       </c>
-      <c r="E174" s="14"/>
+      <c r="E174" s="13"/>
       <c r="F174" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G174" s="8">
+      <c r="G174" s="7">
         <v>1000</v>
       </c>
-      <c r="H174" s="14"/>
-      <c r="I174" s="15"/>
-      <c r="J174" s="10">
-        <v>60</v>
-      </c>
-      <c r="K174" s="11" t="s">
+      <c r="H174" s="13"/>
+      <c r="I174" s="7"/>
+      <c r="J174" s="9">
+        <v>300</v>
+      </c>
+      <c r="K174" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7731,19 +7725,19 @@
       <c r="D175" s="5">
         <v>1</v>
       </c>
-      <c r="E175" s="14"/>
+      <c r="E175" s="13"/>
       <c r="F175" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G175" s="8">
+      <c r="G175" s="7">
         <v>100</v>
       </c>
-      <c r="H175" s="14"/>
-      <c r="I175" s="15"/>
-      <c r="J175" s="10">
-        <v>60</v>
-      </c>
-      <c r="K175" s="11" t="s">
+      <c r="H175" s="13"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="9">
+        <v>5</v>
+      </c>
+      <c r="K175" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7761,19 +7755,19 @@
       <c r="D176" s="5">
         <v>2</v>
       </c>
-      <c r="E176" s="14"/>
+      <c r="E176" s="13"/>
       <c r="F176" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G176" s="8">
+      <c r="G176" s="7">
         <v>200</v>
       </c>
-      <c r="H176" s="14"/>
-      <c r="I176" s="15"/>
-      <c r="J176" s="10">
-        <v>60</v>
-      </c>
-      <c r="K176" s="11" t="s">
+      <c r="H176" s="13"/>
+      <c r="I176" s="7"/>
+      <c r="J176" s="9">
+        <v>10</v>
+      </c>
+      <c r="K176" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7791,19 +7785,19 @@
       <c r="D177" s="5">
         <v>3</v>
       </c>
-      <c r="E177" s="14"/>
+      <c r="E177" s="13"/>
       <c r="F177" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G177" s="8">
+      <c r="G177" s="7">
         <v>300</v>
       </c>
-      <c r="H177" s="14"/>
-      <c r="I177" s="15"/>
-      <c r="J177" s="10">
-        <v>60</v>
-      </c>
-      <c r="K177" s="11" t="s">
+      <c r="H177" s="13"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="9">
+        <v>20</v>
+      </c>
+      <c r="K177" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7821,19 +7815,19 @@
       <c r="D178" s="5">
         <v>4</v>
       </c>
-      <c r="E178" s="14"/>
+      <c r="E178" s="13"/>
       <c r="F178" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G178" s="8">
+      <c r="G178" s="7">
         <v>400</v>
       </c>
-      <c r="H178" s="14"/>
-      <c r="I178" s="15"/>
-      <c r="J178" s="10">
-        <v>60</v>
-      </c>
-      <c r="K178" s="11" t="s">
+      <c r="H178" s="13"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="9">
+        <v>30</v>
+      </c>
+      <c r="K178" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7851,19 +7845,19 @@
       <c r="D179" s="5">
         <v>5</v>
       </c>
-      <c r="E179" s="14"/>
+      <c r="E179" s="13"/>
       <c r="F179" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G179" s="8">
+      <c r="G179" s="7">
         <v>500</v>
       </c>
-      <c r="H179" s="14"/>
-      <c r="I179" s="15"/>
-      <c r="J179" s="10">
+      <c r="H179" s="13"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="9">
         <v>60</v>
       </c>
-      <c r="K179" s="11" t="s">
+      <c r="K179" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7881,19 +7875,19 @@
       <c r="D180" s="5">
         <v>6</v>
       </c>
-      <c r="E180" s="14"/>
+      <c r="E180" s="13"/>
       <c r="F180" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G180" s="8">
+      <c r="G180" s="7">
         <v>600</v>
       </c>
-      <c r="H180" s="14"/>
-      <c r="I180" s="15"/>
-      <c r="J180" s="10">
-        <v>60</v>
-      </c>
-      <c r="K180" s="11" t="s">
+      <c r="H180" s="13"/>
+      <c r="I180" s="7"/>
+      <c r="J180" s="9">
+        <v>80</v>
+      </c>
+      <c r="K180" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7911,19 +7905,19 @@
       <c r="D181" s="5">
         <v>7</v>
       </c>
-      <c r="E181" s="14"/>
+      <c r="E181" s="13"/>
       <c r="F181" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G181" s="8">
+      <c r="G181" s="7">
         <v>700</v>
       </c>
-      <c r="H181" s="14"/>
-      <c r="I181" s="15"/>
-      <c r="J181" s="10">
-        <v>60</v>
-      </c>
-      <c r="K181" s="11" t="s">
+      <c r="H181" s="13"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="9">
+        <v>120</v>
+      </c>
+      <c r="K181" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7941,19 +7935,19 @@
       <c r="D182" s="5">
         <v>8</v>
       </c>
-      <c r="E182" s="14"/>
+      <c r="E182" s="13"/>
       <c r="F182" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G182" s="8">
+      <c r="G182" s="7">
         <v>800</v>
       </c>
-      <c r="H182" s="14"/>
-      <c r="I182" s="15"/>
-      <c r="J182" s="10">
-        <v>60</v>
-      </c>
-      <c r="K182" s="11" t="s">
+      <c r="H182" s="13"/>
+      <c r="I182" s="7"/>
+      <c r="J182" s="9">
+        <v>150</v>
+      </c>
+      <c r="K182" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7968,22 +7962,22 @@
       <c r="C183" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D183" s="12">
+      <c r="D183" s="11">
         <v>9</v>
       </c>
-      <c r="E183" s="14"/>
+      <c r="E183" s="13"/>
       <c r="F183" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G183" s="8">
+      <c r="G183" s="7">
         <v>900</v>
       </c>
-      <c r="H183" s="14"/>
-      <c r="I183" s="15"/>
-      <c r="J183" s="10">
-        <v>60</v>
-      </c>
-      <c r="K183" s="11" t="s">
+      <c r="H183" s="13"/>
+      <c r="I183" s="7"/>
+      <c r="J183" s="9">
+        <v>200</v>
+      </c>
+      <c r="K183" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -8001,19 +7995,19 @@
       <c r="D184" s="5">
         <v>10</v>
       </c>
-      <c r="E184" s="14"/>
+      <c r="E184" s="13"/>
       <c r="F184" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G184" s="8">
+      <c r="G184" s="7">
         <v>1000</v>
       </c>
-      <c r="H184" s="14"/>
-      <c r="I184" s="15"/>
-      <c r="J184" s="10">
-        <v>60</v>
-      </c>
-      <c r="K184" s="11" t="s">
+      <c r="H184" s="13"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="9">
+        <v>300</v>
+      </c>
+      <c r="K184" s="10" t="s">
         <v>28</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -31905,7 +31905,7 @@
         <v>4030001</v>
       </c>
       <c r="I845" s="30">
-        <v>1101101</v>
+        <v>100300</v>
       </c>
       <c r="J845" s="30"/>
       <c r="K845" s="31" t="s">
@@ -31943,7 +31943,7 @@
         <v>4030001</v>
       </c>
       <c r="I846" s="30">
-        <v>1101102</v>
+        <v>103400</v>
       </c>
       <c r="J846" s="30"/>
       <c r="K846" s="31" t="s">
@@ -31958,7 +31958,7 @@
     </row>
     <row r="847" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A847" s="29">
-        <f t="shared" ref="A847:A884" si="32">B847*1000+D847</f>
+        <f t="shared" ref="A847:A894" si="32">B847*1000+D847</f>
         <v>1302003</v>
       </c>
       <c r="B847" s="29">
@@ -31981,7 +31981,7 @@
         <v>4030001</v>
       </c>
       <c r="I847" s="30">
-        <v>1101103</v>
+        <v>103401</v>
       </c>
       <c r="J847" s="30"/>
       <c r="K847" s="31" t="s">
@@ -32019,7 +32019,7 @@
         <v>4030001</v>
       </c>
       <c r="I848" s="30">
-        <v>1101104</v>
+        <v>101400</v>
       </c>
       <c r="J848" s="30"/>
       <c r="K848" s="31" t="s">
@@ -32057,7 +32057,7 @@
         <v>4030001</v>
       </c>
       <c r="I849" s="30">
-        <v>1101105</v>
+        <v>103500</v>
       </c>
       <c r="J849" s="30"/>
       <c r="K849" s="31" t="s">
@@ -32095,7 +32095,7 @@
         <v>4030001</v>
       </c>
       <c r="I850" s="30">
-        <v>1101106</v>
+        <v>103501</v>
       </c>
       <c r="J850" s="30"/>
       <c r="K850" s="31" t="s">
@@ -32133,7 +32133,7 @@
         <v>4030001</v>
       </c>
       <c r="I851" s="30">
-        <v>1101107</v>
+        <v>100700</v>
       </c>
       <c r="J851" s="30"/>
       <c r="K851" s="31" t="s">
@@ -32171,7 +32171,7 @@
         <v>4030001</v>
       </c>
       <c r="I852" s="30">
-        <v>1101108</v>
+        <v>103700</v>
       </c>
       <c r="J852" s="30"/>
       <c r="K852" s="31" t="s">
@@ -32209,7 +32209,7 @@
         <v>4030001</v>
       </c>
       <c r="I853" s="30">
-        <v>1101109</v>
+        <v>103600</v>
       </c>
       <c r="J853" s="30"/>
       <c r="K853" s="31" t="s">
@@ -32247,7 +32247,7 @@
         <v>4030001</v>
       </c>
       <c r="I854" s="30">
-        <v>1101110</v>
+        <v>101700</v>
       </c>
       <c r="J854" s="30"/>
       <c r="K854" s="31" t="s">
@@ -32284,9 +32284,7 @@
       <c r="H855" s="30">
         <v>4030001</v>
       </c>
-      <c r="I855" s="30">
-        <v>1101111</v>
-      </c>
+      <c r="I855" s="30"/>
       <c r="J855" s="30"/>
       <c r="K855" s="31" t="s">
         <v>141</v>
@@ -32322,9 +32320,7 @@
       <c r="H856" s="30">
         <v>4030001</v>
       </c>
-      <c r="I856" s="30">
-        <v>1101112</v>
-      </c>
+      <c r="I856" s="30"/>
       <c r="J856" s="30"/>
       <c r="K856" s="31" t="s">
         <v>142</v>
@@ -32360,9 +32356,7 @@
       <c r="H857" s="30">
         <v>4030001</v>
       </c>
-      <c r="I857" s="30">
-        <v>1101113</v>
-      </c>
+      <c r="I857" s="30"/>
       <c r="J857" s="30"/>
       <c r="K857" s="31" t="s">
         <v>143</v>
@@ -32398,9 +32392,7 @@
       <c r="H858" s="30">
         <v>4030001</v>
       </c>
-      <c r="I858" s="30">
-        <v>1101114</v>
-      </c>
+      <c r="I858" s="30"/>
       <c r="J858" s="30"/>
       <c r="K858" s="31" t="s">
         <v>144</v>
@@ -32436,9 +32428,7 @@
       <c r="H859" s="30">
         <v>4030001</v>
       </c>
-      <c r="I859" s="30">
-        <v>1101115</v>
-      </c>
+      <c r="I859" s="30"/>
       <c r="J859" s="30"/>
       <c r="K859" s="31" t="s">
         <v>145</v>
@@ -32474,9 +32464,7 @@
       <c r="H860" s="30">
         <v>4030001</v>
       </c>
-      <c r="I860" s="30">
-        <v>1101116</v>
-      </c>
+      <c r="I860" s="30"/>
       <c r="J860" s="30"/>
       <c r="K860" s="31" t="s">
         <v>146</v>
@@ -32512,9 +32500,7 @@
       <c r="H861" s="30">
         <v>4030001</v>
       </c>
-      <c r="I861" s="30">
-        <v>1101117</v>
-      </c>
+      <c r="I861" s="30"/>
       <c r="J861" s="30"/>
       <c r="K861" s="31" t="s">
         <v>147</v>
@@ -32550,9 +32536,7 @@
       <c r="H862" s="30">
         <v>4030001</v>
       </c>
-      <c r="I862" s="30">
-        <v>1101118</v>
-      </c>
+      <c r="I862" s="30"/>
       <c r="J862" s="30"/>
       <c r="K862" s="31">
         <v>1101269</v>
@@ -33278,7 +33262,7 @@
     </row>
     <row r="885" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A885" s="21">
-        <f>B885*1000+D885</f>
+        <f t="shared" si="32"/>
         <v>1303001</v>
       </c>
       <c r="B885" s="21">
@@ -33312,7 +33296,7 @@
     </row>
     <row r="886" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A886" s="21">
-        <f>B886*1000+D886</f>
+        <f t="shared" si="32"/>
         <v>1303002</v>
       </c>
       <c r="B886" s="21">
@@ -33346,7 +33330,7 @@
     </row>
     <row r="887" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A887" s="21">
-        <f>B887*1000+D887</f>
+        <f t="shared" si="32"/>
         <v>1303003</v>
       </c>
       <c r="B887" s="21">
@@ -33380,7 +33364,7 @@
     </row>
     <row r="888" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A888" s="21">
-        <f>B888*1000+D888</f>
+        <f t="shared" si="32"/>
         <v>1303004</v>
       </c>
       <c r="B888" s="21">
@@ -33414,7 +33398,7 @@
     </row>
     <row r="889" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A889" s="21">
-        <f>B889*1000+D889</f>
+        <f t="shared" si="32"/>
         <v>1303005</v>
       </c>
       <c r="B889" s="21">
@@ -33448,7 +33432,7 @@
     </row>
     <row r="890" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A890" s="21">
-        <f>B890*1000+D890</f>
+        <f t="shared" si="32"/>
         <v>1303006</v>
       </c>
       <c r="B890" s="21">
@@ -33482,7 +33466,7 @@
     </row>
     <row r="891" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A891" s="21">
-        <f>B891*1000+D891</f>
+        <f t="shared" si="32"/>
         <v>1303007</v>
       </c>
       <c r="B891" s="21">
@@ -33516,7 +33500,7 @@
     </row>
     <row r="892" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A892" s="21">
-        <f>B892*1000+D892</f>
+        <f t="shared" si="32"/>
         <v>1303008</v>
       </c>
       <c r="B892" s="21">
@@ -33550,7 +33534,7 @@
     </row>
     <row r="893" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A893" s="21">
-        <f>B893*1000+D893</f>
+        <f t="shared" si="32"/>
         <v>1303009</v>
       </c>
       <c r="B893" s="21">
@@ -33584,7 +33568,7 @@
     </row>
     <row r="894" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A894" s="21">
-        <f>B894*1000+D894</f>
+        <f t="shared" si="32"/>
         <v>1303010</v>
       </c>
       <c r="B894" s="21">

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -3595,7 +3595,9 @@
       <c r="D43" s="17">
         <v>39</v>
       </c>
-      <c r="E43" s="17"/>
+      <c r="E43" s="17">
+        <v>38</v>
+      </c>
       <c r="F43" s="17" t="s">
         <v>71</v>
       </c>
@@ -3627,7 +3629,9 @@
       <c r="D44" s="17">
         <v>40</v>
       </c>
-      <c r="E44" s="17"/>
+      <c r="E44" s="17">
+        <v>38</v>
+      </c>
       <c r="F44" s="17" t="s">
         <v>72</v>
       </c>
@@ -3659,7 +3663,9 @@
       <c r="D45" s="17">
         <v>41</v>
       </c>
-      <c r="E45" s="17"/>
+      <c r="E45" s="17">
+        <v>38</v>
+      </c>
       <c r="F45" s="17" t="s">
         <v>73</v>
       </c>
@@ -3691,7 +3697,9 @@
       <c r="D46" s="17">
         <v>42</v>
       </c>
-      <c r="E46" s="17"/>
+      <c r="E46" s="17">
+        <v>38</v>
+      </c>
       <c r="F46" s="17" t="s">
         <v>74</v>
       </c>
@@ -3723,7 +3731,9 @@
       <c r="D47" s="17">
         <v>43</v>
       </c>
-      <c r="E47" s="17"/>
+      <c r="E47" s="17">
+        <v>38</v>
+      </c>
       <c r="F47" s="17" t="s">
         <v>75</v>
       </c>
@@ -3755,7 +3765,9 @@
       <c r="D48" s="17">
         <v>44</v>
       </c>
-      <c r="E48" s="17"/>
+      <c r="E48" s="17">
+        <v>38</v>
+      </c>
       <c r="F48" s="17" t="s">
         <v>76</v>
       </c>
@@ -3787,7 +3799,9 @@
       <c r="D49" s="17">
         <v>45</v>
       </c>
-      <c r="E49" s="17"/>
+      <c r="E49" s="17">
+        <v>38</v>
+      </c>
       <c r="F49" s="17" t="s">
         <v>77</v>
       </c>
@@ -3819,7 +3833,9 @@
       <c r="D50" s="17">
         <v>46</v>
       </c>
-      <c r="E50" s="17"/>
+      <c r="E50" s="17">
+        <v>38</v>
+      </c>
       <c r="F50" s="17" t="s">
         <v>78</v>
       </c>
@@ -3851,7 +3867,9 @@
       <c r="D51" s="17">
         <v>47</v>
       </c>
-      <c r="E51" s="17"/>
+      <c r="E51" s="17">
+        <v>38</v>
+      </c>
       <c r="F51" s="17" t="s">
         <v>79</v>
       </c>
@@ -3883,7 +3901,9 @@
       <c r="D52" s="17">
         <v>48</v>
       </c>
-      <c r="E52" s="17"/>
+      <c r="E52" s="17">
+        <v>38</v>
+      </c>
       <c r="F52" s="17" t="s">
         <v>80</v>
       </c>
@@ -3915,7 +3935,9 @@
       <c r="D53" s="17">
         <v>49</v>
       </c>
-      <c r="E53" s="17"/>
+      <c r="E53" s="17">
+        <v>38</v>
+      </c>
       <c r="F53" s="17" t="s">
         <v>81</v>
       </c>
@@ -3947,7 +3969,9 @@
       <c r="D54" s="17">
         <v>50</v>
       </c>
-      <c r="E54" s="17"/>
+      <c r="E54" s="17">
+        <v>38</v>
+      </c>
       <c r="F54" s="17" t="s">
         <v>82</v>
       </c>
@@ -3979,7 +4003,9 @@
       <c r="D55" s="17">
         <v>51</v>
       </c>
-      <c r="E55" s="17"/>
+      <c r="E55" s="17">
+        <v>38</v>
+      </c>
       <c r="F55" s="17" t="s">
         <v>83</v>
       </c>
@@ -4011,7 +4037,9 @@
       <c r="D56" s="17">
         <v>52</v>
       </c>
-      <c r="E56" s="17"/>
+      <c r="E56" s="17">
+        <v>38</v>
+      </c>
       <c r="F56" s="17" t="s">
         <v>84</v>
       </c>
@@ -4043,7 +4071,9 @@
       <c r="D57" s="17">
         <v>53</v>
       </c>
-      <c r="E57" s="17"/>
+      <c r="E57" s="17">
+        <v>38</v>
+      </c>
       <c r="F57" s="17" t="s">
         <v>85</v>
       </c>
@@ -4075,7 +4105,9 @@
       <c r="D58" s="17">
         <v>54</v>
       </c>
-      <c r="E58" s="17"/>
+      <c r="E58" s="17">
+        <v>38</v>
+      </c>
       <c r="F58" s="17" t="s">
         <v>86</v>
       </c>
@@ -4107,7 +4139,9 @@
       <c r="D59" s="17">
         <v>55</v>
       </c>
-      <c r="E59" s="17"/>
+      <c r="E59" s="17">
+        <v>38</v>
+      </c>
       <c r="F59" s="17" t="s">
         <v>87</v>
       </c>
@@ -4139,7 +4173,9 @@
       <c r="D60" s="17">
         <v>56</v>
       </c>
-      <c r="E60" s="17"/>
+      <c r="E60" s="17">
+        <v>38</v>
+      </c>
       <c r="F60" s="17" t="s">
         <v>88</v>
       </c>
@@ -4171,7 +4207,9 @@
       <c r="D61" s="17">
         <v>57</v>
       </c>
-      <c r="E61" s="17"/>
+      <c r="E61" s="17">
+        <v>38</v>
+      </c>
       <c r="F61" s="17" t="s">
         <v>89</v>
       </c>
@@ -4203,7 +4241,9 @@
       <c r="D62" s="17">
         <v>58</v>
       </c>
-      <c r="E62" s="17"/>
+      <c r="E62" s="17">
+        <v>38</v>
+      </c>
       <c r="F62" s="17" t="s">
         <v>90</v>
       </c>
@@ -4235,7 +4275,9 @@
       <c r="D63" s="17">
         <v>59</v>
       </c>
-      <c r="E63" s="17"/>
+      <c r="E63" s="17">
+        <v>38</v>
+      </c>
       <c r="F63" s="17" t="s">
         <v>91</v>
       </c>
@@ -4267,7 +4309,9 @@
       <c r="D64" s="17">
         <v>60</v>
       </c>
-      <c r="E64" s="17"/>
+      <c r="E64" s="17">
+        <v>38</v>
+      </c>
       <c r="F64" s="17" t="s">
         <v>92</v>
       </c>
@@ -5405,7 +5449,9 @@
       <c r="D94" s="21">
         <v>30</v>
       </c>
-      <c r="E94" s="21"/>
+      <c r="E94" s="21">
+        <v>29</v>
+      </c>
       <c r="F94" s="21" t="s">
         <v>61</v>
       </c>
@@ -5439,7 +5485,9 @@
       <c r="D95" s="21">
         <v>31</v>
       </c>
-      <c r="E95" s="21"/>
+      <c r="E95" s="21">
+        <v>29</v>
+      </c>
       <c r="F95" s="21" t="s">
         <v>63</v>
       </c>
@@ -5473,7 +5521,9 @@
       <c r="D96" s="21">
         <v>32</v>
       </c>
-      <c r="E96" s="21"/>
+      <c r="E96" s="21">
+        <v>29</v>
+      </c>
       <c r="F96" s="21" t="s">
         <v>64</v>
       </c>
@@ -5507,7 +5557,9 @@
       <c r="D97" s="21">
         <v>33</v>
       </c>
-      <c r="E97" s="21"/>
+      <c r="E97" s="21">
+        <v>29</v>
+      </c>
       <c r="F97" s="21" t="s">
         <v>65</v>
       </c>
@@ -5541,7 +5593,9 @@
       <c r="D98" s="21">
         <v>34</v>
       </c>
-      <c r="E98" s="21"/>
+      <c r="E98" s="21">
+        <v>29</v>
+      </c>
       <c r="F98" s="21" t="s">
         <v>66</v>
       </c>
@@ -5575,7 +5629,9 @@
       <c r="D99" s="21">
         <v>35</v>
       </c>
-      <c r="E99" s="21"/>
+      <c r="E99" s="21">
+        <v>29</v>
+      </c>
       <c r="F99" s="21" t="s">
         <v>67</v>
       </c>
@@ -5609,7 +5665,9 @@
       <c r="D100" s="21">
         <v>36</v>
       </c>
-      <c r="E100" s="21"/>
+      <c r="E100" s="21">
+        <v>29</v>
+      </c>
       <c r="F100" s="21" t="s">
         <v>68</v>
       </c>
@@ -5643,7 +5701,9 @@
       <c r="D101" s="21">
         <v>37</v>
       </c>
-      <c r="E101" s="21"/>
+      <c r="E101" s="21">
+        <v>29</v>
+      </c>
       <c r="F101" s="21" t="s">
         <v>69</v>
       </c>
@@ -5677,7 +5737,9 @@
       <c r="D102" s="21">
         <v>38</v>
       </c>
-      <c r="E102" s="21"/>
+      <c r="E102" s="21">
+        <v>29</v>
+      </c>
       <c r="F102" s="21" t="s">
         <v>70</v>
       </c>
@@ -5711,7 +5773,9 @@
       <c r="D103" s="21">
         <v>39</v>
       </c>
-      <c r="E103" s="21"/>
+      <c r="E103" s="21">
+        <v>29</v>
+      </c>
       <c r="F103" s="21" t="s">
         <v>71</v>
       </c>
@@ -5745,7 +5809,9 @@
       <c r="D104" s="21">
         <v>40</v>
       </c>
-      <c r="E104" s="21"/>
+      <c r="E104" s="21">
+        <v>29</v>
+      </c>
       <c r="F104" s="21" t="s">
         <v>72</v>
       </c>
@@ -5779,7 +5845,9 @@
       <c r="D105" s="21">
         <v>41</v>
       </c>
-      <c r="E105" s="21"/>
+      <c r="E105" s="21">
+        <v>29</v>
+      </c>
       <c r="F105" s="21" t="s">
         <v>73</v>
       </c>
@@ -5813,7 +5881,9 @@
       <c r="D106" s="21">
         <v>42</v>
       </c>
-      <c r="E106" s="21"/>
+      <c r="E106" s="21">
+        <v>29</v>
+      </c>
       <c r="F106" s="21" t="s">
         <v>74</v>
       </c>
@@ -5847,7 +5917,9 @@
       <c r="D107" s="21">
         <v>43</v>
       </c>
-      <c r="E107" s="21"/>
+      <c r="E107" s="21">
+        <v>29</v>
+      </c>
       <c r="F107" s="21" t="s">
         <v>75</v>
       </c>
@@ -5881,7 +5953,9 @@
       <c r="D108" s="21">
         <v>44</v>
       </c>
-      <c r="E108" s="21"/>
+      <c r="E108" s="21">
+        <v>29</v>
+      </c>
       <c r="F108" s="21" t="s">
         <v>76</v>
       </c>
@@ -5915,7 +5989,9 @@
       <c r="D109" s="21">
         <v>45</v>
       </c>
-      <c r="E109" s="21"/>
+      <c r="E109" s="21">
+        <v>29</v>
+      </c>
       <c r="F109" s="21" t="s">
         <v>77</v>
       </c>
@@ -5949,7 +6025,9 @@
       <c r="D110" s="21">
         <v>46</v>
       </c>
-      <c r="E110" s="21"/>
+      <c r="E110" s="21">
+        <v>29</v>
+      </c>
       <c r="F110" s="21" t="s">
         <v>78</v>
       </c>
@@ -5983,7 +6061,9 @@
       <c r="D111" s="21">
         <v>47</v>
       </c>
-      <c r="E111" s="21"/>
+      <c r="E111" s="21">
+        <v>29</v>
+      </c>
       <c r="F111" s="21" t="s">
         <v>79</v>
       </c>
@@ -6017,7 +6097,9 @@
       <c r="D112" s="21">
         <v>48</v>
       </c>
-      <c r="E112" s="21"/>
+      <c r="E112" s="21">
+        <v>29</v>
+      </c>
       <c r="F112" s="21" t="s">
         <v>80</v>
       </c>
@@ -6051,7 +6133,9 @@
       <c r="D113" s="21">
         <v>49</v>
       </c>
-      <c r="E113" s="21"/>
+      <c r="E113" s="21">
+        <v>29</v>
+      </c>
       <c r="F113" s="21" t="s">
         <v>81</v>
       </c>
@@ -6085,7 +6169,9 @@
       <c r="D114" s="21">
         <v>50</v>
       </c>
-      <c r="E114" s="21"/>
+      <c r="E114" s="21">
+        <v>29</v>
+      </c>
       <c r="F114" s="21" t="s">
         <v>82</v>
       </c>
@@ -6119,7 +6205,9 @@
       <c r="D115" s="21">
         <v>51</v>
       </c>
-      <c r="E115" s="21"/>
+      <c r="E115" s="21">
+        <v>29</v>
+      </c>
       <c r="F115" s="21" t="s">
         <v>83</v>
       </c>
@@ -6153,7 +6241,9 @@
       <c r="D116" s="21">
         <v>52</v>
       </c>
-      <c r="E116" s="21"/>
+      <c r="E116" s="21">
+        <v>29</v>
+      </c>
       <c r="F116" s="21" t="s">
         <v>84</v>
       </c>
@@ -6187,7 +6277,9 @@
       <c r="D117" s="21">
         <v>53</v>
       </c>
-      <c r="E117" s="21"/>
+      <c r="E117" s="21">
+        <v>29</v>
+      </c>
       <c r="F117" s="21" t="s">
         <v>85</v>
       </c>
@@ -6221,7 +6313,9 @@
       <c r="D118" s="21">
         <v>54</v>
       </c>
-      <c r="E118" s="21"/>
+      <c r="E118" s="21">
+        <v>29</v>
+      </c>
       <c r="F118" s="21" t="s">
         <v>86</v>
       </c>
@@ -6255,7 +6349,9 @@
       <c r="D119" s="21">
         <v>55</v>
       </c>
-      <c r="E119" s="21"/>
+      <c r="E119" s="21">
+        <v>29</v>
+      </c>
       <c r="F119" s="21" t="s">
         <v>87</v>
       </c>
@@ -6289,7 +6385,9 @@
       <c r="D120" s="21">
         <v>56</v>
       </c>
-      <c r="E120" s="21"/>
+      <c r="E120" s="21">
+        <v>29</v>
+      </c>
       <c r="F120" s="21" t="s">
         <v>88</v>
       </c>
@@ -6323,7 +6421,9 @@
       <c r="D121" s="21">
         <v>57</v>
       </c>
-      <c r="E121" s="21"/>
+      <c r="E121" s="21">
+        <v>29</v>
+      </c>
       <c r="F121" s="21" t="s">
         <v>89</v>
       </c>
@@ -6357,7 +6457,9 @@
       <c r="D122" s="21">
         <v>58</v>
       </c>
-      <c r="E122" s="21"/>
+      <c r="E122" s="21">
+        <v>29</v>
+      </c>
       <c r="F122" s="21" t="s">
         <v>90</v>
       </c>
@@ -6391,7 +6493,9 @@
       <c r="D123" s="21">
         <v>59</v>
       </c>
-      <c r="E123" s="21"/>
+      <c r="E123" s="21">
+        <v>29</v>
+      </c>
       <c r="F123" s="21" t="s">
         <v>91</v>
       </c>
@@ -6425,7 +6529,9 @@
       <c r="D124" s="21">
         <v>60</v>
       </c>
-      <c r="E124" s="21"/>
+      <c r="E124" s="21">
+        <v>29</v>
+      </c>
       <c r="F124" s="21" t="s">
         <v>92</v>
       </c>
@@ -7607,7 +7713,9 @@
       <c r="D156" s="17">
         <v>32</v>
       </c>
-      <c r="E156" s="17"/>
+      <c r="E156" s="17">
+        <v>31</v>
+      </c>
       <c r="F156" s="17" t="s">
         <v>64</v>
       </c>
@@ -7639,7 +7747,9 @@
       <c r="D157" s="17">
         <v>33</v>
       </c>
-      <c r="E157" s="17"/>
+      <c r="E157" s="17">
+        <v>31</v>
+      </c>
       <c r="F157" s="17" t="s">
         <v>65</v>
       </c>
@@ -7671,7 +7781,9 @@
       <c r="D158" s="17">
         <v>34</v>
       </c>
-      <c r="E158" s="17"/>
+      <c r="E158" s="17">
+        <v>31</v>
+      </c>
       <c r="F158" s="17" t="s">
         <v>66</v>
       </c>
@@ -7703,7 +7815,9 @@
       <c r="D159" s="17">
         <v>35</v>
       </c>
-      <c r="E159" s="17"/>
+      <c r="E159" s="17">
+        <v>31</v>
+      </c>
       <c r="F159" s="17" t="s">
         <v>67</v>
       </c>
@@ -7735,7 +7849,9 @@
       <c r="D160" s="17">
         <v>36</v>
       </c>
-      <c r="E160" s="17"/>
+      <c r="E160" s="17">
+        <v>31</v>
+      </c>
       <c r="F160" s="17" t="s">
         <v>68</v>
       </c>
@@ -7767,7 +7883,9 @@
       <c r="D161" s="17">
         <v>37</v>
       </c>
-      <c r="E161" s="17"/>
+      <c r="E161" s="17">
+        <v>31</v>
+      </c>
       <c r="F161" s="17" t="s">
         <v>69</v>
       </c>
@@ -7799,7 +7917,9 @@
       <c r="D162" s="17">
         <v>38</v>
       </c>
-      <c r="E162" s="17"/>
+      <c r="E162" s="17">
+        <v>31</v>
+      </c>
       <c r="F162" s="17" t="s">
         <v>70</v>
       </c>
@@ -7831,7 +7951,9 @@
       <c r="D163" s="17">
         <v>39</v>
       </c>
-      <c r="E163" s="17"/>
+      <c r="E163" s="17">
+        <v>31</v>
+      </c>
       <c r="F163" s="17" t="s">
         <v>71</v>
       </c>
@@ -7863,7 +7985,9 @@
       <c r="D164" s="17">
         <v>40</v>
       </c>
-      <c r="E164" s="17"/>
+      <c r="E164" s="17">
+        <v>31</v>
+      </c>
       <c r="F164" s="17" t="s">
         <v>72</v>
       </c>
@@ -7895,7 +8019,9 @@
       <c r="D165" s="17">
         <v>41</v>
       </c>
-      <c r="E165" s="17"/>
+      <c r="E165" s="17">
+        <v>31</v>
+      </c>
       <c r="F165" s="17" t="s">
         <v>73</v>
       </c>
@@ -7927,7 +8053,9 @@
       <c r="D166" s="17">
         <v>42</v>
       </c>
-      <c r="E166" s="17"/>
+      <c r="E166" s="17">
+        <v>31</v>
+      </c>
       <c r="F166" s="17" t="s">
         <v>74</v>
       </c>
@@ -7959,7 +8087,9 @@
       <c r="D167" s="17">
         <v>43</v>
       </c>
-      <c r="E167" s="17"/>
+      <c r="E167" s="17">
+        <v>31</v>
+      </c>
       <c r="F167" s="17" t="s">
         <v>75</v>
       </c>
@@ -7991,7 +8121,9 @@
       <c r="D168" s="17">
         <v>44</v>
       </c>
-      <c r="E168" s="17"/>
+      <c r="E168" s="17">
+        <v>31</v>
+      </c>
       <c r="F168" s="17" t="s">
         <v>76</v>
       </c>
@@ -8023,7 +8155,9 @@
       <c r="D169" s="17">
         <v>45</v>
       </c>
-      <c r="E169" s="17"/>
+      <c r="E169" s="17">
+        <v>31</v>
+      </c>
       <c r="F169" s="17" t="s">
         <v>77</v>
       </c>
@@ -8055,7 +8189,9 @@
       <c r="D170" s="17">
         <v>46</v>
       </c>
-      <c r="E170" s="17"/>
+      <c r="E170" s="17">
+        <v>31</v>
+      </c>
       <c r="F170" s="17" t="s">
         <v>78</v>
       </c>
@@ -8087,7 +8223,9 @@
       <c r="D171" s="17">
         <v>47</v>
       </c>
-      <c r="E171" s="17"/>
+      <c r="E171" s="17">
+        <v>31</v>
+      </c>
       <c r="F171" s="17" t="s">
         <v>79</v>
       </c>
@@ -8119,7 +8257,9 @@
       <c r="D172" s="17">
         <v>48</v>
       </c>
-      <c r="E172" s="17"/>
+      <c r="E172" s="17">
+        <v>31</v>
+      </c>
       <c r="F172" s="17" t="s">
         <v>80</v>
       </c>
@@ -8151,7 +8291,9 @@
       <c r="D173" s="17">
         <v>49</v>
       </c>
-      <c r="E173" s="17"/>
+      <c r="E173" s="17">
+        <v>31</v>
+      </c>
       <c r="F173" s="17" t="s">
         <v>81</v>
       </c>
@@ -8183,7 +8325,9 @@
       <c r="D174" s="17">
         <v>50</v>
       </c>
-      <c r="E174" s="17"/>
+      <c r="E174" s="17">
+        <v>31</v>
+      </c>
       <c r="F174" s="17" t="s">
         <v>82</v>
       </c>
@@ -8215,7 +8359,9 @@
       <c r="D175" s="17">
         <v>51</v>
       </c>
-      <c r="E175" s="17"/>
+      <c r="E175" s="17">
+        <v>31</v>
+      </c>
       <c r="F175" s="17" t="s">
         <v>83</v>
       </c>
@@ -8247,7 +8393,9 @@
       <c r="D176" s="17">
         <v>52</v>
       </c>
-      <c r="E176" s="17"/>
+      <c r="E176" s="17">
+        <v>31</v>
+      </c>
       <c r="F176" s="17" t="s">
         <v>84</v>
       </c>
@@ -8279,7 +8427,9 @@
       <c r="D177" s="17">
         <v>53</v>
       </c>
-      <c r="E177" s="17"/>
+      <c r="E177" s="17">
+        <v>31</v>
+      </c>
       <c r="F177" s="17" t="s">
         <v>85</v>
       </c>
@@ -8311,7 +8461,9 @@
       <c r="D178" s="17">
         <v>54</v>
       </c>
-      <c r="E178" s="17"/>
+      <c r="E178" s="17">
+        <v>31</v>
+      </c>
       <c r="F178" s="17" t="s">
         <v>86</v>
       </c>
@@ -8343,7 +8495,9 @@
       <c r="D179" s="17">
         <v>55</v>
       </c>
-      <c r="E179" s="17"/>
+      <c r="E179" s="17">
+        <v>31</v>
+      </c>
       <c r="F179" s="17" t="s">
         <v>87</v>
       </c>
@@ -8375,7 +8529,9 @@
       <c r="D180" s="17">
         <v>56</v>
       </c>
-      <c r="E180" s="17"/>
+      <c r="E180" s="17">
+        <v>31</v>
+      </c>
       <c r="F180" s="17" t="s">
         <v>88</v>
       </c>
@@ -8407,7 +8563,9 @@
       <c r="D181" s="17">
         <v>57</v>
       </c>
-      <c r="E181" s="17"/>
+      <c r="E181" s="17">
+        <v>31</v>
+      </c>
       <c r="F181" s="17" t="s">
         <v>89</v>
       </c>
@@ -8439,7 +8597,9 @@
       <c r="D182" s="17">
         <v>58</v>
       </c>
-      <c r="E182" s="17"/>
+      <c r="E182" s="17">
+        <v>31</v>
+      </c>
       <c r="F182" s="17" t="s">
         <v>90</v>
       </c>
@@ -8471,7 +8631,9 @@
       <c r="D183" s="17">
         <v>59</v>
       </c>
-      <c r="E183" s="17"/>
+      <c r="E183" s="17">
+        <v>31</v>
+      </c>
       <c r="F183" s="17" t="s">
         <v>91</v>
       </c>
@@ -8503,7 +8665,9 @@
       <c r="D184" s="17">
         <v>60</v>
       </c>
-      <c r="E184" s="17"/>
+      <c r="E184" s="17">
+        <v>31</v>
+      </c>
       <c r="F184" s="17" t="s">
         <v>92</v>
       </c>
@@ -9569,7 +9733,9 @@
       <c r="D212" s="21">
         <v>28</v>
       </c>
-      <c r="E212" s="21"/>
+      <c r="E212" s="21">
+        <v>27</v>
+      </c>
       <c r="F212" s="21" t="s">
         <v>59</v>
       </c>
@@ -9603,7 +9769,9 @@
       <c r="D213" s="21">
         <v>29</v>
       </c>
-      <c r="E213" s="21"/>
+      <c r="E213" s="21">
+        <v>27</v>
+      </c>
       <c r="F213" s="21" t="s">
         <v>60</v>
       </c>
@@ -9637,7 +9805,9 @@
       <c r="D214" s="21">
         <v>30</v>
       </c>
-      <c r="E214" s="21"/>
+      <c r="E214" s="21">
+        <v>27</v>
+      </c>
       <c r="F214" s="21" t="s">
         <v>61</v>
       </c>
@@ -9671,7 +9841,9 @@
       <c r="D215" s="21">
         <v>31</v>
       </c>
-      <c r="E215" s="21"/>
+      <c r="E215" s="21">
+        <v>27</v>
+      </c>
       <c r="F215" s="21" t="s">
         <v>63</v>
       </c>
@@ -9705,7 +9877,9 @@
       <c r="D216" s="21">
         <v>32</v>
       </c>
-      <c r="E216" s="21"/>
+      <c r="E216" s="21">
+        <v>27</v>
+      </c>
       <c r="F216" s="21" t="s">
         <v>64</v>
       </c>
@@ -9739,7 +9913,9 @@
       <c r="D217" s="21">
         <v>33</v>
       </c>
-      <c r="E217" s="21"/>
+      <c r="E217" s="21">
+        <v>27</v>
+      </c>
       <c r="F217" s="21" t="s">
         <v>65</v>
       </c>
@@ -9773,7 +9949,9 @@
       <c r="D218" s="21">
         <v>34</v>
       </c>
-      <c r="E218" s="21"/>
+      <c r="E218" s="21">
+        <v>27</v>
+      </c>
       <c r="F218" s="21" t="s">
         <v>66</v>
       </c>
@@ -9807,7 +9985,9 @@
       <c r="D219" s="21">
         <v>35</v>
       </c>
-      <c r="E219" s="21"/>
+      <c r="E219" s="21">
+        <v>27</v>
+      </c>
       <c r="F219" s="21" t="s">
         <v>67</v>
       </c>
@@ -9841,7 +10021,9 @@
       <c r="D220" s="21">
         <v>36</v>
       </c>
-      <c r="E220" s="21"/>
+      <c r="E220" s="21">
+        <v>27</v>
+      </c>
       <c r="F220" s="21" t="s">
         <v>68</v>
       </c>
@@ -9875,7 +10057,9 @@
       <c r="D221" s="21">
         <v>37</v>
       </c>
-      <c r="E221" s="21"/>
+      <c r="E221" s="21">
+        <v>27</v>
+      </c>
       <c r="F221" s="21" t="s">
         <v>69</v>
       </c>
@@ -9909,7 +10093,9 @@
       <c r="D222" s="21">
         <v>38</v>
       </c>
-      <c r="E222" s="21"/>
+      <c r="E222" s="21">
+        <v>27</v>
+      </c>
       <c r="F222" s="21" t="s">
         <v>70</v>
       </c>
@@ -9943,7 +10129,9 @@
       <c r="D223" s="21">
         <v>39</v>
       </c>
-      <c r="E223" s="21"/>
+      <c r="E223" s="21">
+        <v>27</v>
+      </c>
       <c r="F223" s="21" t="s">
         <v>71</v>
       </c>
@@ -9977,7 +10165,9 @@
       <c r="D224" s="21">
         <v>40</v>
       </c>
-      <c r="E224" s="21"/>
+      <c r="E224" s="21">
+        <v>27</v>
+      </c>
       <c r="F224" s="21" t="s">
         <v>72</v>
       </c>
@@ -10011,7 +10201,9 @@
       <c r="D225" s="21">
         <v>41</v>
       </c>
-      <c r="E225" s="21"/>
+      <c r="E225" s="21">
+        <v>27</v>
+      </c>
       <c r="F225" s="21" t="s">
         <v>73</v>
       </c>
@@ -10045,7 +10237,9 @@
       <c r="D226" s="21">
         <v>42</v>
       </c>
-      <c r="E226" s="21"/>
+      <c r="E226" s="21">
+        <v>27</v>
+      </c>
       <c r="F226" s="21" t="s">
         <v>74</v>
       </c>
@@ -10079,7 +10273,9 @@
       <c r="D227" s="21">
         <v>43</v>
       </c>
-      <c r="E227" s="21"/>
+      <c r="E227" s="21">
+        <v>27</v>
+      </c>
       <c r="F227" s="21" t="s">
         <v>75</v>
       </c>
@@ -10113,7 +10309,9 @@
       <c r="D228" s="21">
         <v>44</v>
       </c>
-      <c r="E228" s="21"/>
+      <c r="E228" s="21">
+        <v>27</v>
+      </c>
       <c r="F228" s="21" t="s">
         <v>76</v>
       </c>
@@ -10147,7 +10345,9 @@
       <c r="D229" s="21">
         <v>45</v>
       </c>
-      <c r="E229" s="21"/>
+      <c r="E229" s="21">
+        <v>27</v>
+      </c>
       <c r="F229" s="21" t="s">
         <v>77</v>
       </c>
@@ -10181,7 +10381,9 @@
       <c r="D230" s="21">
         <v>46</v>
       </c>
-      <c r="E230" s="21"/>
+      <c r="E230" s="21">
+        <v>27</v>
+      </c>
       <c r="F230" s="21" t="s">
         <v>78</v>
       </c>
@@ -10215,7 +10417,9 @@
       <c r="D231" s="21">
         <v>47</v>
       </c>
-      <c r="E231" s="21"/>
+      <c r="E231" s="21">
+        <v>27</v>
+      </c>
       <c r="F231" s="21" t="s">
         <v>79</v>
       </c>
@@ -10249,7 +10453,9 @@
       <c r="D232" s="21">
         <v>48</v>
       </c>
-      <c r="E232" s="21"/>
+      <c r="E232" s="21">
+        <v>27</v>
+      </c>
       <c r="F232" s="21" t="s">
         <v>80</v>
       </c>
@@ -10283,7 +10489,9 @@
       <c r="D233" s="21">
         <v>49</v>
       </c>
-      <c r="E233" s="21"/>
+      <c r="E233" s="21">
+        <v>27</v>
+      </c>
       <c r="F233" s="21" t="s">
         <v>81</v>
       </c>
@@ -10317,7 +10525,9 @@
       <c r="D234" s="21">
         <v>50</v>
       </c>
-      <c r="E234" s="21"/>
+      <c r="E234" s="21">
+        <v>27</v>
+      </c>
       <c r="F234" s="21" t="s">
         <v>82</v>
       </c>
@@ -10351,7 +10561,9 @@
       <c r="D235" s="21">
         <v>51</v>
       </c>
-      <c r="E235" s="21"/>
+      <c r="E235" s="21">
+        <v>27</v>
+      </c>
       <c r="F235" s="21" t="s">
         <v>83</v>
       </c>
@@ -10385,7 +10597,9 @@
       <c r="D236" s="21">
         <v>52</v>
       </c>
-      <c r="E236" s="21"/>
+      <c r="E236" s="21">
+        <v>27</v>
+      </c>
       <c r="F236" s="21" t="s">
         <v>84</v>
       </c>
@@ -10419,7 +10633,9 @@
       <c r="D237" s="21">
         <v>53</v>
       </c>
-      <c r="E237" s="21"/>
+      <c r="E237" s="21">
+        <v>27</v>
+      </c>
       <c r="F237" s="21" t="s">
         <v>85</v>
       </c>
@@ -10453,7 +10669,9 @@
       <c r="D238" s="21">
         <v>54</v>
       </c>
-      <c r="E238" s="21"/>
+      <c r="E238" s="21">
+        <v>27</v>
+      </c>
       <c r="F238" s="21" t="s">
         <v>86</v>
       </c>
@@ -10487,7 +10705,9 @@
       <c r="D239" s="21">
         <v>55</v>
       </c>
-      <c r="E239" s="21"/>
+      <c r="E239" s="21">
+        <v>27</v>
+      </c>
       <c r="F239" s="21" t="s">
         <v>87</v>
       </c>
@@ -10521,7 +10741,9 @@
       <c r="D240" s="21">
         <v>56</v>
       </c>
-      <c r="E240" s="21"/>
+      <c r="E240" s="21">
+        <v>27</v>
+      </c>
       <c r="F240" s="21" t="s">
         <v>88</v>
       </c>
@@ -10555,7 +10777,9 @@
       <c r="D241" s="21">
         <v>57</v>
       </c>
-      <c r="E241" s="21"/>
+      <c r="E241" s="21">
+        <v>27</v>
+      </c>
       <c r="F241" s="21" t="s">
         <v>89</v>
       </c>
@@ -10589,7 +10813,9 @@
       <c r="D242" s="21">
         <v>58</v>
       </c>
-      <c r="E242" s="21"/>
+      <c r="E242" s="21">
+        <v>27</v>
+      </c>
       <c r="F242" s="21" t="s">
         <v>90</v>
       </c>
@@ -10623,7 +10849,9 @@
       <c r="D243" s="21">
         <v>59</v>
       </c>
-      <c r="E243" s="21"/>
+      <c r="E243" s="21">
+        <v>27</v>
+      </c>
       <c r="F243" s="21" t="s">
         <v>91</v>
       </c>
@@ -10657,7 +10885,9 @@
       <c r="D244" s="21">
         <v>60</v>
       </c>
-      <c r="E244" s="21"/>
+      <c r="E244" s="21">
+        <v>27</v>
+      </c>
       <c r="F244" s="21" t="s">
         <v>92</v>
       </c>
@@ -11669,7 +11899,9 @@
       <c r="D271" s="17">
         <v>27</v>
       </c>
-      <c r="E271" s="17"/>
+      <c r="E271" s="17">
+        <v>26</v>
+      </c>
       <c r="F271" s="17" t="s">
         <v>58</v>
       </c>
@@ -11701,7 +11933,9 @@
       <c r="D272" s="17">
         <v>28</v>
       </c>
-      <c r="E272" s="17"/>
+      <c r="E272" s="17">
+        <v>26</v>
+      </c>
       <c r="F272" s="17" t="s">
         <v>59</v>
       </c>
@@ -11733,7 +11967,9 @@
       <c r="D273" s="17">
         <v>29</v>
       </c>
-      <c r="E273" s="17"/>
+      <c r="E273" s="17">
+        <v>26</v>
+      </c>
       <c r="F273" s="17" t="s">
         <v>60</v>
       </c>
@@ -11765,7 +12001,9 @@
       <c r="D274" s="17">
         <v>30</v>
       </c>
-      <c r="E274" s="17"/>
+      <c r="E274" s="17">
+        <v>26</v>
+      </c>
       <c r="F274" s="17" t="s">
         <v>61</v>
       </c>
@@ -11797,7 +12035,9 @@
       <c r="D275" s="17">
         <v>31</v>
       </c>
-      <c r="E275" s="17"/>
+      <c r="E275" s="17">
+        <v>26</v>
+      </c>
       <c r="F275" s="17" t="s">
         <v>63</v>
       </c>
@@ -11829,7 +12069,9 @@
       <c r="D276" s="17">
         <v>32</v>
       </c>
-      <c r="E276" s="17"/>
+      <c r="E276" s="17">
+        <v>26</v>
+      </c>
       <c r="F276" s="17" t="s">
         <v>64</v>
       </c>
@@ -11861,7 +12103,9 @@
       <c r="D277" s="17">
         <v>33</v>
       </c>
-      <c r="E277" s="17"/>
+      <c r="E277" s="17">
+        <v>26</v>
+      </c>
       <c r="F277" s="17" t="s">
         <v>65</v>
       </c>
@@ -11893,7 +12137,9 @@
       <c r="D278" s="17">
         <v>34</v>
       </c>
-      <c r="E278" s="17"/>
+      <c r="E278" s="17">
+        <v>26</v>
+      </c>
       <c r="F278" s="17" t="s">
         <v>66</v>
       </c>
@@ -11925,7 +12171,9 @@
       <c r="D279" s="17">
         <v>35</v>
       </c>
-      <c r="E279" s="17"/>
+      <c r="E279" s="17">
+        <v>26</v>
+      </c>
       <c r="F279" s="17" t="s">
         <v>67</v>
       </c>
@@ -11957,7 +12205,9 @@
       <c r="D280" s="17">
         <v>36</v>
       </c>
-      <c r="E280" s="17"/>
+      <c r="E280" s="17">
+        <v>26</v>
+      </c>
       <c r="F280" s="17" t="s">
         <v>68</v>
       </c>
@@ -11989,7 +12239,9 @@
       <c r="D281" s="17">
         <v>37</v>
       </c>
-      <c r="E281" s="17"/>
+      <c r="E281" s="17">
+        <v>26</v>
+      </c>
       <c r="F281" s="17" t="s">
         <v>69</v>
       </c>
@@ -12021,7 +12273,9 @@
       <c r="D282" s="17">
         <v>38</v>
       </c>
-      <c r="E282" s="17"/>
+      <c r="E282" s="17">
+        <v>26</v>
+      </c>
       <c r="F282" s="17" t="s">
         <v>70</v>
       </c>
@@ -12053,7 +12307,9 @@
       <c r="D283" s="17">
         <v>39</v>
       </c>
-      <c r="E283" s="17"/>
+      <c r="E283" s="17">
+        <v>26</v>
+      </c>
       <c r="F283" s="17" t="s">
         <v>71</v>
       </c>
@@ -12085,7 +12341,9 @@
       <c r="D284" s="17">
         <v>40</v>
       </c>
-      <c r="E284" s="17"/>
+      <c r="E284" s="17">
+        <v>26</v>
+      </c>
       <c r="F284" s="17" t="s">
         <v>72</v>
       </c>
@@ -12117,7 +12375,9 @@
       <c r="D285" s="17">
         <v>41</v>
       </c>
-      <c r="E285" s="17"/>
+      <c r="E285" s="17">
+        <v>26</v>
+      </c>
       <c r="F285" s="17" t="s">
         <v>73</v>
       </c>
@@ -12149,7 +12409,9 @@
       <c r="D286" s="17">
         <v>42</v>
       </c>
-      <c r="E286" s="17"/>
+      <c r="E286" s="17">
+        <v>26</v>
+      </c>
       <c r="F286" s="17" t="s">
         <v>74</v>
       </c>
@@ -12181,7 +12443,9 @@
       <c r="D287" s="17">
         <v>43</v>
       </c>
-      <c r="E287" s="17"/>
+      <c r="E287" s="17">
+        <v>26</v>
+      </c>
       <c r="F287" s="17" t="s">
         <v>75</v>
       </c>
@@ -12213,7 +12477,9 @@
       <c r="D288" s="17">
         <v>44</v>
       </c>
-      <c r="E288" s="17"/>
+      <c r="E288" s="17">
+        <v>26</v>
+      </c>
       <c r="F288" s="17" t="s">
         <v>76</v>
       </c>
@@ -12245,7 +12511,9 @@
       <c r="D289" s="17">
         <v>45</v>
       </c>
-      <c r="E289" s="17"/>
+      <c r="E289" s="17">
+        <v>26</v>
+      </c>
       <c r="F289" s="17" t="s">
         <v>77</v>
       </c>
@@ -12277,7 +12545,9 @@
       <c r="D290" s="17">
         <v>46</v>
       </c>
-      <c r="E290" s="17"/>
+      <c r="E290" s="17">
+        <v>26</v>
+      </c>
       <c r="F290" s="17" t="s">
         <v>78</v>
       </c>
@@ -12309,7 +12579,9 @@
       <c r="D291" s="17">
         <v>47</v>
       </c>
-      <c r="E291" s="17"/>
+      <c r="E291" s="17">
+        <v>26</v>
+      </c>
       <c r="F291" s="17" t="s">
         <v>79</v>
       </c>
@@ -12341,7 +12613,9 @@
       <c r="D292" s="17">
         <v>48</v>
       </c>
-      <c r="E292" s="17"/>
+      <c r="E292" s="17">
+        <v>26</v>
+      </c>
       <c r="F292" s="17" t="s">
         <v>80</v>
       </c>
@@ -12373,7 +12647,9 @@
       <c r="D293" s="17">
         <v>49</v>
       </c>
-      <c r="E293" s="17"/>
+      <c r="E293" s="17">
+        <v>26</v>
+      </c>
       <c r="F293" s="17" t="s">
         <v>81</v>
       </c>
@@ -12405,7 +12681,9 @@
       <c r="D294" s="17">
         <v>50</v>
       </c>
-      <c r="E294" s="17"/>
+      <c r="E294" s="17">
+        <v>26</v>
+      </c>
       <c r="F294" s="17" t="s">
         <v>82</v>
       </c>
@@ -12437,7 +12715,9 @@
       <c r="D295" s="17">
         <v>51</v>
       </c>
-      <c r="E295" s="17"/>
+      <c r="E295" s="17">
+        <v>26</v>
+      </c>
       <c r="F295" s="17" t="s">
         <v>83</v>
       </c>
@@ -12469,7 +12749,9 @@
       <c r="D296" s="17">
         <v>52</v>
       </c>
-      <c r="E296" s="17"/>
+      <c r="E296" s="17">
+        <v>26</v>
+      </c>
       <c r="F296" s="17" t="s">
         <v>84</v>
       </c>
@@ -12501,7 +12783,9 @@
       <c r="D297" s="17">
         <v>53</v>
       </c>
-      <c r="E297" s="17"/>
+      <c r="E297" s="17">
+        <v>26</v>
+      </c>
       <c r="F297" s="17" t="s">
         <v>85</v>
       </c>
@@ -12533,7 +12817,9 @@
       <c r="D298" s="17">
         <v>54</v>
       </c>
-      <c r="E298" s="17"/>
+      <c r="E298" s="17">
+        <v>26</v>
+      </c>
       <c r="F298" s="17" t="s">
         <v>86</v>
       </c>
@@ -12565,7 +12851,9 @@
       <c r="D299" s="17">
         <v>55</v>
       </c>
-      <c r="E299" s="17"/>
+      <c r="E299" s="17">
+        <v>26</v>
+      </c>
       <c r="F299" s="17" t="s">
         <v>87</v>
       </c>
@@ -12597,7 +12885,9 @@
       <c r="D300" s="17">
         <v>56</v>
       </c>
-      <c r="E300" s="17"/>
+      <c r="E300" s="17">
+        <v>26</v>
+      </c>
       <c r="F300" s="17" t="s">
         <v>88</v>
       </c>
@@ -12629,7 +12919,9 @@
       <c r="D301" s="17">
         <v>57</v>
       </c>
-      <c r="E301" s="17"/>
+      <c r="E301" s="17">
+        <v>26</v>
+      </c>
       <c r="F301" s="17" t="s">
         <v>89</v>
       </c>
@@ -12661,7 +12953,9 @@
       <c r="D302" s="17">
         <v>58</v>
       </c>
-      <c r="E302" s="17"/>
+      <c r="E302" s="17">
+        <v>26</v>
+      </c>
       <c r="F302" s="17" t="s">
         <v>90</v>
       </c>
@@ -12693,7 +12987,9 @@
       <c r="D303" s="17">
         <v>59</v>
       </c>
-      <c r="E303" s="17"/>
+      <c r="E303" s="17">
+        <v>26</v>
+      </c>
       <c r="F303" s="17" t="s">
         <v>91</v>
       </c>
@@ -12725,7 +13021,9 @@
       <c r="D304" s="17">
         <v>60</v>
       </c>
-      <c r="E304" s="17"/>
+      <c r="E304" s="17">
+        <v>26</v>
+      </c>
       <c r="F304" s="17" t="s">
         <v>92</v>
       </c>
@@ -13931,7 +14229,9 @@
       <c r="D335" s="21">
         <v>31</v>
       </c>
-      <c r="E335" s="21"/>
+      <c r="E335" s="21">
+        <v>30</v>
+      </c>
       <c r="F335" s="21" t="s">
         <v>63</v>
       </c>
@@ -13965,7 +14265,9 @@
       <c r="D336" s="21">
         <v>32</v>
       </c>
-      <c r="E336" s="21"/>
+      <c r="E336" s="21">
+        <v>30</v>
+      </c>
       <c r="F336" s="21" t="s">
         <v>64</v>
       </c>
@@ -13999,7 +14301,9 @@
       <c r="D337" s="21">
         <v>33</v>
       </c>
-      <c r="E337" s="21"/>
+      <c r="E337" s="21">
+        <v>30</v>
+      </c>
       <c r="F337" s="21" t="s">
         <v>65</v>
       </c>
@@ -14033,7 +14337,9 @@
       <c r="D338" s="21">
         <v>34</v>
       </c>
-      <c r="E338" s="21"/>
+      <c r="E338" s="21">
+        <v>30</v>
+      </c>
       <c r="F338" s="21" t="s">
         <v>66</v>
       </c>
@@ -14067,7 +14373,9 @@
       <c r="D339" s="21">
         <v>35</v>
       </c>
-      <c r="E339" s="21"/>
+      <c r="E339" s="21">
+        <v>30</v>
+      </c>
       <c r="F339" s="21" t="s">
         <v>67</v>
       </c>
@@ -14101,7 +14409,9 @@
       <c r="D340" s="21">
         <v>36</v>
       </c>
-      <c r="E340" s="21"/>
+      <c r="E340" s="21">
+        <v>30</v>
+      </c>
       <c r="F340" s="21" t="s">
         <v>68</v>
       </c>
@@ -14135,7 +14445,9 @@
       <c r="D341" s="21">
         <v>37</v>
       </c>
-      <c r="E341" s="21"/>
+      <c r="E341" s="21">
+        <v>30</v>
+      </c>
       <c r="F341" s="21" t="s">
         <v>69</v>
       </c>
@@ -14169,7 +14481,9 @@
       <c r="D342" s="21">
         <v>38</v>
       </c>
-      <c r="E342" s="21"/>
+      <c r="E342" s="21">
+        <v>30</v>
+      </c>
       <c r="F342" s="21" t="s">
         <v>70</v>
       </c>
@@ -14203,7 +14517,9 @@
       <c r="D343" s="21">
         <v>39</v>
       </c>
-      <c r="E343" s="21"/>
+      <c r="E343" s="21">
+        <v>30</v>
+      </c>
       <c r="F343" s="21" t="s">
         <v>71</v>
       </c>
@@ -14237,7 +14553,9 @@
       <c r="D344" s="21">
         <v>40</v>
       </c>
-      <c r="E344" s="21"/>
+      <c r="E344" s="21">
+        <v>30</v>
+      </c>
       <c r="F344" s="21" t="s">
         <v>72</v>
       </c>
@@ -14271,7 +14589,9 @@
       <c r="D345" s="21">
         <v>41</v>
       </c>
-      <c r="E345" s="21"/>
+      <c r="E345" s="21">
+        <v>30</v>
+      </c>
       <c r="F345" s="21" t="s">
         <v>73</v>
       </c>
@@ -14305,7 +14625,9 @@
       <c r="D346" s="21">
         <v>42</v>
       </c>
-      <c r="E346" s="21"/>
+      <c r="E346" s="21">
+        <v>30</v>
+      </c>
       <c r="F346" s="21" t="s">
         <v>74</v>
       </c>
@@ -14339,7 +14661,9 @@
       <c r="D347" s="21">
         <v>43</v>
       </c>
-      <c r="E347" s="21"/>
+      <c r="E347" s="21">
+        <v>30</v>
+      </c>
       <c r="F347" s="21" t="s">
         <v>75</v>
       </c>
@@ -14373,7 +14697,9 @@
       <c r="D348" s="21">
         <v>44</v>
       </c>
-      <c r="E348" s="21"/>
+      <c r="E348" s="21">
+        <v>30</v>
+      </c>
       <c r="F348" s="21" t="s">
         <v>76</v>
       </c>
@@ -14407,7 +14733,9 @@
       <c r="D349" s="21">
         <v>45</v>
       </c>
-      <c r="E349" s="21"/>
+      <c r="E349" s="21">
+        <v>30</v>
+      </c>
       <c r="F349" s="21" t="s">
         <v>77</v>
       </c>
@@ -14441,7 +14769,9 @@
       <c r="D350" s="21">
         <v>46</v>
       </c>
-      <c r="E350" s="21"/>
+      <c r="E350" s="21">
+        <v>30</v>
+      </c>
       <c r="F350" s="21" t="s">
         <v>78</v>
       </c>
@@ -14475,7 +14805,9 @@
       <c r="D351" s="21">
         <v>47</v>
       </c>
-      <c r="E351" s="21"/>
+      <c r="E351" s="21">
+        <v>30</v>
+      </c>
       <c r="F351" s="21" t="s">
         <v>79</v>
       </c>
@@ -14509,7 +14841,9 @@
       <c r="D352" s="21">
         <v>48</v>
       </c>
-      <c r="E352" s="21"/>
+      <c r="E352" s="21">
+        <v>30</v>
+      </c>
       <c r="F352" s="21" t="s">
         <v>80</v>
       </c>
@@ -14543,7 +14877,9 @@
       <c r="D353" s="21">
         <v>49</v>
       </c>
-      <c r="E353" s="21"/>
+      <c r="E353" s="21">
+        <v>30</v>
+      </c>
       <c r="F353" s="21" t="s">
         <v>81</v>
       </c>
@@ -14577,7 +14913,9 @@
       <c r="D354" s="21">
         <v>50</v>
       </c>
-      <c r="E354" s="21"/>
+      <c r="E354" s="21">
+        <v>30</v>
+      </c>
       <c r="F354" s="21" t="s">
         <v>82</v>
       </c>
@@ -14611,7 +14949,9 @@
       <c r="D355" s="21">
         <v>51</v>
       </c>
-      <c r="E355" s="21"/>
+      <c r="E355" s="21">
+        <v>30</v>
+      </c>
       <c r="F355" s="21" t="s">
         <v>83</v>
       </c>
@@ -14645,7 +14985,9 @@
       <c r="D356" s="21">
         <v>52</v>
       </c>
-      <c r="E356" s="21"/>
+      <c r="E356" s="21">
+        <v>30</v>
+      </c>
       <c r="F356" s="21" t="s">
         <v>84</v>
       </c>
@@ -14679,7 +15021,9 @@
       <c r="D357" s="21">
         <v>53</v>
       </c>
-      <c r="E357" s="21"/>
+      <c r="E357" s="21">
+        <v>30</v>
+      </c>
       <c r="F357" s="21" t="s">
         <v>85</v>
       </c>
@@ -14713,7 +15057,9 @@
       <c r="D358" s="21">
         <v>54</v>
       </c>
-      <c r="E358" s="21"/>
+      <c r="E358" s="21">
+        <v>30</v>
+      </c>
       <c r="F358" s="21" t="s">
         <v>86</v>
       </c>
@@ -14747,7 +15093,9 @@
       <c r="D359" s="21">
         <v>55</v>
       </c>
-      <c r="E359" s="21"/>
+      <c r="E359" s="21">
+        <v>30</v>
+      </c>
       <c r="F359" s="21" t="s">
         <v>87</v>
       </c>
@@ -14781,7 +15129,9 @@
       <c r="D360" s="21">
         <v>56</v>
       </c>
-      <c r="E360" s="21"/>
+      <c r="E360" s="21">
+        <v>30</v>
+      </c>
       <c r="F360" s="21" t="s">
         <v>88</v>
       </c>
@@ -14815,7 +15165,9 @@
       <c r="D361" s="21">
         <v>57</v>
       </c>
-      <c r="E361" s="21"/>
+      <c r="E361" s="21">
+        <v>30</v>
+      </c>
       <c r="F361" s="21" t="s">
         <v>89</v>
       </c>
@@ -14849,7 +15201,9 @@
       <c r="D362" s="21">
         <v>58</v>
       </c>
-      <c r="E362" s="21"/>
+      <c r="E362" s="21">
+        <v>30</v>
+      </c>
       <c r="F362" s="21" t="s">
         <v>90</v>
       </c>
@@ -14883,7 +15237,9 @@
       <c r="D363" s="21">
         <v>59</v>
       </c>
-      <c r="E363" s="21"/>
+      <c r="E363" s="21">
+        <v>30</v>
+      </c>
       <c r="F363" s="21" t="s">
         <v>91</v>
       </c>
@@ -14917,7 +15273,9 @@
       <c r="D364" s="21">
         <v>60</v>
       </c>
-      <c r="E364" s="21"/>
+      <c r="E364" s="21">
+        <v>30</v>
+      </c>
       <c r="F364" s="21" t="s">
         <v>92</v>
       </c>
@@ -15977,7 +16335,9 @@
       <c r="D391" s="17">
         <v>27</v>
       </c>
-      <c r="E391" s="17"/>
+      <c r="E391" s="17">
+        <v>26</v>
+      </c>
       <c r="F391" s="17" t="s">
         <v>58</v>
       </c>
@@ -16009,7 +16369,9 @@
       <c r="D392" s="17">
         <v>28</v>
       </c>
-      <c r="E392" s="17"/>
+      <c r="E392" s="17">
+        <v>26</v>
+      </c>
       <c r="F392" s="17" t="s">
         <v>59</v>
       </c>
@@ -16041,7 +16403,9 @@
       <c r="D393" s="17">
         <v>29</v>
       </c>
-      <c r="E393" s="17"/>
+      <c r="E393" s="17">
+        <v>26</v>
+      </c>
       <c r="F393" s="17" t="s">
         <v>60</v>
       </c>
@@ -16073,7 +16437,9 @@
       <c r="D394" s="17">
         <v>30</v>
       </c>
-      <c r="E394" s="17"/>
+      <c r="E394" s="17">
+        <v>26</v>
+      </c>
       <c r="F394" s="17" t="s">
         <v>61</v>
       </c>
@@ -16105,7 +16471,9 @@
       <c r="D395" s="17">
         <v>31</v>
       </c>
-      <c r="E395" s="17"/>
+      <c r="E395" s="17">
+        <v>26</v>
+      </c>
       <c r="F395" s="17" t="s">
         <v>63</v>
       </c>
@@ -16137,7 +16505,9 @@
       <c r="D396" s="17">
         <v>32</v>
       </c>
-      <c r="E396" s="17"/>
+      <c r="E396" s="17">
+        <v>26</v>
+      </c>
       <c r="F396" s="17" t="s">
         <v>64</v>
       </c>
@@ -16169,7 +16539,9 @@
       <c r="D397" s="17">
         <v>33</v>
       </c>
-      <c r="E397" s="17"/>
+      <c r="E397" s="17">
+        <v>26</v>
+      </c>
       <c r="F397" s="17" t="s">
         <v>65</v>
       </c>
@@ -16201,7 +16573,9 @@
       <c r="D398" s="17">
         <v>34</v>
       </c>
-      <c r="E398" s="17"/>
+      <c r="E398" s="17">
+        <v>26</v>
+      </c>
       <c r="F398" s="17" t="s">
         <v>66</v>
       </c>
@@ -16233,7 +16607,9 @@
       <c r="D399" s="17">
         <v>35</v>
       </c>
-      <c r="E399" s="17"/>
+      <c r="E399" s="17">
+        <v>26</v>
+      </c>
       <c r="F399" s="17" t="s">
         <v>67</v>
       </c>
@@ -16265,7 +16641,9 @@
       <c r="D400" s="17">
         <v>36</v>
       </c>
-      <c r="E400" s="17"/>
+      <c r="E400" s="17">
+        <v>26</v>
+      </c>
       <c r="F400" s="17" t="s">
         <v>68</v>
       </c>
@@ -16297,7 +16675,9 @@
       <c r="D401" s="17">
         <v>37</v>
       </c>
-      <c r="E401" s="17"/>
+      <c r="E401" s="17">
+        <v>26</v>
+      </c>
       <c r="F401" s="17" t="s">
         <v>69</v>
       </c>
@@ -16329,7 +16709,9 @@
       <c r="D402" s="17">
         <v>38</v>
       </c>
-      <c r="E402" s="17"/>
+      <c r="E402" s="17">
+        <v>26</v>
+      </c>
       <c r="F402" s="17" t="s">
         <v>70</v>
       </c>
@@ -16361,7 +16743,9 @@
       <c r="D403" s="17">
         <v>39</v>
       </c>
-      <c r="E403" s="17"/>
+      <c r="E403" s="17">
+        <v>26</v>
+      </c>
       <c r="F403" s="17" t="s">
         <v>71</v>
       </c>
@@ -16393,7 +16777,9 @@
       <c r="D404" s="17">
         <v>40</v>
       </c>
-      <c r="E404" s="17"/>
+      <c r="E404" s="17">
+        <v>26</v>
+      </c>
       <c r="F404" s="17" t="s">
         <v>72</v>
       </c>
@@ -16425,7 +16811,9 @@
       <c r="D405" s="17">
         <v>41</v>
       </c>
-      <c r="E405" s="17"/>
+      <c r="E405" s="17">
+        <v>26</v>
+      </c>
       <c r="F405" s="17" t="s">
         <v>73</v>
       </c>
@@ -16457,7 +16845,9 @@
       <c r="D406" s="17">
         <v>42</v>
       </c>
-      <c r="E406" s="17"/>
+      <c r="E406" s="17">
+        <v>26</v>
+      </c>
       <c r="F406" s="17" t="s">
         <v>74</v>
       </c>
@@ -16489,7 +16879,9 @@
       <c r="D407" s="17">
         <v>43</v>
       </c>
-      <c r="E407" s="17"/>
+      <c r="E407" s="17">
+        <v>26</v>
+      </c>
       <c r="F407" s="17" t="s">
         <v>75</v>
       </c>
@@ -16521,7 +16913,9 @@
       <c r="D408" s="17">
         <v>44</v>
       </c>
-      <c r="E408" s="17"/>
+      <c r="E408" s="17">
+        <v>26</v>
+      </c>
       <c r="F408" s="17" t="s">
         <v>76</v>
       </c>
@@ -16553,7 +16947,9 @@
       <c r="D409" s="17">
         <v>45</v>
       </c>
-      <c r="E409" s="17"/>
+      <c r="E409" s="17">
+        <v>26</v>
+      </c>
       <c r="F409" s="17" t="s">
         <v>77</v>
       </c>
@@ -16585,7 +16981,9 @@
       <c r="D410" s="17">
         <v>46</v>
       </c>
-      <c r="E410" s="17"/>
+      <c r="E410" s="17">
+        <v>26</v>
+      </c>
       <c r="F410" s="17" t="s">
         <v>78</v>
       </c>
@@ -16617,7 +17015,9 @@
       <c r="D411" s="17">
         <v>47</v>
       </c>
-      <c r="E411" s="17"/>
+      <c r="E411" s="17">
+        <v>26</v>
+      </c>
       <c r="F411" s="17" t="s">
         <v>79</v>
       </c>
@@ -16649,7 +17049,9 @@
       <c r="D412" s="17">
         <v>48</v>
       </c>
-      <c r="E412" s="17"/>
+      <c r="E412" s="17">
+        <v>26</v>
+      </c>
       <c r="F412" s="17" t="s">
         <v>80</v>
       </c>
@@ -16681,7 +17083,9 @@
       <c r="D413" s="17">
         <v>49</v>
       </c>
-      <c r="E413" s="17"/>
+      <c r="E413" s="17">
+        <v>26</v>
+      </c>
       <c r="F413" s="17" t="s">
         <v>81</v>
       </c>
@@ -16713,7 +17117,9 @@
       <c r="D414" s="17">
         <v>50</v>
       </c>
-      <c r="E414" s="17"/>
+      <c r="E414" s="17">
+        <v>26</v>
+      </c>
       <c r="F414" s="17" t="s">
         <v>82</v>
       </c>
@@ -16745,7 +17151,9 @@
       <c r="D415" s="17">
         <v>51</v>
       </c>
-      <c r="E415" s="17"/>
+      <c r="E415" s="17">
+        <v>26</v>
+      </c>
       <c r="F415" s="17" t="s">
         <v>83</v>
       </c>
@@ -16777,7 +17185,9 @@
       <c r="D416" s="17">
         <v>52</v>
       </c>
-      <c r="E416" s="17"/>
+      <c r="E416" s="17">
+        <v>26</v>
+      </c>
       <c r="F416" s="17" t="s">
         <v>84</v>
       </c>
@@ -16809,7 +17219,9 @@
       <c r="D417" s="17">
         <v>53</v>
       </c>
-      <c r="E417" s="17"/>
+      <c r="E417" s="17">
+        <v>26</v>
+      </c>
       <c r="F417" s="17" t="s">
         <v>85</v>
       </c>
@@ -16841,7 +17253,9 @@
       <c r="D418" s="17">
         <v>54</v>
       </c>
-      <c r="E418" s="17"/>
+      <c r="E418" s="17">
+        <v>26</v>
+      </c>
       <c r="F418" s="17" t="s">
         <v>86</v>
       </c>
@@ -16873,7 +17287,9 @@
       <c r="D419" s="17">
         <v>55</v>
       </c>
-      <c r="E419" s="17"/>
+      <c r="E419" s="17">
+        <v>26</v>
+      </c>
       <c r="F419" s="17" t="s">
         <v>87</v>
       </c>
@@ -16905,7 +17321,9 @@
       <c r="D420" s="17">
         <v>56</v>
       </c>
-      <c r="E420" s="17"/>
+      <c r="E420" s="17">
+        <v>26</v>
+      </c>
       <c r="F420" s="17" t="s">
         <v>88</v>
       </c>
@@ -16937,7 +17355,9 @@
       <c r="D421" s="17">
         <v>57</v>
       </c>
-      <c r="E421" s="17"/>
+      <c r="E421" s="17">
+        <v>26</v>
+      </c>
       <c r="F421" s="17" t="s">
         <v>89</v>
       </c>
@@ -16969,7 +17389,9 @@
       <c r="D422" s="17">
         <v>58</v>
       </c>
-      <c r="E422" s="17"/>
+      <c r="E422" s="17">
+        <v>26</v>
+      </c>
       <c r="F422" s="17" t="s">
         <v>90</v>
       </c>
@@ -17001,7 +17423,9 @@
       <c r="D423" s="17">
         <v>59</v>
       </c>
-      <c r="E423" s="17"/>
+      <c r="E423" s="17">
+        <v>26</v>
+      </c>
       <c r="F423" s="17" t="s">
         <v>91</v>
       </c>
@@ -17033,7 +17457,9 @@
       <c r="D424" s="17">
         <v>60</v>
       </c>
-      <c r="E424" s="17"/>
+      <c r="E424" s="17">
+        <v>26</v>
+      </c>
       <c r="F424" s="17" t="s">
         <v>92</v>
       </c>
@@ -17943,7 +18369,9 @@
       <c r="D447" s="21">
         <v>23</v>
       </c>
-      <c r="E447" s="21"/>
+      <c r="E447" s="21">
+        <v>22</v>
+      </c>
       <c r="F447" s="21" t="s">
         <v>54</v>
       </c>
@@ -17981,7 +18409,9 @@
       <c r="D448" s="21">
         <v>24</v>
       </c>
-      <c r="E448" s="21"/>
+      <c r="E448" s="21">
+        <v>22</v>
+      </c>
       <c r="F448" s="21" t="s">
         <v>55</v>
       </c>
@@ -18019,7 +18449,9 @@
       <c r="D449" s="21">
         <v>25</v>
       </c>
-      <c r="E449" s="21"/>
+      <c r="E449" s="21">
+        <v>22</v>
+      </c>
       <c r="F449" s="21" t="s">
         <v>56</v>
       </c>
@@ -18053,7 +18485,9 @@
       <c r="D450" s="21">
         <v>26</v>
       </c>
-      <c r="E450" s="21"/>
+      <c r="E450" s="21">
+        <v>22</v>
+      </c>
       <c r="F450" s="21" t="s">
         <v>57</v>
       </c>
@@ -18087,7 +18521,9 @@
       <c r="D451" s="21">
         <v>27</v>
       </c>
-      <c r="E451" s="21"/>
+      <c r="E451" s="21">
+        <v>22</v>
+      </c>
       <c r="F451" s="21" t="s">
         <v>58</v>
       </c>
@@ -18121,7 +18557,9 @@
       <c r="D452" s="21">
         <v>28</v>
       </c>
-      <c r="E452" s="21"/>
+      <c r="E452" s="21">
+        <v>22</v>
+      </c>
       <c r="F452" s="21" t="s">
         <v>59</v>
       </c>
@@ -18155,7 +18593,9 @@
       <c r="D453" s="21">
         <v>29</v>
       </c>
-      <c r="E453" s="21"/>
+      <c r="E453" s="21">
+        <v>22</v>
+      </c>
       <c r="F453" s="21" t="s">
         <v>60</v>
       </c>
@@ -18189,7 +18629,9 @@
       <c r="D454" s="21">
         <v>30</v>
       </c>
-      <c r="E454" s="21"/>
+      <c r="E454" s="21">
+        <v>22</v>
+      </c>
       <c r="F454" s="21" t="s">
         <v>61</v>
       </c>
@@ -18223,7 +18665,9 @@
       <c r="D455" s="21">
         <v>31</v>
       </c>
-      <c r="E455" s="21"/>
+      <c r="E455" s="21">
+        <v>22</v>
+      </c>
       <c r="F455" s="21" t="s">
         <v>63</v>
       </c>
@@ -18257,7 +18701,9 @@
       <c r="D456" s="21">
         <v>32</v>
       </c>
-      <c r="E456" s="21"/>
+      <c r="E456" s="21">
+        <v>22</v>
+      </c>
       <c r="F456" s="21" t="s">
         <v>64</v>
       </c>
@@ -18291,7 +18737,9 @@
       <c r="D457" s="21">
         <v>33</v>
       </c>
-      <c r="E457" s="21"/>
+      <c r="E457" s="21">
+        <v>22</v>
+      </c>
       <c r="F457" s="21" t="s">
         <v>65</v>
       </c>
@@ -18325,7 +18773,9 @@
       <c r="D458" s="21">
         <v>34</v>
       </c>
-      <c r="E458" s="21"/>
+      <c r="E458" s="21">
+        <v>22</v>
+      </c>
       <c r="F458" s="21" t="s">
         <v>66</v>
       </c>
@@ -18359,7 +18809,9 @@
       <c r="D459" s="21">
         <v>35</v>
       </c>
-      <c r="E459" s="21"/>
+      <c r="E459" s="21">
+        <v>22</v>
+      </c>
       <c r="F459" s="21" t="s">
         <v>67</v>
       </c>
@@ -18393,7 +18845,9 @@
       <c r="D460" s="21">
         <v>36</v>
       </c>
-      <c r="E460" s="21"/>
+      <c r="E460" s="21">
+        <v>22</v>
+      </c>
       <c r="F460" s="21" t="s">
         <v>68</v>
       </c>
@@ -18427,7 +18881,9 @@
       <c r="D461" s="21">
         <v>37</v>
       </c>
-      <c r="E461" s="21"/>
+      <c r="E461" s="21">
+        <v>22</v>
+      </c>
       <c r="F461" s="21" t="s">
         <v>69</v>
       </c>
@@ -18461,7 +18917,9 @@
       <c r="D462" s="21">
         <v>38</v>
       </c>
-      <c r="E462" s="21"/>
+      <c r="E462" s="21">
+        <v>22</v>
+      </c>
       <c r="F462" s="21" t="s">
         <v>70</v>
       </c>
@@ -18495,7 +18953,9 @@
       <c r="D463" s="21">
         <v>39</v>
       </c>
-      <c r="E463" s="21"/>
+      <c r="E463" s="21">
+        <v>22</v>
+      </c>
       <c r="F463" s="21" t="s">
         <v>71</v>
       </c>
@@ -18529,7 +18989,9 @@
       <c r="D464" s="21">
         <v>40</v>
       </c>
-      <c r="E464" s="21"/>
+      <c r="E464" s="21">
+        <v>22</v>
+      </c>
       <c r="F464" s="21" t="s">
         <v>72</v>
       </c>
@@ -18563,7 +19025,9 @@
       <c r="D465" s="21">
         <v>41</v>
       </c>
-      <c r="E465" s="21"/>
+      <c r="E465" s="21">
+        <v>22</v>
+      </c>
       <c r="F465" s="21" t="s">
         <v>73</v>
       </c>
@@ -18597,7 +19061,9 @@
       <c r="D466" s="21">
         <v>42</v>
       </c>
-      <c r="E466" s="21"/>
+      <c r="E466" s="21">
+        <v>22</v>
+      </c>
       <c r="F466" s="21" t="s">
         <v>74</v>
       </c>
@@ -18631,7 +19097,9 @@
       <c r="D467" s="21">
         <v>43</v>
       </c>
-      <c r="E467" s="21"/>
+      <c r="E467" s="21">
+        <v>22</v>
+      </c>
       <c r="F467" s="21" t="s">
         <v>75</v>
       </c>
@@ -18665,7 +19133,9 @@
       <c r="D468" s="21">
         <v>44</v>
       </c>
-      <c r="E468" s="21"/>
+      <c r="E468" s="21">
+        <v>22</v>
+      </c>
       <c r="F468" s="21" t="s">
         <v>76</v>
       </c>
@@ -18699,7 +19169,9 @@
       <c r="D469" s="21">
         <v>45</v>
       </c>
-      <c r="E469" s="21"/>
+      <c r="E469" s="21">
+        <v>22</v>
+      </c>
       <c r="F469" s="21" t="s">
         <v>77</v>
       </c>
@@ -18733,7 +19205,9 @@
       <c r="D470" s="21">
         <v>46</v>
       </c>
-      <c r="E470" s="21"/>
+      <c r="E470" s="21">
+        <v>22</v>
+      </c>
       <c r="F470" s="21" t="s">
         <v>78</v>
       </c>
@@ -18767,7 +19241,9 @@
       <c r="D471" s="21">
         <v>47</v>
       </c>
-      <c r="E471" s="21"/>
+      <c r="E471" s="21">
+        <v>22</v>
+      </c>
       <c r="F471" s="21" t="s">
         <v>79</v>
       </c>
@@ -18801,7 +19277,9 @@
       <c r="D472" s="21">
         <v>48</v>
       </c>
-      <c r="E472" s="21"/>
+      <c r="E472" s="21">
+        <v>22</v>
+      </c>
       <c r="F472" s="21" t="s">
         <v>80</v>
       </c>
@@ -18835,7 +19313,9 @@
       <c r="D473" s="21">
         <v>49</v>
       </c>
-      <c r="E473" s="21"/>
+      <c r="E473" s="21">
+        <v>22</v>
+      </c>
       <c r="F473" s="21" t="s">
         <v>81</v>
       </c>
@@ -18869,7 +19349,9 @@
       <c r="D474" s="21">
         <v>50</v>
       </c>
-      <c r="E474" s="21"/>
+      <c r="E474" s="21">
+        <v>22</v>
+      </c>
       <c r="F474" s="21" t="s">
         <v>82</v>
       </c>
@@ -18903,7 +19385,9 @@
       <c r="D475" s="21">
         <v>51</v>
       </c>
-      <c r="E475" s="21"/>
+      <c r="E475" s="21">
+        <v>22</v>
+      </c>
       <c r="F475" s="21" t="s">
         <v>83</v>
       </c>
@@ -18937,7 +19421,9 @@
       <c r="D476" s="21">
         <v>52</v>
       </c>
-      <c r="E476" s="21"/>
+      <c r="E476" s="21">
+        <v>22</v>
+      </c>
       <c r="F476" s="21" t="s">
         <v>84</v>
       </c>
@@ -18971,7 +19457,9 @@
       <c r="D477" s="21">
         <v>53</v>
       </c>
-      <c r="E477" s="21"/>
+      <c r="E477" s="21">
+        <v>22</v>
+      </c>
       <c r="F477" s="21" t="s">
         <v>85</v>
       </c>
@@ -19005,7 +19493,9 @@
       <c r="D478" s="21">
         <v>54</v>
       </c>
-      <c r="E478" s="21"/>
+      <c r="E478" s="21">
+        <v>22</v>
+      </c>
       <c r="F478" s="21" t="s">
         <v>86</v>
       </c>
@@ -19039,7 +19529,9 @@
       <c r="D479" s="21">
         <v>55</v>
       </c>
-      <c r="E479" s="21"/>
+      <c r="E479" s="21">
+        <v>22</v>
+      </c>
       <c r="F479" s="21" t="s">
         <v>87</v>
       </c>
@@ -19073,7 +19565,9 @@
       <c r="D480" s="21">
         <v>56</v>
       </c>
-      <c r="E480" s="21"/>
+      <c r="E480" s="21">
+        <v>22</v>
+      </c>
       <c r="F480" s="21" t="s">
         <v>88</v>
       </c>
@@ -19107,7 +19601,9 @@
       <c r="D481" s="21">
         <v>57</v>
       </c>
-      <c r="E481" s="21"/>
+      <c r="E481" s="21">
+        <v>22</v>
+      </c>
       <c r="F481" s="21" t="s">
         <v>89</v>
       </c>
@@ -19141,7 +19637,9 @@
       <c r="D482" s="21">
         <v>58</v>
       </c>
-      <c r="E482" s="21"/>
+      <c r="E482" s="21">
+        <v>22</v>
+      </c>
       <c r="F482" s="21" t="s">
         <v>90</v>
       </c>
@@ -19175,7 +19673,9 @@
       <c r="D483" s="21">
         <v>59</v>
       </c>
-      <c r="E483" s="21"/>
+      <c r="E483" s="21">
+        <v>22</v>
+      </c>
       <c r="F483" s="21" t="s">
         <v>91</v>
       </c>
@@ -19209,7 +19709,9 @@
       <c r="D484" s="21">
         <v>60</v>
       </c>
-      <c r="E484" s="21"/>
+      <c r="E484" s="21">
+        <v>22</v>
+      </c>
       <c r="F484" s="21" t="s">
         <v>92</v>
       </c>
@@ -20303,7 +20805,9 @@
       <c r="D512" s="17">
         <v>28</v>
       </c>
-      <c r="E512" s="17"/>
+      <c r="E512" s="17">
+        <v>27</v>
+      </c>
       <c r="F512" s="17" t="s">
         <v>59</v>
       </c>
@@ -20335,7 +20839,9 @@
       <c r="D513" s="17">
         <v>29</v>
       </c>
-      <c r="E513" s="17"/>
+      <c r="E513" s="17">
+        <v>27</v>
+      </c>
       <c r="F513" s="17" t="s">
         <v>60</v>
       </c>
@@ -20367,7 +20873,9 @@
       <c r="D514" s="17">
         <v>30</v>
       </c>
-      <c r="E514" s="17"/>
+      <c r="E514" s="17">
+        <v>27</v>
+      </c>
       <c r="F514" s="17" t="s">
         <v>61</v>
       </c>
@@ -20399,7 +20907,9 @@
       <c r="D515" s="17">
         <v>31</v>
       </c>
-      <c r="E515" s="17"/>
+      <c r="E515" s="17">
+        <v>27</v>
+      </c>
       <c r="F515" s="17" t="s">
         <v>63</v>
       </c>
@@ -20431,7 +20941,9 @@
       <c r="D516" s="17">
         <v>32</v>
       </c>
-      <c r="E516" s="17"/>
+      <c r="E516" s="17">
+        <v>27</v>
+      </c>
       <c r="F516" s="17" t="s">
         <v>64</v>
       </c>
@@ -20463,7 +20975,9 @@
       <c r="D517" s="17">
         <v>33</v>
       </c>
-      <c r="E517" s="17"/>
+      <c r="E517" s="17">
+        <v>27</v>
+      </c>
       <c r="F517" s="17" t="s">
         <v>65</v>
       </c>
@@ -20495,7 +21009,9 @@
       <c r="D518" s="17">
         <v>34</v>
       </c>
-      <c r="E518" s="17"/>
+      <c r="E518" s="17">
+        <v>27</v>
+      </c>
       <c r="F518" s="17" t="s">
         <v>66</v>
       </c>
@@ -20527,7 +21043,9 @@
       <c r="D519" s="17">
         <v>35</v>
       </c>
-      <c r="E519" s="17"/>
+      <c r="E519" s="17">
+        <v>27</v>
+      </c>
       <c r="F519" s="17" t="s">
         <v>67</v>
       </c>
@@ -20559,7 +21077,9 @@
       <c r="D520" s="17">
         <v>36</v>
       </c>
-      <c r="E520" s="17"/>
+      <c r="E520" s="17">
+        <v>27</v>
+      </c>
       <c r="F520" s="17" t="s">
         <v>68</v>
       </c>
@@ -20591,7 +21111,9 @@
       <c r="D521" s="17">
         <v>37</v>
       </c>
-      <c r="E521" s="17"/>
+      <c r="E521" s="17">
+        <v>27</v>
+      </c>
       <c r="F521" s="17" t="s">
         <v>69</v>
       </c>
@@ -20623,7 +21145,9 @@
       <c r="D522" s="17">
         <v>38</v>
       </c>
-      <c r="E522" s="17"/>
+      <c r="E522" s="17">
+        <v>27</v>
+      </c>
       <c r="F522" s="17" t="s">
         <v>70</v>
       </c>
@@ -20655,7 +21179,9 @@
       <c r="D523" s="17">
         <v>39</v>
       </c>
-      <c r="E523" s="17"/>
+      <c r="E523" s="17">
+        <v>27</v>
+      </c>
       <c r="F523" s="17" t="s">
         <v>71</v>
       </c>
@@ -20687,7 +21213,9 @@
       <c r="D524" s="17">
         <v>40</v>
       </c>
-      <c r="E524" s="17"/>
+      <c r="E524" s="17">
+        <v>27</v>
+      </c>
       <c r="F524" s="17" t="s">
         <v>72</v>
       </c>
@@ -20719,7 +21247,9 @@
       <c r="D525" s="17">
         <v>41</v>
       </c>
-      <c r="E525" s="17"/>
+      <c r="E525" s="17">
+        <v>27</v>
+      </c>
       <c r="F525" s="17" t="s">
         <v>73</v>
       </c>
@@ -20751,7 +21281,9 @@
       <c r="D526" s="17">
         <v>42</v>
       </c>
-      <c r="E526" s="17"/>
+      <c r="E526" s="17">
+        <v>27</v>
+      </c>
       <c r="F526" s="17" t="s">
         <v>74</v>
       </c>
@@ -20783,7 +21315,9 @@
       <c r="D527" s="17">
         <v>43</v>
       </c>
-      <c r="E527" s="17"/>
+      <c r="E527" s="17">
+        <v>27</v>
+      </c>
       <c r="F527" s="17" t="s">
         <v>75</v>
       </c>
@@ -20815,7 +21349,9 @@
       <c r="D528" s="17">
         <v>44</v>
       </c>
-      <c r="E528" s="17"/>
+      <c r="E528" s="17">
+        <v>27</v>
+      </c>
       <c r="F528" s="17" t="s">
         <v>76</v>
       </c>
@@ -20847,7 +21383,9 @@
       <c r="D529" s="17">
         <v>45</v>
       </c>
-      <c r="E529" s="17"/>
+      <c r="E529" s="17">
+        <v>27</v>
+      </c>
       <c r="F529" s="17" t="s">
         <v>77</v>
       </c>
@@ -20879,7 +21417,9 @@
       <c r="D530" s="17">
         <v>46</v>
       </c>
-      <c r="E530" s="17"/>
+      <c r="E530" s="17">
+        <v>27</v>
+      </c>
       <c r="F530" s="17" t="s">
         <v>78</v>
       </c>
@@ -20911,7 +21451,9 @@
       <c r="D531" s="17">
         <v>47</v>
       </c>
-      <c r="E531" s="17"/>
+      <c r="E531" s="17">
+        <v>27</v>
+      </c>
       <c r="F531" s="17" t="s">
         <v>79</v>
       </c>
@@ -20943,7 +21485,9 @@
       <c r="D532" s="17">
         <v>48</v>
       </c>
-      <c r="E532" s="17"/>
+      <c r="E532" s="17">
+        <v>27</v>
+      </c>
       <c r="F532" s="17" t="s">
         <v>80</v>
       </c>
@@ -20975,7 +21519,9 @@
       <c r="D533" s="17">
         <v>49</v>
       </c>
-      <c r="E533" s="17"/>
+      <c r="E533" s="17">
+        <v>27</v>
+      </c>
       <c r="F533" s="17" t="s">
         <v>81</v>
       </c>
@@ -21007,7 +21553,9 @@
       <c r="D534" s="17">
         <v>50</v>
       </c>
-      <c r="E534" s="17"/>
+      <c r="E534" s="17">
+        <v>27</v>
+      </c>
       <c r="F534" s="17" t="s">
         <v>82</v>
       </c>
@@ -21039,7 +21587,9 @@
       <c r="D535" s="17">
         <v>51</v>
       </c>
-      <c r="E535" s="17"/>
+      <c r="E535" s="17">
+        <v>27</v>
+      </c>
       <c r="F535" s="17" t="s">
         <v>83</v>
       </c>
@@ -21071,7 +21621,9 @@
       <c r="D536" s="17">
         <v>52</v>
       </c>
-      <c r="E536" s="17"/>
+      <c r="E536" s="17">
+        <v>27</v>
+      </c>
       <c r="F536" s="17" t="s">
         <v>84</v>
       </c>
@@ -21103,7 +21655,9 @@
       <c r="D537" s="17">
         <v>53</v>
       </c>
-      <c r="E537" s="17"/>
+      <c r="E537" s="17">
+        <v>27</v>
+      </c>
       <c r="F537" s="17" t="s">
         <v>85</v>
       </c>
@@ -21135,7 +21689,9 @@
       <c r="D538" s="17">
         <v>54</v>
       </c>
-      <c r="E538" s="17"/>
+      <c r="E538" s="17">
+        <v>27</v>
+      </c>
       <c r="F538" s="17" t="s">
         <v>86</v>
       </c>
@@ -21167,7 +21723,9 @@
       <c r="D539" s="17">
         <v>55</v>
       </c>
-      <c r="E539" s="17"/>
+      <c r="E539" s="17">
+        <v>27</v>
+      </c>
       <c r="F539" s="17" t="s">
         <v>87</v>
       </c>
@@ -21199,7 +21757,9 @@
       <c r="D540" s="17">
         <v>56</v>
       </c>
-      <c r="E540" s="17"/>
+      <c r="E540" s="17">
+        <v>27</v>
+      </c>
       <c r="F540" s="17" t="s">
         <v>88</v>
       </c>
@@ -21231,7 +21791,9 @@
       <c r="D541" s="17">
         <v>57</v>
       </c>
-      <c r="E541" s="17"/>
+      <c r="E541" s="17">
+        <v>27</v>
+      </c>
       <c r="F541" s="17" t="s">
         <v>89</v>
       </c>
@@ -21263,7 +21825,9 @@
       <c r="D542" s="17">
         <v>58</v>
       </c>
-      <c r="E542" s="17"/>
+      <c r="E542" s="17">
+        <v>27</v>
+      </c>
       <c r="F542" s="17" t="s">
         <v>90</v>
       </c>
@@ -21295,7 +21859,9 @@
       <c r="D543" s="17">
         <v>59</v>
       </c>
-      <c r="E543" s="17"/>
+      <c r="E543" s="17">
+        <v>27</v>
+      </c>
       <c r="F543" s="17" t="s">
         <v>91</v>
       </c>
@@ -21327,7 +21893,9 @@
       <c r="D544" s="17">
         <v>60</v>
       </c>
-      <c r="E544" s="17"/>
+      <c r="E544" s="17">
+        <v>27</v>
+      </c>
       <c r="F544" s="17" t="s">
         <v>92</v>
       </c>
@@ -22461,7 +23029,9 @@
       <c r="D573" s="21">
         <v>29</v>
       </c>
-      <c r="E573" s="21"/>
+      <c r="E573" s="21">
+        <v>28</v>
+      </c>
       <c r="F573" s="21" t="s">
         <v>60</v>
       </c>
@@ -22495,7 +23065,9 @@
       <c r="D574" s="21">
         <v>30</v>
       </c>
-      <c r="E574" s="21"/>
+      <c r="E574" s="21">
+        <v>28</v>
+      </c>
       <c r="F574" s="21" t="s">
         <v>61</v>
       </c>
@@ -22529,7 +23101,9 @@
       <c r="D575" s="21">
         <v>31</v>
       </c>
-      <c r="E575" s="21"/>
+      <c r="E575" s="21">
+        <v>28</v>
+      </c>
       <c r="F575" s="21" t="s">
         <v>63</v>
       </c>
@@ -22563,7 +23137,9 @@
       <c r="D576" s="21">
         <v>32</v>
       </c>
-      <c r="E576" s="21"/>
+      <c r="E576" s="21">
+        <v>28</v>
+      </c>
       <c r="F576" s="21" t="s">
         <v>64</v>
       </c>
@@ -22597,7 +23173,9 @@
       <c r="D577" s="21">
         <v>33</v>
       </c>
-      <c r="E577" s="21"/>
+      <c r="E577" s="21">
+        <v>28</v>
+      </c>
       <c r="F577" s="21" t="s">
         <v>65</v>
       </c>
@@ -22631,7 +23209,9 @@
       <c r="D578" s="21">
         <v>34</v>
       </c>
-      <c r="E578" s="21"/>
+      <c r="E578" s="21">
+        <v>28</v>
+      </c>
       <c r="F578" s="21" t="s">
         <v>66</v>
       </c>
@@ -22665,7 +23245,9 @@
       <c r="D579" s="21">
         <v>35</v>
       </c>
-      <c r="E579" s="21"/>
+      <c r="E579" s="21">
+        <v>28</v>
+      </c>
       <c r="F579" s="21" t="s">
         <v>67</v>
       </c>
@@ -22699,7 +23281,9 @@
       <c r="D580" s="21">
         <v>36</v>
       </c>
-      <c r="E580" s="21"/>
+      <c r="E580" s="21">
+        <v>28</v>
+      </c>
       <c r="F580" s="21" t="s">
         <v>68</v>
       </c>
@@ -22733,7 +23317,9 @@
       <c r="D581" s="21">
         <v>37</v>
       </c>
-      <c r="E581" s="21"/>
+      <c r="E581" s="21">
+        <v>28</v>
+      </c>
       <c r="F581" s="21" t="s">
         <v>69</v>
       </c>
@@ -22767,7 +23353,9 @@
       <c r="D582" s="21">
         <v>38</v>
       </c>
-      <c r="E582" s="21"/>
+      <c r="E582" s="21">
+        <v>28</v>
+      </c>
       <c r="F582" s="21" t="s">
         <v>70</v>
       </c>
@@ -22801,7 +23389,9 @@
       <c r="D583" s="21">
         <v>39</v>
       </c>
-      <c r="E583" s="21"/>
+      <c r="E583" s="21">
+        <v>28</v>
+      </c>
       <c r="F583" s="21" t="s">
         <v>71</v>
       </c>
@@ -22835,7 +23425,9 @@
       <c r="D584" s="21">
         <v>40</v>
       </c>
-      <c r="E584" s="21"/>
+      <c r="E584" s="21">
+        <v>28</v>
+      </c>
       <c r="F584" s="21" t="s">
         <v>72</v>
       </c>
@@ -22869,7 +23461,9 @@
       <c r="D585" s="21">
         <v>41</v>
       </c>
-      <c r="E585" s="21"/>
+      <c r="E585" s="21">
+        <v>28</v>
+      </c>
       <c r="F585" s="21" t="s">
         <v>73</v>
       </c>
@@ -22903,7 +23497,9 @@
       <c r="D586" s="21">
         <v>42</v>
       </c>
-      <c r="E586" s="21"/>
+      <c r="E586" s="21">
+        <v>28</v>
+      </c>
       <c r="F586" s="21" t="s">
         <v>74</v>
       </c>
@@ -22937,7 +23533,9 @@
       <c r="D587" s="21">
         <v>43</v>
       </c>
-      <c r="E587" s="21"/>
+      <c r="E587" s="21">
+        <v>28</v>
+      </c>
       <c r="F587" s="21" t="s">
         <v>75</v>
       </c>
@@ -22971,7 +23569,9 @@
       <c r="D588" s="21">
         <v>44</v>
       </c>
-      <c r="E588" s="21"/>
+      <c r="E588" s="21">
+        <v>28</v>
+      </c>
       <c r="F588" s="21" t="s">
         <v>76</v>
       </c>
@@ -23005,7 +23605,9 @@
       <c r="D589" s="21">
         <v>45</v>
       </c>
-      <c r="E589" s="21"/>
+      <c r="E589" s="21">
+        <v>28</v>
+      </c>
       <c r="F589" s="21" t="s">
         <v>77</v>
       </c>
@@ -23039,7 +23641,9 @@
       <c r="D590" s="21">
         <v>46</v>
       </c>
-      <c r="E590" s="21"/>
+      <c r="E590" s="21">
+        <v>28</v>
+      </c>
       <c r="F590" s="21" t="s">
         <v>78</v>
       </c>
@@ -23073,7 +23677,9 @@
       <c r="D591" s="21">
         <v>47</v>
       </c>
-      <c r="E591" s="21"/>
+      <c r="E591" s="21">
+        <v>28</v>
+      </c>
       <c r="F591" s="21" t="s">
         <v>79</v>
       </c>
@@ -23107,7 +23713,9 @@
       <c r="D592" s="21">
         <v>48</v>
       </c>
-      <c r="E592" s="21"/>
+      <c r="E592" s="21">
+        <v>28</v>
+      </c>
       <c r="F592" s="21" t="s">
         <v>80</v>
       </c>
@@ -23141,7 +23749,9 @@
       <c r="D593" s="21">
         <v>49</v>
       </c>
-      <c r="E593" s="21"/>
+      <c r="E593" s="21">
+        <v>28</v>
+      </c>
       <c r="F593" s="21" t="s">
         <v>81</v>
       </c>
@@ -23175,7 +23785,9 @@
       <c r="D594" s="21">
         <v>50</v>
       </c>
-      <c r="E594" s="21"/>
+      <c r="E594" s="21">
+        <v>28</v>
+      </c>
       <c r="F594" s="21" t="s">
         <v>82</v>
       </c>
@@ -23209,7 +23821,9 @@
       <c r="D595" s="21">
         <v>51</v>
       </c>
-      <c r="E595" s="21"/>
+      <c r="E595" s="21">
+        <v>28</v>
+      </c>
       <c r="F595" s="21" t="s">
         <v>83</v>
       </c>
@@ -23243,7 +23857,9 @@
       <c r="D596" s="21">
         <v>52</v>
       </c>
-      <c r="E596" s="21"/>
+      <c r="E596" s="21">
+        <v>28</v>
+      </c>
       <c r="F596" s="21" t="s">
         <v>84</v>
       </c>
@@ -23277,7 +23893,9 @@
       <c r="D597" s="21">
         <v>53</v>
       </c>
-      <c r="E597" s="21"/>
+      <c r="E597" s="21">
+        <v>28</v>
+      </c>
       <c r="F597" s="21" t="s">
         <v>85</v>
       </c>
@@ -23311,7 +23929,9 @@
       <c r="D598" s="21">
         <v>54</v>
       </c>
-      <c r="E598" s="21"/>
+      <c r="E598" s="21">
+        <v>28</v>
+      </c>
       <c r="F598" s="21" t="s">
         <v>86</v>
       </c>
@@ -23345,7 +23965,9 @@
       <c r="D599" s="21">
         <v>55</v>
       </c>
-      <c r="E599" s="21"/>
+      <c r="E599" s="21">
+        <v>28</v>
+      </c>
       <c r="F599" s="21" t="s">
         <v>87</v>
       </c>
@@ -23379,7 +24001,9 @@
       <c r="D600" s="21">
         <v>56</v>
       </c>
-      <c r="E600" s="21"/>
+      <c r="E600" s="21">
+        <v>28</v>
+      </c>
       <c r="F600" s="21" t="s">
         <v>88</v>
       </c>
@@ -23413,7 +24037,9 @@
       <c r="D601" s="21">
         <v>57</v>
       </c>
-      <c r="E601" s="21"/>
+      <c r="E601" s="21">
+        <v>28</v>
+      </c>
       <c r="F601" s="21" t="s">
         <v>89</v>
       </c>
@@ -23447,7 +24073,9 @@
       <c r="D602" s="21">
         <v>58</v>
       </c>
-      <c r="E602" s="21"/>
+      <c r="E602" s="21">
+        <v>28</v>
+      </c>
       <c r="F602" s="21" t="s">
         <v>90</v>
       </c>
@@ -23481,7 +24109,9 @@
       <c r="D603" s="21">
         <v>59</v>
       </c>
-      <c r="E603" s="21"/>
+      <c r="E603" s="21">
+        <v>28</v>
+      </c>
       <c r="F603" s="21" t="s">
         <v>91</v>
       </c>
@@ -23515,7 +24145,9 @@
       <c r="D604" s="21">
         <v>60</v>
       </c>
-      <c r="E604" s="21"/>
+      <c r="E604" s="21">
+        <v>28</v>
+      </c>
       <c r="F604" s="21" t="s">
         <v>92</v>
       </c>
@@ -24615,7 +25247,9 @@
       <c r="D632" s="17">
         <v>28</v>
       </c>
-      <c r="E632" s="17"/>
+      <c r="E632" s="17">
+        <v>27</v>
+      </c>
       <c r="F632" s="17" t="s">
         <v>59</v>
       </c>
@@ -24649,7 +25283,9 @@
       <c r="D633" s="17">
         <v>29</v>
       </c>
-      <c r="E633" s="17"/>
+      <c r="E633" s="17">
+        <v>27</v>
+      </c>
       <c r="F633" s="17" t="s">
         <v>60</v>
       </c>
@@ -24683,7 +25319,9 @@
       <c r="D634" s="17">
         <v>30</v>
       </c>
-      <c r="E634" s="17"/>
+      <c r="E634" s="17">
+        <v>27</v>
+      </c>
       <c r="F634" s="17" t="s">
         <v>61</v>
       </c>
@@ -24717,7 +25355,9 @@
       <c r="D635" s="17">
         <v>31</v>
       </c>
-      <c r="E635" s="17"/>
+      <c r="E635" s="17">
+        <v>27</v>
+      </c>
       <c r="F635" s="17" t="s">
         <v>63</v>
       </c>
@@ -24751,7 +25391,9 @@
       <c r="D636" s="17">
         <v>32</v>
       </c>
-      <c r="E636" s="17"/>
+      <c r="E636" s="17">
+        <v>27</v>
+      </c>
       <c r="F636" s="17" t="s">
         <v>64</v>
       </c>
@@ -24785,7 +25427,9 @@
       <c r="D637" s="17">
         <v>33</v>
       </c>
-      <c r="E637" s="17"/>
+      <c r="E637" s="17">
+        <v>27</v>
+      </c>
       <c r="F637" s="17" t="s">
         <v>65</v>
       </c>
@@ -24819,7 +25463,9 @@
       <c r="D638" s="17">
         <v>34</v>
       </c>
-      <c r="E638" s="17"/>
+      <c r="E638" s="17">
+        <v>27</v>
+      </c>
       <c r="F638" s="17" t="s">
         <v>66</v>
       </c>
@@ -24853,7 +25499,9 @@
       <c r="D639" s="17">
         <v>35</v>
       </c>
-      <c r="E639" s="17"/>
+      <c r="E639" s="17">
+        <v>27</v>
+      </c>
       <c r="F639" s="17" t="s">
         <v>67</v>
       </c>
@@ -24887,7 +25535,9 @@
       <c r="D640" s="17">
         <v>36</v>
       </c>
-      <c r="E640" s="17"/>
+      <c r="E640" s="17">
+        <v>27</v>
+      </c>
       <c r="F640" s="17" t="s">
         <v>68</v>
       </c>
@@ -24921,7 +25571,9 @@
       <c r="D641" s="17">
         <v>37</v>
       </c>
-      <c r="E641" s="17"/>
+      <c r="E641" s="17">
+        <v>27</v>
+      </c>
       <c r="F641" s="17" t="s">
         <v>69</v>
       </c>
@@ -24955,7 +25607,9 @@
       <c r="D642" s="17">
         <v>38</v>
       </c>
-      <c r="E642" s="17"/>
+      <c r="E642" s="17">
+        <v>27</v>
+      </c>
       <c r="F642" s="17" t="s">
         <v>70</v>
       </c>
@@ -24989,7 +25643,9 @@
       <c r="D643" s="17">
         <v>39</v>
       </c>
-      <c r="E643" s="17"/>
+      <c r="E643" s="17">
+        <v>27</v>
+      </c>
       <c r="F643" s="17" t="s">
         <v>71</v>
       </c>
@@ -25023,7 +25679,9 @@
       <c r="D644" s="17">
         <v>40</v>
       </c>
-      <c r="E644" s="17"/>
+      <c r="E644" s="17">
+        <v>27</v>
+      </c>
       <c r="F644" s="17" t="s">
         <v>72</v>
       </c>
@@ -25057,7 +25715,9 @@
       <c r="D645" s="17">
         <v>41</v>
       </c>
-      <c r="E645" s="17"/>
+      <c r="E645" s="17">
+        <v>27</v>
+      </c>
       <c r="F645" s="17" t="s">
         <v>73</v>
       </c>
@@ -25091,7 +25751,9 @@
       <c r="D646" s="17">
         <v>42</v>
       </c>
-      <c r="E646" s="17"/>
+      <c r="E646" s="17">
+        <v>27</v>
+      </c>
       <c r="F646" s="17" t="s">
         <v>74</v>
       </c>
@@ -25125,7 +25787,9 @@
       <c r="D647" s="17">
         <v>43</v>
       </c>
-      <c r="E647" s="17"/>
+      <c r="E647" s="17">
+        <v>27</v>
+      </c>
       <c r="F647" s="17" t="s">
         <v>75</v>
       </c>
@@ -25159,7 +25823,9 @@
       <c r="D648" s="17">
         <v>44</v>
       </c>
-      <c r="E648" s="17"/>
+      <c r="E648" s="17">
+        <v>27</v>
+      </c>
       <c r="F648" s="17" t="s">
         <v>76</v>
       </c>
@@ -25193,7 +25859,9 @@
       <c r="D649" s="17">
         <v>45</v>
       </c>
-      <c r="E649" s="17"/>
+      <c r="E649" s="17">
+        <v>27</v>
+      </c>
       <c r="F649" s="17" t="s">
         <v>77</v>
       </c>
@@ -25227,7 +25895,9 @@
       <c r="D650" s="17">
         <v>46</v>
       </c>
-      <c r="E650" s="17"/>
+      <c r="E650" s="17">
+        <v>27</v>
+      </c>
       <c r="F650" s="17" t="s">
         <v>78</v>
       </c>
@@ -25261,7 +25931,9 @@
       <c r="D651" s="17">
         <v>47</v>
       </c>
-      <c r="E651" s="17"/>
+      <c r="E651" s="17">
+        <v>27</v>
+      </c>
       <c r="F651" s="17" t="s">
         <v>79</v>
       </c>
@@ -25295,7 +25967,9 @@
       <c r="D652" s="17">
         <v>48</v>
       </c>
-      <c r="E652" s="17"/>
+      <c r="E652" s="17">
+        <v>27</v>
+      </c>
       <c r="F652" s="17" t="s">
         <v>80</v>
       </c>
@@ -25329,7 +26003,9 @@
       <c r="D653" s="17">
         <v>49</v>
       </c>
-      <c r="E653" s="17"/>
+      <c r="E653" s="17">
+        <v>27</v>
+      </c>
       <c r="F653" s="17" t="s">
         <v>81</v>
       </c>
@@ -25363,7 +26039,9 @@
       <c r="D654" s="17">
         <v>50</v>
       </c>
-      <c r="E654" s="17"/>
+      <c r="E654" s="17">
+        <v>27</v>
+      </c>
       <c r="F654" s="17" t="s">
         <v>82</v>
       </c>
@@ -25397,7 +26075,9 @@
       <c r="D655" s="17">
         <v>51</v>
       </c>
-      <c r="E655" s="17"/>
+      <c r="E655" s="17">
+        <v>27</v>
+      </c>
       <c r="F655" s="17" t="s">
         <v>83</v>
       </c>
@@ -25431,7 +26111,9 @@
       <c r="D656" s="17">
         <v>52</v>
       </c>
-      <c r="E656" s="17"/>
+      <c r="E656" s="17">
+        <v>27</v>
+      </c>
       <c r="F656" s="17" t="s">
         <v>84</v>
       </c>
@@ -25465,7 +26147,9 @@
       <c r="D657" s="17">
         <v>53</v>
       </c>
-      <c r="E657" s="17"/>
+      <c r="E657" s="17">
+        <v>27</v>
+      </c>
       <c r="F657" s="17" t="s">
         <v>85</v>
       </c>
@@ -25499,7 +26183,9 @@
       <c r="D658" s="17">
         <v>54</v>
       </c>
-      <c r="E658" s="17"/>
+      <c r="E658" s="17">
+        <v>27</v>
+      </c>
       <c r="F658" s="17" t="s">
         <v>86</v>
       </c>
@@ -25533,7 +26219,9 @@
       <c r="D659" s="17">
         <v>55</v>
       </c>
-      <c r="E659" s="17"/>
+      <c r="E659" s="17">
+        <v>27</v>
+      </c>
       <c r="F659" s="17" t="s">
         <v>87</v>
       </c>
@@ -25567,7 +26255,9 @@
       <c r="D660" s="17">
         <v>56</v>
       </c>
-      <c r="E660" s="17"/>
+      <c r="E660" s="17">
+        <v>27</v>
+      </c>
       <c r="F660" s="17" t="s">
         <v>88</v>
       </c>
@@ -25601,7 +26291,9 @@
       <c r="D661" s="17">
         <v>57</v>
       </c>
-      <c r="E661" s="17"/>
+      <c r="E661" s="17">
+        <v>27</v>
+      </c>
       <c r="F661" s="17" t="s">
         <v>89</v>
       </c>
@@ -25635,7 +26327,9 @@
       <c r="D662" s="17">
         <v>58</v>
       </c>
-      <c r="E662" s="17"/>
+      <c r="E662" s="17">
+        <v>27</v>
+      </c>
       <c r="F662" s="17" t="s">
         <v>90</v>
       </c>
@@ -25669,7 +26363,9 @@
       <c r="D663" s="17">
         <v>59</v>
       </c>
-      <c r="E663" s="17"/>
+      <c r="E663" s="17">
+        <v>27</v>
+      </c>
       <c r="F663" s="17" t="s">
         <v>91</v>
       </c>
@@ -25703,7 +26399,9 @@
       <c r="D664" s="17">
         <v>60</v>
       </c>
-      <c r="E664" s="17"/>
+      <c r="E664" s="17">
+        <v>27</v>
+      </c>
       <c r="F664" s="17" t="s">
         <v>92</v>
       </c>
@@ -27331,7 +28029,9 @@
       <c r="D708" s="21">
         <v>44</v>
       </c>
-      <c r="E708" s="21"/>
+      <c r="E708" s="21">
+        <v>43</v>
+      </c>
       <c r="F708" s="21" t="s">
         <v>76</v>
       </c>
@@ -27365,7 +28065,9 @@
       <c r="D709" s="21">
         <v>45</v>
       </c>
-      <c r="E709" s="21"/>
+      <c r="E709" s="21">
+        <v>43</v>
+      </c>
       <c r="F709" s="21" t="s">
         <v>77</v>
       </c>
@@ -27399,7 +28101,9 @@
       <c r="D710" s="21">
         <v>46</v>
       </c>
-      <c r="E710" s="21"/>
+      <c r="E710" s="21">
+        <v>43</v>
+      </c>
       <c r="F710" s="21" t="s">
         <v>78</v>
       </c>
@@ -27433,7 +28137,9 @@
       <c r="D711" s="21">
         <v>47</v>
       </c>
-      <c r="E711" s="21"/>
+      <c r="E711" s="21">
+        <v>43</v>
+      </c>
       <c r="F711" s="21" t="s">
         <v>79</v>
       </c>
@@ -27467,7 +28173,9 @@
       <c r="D712" s="21">
         <v>48</v>
       </c>
-      <c r="E712" s="21"/>
+      <c r="E712" s="21">
+        <v>43</v>
+      </c>
       <c r="F712" s="21" t="s">
         <v>80</v>
       </c>
@@ -27501,7 +28209,9 @@
       <c r="D713" s="21">
         <v>49</v>
       </c>
-      <c r="E713" s="21"/>
+      <c r="E713" s="21">
+        <v>43</v>
+      </c>
       <c r="F713" s="21" t="s">
         <v>81</v>
       </c>
@@ -27535,7 +28245,9 @@
       <c r="D714" s="21">
         <v>50</v>
       </c>
-      <c r="E714" s="21"/>
+      <c r="E714" s="21">
+        <v>43</v>
+      </c>
       <c r="F714" s="21" t="s">
         <v>82</v>
       </c>
@@ -27569,7 +28281,9 @@
       <c r="D715" s="21">
         <v>51</v>
       </c>
-      <c r="E715" s="21"/>
+      <c r="E715" s="21">
+        <v>43</v>
+      </c>
       <c r="F715" s="21" t="s">
         <v>83</v>
       </c>
@@ -27603,7 +28317,9 @@
       <c r="D716" s="21">
         <v>52</v>
       </c>
-      <c r="E716" s="21"/>
+      <c r="E716" s="21">
+        <v>43</v>
+      </c>
       <c r="F716" s="21" t="s">
         <v>84</v>
       </c>
@@ -27637,7 +28353,9 @@
       <c r="D717" s="21">
         <v>53</v>
       </c>
-      <c r="E717" s="21"/>
+      <c r="E717" s="21">
+        <v>43</v>
+      </c>
       <c r="F717" s="21" t="s">
         <v>85</v>
       </c>
@@ -27671,7 +28389,9 @@
       <c r="D718" s="21">
         <v>54</v>
       </c>
-      <c r="E718" s="21"/>
+      <c r="E718" s="21">
+        <v>43</v>
+      </c>
       <c r="F718" s="21" t="s">
         <v>86</v>
       </c>
@@ -27705,7 +28425,9 @@
       <c r="D719" s="21">
         <v>55</v>
       </c>
-      <c r="E719" s="21"/>
+      <c r="E719" s="21">
+        <v>43</v>
+      </c>
       <c r="F719" s="21" t="s">
         <v>87</v>
       </c>
@@ -27739,7 +28461,9 @@
       <c r="D720" s="21">
         <v>56</v>
       </c>
-      <c r="E720" s="21"/>
+      <c r="E720" s="21">
+        <v>43</v>
+      </c>
       <c r="F720" s="21" t="s">
         <v>88</v>
       </c>
@@ -27773,7 +28497,9 @@
       <c r="D721" s="21">
         <v>57</v>
       </c>
-      <c r="E721" s="21"/>
+      <c r="E721" s="21">
+        <v>43</v>
+      </c>
       <c r="F721" s="21" t="s">
         <v>89</v>
       </c>
@@ -27807,7 +28533,9 @@
       <c r="D722" s="21">
         <v>58</v>
       </c>
-      <c r="E722" s="21"/>
+      <c r="E722" s="21">
+        <v>43</v>
+      </c>
       <c r="F722" s="21" t="s">
         <v>90</v>
       </c>
@@ -27841,7 +28569,9 @@
       <c r="D723" s="21">
         <v>59</v>
       </c>
-      <c r="E723" s="21"/>
+      <c r="E723" s="21">
+        <v>43</v>
+      </c>
       <c r="F723" s="21" t="s">
         <v>91</v>
       </c>
@@ -27875,7 +28605,9 @@
       <c r="D724" s="21">
         <v>60</v>
       </c>
-      <c r="E724" s="21"/>
+      <c r="E724" s="21">
+        <v>43</v>
+      </c>
       <c r="F724" s="21" t="s">
         <v>92</v>
       </c>
@@ -28999,7 +29731,9 @@
       <c r="D755" s="17">
         <v>31</v>
       </c>
-      <c r="E755" s="17"/>
+      <c r="E755" s="17">
+        <v>30</v>
+      </c>
       <c r="F755" s="17" t="s">
         <v>63</v>
       </c>
@@ -29031,7 +29765,9 @@
       <c r="D756" s="17">
         <v>32</v>
       </c>
-      <c r="E756" s="17"/>
+      <c r="E756" s="17">
+        <v>30</v>
+      </c>
       <c r="F756" s="17" t="s">
         <v>64</v>
       </c>
@@ -29063,7 +29799,9 @@
       <c r="D757" s="17">
         <v>33</v>
       </c>
-      <c r="E757" s="17"/>
+      <c r="E757" s="17">
+        <v>30</v>
+      </c>
       <c r="F757" s="17" t="s">
         <v>65</v>
       </c>
@@ -29095,6 +29833,9 @@
       <c r="D758" s="17">
         <v>34</v>
       </c>
+      <c r="E758" s="17">
+        <v>30</v>
+      </c>
       <c r="F758" s="17" t="s">
         <v>66</v>
       </c>
@@ -29126,7 +29867,9 @@
       <c r="D759" s="17">
         <v>35</v>
       </c>
-      <c r="E759" s="17"/>
+      <c r="E759" s="17">
+        <v>30</v>
+      </c>
       <c r="F759" s="17" t="s">
         <v>67</v>
       </c>
@@ -29158,7 +29901,9 @@
       <c r="D760" s="17">
         <v>36</v>
       </c>
-      <c r="E760" s="17"/>
+      <c r="E760" s="17">
+        <v>30</v>
+      </c>
       <c r="F760" s="17" t="s">
         <v>68</v>
       </c>
@@ -29190,7 +29935,9 @@
       <c r="D761" s="17">
         <v>37</v>
       </c>
-      <c r="E761" s="17"/>
+      <c r="E761" s="17">
+        <v>30</v>
+      </c>
       <c r="F761" s="17" t="s">
         <v>69</v>
       </c>
@@ -29222,7 +29969,9 @@
       <c r="D762" s="17">
         <v>38</v>
       </c>
-      <c r="E762" s="17"/>
+      <c r="E762" s="17">
+        <v>30</v>
+      </c>
       <c r="F762" s="17" t="s">
         <v>70</v>
       </c>
@@ -29254,7 +30003,9 @@
       <c r="D763" s="17">
         <v>39</v>
       </c>
-      <c r="E763" s="17"/>
+      <c r="E763" s="17">
+        <v>30</v>
+      </c>
       <c r="F763" s="17" t="s">
         <v>71</v>
       </c>
@@ -29286,7 +30037,9 @@
       <c r="D764" s="17">
         <v>40</v>
       </c>
-      <c r="E764" s="17"/>
+      <c r="E764" s="17">
+        <v>30</v>
+      </c>
       <c r="F764" s="17" t="s">
         <v>72</v>
       </c>
@@ -29318,7 +30071,9 @@
       <c r="D765" s="17">
         <v>41</v>
       </c>
-      <c r="E765" s="17"/>
+      <c r="E765" s="17">
+        <v>30</v>
+      </c>
       <c r="F765" s="17" t="s">
         <v>73</v>
       </c>
@@ -29350,7 +30105,9 @@
       <c r="D766" s="17">
         <v>42</v>
       </c>
-      <c r="E766" s="17"/>
+      <c r="E766" s="17">
+        <v>30</v>
+      </c>
       <c r="F766" s="17" t="s">
         <v>74</v>
       </c>
@@ -29382,7 +30139,9 @@
       <c r="D767" s="17">
         <v>43</v>
       </c>
-      <c r="E767" s="17"/>
+      <c r="E767" s="17">
+        <v>30</v>
+      </c>
       <c r="F767" s="17" t="s">
         <v>75</v>
       </c>
@@ -29414,7 +30173,9 @@
       <c r="D768" s="17">
         <v>44</v>
       </c>
-      <c r="E768" s="17"/>
+      <c r="E768" s="17">
+        <v>30</v>
+      </c>
       <c r="F768" s="17" t="s">
         <v>76</v>
       </c>
@@ -29446,7 +30207,9 @@
       <c r="D769" s="17">
         <v>45</v>
       </c>
-      <c r="E769" s="17"/>
+      <c r="E769" s="17">
+        <v>30</v>
+      </c>
       <c r="F769" s="17" t="s">
         <v>77</v>
       </c>
@@ -29478,7 +30241,9 @@
       <c r="D770" s="17">
         <v>46</v>
       </c>
-      <c r="E770" s="17"/>
+      <c r="E770" s="17">
+        <v>30</v>
+      </c>
       <c r="F770" s="17" t="s">
         <v>78</v>
       </c>
@@ -29510,7 +30275,9 @@
       <c r="D771" s="17">
         <v>47</v>
       </c>
-      <c r="E771" s="17"/>
+      <c r="E771" s="17">
+        <v>30</v>
+      </c>
       <c r="F771" s="17" t="s">
         <v>79</v>
       </c>
@@ -29542,7 +30309,9 @@
       <c r="D772" s="17">
         <v>48</v>
       </c>
-      <c r="E772" s="17"/>
+      <c r="E772" s="17">
+        <v>30</v>
+      </c>
       <c r="F772" s="17" t="s">
         <v>80</v>
       </c>
@@ -29574,7 +30343,9 @@
       <c r="D773" s="17">
         <v>49</v>
       </c>
-      <c r="E773" s="17"/>
+      <c r="E773" s="17">
+        <v>30</v>
+      </c>
       <c r="F773" s="17" t="s">
         <v>81</v>
       </c>
@@ -29606,7 +30377,9 @@
       <c r="D774" s="17">
         <v>50</v>
       </c>
-      <c r="E774" s="17"/>
+      <c r="E774" s="17">
+        <v>30</v>
+      </c>
       <c r="F774" s="17" t="s">
         <v>82</v>
       </c>
@@ -29638,7 +30411,9 @@
       <c r="D775" s="17">
         <v>51</v>
       </c>
-      <c r="E775" s="17"/>
+      <c r="E775" s="17">
+        <v>30</v>
+      </c>
       <c r="F775" s="17" t="s">
         <v>83</v>
       </c>
@@ -29670,7 +30445,9 @@
       <c r="D776" s="17">
         <v>52</v>
       </c>
-      <c r="E776" s="17"/>
+      <c r="E776" s="17">
+        <v>30</v>
+      </c>
       <c r="F776" s="17" t="s">
         <v>84</v>
       </c>
@@ -29702,7 +30479,9 @@
       <c r="D777" s="17">
         <v>53</v>
       </c>
-      <c r="E777" s="17"/>
+      <c r="E777" s="17">
+        <v>30</v>
+      </c>
       <c r="F777" s="17" t="s">
         <v>85</v>
       </c>
@@ -29734,7 +30513,9 @@
       <c r="D778" s="17">
         <v>54</v>
       </c>
-      <c r="E778" s="17"/>
+      <c r="E778" s="17">
+        <v>30</v>
+      </c>
       <c r="F778" s="17" t="s">
         <v>86</v>
       </c>
@@ -29766,7 +30547,9 @@
       <c r="D779" s="17">
         <v>55</v>
       </c>
-      <c r="E779" s="17"/>
+      <c r="E779" s="17">
+        <v>30</v>
+      </c>
       <c r="F779" s="17" t="s">
         <v>87</v>
       </c>
@@ -29798,7 +30581,9 @@
       <c r="D780" s="17">
         <v>56</v>
       </c>
-      <c r="E780" s="17"/>
+      <c r="E780" s="17">
+        <v>30</v>
+      </c>
       <c r="F780" s="17" t="s">
         <v>88</v>
       </c>
@@ -29830,7 +30615,9 @@
       <c r="D781" s="17">
         <v>57</v>
       </c>
-      <c r="E781" s="17"/>
+      <c r="E781" s="17">
+        <v>30</v>
+      </c>
       <c r="F781" s="17" t="s">
         <v>89</v>
       </c>
@@ -29862,7 +30649,9 @@
       <c r="D782" s="17">
         <v>58</v>
       </c>
-      <c r="E782" s="17"/>
+      <c r="E782" s="17">
+        <v>30</v>
+      </c>
       <c r="F782" s="17" t="s">
         <v>90</v>
       </c>
@@ -29894,7 +30683,9 @@
       <c r="D783" s="17">
         <v>59</v>
       </c>
-      <c r="E783" s="17"/>
+      <c r="E783" s="17">
+        <v>30</v>
+      </c>
       <c r="F783" s="17" t="s">
         <v>91</v>
       </c>
@@ -29926,7 +30717,9 @@
       <c r="D784" s="17">
         <v>60</v>
       </c>
-      <c r="E784" s="17"/>
+      <c r="E784" s="17">
+        <v>30</v>
+      </c>
       <c r="F784" s="17" t="s">
         <v>92</v>
       </c>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -32017,7 +32017,7 @@
     </row>
     <row r="827" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A827" s="20">
-        <f t="shared" ref="A827:A846" si="31">B827*1000+D827</f>
+        <f t="shared" ref="A827:A854" si="31">B827*1000+D827</f>
         <v>1301043</v>
       </c>
       <c r="B827" s="20">
@@ -32667,7 +32667,7 @@
     </row>
     <row r="847" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A847" s="28">
-        <f>B847*1000+D847</f>
+        <f t="shared" si="31"/>
         <v>1302003</v>
       </c>
       <c r="B847" s="28">
@@ -32705,7 +32705,7 @@
     </row>
     <row r="848" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A848" s="28">
-        <f>B848*1000+D848</f>
+        <f t="shared" si="31"/>
         <v>1302004</v>
       </c>
       <c r="B848" s="28">
@@ -32743,7 +32743,7 @@
     </row>
     <row r="849" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A849" s="28">
-        <f>B849*1000+D849</f>
+        <f t="shared" si="31"/>
         <v>1302005</v>
       </c>
       <c r="B849" s="28">
@@ -32781,7 +32781,7 @@
     </row>
     <row r="850" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A850" s="28">
-        <f>B850*1000+D850</f>
+        <f t="shared" si="31"/>
         <v>1302006</v>
       </c>
       <c r="B850" s="28">
@@ -32819,7 +32819,7 @@
     </row>
     <row r="851" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A851" s="28">
-        <f>B851*1000+D851</f>
+        <f t="shared" si="31"/>
         <v>1302007</v>
       </c>
       <c r="B851" s="28">
@@ -32857,7 +32857,7 @@
     </row>
     <row r="852" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A852" s="28">
-        <f>B852*1000+D852</f>
+        <f t="shared" si="31"/>
         <v>1302008</v>
       </c>
       <c r="B852" s="28">
@@ -32895,7 +32895,7 @@
     </row>
     <row r="853" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A853" s="28">
-        <f>B853*1000+D853</f>
+        <f t="shared" si="31"/>
         <v>1302009</v>
       </c>
       <c r="B853" s="28">
@@ -32933,7 +32933,7 @@
     </row>
     <row r="854" s="4" customFormat="1" customHeight="1" spans="1:13">
       <c r="A854" s="28">
-        <f>B854*1000+D854</f>
+        <f t="shared" si="31"/>
         <v>1302010</v>
       </c>
       <c r="B854" s="28">
@@ -32947,7 +32947,7 @@
       </c>
       <c r="E854" s="4"/>
       <c r="F854" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G854" s="29">
         <v>10</v>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -366,7 +366,7 @@
     <t>1980000_10000</t>
   </si>
   <si>
-    <t>1102251_1102252_1102255</t>
+    <t>1102251_1102252_1102255_1102264_1102265_1102266_1102267_1102268_1102269</t>
   </si>
   <si>
     <t>1990000_1000,1990000_1100,1990000_1200,1990000_1300,1990000_1400,1990000_1500,1990000_1700,1990000_1600,1990000_2000</t>
@@ -555,25 +555,25 @@
     <t>辉煌厅</t>
   </si>
   <si>
-    <t>1103251_1103252_1103258</t>
+    <t>1103251_1103252_1103258_1103253_1103254_1103255_1103256_1103257_1103259</t>
   </si>
   <si>
     <t>鸿运厅</t>
   </si>
   <si>
-    <t>1104251_1104252_1104256</t>
+    <t>1104251_1104252_1104256_1104253_1104254_1104255_1104257</t>
   </si>
   <si>
     <t>尊享厅</t>
   </si>
   <si>
-    <t>1105251_1105252_1105258</t>
+    <t>1105251_1105252_1105258_1105253_1105254_1105255_1105256_1105257_1105259</t>
   </si>
   <si>
     <t>至尊厅</t>
   </si>
   <si>
-    <t>1106251_1106252_1106262</t>
+    <t>1106251_1106252_1106262_1106253_1106254_1106255_1106256_1106257</t>
   </si>
   <si>
     <t>博弈扑克厅</t>
@@ -585,13 +585,13 @@
     <t>沙龙扑克厅</t>
   </si>
   <si>
-    <t>1108251_1108252_1108254</t>
+    <t>1108251_1108252_1108254_1108253</t>
   </si>
   <si>
     <t>精英扑克厅</t>
   </si>
   <si>
-    <t>1109251_1109254_1109252</t>
+    <t>1109251_1109254_1109252_1109253</t>
   </si>
   <si>
     <t>欢乐捕鱼厅</t>
@@ -603,13 +603,13 @@
     <t>天际捕鱼厅</t>
   </si>
   <si>
-    <t>1111251_1111252_1111254</t>
+    <t>1111251_1111252_1111254_1111255_1111256_1111257</t>
   </si>
   <si>
     <t>富豪捕鱼厅</t>
   </si>
   <si>
-    <t>1112251_1112252_1112255</t>
+    <t>1112251_1112252_1112255_1112254</t>
   </si>
   <si>
     <t>普通休息区</t>
@@ -1410,7 +1410,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1478,7 +1478,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1486,8 +1486,14 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -2630,7 +2636,7 @@
         <v>11021111</v>
       </c>
       <c r="K15" s="9">
-        <v>1102264</v>
+        <v>1102270</v>
       </c>
       <c r="L15" s="18">
         <v>360</v>
@@ -2670,7 +2676,7 @@
         <v>11021121</v>
       </c>
       <c r="K16" s="9">
-        <v>1102265</v>
+        <v>1102271</v>
       </c>
       <c r="L16" s="18">
         <v>420</v>
@@ -2710,7 +2716,7 @@
         <v>11021131</v>
       </c>
       <c r="K17" s="9">
-        <v>1102266</v>
+        <v>1102272</v>
       </c>
       <c r="L17" s="18">
         <v>480</v>
@@ -2750,7 +2756,7 @@
         <v>11021141</v>
       </c>
       <c r="K18" s="9">
-        <v>1102267</v>
+        <v>1102273</v>
       </c>
       <c r="L18" s="18">
         <v>540</v>
@@ -2790,7 +2796,7 @@
         <v>11021151</v>
       </c>
       <c r="K19" s="9">
-        <v>1102268</v>
+        <v>1102274</v>
       </c>
       <c r="L19" s="18">
         <v>600</v>
@@ -2830,7 +2836,7 @@
         <v>11021161</v>
       </c>
       <c r="K20" s="9">
-        <v>1102269</v>
+        <v>1102275</v>
       </c>
       <c r="L20" s="18">
         <v>600</v>
@@ -2870,7 +2876,7 @@
         <v>11021171</v>
       </c>
       <c r="K21" s="9">
-        <v>1102270</v>
+        <v>1102276</v>
       </c>
       <c r="L21" s="18">
         <v>600</v>
@@ -2910,7 +2916,7 @@
         <v>11021181</v>
       </c>
       <c r="K22" s="9">
-        <v>1102271</v>
+        <v>1102277</v>
       </c>
       <c r="L22" s="18">
         <v>600</v>
@@ -2944,7 +2950,7 @@
       </c>
       <c r="H23" s="8"/>
       <c r="K23" s="9">
-        <v>1102272</v>
+        <v>1102278</v>
       </c>
       <c r="L23" s="18">
         <v>600</v>
@@ -2978,7 +2984,7 @@
       </c>
       <c r="H24" s="8"/>
       <c r="K24" s="9">
-        <v>1102273</v>
+        <v>1102279</v>
       </c>
       <c r="L24" s="18">
         <v>600</v>
@@ -3011,9 +3017,6 @@
         <v>5000</v>
       </c>
       <c r="H25" s="8"/>
-      <c r="K25" s="9">
-        <v>1102274</v>
-      </c>
       <c r="L25" s="18">
         <v>600</v>
       </c>
@@ -3045,9 +3048,6 @@
         <v>5200</v>
       </c>
       <c r="H26" s="8"/>
-      <c r="K26" s="9">
-        <v>1102275</v>
-      </c>
       <c r="L26" s="18">
         <v>600</v>
       </c>
@@ -3079,9 +3079,6 @@
         <v>5400</v>
       </c>
       <c r="H27" s="8"/>
-      <c r="K27" s="9">
-        <v>1102276</v>
-      </c>
       <c r="L27" s="18">
         <v>600</v>
       </c>
@@ -3113,9 +3110,6 @@
         <v>5600</v>
       </c>
       <c r="H28" s="8"/>
-      <c r="K28" s="9">
-        <v>1102277</v>
-      </c>
       <c r="L28" s="18">
         <v>600</v>
       </c>
@@ -3147,9 +3141,6 @@
         <v>5800</v>
       </c>
       <c r="H29" s="8"/>
-      <c r="K29" s="9">
-        <v>1102278</v>
-      </c>
       <c r="L29" s="18">
         <v>600</v>
       </c>
@@ -3181,9 +3172,6 @@
         <v>6000</v>
       </c>
       <c r="H30" s="8"/>
-      <c r="K30" s="9">
-        <v>1102279</v>
-      </c>
       <c r="L30" s="18">
         <v>600</v>
       </c>
@@ -4406,8 +4394,8 @@
       <c r="J66" s="21">
         <v>11031021</v>
       </c>
-      <c r="K66" s="22">
-        <v>1103253</v>
+      <c r="K66" s="25">
+        <v>1103260</v>
       </c>
       <c r="L66" s="23">
         <v>10</v>
@@ -4446,8 +4434,8 @@
       <c r="J67" s="21">
         <v>11031031</v>
       </c>
-      <c r="K67" s="22">
-        <v>1103254</v>
+      <c r="K67" s="25">
+        <v>1103261</v>
       </c>
       <c r="L67" s="23">
         <v>20</v>
@@ -4486,8 +4474,8 @@
       <c r="J68" s="21">
         <v>11031041</v>
       </c>
-      <c r="K68" s="22">
-        <v>1103255</v>
+      <c r="K68" s="25">
+        <v>1103262</v>
       </c>
       <c r="L68" s="23">
         <v>30</v>
@@ -4526,8 +4514,8 @@
       <c r="J69" s="21">
         <v>11031051</v>
       </c>
-      <c r="K69" s="22">
-        <v>1103256</v>
+      <c r="K69" s="25">
+        <v>1103263</v>
       </c>
       <c r="L69" s="23">
         <v>60</v>
@@ -4566,8 +4554,8 @@
       <c r="J70" s="21">
         <v>11031061</v>
       </c>
-      <c r="K70" s="22">
-        <v>1103257</v>
+      <c r="K70" s="25">
+        <v>1103264</v>
       </c>
       <c r="L70" s="23">
         <v>80</v>
@@ -4606,8 +4594,8 @@
       <c r="J71" s="21">
         <v>11031071</v>
       </c>
-      <c r="K71" s="22">
-        <v>1103259</v>
+      <c r="K71" s="25">
+        <v>1103265</v>
       </c>
       <c r="L71" s="23">
         <v>120</v>
@@ -4646,8 +4634,8 @@
       <c r="J72" s="21">
         <v>11031081</v>
       </c>
-      <c r="K72" s="22">
-        <v>1103260</v>
+      <c r="K72" s="25">
+        <v>1103266</v>
       </c>
       <c r="L72" s="23">
         <v>150</v>
@@ -4686,8 +4674,8 @@
       <c r="J73" s="21">
         <v>11031091</v>
       </c>
-      <c r="K73" s="22">
-        <v>1103261</v>
+      <c r="K73" s="25">
+        <v>1103267</v>
       </c>
       <c r="L73" s="23">
         <v>200</v>
@@ -4726,8 +4714,8 @@
       <c r="J74" s="21">
         <v>11031101</v>
       </c>
-      <c r="K74" s="22">
-        <v>1103262</v>
+      <c r="K74" s="25">
+        <v>1103268</v>
       </c>
       <c r="L74" s="23">
         <v>300</v>
@@ -4766,8 +4754,8 @@
       <c r="J75" s="21">
         <v>11031111</v>
       </c>
-      <c r="K75" s="22">
-        <v>1103263</v>
+      <c r="K75" s="25">
+        <v>1103269</v>
       </c>
       <c r="L75" s="23">
         <v>360</v>
@@ -4806,8 +4794,8 @@
       <c r="J76" s="21">
         <v>11031121</v>
       </c>
-      <c r="K76" s="22">
-        <v>1103264</v>
+      <c r="K76" s="25">
+        <v>1103270</v>
       </c>
       <c r="L76" s="23">
         <v>420</v>
@@ -4846,8 +4834,8 @@
       <c r="J77" s="21">
         <v>11031131</v>
       </c>
-      <c r="K77" s="22">
-        <v>1103265</v>
+      <c r="K77" s="25">
+        <v>1103271</v>
       </c>
       <c r="L77" s="23">
         <v>480</v>
@@ -4886,8 +4874,8 @@
       <c r="J78" s="21">
         <v>11031141</v>
       </c>
-      <c r="K78" s="22">
-        <v>1103266</v>
+      <c r="K78" s="25">
+        <v>1103272</v>
       </c>
       <c r="L78" s="23">
         <v>540</v>
@@ -4926,8 +4914,8 @@
       <c r="J79" s="21">
         <v>11031151</v>
       </c>
-      <c r="K79" s="22">
-        <v>1103267</v>
+      <c r="K79" s="25">
+        <v>1103273</v>
       </c>
       <c r="L79" s="23">
         <v>600</v>
@@ -4966,8 +4954,8 @@
       <c r="J80" s="21">
         <v>11031161</v>
       </c>
-      <c r="K80" s="22">
-        <v>1103268</v>
+      <c r="K80" s="25">
+        <v>1103274</v>
       </c>
       <c r="L80" s="23">
         <v>600</v>
@@ -5002,8 +4990,8 @@
       <c r="H81" s="21"/>
       <c r="I81" s="21"/>
       <c r="J81" s="21"/>
-      <c r="K81" s="22">
-        <v>1103269</v>
+      <c r="K81" s="25">
+        <v>1103275</v>
       </c>
       <c r="L81" s="23">
         <v>600</v>
@@ -5038,9 +5026,6 @@
       <c r="H82" s="21"/>
       <c r="I82" s="21"/>
       <c r="J82" s="21"/>
-      <c r="K82" s="22">
-        <v>1103270</v>
-      </c>
       <c r="L82" s="23">
         <v>600</v>
       </c>
@@ -5074,9 +5059,6 @@
       <c r="H83" s="21"/>
       <c r="I83" s="21"/>
       <c r="J83" s="21"/>
-      <c r="K83" s="22">
-        <v>1103271</v>
-      </c>
       <c r="L83" s="23">
         <v>600</v>
       </c>
@@ -5110,9 +5092,6 @@
       <c r="H84" s="21"/>
       <c r="I84" s="21"/>
       <c r="J84" s="21"/>
-      <c r="K84" s="22">
-        <v>1103272</v>
-      </c>
       <c r="L84" s="23">
         <v>600</v>
       </c>
@@ -5146,9 +5125,6 @@
       <c r="H85" s="21"/>
       <c r="I85" s="21"/>
       <c r="J85" s="21"/>
-      <c r="K85" s="22">
-        <v>1103273</v>
-      </c>
       <c r="L85" s="23">
         <v>600</v>
       </c>
@@ -5182,9 +5158,6 @@
       <c r="H86" s="21"/>
       <c r="I86" s="21"/>
       <c r="J86" s="21"/>
-      <c r="K86" s="22">
-        <v>1103274</v>
-      </c>
       <c r="L86" s="23">
         <v>600</v>
       </c>
@@ -5218,9 +5191,6 @@
       <c r="H87" s="21"/>
       <c r="I87" s="21"/>
       <c r="J87" s="21"/>
-      <c r="K87" s="22">
-        <v>1103275</v>
-      </c>
       <c r="L87" s="23">
         <v>600</v>
       </c>
@@ -5320,7 +5290,7 @@
       <c r="H90" s="21"/>
       <c r="I90" s="21"/>
       <c r="J90" s="21"/>
-      <c r="K90" s="25" t="s">
+      <c r="K90" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L90" s="23">
@@ -5356,7 +5326,7 @@
       <c r="H91" s="21"/>
       <c r="I91" s="21"/>
       <c r="J91" s="21"/>
-      <c r="K91" s="25" t="s">
+      <c r="K91" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L91" s="23">
@@ -5392,7 +5362,7 @@
       <c r="H92" s="21"/>
       <c r="I92" s="21"/>
       <c r="J92" s="21"/>
-      <c r="K92" s="25" t="s">
+      <c r="K92" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L92" s="23">
@@ -5428,7 +5398,7 @@
       <c r="H93" s="21"/>
       <c r="I93" s="21"/>
       <c r="J93" s="21"/>
-      <c r="K93" s="25" t="s">
+      <c r="K93" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L93" s="23">
@@ -5464,7 +5434,7 @@
       <c r="H94" s="21"/>
       <c r="I94" s="21"/>
       <c r="J94" s="21"/>
-      <c r="K94" s="25" t="s">
+      <c r="K94" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L94" s="23">
@@ -5500,7 +5470,7 @@
       <c r="H95" s="21"/>
       <c r="I95" s="21"/>
       <c r="J95" s="21"/>
-      <c r="K95" s="25" t="s">
+      <c r="K95" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L95" s="23">
@@ -5536,7 +5506,7 @@
       <c r="H96" s="21"/>
       <c r="I96" s="21"/>
       <c r="J96" s="21"/>
-      <c r="K96" s="25" t="s">
+      <c r="K96" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L96" s="23">
@@ -5572,7 +5542,7 @@
       <c r="H97" s="21"/>
       <c r="I97" s="21"/>
       <c r="J97" s="21"/>
-      <c r="K97" s="25" t="s">
+      <c r="K97" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L97" s="23">
@@ -5608,7 +5578,7 @@
       <c r="H98" s="21"/>
       <c r="I98" s="21"/>
       <c r="J98" s="21"/>
-      <c r="K98" s="25" t="s">
+      <c r="K98" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L98" s="23">
@@ -5644,7 +5614,7 @@
       <c r="H99" s="21"/>
       <c r="I99" s="21"/>
       <c r="J99" s="21"/>
-      <c r="K99" s="25" t="s">
+      <c r="K99" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L99" s="23">
@@ -5680,7 +5650,7 @@
       <c r="H100" s="21"/>
       <c r="I100" s="21"/>
       <c r="J100" s="21"/>
-      <c r="K100" s="25" t="s">
+      <c r="K100" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L100" s="23">
@@ -5716,7 +5686,7 @@
       <c r="H101" s="21"/>
       <c r="I101" s="21"/>
       <c r="J101" s="21"/>
-      <c r="K101" s="25" t="s">
+      <c r="K101" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L101" s="23">
@@ -5752,7 +5722,7 @@
       <c r="H102" s="21"/>
       <c r="I102" s="21"/>
       <c r="J102" s="21"/>
-      <c r="K102" s="25" t="s">
+      <c r="K102" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L102" s="23">
@@ -5788,7 +5758,7 @@
       <c r="H103" s="21"/>
       <c r="I103" s="21"/>
       <c r="J103" s="21"/>
-      <c r="K103" s="25" t="s">
+      <c r="K103" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L103" s="23">
@@ -5824,7 +5794,7 @@
       <c r="H104" s="21"/>
       <c r="I104" s="21"/>
       <c r="J104" s="21"/>
-      <c r="K104" s="25" t="s">
+      <c r="K104" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L104" s="23">
@@ -5860,7 +5830,7 @@
       <c r="H105" s="21"/>
       <c r="I105" s="21"/>
       <c r="J105" s="21"/>
-      <c r="K105" s="25" t="s">
+      <c r="K105" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L105" s="23">
@@ -5896,7 +5866,7 @@
       <c r="H106" s="21"/>
       <c r="I106" s="21"/>
       <c r="J106" s="21"/>
-      <c r="K106" s="22" t="s">
+      <c r="K106" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L106" s="23">
@@ -5932,7 +5902,7 @@
       <c r="H107" s="21"/>
       <c r="I107" s="21"/>
       <c r="J107" s="21"/>
-      <c r="K107" s="22" t="s">
+      <c r="K107" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L107" s="23">
@@ -5968,7 +5938,7 @@
       <c r="H108" s="21"/>
       <c r="I108" s="21"/>
       <c r="J108" s="21"/>
-      <c r="K108" s="22" t="s">
+      <c r="K108" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L108" s="23">
@@ -6004,7 +5974,7 @@
       <c r="H109" s="21"/>
       <c r="I109" s="21"/>
       <c r="J109" s="21"/>
-      <c r="K109" s="22" t="s">
+      <c r="K109" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L109" s="23">
@@ -6040,7 +6010,7 @@
       <c r="H110" s="21"/>
       <c r="I110" s="21"/>
       <c r="J110" s="21"/>
-      <c r="K110" s="22" t="s">
+      <c r="K110" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L110" s="23">
@@ -6076,7 +6046,7 @@
       <c r="H111" s="21"/>
       <c r="I111" s="21"/>
       <c r="J111" s="21"/>
-      <c r="K111" s="22" t="s">
+      <c r="K111" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L111" s="23">
@@ -6112,7 +6082,7 @@
       <c r="H112" s="21"/>
       <c r="I112" s="21"/>
       <c r="J112" s="21"/>
-      <c r="K112" s="22" t="s">
+      <c r="K112" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L112" s="23">
@@ -6148,7 +6118,7 @@
       <c r="H113" s="21"/>
       <c r="I113" s="21"/>
       <c r="J113" s="21"/>
-      <c r="K113" s="22" t="s">
+      <c r="K113" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L113" s="23">
@@ -6184,7 +6154,7 @@
       <c r="H114" s="21"/>
       <c r="I114" s="21"/>
       <c r="J114" s="21"/>
-      <c r="K114" s="22" t="s">
+      <c r="K114" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L114" s="23">
@@ -6220,7 +6190,7 @@
       <c r="H115" s="21"/>
       <c r="I115" s="21"/>
       <c r="J115" s="21"/>
-      <c r="K115" s="22" t="s">
+      <c r="K115" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L115" s="23">
@@ -6256,7 +6226,7 @@
       <c r="H116" s="21"/>
       <c r="I116" s="21"/>
       <c r="J116" s="21"/>
-      <c r="K116" s="22" t="s">
+      <c r="K116" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L116" s="23">
@@ -6292,7 +6262,7 @@
       <c r="H117" s="21"/>
       <c r="I117" s="21"/>
       <c r="J117" s="21"/>
-      <c r="K117" s="22" t="s">
+      <c r="K117" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L117" s="23">
@@ -6328,7 +6298,7 @@
       <c r="H118" s="21"/>
       <c r="I118" s="21"/>
       <c r="J118" s="21"/>
-      <c r="K118" s="22" t="s">
+      <c r="K118" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L118" s="23">
@@ -6364,7 +6334,7 @@
       <c r="H119" s="21"/>
       <c r="I119" s="21"/>
       <c r="J119" s="21"/>
-      <c r="K119" s="22" t="s">
+      <c r="K119" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L119" s="23">
@@ -6400,7 +6370,7 @@
       <c r="H120" s="21"/>
       <c r="I120" s="21"/>
       <c r="J120" s="21"/>
-      <c r="K120" s="22" t="s">
+      <c r="K120" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L120" s="23">
@@ -6436,7 +6406,7 @@
       <c r="H121" s="21"/>
       <c r="I121" s="21"/>
       <c r="J121" s="21"/>
-      <c r="K121" s="22" t="s">
+      <c r="K121" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L121" s="23">
@@ -6472,7 +6442,7 @@
       <c r="H122" s="21"/>
       <c r="I122" s="21"/>
       <c r="J122" s="21"/>
-      <c r="K122" s="22" t="s">
+      <c r="K122" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L122" s="23">
@@ -6508,7 +6478,7 @@
       <c r="H123" s="21"/>
       <c r="I123" s="21"/>
       <c r="J123" s="21"/>
-      <c r="K123" s="22" t="s">
+      <c r="K123" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L123" s="23">
@@ -6544,7 +6514,7 @@
       <c r="H124" s="21"/>
       <c r="I124" s="21"/>
       <c r="J124" s="21"/>
-      <c r="K124" s="22" t="s">
+      <c r="K124" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L124" s="23"/>
@@ -6582,7 +6552,7 @@
       <c r="J125" s="8">
         <v>11041011</v>
       </c>
-      <c r="K125" s="9" t="s">
+      <c r="K125" s="27" t="s">
         <v>97</v>
       </c>
       <c r="L125" s="18">
@@ -6623,7 +6593,7 @@
         <v>11041021</v>
       </c>
       <c r="K126" s="9">
-        <v>1104253</v>
+        <v>1104258</v>
       </c>
       <c r="L126" s="18">
         <v>10</v>
@@ -6663,7 +6633,7 @@
         <v>11041031</v>
       </c>
       <c r="K127" s="9">
-        <v>1104254</v>
+        <v>1104259</v>
       </c>
       <c r="L127" s="18">
         <v>20</v>
@@ -6703,7 +6673,7 @@
         <v>11041041</v>
       </c>
       <c r="K128" s="9">
-        <v>1104255</v>
+        <v>1104260</v>
       </c>
       <c r="L128" s="18">
         <v>30</v>
@@ -6743,7 +6713,7 @@
         <v>11041051</v>
       </c>
       <c r="K129" s="9">
-        <v>1104257</v>
+        <v>1104261</v>
       </c>
       <c r="L129" s="18">
         <v>60</v>
@@ -6783,7 +6753,7 @@
         <v>11041061</v>
       </c>
       <c r="K130" s="9">
-        <v>1104258</v>
+        <v>1104262</v>
       </c>
       <c r="L130" s="18">
         <v>80</v>
@@ -6823,7 +6793,7 @@
         <v>11041071</v>
       </c>
       <c r="K131" s="9">
-        <v>1104259</v>
+        <v>1104263</v>
       </c>
       <c r="L131" s="18">
         <v>120</v>
@@ -6863,7 +6833,7 @@
         <v>11041081</v>
       </c>
       <c r="K132" s="9">
-        <v>1104260</v>
+        <v>1104264</v>
       </c>
       <c r="L132" s="18">
         <v>150</v>
@@ -6903,7 +6873,7 @@
         <v>11041091</v>
       </c>
       <c r="K133" s="9">
-        <v>1104261</v>
+        <v>1104265</v>
       </c>
       <c r="L133" s="18">
         <v>200</v>
@@ -6943,7 +6913,7 @@
         <v>11041101</v>
       </c>
       <c r="K134" s="9">
-        <v>1104262</v>
+        <v>1104266</v>
       </c>
       <c r="L134" s="18">
         <v>300</v>
@@ -6983,7 +6953,7 @@
         <v>11041111</v>
       </c>
       <c r="K135" s="9">
-        <v>1104263</v>
+        <v>1104267</v>
       </c>
       <c r="L135" s="18">
         <v>360</v>
@@ -7023,7 +6993,7 @@
         <v>11041121</v>
       </c>
       <c r="K136" s="9">
-        <v>1104264</v>
+        <v>1104268</v>
       </c>
       <c r="L136" s="18">
         <v>420</v>
@@ -7063,7 +7033,7 @@
         <v>11041131</v>
       </c>
       <c r="K137" s="9">
-        <v>1104265</v>
+        <v>1104269</v>
       </c>
       <c r="L137" s="18">
         <v>480</v>
@@ -7103,7 +7073,7 @@
         <v>11041141</v>
       </c>
       <c r="K138" s="9">
-        <v>1104266</v>
+        <v>1104270</v>
       </c>
       <c r="L138" s="18">
         <v>540</v>
@@ -7143,7 +7113,7 @@
         <v>11041151</v>
       </c>
       <c r="K139" s="9">
-        <v>1104267</v>
+        <v>1104271</v>
       </c>
       <c r="L139" s="18">
         <v>600</v>
@@ -7183,7 +7153,7 @@
         <v>11041161</v>
       </c>
       <c r="K140" s="9">
-        <v>1104268</v>
+        <v>1104272</v>
       </c>
       <c r="L140" s="18">
         <v>600</v>
@@ -7216,9 +7186,6 @@
         <v>18000</v>
       </c>
       <c r="H141" s="8"/>
-      <c r="K141" s="9">
-        <v>1104269</v>
-      </c>
       <c r="L141" s="18">
         <v>600</v>
       </c>
@@ -7250,9 +7217,6 @@
         <v>19000</v>
       </c>
       <c r="H142" s="8"/>
-      <c r="K142" s="9">
-        <v>1104270</v>
-      </c>
       <c r="L142" s="18">
         <v>600</v>
       </c>
@@ -7284,9 +7248,6 @@
         <v>20000</v>
       </c>
       <c r="H143" s="8"/>
-      <c r="K143" s="9">
-        <v>1104271</v>
-      </c>
       <c r="L143" s="18">
         <v>600</v>
       </c>
@@ -7318,9 +7279,6 @@
         <v>21000</v>
       </c>
       <c r="H144" s="8"/>
-      <c r="K144" s="9">
-        <v>1104272</v>
-      </c>
       <c r="L144" s="18">
         <v>600</v>
       </c>
@@ -8750,8 +8708,8 @@
       <c r="J186" s="23">
         <v>11051021</v>
       </c>
-      <c r="K186" s="22">
-        <v>1105253</v>
+      <c r="K186" s="25">
+        <v>1105260</v>
       </c>
       <c r="L186" s="23">
         <v>10</v>
@@ -8790,8 +8748,8 @@
       <c r="J187" s="23">
         <v>11051031</v>
       </c>
-      <c r="K187" s="22">
-        <v>1105254</v>
+      <c r="K187" s="25">
+        <v>1105261</v>
       </c>
       <c r="L187" s="23">
         <v>20</v>
@@ -8830,8 +8788,8 @@
       <c r="J188" s="23">
         <v>11051041</v>
       </c>
-      <c r="K188" s="22">
-        <v>1105255</v>
+      <c r="K188" s="25">
+        <v>1105262</v>
       </c>
       <c r="L188" s="23">
         <v>30</v>
@@ -8870,8 +8828,8 @@
       <c r="J189" s="23">
         <v>11051051</v>
       </c>
-      <c r="K189" s="22">
-        <v>1105256</v>
+      <c r="K189" s="25">
+        <v>1105263</v>
       </c>
       <c r="L189" s="23">
         <v>60</v>
@@ -8910,8 +8868,8 @@
       <c r="J190" s="23">
         <v>11051061</v>
       </c>
-      <c r="K190" s="22">
-        <v>1105257</v>
+      <c r="K190" s="25">
+        <v>1105264</v>
       </c>
       <c r="L190" s="23">
         <v>80</v>
@@ -8950,8 +8908,8 @@
       <c r="J191" s="23">
         <v>11051071</v>
       </c>
-      <c r="K191" s="22">
-        <v>1105259</v>
+      <c r="K191" s="25">
+        <v>1105265</v>
       </c>
       <c r="L191" s="23">
         <v>120</v>
@@ -8990,8 +8948,8 @@
       <c r="J192" s="23">
         <v>11051081</v>
       </c>
-      <c r="K192" s="22">
-        <v>1105260</v>
+      <c r="K192" s="25">
+        <v>1105266</v>
       </c>
       <c r="L192" s="23">
         <v>150</v>
@@ -9030,8 +8988,8 @@
       <c r="J193" s="23">
         <v>11051091</v>
       </c>
-      <c r="K193" s="22">
-        <v>1105261</v>
+      <c r="K193" s="25">
+        <v>1105267</v>
       </c>
       <c r="L193" s="23">
         <v>200</v>
@@ -9070,8 +9028,8 @@
       <c r="J194" s="23">
         <v>11051101</v>
       </c>
-      <c r="K194" s="22">
-        <v>1105262</v>
+      <c r="K194" s="25">
+        <v>1105268</v>
       </c>
       <c r="L194" s="23">
         <v>300</v>
@@ -9110,8 +9068,8 @@
       <c r="J195" s="23">
         <v>11051111</v>
       </c>
-      <c r="K195" s="22">
-        <v>1105263</v>
+      <c r="K195" s="25">
+        <v>1105269</v>
       </c>
       <c r="L195" s="23">
         <v>360</v>
@@ -9150,8 +9108,8 @@
       <c r="J196" s="23">
         <v>11051121</v>
       </c>
-      <c r="K196" s="22">
-        <v>1105264</v>
+      <c r="K196" s="25">
+        <v>1105270</v>
       </c>
       <c r="L196" s="23">
         <v>420</v>
@@ -9190,8 +9148,8 @@
       <c r="J197" s="23">
         <v>11051131</v>
       </c>
-      <c r="K197" s="22">
-        <v>1105265</v>
+      <c r="K197" s="25">
+        <v>1105271</v>
       </c>
       <c r="L197" s="23">
         <v>480</v>
@@ -9230,8 +9188,8 @@
       <c r="J198" s="23">
         <v>11051141</v>
       </c>
-      <c r="K198" s="22">
-        <v>1105266</v>
+      <c r="K198" s="25">
+        <v>1105272</v>
       </c>
       <c r="L198" s="23">
         <v>540</v>
@@ -9270,8 +9228,8 @@
       <c r="J199" s="23">
         <v>11051151</v>
       </c>
-      <c r="K199" s="22">
-        <v>1105267</v>
+      <c r="K199" s="25">
+        <v>1105273</v>
       </c>
       <c r="L199" s="23">
         <v>600</v>
@@ -9310,8 +9268,8 @@
       <c r="J200" s="23">
         <v>11051161</v>
       </c>
-      <c r="K200" s="22">
-        <v>1105268</v>
+      <c r="K200" s="25">
+        <v>1105274</v>
       </c>
       <c r="L200" s="23">
         <v>600</v>
@@ -9346,8 +9304,8 @@
       <c r="H201" s="21"/>
       <c r="I201" s="21"/>
       <c r="J201" s="21"/>
-      <c r="K201" s="22">
-        <v>1105269</v>
+      <c r="K201" s="25">
+        <v>1105275</v>
       </c>
       <c r="L201" s="23">
         <v>600</v>
@@ -9382,9 +9340,6 @@
       <c r="H202" s="21"/>
       <c r="I202" s="21"/>
       <c r="J202" s="21"/>
-      <c r="K202" s="22">
-        <v>1105270</v>
-      </c>
       <c r="L202" s="23">
         <v>600</v>
       </c>
@@ -9418,9 +9373,6 @@
       <c r="H203" s="21"/>
       <c r="I203" s="21"/>
       <c r="J203" s="21"/>
-      <c r="K203" s="22">
-        <v>1105271</v>
-      </c>
       <c r="L203" s="23">
         <v>600</v>
       </c>
@@ -9454,9 +9406,6 @@
       <c r="H204" s="21"/>
       <c r="I204" s="21"/>
       <c r="J204" s="21"/>
-      <c r="K204" s="22">
-        <v>1105272</v>
-      </c>
       <c r="L204" s="23">
         <v>600</v>
       </c>
@@ -9490,9 +9439,6 @@
       <c r="H205" s="21"/>
       <c r="I205" s="21"/>
       <c r="J205" s="21"/>
-      <c r="K205" s="22">
-        <v>1105273</v>
-      </c>
       <c r="L205" s="23">
         <v>600</v>
       </c>
@@ -9526,9 +9472,6 @@
       <c r="H206" s="21"/>
       <c r="I206" s="21"/>
       <c r="J206" s="21"/>
-      <c r="K206" s="22">
-        <v>1105274</v>
-      </c>
       <c r="L206" s="23">
         <v>600</v>
       </c>
@@ -9562,9 +9505,6 @@
       <c r="H207" s="21"/>
       <c r="I207" s="21"/>
       <c r="J207" s="21"/>
-      <c r="K207" s="22">
-        <v>1105275</v>
-      </c>
       <c r="L207" s="23">
         <v>600</v>
       </c>
@@ -9664,7 +9604,7 @@
       <c r="H210" s="21"/>
       <c r="I210" s="21"/>
       <c r="J210" s="21"/>
-      <c r="K210" s="25" t="s">
+      <c r="K210" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L210" s="23">
@@ -9700,7 +9640,7 @@
       <c r="H211" s="21"/>
       <c r="I211" s="21"/>
       <c r="J211" s="21"/>
-      <c r="K211" s="25" t="s">
+      <c r="K211" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L211" s="23">
@@ -9736,7 +9676,7 @@
       <c r="H212" s="21"/>
       <c r="I212" s="21"/>
       <c r="J212" s="21"/>
-      <c r="K212" s="25" t="s">
+      <c r="K212" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L212" s="23">
@@ -9772,7 +9712,7 @@
       <c r="H213" s="21"/>
       <c r="I213" s="21"/>
       <c r="J213" s="21"/>
-      <c r="K213" s="25" t="s">
+      <c r="K213" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L213" s="23">
@@ -9808,7 +9748,7 @@
       <c r="H214" s="21"/>
       <c r="I214" s="21"/>
       <c r="J214" s="21"/>
-      <c r="K214" s="25" t="s">
+      <c r="K214" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L214" s="23">
@@ -9844,7 +9784,7 @@
       <c r="H215" s="21"/>
       <c r="I215" s="21"/>
       <c r="J215" s="21"/>
-      <c r="K215" s="25" t="s">
+      <c r="K215" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L215" s="23">
@@ -9880,7 +9820,7 @@
       <c r="H216" s="21"/>
       <c r="I216" s="21"/>
       <c r="J216" s="21"/>
-      <c r="K216" s="25" t="s">
+      <c r="K216" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L216" s="23">
@@ -9916,7 +9856,7 @@
       <c r="H217" s="21"/>
       <c r="I217" s="21"/>
       <c r="J217" s="21"/>
-      <c r="K217" s="25" t="s">
+      <c r="K217" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L217" s="23">
@@ -9952,7 +9892,7 @@
       <c r="H218" s="21"/>
       <c r="I218" s="21"/>
       <c r="J218" s="21"/>
-      <c r="K218" s="25" t="s">
+      <c r="K218" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L218" s="23">
@@ -9988,7 +9928,7 @@
       <c r="H219" s="21"/>
       <c r="I219" s="21"/>
       <c r="J219" s="21"/>
-      <c r="K219" s="25" t="s">
+      <c r="K219" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L219" s="23">
@@ -10024,7 +9964,7 @@
       <c r="H220" s="21"/>
       <c r="I220" s="21"/>
       <c r="J220" s="21"/>
-      <c r="K220" s="25" t="s">
+      <c r="K220" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L220" s="23">
@@ -10060,7 +10000,7 @@
       <c r="H221" s="21"/>
       <c r="I221" s="21"/>
       <c r="J221" s="21"/>
-      <c r="K221" s="25" t="s">
+      <c r="K221" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L221" s="23">
@@ -10096,7 +10036,7 @@
       <c r="H222" s="21"/>
       <c r="I222" s="21"/>
       <c r="J222" s="21"/>
-      <c r="K222" s="25" t="s">
+      <c r="K222" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L222" s="23">
@@ -10132,7 +10072,7 @@
       <c r="H223" s="21"/>
       <c r="I223" s="21"/>
       <c r="J223" s="21"/>
-      <c r="K223" s="25" t="s">
+      <c r="K223" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L223" s="23">
@@ -10168,7 +10108,7 @@
       <c r="H224" s="21"/>
       <c r="I224" s="21"/>
       <c r="J224" s="21"/>
-      <c r="K224" s="25" t="s">
+      <c r="K224" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L224" s="23">
@@ -10204,7 +10144,7 @@
       <c r="H225" s="21"/>
       <c r="I225" s="21"/>
       <c r="J225" s="21"/>
-      <c r="K225" s="25" t="s">
+      <c r="K225" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L225" s="23">
@@ -10240,7 +10180,7 @@
       <c r="H226" s="21"/>
       <c r="I226" s="21"/>
       <c r="J226" s="21"/>
-      <c r="K226" s="22" t="s">
+      <c r="K226" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L226" s="23">
@@ -10276,7 +10216,7 @@
       <c r="H227" s="21"/>
       <c r="I227" s="21"/>
       <c r="J227" s="21"/>
-      <c r="K227" s="22" t="s">
+      <c r="K227" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L227" s="23">
@@ -10312,7 +10252,7 @@
       <c r="H228" s="21"/>
       <c r="I228" s="21"/>
       <c r="J228" s="21"/>
-      <c r="K228" s="22" t="s">
+      <c r="K228" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L228" s="23">
@@ -10348,7 +10288,7 @@
       <c r="H229" s="21"/>
       <c r="I229" s="21"/>
       <c r="J229" s="21"/>
-      <c r="K229" s="22" t="s">
+      <c r="K229" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L229" s="23">
@@ -10384,7 +10324,7 @@
       <c r="H230" s="21"/>
       <c r="I230" s="21"/>
       <c r="J230" s="21"/>
-      <c r="K230" s="22" t="s">
+      <c r="K230" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L230" s="23">
@@ -10420,7 +10360,7 @@
       <c r="H231" s="21"/>
       <c r="I231" s="21"/>
       <c r="J231" s="21"/>
-      <c r="K231" s="22" t="s">
+      <c r="K231" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L231" s="23">
@@ -10456,7 +10396,7 @@
       <c r="H232" s="21"/>
       <c r="I232" s="21"/>
       <c r="J232" s="21"/>
-      <c r="K232" s="22" t="s">
+      <c r="K232" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L232" s="23">
@@ -10492,7 +10432,7 @@
       <c r="H233" s="21"/>
       <c r="I233" s="21"/>
       <c r="J233" s="21"/>
-      <c r="K233" s="22" t="s">
+      <c r="K233" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L233" s="23">
@@ -10528,7 +10468,7 @@
       <c r="H234" s="21"/>
       <c r="I234" s="21"/>
       <c r="J234" s="21"/>
-      <c r="K234" s="22" t="s">
+      <c r="K234" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L234" s="23">
@@ -10564,7 +10504,7 @@
       <c r="H235" s="21"/>
       <c r="I235" s="21"/>
       <c r="J235" s="21"/>
-      <c r="K235" s="22" t="s">
+      <c r="K235" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L235" s="23">
@@ -10600,7 +10540,7 @@
       <c r="H236" s="21"/>
       <c r="I236" s="21"/>
       <c r="J236" s="21"/>
-      <c r="K236" s="22" t="s">
+      <c r="K236" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L236" s="23">
@@ -10636,7 +10576,7 @@
       <c r="H237" s="21"/>
       <c r="I237" s="21"/>
       <c r="J237" s="21"/>
-      <c r="K237" s="22" t="s">
+      <c r="K237" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L237" s="23">
@@ -10672,7 +10612,7 @@
       <c r="H238" s="21"/>
       <c r="I238" s="21"/>
       <c r="J238" s="21"/>
-      <c r="K238" s="22" t="s">
+      <c r="K238" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L238" s="23">
@@ -10708,7 +10648,7 @@
       <c r="H239" s="21"/>
       <c r="I239" s="21"/>
       <c r="J239" s="21"/>
-      <c r="K239" s="22" t="s">
+      <c r="K239" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L239" s="23">
@@ -10744,7 +10684,7 @@
       <c r="H240" s="21"/>
       <c r="I240" s="21"/>
       <c r="J240" s="21"/>
-      <c r="K240" s="22" t="s">
+      <c r="K240" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L240" s="23">
@@ -10780,7 +10720,7 @@
       <c r="H241" s="21"/>
       <c r="I241" s="21"/>
       <c r="J241" s="21"/>
-      <c r="K241" s="22" t="s">
+      <c r="K241" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L241" s="23">
@@ -10816,7 +10756,7 @@
       <c r="H242" s="21"/>
       <c r="I242" s="21"/>
       <c r="J242" s="21"/>
-      <c r="K242" s="22" t="s">
+      <c r="K242" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L242" s="23">
@@ -10852,7 +10792,7 @@
       <c r="H243" s="21"/>
       <c r="I243" s="21"/>
       <c r="J243" s="21"/>
-      <c r="K243" s="22" t="s">
+      <c r="K243" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L243" s="23">
@@ -10888,7 +10828,7 @@
       <c r="H244" s="21"/>
       <c r="I244" s="21"/>
       <c r="J244" s="21"/>
-      <c r="K244" s="22" t="s">
+      <c r="K244" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L244" s="23"/>
@@ -10926,7 +10866,7 @@
       <c r="J245" s="18">
         <v>11061011</v>
       </c>
-      <c r="K245" s="9" t="s">
+      <c r="K245" s="27" t="s">
         <v>101</v>
       </c>
       <c r="L245" s="18">
@@ -10967,7 +10907,7 @@
         <v>11061021</v>
       </c>
       <c r="K246" s="9">
-        <v>1106253</v>
+        <v>1106258</v>
       </c>
       <c r="L246" s="18">
         <v>10</v>
@@ -11007,7 +10947,7 @@
         <v>11061031</v>
       </c>
       <c r="K247" s="9">
-        <v>1106254</v>
+        <v>1106259</v>
       </c>
       <c r="L247" s="18">
         <v>20</v>
@@ -11047,7 +10987,7 @@
         <v>11061041</v>
       </c>
       <c r="K248" s="9">
-        <v>1106255</v>
+        <v>1106260</v>
       </c>
       <c r="L248" s="18">
         <v>30</v>
@@ -11087,7 +11027,7 @@
         <v>11061051</v>
       </c>
       <c r="K249" s="9">
-        <v>1106256</v>
+        <v>1106261</v>
       </c>
       <c r="L249" s="18">
         <v>60</v>
@@ -11127,7 +11067,7 @@
         <v>11061061</v>
       </c>
       <c r="K250" s="9">
-        <v>1106257</v>
+        <v>1106263</v>
       </c>
       <c r="L250" s="18">
         <v>80</v>
@@ -11167,7 +11107,7 @@
         <v>11061071</v>
       </c>
       <c r="K251" s="9">
-        <v>1106258</v>
+        <v>1106264</v>
       </c>
       <c r="L251" s="18">
         <v>120</v>
@@ -11207,7 +11147,7 @@
         <v>11061081</v>
       </c>
       <c r="K252" s="9">
-        <v>1106259</v>
+        <v>1106265</v>
       </c>
       <c r="L252" s="18">
         <v>150</v>
@@ -11247,7 +11187,7 @@
         <v>11061091</v>
       </c>
       <c r="K253" s="9">
-        <v>1106260</v>
+        <v>1106266</v>
       </c>
       <c r="L253" s="18">
         <v>200</v>
@@ -11287,7 +11227,7 @@
         <v>11061101</v>
       </c>
       <c r="K254" s="9">
-        <v>1106261</v>
+        <v>1106267</v>
       </c>
       <c r="L254" s="18">
         <v>300</v>
@@ -11327,7 +11267,7 @@
         <v>11061111</v>
       </c>
       <c r="K255" s="9">
-        <v>1106263</v>
+        <v>1106268</v>
       </c>
       <c r="L255" s="18">
         <v>360</v>
@@ -11367,7 +11307,7 @@
         <v>11061121</v>
       </c>
       <c r="K256" s="9">
-        <v>1106264</v>
+        <v>1106269</v>
       </c>
       <c r="L256" s="18">
         <v>420</v>
@@ -11407,7 +11347,7 @@
         <v>11061131</v>
       </c>
       <c r="K257" s="9">
-        <v>1106265</v>
+        <v>1106270</v>
       </c>
       <c r="L257" s="18">
         <v>480</v>
@@ -11446,9 +11386,6 @@
       <c r="J258" s="18">
         <v>11061141</v>
       </c>
-      <c r="K258" s="9">
-        <v>1106266</v>
-      </c>
       <c r="L258" s="18">
         <v>540</v>
       </c>
@@ -11486,9 +11423,6 @@
       <c r="J259" s="18">
         <v>11061151</v>
       </c>
-      <c r="K259" s="9">
-        <v>1106267</v>
-      </c>
       <c r="L259" s="18">
         <v>600</v>
       </c>
@@ -11526,9 +11460,6 @@
       <c r="J260" s="18">
         <v>11061161</v>
       </c>
-      <c r="K260" s="9">
-        <v>1106268</v>
-      </c>
       <c r="L260" s="18">
         <v>600</v>
       </c>
@@ -11560,9 +11491,6 @@
         <v>18000</v>
       </c>
       <c r="H261" s="8"/>
-      <c r="K261" s="9">
-        <v>1106269</v>
-      </c>
       <c r="L261" s="18">
         <v>600</v>
       </c>
@@ -11594,9 +11522,6 @@
         <v>19000</v>
       </c>
       <c r="H262" s="8"/>
-      <c r="K262" s="9">
-        <v>1106270</v>
-      </c>
       <c r="L262" s="18">
         <v>600</v>
       </c>
@@ -13054,7 +12979,7 @@
       <c r="J305" s="21">
         <v>11071011</v>
       </c>
-      <c r="K305" s="22" t="s">
+      <c r="K305" s="25" t="s">
         <v>103</v>
       </c>
       <c r="L305" s="23">
@@ -13094,7 +13019,7 @@
       <c r="J306" s="21">
         <v>11071012</v>
       </c>
-      <c r="K306" s="22">
+      <c r="K306" s="25">
         <v>1107252</v>
       </c>
       <c r="L306" s="23">
@@ -13134,7 +13059,7 @@
       <c r="J307" s="21">
         <v>11071013</v>
       </c>
-      <c r="K307" s="22">
+      <c r="K307" s="25">
         <v>1107254</v>
       </c>
       <c r="L307" s="23">
@@ -13174,7 +13099,7 @@
       <c r="J308" s="21">
         <v>11071014</v>
       </c>
-      <c r="K308" s="22">
+      <c r="K308" s="25">
         <v>1107255</v>
       </c>
       <c r="L308" s="23">
@@ -13214,7 +13139,7 @@
       <c r="J309" s="21">
         <v>11071015</v>
       </c>
-      <c r="K309" s="22">
+      <c r="K309" s="25">
         <v>1107256</v>
       </c>
       <c r="L309" s="23">
@@ -13254,7 +13179,7 @@
       <c r="J310" s="21">
         <v>11071016</v>
       </c>
-      <c r="K310" s="22">
+      <c r="K310" s="25">
         <v>1107257</v>
       </c>
       <c r="L310" s="23">
@@ -13294,7 +13219,7 @@
       <c r="J311" s="23">
         <v>11071021</v>
       </c>
-      <c r="K311" s="22">
+      <c r="K311" s="25">
         <v>1107258</v>
       </c>
       <c r="L311" s="23">
@@ -13334,7 +13259,7 @@
       <c r="J312" s="23">
         <v>11071022</v>
       </c>
-      <c r="K312" s="22">
+      <c r="K312" s="25">
         <v>1107259</v>
       </c>
       <c r="L312" s="23">
@@ -13374,7 +13299,7 @@
       <c r="J313" s="23">
         <v>11071023</v>
       </c>
-      <c r="K313" s="22">
+      <c r="K313" s="25">
         <v>1107260</v>
       </c>
       <c r="L313" s="23">
@@ -13414,7 +13339,7 @@
       <c r="J314" s="23">
         <v>11071024</v>
       </c>
-      <c r="K314" s="22">
+      <c r="K314" s="25">
         <v>1107261</v>
       </c>
       <c r="L314" s="23">
@@ -13454,7 +13379,7 @@
       <c r="J315" s="23">
         <v>11071025</v>
       </c>
-      <c r="K315" s="22">
+      <c r="K315" s="25">
         <v>1107262</v>
       </c>
       <c r="L315" s="23">
@@ -13494,7 +13419,7 @@
       <c r="J316" s="23">
         <v>11071026</v>
       </c>
-      <c r="K316" s="22">
+      <c r="K316" s="25">
         <v>1107263</v>
       </c>
       <c r="L316" s="23">
@@ -13534,7 +13459,7 @@
       <c r="J317" s="21">
         <v>11071031</v>
       </c>
-      <c r="K317" s="22">
+      <c r="K317" s="25">
         <v>1107264</v>
       </c>
       <c r="L317" s="23">
@@ -13574,7 +13499,7 @@
       <c r="J318" s="21">
         <v>11071032</v>
       </c>
-      <c r="K318" s="22">
+      <c r="K318" s="25">
         <v>1107265</v>
       </c>
       <c r="L318" s="23">
@@ -13614,7 +13539,7 @@
       <c r="J319" s="21">
         <v>11071033</v>
       </c>
-      <c r="K319" s="22">
+      <c r="K319" s="25">
         <v>1107266</v>
       </c>
       <c r="L319" s="23">
@@ -13654,7 +13579,7 @@
       <c r="J320" s="21">
         <v>11071034</v>
       </c>
-      <c r="K320" s="22">
+      <c r="K320" s="25">
         <v>1107267</v>
       </c>
       <c r="L320" s="23">
@@ -13731,7 +13656,7 @@
       <c r="J322" s="21">
         <v>11071036</v>
       </c>
-      <c r="K322" s="22" t="s">
+      <c r="K322" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L322" s="23">
@@ -13771,7 +13696,7 @@
       <c r="J323" s="21">
         <v>11071041</v>
       </c>
-      <c r="K323" s="22" t="s">
+      <c r="K323" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L323" s="23">
@@ -13811,7 +13736,7 @@
       <c r="J324" s="21">
         <v>11071042</v>
       </c>
-      <c r="K324" s="22" t="s">
+      <c r="K324" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L324" s="23">
@@ -13851,7 +13776,7 @@
       <c r="J325" s="21">
         <v>11071043</v>
       </c>
-      <c r="K325" s="22" t="s">
+      <c r="K325" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L325" s="23">
@@ -13891,7 +13816,7 @@
       <c r="J326" s="21">
         <v>11071044</v>
       </c>
-      <c r="K326" s="22" t="s">
+      <c r="K326" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L326" s="23">
@@ -13931,7 +13856,7 @@
       <c r="J327" s="21">
         <v>11071045</v>
       </c>
-      <c r="K327" s="22" t="s">
+      <c r="K327" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L327" s="23">
@@ -13971,7 +13896,7 @@
       <c r="J328" s="21">
         <v>11071046</v>
       </c>
-      <c r="K328" s="22" t="s">
+      <c r="K328" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L328" s="23">
@@ -14007,7 +13932,7 @@
       <c r="H329" s="21"/>
       <c r="I329" s="21"/>
       <c r="J329" s="21"/>
-      <c r="K329" s="25" t="s">
+      <c r="K329" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L329" s="23">
@@ -14043,7 +13968,7 @@
       <c r="H330" s="21"/>
       <c r="I330" s="21"/>
       <c r="J330" s="21"/>
-      <c r="K330" s="25" t="s">
+      <c r="K330" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L330" s="23">
@@ -14079,7 +14004,7 @@
       <c r="H331" s="21"/>
       <c r="I331" s="21"/>
       <c r="J331" s="21"/>
-      <c r="K331" s="25" t="s">
+      <c r="K331" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L331" s="23">
@@ -14115,7 +14040,7 @@
       <c r="H332" s="21"/>
       <c r="I332" s="21"/>
       <c r="J332" s="21"/>
-      <c r="K332" s="25" t="s">
+      <c r="K332" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L332" s="23">
@@ -14151,7 +14076,7 @@
       <c r="H333" s="21"/>
       <c r="I333" s="21"/>
       <c r="J333" s="21"/>
-      <c r="K333" s="25" t="s">
+      <c r="K333" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L333" s="23">
@@ -14187,7 +14112,7 @@
       <c r="H334" s="21"/>
       <c r="I334" s="21"/>
       <c r="J334" s="21"/>
-      <c r="K334" s="25" t="s">
+      <c r="K334" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L334" s="23">
@@ -14223,7 +14148,7 @@
       <c r="H335" s="21"/>
       <c r="I335" s="21"/>
       <c r="J335" s="21"/>
-      <c r="K335" s="25" t="s">
+      <c r="K335" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L335" s="23">
@@ -14259,7 +14184,7 @@
       <c r="H336" s="21"/>
       <c r="I336" s="21"/>
       <c r="J336" s="21"/>
-      <c r="K336" s="25" t="s">
+      <c r="K336" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L336" s="23">
@@ -14295,7 +14220,7 @@
       <c r="H337" s="21"/>
       <c r="I337" s="21"/>
       <c r="J337" s="21"/>
-      <c r="K337" s="25" t="s">
+      <c r="K337" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L337" s="23">
@@ -14331,7 +14256,7 @@
       <c r="H338" s="21"/>
       <c r="I338" s="21"/>
       <c r="J338" s="21"/>
-      <c r="K338" s="25" t="s">
+      <c r="K338" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L338" s="23">
@@ -14367,7 +14292,7 @@
       <c r="H339" s="21"/>
       <c r="I339" s="21"/>
       <c r="J339" s="21"/>
-      <c r="K339" s="25" t="s">
+      <c r="K339" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L339" s="23">
@@ -14403,7 +14328,7 @@
       <c r="H340" s="21"/>
       <c r="I340" s="21"/>
       <c r="J340" s="21"/>
-      <c r="K340" s="25" t="s">
+      <c r="K340" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L340" s="23">
@@ -14439,7 +14364,7 @@
       <c r="H341" s="21"/>
       <c r="I341" s="21"/>
       <c r="J341" s="21"/>
-      <c r="K341" s="25" t="s">
+      <c r="K341" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L341" s="23">
@@ -14475,7 +14400,7 @@
       <c r="H342" s="21"/>
       <c r="I342" s="21"/>
       <c r="J342" s="21"/>
-      <c r="K342" s="25" t="s">
+      <c r="K342" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L342" s="23">
@@ -14511,7 +14436,7 @@
       <c r="H343" s="21"/>
       <c r="I343" s="21"/>
       <c r="J343" s="21"/>
-      <c r="K343" s="25" t="s">
+      <c r="K343" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L343" s="23">
@@ -14547,7 +14472,7 @@
       <c r="H344" s="21"/>
       <c r="I344" s="21"/>
       <c r="J344" s="21"/>
-      <c r="K344" s="25" t="s">
+      <c r="K344" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L344" s="23">
@@ -14583,7 +14508,7 @@
       <c r="H345" s="21"/>
       <c r="I345" s="21"/>
       <c r="J345" s="21"/>
-      <c r="K345" s="25" t="s">
+      <c r="K345" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L345" s="23">
@@ -14619,7 +14544,7 @@
       <c r="H346" s="21"/>
       <c r="I346" s="21"/>
       <c r="J346" s="21"/>
-      <c r="K346" s="22" t="s">
+      <c r="K346" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L346" s="23">
@@ -14655,7 +14580,7 @@
       <c r="H347" s="21"/>
       <c r="I347" s="21"/>
       <c r="J347" s="21"/>
-      <c r="K347" s="22" t="s">
+      <c r="K347" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L347" s="23">
@@ -14691,7 +14616,7 @@
       <c r="H348" s="21"/>
       <c r="I348" s="21"/>
       <c r="J348" s="21"/>
-      <c r="K348" s="22" t="s">
+      <c r="K348" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L348" s="23">
@@ -14727,7 +14652,7 @@
       <c r="H349" s="21"/>
       <c r="I349" s="21"/>
       <c r="J349" s="21"/>
-      <c r="K349" s="22" t="s">
+      <c r="K349" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L349" s="23">
@@ -14763,7 +14688,7 @@
       <c r="H350" s="21"/>
       <c r="I350" s="21"/>
       <c r="J350" s="21"/>
-      <c r="K350" s="22" t="s">
+      <c r="K350" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L350" s="23">
@@ -14799,7 +14724,7 @@
       <c r="H351" s="21"/>
       <c r="I351" s="21"/>
       <c r="J351" s="21"/>
-      <c r="K351" s="22" t="s">
+      <c r="K351" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L351" s="23">
@@ -14835,7 +14760,7 @@
       <c r="H352" s="21"/>
       <c r="I352" s="21"/>
       <c r="J352" s="21"/>
-      <c r="K352" s="22" t="s">
+      <c r="K352" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L352" s="23">
@@ -14871,7 +14796,7 @@
       <c r="H353" s="21"/>
       <c r="I353" s="21"/>
       <c r="J353" s="21"/>
-      <c r="K353" s="22" t="s">
+      <c r="K353" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L353" s="23">
@@ -14907,7 +14832,7 @@
       <c r="H354" s="21"/>
       <c r="I354" s="21"/>
       <c r="J354" s="21"/>
-      <c r="K354" s="22" t="s">
+      <c r="K354" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L354" s="23">
@@ -14943,7 +14868,7 @@
       <c r="H355" s="21"/>
       <c r="I355" s="21"/>
       <c r="J355" s="21"/>
-      <c r="K355" s="22" t="s">
+      <c r="K355" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L355" s="23">
@@ -14979,7 +14904,7 @@
       <c r="H356" s="21"/>
       <c r="I356" s="21"/>
       <c r="J356" s="21"/>
-      <c r="K356" s="22" t="s">
+      <c r="K356" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L356" s="23">
@@ -15015,7 +14940,7 @@
       <c r="H357" s="21"/>
       <c r="I357" s="21"/>
       <c r="J357" s="21"/>
-      <c r="K357" s="22" t="s">
+      <c r="K357" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L357" s="23">
@@ -15051,7 +14976,7 @@
       <c r="H358" s="21"/>
       <c r="I358" s="21"/>
       <c r="J358" s="21"/>
-      <c r="K358" s="22" t="s">
+      <c r="K358" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L358" s="23">
@@ -15087,7 +15012,7 @@
       <c r="H359" s="21"/>
       <c r="I359" s="21"/>
       <c r="J359" s="21"/>
-      <c r="K359" s="22" t="s">
+      <c r="K359" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L359" s="23">
@@ -15123,7 +15048,7 @@
       <c r="H360" s="21"/>
       <c r="I360" s="21"/>
       <c r="J360" s="21"/>
-      <c r="K360" s="22" t="s">
+      <c r="K360" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L360" s="23">
@@ -15159,7 +15084,7 @@
       <c r="H361" s="21"/>
       <c r="I361" s="21"/>
       <c r="J361" s="21"/>
-      <c r="K361" s="22" t="s">
+      <c r="K361" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L361" s="23">
@@ -15195,7 +15120,7 @@
       <c r="H362" s="21"/>
       <c r="I362" s="21"/>
       <c r="J362" s="21"/>
-      <c r="K362" s="22" t="s">
+      <c r="K362" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L362" s="23">
@@ -15231,7 +15156,7 @@
       <c r="H363" s="21"/>
       <c r="I363" s="21"/>
       <c r="J363" s="21"/>
-      <c r="K363" s="22" t="s">
+      <c r="K363" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L363" s="23">
@@ -15267,7 +15192,7 @@
       <c r="H364" s="21"/>
       <c r="I364" s="21"/>
       <c r="J364" s="21"/>
-      <c r="K364" s="22" t="s">
+      <c r="K364" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L364" s="23"/>
@@ -15346,7 +15271,7 @@
         <v>11081012</v>
       </c>
       <c r="K366" s="9">
-        <v>1108253</v>
+        <v>1108255</v>
       </c>
       <c r="L366" s="18">
         <v>10</v>
@@ -15386,7 +15311,7 @@
         <v>11081013</v>
       </c>
       <c r="K367" s="9">
-        <v>1108255</v>
+        <v>1108256</v>
       </c>
       <c r="L367" s="18">
         <v>20</v>
@@ -15426,7 +15351,7 @@
         <v>11081014</v>
       </c>
       <c r="K368" s="9">
-        <v>1108256</v>
+        <v>1108257</v>
       </c>
       <c r="L368" s="18">
         <v>30</v>
@@ -15466,7 +15391,7 @@
         <v>11081015</v>
       </c>
       <c r="K369" s="9">
-        <v>1108257</v>
+        <v>1108258</v>
       </c>
       <c r="L369" s="18">
         <v>60</v>
@@ -15506,7 +15431,7 @@
         <v>11081016</v>
       </c>
       <c r="K370" s="9">
-        <v>1108258</v>
+        <v>1108259</v>
       </c>
       <c r="L370" s="18">
         <v>80</v>
@@ -15546,7 +15471,7 @@
         <v>11081021</v>
       </c>
       <c r="K371" s="9">
-        <v>1108259</v>
+        <v>1108260</v>
       </c>
       <c r="L371" s="18">
         <v>120</v>
@@ -15586,7 +15511,7 @@
         <v>11081022</v>
       </c>
       <c r="K372" s="9">
-        <v>1108260</v>
+        <v>1108261</v>
       </c>
       <c r="L372" s="18">
         <v>150</v>
@@ -15626,7 +15551,7 @@
         <v>11081023</v>
       </c>
       <c r="K373" s="9">
-        <v>1108261</v>
+        <v>1108262</v>
       </c>
       <c r="L373" s="18">
         <v>200</v>
@@ -15666,7 +15591,7 @@
         <v>11081024</v>
       </c>
       <c r="K374" s="9">
-        <v>1108262</v>
+        <v>1108263</v>
       </c>
       <c r="L374" s="18">
         <v>300</v>
@@ -15706,7 +15631,7 @@
         <v>11081025</v>
       </c>
       <c r="K375" s="9">
-        <v>1108263</v>
+        <v>1108264</v>
       </c>
       <c r="L375" s="18">
         <v>360</v>
@@ -15746,7 +15671,7 @@
         <v>11081026</v>
       </c>
       <c r="K376" s="9">
-        <v>1108264</v>
+        <v>1108265</v>
       </c>
       <c r="L376" s="18">
         <v>420</v>
@@ -15786,7 +15711,7 @@
         <v>11081031</v>
       </c>
       <c r="K377" s="9">
-        <v>1108265</v>
+        <v>1108266</v>
       </c>
       <c r="L377" s="18">
         <v>480</v>
@@ -15826,7 +15751,7 @@
         <v>11081032</v>
       </c>
       <c r="K378" s="9">
-        <v>1108266</v>
+        <v>1108267</v>
       </c>
       <c r="L378" s="18">
         <v>540</v>
@@ -15866,7 +15791,7 @@
         <v>11081033</v>
       </c>
       <c r="K379" s="9">
-        <v>1108267</v>
+        <v>1108268</v>
       </c>
       <c r="L379" s="18">
         <v>600</v>
@@ -15905,9 +15830,6 @@
       <c r="J380" s="8">
         <v>11081034</v>
       </c>
-      <c r="K380" s="9">
-        <v>1108268</v>
-      </c>
       <c r="L380" s="18">
         <v>600</v>
       </c>
@@ -17481,7 +17403,7 @@
       <c r="J425" s="21">
         <v>11091011</v>
       </c>
-      <c r="K425" s="22" t="s">
+      <c r="K425" s="25" t="s">
         <v>107</v>
       </c>
       <c r="L425" s="23">
@@ -17521,8 +17443,8 @@
       <c r="J426" s="21">
         <v>11091012</v>
       </c>
-      <c r="K426" s="22">
-        <v>1109253</v>
+      <c r="K426" s="25">
+        <v>1109255</v>
       </c>
       <c r="L426" s="23">
         <v>10</v>
@@ -17561,8 +17483,8 @@
       <c r="J427" s="21">
         <v>11091013</v>
       </c>
-      <c r="K427" s="22">
-        <v>1109255</v>
+      <c r="K427" s="25">
+        <v>1109256</v>
       </c>
       <c r="L427" s="23">
         <v>20</v>
@@ -17601,8 +17523,8 @@
       <c r="J428" s="21">
         <v>11091014</v>
       </c>
-      <c r="K428" s="22">
-        <v>1109256</v>
+      <c r="K428" s="25">
+        <v>1109257</v>
       </c>
       <c r="L428" s="23">
         <v>30</v>
@@ -17641,8 +17563,8 @@
       <c r="J429" s="21">
         <v>11091015</v>
       </c>
-      <c r="K429" s="22">
-        <v>1109257</v>
+      <c r="K429" s="25">
+        <v>1109258</v>
       </c>
       <c r="L429" s="23">
         <v>60</v>
@@ -17681,8 +17603,8 @@
       <c r="J430" s="21">
         <v>11091016</v>
       </c>
-      <c r="K430" s="22">
-        <v>1109258</v>
+      <c r="K430" s="25">
+        <v>1109259</v>
       </c>
       <c r="L430" s="23">
         <v>80</v>
@@ -17721,8 +17643,8 @@
       <c r="J431" s="21">
         <v>11091021</v>
       </c>
-      <c r="K431" s="22">
-        <v>1109259</v>
+      <c r="K431" s="25">
+        <v>1109260</v>
       </c>
       <c r="L431" s="23">
         <v>120</v>
@@ -17761,8 +17683,8 @@
       <c r="J432" s="21">
         <v>11091022</v>
       </c>
-      <c r="K432" s="22">
-        <v>1109260</v>
+      <c r="K432" s="25">
+        <v>1109261</v>
       </c>
       <c r="L432" s="23">
         <v>150</v>
@@ -17801,8 +17723,8 @@
       <c r="J433" s="21">
         <v>11091023</v>
       </c>
-      <c r="K433" s="22">
-        <v>1109261</v>
+      <c r="K433" s="25">
+        <v>1109262</v>
       </c>
       <c r="L433" s="23">
         <v>200</v>
@@ -17841,8 +17763,8 @@
       <c r="J434" s="21">
         <v>11091024</v>
       </c>
-      <c r="K434" s="22">
-        <v>1109262</v>
+      <c r="K434" s="25">
+        <v>1109263</v>
       </c>
       <c r="L434" s="23">
         <v>300</v>
@@ -17881,8 +17803,8 @@
       <c r="J435" s="21">
         <v>11091025</v>
       </c>
-      <c r="K435" s="22">
-        <v>1109263</v>
+      <c r="K435" s="25">
+        <v>1109264</v>
       </c>
       <c r="L435" s="23">
         <v>360</v>
@@ -17921,8 +17843,8 @@
       <c r="J436" s="21">
         <v>11091026</v>
       </c>
-      <c r="K436" s="22">
-        <v>1109264</v>
+      <c r="K436" s="25">
+        <v>1109265</v>
       </c>
       <c r="L436" s="23">
         <v>420</v>
@@ -17961,8 +17883,8 @@
       <c r="J437" s="21">
         <v>11091031</v>
       </c>
-      <c r="K437" s="22">
-        <v>1109265</v>
+      <c r="K437" s="25">
+        <v>1109266</v>
       </c>
       <c r="L437" s="23">
         <v>480</v>
@@ -18001,8 +17923,8 @@
       <c r="J438" s="21">
         <v>11091032</v>
       </c>
-      <c r="K438" s="22">
-        <v>1109266</v>
+      <c r="K438" s="25">
+        <v>1109267</v>
       </c>
       <c r="L438" s="23">
         <v>540</v>
@@ -18041,8 +17963,8 @@
       <c r="J439" s="21">
         <v>11091033</v>
       </c>
-      <c r="K439" s="22">
-        <v>1109267</v>
+      <c r="K439" s="25">
+        <v>1109268</v>
       </c>
       <c r="L439" s="23">
         <v>600</v>
@@ -18081,9 +18003,6 @@
       <c r="J440" s="21">
         <v>11091034</v>
       </c>
-      <c r="K440" s="22">
-        <v>1109268</v>
-      </c>
       <c r="L440" s="23">
         <v>600</v>
       </c>
@@ -18195,7 +18114,7 @@
       <c r="J443" s="21">
         <v>11091041</v>
       </c>
-      <c r="K443" s="22" t="s">
+      <c r="K443" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L443" s="23">
@@ -18235,7 +18154,7 @@
       <c r="J444" s="21">
         <v>11091042</v>
       </c>
-      <c r="K444" s="22" t="s">
+      <c r="K444" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L444" s="23">
@@ -18275,7 +18194,7 @@
       <c r="J445" s="21">
         <v>11091043</v>
       </c>
-      <c r="K445" s="22" t="s">
+      <c r="K445" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L445" s="23">
@@ -18315,7 +18234,7 @@
       <c r="J446" s="21">
         <v>11091044</v>
       </c>
-      <c r="K446" s="22" t="s">
+      <c r="K446" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L446" s="23">
@@ -18355,7 +18274,7 @@
       <c r="J447" s="21">
         <v>11091045</v>
       </c>
-      <c r="K447" s="22" t="s">
+      <c r="K447" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L447" s="23">
@@ -18395,7 +18314,7 @@
       <c r="J448" s="21">
         <v>11091046</v>
       </c>
-      <c r="K448" s="22" t="s">
+      <c r="K448" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L448" s="23">
@@ -18431,7 +18350,7 @@
       <c r="H449" s="21"/>
       <c r="I449" s="21"/>
       <c r="J449" s="21"/>
-      <c r="K449" s="25" t="s">
+      <c r="K449" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L449" s="23">
@@ -18467,7 +18386,7 @@
       <c r="H450" s="21"/>
       <c r="I450" s="21"/>
       <c r="J450" s="21"/>
-      <c r="K450" s="25" t="s">
+      <c r="K450" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L450" s="23">
@@ -18503,7 +18422,7 @@
       <c r="H451" s="21"/>
       <c r="I451" s="21"/>
       <c r="J451" s="21"/>
-      <c r="K451" s="25" t="s">
+      <c r="K451" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L451" s="23">
@@ -18539,7 +18458,7 @@
       <c r="H452" s="21"/>
       <c r="I452" s="21"/>
       <c r="J452" s="21"/>
-      <c r="K452" s="25" t="s">
+      <c r="K452" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L452" s="23">
@@ -18575,7 +18494,7 @@
       <c r="H453" s="21"/>
       <c r="I453" s="21"/>
       <c r="J453" s="21"/>
-      <c r="K453" s="25" t="s">
+      <c r="K453" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L453" s="23">
@@ -18611,7 +18530,7 @@
       <c r="H454" s="21"/>
       <c r="I454" s="21"/>
       <c r="J454" s="21"/>
-      <c r="K454" s="25" t="s">
+      <c r="K454" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L454" s="23">
@@ -18647,7 +18566,7 @@
       <c r="H455" s="21"/>
       <c r="I455" s="21"/>
       <c r="J455" s="21"/>
-      <c r="K455" s="25" t="s">
+      <c r="K455" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L455" s="23">
@@ -18683,7 +18602,7 @@
       <c r="H456" s="21"/>
       <c r="I456" s="21"/>
       <c r="J456" s="21"/>
-      <c r="K456" s="25" t="s">
+      <c r="K456" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L456" s="23">
@@ -18719,7 +18638,7 @@
       <c r="H457" s="21"/>
       <c r="I457" s="21"/>
       <c r="J457" s="21"/>
-      <c r="K457" s="25" t="s">
+      <c r="K457" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L457" s="23">
@@ -18755,7 +18674,7 @@
       <c r="H458" s="21"/>
       <c r="I458" s="21"/>
       <c r="J458" s="21"/>
-      <c r="K458" s="25" t="s">
+      <c r="K458" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L458" s="23">
@@ -18791,7 +18710,7 @@
       <c r="H459" s="21"/>
       <c r="I459" s="21"/>
       <c r="J459" s="21"/>
-      <c r="K459" s="25" t="s">
+      <c r="K459" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L459" s="23">
@@ -18827,7 +18746,7 @@
       <c r="H460" s="21"/>
       <c r="I460" s="21"/>
       <c r="J460" s="21"/>
-      <c r="K460" s="25" t="s">
+      <c r="K460" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L460" s="23">
@@ -18863,7 +18782,7 @@
       <c r="H461" s="21"/>
       <c r="I461" s="21"/>
       <c r="J461" s="21"/>
-      <c r="K461" s="25" t="s">
+      <c r="K461" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L461" s="23">
@@ -18899,7 +18818,7 @@
       <c r="H462" s="21"/>
       <c r="I462" s="21"/>
       <c r="J462" s="21"/>
-      <c r="K462" s="25" t="s">
+      <c r="K462" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L462" s="23">
@@ -18935,7 +18854,7 @@
       <c r="H463" s="21"/>
       <c r="I463" s="21"/>
       <c r="J463" s="21"/>
-      <c r="K463" s="25" t="s">
+      <c r="K463" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L463" s="23">
@@ -18971,7 +18890,7 @@
       <c r="H464" s="21"/>
       <c r="I464" s="21"/>
       <c r="J464" s="21"/>
-      <c r="K464" s="25" t="s">
+      <c r="K464" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L464" s="23">
@@ -19007,7 +18926,7 @@
       <c r="H465" s="21"/>
       <c r="I465" s="21"/>
       <c r="J465" s="21"/>
-      <c r="K465" s="25" t="s">
+      <c r="K465" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L465" s="23">
@@ -19043,7 +18962,7 @@
       <c r="H466" s="21"/>
       <c r="I466" s="21"/>
       <c r="J466" s="21"/>
-      <c r="K466" s="25" t="s">
+      <c r="K466" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L466" s="23">
@@ -19079,7 +18998,7 @@
       <c r="H467" s="21"/>
       <c r="I467" s="21"/>
       <c r="J467" s="21"/>
-      <c r="K467" s="22" t="s">
+      <c r="K467" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L467" s="23">
@@ -19115,7 +19034,7 @@
       <c r="H468" s="21"/>
       <c r="I468" s="21"/>
       <c r="J468" s="21"/>
-      <c r="K468" s="22" t="s">
+      <c r="K468" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L468" s="23">
@@ -19151,7 +19070,7 @@
       <c r="H469" s="21"/>
       <c r="I469" s="21"/>
       <c r="J469" s="21"/>
-      <c r="K469" s="22" t="s">
+      <c r="K469" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L469" s="23">
@@ -19187,7 +19106,7 @@
       <c r="H470" s="21"/>
       <c r="I470" s="21"/>
       <c r="J470" s="21"/>
-      <c r="K470" s="22" t="s">
+      <c r="K470" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L470" s="23">
@@ -19223,7 +19142,7 @@
       <c r="H471" s="21"/>
       <c r="I471" s="21"/>
       <c r="J471" s="21"/>
-      <c r="K471" s="22" t="s">
+      <c r="K471" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L471" s="23">
@@ -19259,7 +19178,7 @@
       <c r="H472" s="21"/>
       <c r="I472" s="21"/>
       <c r="J472" s="21"/>
-      <c r="K472" s="22" t="s">
+      <c r="K472" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L472" s="23">
@@ -19295,7 +19214,7 @@
       <c r="H473" s="21"/>
       <c r="I473" s="21"/>
       <c r="J473" s="21"/>
-      <c r="K473" s="22" t="s">
+      <c r="K473" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L473" s="23">
@@ -19331,7 +19250,7 @@
       <c r="H474" s="21"/>
       <c r="I474" s="21"/>
       <c r="J474" s="21"/>
-      <c r="K474" s="22" t="s">
+      <c r="K474" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L474" s="23">
@@ -19367,7 +19286,7 @@
       <c r="H475" s="21"/>
       <c r="I475" s="21"/>
       <c r="J475" s="21"/>
-      <c r="K475" s="22" t="s">
+      <c r="K475" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L475" s="23">
@@ -19403,7 +19322,7 @@
       <c r="H476" s="21"/>
       <c r="I476" s="21"/>
       <c r="J476" s="21"/>
-      <c r="K476" s="22" t="s">
+      <c r="K476" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L476" s="23">
@@ -19439,7 +19358,7 @@
       <c r="H477" s="21"/>
       <c r="I477" s="21"/>
       <c r="J477" s="21"/>
-      <c r="K477" s="22" t="s">
+      <c r="K477" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L477" s="23">
@@ -19475,7 +19394,7 @@
       <c r="H478" s="21"/>
       <c r="I478" s="21"/>
       <c r="J478" s="21"/>
-      <c r="K478" s="22" t="s">
+      <c r="K478" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L478" s="23">
@@ -19511,7 +19430,7 @@
       <c r="H479" s="21"/>
       <c r="I479" s="21"/>
       <c r="J479" s="21"/>
-      <c r="K479" s="22" t="s">
+      <c r="K479" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L479" s="23">
@@ -19547,7 +19466,7 @@
       <c r="H480" s="21"/>
       <c r="I480" s="21"/>
       <c r="J480" s="21"/>
-      <c r="K480" s="22" t="s">
+      <c r="K480" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L480" s="23">
@@ -19583,7 +19502,7 @@
       <c r="H481" s="21"/>
       <c r="I481" s="21"/>
       <c r="J481" s="21"/>
-      <c r="K481" s="22" t="s">
+      <c r="K481" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L481" s="23">
@@ -19619,7 +19538,7 @@
       <c r="H482" s="21"/>
       <c r="I482" s="21"/>
       <c r="J482" s="21"/>
-      <c r="K482" s="22" t="s">
+      <c r="K482" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L482" s="23">
@@ -19655,7 +19574,7 @@
       <c r="H483" s="21"/>
       <c r="I483" s="21"/>
       <c r="J483" s="21"/>
-      <c r="K483" s="22" t="s">
+      <c r="K483" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L483" s="23">
@@ -19691,7 +19610,7 @@
       <c r="H484" s="21"/>
       <c r="I484" s="21"/>
       <c r="J484" s="21"/>
-      <c r="K484" s="22" t="s">
+      <c r="K484" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L484" s="23"/>
@@ -21908,7 +21827,7 @@
       <c r="J545" s="21">
         <v>11111011</v>
       </c>
-      <c r="K545" s="22" t="s">
+      <c r="K545" s="25" t="s">
         <v>111</v>
       </c>
       <c r="L545" s="23">
@@ -21948,7 +21867,7 @@
       <c r="J546" s="21">
         <v>11111012</v>
       </c>
-      <c r="K546" s="22">
+      <c r="K546" s="23">
         <v>1111253</v>
       </c>
       <c r="L546" s="23">
@@ -21988,8 +21907,8 @@
       <c r="J547" s="21">
         <v>11111013</v>
       </c>
-      <c r="K547" s="22">
-        <v>1111255</v>
+      <c r="K547" s="25">
+        <v>1111258</v>
       </c>
       <c r="L547" s="23">
         <v>20</v>
@@ -22028,8 +21947,8 @@
       <c r="J548" s="21">
         <v>11111014</v>
       </c>
-      <c r="K548" s="22">
-        <v>1111256</v>
+      <c r="K548" s="25">
+        <v>1111259</v>
       </c>
       <c r="L548" s="23">
         <v>30</v>
@@ -22068,8 +21987,8 @@
       <c r="J549" s="21">
         <v>11111015</v>
       </c>
-      <c r="K549" s="22">
-        <v>1111257</v>
+      <c r="K549" s="25">
+        <v>1111260</v>
       </c>
       <c r="L549" s="23">
         <v>60</v>
@@ -22108,8 +22027,8 @@
       <c r="J550" s="21">
         <v>11111016</v>
       </c>
-      <c r="K550" s="22">
-        <v>1111258</v>
+      <c r="K550" s="25">
+        <v>1111261</v>
       </c>
       <c r="L550" s="23">
         <v>80</v>
@@ -22148,8 +22067,8 @@
       <c r="J551" s="21">
         <v>11111021</v>
       </c>
-      <c r="K551" s="22">
-        <v>1111259</v>
+      <c r="K551" s="25">
+        <v>1111262</v>
       </c>
       <c r="L551" s="23">
         <v>120</v>
@@ -22188,8 +22107,8 @@
       <c r="J552" s="21">
         <v>11111022</v>
       </c>
-      <c r="K552" s="22">
-        <v>1111260</v>
+      <c r="K552" s="25">
+        <v>1111263</v>
       </c>
       <c r="L552" s="23">
         <v>150</v>
@@ -22228,8 +22147,8 @@
       <c r="J553" s="21">
         <v>11111023</v>
       </c>
-      <c r="K553" s="22">
-        <v>1111261</v>
+      <c r="K553" s="25">
+        <v>1111264</v>
       </c>
       <c r="L553" s="23">
         <v>200</v>
@@ -22268,8 +22187,8 @@
       <c r="J554" s="21">
         <v>11111024</v>
       </c>
-      <c r="K554" s="22">
-        <v>1111262</v>
+      <c r="K554" s="25">
+        <v>1111265</v>
       </c>
       <c r="L554" s="23">
         <v>300</v>
@@ -22308,8 +22227,8 @@
       <c r="J555" s="21">
         <v>11111025</v>
       </c>
-      <c r="K555" s="22">
-        <v>1111263</v>
+      <c r="K555" s="25">
+        <v>1111266</v>
       </c>
       <c r="L555" s="23">
         <v>360</v>
@@ -22348,8 +22267,8 @@
       <c r="J556" s="21">
         <v>11111026</v>
       </c>
-      <c r="K556" s="22">
-        <v>1111264</v>
+      <c r="K556" s="25">
+        <v>1111267</v>
       </c>
       <c r="L556" s="23">
         <v>420</v>
@@ -22388,8 +22307,8 @@
       <c r="J557" s="21">
         <v>11111031</v>
       </c>
-      <c r="K557" s="22">
-        <v>1111265</v>
+      <c r="K557" s="25">
+        <v>1111268</v>
       </c>
       <c r="L557" s="23">
         <v>480</v>
@@ -22428,8 +22347,8 @@
       <c r="J558" s="21">
         <v>11111032</v>
       </c>
-      <c r="K558" s="22">
-        <v>1111266</v>
+      <c r="K558" s="25">
+        <v>1111269</v>
       </c>
       <c r="L558" s="23">
         <v>540</v>
@@ -22468,8 +22387,8 @@
       <c r="J559" s="21">
         <v>11111033</v>
       </c>
-      <c r="K559" s="22">
-        <v>1111267</v>
+      <c r="K559" s="25">
+        <v>1111270</v>
       </c>
       <c r="L559" s="23">
         <v>600</v>
@@ -22508,9 +22427,6 @@
       <c r="J560" s="21">
         <v>11111034</v>
       </c>
-      <c r="K560" s="22">
-        <v>1111268</v>
-      </c>
       <c r="L560" s="23">
         <v>600</v>
       </c>
@@ -22548,9 +22464,6 @@
       <c r="J561" s="21">
         <v>11111035</v>
       </c>
-      <c r="K561" s="22">
-        <v>1111269</v>
-      </c>
       <c r="L561" s="23">
         <v>600</v>
       </c>
@@ -22588,9 +22501,6 @@
       <c r="J562" s="21">
         <v>11111036</v>
       </c>
-      <c r="K562" s="22">
-        <v>1111270</v>
-      </c>
       <c r="L562" s="23">
         <v>600</v>
       </c>
@@ -22702,7 +22612,7 @@
       <c r="J565" s="21">
         <v>11111043</v>
       </c>
-      <c r="K565" s="22" t="s">
+      <c r="K565" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L565" s="23">
@@ -22742,7 +22652,7 @@
       <c r="J566" s="21">
         <v>11111044</v>
       </c>
-      <c r="K566" s="22" t="s">
+      <c r="K566" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L566" s="23">
@@ -22782,7 +22692,7 @@
       <c r="J567" s="21">
         <v>11111045</v>
       </c>
-      <c r="K567" s="22" t="s">
+      <c r="K567" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L567" s="23">
@@ -22822,7 +22732,7 @@
       <c r="J568" s="21">
         <v>11111046</v>
       </c>
-      <c r="K568" s="22" t="s">
+      <c r="K568" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L568" s="23">
@@ -22858,7 +22768,7 @@
       <c r="H569" s="21"/>
       <c r="I569" s="21"/>
       <c r="J569" s="21"/>
-      <c r="K569" s="25" t="s">
+      <c r="K569" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L569" s="23">
@@ -22894,7 +22804,7 @@
       <c r="H570" s="21"/>
       <c r="I570" s="21"/>
       <c r="J570" s="21"/>
-      <c r="K570" s="25" t="s">
+      <c r="K570" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L570" s="23">
@@ -22930,7 +22840,7 @@
       <c r="H571" s="21"/>
       <c r="I571" s="21"/>
       <c r="J571" s="21"/>
-      <c r="K571" s="25" t="s">
+      <c r="K571" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L571" s="23">
@@ -22966,7 +22876,7 @@
       <c r="H572" s="21"/>
       <c r="I572" s="21"/>
       <c r="J572" s="21"/>
-      <c r="K572" s="25" t="s">
+      <c r="K572" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L572" s="23">
@@ -23002,7 +22912,7 @@
       <c r="H573" s="21"/>
       <c r="I573" s="21"/>
       <c r="J573" s="21"/>
-      <c r="K573" s="25" t="s">
+      <c r="K573" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L573" s="23">
@@ -23038,7 +22948,7 @@
       <c r="H574" s="21"/>
       <c r="I574" s="21"/>
       <c r="J574" s="21"/>
-      <c r="K574" s="25" t="s">
+      <c r="K574" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L574" s="23">
@@ -23074,7 +22984,7 @@
       <c r="H575" s="21"/>
       <c r="I575" s="21"/>
       <c r="J575" s="21"/>
-      <c r="K575" s="25" t="s">
+      <c r="K575" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L575" s="23">
@@ -23110,7 +23020,7 @@
       <c r="H576" s="21"/>
       <c r="I576" s="21"/>
       <c r="J576" s="21"/>
-      <c r="K576" s="25" t="s">
+      <c r="K576" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L576" s="23">
@@ -23146,7 +23056,7 @@
       <c r="H577" s="21"/>
       <c r="I577" s="21"/>
       <c r="J577" s="21"/>
-      <c r="K577" s="25" t="s">
+      <c r="K577" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L577" s="23">
@@ -23182,7 +23092,7 @@
       <c r="H578" s="21"/>
       <c r="I578" s="21"/>
       <c r="J578" s="21"/>
-      <c r="K578" s="25" t="s">
+      <c r="K578" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L578" s="23">
@@ -23218,7 +23128,7 @@
       <c r="H579" s="21"/>
       <c r="I579" s="21"/>
       <c r="J579" s="21"/>
-      <c r="K579" s="25" t="s">
+      <c r="K579" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L579" s="23">
@@ -23254,7 +23164,7 @@
       <c r="H580" s="21"/>
       <c r="I580" s="21"/>
       <c r="J580" s="21"/>
-      <c r="K580" s="25" t="s">
+      <c r="K580" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L580" s="23">
@@ -23290,7 +23200,7 @@
       <c r="H581" s="21"/>
       <c r="I581" s="21"/>
       <c r="J581" s="21"/>
-      <c r="K581" s="25" t="s">
+      <c r="K581" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L581" s="23">
@@ -23326,7 +23236,7 @@
       <c r="H582" s="21"/>
       <c r="I582" s="21"/>
       <c r="J582" s="21"/>
-      <c r="K582" s="25" t="s">
+      <c r="K582" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L582" s="23">
@@ -23362,7 +23272,7 @@
       <c r="H583" s="21"/>
       <c r="I583" s="21"/>
       <c r="J583" s="21"/>
-      <c r="K583" s="25" t="s">
+      <c r="K583" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L583" s="23">
@@ -23398,7 +23308,7 @@
       <c r="H584" s="21"/>
       <c r="I584" s="21"/>
       <c r="J584" s="21"/>
-      <c r="K584" s="25" t="s">
+      <c r="K584" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L584" s="23">
@@ -23434,7 +23344,7 @@
       <c r="H585" s="21"/>
       <c r="I585" s="21"/>
       <c r="J585" s="21"/>
-      <c r="K585" s="25" t="s">
+      <c r="K585" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L585" s="23">
@@ -23470,7 +23380,7 @@
       <c r="H586" s="21"/>
       <c r="I586" s="21"/>
       <c r="J586" s="21"/>
-      <c r="K586" s="25" t="s">
+      <c r="K586" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L586" s="23">
@@ -23506,7 +23416,7 @@
       <c r="H587" s="21"/>
       <c r="I587" s="21"/>
       <c r="J587" s="21"/>
-      <c r="K587" s="25" t="s">
+      <c r="K587" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L587" s="23">
@@ -23542,7 +23452,7 @@
       <c r="H588" s="21"/>
       <c r="I588" s="21"/>
       <c r="J588" s="21"/>
-      <c r="K588" s="25" t="s">
+      <c r="K588" s="26" t="s">
         <v>63</v>
       </c>
       <c r="L588" s="23">
@@ -23578,7 +23488,7 @@
       <c r="H589" s="21"/>
       <c r="I589" s="21"/>
       <c r="J589" s="21"/>
-      <c r="K589" s="22" t="s">
+      <c r="K589" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L589" s="23">
@@ -23614,7 +23524,7 @@
       <c r="H590" s="21"/>
       <c r="I590" s="21"/>
       <c r="J590" s="21"/>
-      <c r="K590" s="22" t="s">
+      <c r="K590" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L590" s="23">
@@ -23650,7 +23560,7 @@
       <c r="H591" s="21"/>
       <c r="I591" s="21"/>
       <c r="J591" s="21"/>
-      <c r="K591" s="22" t="s">
+      <c r="K591" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L591" s="23">
@@ -23686,7 +23596,7 @@
       <c r="H592" s="21"/>
       <c r="I592" s="21"/>
       <c r="J592" s="21"/>
-      <c r="K592" s="22" t="s">
+      <c r="K592" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L592" s="23">
@@ -23722,7 +23632,7 @@
       <c r="H593" s="21"/>
       <c r="I593" s="21"/>
       <c r="J593" s="21"/>
-      <c r="K593" s="22" t="s">
+      <c r="K593" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L593" s="23">
@@ -23758,7 +23668,7 @@
       <c r="H594" s="21"/>
       <c r="I594" s="21"/>
       <c r="J594" s="21"/>
-      <c r="K594" s="22" t="s">
+      <c r="K594" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L594" s="23">
@@ -23794,7 +23704,7 @@
       <c r="H595" s="21"/>
       <c r="I595" s="21"/>
       <c r="J595" s="21"/>
-      <c r="K595" s="22" t="s">
+      <c r="K595" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L595" s="23">
@@ -23830,7 +23740,7 @@
       <c r="H596" s="21"/>
       <c r="I596" s="21"/>
       <c r="J596" s="21"/>
-      <c r="K596" s="22" t="s">
+      <c r="K596" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L596" s="23">
@@ -23866,7 +23776,7 @@
       <c r="H597" s="21"/>
       <c r="I597" s="21"/>
       <c r="J597" s="21"/>
-      <c r="K597" s="22" t="s">
+      <c r="K597" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L597" s="23">
@@ -23902,7 +23812,7 @@
       <c r="H598" s="21"/>
       <c r="I598" s="21"/>
       <c r="J598" s="21"/>
-      <c r="K598" s="22" t="s">
+      <c r="K598" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L598" s="23">
@@ -23938,7 +23848,7 @@
       <c r="H599" s="21"/>
       <c r="I599" s="21"/>
       <c r="J599" s="21"/>
-      <c r="K599" s="22" t="s">
+      <c r="K599" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L599" s="23">
@@ -23974,7 +23884,7 @@
       <c r="H600" s="21"/>
       <c r="I600" s="21"/>
       <c r="J600" s="21"/>
-      <c r="K600" s="22" t="s">
+      <c r="K600" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L600" s="23">
@@ -24010,7 +23920,7 @@
       <c r="H601" s="21"/>
       <c r="I601" s="21"/>
       <c r="J601" s="21"/>
-      <c r="K601" s="22" t="s">
+      <c r="K601" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L601" s="23">
@@ -24046,7 +23956,7 @@
       <c r="H602" s="21"/>
       <c r="I602" s="21"/>
       <c r="J602" s="21"/>
-      <c r="K602" s="22" t="s">
+      <c r="K602" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L602" s="23">
@@ -24082,7 +23992,7 @@
       <c r="H603" s="21"/>
       <c r="I603" s="21"/>
       <c r="J603" s="21"/>
-      <c r="K603" s="22" t="s">
+      <c r="K603" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L603" s="23">
@@ -24118,7 +24028,7 @@
       <c r="H604" s="21"/>
       <c r="I604" s="21"/>
       <c r="J604" s="21"/>
-      <c r="K604" s="22" t="s">
+      <c r="K604" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L604" s="23"/>
@@ -24237,7 +24147,7 @@
         <v>11121013</v>
       </c>
       <c r="K607" s="9">
-        <v>1112254</v>
+        <v>1112256</v>
       </c>
       <c r="L607" s="18">
         <v>20</v>
@@ -24277,7 +24187,7 @@
         <v>11121014</v>
       </c>
       <c r="K608" s="9">
-        <v>1112256</v>
+        <v>1112257</v>
       </c>
       <c r="L608" s="18">
         <v>30</v>
@@ -24317,7 +24227,7 @@
         <v>11121015</v>
       </c>
       <c r="K609" s="9">
-        <v>1112257</v>
+        <v>1112258</v>
       </c>
       <c r="L609" s="18">
         <v>60</v>
@@ -24357,7 +24267,7 @@
         <v>11121016</v>
       </c>
       <c r="K610" s="9">
-        <v>1112258</v>
+        <v>1112259</v>
       </c>
       <c r="L610" s="18">
         <v>80</v>
@@ -24397,7 +24307,7 @@
         <v>11121021</v>
       </c>
       <c r="K611" s="9">
-        <v>1112259</v>
+        <v>1112260</v>
       </c>
       <c r="L611" s="18">
         <v>120</v>
@@ -24437,7 +24347,7 @@
         <v>11121022</v>
       </c>
       <c r="K612" s="9">
-        <v>1112260</v>
+        <v>1112261</v>
       </c>
       <c r="L612" s="18">
         <v>150</v>
@@ -24477,7 +24387,7 @@
         <v>11121023</v>
       </c>
       <c r="K613" s="9">
-        <v>1112261</v>
+        <v>1112262</v>
       </c>
       <c r="L613" s="18">
         <v>200</v>
@@ -24517,7 +24427,7 @@
         <v>11121024</v>
       </c>
       <c r="K614" s="9">
-        <v>1112262</v>
+        <v>1112263</v>
       </c>
       <c r="L614" s="18">
         <v>300</v>
@@ -24557,7 +24467,7 @@
         <v>11121025</v>
       </c>
       <c r="K615" s="9">
-        <v>1112263</v>
+        <v>1112264</v>
       </c>
       <c r="L615" s="18">
         <v>360</v>
@@ -24597,7 +24507,7 @@
         <v>11121026</v>
       </c>
       <c r="K616" s="9">
-        <v>1112264</v>
+        <v>1112265</v>
       </c>
       <c r="L616" s="18">
         <v>420</v>
@@ -24637,7 +24547,7 @@
         <v>11121031</v>
       </c>
       <c r="K617" s="9">
-        <v>1112265</v>
+        <v>1112266</v>
       </c>
       <c r="L617" s="18">
         <v>480</v>
@@ -24677,7 +24587,7 @@
         <v>11121032</v>
       </c>
       <c r="K618" s="9">
-        <v>1112266</v>
+        <v>1112267</v>
       </c>
       <c r="L618" s="18">
         <v>540</v>
@@ -24717,7 +24627,7 @@
         <v>11121033</v>
       </c>
       <c r="K619" s="9">
-        <v>1112267</v>
+        <v>1112268</v>
       </c>
       <c r="L619" s="18">
         <v>600</v>
@@ -24757,7 +24667,7 @@
         <v>11121034</v>
       </c>
       <c r="K620" s="9">
-        <v>1112268</v>
+        <v>1112269</v>
       </c>
       <c r="L620" s="18">
         <v>600</v>
@@ -24797,7 +24707,7 @@
         <v>11121035</v>
       </c>
       <c r="K621" s="9">
-        <v>1112269</v>
+        <v>1112270</v>
       </c>
       <c r="L621" s="18">
         <v>600</v>
@@ -24837,7 +24747,7 @@
         <v>11121036</v>
       </c>
       <c r="K622" s="9">
-        <v>1112270</v>
+        <v>1112271</v>
       </c>
       <c r="L622" s="18">
         <v>600</v>
@@ -24876,9 +24786,6 @@
       <c r="J623" s="8">
         <v>11121041</v>
       </c>
-      <c r="K623" s="9">
-        <v>1112271</v>
-      </c>
       <c r="L623" s="18">
         <v>600</v>
       </c>
@@ -25106,7 +25013,7 @@
       <c r="H629" s="8"/>
       <c r="I629" s="8"/>
       <c r="J629" s="8"/>
-      <c r="K629" s="26" t="s">
+      <c r="K629" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L629" s="18">
@@ -25142,7 +25049,7 @@
       <c r="H630" s="8"/>
       <c r="I630" s="8"/>
       <c r="J630" s="8"/>
-      <c r="K630" s="26" t="s">
+      <c r="K630" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L630" s="18">
@@ -25178,7 +25085,7 @@
       <c r="H631" s="8"/>
       <c r="I631" s="8"/>
       <c r="J631" s="8"/>
-      <c r="K631" s="26" t="s">
+      <c r="K631" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L631" s="18">
@@ -25214,7 +25121,7 @@
       <c r="H632" s="8"/>
       <c r="I632" s="8"/>
       <c r="J632" s="8"/>
-      <c r="K632" s="26" t="s">
+      <c r="K632" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L632" s="18">
@@ -25250,7 +25157,7 @@
       <c r="H633" s="8"/>
       <c r="I633" s="8"/>
       <c r="J633" s="8"/>
-      <c r="K633" s="26" t="s">
+      <c r="K633" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L633" s="18">
@@ -25286,7 +25193,7 @@
       <c r="H634" s="8"/>
       <c r="I634" s="8"/>
       <c r="J634" s="8"/>
-      <c r="K634" s="26" t="s">
+      <c r="K634" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L634" s="18">
@@ -25322,7 +25229,7 @@
       <c r="H635" s="8"/>
       <c r="I635" s="8"/>
       <c r="J635" s="8"/>
-      <c r="K635" s="26" t="s">
+      <c r="K635" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L635" s="18">
@@ -25358,7 +25265,7 @@
       <c r="H636" s="8"/>
       <c r="I636" s="8"/>
       <c r="J636" s="8"/>
-      <c r="K636" s="26" t="s">
+      <c r="K636" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L636" s="18">
@@ -25394,7 +25301,7 @@
       <c r="H637" s="8"/>
       <c r="I637" s="8"/>
       <c r="J637" s="8"/>
-      <c r="K637" s="26" t="s">
+      <c r="K637" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L637" s="18">
@@ -25430,7 +25337,7 @@
       <c r="H638" s="8"/>
       <c r="I638" s="8"/>
       <c r="J638" s="8"/>
-      <c r="K638" s="26" t="s">
+      <c r="K638" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L638" s="18">
@@ -25466,7 +25373,7 @@
       <c r="H639" s="8"/>
       <c r="I639" s="8"/>
       <c r="J639" s="8"/>
-      <c r="K639" s="26" t="s">
+      <c r="K639" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L639" s="18">
@@ -25502,7 +25409,7 @@
       <c r="H640" s="8"/>
       <c r="I640" s="8"/>
       <c r="J640" s="8"/>
-      <c r="K640" s="26" t="s">
+      <c r="K640" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L640" s="18">
@@ -25538,7 +25445,7 @@
       <c r="H641" s="8"/>
       <c r="I641" s="8"/>
       <c r="J641" s="8"/>
-      <c r="K641" s="26" t="s">
+      <c r="K641" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L641" s="18">
@@ -25574,7 +25481,7 @@
       <c r="H642" s="8"/>
       <c r="I642" s="8"/>
       <c r="J642" s="8"/>
-      <c r="K642" s="26" t="s">
+      <c r="K642" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L642" s="18">
@@ -25610,7 +25517,7 @@
       <c r="H643" s="8"/>
       <c r="I643" s="8"/>
       <c r="J643" s="8"/>
-      <c r="K643" s="26" t="s">
+      <c r="K643" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L643" s="18">
@@ -25646,7 +25553,7 @@
       <c r="H644" s="8"/>
       <c r="I644" s="8"/>
       <c r="J644" s="8"/>
-      <c r="K644" s="26" t="s">
+      <c r="K644" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L644" s="18">
@@ -25682,7 +25589,7 @@
       <c r="H645" s="8"/>
       <c r="I645" s="8"/>
       <c r="J645" s="8"/>
-      <c r="K645" s="26" t="s">
+      <c r="K645" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L645" s="18">
@@ -25718,7 +25625,7 @@
       <c r="H646" s="8"/>
       <c r="I646" s="8"/>
       <c r="J646" s="8"/>
-      <c r="K646" s="26" t="s">
+      <c r="K646" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L646" s="18">
@@ -25754,7 +25661,7 @@
       <c r="H647" s="8"/>
       <c r="I647" s="8"/>
       <c r="J647" s="8"/>
-      <c r="K647" s="26" t="s">
+      <c r="K647" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L647" s="18">
@@ -25790,7 +25697,7 @@
       <c r="H648" s="8"/>
       <c r="I648" s="8"/>
       <c r="J648" s="8"/>
-      <c r="K648" s="26" t="s">
+      <c r="K648" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L648" s="18">
@@ -25826,7 +25733,7 @@
       <c r="H649" s="8"/>
       <c r="I649" s="8"/>
       <c r="J649" s="8"/>
-      <c r="K649" s="26" t="s">
+      <c r="K649" s="28" t="s">
         <v>63</v>
       </c>
       <c r="L649" s="18">
@@ -26404,7 +26311,7 @@
       <c r="J665" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="K665" s="22" t="s">
+      <c r="K665" s="25" t="s">
         <v>116</v>
       </c>
       <c r="L665" s="23">
@@ -26484,7 +26391,7 @@
       <c r="J667" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="K667" s="22">
+      <c r="K667" s="25">
         <v>1201264</v>
       </c>
       <c r="L667" s="23">
@@ -26524,7 +26431,7 @@
       <c r="J668" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="K668" s="22">
+      <c r="K668" s="25">
         <v>1201265</v>
       </c>
       <c r="L668" s="23">
@@ -26604,7 +26511,7 @@
       <c r="J670" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="K670" s="22">
+      <c r="K670" s="25">
         <v>1201267</v>
       </c>
       <c r="L670" s="23">
@@ -26644,7 +26551,7 @@
       <c r="J671" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="K671" s="22">
+      <c r="K671" s="25">
         <v>1201268</v>
       </c>
       <c r="L671" s="23">
@@ -26684,7 +26591,7 @@
       <c r="J672" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="K672" s="22">
+      <c r="K672" s="25">
         <v>1201269</v>
       </c>
       <c r="L672" s="23">
@@ -26724,7 +26631,7 @@
       <c r="J673" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="K673" s="22" t="s">
+      <c r="K673" s="25" t="s">
         <v>126</v>
       </c>
       <c r="L673" s="23">
@@ -26764,7 +26671,7 @@
       <c r="J674" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="K674" s="22">
+      <c r="K674" s="25">
         <v>1201271</v>
       </c>
       <c r="L674" s="23">
@@ -26804,7 +26711,7 @@
       <c r="J675" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="K675" s="22">
+      <c r="K675" s="25">
         <v>1201272</v>
       </c>
       <c r="L675" s="23">
@@ -26844,7 +26751,7 @@
       <c r="J676" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="K676" s="22">
+      <c r="K676" s="25">
         <v>1201273</v>
       </c>
       <c r="L676" s="23">
@@ -26880,7 +26787,7 @@
       <c r="H677" s="21"/>
       <c r="I677" s="21"/>
       <c r="J677" s="21"/>
-      <c r="K677" s="22">
+      <c r="K677" s="25">
         <v>1201254</v>
       </c>
       <c r="L677" s="23">
@@ -26916,7 +26823,7 @@
       <c r="H678" s="21"/>
       <c r="I678" s="21"/>
       <c r="J678" s="21"/>
-      <c r="K678" s="22">
+      <c r="K678" s="25">
         <v>1201255</v>
       </c>
       <c r="L678" s="23">
@@ -26988,7 +26895,7 @@
       <c r="H680" s="21"/>
       <c r="I680" s="21"/>
       <c r="J680" s="21"/>
-      <c r="K680" s="22">
+      <c r="K680" s="25">
         <v>1201257</v>
       </c>
       <c r="L680" s="23">
@@ -27024,7 +26931,7 @@
       <c r="H681" s="21"/>
       <c r="I681" s="21"/>
       <c r="J681" s="21"/>
-      <c r="K681" s="22">
+      <c r="K681" s="25">
         <v>1201258</v>
       </c>
       <c r="L681" s="23">
@@ -27060,7 +26967,7 @@
       <c r="H682" s="21"/>
       <c r="I682" s="21"/>
       <c r="J682" s="21"/>
-      <c r="K682" s="22">
+      <c r="K682" s="25">
         <v>1201259</v>
       </c>
       <c r="L682" s="23">
@@ -27096,7 +27003,7 @@
       <c r="H683" s="21"/>
       <c r="I683" s="21"/>
       <c r="J683" s="21"/>
-      <c r="K683" s="22">
+      <c r="K683" s="25">
         <v>1201260</v>
       </c>
       <c r="L683" s="23">
@@ -27132,7 +27039,7 @@
       <c r="H684" s="21"/>
       <c r="I684" s="21"/>
       <c r="J684" s="21"/>
-      <c r="K684" s="22">
+      <c r="K684" s="25">
         <v>1201261</v>
       </c>
       <c r="L684" s="23">
@@ -27333,7 +27240,7 @@
       <c r="H690" s="21"/>
       <c r="I690" s="21"/>
       <c r="J690" s="21"/>
-      <c r="K690" s="27" t="s">
+      <c r="K690" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L690" s="23">
@@ -27369,7 +27276,7 @@
       <c r="H691" s="21"/>
       <c r="I691" s="21"/>
       <c r="J691" s="21"/>
-      <c r="K691" s="27" t="s">
+      <c r="K691" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L691" s="23">
@@ -27405,7 +27312,7 @@
       <c r="H692" s="21"/>
       <c r="I692" s="21"/>
       <c r="J692" s="21"/>
-      <c r="K692" s="27" t="s">
+      <c r="K692" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L692" s="23">
@@ -27441,7 +27348,7 @@
       <c r="H693" s="21"/>
       <c r="I693" s="21"/>
       <c r="J693" s="21"/>
-      <c r="K693" s="27" t="s">
+      <c r="K693" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L693" s="23">
@@ -27477,7 +27384,7 @@
       <c r="H694" s="21"/>
       <c r="I694" s="21"/>
       <c r="J694" s="21"/>
-      <c r="K694" s="27" t="s">
+      <c r="K694" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L694" s="23">
@@ -27513,7 +27420,7 @@
       <c r="H695" s="21"/>
       <c r="I695" s="21"/>
       <c r="J695" s="21"/>
-      <c r="K695" s="27" t="s">
+      <c r="K695" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L695" s="23">
@@ -27549,7 +27456,7 @@
       <c r="H696" s="21"/>
       <c r="I696" s="21"/>
       <c r="J696" s="21"/>
-      <c r="K696" s="27" t="s">
+      <c r="K696" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L696" s="23">
@@ -27585,7 +27492,7 @@
       <c r="H697" s="21"/>
       <c r="I697" s="21"/>
       <c r="J697" s="21"/>
-      <c r="K697" s="27" t="s">
+      <c r="K697" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L697" s="23">
@@ -27621,7 +27528,7 @@
       <c r="H698" s="21"/>
       <c r="I698" s="21"/>
       <c r="J698" s="21"/>
-      <c r="K698" s="27" t="s">
+      <c r="K698" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L698" s="23">
@@ -27657,7 +27564,7 @@
       <c r="H699" s="21"/>
       <c r="I699" s="21"/>
       <c r="J699" s="21"/>
-      <c r="K699" s="27" t="s">
+      <c r="K699" s="29" t="s">
         <v>63</v>
       </c>
       <c r="L699" s="23">
@@ -27693,7 +27600,7 @@
       <c r="H700" s="21"/>
       <c r="I700" s="21"/>
       <c r="J700" s="21"/>
-      <c r="K700" s="22" t="s">
+      <c r="K700" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L700" s="23">
@@ -27729,7 +27636,7 @@
       <c r="H701" s="21"/>
       <c r="I701" s="21"/>
       <c r="J701" s="21"/>
-      <c r="K701" s="22" t="s">
+      <c r="K701" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L701" s="23">
@@ -27765,7 +27672,7 @@
       <c r="H702" s="21"/>
       <c r="I702" s="21"/>
       <c r="J702" s="21"/>
-      <c r="K702" s="22" t="s">
+      <c r="K702" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L702" s="23">
@@ -27801,7 +27708,7 @@
       <c r="H703" s="21"/>
       <c r="I703" s="21"/>
       <c r="J703" s="21"/>
-      <c r="K703" s="22" t="s">
+      <c r="K703" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L703" s="23">
@@ -27837,7 +27744,7 @@
       <c r="H704" s="21"/>
       <c r="I704" s="21"/>
       <c r="J704" s="21"/>
-      <c r="K704" s="22" t="s">
+      <c r="K704" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L704" s="23">
@@ -27873,7 +27780,7 @@
       <c r="H705" s="21"/>
       <c r="I705" s="21"/>
       <c r="J705" s="21"/>
-      <c r="K705" s="22" t="s">
+      <c r="K705" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L705" s="23">
@@ -27909,7 +27816,7 @@
       <c r="H706" s="21"/>
       <c r="I706" s="21"/>
       <c r="J706" s="21"/>
-      <c r="K706" s="22" t="s">
+      <c r="K706" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L706" s="23">
@@ -27945,7 +27852,7 @@
       <c r="H707" s="21"/>
       <c r="I707" s="21"/>
       <c r="J707" s="21"/>
-      <c r="K707" s="22" t="s">
+      <c r="K707" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L707" s="23">
@@ -27981,7 +27888,7 @@
       <c r="H708" s="21"/>
       <c r="I708" s="21"/>
       <c r="J708" s="21"/>
-      <c r="K708" s="22" t="s">
+      <c r="K708" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L708" s="23">
@@ -28017,7 +27924,7 @@
       <c r="H709" s="21"/>
       <c r="I709" s="21"/>
       <c r="J709" s="21"/>
-      <c r="K709" s="22" t="s">
+      <c r="K709" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L709" s="23">
@@ -28053,7 +27960,7 @@
       <c r="H710" s="21"/>
       <c r="I710" s="21"/>
       <c r="J710" s="21"/>
-      <c r="K710" s="22" t="s">
+      <c r="K710" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L710" s="23">
@@ -28089,7 +27996,7 @@
       <c r="H711" s="21"/>
       <c r="I711" s="21"/>
       <c r="J711" s="21"/>
-      <c r="K711" s="22" t="s">
+      <c r="K711" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L711" s="23">
@@ -28125,7 +28032,7 @@
       <c r="H712" s="21"/>
       <c r="I712" s="21"/>
       <c r="J712" s="21"/>
-      <c r="K712" s="22" t="s">
+      <c r="K712" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L712" s="23">
@@ -28161,7 +28068,7 @@
       <c r="H713" s="21"/>
       <c r="I713" s="21"/>
       <c r="J713" s="21"/>
-      <c r="K713" s="22" t="s">
+      <c r="K713" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L713" s="23">
@@ -28197,7 +28104,7 @@
       <c r="H714" s="21"/>
       <c r="I714" s="21"/>
       <c r="J714" s="21"/>
-      <c r="K714" s="22" t="s">
+      <c r="K714" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L714" s="23">
@@ -28233,7 +28140,7 @@
       <c r="H715" s="21"/>
       <c r="I715" s="21"/>
       <c r="J715" s="21"/>
-      <c r="K715" s="22" t="s">
+      <c r="K715" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L715" s="23">
@@ -28269,7 +28176,7 @@
       <c r="H716" s="21"/>
       <c r="I716" s="21"/>
       <c r="J716" s="21"/>
-      <c r="K716" s="22" t="s">
+      <c r="K716" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L716" s="23">
@@ -28305,7 +28212,7 @@
       <c r="H717" s="21"/>
       <c r="I717" s="21"/>
       <c r="J717" s="21"/>
-      <c r="K717" s="22" t="s">
+      <c r="K717" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L717" s="23">
@@ -28341,7 +28248,7 @@
       <c r="H718" s="21"/>
       <c r="I718" s="21"/>
       <c r="J718" s="21"/>
-      <c r="K718" s="22" t="s">
+      <c r="K718" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L718" s="23">
@@ -28377,7 +28284,7 @@
       <c r="H719" s="21"/>
       <c r="I719" s="21"/>
       <c r="J719" s="21"/>
-      <c r="K719" s="22" t="s">
+      <c r="K719" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L719" s="23">
@@ -28413,7 +28320,7 @@
       <c r="H720" s="21"/>
       <c r="I720" s="21"/>
       <c r="J720" s="21"/>
-      <c r="K720" s="22" t="s">
+      <c r="K720" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L720" s="23">
@@ -28449,7 +28356,7 @@
       <c r="H721" s="21"/>
       <c r="I721" s="21"/>
       <c r="J721" s="21"/>
-      <c r="K721" s="22" t="s">
+      <c r="K721" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L721" s="23">
@@ -28485,7 +28392,7 @@
       <c r="H722" s="21"/>
       <c r="I722" s="21"/>
       <c r="J722" s="21"/>
-      <c r="K722" s="22" t="s">
+      <c r="K722" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L722" s="23">
@@ -28521,7 +28428,7 @@
       <c r="H723" s="21"/>
       <c r="I723" s="21"/>
       <c r="J723" s="21"/>
-      <c r="K723" s="22" t="s">
+      <c r="K723" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L723" s="23">
@@ -28557,7 +28464,7 @@
       <c r="H724" s="21"/>
       <c r="I724" s="21"/>
       <c r="J724" s="21"/>
-      <c r="K724" s="22" t="s">
+      <c r="K724" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L724" s="23"/>
@@ -30675,7 +30582,7 @@
       <c r="H785" s="2"/>
       <c r="I785" s="21"/>
       <c r="J785" s="21"/>
-      <c r="K785" s="22">
+      <c r="K785" s="25">
         <v>1301201</v>
       </c>
       <c r="L785" s="23">
@@ -30709,7 +30616,7 @@
       <c r="H786" s="2"/>
       <c r="I786" s="21"/>
       <c r="J786" s="21"/>
-      <c r="K786" s="22">
+      <c r="K786" s="25">
         <v>1301202</v>
       </c>
       <c r="L786" s="23">
@@ -30743,7 +30650,7 @@
       <c r="H787" s="2"/>
       <c r="I787" s="21"/>
       <c r="J787" s="21"/>
-      <c r="K787" s="22">
+      <c r="K787" s="25">
         <v>1301203</v>
       </c>
       <c r="L787" s="23">
@@ -30777,7 +30684,7 @@
       <c r="H788" s="2"/>
       <c r="I788" s="21"/>
       <c r="J788" s="21"/>
-      <c r="K788" s="22">
+      <c r="K788" s="25">
         <v>1301204</v>
       </c>
       <c r="L788" s="23">
@@ -30811,7 +30718,7 @@
       <c r="H789" s="2"/>
       <c r="I789" s="21"/>
       <c r="J789" s="21"/>
-      <c r="K789" s="22">
+      <c r="K789" s="25">
         <v>1301205</v>
       </c>
       <c r="L789" s="23">
@@ -30845,7 +30752,7 @@
       <c r="H790" s="2"/>
       <c r="I790" s="21"/>
       <c r="J790" s="21"/>
-      <c r="K790" s="22">
+      <c r="K790" s="25">
         <v>1301206</v>
       </c>
       <c r="L790" s="23">
@@ -30879,7 +30786,7 @@
       <c r="H791" s="2"/>
       <c r="I791" s="21"/>
       <c r="J791" s="21"/>
-      <c r="K791" s="22">
+      <c r="K791" s="25">
         <v>1301207</v>
       </c>
       <c r="L791" s="23">
@@ -30913,7 +30820,7 @@
       <c r="H792" s="2"/>
       <c r="I792" s="21"/>
       <c r="J792" s="21"/>
-      <c r="K792" s="22">
+      <c r="K792" s="25">
         <v>1301208</v>
       </c>
       <c r="L792" s="23">
@@ -30947,7 +30854,7 @@
       <c r="H793" s="2"/>
       <c r="I793" s="21"/>
       <c r="J793" s="21"/>
-      <c r="K793" s="22">
+      <c r="K793" s="25">
         <v>1301209</v>
       </c>
       <c r="L793" s="23">
@@ -30981,7 +30888,7 @@
       <c r="H794" s="2"/>
       <c r="I794" s="21"/>
       <c r="J794" s="21"/>
-      <c r="K794" s="22" t="s">
+      <c r="K794" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L794" s="23">
@@ -31013,7 +30920,7 @@
       </c>
       <c r="I795" s="21"/>
       <c r="J795" s="21"/>
-      <c r="K795" s="22" t="s">
+      <c r="K795" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L795" s="23">
@@ -31045,7 +30952,7 @@
       </c>
       <c r="I796" s="21"/>
       <c r="J796" s="21"/>
-      <c r="K796" s="22" t="s">
+      <c r="K796" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L796" s="23">
@@ -31077,7 +30984,7 @@
       </c>
       <c r="I797" s="21"/>
       <c r="J797" s="21"/>
-      <c r="K797" s="22" t="s">
+      <c r="K797" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L797" s="23">
@@ -31109,7 +31016,7 @@
       </c>
       <c r="I798" s="21"/>
       <c r="J798" s="21"/>
-      <c r="K798" s="22" t="s">
+      <c r="K798" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L798" s="23">
@@ -31141,7 +31048,7 @@
       </c>
       <c r="I799" s="21"/>
       <c r="J799" s="21"/>
-      <c r="K799" s="22" t="s">
+      <c r="K799" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L799" s="23">
@@ -31173,7 +31080,7 @@
       </c>
       <c r="I800" s="21"/>
       <c r="J800" s="21"/>
-      <c r="K800" s="22" t="s">
+      <c r="K800" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L800" s="23">
@@ -31205,7 +31112,7 @@
       </c>
       <c r="I801" s="21"/>
       <c r="J801" s="21"/>
-      <c r="K801" s="22" t="s">
+      <c r="K801" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L801" s="23">
@@ -31237,7 +31144,7 @@
       </c>
       <c r="I802" s="21"/>
       <c r="J802" s="21"/>
-      <c r="K802" s="22" t="s">
+      <c r="K802" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L802" s="23">
@@ -31269,7 +31176,7 @@
       </c>
       <c r="I803" s="21"/>
       <c r="J803" s="21"/>
-      <c r="K803" s="22" t="s">
+      <c r="K803" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L803" s="23">
@@ -31301,7 +31208,7 @@
       </c>
       <c r="I804" s="21"/>
       <c r="J804" s="21"/>
-      <c r="K804" s="22" t="s">
+      <c r="K804" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L804" s="23">
@@ -31333,7 +31240,7 @@
       </c>
       <c r="I805" s="21"/>
       <c r="J805" s="21"/>
-      <c r="K805" s="22" t="s">
+      <c r="K805" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L805" s="23">
@@ -31365,7 +31272,7 @@
       </c>
       <c r="I806" s="21"/>
       <c r="J806" s="21"/>
-      <c r="K806" s="22" t="s">
+      <c r="K806" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L806" s="23">
@@ -31397,7 +31304,7 @@
       </c>
       <c r="I807" s="21"/>
       <c r="J807" s="21"/>
-      <c r="K807" s="22" t="s">
+      <c r="K807" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L807" s="23">
@@ -31429,7 +31336,7 @@
       </c>
       <c r="I808" s="21"/>
       <c r="J808" s="21"/>
-      <c r="K808" s="22" t="s">
+      <c r="K808" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L808" s="23">
@@ -31461,7 +31368,7 @@
       </c>
       <c r="I809" s="21"/>
       <c r="J809" s="21"/>
-      <c r="K809" s="22" t="s">
+      <c r="K809" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L809" s="23">
@@ -31493,7 +31400,7 @@
       </c>
       <c r="I810" s="21"/>
       <c r="J810" s="21"/>
-      <c r="K810" s="22" t="s">
+      <c r="K810" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L810" s="23">
@@ -31525,7 +31432,7 @@
       </c>
       <c r="I811" s="21"/>
       <c r="J811" s="21"/>
-      <c r="K811" s="22" t="s">
+      <c r="K811" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L811" s="23">
@@ -31557,7 +31464,7 @@
       </c>
       <c r="I812" s="21"/>
       <c r="J812" s="21"/>
-      <c r="K812" s="22" t="s">
+      <c r="K812" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L812" s="23">
@@ -31589,7 +31496,7 @@
       </c>
       <c r="I813" s="21"/>
       <c r="J813" s="21"/>
-      <c r="K813" s="22" t="s">
+      <c r="K813" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L813" s="23">
@@ -31621,7 +31528,7 @@
       </c>
       <c r="I814" s="21"/>
       <c r="J814" s="21"/>
-      <c r="K814" s="22" t="s">
+      <c r="K814" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L814" s="23">
@@ -31653,7 +31560,7 @@
       </c>
       <c r="I815" s="21"/>
       <c r="J815" s="21"/>
-      <c r="K815" s="22" t="s">
+      <c r="K815" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L815" s="23">
@@ -31685,7 +31592,7 @@
       </c>
       <c r="I816" s="21"/>
       <c r="J816" s="21"/>
-      <c r="K816" s="22" t="s">
+      <c r="K816" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L816" s="23">
@@ -31717,7 +31624,7 @@
       </c>
       <c r="I817" s="21"/>
       <c r="J817" s="21"/>
-      <c r="K817" s="22" t="s">
+      <c r="K817" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L817" s="23">
@@ -31749,7 +31656,7 @@
       </c>
       <c r="I818" s="21"/>
       <c r="J818" s="21"/>
-      <c r="K818" s="22" t="s">
+      <c r="K818" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L818" s="23">
@@ -31781,7 +31688,7 @@
       </c>
       <c r="I819" s="21"/>
       <c r="J819" s="21"/>
-      <c r="K819" s="22" t="s">
+      <c r="K819" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L819" s="23">
@@ -31813,7 +31720,7 @@
       </c>
       <c r="I820" s="21"/>
       <c r="J820" s="21"/>
-      <c r="K820" s="22" t="s">
+      <c r="K820" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L820" s="23">
@@ -31845,7 +31752,7 @@
       </c>
       <c r="I821" s="21"/>
       <c r="J821" s="21"/>
-      <c r="K821" s="22" t="s">
+      <c r="K821" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L821" s="23">
@@ -31877,7 +31784,7 @@
       </c>
       <c r="I822" s="21"/>
       <c r="J822" s="21"/>
-      <c r="K822" s="22" t="s">
+      <c r="K822" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L822" s="23">
@@ -31909,7 +31816,7 @@
       </c>
       <c r="I823" s="21"/>
       <c r="J823" s="21"/>
-      <c r="K823" s="22" t="s">
+      <c r="K823" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L823" s="23">
@@ -31941,7 +31848,7 @@
       </c>
       <c r="I824" s="21"/>
       <c r="J824" s="21"/>
-      <c r="K824" s="22" t="s">
+      <c r="K824" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L824" s="23">
@@ -31973,7 +31880,7 @@
       </c>
       <c r="I825" s="21"/>
       <c r="J825" s="21"/>
-      <c r="K825" s="22" t="s">
+      <c r="K825" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L825" s="23">
@@ -32005,7 +31912,7 @@
       </c>
       <c r="I826" s="21"/>
       <c r="J826" s="21"/>
-      <c r="K826" s="22" t="s">
+      <c r="K826" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L826" s="23">
@@ -32037,7 +31944,7 @@
       </c>
       <c r="I827" s="21"/>
       <c r="J827" s="21"/>
-      <c r="K827" s="22" t="s">
+      <c r="K827" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L827" s="23">
@@ -32069,7 +31976,7 @@
       </c>
       <c r="I828" s="21"/>
       <c r="J828" s="21"/>
-      <c r="K828" s="22" t="s">
+      <c r="K828" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L828" s="23">
@@ -32101,7 +32008,7 @@
       </c>
       <c r="I829" s="21"/>
       <c r="J829" s="21"/>
-      <c r="K829" s="22" t="s">
+      <c r="K829" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L829" s="23">
@@ -32133,7 +32040,7 @@
       </c>
       <c r="I830" s="21"/>
       <c r="J830" s="21"/>
-      <c r="K830" s="22" t="s">
+      <c r="K830" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L830" s="23">
@@ -32165,7 +32072,7 @@
       </c>
       <c r="I831" s="21"/>
       <c r="J831" s="21"/>
-      <c r="K831" s="22" t="s">
+      <c r="K831" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L831" s="23">
@@ -32197,7 +32104,7 @@
       </c>
       <c r="I832" s="21"/>
       <c r="J832" s="21"/>
-      <c r="K832" s="22" t="s">
+      <c r="K832" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L832" s="23">
@@ -32229,7 +32136,7 @@
       </c>
       <c r="I833" s="21"/>
       <c r="J833" s="21"/>
-      <c r="K833" s="22" t="s">
+      <c r="K833" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L833" s="23">
@@ -32261,7 +32168,7 @@
       </c>
       <c r="I834" s="21"/>
       <c r="J834" s="21"/>
-      <c r="K834" s="22" t="s">
+      <c r="K834" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L834" s="23">
@@ -32293,7 +32200,7 @@
       </c>
       <c r="I835" s="21"/>
       <c r="J835" s="21"/>
-      <c r="K835" s="22" t="s">
+      <c r="K835" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L835" s="23">
@@ -32325,7 +32232,7 @@
       </c>
       <c r="I836" s="21"/>
       <c r="J836" s="21"/>
-      <c r="K836" s="22" t="s">
+      <c r="K836" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L836" s="23">
@@ -32357,7 +32264,7 @@
       </c>
       <c r="I837" s="21"/>
       <c r="J837" s="21"/>
-      <c r="K837" s="22" t="s">
+      <c r="K837" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L837" s="23">
@@ -32389,7 +32296,7 @@
       </c>
       <c r="I838" s="21"/>
       <c r="J838" s="21"/>
-      <c r="K838" s="22" t="s">
+      <c r="K838" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L838" s="23">
@@ -32421,7 +32328,7 @@
       </c>
       <c r="I839" s="21"/>
       <c r="J839" s="21"/>
-      <c r="K839" s="22" t="s">
+      <c r="K839" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L839" s="23">
@@ -32453,7 +32360,7 @@
       </c>
       <c r="I840" s="21"/>
       <c r="J840" s="21"/>
-      <c r="K840" s="22" t="s">
+      <c r="K840" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L840" s="23">
@@ -32485,7 +32392,7 @@
       </c>
       <c r="I841" s="21"/>
       <c r="J841" s="21"/>
-      <c r="K841" s="22" t="s">
+      <c r="K841" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L841" s="23">
@@ -32517,7 +32424,7 @@
       </c>
       <c r="I842" s="21"/>
       <c r="J842" s="21"/>
-      <c r="K842" s="22" t="s">
+      <c r="K842" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L842" s="23">
@@ -32549,7 +32456,7 @@
       </c>
       <c r="I843" s="21"/>
       <c r="J843" s="21"/>
-      <c r="K843" s="22" t="s">
+      <c r="K843" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L843" s="23">
@@ -32581,7 +32488,7 @@
       </c>
       <c r="I844" s="21"/>
       <c r="J844" s="21"/>
-      <c r="K844" s="22" t="s">
+      <c r="K844" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L844" s="23"/>
@@ -32590,1022 +32497,1022 @@
       </c>
     </row>
     <row r="845" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A845" s="28">
+      <c r="A845" s="30">
         <f t="shared" si="31"/>
         <v>1302001</v>
       </c>
-      <c r="B845" s="28">
+      <c r="B845" s="30">
         <v>1302</v>
       </c>
-      <c r="C845" s="28" t="s">
+      <c r="C845" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D845" s="28">
+      <c r="D845" s="30">
         <v>1</v>
       </c>
       <c r="E845" s="4"/>
-      <c r="F845" s="28" t="s">
+      <c r="F845" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G845" s="29">
+      <c r="G845" s="31">
         <v>1</v>
       </c>
-      <c r="H845" s="29">
+      <c r="H845" s="31">
         <v>4030001</v>
       </c>
-      <c r="I845" s="29">
+      <c r="I845" s="31">
         <v>100300</v>
       </c>
-      <c r="J845" s="29"/>
-      <c r="K845" s="30">
+      <c r="J845" s="31"/>
+      <c r="K845" s="32">
         <v>1302201</v>
       </c>
-      <c r="L845" s="30">
+      <c r="L845" s="32">
         <v>10</v>
       </c>
-      <c r="M845" s="31" t="s">
+      <c r="M845" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="846" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A846" s="28">
+      <c r="A846" s="30">
         <f t="shared" si="31"/>
         <v>1302002</v>
       </c>
-      <c r="B846" s="28">
+      <c r="B846" s="30">
         <v>1302</v>
       </c>
-      <c r="C846" s="28" t="s">
+      <c r="C846" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D846" s="28">
+      <c r="D846" s="30">
         <v>2</v>
       </c>
       <c r="E846" s="4"/>
-      <c r="F846" s="28" t="s">
+      <c r="F846" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G846" s="29">
+      <c r="G846" s="31">
         <v>2</v>
       </c>
-      <c r="H846" s="29">
+      <c r="H846" s="31">
         <v>4030001</v>
       </c>
-      <c r="I846" s="29">
+      <c r="I846" s="31">
         <v>103400</v>
       </c>
-      <c r="J846" s="29"/>
-      <c r="K846" s="30">
+      <c r="J846" s="31"/>
+      <c r="K846" s="32">
         <v>1302202</v>
       </c>
-      <c r="L846" s="30">
+      <c r="L846" s="32">
         <v>30</v>
       </c>
-      <c r="M846" s="31" t="s">
+      <c r="M846" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="847" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A847" s="28">
+      <c r="A847" s="30">
         <f t="shared" si="31"/>
         <v>1302003</v>
       </c>
-      <c r="B847" s="28">
+      <c r="B847" s="30">
         <v>1302</v>
       </c>
-      <c r="C847" s="28" t="s">
+      <c r="C847" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D847" s="28">
+      <c r="D847" s="30">
         <v>3</v>
       </c>
       <c r="E847" s="4"/>
-      <c r="F847" s="28" t="s">
+      <c r="F847" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="G847" s="29">
+      <c r="G847" s="31">
         <v>3</v>
       </c>
-      <c r="H847" s="29">
+      <c r="H847" s="31">
         <v>4030001</v>
       </c>
-      <c r="I847" s="29">
+      <c r="I847" s="31">
         <v>103401</v>
       </c>
-      <c r="J847" s="29"/>
-      <c r="K847" s="30">
+      <c r="J847" s="31"/>
+      <c r="K847" s="32">
         <v>1302203</v>
       </c>
-      <c r="L847" s="30">
+      <c r="L847" s="32">
         <v>60</v>
       </c>
-      <c r="M847" s="31" t="s">
+      <c r="M847" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="848" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A848" s="28">
+      <c r="A848" s="30">
         <f t="shared" si="31"/>
         <v>1302004</v>
       </c>
-      <c r="B848" s="28">
+      <c r="B848" s="30">
         <v>1302</v>
       </c>
-      <c r="C848" s="28" t="s">
+      <c r="C848" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D848" s="28">
+      <c r="D848" s="30">
         <v>4</v>
       </c>
       <c r="E848" s="4"/>
-      <c r="F848" s="28" t="s">
+      <c r="F848" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="G848" s="29">
+      <c r="G848" s="31">
         <v>4</v>
       </c>
-      <c r="H848" s="29">
+      <c r="H848" s="31">
         <v>4030001</v>
       </c>
-      <c r="I848" s="29">
+      <c r="I848" s="31">
         <v>101400</v>
       </c>
-      <c r="J848" s="29"/>
-      <c r="K848" s="32" t="s">
+      <c r="J848" s="31"/>
+      <c r="K848" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="L848" s="30">
+      <c r="L848" s="32">
         <v>90</v>
       </c>
-      <c r="M848" s="31" t="s">
+      <c r="M848" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="849" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A849" s="28">
+      <c r="A849" s="30">
         <f t="shared" si="31"/>
         <v>1302005</v>
       </c>
-      <c r="B849" s="28">
+      <c r="B849" s="30">
         <v>1302</v>
       </c>
-      <c r="C849" s="28" t="s">
+      <c r="C849" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D849" s="28">
+      <c r="D849" s="30">
         <v>5</v>
       </c>
       <c r="E849" s="4"/>
-      <c r="F849" s="28" t="s">
+      <c r="F849" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G849" s="29">
+      <c r="G849" s="31">
         <v>5</v>
       </c>
-      <c r="H849" s="29">
+      <c r="H849" s="31">
         <v>4030001</v>
       </c>
-      <c r="I849" s="29">
+      <c r="I849" s="31">
         <v>103500</v>
       </c>
-      <c r="J849" s="29"/>
-      <c r="K849" s="32" t="s">
+      <c r="J849" s="31"/>
+      <c r="K849" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="L849" s="30">
+      <c r="L849" s="32">
         <v>120</v>
       </c>
-      <c r="M849" s="31" t="s">
+      <c r="M849" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="850" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A850" s="28">
+      <c r="A850" s="30">
         <f t="shared" si="31"/>
         <v>1302006</v>
       </c>
-      <c r="B850" s="28">
+      <c r="B850" s="30">
         <v>1302</v>
       </c>
-      <c r="C850" s="28" t="s">
+      <c r="C850" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D850" s="28">
+      <c r="D850" s="30">
         <v>6</v>
       </c>
       <c r="E850" s="4"/>
-      <c r="F850" s="28" t="s">
+      <c r="F850" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="G850" s="29">
+      <c r="G850" s="31">
         <v>6</v>
       </c>
-      <c r="H850" s="29">
+      <c r="H850" s="31">
         <v>4030001</v>
       </c>
-      <c r="I850" s="29">
+      <c r="I850" s="31">
         <v>103501</v>
       </c>
-      <c r="J850" s="29"/>
-      <c r="K850" s="32" t="s">
+      <c r="J850" s="31"/>
+      <c r="K850" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="L850" s="30">
+      <c r="L850" s="32">
         <v>150</v>
       </c>
-      <c r="M850" s="31" t="s">
+      <c r="M850" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="851" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A851" s="28">
+      <c r="A851" s="30">
         <f t="shared" si="31"/>
         <v>1302007</v>
       </c>
-      <c r="B851" s="28">
+      <c r="B851" s="30">
         <v>1302</v>
       </c>
-      <c r="C851" s="28" t="s">
+      <c r="C851" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D851" s="28">
+      <c r="D851" s="30">
         <v>7</v>
       </c>
       <c r="E851" s="4"/>
-      <c r="F851" s="28" t="s">
+      <c r="F851" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G851" s="29">
+      <c r="G851" s="31">
         <v>7</v>
       </c>
-      <c r="H851" s="29">
+      <c r="H851" s="31">
         <v>4030001</v>
       </c>
-      <c r="I851" s="29">
+      <c r="I851" s="31">
         <v>100700</v>
       </c>
-      <c r="J851" s="29"/>
-      <c r="K851" s="32" t="s">
+      <c r="J851" s="31"/>
+      <c r="K851" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="L851" s="30">
+      <c r="L851" s="32">
         <v>180</v>
       </c>
-      <c r="M851" s="31" t="s">
+      <c r="M851" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="852" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A852" s="28">
+      <c r="A852" s="30">
         <f t="shared" si="31"/>
         <v>1302008</v>
       </c>
-      <c r="B852" s="28">
+      <c r="B852" s="30">
         <v>1302</v>
       </c>
-      <c r="C852" s="28" t="s">
+      <c r="C852" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D852" s="28">
+      <c r="D852" s="30">
         <v>8</v>
       </c>
       <c r="E852" s="4"/>
-      <c r="F852" s="28" t="s">
+      <c r="F852" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="G852" s="29">
+      <c r="G852" s="31">
         <v>8</v>
       </c>
-      <c r="H852" s="29">
+      <c r="H852" s="31">
         <v>4030001</v>
       </c>
-      <c r="I852" s="29">
+      <c r="I852" s="31">
         <v>103700</v>
       </c>
-      <c r="J852" s="29"/>
-      <c r="K852" s="32" t="s">
+      <c r="J852" s="31"/>
+      <c r="K852" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="L852" s="30">
+      <c r="L852" s="32">
         <v>210</v>
       </c>
-      <c r="M852" s="31" t="s">
+      <c r="M852" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="853" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A853" s="28">
+      <c r="A853" s="30">
         <f t="shared" si="31"/>
         <v>1302009</v>
       </c>
-      <c r="B853" s="28">
+      <c r="B853" s="30">
         <v>1302</v>
       </c>
-      <c r="C853" s="28" t="s">
+      <c r="C853" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D853" s="28">
+      <c r="D853" s="30">
         <v>9</v>
       </c>
       <c r="E853" s="4"/>
-      <c r="F853" s="28" t="s">
+      <c r="F853" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G853" s="29">
+      <c r="G853" s="31">
         <v>9</v>
       </c>
-      <c r="H853" s="29">
+      <c r="H853" s="31">
         <v>4030001</v>
       </c>
-      <c r="I853" s="29">
+      <c r="I853" s="31">
         <v>103600</v>
       </c>
-      <c r="J853" s="29"/>
-      <c r="K853" s="32" t="s">
+      <c r="J853" s="31"/>
+      <c r="K853" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="L853" s="30">
+      <c r="L853" s="32">
         <v>240</v>
       </c>
-      <c r="M853" s="31" t="s">
+      <c r="M853" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="854" s="4" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A854" s="28">
+      <c r="A854" s="30">
         <f t="shared" si="31"/>
         <v>1302010</v>
       </c>
-      <c r="B854" s="28">
+      <c r="B854" s="30">
         <v>1302</v>
       </c>
-      <c r="C854" s="28" t="s">
+      <c r="C854" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D854" s="28">
+      <c r="D854" s="30">
         <v>10</v>
       </c>
       <c r="E854" s="4"/>
-      <c r="F854" s="28" t="s">
+      <c r="F854" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G854" s="29">
+      <c r="G854" s="31">
         <v>10</v>
       </c>
-      <c r="H854" s="29">
+      <c r="H854" s="31">
         <v>4030001</v>
       </c>
-      <c r="I854" s="29">
+      <c r="I854" s="31">
         <v>101700</v>
       </c>
-      <c r="J854" s="29"/>
-      <c r="K854" s="32" t="s">
+      <c r="J854" s="31"/>
+      <c r="K854" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="L854" s="30">
+      <c r="L854" s="32">
         <v>300</v>
       </c>
-      <c r="M854" s="31" t="s">
+      <c r="M854" s="33" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="855" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A855" s="33">
+      <c r="A855" s="35">
         <f t="shared" ref="A855:A884" si="32">B855*1000+D855</f>
         <v>1101001</v>
       </c>
-      <c r="B855" s="33">
+      <c r="B855" s="35">
         <v>1101</v>
       </c>
-      <c r="C855" s="33" t="s">
+      <c r="C855" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D855" s="33">
+      <c r="D855" s="35">
         <v>1</v>
       </c>
       <c r="E855" s="5"/>
-      <c r="F855" s="33" t="s">
+      <c r="F855" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G855" s="34">
+      <c r="G855" s="36">
         <v>100</v>
       </c>
-      <c r="H855" s="34"/>
-      <c r="I855" s="34"/>
-      <c r="J855" s="34"/>
-      <c r="K855" s="35"/>
-      <c r="L855" s="36">
+      <c r="H855" s="36"/>
+      <c r="I855" s="36"/>
+      <c r="J855" s="36"/>
+      <c r="K855" s="37"/>
+      <c r="L855" s="38">
         <v>5</v>
       </c>
-      <c r="M855" s="37" t="s">
+      <c r="M855" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="856" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A856" s="33">
+      <c r="A856" s="35">
         <f t="shared" si="32"/>
         <v>1101002</v>
       </c>
-      <c r="B856" s="33">
+      <c r="B856" s="35">
         <v>1101</v>
       </c>
-      <c r="C856" s="33" t="s">
+      <c r="C856" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D856" s="33">
+      <c r="D856" s="35">
         <v>2</v>
       </c>
       <c r="E856" s="5"/>
-      <c r="F856" s="33" t="s">
+      <c r="F856" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G856" s="34">
+      <c r="G856" s="36">
         <v>200</v>
       </c>
-      <c r="H856" s="34"/>
-      <c r="I856" s="34"/>
-      <c r="J856" s="34"/>
-      <c r="K856" s="35"/>
-      <c r="L856" s="36">
+      <c r="H856" s="36"/>
+      <c r="I856" s="36"/>
+      <c r="J856" s="36"/>
+      <c r="K856" s="37"/>
+      <c r="L856" s="38">
         <v>10</v>
       </c>
-      <c r="M856" s="37" t="s">
+      <c r="M856" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="857" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A857" s="33">
+      <c r="A857" s="35">
         <f t="shared" si="32"/>
         <v>1101003</v>
       </c>
-      <c r="B857" s="33">
+      <c r="B857" s="35">
         <v>1101</v>
       </c>
-      <c r="C857" s="33" t="s">
+      <c r="C857" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D857" s="33">
+      <c r="D857" s="35">
         <v>3</v>
       </c>
       <c r="E857" s="5"/>
-      <c r="F857" s="33" t="s">
+      <c r="F857" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G857" s="34">
+      <c r="G857" s="36">
         <v>300</v>
       </c>
-      <c r="H857" s="34"/>
-      <c r="I857" s="34"/>
-      <c r="J857" s="34"/>
-      <c r="K857" s="35"/>
-      <c r="L857" s="36">
+      <c r="H857" s="36"/>
+      <c r="I857" s="36"/>
+      <c r="J857" s="36"/>
+      <c r="K857" s="37"/>
+      <c r="L857" s="38">
         <v>20</v>
       </c>
-      <c r="M857" s="37" t="s">
+      <c r="M857" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="858" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A858" s="33">
+      <c r="A858" s="35">
         <f t="shared" si="32"/>
         <v>1101004</v>
       </c>
-      <c r="B858" s="33">
+      <c r="B858" s="35">
         <v>1101</v>
       </c>
-      <c r="C858" s="33" t="s">
+      <c r="C858" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D858" s="33">
+      <c r="D858" s="35">
         <v>4</v>
       </c>
       <c r="E858" s="5"/>
-      <c r="F858" s="33" t="s">
+      <c r="F858" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G858" s="34">
+      <c r="G858" s="36">
         <v>400</v>
       </c>
-      <c r="H858" s="34"/>
-      <c r="I858" s="34"/>
-      <c r="J858" s="34"/>
-      <c r="K858" s="35"/>
-      <c r="L858" s="36">
+      <c r="H858" s="36"/>
+      <c r="I858" s="36"/>
+      <c r="J858" s="36"/>
+      <c r="K858" s="37"/>
+      <c r="L858" s="38">
         <v>30</v>
       </c>
-      <c r="M858" s="37" t="s">
+      <c r="M858" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="859" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A859" s="33">
+      <c r="A859" s="35">
         <f t="shared" si="32"/>
         <v>1101005</v>
       </c>
-      <c r="B859" s="33">
+      <c r="B859" s="35">
         <v>1101</v>
       </c>
-      <c r="C859" s="33" t="s">
+      <c r="C859" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D859" s="33">
+      <c r="D859" s="35">
         <v>5</v>
       </c>
       <c r="E859" s="5"/>
-      <c r="F859" s="33" t="s">
+      <c r="F859" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G859" s="34">
+      <c r="G859" s="36">
         <v>500</v>
       </c>
-      <c r="H859" s="34"/>
-      <c r="I859" s="34"/>
-      <c r="J859" s="34"/>
-      <c r="K859" s="35"/>
-      <c r="L859" s="36">
+      <c r="H859" s="36"/>
+      <c r="I859" s="36"/>
+      <c r="J859" s="36"/>
+      <c r="K859" s="37"/>
+      <c r="L859" s="38">
         <v>60</v>
       </c>
-      <c r="M859" s="37" t="s">
+      <c r="M859" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="860" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A860" s="33">
+      <c r="A860" s="35">
         <f t="shared" si="32"/>
         <v>1101006</v>
       </c>
-      <c r="B860" s="33">
+      <c r="B860" s="35">
         <v>1101</v>
       </c>
-      <c r="C860" s="33" t="s">
+      <c r="C860" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D860" s="33">
+      <c r="D860" s="35">
         <v>6</v>
       </c>
       <c r="E860" s="5"/>
-      <c r="F860" s="33" t="s">
+      <c r="F860" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G860" s="34">
-        <v>600</v>
-      </c>
-      <c r="H860" s="34"/>
-      <c r="I860" s="34"/>
-      <c r="J860" s="34"/>
-      <c r="K860" s="35"/>
-      <c r="L860" s="36">
+      <c r="G860" s="36">
+        <v>600</v>
+      </c>
+      <c r="H860" s="36"/>
+      <c r="I860" s="36"/>
+      <c r="J860" s="36"/>
+      <c r="K860" s="37"/>
+      <c r="L860" s="38">
         <v>80</v>
       </c>
-      <c r="M860" s="37" t="s">
+      <c r="M860" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="861" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A861" s="33">
+      <c r="A861" s="35">
         <f t="shared" si="32"/>
         <v>1101007</v>
       </c>
-      <c r="B861" s="33">
+      <c r="B861" s="35">
         <v>1101</v>
       </c>
-      <c r="C861" s="33" t="s">
+      <c r="C861" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D861" s="33">
+      <c r="D861" s="35">
         <v>7</v>
       </c>
       <c r="E861" s="5"/>
-      <c r="F861" s="33" t="s">
+      <c r="F861" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G861" s="34">
+      <c r="G861" s="36">
         <v>700</v>
       </c>
-      <c r="H861" s="34"/>
-      <c r="I861" s="34"/>
-      <c r="J861" s="34"/>
-      <c r="K861" s="35"/>
-      <c r="L861" s="36">
+      <c r="H861" s="36"/>
+      <c r="I861" s="36"/>
+      <c r="J861" s="36"/>
+      <c r="K861" s="37"/>
+      <c r="L861" s="38">
         <v>120</v>
       </c>
-      <c r="M861" s="37" t="s">
+      <c r="M861" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="862" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A862" s="33">
+      <c r="A862" s="35">
         <f t="shared" si="32"/>
         <v>1101008</v>
       </c>
-      <c r="B862" s="33">
+      <c r="B862" s="35">
         <v>1101</v>
       </c>
-      <c r="C862" s="33" t="s">
+      <c r="C862" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D862" s="33">
+      <c r="D862" s="35">
         <v>8</v>
       </c>
       <c r="E862" s="5"/>
-      <c r="F862" s="33" t="s">
+      <c r="F862" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G862" s="34">
+      <c r="G862" s="36">
         <v>800</v>
       </c>
-      <c r="H862" s="34"/>
-      <c r="I862" s="34"/>
-      <c r="J862" s="34"/>
-      <c r="K862" s="35"/>
-      <c r="L862" s="36">
+      <c r="H862" s="36"/>
+      <c r="I862" s="36"/>
+      <c r="J862" s="36"/>
+      <c r="K862" s="37"/>
+      <c r="L862" s="38">
         <v>150</v>
       </c>
-      <c r="M862" s="37" t="s">
+      <c r="M862" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="863" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A863" s="33">
+      <c r="A863" s="35">
         <f t="shared" si="32"/>
         <v>1101009</v>
       </c>
-      <c r="B863" s="33">
+      <c r="B863" s="35">
         <v>1101</v>
       </c>
-      <c r="C863" s="33" t="s">
+      <c r="C863" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D863" s="33">
+      <c r="D863" s="35">
         <v>9</v>
       </c>
       <c r="E863" s="5"/>
-      <c r="F863" s="33" t="s">
+      <c r="F863" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G863" s="34">
+      <c r="G863" s="36">
         <v>900</v>
       </c>
-      <c r="H863" s="34"/>
-      <c r="I863" s="34"/>
-      <c r="J863" s="34"/>
-      <c r="K863" s="35"/>
-      <c r="L863" s="36">
+      <c r="H863" s="36"/>
+      <c r="I863" s="36"/>
+      <c r="J863" s="36"/>
+      <c r="K863" s="37"/>
+      <c r="L863" s="38">
         <v>200</v>
       </c>
-      <c r="M863" s="37" t="s">
+      <c r="M863" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="864" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A864" s="33">
+      <c r="A864" s="35">
         <f t="shared" si="32"/>
         <v>1101010</v>
       </c>
-      <c r="B864" s="33">
+      <c r="B864" s="35">
         <v>1101</v>
       </c>
-      <c r="C864" s="33" t="s">
+      <c r="C864" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D864" s="33">
+      <c r="D864" s="35">
         <v>10</v>
       </c>
       <c r="E864" s="5"/>
-      <c r="F864" s="33" t="s">
+      <c r="F864" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G864" s="34">
+      <c r="G864" s="36">
         <v>1000</v>
       </c>
-      <c r="H864" s="34"/>
-      <c r="I864" s="34"/>
-      <c r="J864" s="34"/>
-      <c r="K864" s="35"/>
-      <c r="L864" s="36">
+      <c r="H864" s="36"/>
+      <c r="I864" s="36"/>
+      <c r="J864" s="36"/>
+      <c r="K864" s="37"/>
+      <c r="L864" s="38">
         <v>300</v>
       </c>
-      <c r="M864" s="37" t="s">
+      <c r="M864" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="865" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A865" s="33">
+      <c r="A865" s="35">
         <f t="shared" si="32"/>
         <v>1101011</v>
       </c>
-      <c r="B865" s="33">
+      <c r="B865" s="35">
         <v>1101</v>
       </c>
-      <c r="C865" s="33" t="s">
+      <c r="C865" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D865" s="33">
+      <c r="D865" s="35">
         <v>11</v>
       </c>
       <c r="E865" s="5"/>
-      <c r="F865" s="33" t="s">
+      <c r="F865" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G865" s="34">
+      <c r="G865" s="36">
         <v>1100</v>
       </c>
-      <c r="H865" s="34"/>
-      <c r="I865" s="34"/>
-      <c r="J865" s="34"/>
-      <c r="K865" s="35"/>
-      <c r="L865" s="36">
+      <c r="H865" s="36"/>
+      <c r="I865" s="36"/>
+      <c r="J865" s="36"/>
+      <c r="K865" s="37"/>
+      <c r="L865" s="38">
         <v>360</v>
       </c>
-      <c r="M865" s="37" t="s">
+      <c r="M865" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="866" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A866" s="33">
+      <c r="A866" s="35">
         <f t="shared" si="32"/>
         <v>1101012</v>
       </c>
-      <c r="B866" s="33">
+      <c r="B866" s="35">
         <v>1101</v>
       </c>
-      <c r="C866" s="33" t="s">
+      <c r="C866" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D866" s="33">
+      <c r="D866" s="35">
         <v>12</v>
       </c>
       <c r="E866" s="5"/>
-      <c r="F866" s="33" t="s">
+      <c r="F866" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G866" s="34">
+      <c r="G866" s="36">
         <v>1200</v>
       </c>
-      <c r="H866" s="34"/>
-      <c r="I866" s="34"/>
-      <c r="J866" s="34"/>
-      <c r="K866" s="35"/>
-      <c r="L866" s="36">
+      <c r="H866" s="36"/>
+      <c r="I866" s="36"/>
+      <c r="J866" s="36"/>
+      <c r="K866" s="37"/>
+      <c r="L866" s="38">
         <v>420</v>
       </c>
-      <c r="M866" s="37" t="s">
+      <c r="M866" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="867" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A867" s="33">
+      <c r="A867" s="35">
         <f t="shared" si="32"/>
         <v>1101013</v>
       </c>
-      <c r="B867" s="33">
+      <c r="B867" s="35">
         <v>1101</v>
       </c>
-      <c r="C867" s="33" t="s">
+      <c r="C867" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D867" s="33">
+      <c r="D867" s="35">
         <v>13</v>
       </c>
       <c r="E867" s="5"/>
-      <c r="F867" s="33" t="s">
+      <c r="F867" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G867" s="34">
+      <c r="G867" s="36">
         <v>1300</v>
       </c>
-      <c r="H867" s="34"/>
-      <c r="I867" s="34"/>
-      <c r="J867" s="34"/>
-      <c r="K867" s="35"/>
-      <c r="L867" s="36">
+      <c r="H867" s="36"/>
+      <c r="I867" s="36"/>
+      <c r="J867" s="36"/>
+      <c r="K867" s="37"/>
+      <c r="L867" s="38">
         <v>480</v>
       </c>
-      <c r="M867" s="37" t="s">
+      <c r="M867" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="868" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A868" s="33">
+      <c r="A868" s="35">
         <f t="shared" si="32"/>
         <v>1101014</v>
       </c>
-      <c r="B868" s="33">
+      <c r="B868" s="35">
         <v>1101</v>
       </c>
-      <c r="C868" s="33" t="s">
+      <c r="C868" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D868" s="33">
+      <c r="D868" s="35">
         <v>14</v>
       </c>
       <c r="E868" s="5"/>
-      <c r="F868" s="33" t="s">
+      <c r="F868" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G868" s="34">
+      <c r="G868" s="36">
         <v>1400</v>
       </c>
-      <c r="H868" s="34"/>
-      <c r="I868" s="34"/>
-      <c r="J868" s="34"/>
-      <c r="K868" s="35"/>
-      <c r="L868" s="36">
+      <c r="H868" s="36"/>
+      <c r="I868" s="36"/>
+      <c r="J868" s="36"/>
+      <c r="K868" s="37"/>
+      <c r="L868" s="38">
         <v>540</v>
       </c>
-      <c r="M868" s="37" t="s">
+      <c r="M868" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="869" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A869" s="33">
+      <c r="A869" s="35">
         <f t="shared" si="32"/>
         <v>1101015</v>
       </c>
-      <c r="B869" s="33">
+      <c r="B869" s="35">
         <v>1101</v>
       </c>
-      <c r="C869" s="33" t="s">
+      <c r="C869" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D869" s="33">
+      <c r="D869" s="35">
         <v>15</v>
       </c>
       <c r="E869" s="5"/>
-      <c r="F869" s="33" t="s">
+      <c r="F869" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G869" s="34">
+      <c r="G869" s="36">
         <v>1500</v>
       </c>
-      <c r="H869" s="34"/>
-      <c r="I869" s="34"/>
-      <c r="J869" s="34"/>
-      <c r="K869" s="35"/>
-      <c r="L869" s="36">
-        <v>600</v>
-      </c>
-      <c r="M869" s="37" t="s">
+      <c r="H869" s="36"/>
+      <c r="I869" s="36"/>
+      <c r="J869" s="36"/>
+      <c r="K869" s="37"/>
+      <c r="L869" s="38">
+        <v>600</v>
+      </c>
+      <c r="M869" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="870" s="5" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A870" s="33">
+      <c r="A870" s="35">
         <f t="shared" si="32"/>
         <v>1101016</v>
       </c>
-      <c r="B870" s="33">
+      <c r="B870" s="35">
         <v>1101</v>
       </c>
-      <c r="C870" s="33" t="s">
+      <c r="C870" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D870" s="33">
+      <c r="D870" s="35">
         <v>16</v>
       </c>
       <c r="E870" s="5"/>
-      <c r="F870" s="33" t="s">
+      <c r="F870" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G870" s="34">
+      <c r="G870" s="36">
         <v>1600</v>
       </c>
-      <c r="H870" s="34"/>
-      <c r="I870" s="34"/>
-      <c r="J870" s="34"/>
-      <c r="K870" s="35"/>
-      <c r="L870" s="36">
-        <v>600</v>
-      </c>
-      <c r="M870" s="37" t="s">
+      <c r="H870" s="36"/>
+      <c r="I870" s="36"/>
+      <c r="J870" s="36"/>
+      <c r="K870" s="37"/>
+      <c r="L870" s="38">
+        <v>600</v>
+      </c>
+      <c r="M870" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="871" s="6" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A871" s="33">
+      <c r="A871" s="35">
         <f t="shared" si="32"/>
         <v>1101017</v>
       </c>
-      <c r="B871" s="33">
+      <c r="B871" s="35">
         <v>1101</v>
       </c>
-      <c r="C871" s="33" t="s">
+      <c r="C871" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D871" s="33">
+      <c r="D871" s="35">
         <v>17</v>
       </c>
       <c r="E871" s="5"/>
-      <c r="F871" s="33" t="s">
+      <c r="F871" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G871" s="34">
+      <c r="G871" s="36">
         <v>1700</v>
       </c>
-      <c r="H871" s="34"/>
-      <c r="I871" s="34"/>
-      <c r="J871" s="34"/>
-      <c r="K871" s="35"/>
-      <c r="L871" s="36">
-        <v>600</v>
-      </c>
-      <c r="M871" s="37" t="s">
+      <c r="H871" s="36"/>
+      <c r="I871" s="36"/>
+      <c r="J871" s="36"/>
+      <c r="K871" s="37"/>
+      <c r="L871" s="38">
+        <v>600</v>
+      </c>
+      <c r="M871" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="872" s="6" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A872" s="33">
+      <c r="A872" s="35">
         <f t="shared" si="32"/>
         <v>1101018</v>
       </c>
-      <c r="B872" s="33">
+      <c r="B872" s="35">
         <v>1101</v>
       </c>
-      <c r="C872" s="33" t="s">
+      <c r="C872" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D872" s="33">
+      <c r="D872" s="35">
         <v>18</v>
       </c>
       <c r="E872" s="5"/>
-      <c r="F872" s="33" t="s">
+      <c r="F872" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G872" s="34">
+      <c r="G872" s="36">
         <v>1800</v>
       </c>
-      <c r="H872" s="34"/>
-      <c r="I872" s="34"/>
-      <c r="J872" s="34"/>
-      <c r="K872" s="35"/>
-      <c r="L872" s="36">
-        <v>600</v>
-      </c>
-      <c r="M872" s="37" t="s">
+      <c r="H872" s="36"/>
+      <c r="I872" s="36"/>
+      <c r="J872" s="36"/>
+      <c r="K872" s="37"/>
+      <c r="L872" s="38">
+        <v>600</v>
+      </c>
+      <c r="M872" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="873" s="6" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A873" s="33">
+      <c r="A873" s="35">
         <f t="shared" si="32"/>
         <v>1101019</v>
       </c>
-      <c r="B873" s="33">
+      <c r="B873" s="35">
         <v>1101</v>
       </c>
-      <c r="C873" s="33" t="s">
+      <c r="C873" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D873" s="33">
+      <c r="D873" s="35">
         <v>19</v>
       </c>
       <c r="E873" s="5"/>
-      <c r="F873" s="33" t="s">
+      <c r="F873" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G873" s="34">
+      <c r="G873" s="36">
         <v>1900</v>
       </c>
-      <c r="H873" s="34"/>
-      <c r="I873" s="34"/>
-      <c r="J873" s="34"/>
-      <c r="K873" s="35"/>
-      <c r="L873" s="36">
-        <v>600</v>
-      </c>
-      <c r="M873" s="37" t="s">
+      <c r="H873" s="36"/>
+      <c r="I873" s="36"/>
+      <c r="J873" s="36"/>
+      <c r="K873" s="37"/>
+      <c r="L873" s="38">
+        <v>600</v>
+      </c>
+      <c r="M873" s="39" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="874" s="6" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A874" s="33">
+      <c r="A874" s="35">
         <f t="shared" si="32"/>
         <v>1101020</v>
       </c>
-      <c r="B874" s="33">
+      <c r="B874" s="35">
         <v>1101</v>
       </c>
-      <c r="C874" s="33" t="s">
+      <c r="C874" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D874" s="33">
+      <c r="D874" s="35">
         <v>20</v>
       </c>
       <c r="E874" s="5"/>
-      <c r="F874" s="33" t="s">
+      <c r="F874" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G874" s="34">
+      <c r="G874" s="36">
         <v>2000</v>
       </c>
-      <c r="H874" s="34"/>
-      <c r="I874" s="34"/>
-      <c r="J874" s="34"/>
-      <c r="K874" s="35"/>
-      <c r="L874" s="36">
-        <v>600</v>
-      </c>
-      <c r="M874" s="37" t="s">
+      <c r="H874" s="36"/>
+      <c r="I874" s="36"/>
+      <c r="J874" s="36"/>
+      <c r="K874" s="37"/>
+      <c r="L874" s="38">
+        <v>600</v>
+      </c>
+      <c r="M874" s="39" t="s">
         <v>157</v>
       </c>
     </row>
@@ -33633,7 +33540,7 @@
       <c r="H875" s="2"/>
       <c r="I875" s="21"/>
       <c r="J875" s="21"/>
-      <c r="K875" s="22">
+      <c r="K875" s="25">
         <v>1303201</v>
       </c>
       <c r="L875" s="23">
@@ -33667,7 +33574,7 @@
       <c r="H876" s="2"/>
       <c r="I876" s="21"/>
       <c r="J876" s="21"/>
-      <c r="K876" s="22">
+      <c r="K876" s="25">
         <v>1303202</v>
       </c>
       <c r="L876" s="23">
@@ -33701,7 +33608,7 @@
       <c r="H877" s="2"/>
       <c r="I877" s="21"/>
       <c r="J877" s="21"/>
-      <c r="K877" s="22">
+      <c r="K877" s="25">
         <v>1303203</v>
       </c>
       <c r="L877" s="23">
@@ -33735,7 +33642,7 @@
       <c r="H878" s="2"/>
       <c r="I878" s="21"/>
       <c r="J878" s="21"/>
-      <c r="K878" s="22">
+      <c r="K878" s="25">
         <v>1303204</v>
       </c>
       <c r="L878" s="23">
@@ -33769,7 +33676,7 @@
       <c r="H879" s="2"/>
       <c r="I879" s="21"/>
       <c r="J879" s="21"/>
-      <c r="K879" s="22">
+      <c r="K879" s="25">
         <v>1303205</v>
       </c>
       <c r="L879" s="23">
@@ -33803,7 +33710,7 @@
       <c r="H880" s="2"/>
       <c r="I880" s="21"/>
       <c r="J880" s="21"/>
-      <c r="K880" s="22">
+      <c r="K880" s="25">
         <v>1303206</v>
       </c>
       <c r="L880" s="23">
@@ -33837,7 +33744,7 @@
       <c r="H881" s="2"/>
       <c r="I881" s="21"/>
       <c r="J881" s="21"/>
-      <c r="K881" s="22">
+      <c r="K881" s="25">
         <v>1303207</v>
       </c>
       <c r="L881" s="23">
@@ -33871,7 +33778,7 @@
       <c r="H882" s="2"/>
       <c r="I882" s="21"/>
       <c r="J882" s="21"/>
-      <c r="K882" s="22">
+      <c r="K882" s="25">
         <v>1303208</v>
       </c>
       <c r="L882" s="23">
@@ -33905,7 +33812,7 @@
       <c r="H883" s="2"/>
       <c r="I883" s="21"/>
       <c r="J883" s="21"/>
-      <c r="K883" s="22">
+      <c r="K883" s="25">
         <v>1303209</v>
       </c>
       <c r="L883" s="23">
@@ -33939,7 +33846,7 @@
       <c r="H884" s="2"/>
       <c r="I884" s="21"/>
       <c r="J884" s="21"/>
-      <c r="K884" s="22">
+      <c r="K884" s="25">
         <v>1303210</v>
       </c>
       <c r="L884" s="23">
@@ -33973,7 +33880,7 @@
       <c r="H885" s="2"/>
       <c r="I885" s="21"/>
       <c r="J885" s="21"/>
-      <c r="K885" s="22">
+      <c r="K885" s="25">
         <v>1303211</v>
       </c>
       <c r="L885" s="23">
@@ -34007,7 +33914,7 @@
       <c r="H886" s="2"/>
       <c r="I886" s="21"/>
       <c r="J886" s="21"/>
-      <c r="K886" s="22" t="s">
+      <c r="K886" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L886" s="23">
@@ -34041,7 +33948,7 @@
       <c r="H887" s="2"/>
       <c r="I887" s="21"/>
       <c r="J887" s="21"/>
-      <c r="K887" s="22" t="s">
+      <c r="K887" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L887" s="23">
@@ -34075,7 +33982,7 @@
       <c r="H888" s="2"/>
       <c r="I888" s="21"/>
       <c r="J888" s="21"/>
-      <c r="K888" s="22" t="s">
+      <c r="K888" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L888" s="23">
@@ -34109,7 +34016,7 @@
       <c r="H889" s="2"/>
       <c r="I889" s="21"/>
       <c r="J889" s="21"/>
-      <c r="K889" s="22" t="s">
+      <c r="K889" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L889" s="23">
@@ -34143,7 +34050,7 @@
       <c r="H890" s="2"/>
       <c r="I890" s="21"/>
       <c r="J890" s="21"/>
-      <c r="K890" s="22" t="s">
+      <c r="K890" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L890" s="23">
@@ -34177,7 +34084,7 @@
       <c r="H891" s="2"/>
       <c r="I891" s="21"/>
       <c r="J891" s="21"/>
-      <c r="K891" s="22" t="s">
+      <c r="K891" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L891" s="23">
@@ -34211,7 +34118,7 @@
       <c r="H892" s="2"/>
       <c r="I892" s="21"/>
       <c r="J892" s="21"/>
-      <c r="K892" s="22" t="s">
+      <c r="K892" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L892" s="23">
@@ -34245,7 +34152,7 @@
       <c r="H893" s="2"/>
       <c r="I893" s="21"/>
       <c r="J893" s="21"/>
-      <c r="K893" s="22" t="s">
+      <c r="K893" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L893" s="23">
@@ -34279,7 +34186,7 @@
       <c r="H894" s="2"/>
       <c r="I894" s="21"/>
       <c r="J894" s="21"/>
-      <c r="K894" s="22" t="s">
+      <c r="K894" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L894" s="23">
@@ -34313,7 +34220,7 @@
       <c r="H895" s="2"/>
       <c r="I895" s="21"/>
       <c r="J895" s="21"/>
-      <c r="K895" s="22" t="s">
+      <c r="K895" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L895" s="23">
@@ -34347,7 +34254,7 @@
       <c r="H896" s="2"/>
       <c r="I896" s="21"/>
       <c r="J896" s="21"/>
-      <c r="K896" s="22" t="s">
+      <c r="K896" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L896" s="23">
@@ -34381,7 +34288,7 @@
       <c r="H897" s="2"/>
       <c r="I897" s="21"/>
       <c r="J897" s="21"/>
-      <c r="K897" s="22" t="s">
+      <c r="K897" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L897" s="23">
@@ -34415,7 +34322,7 @@
       <c r="H898" s="2"/>
       <c r="I898" s="21"/>
       <c r="J898" s="21"/>
-      <c r="K898" s="22" t="s">
+      <c r="K898" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L898" s="23">
@@ -34449,7 +34356,7 @@
       <c r="H899" s="2"/>
       <c r="I899" s="21"/>
       <c r="J899" s="21"/>
-      <c r="K899" s="22" t="s">
+      <c r="K899" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L899" s="23">
@@ -34483,7 +34390,7 @@
       <c r="H900" s="2"/>
       <c r="I900" s="21"/>
       <c r="J900" s="21"/>
-      <c r="K900" s="22" t="s">
+      <c r="K900" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L900" s="23">
@@ -34517,7 +34424,7 @@
       <c r="H901" s="2"/>
       <c r="I901" s="21"/>
       <c r="J901" s="21"/>
-      <c r="K901" s="22" t="s">
+      <c r="K901" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L901" s="23">
@@ -34551,7 +34458,7 @@
       <c r="H902" s="2"/>
       <c r="I902" s="21"/>
       <c r="J902" s="21"/>
-      <c r="K902" s="22" t="s">
+      <c r="K902" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L902" s="23">
@@ -34585,7 +34492,7 @@
       <c r="H903" s="2"/>
       <c r="I903" s="21"/>
       <c r="J903" s="21"/>
-      <c r="K903" s="22" t="s">
+      <c r="K903" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L903" s="23">
@@ -34619,7 +34526,7 @@
       <c r="H904" s="2"/>
       <c r="I904" s="21"/>
       <c r="J904" s="21"/>
-      <c r="K904" s="22" t="s">
+      <c r="K904" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L904" s="23">
@@ -34653,7 +34560,7 @@
       <c r="H905" s="2"/>
       <c r="I905" s="21"/>
       <c r="J905" s="21"/>
-      <c r="K905" s="22" t="s">
+      <c r="K905" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L905" s="23">
@@ -34687,7 +34594,7 @@
       <c r="H906" s="2"/>
       <c r="I906" s="21"/>
       <c r="J906" s="21"/>
-      <c r="K906" s="22" t="s">
+      <c r="K906" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L906" s="23">
@@ -34721,7 +34628,7 @@
       <c r="H907" s="2"/>
       <c r="I907" s="21"/>
       <c r="J907" s="21"/>
-      <c r="K907" s="22" t="s">
+      <c r="K907" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L907" s="23">
@@ -34755,7 +34662,7 @@
       <c r="H908" s="2"/>
       <c r="I908" s="21"/>
       <c r="J908" s="21"/>
-      <c r="K908" s="22" t="s">
+      <c r="K908" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L908" s="23">
@@ -34789,7 +34696,7 @@
       <c r="H909" s="2"/>
       <c r="I909" s="21"/>
       <c r="J909" s="21"/>
-      <c r="K909" s="22" t="s">
+      <c r="K909" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L909" s="23">
@@ -34823,7 +34730,7 @@
       <c r="H910" s="2"/>
       <c r="I910" s="21"/>
       <c r="J910" s="21"/>
-      <c r="K910" s="22" t="s">
+      <c r="K910" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L910" s="23">
@@ -34857,7 +34764,7 @@
       <c r="H911" s="2"/>
       <c r="I911" s="21"/>
       <c r="J911" s="21"/>
-      <c r="K911" s="22" t="s">
+      <c r="K911" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L911" s="23">
@@ -34891,7 +34798,7 @@
       <c r="H912" s="2"/>
       <c r="I912" s="21"/>
       <c r="J912" s="21"/>
-      <c r="K912" s="22" t="s">
+      <c r="K912" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L912" s="23">
@@ -34925,7 +34832,7 @@
       <c r="H913" s="2"/>
       <c r="I913" s="21"/>
       <c r="J913" s="21"/>
-      <c r="K913" s="22" t="s">
+      <c r="K913" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L913" s="23">
@@ -34959,7 +34866,7 @@
       <c r="H914" s="2"/>
       <c r="I914" s="21"/>
       <c r="J914" s="21"/>
-      <c r="K914" s="22" t="s">
+      <c r="K914" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L914" s="23">
@@ -34993,7 +34900,7 @@
       <c r="H915" s="2"/>
       <c r="I915" s="21"/>
       <c r="J915" s="21"/>
-      <c r="K915" s="22" t="s">
+      <c r="K915" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L915" s="23">
@@ -35027,7 +34934,7 @@
       <c r="H916" s="2"/>
       <c r="I916" s="21"/>
       <c r="J916" s="21"/>
-      <c r="K916" s="22" t="s">
+      <c r="K916" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L916" s="23">
@@ -35061,7 +34968,7 @@
       <c r="H917" s="2"/>
       <c r="I917" s="21"/>
       <c r="J917" s="21"/>
-      <c r="K917" s="22" t="s">
+      <c r="K917" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L917" s="23">
@@ -35095,7 +35002,7 @@
       <c r="H918" s="2"/>
       <c r="I918" s="21"/>
       <c r="J918" s="21"/>
-      <c r="K918" s="22" t="s">
+      <c r="K918" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L918" s="23">
@@ -35129,7 +35036,7 @@
       <c r="H919" s="2"/>
       <c r="I919" s="21"/>
       <c r="J919" s="21"/>
-      <c r="K919" s="22" t="s">
+      <c r="K919" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L919" s="23">
@@ -35163,7 +35070,7 @@
       <c r="H920" s="2"/>
       <c r="I920" s="21"/>
       <c r="J920" s="21"/>
-      <c r="K920" s="22" t="s">
+      <c r="K920" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L920" s="23">
@@ -35197,7 +35104,7 @@
       <c r="H921" s="2"/>
       <c r="I921" s="21"/>
       <c r="J921" s="21"/>
-      <c r="K921" s="22" t="s">
+      <c r="K921" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L921" s="23">
@@ -35231,7 +35138,7 @@
       <c r="H922" s="2"/>
       <c r="I922" s="21"/>
       <c r="J922" s="21"/>
-      <c r="K922" s="22" t="s">
+      <c r="K922" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L922" s="23">
@@ -35265,7 +35172,7 @@
       <c r="H923" s="2"/>
       <c r="I923" s="21"/>
       <c r="J923" s="21"/>
-      <c r="K923" s="22" t="s">
+      <c r="K923" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L923" s="23">
@@ -35299,7 +35206,7 @@
       <c r="H924" s="2"/>
       <c r="I924" s="21"/>
       <c r="J924" s="21"/>
-      <c r="K924" s="22" t="s">
+      <c r="K924" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L924" s="23">
@@ -35333,7 +35240,7 @@
       <c r="H925" s="2"/>
       <c r="I925" s="21"/>
       <c r="J925" s="21"/>
-      <c r="K925" s="22" t="s">
+      <c r="K925" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L925" s="23">
@@ -35367,7 +35274,7 @@
       <c r="H926" s="2"/>
       <c r="I926" s="21"/>
       <c r="J926" s="21"/>
-      <c r="K926" s="22" t="s">
+      <c r="K926" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L926" s="23">
@@ -35401,7 +35308,7 @@
       <c r="H927" s="2"/>
       <c r="I927" s="21"/>
       <c r="J927" s="21"/>
-      <c r="K927" s="22" t="s">
+      <c r="K927" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L927" s="23">
@@ -35435,7 +35342,7 @@
       <c r="H928" s="2"/>
       <c r="I928" s="21"/>
       <c r="J928" s="21"/>
-      <c r="K928" s="22" t="s">
+      <c r="K928" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L928" s="23">
@@ -35469,7 +35376,7 @@
       <c r="H929" s="2"/>
       <c r="I929" s="21"/>
       <c r="J929" s="21"/>
-      <c r="K929" s="22" t="s">
+      <c r="K929" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L929" s="23">
@@ -35503,7 +35410,7 @@
       <c r="H930" s="2"/>
       <c r="I930" s="21"/>
       <c r="J930" s="21"/>
-      <c r="K930" s="22" t="s">
+      <c r="K930" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L930" s="23">
@@ -35537,7 +35444,7 @@
       <c r="H931" s="2"/>
       <c r="I931" s="21"/>
       <c r="J931" s="21"/>
-      <c r="K931" s="22" t="s">
+      <c r="K931" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L931" s="23">
@@ -35571,7 +35478,7 @@
       <c r="H932" s="2"/>
       <c r="I932" s="21"/>
       <c r="J932" s="21"/>
-      <c r="K932" s="22" t="s">
+      <c r="K932" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L932" s="23">
@@ -35605,7 +35512,7 @@
       <c r="H933" s="2"/>
       <c r="I933" s="21"/>
       <c r="J933" s="21"/>
-      <c r="K933" s="22" t="s">
+      <c r="K933" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L933" s="23">
@@ -35639,7 +35546,7 @@
       <c r="H934" s="2"/>
       <c r="I934" s="21"/>
       <c r="J934" s="21"/>
-      <c r="K934" s="22" t="s">
+      <c r="K934" s="25" t="s">
         <v>63</v>
       </c>
       <c r="L934" s="23"/>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -32787,7 +32787,7 @@
         <v>4030001</v>
       </c>
       <c r="I852" s="31">
-        <v>103700</v>
+        <v>101200</v>
       </c>
       <c r="J852" s="31"/>
       <c r="K852" s="34" t="s">

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3680" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="163">
   <si>
     <t>ID</t>
   </si>
@@ -711,28 +711,37 @@
     <t>接待区</t>
   </si>
   <si>
-    <t>研发部</t>
+    <t>研发部&amp;游戏厅</t>
   </si>
   <si>
-    <t>1302204_1302211</t>
+    <t>1302251_1302252_1302268</t>
   </si>
   <si>
-    <t>1302205_1302212</t>
+    <t>1302253_1302269</t>
   </si>
   <si>
-    <t>1302206_1302213</t>
+    <t>1302254_1302270</t>
   </si>
   <si>
-    <t>1302207_1302214</t>
+    <t>1302255_1302256_1302271</t>
   </si>
   <si>
-    <t>1302208_1302215</t>
+    <t>1302257_1302258_1302272</t>
   </si>
   <si>
-    <t>1302209_1302216</t>
+    <t>1302259_1302260_1302273</t>
   </si>
   <si>
-    <t>1302210_1302217</t>
+    <t>1302261_1302262_1302274</t>
+  </si>
+  <si>
+    <t>1302263_1302275</t>
+  </si>
+  <si>
+    <t>1302264_1302276</t>
+  </si>
+  <si>
+    <t>1302265_1302266_1302267_1302277</t>
   </si>
   <si>
     <t>富贵厅</t>
@@ -32488,9 +32497,7 @@
       </c>
       <c r="I844" s="21"/>
       <c r="J844" s="21"/>
-      <c r="K844" s="25" t="s">
-        <v>63</v>
-      </c>
+      <c r="K844" s="25"/>
       <c r="L844" s="23"/>
       <c r="M844" s="24" t="s">
         <v>33</v>
@@ -32524,8 +32531,8 @@
         <v>100300</v>
       </c>
       <c r="J845" s="31"/>
-      <c r="K845" s="32">
-        <v>1302201</v>
+      <c r="K845" s="32" t="s">
+        <v>148</v>
       </c>
       <c r="L845" s="32">
         <v>10</v>
@@ -32559,11 +32566,11 @@
         <v>4030001</v>
       </c>
       <c r="I846" s="31">
-        <v>103400</v>
+        <v>101200</v>
       </c>
       <c r="J846" s="31"/>
-      <c r="K846" s="32">
-        <v>1302202</v>
+      <c r="K846" s="32" t="s">
+        <v>149</v>
       </c>
       <c r="L846" s="32">
         <v>30</v>
@@ -32597,11 +32604,11 @@
         <v>4030001</v>
       </c>
       <c r="I847" s="31">
-        <v>103401</v>
+        <v>100700</v>
       </c>
       <c r="J847" s="31"/>
-      <c r="K847" s="32">
-        <v>1302203</v>
+      <c r="K847" s="32" t="s">
+        <v>150</v>
       </c>
       <c r="L847" s="32">
         <v>60</v>
@@ -32635,11 +32642,11 @@
         <v>4030001</v>
       </c>
       <c r="I848" s="31">
-        <v>101400</v>
+        <v>101800</v>
       </c>
       <c r="J848" s="31"/>
       <c r="K848" s="34" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L848" s="32">
         <v>90</v>
@@ -32673,11 +32680,11 @@
         <v>4030001</v>
       </c>
       <c r="I849" s="31">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="J849" s="31"/>
       <c r="K849" s="34" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L849" s="32">
         <v>120</v>
@@ -32711,11 +32718,11 @@
         <v>4030001</v>
       </c>
       <c r="I850" s="31">
-        <v>103501</v>
+        <v>103100</v>
       </c>
       <c r="J850" s="31"/>
       <c r="K850" s="34" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L850" s="32">
         <v>150</v>
@@ -32749,11 +32756,11 @@
         <v>4030001</v>
       </c>
       <c r="I851" s="31">
-        <v>100700</v>
+        <v>102200</v>
       </c>
       <c r="J851" s="31"/>
       <c r="K851" s="34" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L851" s="32">
         <v>180</v>
@@ -32787,11 +32794,11 @@
         <v>4030001</v>
       </c>
       <c r="I852" s="31">
-        <v>101200</v>
+        <v>102100</v>
       </c>
       <c r="J852" s="31"/>
       <c r="K852" s="34" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L852" s="32">
         <v>210</v>
@@ -32825,11 +32832,11 @@
         <v>4030001</v>
       </c>
       <c r="I853" s="31">
-        <v>103600</v>
+        <v>101600</v>
       </c>
       <c r="J853" s="31"/>
       <c r="K853" s="34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L853" s="32">
         <v>240</v>
@@ -32863,11 +32870,11 @@
         <v>4030001</v>
       </c>
       <c r="I854" s="31">
-        <v>101700</v>
+        <v>102000</v>
       </c>
       <c r="J854" s="31"/>
       <c r="K854" s="34" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L854" s="32">
         <v>300</v>
@@ -32885,14 +32892,14 @@
         <v>1101</v>
       </c>
       <c r="C855" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D855" s="35">
         <v>1</v>
       </c>
       <c r="E855" s="5"/>
       <c r="F855" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G855" s="36">
         <v>100</v>
@@ -32905,7 +32912,7 @@
         <v>5</v>
       </c>
       <c r="M855" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="856" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32917,14 +32924,14 @@
         <v>1101</v>
       </c>
       <c r="C856" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D856" s="35">
         <v>2</v>
       </c>
       <c r="E856" s="5"/>
       <c r="F856" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G856" s="36">
         <v>200</v>
@@ -32937,7 +32944,7 @@
         <v>10</v>
       </c>
       <c r="M856" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="857" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32949,14 +32956,14 @@
         <v>1101</v>
       </c>
       <c r="C857" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D857" s="35">
         <v>3</v>
       </c>
       <c r="E857" s="5"/>
       <c r="F857" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G857" s="36">
         <v>300</v>
@@ -32969,7 +32976,7 @@
         <v>20</v>
       </c>
       <c r="M857" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="858" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32981,14 +32988,14 @@
         <v>1101</v>
       </c>
       <c r="C858" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D858" s="35">
         <v>4</v>
       </c>
       <c r="E858" s="5"/>
       <c r="F858" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G858" s="36">
         <v>400</v>
@@ -33001,7 +33008,7 @@
         <v>30</v>
       </c>
       <c r="M858" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="859" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33013,14 +33020,14 @@
         <v>1101</v>
       </c>
       <c r="C859" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D859" s="35">
         <v>5</v>
       </c>
       <c r="E859" s="5"/>
       <c r="F859" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G859" s="36">
         <v>500</v>
@@ -33033,7 +33040,7 @@
         <v>60</v>
       </c>
       <c r="M859" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="860" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33045,14 +33052,14 @@
         <v>1101</v>
       </c>
       <c r="C860" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D860" s="35">
         <v>6</v>
       </c>
       <c r="E860" s="5"/>
       <c r="F860" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G860" s="36">
         <v>600</v>
@@ -33065,7 +33072,7 @@
         <v>80</v>
       </c>
       <c r="M860" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="861" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33077,14 +33084,14 @@
         <v>1101</v>
       </c>
       <c r="C861" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D861" s="35">
         <v>7</v>
       </c>
       <c r="E861" s="5"/>
       <c r="F861" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G861" s="36">
         <v>700</v>
@@ -33097,7 +33104,7 @@
         <v>120</v>
       </c>
       <c r="M861" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="862" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33109,14 +33116,14 @@
         <v>1101</v>
       </c>
       <c r="C862" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D862" s="35">
         <v>8</v>
       </c>
       <c r="E862" s="5"/>
       <c r="F862" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G862" s="36">
         <v>800</v>
@@ -33129,7 +33136,7 @@
         <v>150</v>
       </c>
       <c r="M862" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="863" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33141,14 +33148,14 @@
         <v>1101</v>
       </c>
       <c r="C863" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D863" s="35">
         <v>9</v>
       </c>
       <c r="E863" s="5"/>
       <c r="F863" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G863" s="36">
         <v>900</v>
@@ -33161,7 +33168,7 @@
         <v>200</v>
       </c>
       <c r="M863" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="864" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33173,14 +33180,14 @@
         <v>1101</v>
       </c>
       <c r="C864" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D864" s="35">
         <v>10</v>
       </c>
       <c r="E864" s="5"/>
       <c r="F864" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G864" s="36">
         <v>1000</v>
@@ -33193,7 +33200,7 @@
         <v>300</v>
       </c>
       <c r="M864" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="865" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33205,14 +33212,14 @@
         <v>1101</v>
       </c>
       <c r="C865" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D865" s="35">
         <v>11</v>
       </c>
       <c r="E865" s="5"/>
       <c r="F865" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G865" s="36">
         <v>1100</v>
@@ -33225,7 +33232,7 @@
         <v>360</v>
       </c>
       <c r="M865" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="866" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33237,14 +33244,14 @@
         <v>1101</v>
       </c>
       <c r="C866" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D866" s="35">
         <v>12</v>
       </c>
       <c r="E866" s="5"/>
       <c r="F866" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G866" s="36">
         <v>1200</v>
@@ -33257,7 +33264,7 @@
         <v>420</v>
       </c>
       <c r="M866" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="867" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33269,14 +33276,14 @@
         <v>1101</v>
       </c>
       <c r="C867" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D867" s="35">
         <v>13</v>
       </c>
       <c r="E867" s="5"/>
       <c r="F867" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G867" s="36">
         <v>1300</v>
@@ -33289,7 +33296,7 @@
         <v>480</v>
       </c>
       <c r="M867" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="868" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33301,14 +33308,14 @@
         <v>1101</v>
       </c>
       <c r="C868" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D868" s="35">
         <v>14</v>
       </c>
       <c r="E868" s="5"/>
       <c r="F868" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G868" s="36">
         <v>1400</v>
@@ -33321,7 +33328,7 @@
         <v>540</v>
       </c>
       <c r="M868" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="869" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33333,14 +33340,14 @@
         <v>1101</v>
       </c>
       <c r="C869" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D869" s="35">
         <v>15</v>
       </c>
       <c r="E869" s="5"/>
       <c r="F869" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G869" s="36">
         <v>1500</v>
@@ -33353,7 +33360,7 @@
         <v>600</v>
       </c>
       <c r="M869" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="870" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -33365,14 +33372,14 @@
         <v>1101</v>
       </c>
       <c r="C870" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D870" s="35">
         <v>16</v>
       </c>
       <c r="E870" s="5"/>
       <c r="F870" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G870" s="36">
         <v>1600</v>
@@ -33385,7 +33392,7 @@
         <v>600</v>
       </c>
       <c r="M870" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="871" s="6" customFormat="1" customHeight="1" spans="1:13">
@@ -33397,14 +33404,14 @@
         <v>1101</v>
       </c>
       <c r="C871" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D871" s="35">
         <v>17</v>
       </c>
       <c r="E871" s="5"/>
       <c r="F871" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G871" s="36">
         <v>1700</v>
@@ -33417,7 +33424,7 @@
         <v>600</v>
       </c>
       <c r="M871" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="872" s="6" customFormat="1" customHeight="1" spans="1:13">
@@ -33429,14 +33436,14 @@
         <v>1101</v>
       </c>
       <c r="C872" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D872" s="35">
         <v>18</v>
       </c>
       <c r="E872" s="5"/>
       <c r="F872" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G872" s="36">
         <v>1800</v>
@@ -33449,7 +33456,7 @@
         <v>600</v>
       </c>
       <c r="M872" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="873" s="6" customFormat="1" customHeight="1" spans="1:13">
@@ -33461,14 +33468,14 @@
         <v>1101</v>
       </c>
       <c r="C873" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D873" s="35">
         <v>19</v>
       </c>
       <c r="E873" s="5"/>
       <c r="F873" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G873" s="36">
         <v>1900</v>
@@ -33481,7 +33488,7 @@
         <v>600</v>
       </c>
       <c r="M873" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="874" s="6" customFormat="1" customHeight="1" spans="1:13">
@@ -33493,14 +33500,14 @@
         <v>1101</v>
       </c>
       <c r="C874" s="35" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D874" s="35">
         <v>20</v>
       </c>
       <c r="E874" s="5"/>
       <c r="F874" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G874" s="36">
         <v>2000</v>
@@ -33513,7 +33520,7 @@
         <v>600</v>
       </c>
       <c r="M874" s="39" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="875" s="2" customFormat="1" customHeight="1" spans="1:13">
@@ -33525,7 +33532,7 @@
         <v>1303</v>
       </c>
       <c r="C875" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D875" s="20">
         <v>1</v>
@@ -33559,7 +33566,7 @@
         <v>1303</v>
       </c>
       <c r="C876" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D876" s="20">
         <v>2</v>
@@ -33593,7 +33600,7 @@
         <v>1303</v>
       </c>
       <c r="C877" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D877" s="20">
         <v>3</v>
@@ -33627,7 +33634,7 @@
         <v>1303</v>
       </c>
       <c r="C878" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D878" s="20">
         <v>4</v>
@@ -33661,7 +33668,7 @@
         <v>1303</v>
       </c>
       <c r="C879" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D879" s="20">
         <v>5</v>
@@ -33695,7 +33702,7 @@
         <v>1303</v>
       </c>
       <c r="C880" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D880" s="20">
         <v>6</v>
@@ -33729,7 +33736,7 @@
         <v>1303</v>
       </c>
       <c r="C881" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D881" s="20">
         <v>7</v>
@@ -33763,7 +33770,7 @@
         <v>1303</v>
       </c>
       <c r="C882" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D882" s="20">
         <v>8</v>
@@ -33797,7 +33804,7 @@
         <v>1303</v>
       </c>
       <c r="C883" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D883" s="20">
         <v>9</v>
@@ -33831,7 +33838,7 @@
         <v>1303</v>
       </c>
       <c r="C884" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D884" s="20">
         <v>10</v>
@@ -33865,7 +33872,7 @@
         <v>1303</v>
       </c>
       <c r="C885" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D885" s="20">
         <v>11</v>
@@ -33899,7 +33906,7 @@
         <v>1303</v>
       </c>
       <c r="C886" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D886" s="20">
         <v>12</v>
@@ -33933,7 +33940,7 @@
         <v>1303</v>
       </c>
       <c r="C887" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D887" s="20">
         <v>13</v>
@@ -33967,7 +33974,7 @@
         <v>1303</v>
       </c>
       <c r="C888" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D888" s="20">
         <v>14</v>
@@ -34001,7 +34008,7 @@
         <v>1303</v>
       </c>
       <c r="C889" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D889" s="20">
         <v>15</v>
@@ -34035,7 +34042,7 @@
         <v>1303</v>
       </c>
       <c r="C890" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D890" s="20">
         <v>16</v>
@@ -34069,7 +34076,7 @@
         <v>1303</v>
       </c>
       <c r="C891" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D891" s="20">
         <v>17</v>
@@ -34103,7 +34110,7 @@
         <v>1303</v>
       </c>
       <c r="C892" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D892" s="20">
         <v>18</v>
@@ -34137,7 +34144,7 @@
         <v>1303</v>
       </c>
       <c r="C893" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D893" s="20">
         <v>19</v>
@@ -34171,7 +34178,7 @@
         <v>1303</v>
       </c>
       <c r="C894" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D894" s="20">
         <v>20</v>
@@ -34205,7 +34212,7 @@
         <v>1303</v>
       </c>
       <c r="C895" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D895" s="20">
         <v>21</v>
@@ -34239,7 +34246,7 @@
         <v>1303</v>
       </c>
       <c r="C896" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D896" s="20">
         <v>22</v>
@@ -34273,7 +34280,7 @@
         <v>1303</v>
       </c>
       <c r="C897" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D897" s="20">
         <v>23</v>
@@ -34307,7 +34314,7 @@
         <v>1303</v>
       </c>
       <c r="C898" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D898" s="20">
         <v>24</v>
@@ -34341,7 +34348,7 @@
         <v>1303</v>
       </c>
       <c r="C899" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D899" s="20">
         <v>25</v>
@@ -34375,7 +34382,7 @@
         <v>1303</v>
       </c>
       <c r="C900" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D900" s="20">
         <v>26</v>
@@ -34409,7 +34416,7 @@
         <v>1303</v>
       </c>
       <c r="C901" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D901" s="20">
         <v>27</v>
@@ -34443,7 +34450,7 @@
         <v>1303</v>
       </c>
       <c r="C902" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D902" s="20">
         <v>28</v>
@@ -34477,7 +34484,7 @@
         <v>1303</v>
       </c>
       <c r="C903" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D903" s="20">
         <v>29</v>
@@ -34511,7 +34518,7 @@
         <v>1303</v>
       </c>
       <c r="C904" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D904" s="20">
         <v>30</v>
@@ -34545,7 +34552,7 @@
         <v>1303</v>
       </c>
       <c r="C905" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D905" s="20">
         <v>31</v>
@@ -34579,7 +34586,7 @@
         <v>1303</v>
       </c>
       <c r="C906" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D906" s="20">
         <v>32</v>
@@ -34613,7 +34620,7 @@
         <v>1303</v>
       </c>
       <c r="C907" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D907" s="20">
         <v>33</v>
@@ -34647,7 +34654,7 @@
         <v>1303</v>
       </c>
       <c r="C908" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D908" s="20">
         <v>34</v>
@@ -34681,7 +34688,7 @@
         <v>1303</v>
       </c>
       <c r="C909" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D909" s="20">
         <v>35</v>
@@ -34715,7 +34722,7 @@
         <v>1303</v>
       </c>
       <c r="C910" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D910" s="20">
         <v>36</v>
@@ -34749,7 +34756,7 @@
         <v>1303</v>
       </c>
       <c r="C911" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D911" s="20">
         <v>37</v>
@@ -34783,7 +34790,7 @@
         <v>1303</v>
       </c>
       <c r="C912" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D912" s="20">
         <v>38</v>
@@ -34817,7 +34824,7 @@
         <v>1303</v>
       </c>
       <c r="C913" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D913" s="20">
         <v>39</v>
@@ -34851,7 +34858,7 @@
         <v>1303</v>
       </c>
       <c r="C914" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D914" s="20">
         <v>40</v>
@@ -34885,7 +34892,7 @@
         <v>1303</v>
       </c>
       <c r="C915" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D915" s="20">
         <v>41</v>
@@ -34919,7 +34926,7 @@
         <v>1303</v>
       </c>
       <c r="C916" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D916" s="20">
         <v>42</v>
@@ -34953,7 +34960,7 @@
         <v>1303</v>
       </c>
       <c r="C917" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D917" s="20">
         <v>43</v>
@@ -34987,7 +34994,7 @@
         <v>1303</v>
       </c>
       <c r="C918" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D918" s="20">
         <v>44</v>
@@ -35021,7 +35028,7 @@
         <v>1303</v>
       </c>
       <c r="C919" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D919" s="20">
         <v>45</v>
@@ -35055,7 +35062,7 @@
         <v>1303</v>
       </c>
       <c r="C920" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D920" s="20">
         <v>46</v>
@@ -35089,7 +35096,7 @@
         <v>1303</v>
       </c>
       <c r="C921" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D921" s="20">
         <v>47</v>
@@ -35123,7 +35130,7 @@
         <v>1303</v>
       </c>
       <c r="C922" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D922" s="20">
         <v>48</v>
@@ -35157,7 +35164,7 @@
         <v>1303</v>
       </c>
       <c r="C923" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D923" s="20">
         <v>49</v>
@@ -35191,7 +35198,7 @@
         <v>1303</v>
       </c>
       <c r="C924" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D924" s="20">
         <v>50</v>
@@ -35225,7 +35232,7 @@
         <v>1303</v>
       </c>
       <c r="C925" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D925" s="20">
         <v>51</v>
@@ -35259,7 +35266,7 @@
         <v>1303</v>
       </c>
       <c r="C926" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D926" s="20">
         <v>52</v>
@@ -35293,7 +35300,7 @@
         <v>1303</v>
       </c>
       <c r="C927" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D927" s="20">
         <v>53</v>
@@ -35327,7 +35334,7 @@
         <v>1303</v>
       </c>
       <c r="C928" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D928" s="20">
         <v>54</v>
@@ -35361,7 +35368,7 @@
         <v>1303</v>
       </c>
       <c r="C929" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D929" s="20">
         <v>55</v>
@@ -35395,7 +35402,7 @@
         <v>1303</v>
       </c>
       <c r="C930" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D930" s="20">
         <v>56</v>
@@ -35429,7 +35436,7 @@
         <v>1303</v>
       </c>
       <c r="C931" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D931" s="20">
         <v>57</v>
@@ -35463,7 +35470,7 @@
         <v>1303</v>
       </c>
       <c r="C932" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D932" s="20">
         <v>58</v>
@@ -35497,7 +35504,7 @@
         <v>1303</v>
       </c>
       <c r="C933" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D933" s="20">
         <v>59</v>
@@ -35531,7 +35538,7 @@
         <v>1303</v>
       </c>
       <c r="C934" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D934" s="20">
         <v>60</v>
@@ -35563,7 +35570,7 @@
         <v>1304</v>
       </c>
       <c r="C935" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D935" s="16">
         <v>1</v>
@@ -35593,7 +35600,7 @@
         <v>1304</v>
       </c>
       <c r="C936" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D936" s="16">
         <v>2</v>
@@ -35623,7 +35630,7 @@
         <v>1304</v>
       </c>
       <c r="C937" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D937" s="16">
         <v>3</v>
@@ -35653,7 +35660,7 @@
         <v>1304</v>
       </c>
       <c r="C938" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D938" s="16">
         <v>4</v>
@@ -35683,7 +35690,7 @@
         <v>1304</v>
       </c>
       <c r="C939" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D939" s="16">
         <v>5</v>
@@ -35713,7 +35720,7 @@
         <v>1304</v>
       </c>
       <c r="C940" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D940" s="16">
         <v>6</v>
@@ -35743,7 +35750,7 @@
         <v>1304</v>
       </c>
       <c r="C941" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D941" s="16">
         <v>7</v>
@@ -35773,7 +35780,7 @@
         <v>1304</v>
       </c>
       <c r="C942" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D942" s="16">
         <v>8</v>
@@ -35803,7 +35810,7 @@
         <v>1304</v>
       </c>
       <c r="C943" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D943" s="16">
         <v>9</v>
@@ -35833,7 +35840,7 @@
         <v>1304</v>
       </c>
       <c r="C944" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D944" s="16">
         <v>10</v>
@@ -35863,7 +35870,7 @@
         <v>1304</v>
       </c>
       <c r="C945" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D945" s="16">
         <v>11</v>
@@ -35893,7 +35900,7 @@
         <v>1304</v>
       </c>
       <c r="C946" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D946" s="16">
         <v>12</v>
@@ -35923,7 +35930,7 @@
         <v>1304</v>
       </c>
       <c r="C947" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D947" s="16">
         <v>13</v>
@@ -35953,7 +35960,7 @@
         <v>1304</v>
       </c>
       <c r="C948" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D948" s="16">
         <v>14</v>
@@ -35983,7 +35990,7 @@
         <v>1304</v>
       </c>
       <c r="C949" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D949" s="16">
         <v>15</v>
@@ -36013,7 +36020,7 @@
         <v>1304</v>
       </c>
       <c r="C950" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D950" s="16">
         <v>16</v>
@@ -36043,7 +36050,7 @@
         <v>1304</v>
       </c>
       <c r="C951" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D951" s="16">
         <v>17</v>
@@ -36073,7 +36080,7 @@
         <v>1304</v>
       </c>
       <c r="C952" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D952" s="16">
         <v>18</v>
@@ -36103,7 +36110,7 @@
         <v>1304</v>
       </c>
       <c r="C953" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D953" s="16">
         <v>19</v>
@@ -36133,7 +36140,7 @@
         <v>1304</v>
       </c>
       <c r="C954" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D954" s="16">
         <v>20</v>
@@ -36163,7 +36170,7 @@
         <v>1304</v>
       </c>
       <c r="C955" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D955" s="16">
         <v>21</v>
@@ -36193,7 +36200,7 @@
         <v>1304</v>
       </c>
       <c r="C956" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D956" s="16">
         <v>22</v>
@@ -36223,7 +36230,7 @@
         <v>1304</v>
       </c>
       <c r="C957" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D957" s="16">
         <v>23</v>
@@ -36253,7 +36260,7 @@
         <v>1304</v>
       </c>
       <c r="C958" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D958" s="16">
         <v>24</v>
@@ -36283,7 +36290,7 @@
         <v>1304</v>
       </c>
       <c r="C959" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D959" s="16">
         <v>25</v>
@@ -36313,7 +36320,7 @@
         <v>1304</v>
       </c>
       <c r="C960" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D960" s="16">
         <v>26</v>
@@ -36343,7 +36350,7 @@
         <v>1304</v>
       </c>
       <c r="C961" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D961" s="16">
         <v>27</v>
@@ -36373,7 +36380,7 @@
         <v>1304</v>
       </c>
       <c r="C962" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D962" s="16">
         <v>28</v>
@@ -36403,7 +36410,7 @@
         <v>1304</v>
       </c>
       <c r="C963" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D963" s="16">
         <v>29</v>
@@ -36433,7 +36440,7 @@
         <v>1304</v>
       </c>
       <c r="C964" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D964" s="16">
         <v>30</v>
@@ -36463,7 +36470,7 @@
         <v>1304</v>
       </c>
       <c r="C965" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D965" s="16">
         <v>31</v>
@@ -36493,7 +36500,7 @@
         <v>1304</v>
       </c>
       <c r="C966" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D966" s="16">
         <v>32</v>
@@ -36523,7 +36530,7 @@
         <v>1304</v>
       </c>
       <c r="C967" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D967" s="16">
         <v>33</v>
@@ -36553,7 +36560,7 @@
         <v>1304</v>
       </c>
       <c r="C968" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D968" s="16">
         <v>34</v>
@@ -36583,7 +36590,7 @@
         <v>1304</v>
       </c>
       <c r="C969" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D969" s="16">
         <v>35</v>
@@ -36613,7 +36620,7 @@
         <v>1304</v>
       </c>
       <c r="C970" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D970" s="16">
         <v>36</v>
@@ -36643,7 +36650,7 @@
         <v>1304</v>
       </c>
       <c r="C971" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D971" s="16">
         <v>37</v>
@@ -36673,7 +36680,7 @@
         <v>1304</v>
       </c>
       <c r="C972" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D972" s="16">
         <v>38</v>
@@ -36703,7 +36710,7 @@
         <v>1304</v>
       </c>
       <c r="C973" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D973" s="16">
         <v>39</v>
@@ -36733,7 +36740,7 @@
         <v>1304</v>
       </c>
       <c r="C974" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D974" s="16">
         <v>40</v>
@@ -36763,7 +36770,7 @@
         <v>1304</v>
       </c>
       <c r="C975" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D975" s="16">
         <v>41</v>
@@ -36793,7 +36800,7 @@
         <v>1304</v>
       </c>
       <c r="C976" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D976" s="16">
         <v>42</v>
@@ -36823,7 +36830,7 @@
         <v>1304</v>
       </c>
       <c r="C977" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D977" s="16">
         <v>43</v>
@@ -36853,7 +36860,7 @@
         <v>1304</v>
       </c>
       <c r="C978" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D978" s="16">
         <v>44</v>
@@ -36883,7 +36890,7 @@
         <v>1304</v>
       </c>
       <c r="C979" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D979" s="16">
         <v>45</v>
@@ -36913,7 +36920,7 @@
         <v>1304</v>
       </c>
       <c r="C980" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D980" s="16">
         <v>46</v>
@@ -36943,7 +36950,7 @@
         <v>1304</v>
       </c>
       <c r="C981" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D981" s="16">
         <v>47</v>
@@ -36973,7 +36980,7 @@
         <v>1304</v>
       </c>
       <c r="C982" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D982" s="16">
         <v>48</v>
@@ -37003,7 +37010,7 @@
         <v>1304</v>
       </c>
       <c r="C983" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D983" s="16">
         <v>49</v>
@@ -37033,7 +37040,7 @@
         <v>1304</v>
       </c>
       <c r="C984" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D984" s="16">
         <v>50</v>
@@ -37063,7 +37070,7 @@
         <v>1304</v>
       </c>
       <c r="C985" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D985" s="16">
         <v>51</v>
@@ -37093,7 +37100,7 @@
         <v>1304</v>
       </c>
       <c r="C986" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D986" s="16">
         <v>52</v>
@@ -37123,7 +37130,7 @@
         <v>1304</v>
       </c>
       <c r="C987" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D987" s="16">
         <v>53</v>
@@ -37153,7 +37160,7 @@
         <v>1304</v>
       </c>
       <c r="C988" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D988" s="16">
         <v>54</v>
@@ -37183,7 +37190,7 @@
         <v>1304</v>
       </c>
       <c r="C989" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D989" s="16">
         <v>55</v>
@@ -37213,7 +37220,7 @@
         <v>1304</v>
       </c>
       <c r="C990" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D990" s="16">
         <v>56</v>
@@ -37243,7 +37250,7 @@
         <v>1304</v>
       </c>
       <c r="C991" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D991" s="16">
         <v>57</v>
@@ -37273,7 +37280,7 @@
         <v>1304</v>
       </c>
       <c r="C992" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D992" s="16">
         <v>58</v>
@@ -37303,7 +37310,7 @@
         <v>1304</v>
       </c>
       <c r="C993" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D993" s="16">
         <v>59</v>
@@ -37333,7 +37340,7 @@
         <v>1304</v>
       </c>
       <c r="C994" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D994" s="16">
         <v>60</v>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -32566,7 +32566,7 @@
         <v>4030001</v>
       </c>
       <c r="I846" s="31">
-        <v>101200</v>
+        <v>103400</v>
       </c>
       <c r="J846" s="31"/>
       <c r="K846" s="32" t="s">
@@ -32604,7 +32604,7 @@
         <v>4030001</v>
       </c>
       <c r="I847" s="31">
-        <v>100700</v>
+        <v>103401</v>
       </c>
       <c r="J847" s="31"/>
       <c r="K847" s="32" t="s">
@@ -32642,7 +32642,7 @@
         <v>4030001</v>
       </c>
       <c r="I848" s="31">
-        <v>101800</v>
+        <v>101400</v>
       </c>
       <c r="J848" s="31"/>
       <c r="K848" s="34" t="s">
@@ -32680,7 +32680,7 @@
         <v>4030001</v>
       </c>
       <c r="I849" s="31">
-        <v>102500</v>
+        <v>103500</v>
       </c>
       <c r="J849" s="31"/>
       <c r="K849" s="34" t="s">
@@ -32718,7 +32718,7 @@
         <v>4030001</v>
       </c>
       <c r="I850" s="31">
-        <v>103100</v>
+        <v>103501</v>
       </c>
       <c r="J850" s="31"/>
       <c r="K850" s="34" t="s">
@@ -32756,7 +32756,7 @@
         <v>4030001</v>
       </c>
       <c r="I851" s="31">
-        <v>102200</v>
+        <v>100700</v>
       </c>
       <c r="J851" s="31"/>
       <c r="K851" s="34" t="s">
@@ -32794,7 +32794,7 @@
         <v>4030001</v>
       </c>
       <c r="I852" s="31">
-        <v>102100</v>
+        <v>103600</v>
       </c>
       <c r="J852" s="31"/>
       <c r="K852" s="34" t="s">
@@ -32832,7 +32832,7 @@
         <v>4030001</v>
       </c>
       <c r="I853" s="31">
-        <v>101600</v>
+        <v>101700</v>
       </c>
       <c r="J853" s="31"/>
       <c r="K853" s="34" t="s">
@@ -32870,7 +32870,7 @@
         <v>4030001</v>
       </c>
       <c r="I854" s="31">
-        <v>102000</v>
+        <v>101200</v>
       </c>
       <c r="J854" s="31"/>
       <c r="K854" s="34" t="s">

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>31</v>
@@ -2269,7 +2269,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="16">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>34</v>
@@ -2309,7 +2309,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="16">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>35</v>
@@ -2349,7 +2349,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="16">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>36</v>
@@ -2389,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="16">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>37</v>
@@ -2429,7 +2429,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="16">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>38</v>
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="E11" s="16">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>39</v>
@@ -2509,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="16">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>40</v>
@@ -2549,7 +2549,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="16">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>41</v>
@@ -2589,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="16">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>42</v>
@@ -2629,7 +2629,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="16">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>43</v>
@@ -2669,7 +2669,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="16">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>44</v>
@@ -2709,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="16">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>45</v>
@@ -2749,7 +2749,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="16">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>46</v>
@@ -2789,7 +2789,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="16">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>47</v>
@@ -2829,7 +2829,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="16">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>48</v>
@@ -2869,7 +2869,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="16">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>49</v>
@@ -2909,7 +2909,7 @@
         <v>18</v>
       </c>
       <c r="E22" s="16">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F22" s="16" t="s">
         <v>50</v>
@@ -2949,7 +2949,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="16">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F23" s="16" t="s">
         <v>51</v>
@@ -2983,7 +2983,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="16">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>52</v>
@@ -3017,7 +3017,7 @@
         <v>21</v>
       </c>
       <c r="E25" s="16">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>53</v>
@@ -3048,7 +3048,7 @@
         <v>22</v>
       </c>
       <c r="E26" s="16">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F26" s="16" t="s">
         <v>54</v>
@@ -3079,7 +3079,7 @@
         <v>23</v>
       </c>
       <c r="E27" s="16">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>55</v>
@@ -3110,7 +3110,7 @@
         <v>24</v>
       </c>
       <c r="E28" s="16">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>56</v>
@@ -3141,7 +3141,7 @@
         <v>25</v>
       </c>
       <c r="E29" s="16">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>57</v>
@@ -3172,7 +3172,7 @@
         <v>26</v>
       </c>
       <c r="E30" s="16">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>58</v>
@@ -3203,7 +3203,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="16">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F31" s="16" t="s">
         <v>59</v>
@@ -3234,7 +3234,7 @@
         <v>28</v>
       </c>
       <c r="E32" s="16">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         <v>29</v>
       </c>
       <c r="E33" s="16">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>61</v>
@@ -3296,7 +3296,7 @@
         <v>30</v>
       </c>
       <c r="E34" s="16">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F34" s="16" t="s">
         <v>62</v>
@@ -3330,7 +3330,7 @@
         <v>31</v>
       </c>
       <c r="E35" s="16">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F35" s="16" t="s">
         <v>64</v>
@@ -3364,7 +3364,7 @@
         <v>32</v>
       </c>
       <c r="E36" s="16">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>65</v>
@@ -3398,7 +3398,7 @@
         <v>33</v>
       </c>
       <c r="E37" s="16">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>66</v>
@@ -3432,7 +3432,7 @@
         <v>34</v>
       </c>
       <c r="E38" s="16">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F38" s="16" t="s">
         <v>67</v>
@@ -3466,7 +3466,7 @@
         <v>35</v>
       </c>
       <c r="E39" s="16">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F39" s="16" t="s">
         <v>68</v>
@@ -3500,7 +3500,7 @@
         <v>36</v>
       </c>
       <c r="E40" s="16">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F40" s="16" t="s">
         <v>69</v>
@@ -3534,7 +3534,7 @@
         <v>37</v>
       </c>
       <c r="E41" s="16">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F41" s="16" t="s">
         <v>70</v>
@@ -3568,7 +3568,7 @@
         <v>38</v>
       </c>
       <c r="E42" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F42" s="16" t="s">
         <v>71</v>
@@ -3602,7 +3602,7 @@
         <v>39</v>
       </c>
       <c r="E43" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F43" s="16" t="s">
         <v>72</v>
@@ -3636,7 +3636,7 @@
         <v>40</v>
       </c>
       <c r="E44" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F44" s="16" t="s">
         <v>73</v>
@@ -3670,7 +3670,7 @@
         <v>41</v>
       </c>
       <c r="E45" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F45" s="16" t="s">
         <v>74</v>
@@ -3704,7 +3704,7 @@
         <v>42</v>
       </c>
       <c r="E46" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F46" s="16" t="s">
         <v>75</v>
@@ -3738,7 +3738,7 @@
         <v>43</v>
       </c>
       <c r="E47" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F47" s="16" t="s">
         <v>76</v>
@@ -3772,7 +3772,7 @@
         <v>44</v>
       </c>
       <c r="E48" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F48" s="16" t="s">
         <v>77</v>
@@ -3806,7 +3806,7 @@
         <v>45</v>
       </c>
       <c r="E49" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F49" s="16" t="s">
         <v>78</v>
@@ -3840,7 +3840,7 @@
         <v>46</v>
       </c>
       <c r="E50" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F50" s="16" t="s">
         <v>79</v>
@@ -3874,7 +3874,7 @@
         <v>47</v>
       </c>
       <c r="E51" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F51" s="16" t="s">
         <v>80</v>
@@ -3908,7 +3908,7 @@
         <v>48</v>
       </c>
       <c r="E52" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F52" s="16" t="s">
         <v>81</v>
@@ -3942,7 +3942,7 @@
         <v>49</v>
       </c>
       <c r="E53" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>82</v>
@@ -3976,7 +3976,7 @@
         <v>50</v>
       </c>
       <c r="E54" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>83</v>
@@ -4010,7 +4010,7 @@
         <v>51</v>
       </c>
       <c r="E55" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F55" s="16" t="s">
         <v>84</v>
@@ -4044,7 +4044,7 @@
         <v>52</v>
       </c>
       <c r="E56" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F56" s="16" t="s">
         <v>85</v>
@@ -4078,7 +4078,7 @@
         <v>53</v>
       </c>
       <c r="E57" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>86</v>
@@ -4112,7 +4112,7 @@
         <v>54</v>
       </c>
       <c r="E58" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F58" s="16" t="s">
         <v>87</v>
@@ -4146,7 +4146,7 @@
         <v>55</v>
       </c>
       <c r="E59" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>88</v>
@@ -4180,7 +4180,7 @@
         <v>56</v>
       </c>
       <c r="E60" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F60" s="16" t="s">
         <v>89</v>
@@ -4214,7 +4214,7 @@
         <v>57</v>
       </c>
       <c r="E61" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F61" s="16" t="s">
         <v>90</v>
@@ -4248,7 +4248,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F62" s="16" t="s">
         <v>91</v>
@@ -4282,7 +4282,7 @@
         <v>59</v>
       </c>
       <c r="E63" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>92</v>
@@ -4316,7 +4316,7 @@
         <v>60</v>
       </c>
       <c r="E64" s="16">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F64" s="16" t="s">
         <v>93</v>
@@ -4348,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="20">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F65" s="20" t="s">
         <v>31</v>
@@ -4388,7 +4388,7 @@
         <v>2</v>
       </c>
       <c r="E66" s="20">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F66" s="20" t="s">
         <v>34</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="E67" s="20">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F67" s="20" t="s">
         <v>35</v>
@@ -4468,7 +4468,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="20">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F68" s="20" t="s">
         <v>36</v>
@@ -4508,7 +4508,7 @@
         <v>5</v>
       </c>
       <c r="E69" s="20">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="F69" s="20" t="s">
         <v>37</v>
@@ -4548,7 +4548,7 @@
         <v>6</v>
       </c>
       <c r="E70" s="20">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="F70" s="20" t="s">
         <v>38</v>
@@ -4588,7 +4588,7 @@
         <v>7</v>
       </c>
       <c r="E71" s="20">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="F71" s="20" t="s">
         <v>39</v>
@@ -4628,7 +4628,7 @@
         <v>8</v>
       </c>
       <c r="E72" s="20">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F72" s="20" t="s">
         <v>40</v>
@@ -4668,7 +4668,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="20">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F73" s="20" t="s">
         <v>41</v>
@@ -4708,7 +4708,7 @@
         <v>10</v>
       </c>
       <c r="E74" s="20">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F74" s="20" t="s">
         <v>42</v>
@@ -4748,7 +4748,7 @@
         <v>11</v>
       </c>
       <c r="E75" s="20">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F75" s="20" t="s">
         <v>43</v>
@@ -4788,7 +4788,7 @@
         <v>12</v>
       </c>
       <c r="E76" s="20">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F76" s="20" t="s">
         <v>44</v>
@@ -4828,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="E77" s="20">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="F77" s="20" t="s">
         <v>45</v>
@@ -4868,7 +4868,7 @@
         <v>14</v>
       </c>
       <c r="E78" s="20">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F78" s="20" t="s">
         <v>46</v>
@@ -4908,7 +4908,7 @@
         <v>15</v>
       </c>
       <c r="E79" s="20">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F79" s="20" t="s">
         <v>47</v>
@@ -4948,7 +4948,7 @@
         <v>16</v>
       </c>
       <c r="E80" s="20">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F80" s="20" t="s">
         <v>48</v>
@@ -4988,7 +4988,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="20">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F81" s="20" t="s">
         <v>49</v>
@@ -5024,7 +5024,7 @@
         <v>18</v>
       </c>
       <c r="E82" s="20">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F82" s="20" t="s">
         <v>50</v>
@@ -5057,7 +5057,7 @@
         <v>19</v>
       </c>
       <c r="E83" s="20">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F83" s="20" t="s">
         <v>51</v>
@@ -5090,7 +5090,7 @@
         <v>20</v>
       </c>
       <c r="E84" s="20">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F84" s="20" t="s">
         <v>52</v>
@@ -5123,7 +5123,7 @@
         <v>21</v>
       </c>
       <c r="E85" s="20">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F85" s="20" t="s">
         <v>53</v>
@@ -5156,7 +5156,7 @@
         <v>22</v>
       </c>
       <c r="E86" s="20">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F86" s="20" t="s">
         <v>54</v>
@@ -5189,7 +5189,7 @@
         <v>23</v>
       </c>
       <c r="E87" s="20">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F87" s="20" t="s">
         <v>55</v>
@@ -5222,7 +5222,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="20">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F88" s="20" t="s">
         <v>56</v>
@@ -5255,7 +5255,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="20">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F89" s="20" t="s">
         <v>57</v>
@@ -5288,7 +5288,7 @@
         <v>26</v>
       </c>
       <c r="E90" s="20">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F90" s="20" t="s">
         <v>58</v>
@@ -5324,7 +5324,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="20">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F91" s="20" t="s">
         <v>59</v>
@@ -5360,7 +5360,7 @@
         <v>28</v>
       </c>
       <c r="E92" s="20">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F92" s="20" t="s">
         <v>60</v>
@@ -5396,7 +5396,7 @@
         <v>29</v>
       </c>
       <c r="E93" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F93" s="20" t="s">
         <v>61</v>
@@ -5432,7 +5432,7 @@
         <v>30</v>
       </c>
       <c r="E94" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F94" s="20" t="s">
         <v>62</v>
@@ -5468,7 +5468,7 @@
         <v>31</v>
       </c>
       <c r="E95" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F95" s="20" t="s">
         <v>64</v>
@@ -5504,7 +5504,7 @@
         <v>32</v>
       </c>
       <c r="E96" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F96" s="20" t="s">
         <v>65</v>
@@ -5540,7 +5540,7 @@
         <v>33</v>
       </c>
       <c r="E97" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F97" s="20" t="s">
         <v>66</v>
@@ -5576,7 +5576,7 @@
         <v>34</v>
       </c>
       <c r="E98" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F98" s="20" t="s">
         <v>67</v>
@@ -5612,7 +5612,7 @@
         <v>35</v>
       </c>
       <c r="E99" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F99" s="20" t="s">
         <v>68</v>
@@ -5648,7 +5648,7 @@
         <v>36</v>
       </c>
       <c r="E100" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F100" s="20" t="s">
         <v>69</v>
@@ -5684,7 +5684,7 @@
         <v>37</v>
       </c>
       <c r="E101" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F101" s="20" t="s">
         <v>70</v>
@@ -5720,7 +5720,7 @@
         <v>38</v>
       </c>
       <c r="E102" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F102" s="20" t="s">
         <v>71</v>
@@ -5756,7 +5756,7 @@
         <v>39</v>
       </c>
       <c r="E103" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F103" s="20" t="s">
         <v>72</v>
@@ -5792,7 +5792,7 @@
         <v>40</v>
       </c>
       <c r="E104" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F104" s="20" t="s">
         <v>73</v>
@@ -5828,7 +5828,7 @@
         <v>41</v>
       </c>
       <c r="E105" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F105" s="20" t="s">
         <v>74</v>
@@ -5864,7 +5864,7 @@
         <v>42</v>
       </c>
       <c r="E106" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F106" s="20" t="s">
         <v>75</v>
@@ -5900,7 +5900,7 @@
         <v>43</v>
       </c>
       <c r="E107" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F107" s="20" t="s">
         <v>76</v>
@@ -5936,7 +5936,7 @@
         <v>44</v>
       </c>
       <c r="E108" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F108" s="20" t="s">
         <v>77</v>
@@ -5972,7 +5972,7 @@
         <v>45</v>
       </c>
       <c r="E109" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F109" s="20" t="s">
         <v>78</v>
@@ -6008,7 +6008,7 @@
         <v>46</v>
       </c>
       <c r="E110" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F110" s="20" t="s">
         <v>79</v>
@@ -6044,7 +6044,7 @@
         <v>47</v>
       </c>
       <c r="E111" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F111" s="20" t="s">
         <v>80</v>
@@ -6080,7 +6080,7 @@
         <v>48</v>
       </c>
       <c r="E112" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F112" s="20" t="s">
         <v>81</v>
@@ -6116,7 +6116,7 @@
         <v>49</v>
       </c>
       <c r="E113" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F113" s="20" t="s">
         <v>82</v>
@@ -6152,7 +6152,7 @@
         <v>50</v>
       </c>
       <c r="E114" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F114" s="20" t="s">
         <v>83</v>
@@ -6188,7 +6188,7 @@
         <v>51</v>
       </c>
       <c r="E115" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F115" s="20" t="s">
         <v>84</v>
@@ -6224,7 +6224,7 @@
         <v>52</v>
       </c>
       <c r="E116" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F116" s="20" t="s">
         <v>85</v>
@@ -6260,7 +6260,7 @@
         <v>53</v>
       </c>
       <c r="E117" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F117" s="20" t="s">
         <v>86</v>
@@ -6296,7 +6296,7 @@
         <v>54</v>
       </c>
       <c r="E118" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F118" s="20" t="s">
         <v>87</v>
@@ -6332,7 +6332,7 @@
         <v>55</v>
       </c>
       <c r="E119" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F119" s="20" t="s">
         <v>88</v>
@@ -6368,7 +6368,7 @@
         <v>56</v>
       </c>
       <c r="E120" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F120" s="20" t="s">
         <v>89</v>
@@ -6404,7 +6404,7 @@
         <v>57</v>
       </c>
       <c r="E121" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F121" s="20" t="s">
         <v>90</v>
@@ -6440,7 +6440,7 @@
         <v>58</v>
       </c>
       <c r="E122" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F122" s="20" t="s">
         <v>91</v>
@@ -6476,7 +6476,7 @@
         <v>59</v>
       </c>
       <c r="E123" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F123" s="20" t="s">
         <v>92</v>
@@ -6512,7 +6512,7 @@
         <v>60</v>
       </c>
       <c r="E124" s="20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F124" s="20" t="s">
         <v>93</v>
@@ -6546,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="E125" s="16">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F125" s="16" t="s">
         <v>31</v>
@@ -6586,7 +6586,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="16">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F126" s="16" t="s">
         <v>34</v>
@@ -6626,7 +6626,7 @@
         <v>3</v>
       </c>
       <c r="E127" s="16">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="F127" s="16" t="s">
         <v>35</v>
@@ -6666,7 +6666,7 @@
         <v>4</v>
       </c>
       <c r="E128" s="16">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F128" s="16" t="s">
         <v>36</v>
@@ -6706,7 +6706,7 @@
         <v>5</v>
       </c>
       <c r="E129" s="16">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="F129" s="16" t="s">
         <v>37</v>
@@ -6746,7 +6746,7 @@
         <v>6</v>
       </c>
       <c r="E130" s="16">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F130" s="16" t="s">
         <v>38</v>
@@ -6786,7 +6786,7 @@
         <v>7</v>
       </c>
       <c r="E131" s="16">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F131" s="16" t="s">
         <v>39</v>
@@ -6826,7 +6826,7 @@
         <v>8</v>
       </c>
       <c r="E132" s="16">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F132" s="16" t="s">
         <v>40</v>
@@ -6866,7 +6866,7 @@
         <v>9</v>
       </c>
       <c r="E133" s="16">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F133" s="16" t="s">
         <v>41</v>
@@ -6906,7 +6906,7 @@
         <v>10</v>
       </c>
       <c r="E134" s="16">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F134" s="16" t="s">
         <v>42</v>
@@ -6946,7 +6946,7 @@
         <v>11</v>
       </c>
       <c r="E135" s="16">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F135" s="16" t="s">
         <v>43</v>
@@ -6986,7 +6986,7 @@
         <v>12</v>
       </c>
       <c r="E136" s="16">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F136" s="16" t="s">
         <v>44</v>
@@ -7026,7 +7026,7 @@
         <v>13</v>
       </c>
       <c r="E137" s="16">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F137" s="16" t="s">
         <v>45</v>
@@ -7066,7 +7066,7 @@
         <v>14</v>
       </c>
       <c r="E138" s="16">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F138" s="16" t="s">
         <v>46</v>
@@ -7106,7 +7106,7 @@
         <v>15</v>
       </c>
       <c r="E139" s="16">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F139" s="16" t="s">
         <v>47</v>
@@ -7146,7 +7146,7 @@
         <v>16</v>
       </c>
       <c r="E140" s="16">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F140" s="16" t="s">
         <v>48</v>
@@ -7186,7 +7186,7 @@
         <v>17</v>
       </c>
       <c r="E141" s="16">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F141" s="16" t="s">
         <v>49</v>
@@ -7217,7 +7217,7 @@
         <v>18</v>
       </c>
       <c r="E142" s="16">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F142" s="16" t="s">
         <v>50</v>
@@ -7248,7 +7248,7 @@
         <v>19</v>
       </c>
       <c r="E143" s="16">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F143" s="16" t="s">
         <v>51</v>
@@ -7279,7 +7279,7 @@
         <v>20</v>
       </c>
       <c r="E144" s="16">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F144" s="16" t="s">
         <v>52</v>
@@ -7310,7 +7310,7 @@
         <v>21</v>
       </c>
       <c r="E145" s="16">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F145" s="16" t="s">
         <v>53</v>
@@ -7341,7 +7341,7 @@
         <v>22</v>
       </c>
       <c r="E146" s="16">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F146" s="16" t="s">
         <v>54</v>
@@ -7372,7 +7372,7 @@
         <v>23</v>
       </c>
       <c r="E147" s="16">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F147" s="16" t="s">
         <v>55</v>
@@ -7406,7 +7406,7 @@
         <v>24</v>
       </c>
       <c r="E148" s="16">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F148" s="16" t="s">
         <v>56</v>
@@ -7440,7 +7440,7 @@
         <v>25</v>
       </c>
       <c r="E149" s="16">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F149" s="16" t="s">
         <v>57</v>
@@ -7474,7 +7474,7 @@
         <v>26</v>
       </c>
       <c r="E150" s="16">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F150" s="16" t="s">
         <v>58</v>
@@ -7508,7 +7508,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="16">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F151" s="16" t="s">
         <v>59</v>
@@ -7542,7 +7542,7 @@
         <v>28</v>
       </c>
       <c r="E152" s="16">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F152" s="16" t="s">
         <v>60</v>
@@ -7576,7 +7576,7 @@
         <v>29</v>
       </c>
       <c r="E153" s="16">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F153" s="16" t="s">
         <v>61</v>
@@ -7610,7 +7610,7 @@
         <v>30</v>
       </c>
       <c r="E154" s="16">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F154" s="16" t="s">
         <v>62</v>
@@ -7644,7 +7644,7 @@
         <v>31</v>
       </c>
       <c r="E155" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F155" s="16" t="s">
         <v>64</v>
@@ -7678,7 +7678,7 @@
         <v>32</v>
       </c>
       <c r="E156" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F156" s="16" t="s">
         <v>65</v>
@@ -7712,7 +7712,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F157" s="16" t="s">
         <v>66</v>
@@ -7746,7 +7746,7 @@
         <v>34</v>
       </c>
       <c r="E158" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F158" s="16" t="s">
         <v>67</v>
@@ -7780,7 +7780,7 @@
         <v>35</v>
       </c>
       <c r="E159" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F159" s="16" t="s">
         <v>68</v>
@@ -7814,7 +7814,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>69</v>
@@ -7848,7 +7848,7 @@
         <v>37</v>
       </c>
       <c r="E161" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>70</v>
@@ -7882,7 +7882,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>71</v>
@@ -7916,7 +7916,7 @@
         <v>39</v>
       </c>
       <c r="E163" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F163" s="16" t="s">
         <v>72</v>
@@ -7950,7 +7950,7 @@
         <v>40</v>
       </c>
       <c r="E164" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F164" s="16" t="s">
         <v>73</v>
@@ -7984,7 +7984,7 @@
         <v>41</v>
       </c>
       <c r="E165" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F165" s="16" t="s">
         <v>74</v>
@@ -8018,7 +8018,7 @@
         <v>42</v>
       </c>
       <c r="E166" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F166" s="16" t="s">
         <v>75</v>
@@ -8052,7 +8052,7 @@
         <v>43</v>
       </c>
       <c r="E167" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F167" s="16" t="s">
         <v>76</v>
@@ -8086,7 +8086,7 @@
         <v>44</v>
       </c>
       <c r="E168" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F168" s="16" t="s">
         <v>77</v>
@@ -8120,7 +8120,7 @@
         <v>45</v>
       </c>
       <c r="E169" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F169" s="16" t="s">
         <v>78</v>
@@ -8154,7 +8154,7 @@
         <v>46</v>
       </c>
       <c r="E170" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F170" s="16" t="s">
         <v>79</v>
@@ -8188,7 +8188,7 @@
         <v>47</v>
       </c>
       <c r="E171" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F171" s="16" t="s">
         <v>80</v>
@@ -8222,7 +8222,7 @@
         <v>48</v>
       </c>
       <c r="E172" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F172" s="16" t="s">
         <v>81</v>
@@ -8256,7 +8256,7 @@
         <v>49</v>
       </c>
       <c r="E173" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F173" s="16" t="s">
         <v>82</v>
@@ -8290,7 +8290,7 @@
         <v>50</v>
       </c>
       <c r="E174" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F174" s="16" t="s">
         <v>83</v>
@@ -8324,7 +8324,7 @@
         <v>51</v>
       </c>
       <c r="E175" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F175" s="16" t="s">
         <v>84</v>
@@ -8358,7 +8358,7 @@
         <v>52</v>
       </c>
       <c r="E176" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F176" s="16" t="s">
         <v>85</v>
@@ -8392,7 +8392,7 @@
         <v>53</v>
       </c>
       <c r="E177" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F177" s="16" t="s">
         <v>86</v>
@@ -8426,7 +8426,7 @@
         <v>54</v>
       </c>
       <c r="E178" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F178" s="16" t="s">
         <v>87</v>
@@ -8460,7 +8460,7 @@
         <v>55</v>
       </c>
       <c r="E179" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F179" s="16" t="s">
         <v>88</v>
@@ -8494,7 +8494,7 @@
         <v>56</v>
       </c>
       <c r="E180" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F180" s="16" t="s">
         <v>89</v>
@@ -8528,7 +8528,7 @@
         <v>57</v>
       </c>
       <c r="E181" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F181" s="16" t="s">
         <v>90</v>
@@ -8562,7 +8562,7 @@
         <v>58</v>
       </c>
       <c r="E182" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F182" s="16" t="s">
         <v>91</v>
@@ -8596,7 +8596,7 @@
         <v>59</v>
       </c>
       <c r="E183" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F183" s="16" t="s">
         <v>92</v>
@@ -8630,7 +8630,7 @@
         <v>60</v>
       </c>
       <c r="E184" s="16">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F184" s="16" t="s">
         <v>93</v>
@@ -8662,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="E185" s="20">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F185" s="20" t="s">
         <v>31</v>
@@ -8702,7 +8702,7 @@
         <v>2</v>
       </c>
       <c r="E186" s="20">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F186" s="20" t="s">
         <v>34</v>
@@ -8742,7 +8742,7 @@
         <v>3</v>
       </c>
       <c r="E187" s="20">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F187" s="20" t="s">
         <v>35</v>
@@ -8782,7 +8782,7 @@
         <v>4</v>
       </c>
       <c r="E188" s="20">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F188" s="20" t="s">
         <v>36</v>
@@ -8822,7 +8822,7 @@
         <v>5</v>
       </c>
       <c r="E189" s="20">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F189" s="20" t="s">
         <v>37</v>
@@ -8862,7 +8862,7 @@
         <v>6</v>
       </c>
       <c r="E190" s="20">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F190" s="20" t="s">
         <v>38</v>
@@ -8902,7 +8902,7 @@
         <v>7</v>
       </c>
       <c r="E191" s="20">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F191" s="20" t="s">
         <v>39</v>
@@ -8942,7 +8942,7 @@
         <v>8</v>
       </c>
       <c r="E192" s="20">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F192" s="20" t="s">
         <v>40</v>
@@ -8982,7 +8982,7 @@
         <v>9</v>
       </c>
       <c r="E193" s="20">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F193" s="20" t="s">
         <v>41</v>
@@ -9022,7 +9022,7 @@
         <v>10</v>
       </c>
       <c r="E194" s="20">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F194" s="20" t="s">
         <v>42</v>
@@ -9062,7 +9062,7 @@
         <v>11</v>
       </c>
       <c r="E195" s="20">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F195" s="20" t="s">
         <v>43</v>
@@ -9102,7 +9102,7 @@
         <v>12</v>
       </c>
       <c r="E196" s="20">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F196" s="20" t="s">
         <v>44</v>
@@ -9142,7 +9142,7 @@
         <v>13</v>
       </c>
       <c r="E197" s="20">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F197" s="20" t="s">
         <v>45</v>
@@ -9182,7 +9182,7 @@
         <v>14</v>
       </c>
       <c r="E198" s="20">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F198" s="20" t="s">
         <v>46</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="E199" s="20">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F199" s="20" t="s">
         <v>47</v>
@@ -9262,7 +9262,7 @@
         <v>16</v>
       </c>
       <c r="E200" s="20">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F200" s="20" t="s">
         <v>48</v>
@@ -9302,7 +9302,7 @@
         <v>17</v>
       </c>
       <c r="E201" s="20">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F201" s="20" t="s">
         <v>49</v>
@@ -9338,7 +9338,7 @@
         <v>18</v>
       </c>
       <c r="E202" s="20">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F202" s="20" t="s">
         <v>50</v>
@@ -9371,7 +9371,7 @@
         <v>19</v>
       </c>
       <c r="E203" s="20">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F203" s="20" t="s">
         <v>51</v>
@@ -9404,7 +9404,7 @@
         <v>20</v>
       </c>
       <c r="E204" s="20">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F204" s="20" t="s">
         <v>52</v>
@@ -9437,7 +9437,7 @@
         <v>21</v>
       </c>
       <c r="E205" s="20">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F205" s="20" t="s">
         <v>53</v>
@@ -9470,7 +9470,7 @@
         <v>22</v>
       </c>
       <c r="E206" s="20">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F206" s="20" t="s">
         <v>54</v>
@@ -9503,7 +9503,7 @@
         <v>23</v>
       </c>
       <c r="E207" s="20">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F207" s="20" t="s">
         <v>55</v>
@@ -9536,7 +9536,7 @@
         <v>24</v>
       </c>
       <c r="E208" s="20">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F208" s="20" t="s">
         <v>56</v>
@@ -9569,7 +9569,7 @@
         <v>25</v>
       </c>
       <c r="E209" s="20">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F209" s="20" t="s">
         <v>57</v>
@@ -9602,7 +9602,7 @@
         <v>26</v>
       </c>
       <c r="E210" s="20">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F210" s="20" t="s">
         <v>58</v>
@@ -9638,7 +9638,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F211" s="20" t="s">
         <v>59</v>
@@ -9674,7 +9674,7 @@
         <v>28</v>
       </c>
       <c r="E212" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F212" s="20" t="s">
         <v>60</v>
@@ -9710,7 +9710,7 @@
         <v>29</v>
       </c>
       <c r="E213" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F213" s="20" t="s">
         <v>61</v>
@@ -9746,7 +9746,7 @@
         <v>30</v>
       </c>
       <c r="E214" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F214" s="20" t="s">
         <v>62</v>
@@ -9782,7 +9782,7 @@
         <v>31</v>
       </c>
       <c r="E215" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F215" s="20" t="s">
         <v>64</v>
@@ -9818,7 +9818,7 @@
         <v>32</v>
       </c>
       <c r="E216" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F216" s="20" t="s">
         <v>65</v>
@@ -9854,7 +9854,7 @@
         <v>33</v>
       </c>
       <c r="E217" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F217" s="20" t="s">
         <v>66</v>
@@ -9890,7 +9890,7 @@
         <v>34</v>
       </c>
       <c r="E218" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F218" s="20" t="s">
         <v>67</v>
@@ -9926,7 +9926,7 @@
         <v>35</v>
       </c>
       <c r="E219" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F219" s="20" t="s">
         <v>68</v>
@@ -9962,7 +9962,7 @@
         <v>36</v>
       </c>
       <c r="E220" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F220" s="20" t="s">
         <v>69</v>
@@ -9998,7 +9998,7 @@
         <v>37</v>
       </c>
       <c r="E221" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F221" s="20" t="s">
         <v>70</v>
@@ -10034,7 +10034,7 @@
         <v>38</v>
       </c>
       <c r="E222" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F222" s="20" t="s">
         <v>71</v>
@@ -10070,7 +10070,7 @@
         <v>39</v>
       </c>
       <c r="E223" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F223" s="20" t="s">
         <v>72</v>
@@ -10106,7 +10106,7 @@
         <v>40</v>
       </c>
       <c r="E224" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F224" s="20" t="s">
         <v>73</v>
@@ -10142,7 +10142,7 @@
         <v>41</v>
       </c>
       <c r="E225" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F225" s="20" t="s">
         <v>74</v>
@@ -10178,7 +10178,7 @@
         <v>42</v>
       </c>
       <c r="E226" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F226" s="20" t="s">
         <v>75</v>
@@ -10214,7 +10214,7 @@
         <v>43</v>
       </c>
       <c r="E227" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F227" s="20" t="s">
         <v>76</v>
@@ -10250,7 +10250,7 @@
         <v>44</v>
       </c>
       <c r="E228" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F228" s="20" t="s">
         <v>77</v>
@@ -10286,7 +10286,7 @@
         <v>45</v>
       </c>
       <c r="E229" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F229" s="20" t="s">
         <v>78</v>
@@ -10322,7 +10322,7 @@
         <v>46</v>
       </c>
       <c r="E230" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F230" s="20" t="s">
         <v>79</v>
@@ -10358,7 +10358,7 @@
         <v>47</v>
       </c>
       <c r="E231" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F231" s="20" t="s">
         <v>80</v>
@@ -10394,7 +10394,7 @@
         <v>48</v>
       </c>
       <c r="E232" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F232" s="20" t="s">
         <v>81</v>
@@ -10430,7 +10430,7 @@
         <v>49</v>
       </c>
       <c r="E233" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F233" s="20" t="s">
         <v>82</v>
@@ -10466,7 +10466,7 @@
         <v>50</v>
       </c>
       <c r="E234" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F234" s="20" t="s">
         <v>83</v>
@@ -10502,7 +10502,7 @@
         <v>51</v>
       </c>
       <c r="E235" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F235" s="20" t="s">
         <v>84</v>
@@ -10538,7 +10538,7 @@
         <v>52</v>
       </c>
       <c r="E236" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F236" s="20" t="s">
         <v>85</v>
@@ -10574,7 +10574,7 @@
         <v>53</v>
       </c>
       <c r="E237" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F237" s="20" t="s">
         <v>86</v>
@@ -10610,7 +10610,7 @@
         <v>54</v>
       </c>
       <c r="E238" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F238" s="20" t="s">
         <v>87</v>
@@ -10646,7 +10646,7 @@
         <v>55</v>
       </c>
       <c r="E239" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F239" s="20" t="s">
         <v>88</v>
@@ -10682,7 +10682,7 @@
         <v>56</v>
       </c>
       <c r="E240" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F240" s="20" t="s">
         <v>89</v>
@@ -10718,7 +10718,7 @@
         <v>57</v>
       </c>
       <c r="E241" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F241" s="20" t="s">
         <v>90</v>
@@ -10754,7 +10754,7 @@
         <v>58</v>
       </c>
       <c r="E242" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F242" s="20" t="s">
         <v>91</v>
@@ -10790,7 +10790,7 @@
         <v>59</v>
       </c>
       <c r="E243" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F243" s="20" t="s">
         <v>92</v>
@@ -10826,7 +10826,7 @@
         <v>60</v>
       </c>
       <c r="E244" s="20">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F244" s="20" t="s">
         <v>93</v>
@@ -10860,7 +10860,7 @@
         <v>1</v>
       </c>
       <c r="E245" s="16">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F245" s="16" t="s">
         <v>31</v>
@@ -10900,7 +10900,7 @@
         <v>2</v>
       </c>
       <c r="E246" s="16">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F246" s="16" t="s">
         <v>34</v>
@@ -10940,7 +10940,7 @@
         <v>3</v>
       </c>
       <c r="E247" s="16">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F247" s="16" t="s">
         <v>35</v>
@@ -10980,7 +10980,7 @@
         <v>4</v>
       </c>
       <c r="E248" s="16">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F248" s="16" t="s">
         <v>36</v>
@@ -11020,7 +11020,7 @@
         <v>5</v>
       </c>
       <c r="E249" s="16">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F249" s="16" t="s">
         <v>37</v>
@@ -11060,7 +11060,7 @@
         <v>6</v>
       </c>
       <c r="E250" s="16">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F250" s="16" t="s">
         <v>38</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="E251" s="16">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F251" s="16" t="s">
         <v>39</v>
@@ -11140,7 +11140,7 @@
         <v>8</v>
       </c>
       <c r="E252" s="16">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F252" s="16" t="s">
         <v>40</v>
@@ -11180,7 +11180,7 @@
         <v>9</v>
       </c>
       <c r="E253" s="16">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F253" s="16" t="s">
         <v>41</v>
@@ -11220,7 +11220,7 @@
         <v>10</v>
       </c>
       <c r="E254" s="16">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F254" s="16" t="s">
         <v>42</v>
@@ -11260,7 +11260,7 @@
         <v>11</v>
       </c>
       <c r="E255" s="16">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F255" s="16" t="s">
         <v>43</v>
@@ -11300,7 +11300,7 @@
         <v>12</v>
       </c>
       <c r="E256" s="16">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F256" s="16" t="s">
         <v>44</v>
@@ -11340,7 +11340,7 @@
         <v>13</v>
       </c>
       <c r="E257" s="16">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F257" s="16" t="s">
         <v>45</v>
@@ -11380,7 +11380,7 @@
         <v>14</v>
       </c>
       <c r="E258" s="16">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F258" s="16" t="s">
         <v>46</v>
@@ -11417,7 +11417,7 @@
         <v>15</v>
       </c>
       <c r="E259" s="16">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F259" s="16" t="s">
         <v>47</v>
@@ -11454,7 +11454,7 @@
         <v>16</v>
       </c>
       <c r="E260" s="16">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F260" s="16" t="s">
         <v>48</v>
@@ -11491,7 +11491,7 @@
         <v>17</v>
       </c>
       <c r="E261" s="16">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F261" s="16" t="s">
         <v>49</v>
@@ -11522,7 +11522,7 @@
         <v>18</v>
       </c>
       <c r="E262" s="16">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F262" s="16" t="s">
         <v>50</v>
@@ -11553,7 +11553,7 @@
         <v>19</v>
       </c>
       <c r="E263" s="16">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F263" s="16" t="s">
         <v>51</v>
@@ -11584,7 +11584,7 @@
         <v>20</v>
       </c>
       <c r="E264" s="16">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F264" s="16" t="s">
         <v>52</v>
@@ -11615,7 +11615,7 @@
         <v>21</v>
       </c>
       <c r="E265" s="16">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F265" s="16" t="s">
         <v>53</v>
@@ -11649,7 +11649,7 @@
         <v>22</v>
       </c>
       <c r="E266" s="16">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F266" s="16" t="s">
         <v>54</v>
@@ -11683,7 +11683,7 @@
         <v>23</v>
       </c>
       <c r="E267" s="16">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F267" s="16" t="s">
         <v>55</v>
@@ -11717,7 +11717,7 @@
         <v>24</v>
       </c>
       <c r="E268" s="16">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F268" s="16" t="s">
         <v>56</v>
@@ -11751,7 +11751,7 @@
         <v>25</v>
       </c>
       <c r="E269" s="16">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F269" s="16" t="s">
         <v>57</v>
@@ -11785,7 +11785,7 @@
         <v>26</v>
       </c>
       <c r="E270" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F270" s="16" t="s">
         <v>58</v>
@@ -11819,7 +11819,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F271" s="16" t="s">
         <v>59</v>
@@ -11853,7 +11853,7 @@
         <v>28</v>
       </c>
       <c r="E272" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F272" s="16" t="s">
         <v>60</v>
@@ -11887,7 +11887,7 @@
         <v>29</v>
       </c>
       <c r="E273" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>61</v>
@@ -11921,7 +11921,7 @@
         <v>30</v>
       </c>
       <c r="E274" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>62</v>
@@ -11955,7 +11955,7 @@
         <v>31</v>
       </c>
       <c r="E275" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F275" s="16" t="s">
         <v>64</v>
@@ -11989,7 +11989,7 @@
         <v>32</v>
       </c>
       <c r="E276" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F276" s="16" t="s">
         <v>65</v>
@@ -12023,7 +12023,7 @@
         <v>33</v>
       </c>
       <c r="E277" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F277" s="16" t="s">
         <v>66</v>
@@ -12057,7 +12057,7 @@
         <v>34</v>
       </c>
       <c r="E278" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F278" s="16" t="s">
         <v>67</v>
@@ -12091,7 +12091,7 @@
         <v>35</v>
       </c>
       <c r="E279" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F279" s="16" t="s">
         <v>68</v>
@@ -12125,7 +12125,7 @@
         <v>36</v>
       </c>
       <c r="E280" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F280" s="16" t="s">
         <v>69</v>
@@ -12159,7 +12159,7 @@
         <v>37</v>
       </c>
       <c r="E281" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F281" s="16" t="s">
         <v>70</v>
@@ -12193,7 +12193,7 @@
         <v>38</v>
       </c>
       <c r="E282" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F282" s="16" t="s">
         <v>71</v>
@@ -12227,7 +12227,7 @@
         <v>39</v>
       </c>
       <c r="E283" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F283" s="16" t="s">
         <v>72</v>
@@ -12261,7 +12261,7 @@
         <v>40</v>
       </c>
       <c r="E284" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F284" s="16" t="s">
         <v>73</v>
@@ -12295,7 +12295,7 @@
         <v>41</v>
       </c>
       <c r="E285" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F285" s="16" t="s">
         <v>74</v>
@@ -12329,7 +12329,7 @@
         <v>42</v>
       </c>
       <c r="E286" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F286" s="16" t="s">
         <v>75</v>
@@ -12363,7 +12363,7 @@
         <v>43</v>
       </c>
       <c r="E287" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F287" s="16" t="s">
         <v>76</v>
@@ -12397,7 +12397,7 @@
         <v>44</v>
       </c>
       <c r="E288" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F288" s="16" t="s">
         <v>77</v>
@@ -12431,7 +12431,7 @@
         <v>45</v>
       </c>
       <c r="E289" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F289" s="16" t="s">
         <v>78</v>
@@ -12465,7 +12465,7 @@
         <v>46</v>
       </c>
       <c r="E290" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F290" s="16" t="s">
         <v>79</v>
@@ -12499,7 +12499,7 @@
         <v>47</v>
       </c>
       <c r="E291" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F291" s="16" t="s">
         <v>80</v>
@@ -12533,7 +12533,7 @@
         <v>48</v>
       </c>
       <c r="E292" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F292" s="16" t="s">
         <v>81</v>
@@ -12567,7 +12567,7 @@
         <v>49</v>
       </c>
       <c r="E293" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F293" s="16" t="s">
         <v>82</v>
@@ -12601,7 +12601,7 @@
         <v>50</v>
       </c>
       <c r="E294" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F294" s="16" t="s">
         <v>83</v>
@@ -12635,7 +12635,7 @@
         <v>51</v>
       </c>
       <c r="E295" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F295" s="16" t="s">
         <v>84</v>
@@ -12669,7 +12669,7 @@
         <v>52</v>
       </c>
       <c r="E296" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F296" s="16" t="s">
         <v>85</v>
@@ -12703,7 +12703,7 @@
         <v>53</v>
       </c>
       <c r="E297" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F297" s="16" t="s">
         <v>86</v>
@@ -12737,7 +12737,7 @@
         <v>54</v>
       </c>
       <c r="E298" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F298" s="16" t="s">
         <v>87</v>
@@ -12771,7 +12771,7 @@
         <v>55</v>
       </c>
       <c r="E299" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F299" s="16" t="s">
         <v>88</v>
@@ -12805,7 +12805,7 @@
         <v>56</v>
       </c>
       <c r="E300" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F300" s="16" t="s">
         <v>89</v>
@@ -12839,7 +12839,7 @@
         <v>57</v>
       </c>
       <c r="E301" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F301" s="16" t="s">
         <v>90</v>
@@ -12873,7 +12873,7 @@
         <v>58</v>
       </c>
       <c r="E302" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F302" s="16" t="s">
         <v>91</v>
@@ -12907,7 +12907,7 @@
         <v>59</v>
       </c>
       <c r="E303" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F303" s="16" t="s">
         <v>92</v>
@@ -12941,7 +12941,7 @@
         <v>60</v>
       </c>
       <c r="E304" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F304" s="16" t="s">
         <v>93</v>
@@ -12973,7 +12973,7 @@
         <v>1</v>
       </c>
       <c r="E305" s="20">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F305" s="20" t="s">
         <v>31</v>
@@ -13013,7 +13013,7 @@
         <v>2</v>
       </c>
       <c r="E306" s="20">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F306" s="20" t="s">
         <v>34</v>
@@ -13053,7 +13053,7 @@
         <v>3</v>
       </c>
       <c r="E307" s="20">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F307" s="20" t="s">
         <v>35</v>
@@ -13093,7 +13093,7 @@
         <v>4</v>
       </c>
       <c r="E308" s="20">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F308" s="20" t="s">
         <v>36</v>
@@ -13133,7 +13133,7 @@
         <v>5</v>
       </c>
       <c r="E309" s="20">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F309" s="20" t="s">
         <v>37</v>
@@ -13173,7 +13173,7 @@
         <v>6</v>
       </c>
       <c r="E310" s="20">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F310" s="20" t="s">
         <v>38</v>
@@ -13213,7 +13213,7 @@
         <v>7</v>
       </c>
       <c r="E311" s="20">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F311" s="20" t="s">
         <v>39</v>
@@ -13253,7 +13253,7 @@
         <v>8</v>
       </c>
       <c r="E312" s="20">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F312" s="20" t="s">
         <v>40</v>
@@ -13293,7 +13293,7 @@
         <v>9</v>
       </c>
       <c r="E313" s="20">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F313" s="20" t="s">
         <v>41</v>
@@ -13333,7 +13333,7 @@
         <v>10</v>
       </c>
       <c r="E314" s="20">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F314" s="20" t="s">
         <v>42</v>
@@ -13373,7 +13373,7 @@
         <v>11</v>
       </c>
       <c r="E315" s="20">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F315" s="20" t="s">
         <v>43</v>
@@ -13413,7 +13413,7 @@
         <v>12</v>
       </c>
       <c r="E316" s="20">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F316" s="20" t="s">
         <v>44</v>
@@ -13453,7 +13453,7 @@
         <v>13</v>
       </c>
       <c r="E317" s="20">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F317" s="20" t="s">
         <v>45</v>
@@ -13493,7 +13493,7 @@
         <v>14</v>
       </c>
       <c r="E318" s="20">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F318" s="20" t="s">
         <v>46</v>
@@ -13533,7 +13533,7 @@
         <v>15</v>
       </c>
       <c r="E319" s="20">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F319" s="20" t="s">
         <v>47</v>
@@ -13573,7 +13573,7 @@
         <v>16</v>
       </c>
       <c r="E320" s="20">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F320" s="20" t="s">
         <v>48</v>
@@ -13613,7 +13613,7 @@
         <v>17</v>
       </c>
       <c r="E321" s="20">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F321" s="20" t="s">
         <v>49</v>
@@ -13650,7 +13650,7 @@
         <v>18</v>
       </c>
       <c r="E322" s="20">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F322" s="20" t="s">
         <v>50</v>
@@ -13690,7 +13690,7 @@
         <v>19</v>
       </c>
       <c r="E323" s="20">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F323" s="20" t="s">
         <v>51</v>
@@ -13730,7 +13730,7 @@
         <v>20</v>
       </c>
       <c r="E324" s="20">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F324" s="20" t="s">
         <v>52</v>
@@ -13770,7 +13770,7 @@
         <v>21</v>
       </c>
       <c r="E325" s="20">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="F325" s="20" t="s">
         <v>53</v>
@@ -13810,7 +13810,7 @@
         <v>22</v>
       </c>
       <c r="E326" s="20">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F326" s="20" t="s">
         <v>54</v>
@@ -13850,7 +13850,7 @@
         <v>23</v>
       </c>
       <c r="E327" s="20">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F327" s="20" t="s">
         <v>55</v>
@@ -13890,7 +13890,7 @@
         <v>24</v>
       </c>
       <c r="E328" s="20">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F328" s="20" t="s">
         <v>56</v>
@@ -13930,7 +13930,7 @@
         <v>25</v>
       </c>
       <c r="E329" s="20">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="F329" s="20" t="s">
         <v>57</v>
@@ -13966,7 +13966,7 @@
         <v>26</v>
       </c>
       <c r="E330" s="20">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F330" s="20" t="s">
         <v>58</v>
@@ -14002,7 +14002,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="20">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="F331" s="20" t="s">
         <v>59</v>
@@ -14038,7 +14038,7 @@
         <v>28</v>
       </c>
       <c r="E332" s="20">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F332" s="20" t="s">
         <v>60</v>
@@ -14074,7 +14074,7 @@
         <v>29</v>
       </c>
       <c r="E333" s="20">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>61</v>
@@ -14110,7 +14110,7 @@
         <v>30</v>
       </c>
       <c r="E334" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F334" s="20" t="s">
         <v>62</v>
@@ -14146,7 +14146,7 @@
         <v>31</v>
       </c>
       <c r="E335" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F335" s="20" t="s">
         <v>64</v>
@@ -14182,7 +14182,7 @@
         <v>32</v>
       </c>
       <c r="E336" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F336" s="20" t="s">
         <v>65</v>
@@ -14218,7 +14218,7 @@
         <v>33</v>
       </c>
       <c r="E337" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F337" s="20" t="s">
         <v>66</v>
@@ -14254,7 +14254,7 @@
         <v>34</v>
       </c>
       <c r="E338" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F338" s="20" t="s">
         <v>67</v>
@@ -14290,7 +14290,7 @@
         <v>35</v>
       </c>
       <c r="E339" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F339" s="20" t="s">
         <v>68</v>
@@ -14326,7 +14326,7 @@
         <v>36</v>
       </c>
       <c r="E340" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F340" s="20" t="s">
         <v>69</v>
@@ -14362,7 +14362,7 @@
         <v>37</v>
       </c>
       <c r="E341" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F341" s="20" t="s">
         <v>70</v>
@@ -14398,7 +14398,7 @@
         <v>38</v>
       </c>
       <c r="E342" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F342" s="20" t="s">
         <v>71</v>
@@ -14434,7 +14434,7 @@
         <v>39</v>
       </c>
       <c r="E343" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F343" s="20" t="s">
         <v>72</v>
@@ -14470,7 +14470,7 @@
         <v>40</v>
       </c>
       <c r="E344" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F344" s="20" t="s">
         <v>73</v>
@@ -14506,7 +14506,7 @@
         <v>41</v>
       </c>
       <c r="E345" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F345" s="20" t="s">
         <v>74</v>
@@ -14542,7 +14542,7 @@
         <v>42</v>
       </c>
       <c r="E346" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F346" s="20" t="s">
         <v>75</v>
@@ -14578,7 +14578,7 @@
         <v>43</v>
       </c>
       <c r="E347" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F347" s="20" t="s">
         <v>76</v>
@@ -14614,7 +14614,7 @@
         <v>44</v>
       </c>
       <c r="E348" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F348" s="20" t="s">
         <v>77</v>
@@ -14650,7 +14650,7 @@
         <v>45</v>
       </c>
       <c r="E349" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F349" s="20" t="s">
         <v>78</v>
@@ -14686,7 +14686,7 @@
         <v>46</v>
       </c>
       <c r="E350" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F350" s="20" t="s">
         <v>79</v>
@@ -14722,7 +14722,7 @@
         <v>47</v>
       </c>
       <c r="E351" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F351" s="20" t="s">
         <v>80</v>
@@ -14758,7 +14758,7 @@
         <v>48</v>
       </c>
       <c r="E352" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F352" s="20" t="s">
         <v>81</v>
@@ -14794,7 +14794,7 @@
         <v>49</v>
       </c>
       <c r="E353" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F353" s="20" t="s">
         <v>82</v>
@@ -14830,7 +14830,7 @@
         <v>50</v>
       </c>
       <c r="E354" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F354" s="20" t="s">
         <v>83</v>
@@ -14866,7 +14866,7 @@
         <v>51</v>
       </c>
       <c r="E355" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F355" s="20" t="s">
         <v>84</v>
@@ -14902,7 +14902,7 @@
         <v>52</v>
       </c>
       <c r="E356" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F356" s="20" t="s">
         <v>85</v>
@@ -14938,7 +14938,7 @@
         <v>53</v>
       </c>
       <c r="E357" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F357" s="20" t="s">
         <v>86</v>
@@ -14974,7 +14974,7 @@
         <v>54</v>
       </c>
       <c r="E358" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F358" s="20" t="s">
         <v>87</v>
@@ -15010,7 +15010,7 @@
         <v>55</v>
       </c>
       <c r="E359" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F359" s="20" t="s">
         <v>88</v>
@@ -15046,7 +15046,7 @@
         <v>56</v>
       </c>
       <c r="E360" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F360" s="20" t="s">
         <v>89</v>
@@ -15082,7 +15082,7 @@
         <v>57</v>
       </c>
       <c r="E361" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F361" s="20" t="s">
         <v>90</v>
@@ -15118,7 +15118,7 @@
         <v>58</v>
       </c>
       <c r="E362" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F362" s="20" t="s">
         <v>91</v>
@@ -15154,7 +15154,7 @@
         <v>59</v>
       </c>
       <c r="E363" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F363" s="20" t="s">
         <v>92</v>
@@ -15190,7 +15190,7 @@
         <v>60</v>
       </c>
       <c r="E364" s="20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F364" s="20" t="s">
         <v>93</v>
@@ -15224,7 +15224,7 @@
         <v>1</v>
       </c>
       <c r="E365" s="16">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F365" s="16" t="s">
         <v>31</v>
@@ -15264,7 +15264,7 @@
         <v>2</v>
       </c>
       <c r="E366" s="16">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F366" s="16" t="s">
         <v>34</v>
@@ -15304,7 +15304,7 @@
         <v>3</v>
       </c>
       <c r="E367" s="16">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F367" s="16" t="s">
         <v>35</v>
@@ -15344,7 +15344,7 @@
         <v>4</v>
       </c>
       <c r="E368" s="16">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F368" s="16" t="s">
         <v>36</v>
@@ -15384,7 +15384,7 @@
         <v>5</v>
       </c>
       <c r="E369" s="16">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F369" s="16" t="s">
         <v>37</v>
@@ -15424,7 +15424,7 @@
         <v>6</v>
       </c>
       <c r="E370" s="16">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F370" s="16" t="s">
         <v>38</v>
@@ -15464,7 +15464,7 @@
         <v>7</v>
       </c>
       <c r="E371" s="16">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F371" s="16" t="s">
         <v>39</v>
@@ -15504,7 +15504,7 @@
         <v>8</v>
       </c>
       <c r="E372" s="16">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F372" s="16" t="s">
         <v>40</v>
@@ -15544,7 +15544,7 @@
         <v>9</v>
       </c>
       <c r="E373" s="16">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F373" s="16" t="s">
         <v>41</v>
@@ -15584,7 +15584,7 @@
         <v>10</v>
       </c>
       <c r="E374" s="16">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F374" s="16" t="s">
         <v>42</v>
@@ -15624,7 +15624,7 @@
         <v>11</v>
       </c>
       <c r="E375" s="16">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F375" s="16" t="s">
         <v>43</v>
@@ -15664,7 +15664,7 @@
         <v>12</v>
       </c>
       <c r="E376" s="16">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F376" s="16" t="s">
         <v>44</v>
@@ -15704,7 +15704,7 @@
         <v>13</v>
       </c>
       <c r="E377" s="16">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F377" s="16" t="s">
         <v>45</v>
@@ -15744,7 +15744,7 @@
         <v>14</v>
       </c>
       <c r="E378" s="16">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F378" s="16" t="s">
         <v>46</v>
@@ -15784,7 +15784,7 @@
         <v>15</v>
       </c>
       <c r="E379" s="16">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F379" s="16" t="s">
         <v>47</v>
@@ -15824,7 +15824,7 @@
         <v>16</v>
       </c>
       <c r="E380" s="16">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F380" s="16" t="s">
         <v>48</v>
@@ -15861,7 +15861,7 @@
         <v>17</v>
       </c>
       <c r="E381" s="16">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F381" s="16" t="s">
         <v>49</v>
@@ -15898,7 +15898,7 @@
         <v>18</v>
       </c>
       <c r="E382" s="16">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F382" s="16" t="s">
         <v>50</v>
@@ -15935,7 +15935,7 @@
         <v>19</v>
       </c>
       <c r="E383" s="16">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F383" s="16" t="s">
         <v>51</v>
@@ -15975,7 +15975,7 @@
         <v>20</v>
       </c>
       <c r="E384" s="16">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F384" s="16" t="s">
         <v>52</v>
@@ -16015,7 +16015,7 @@
         <v>21</v>
       </c>
       <c r="E385" s="16">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F385" s="16" t="s">
         <v>53</v>
@@ -16055,7 +16055,7 @@
         <v>22</v>
       </c>
       <c r="E386" s="16">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F386" s="16" t="s">
         <v>54</v>
@@ -16095,7 +16095,7 @@
         <v>23</v>
       </c>
       <c r="E387" s="16">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F387" s="16" t="s">
         <v>55</v>
@@ -16135,7 +16135,7 @@
         <v>24</v>
       </c>
       <c r="E388" s="16">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F388" s="16" t="s">
         <v>56</v>
@@ -16175,7 +16175,7 @@
         <v>25</v>
       </c>
       <c r="E389" s="16">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F389" s="16" t="s">
         <v>57</v>
@@ -16209,7 +16209,7 @@
         <v>26</v>
       </c>
       <c r="E390" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F390" s="16" t="s">
         <v>58</v>
@@ -16243,7 +16243,7 @@
         <v>27</v>
       </c>
       <c r="E391" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F391" s="16" t="s">
         <v>59</v>
@@ -16277,7 +16277,7 @@
         <v>28</v>
       </c>
       <c r="E392" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F392" s="16" t="s">
         <v>60</v>
@@ -16311,7 +16311,7 @@
         <v>29</v>
       </c>
       <c r="E393" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F393" s="16" t="s">
         <v>61</v>
@@ -16345,7 +16345,7 @@
         <v>30</v>
       </c>
       <c r="E394" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F394" s="16" t="s">
         <v>62</v>
@@ -16379,7 +16379,7 @@
         <v>31</v>
       </c>
       <c r="E395" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F395" s="16" t="s">
         <v>64</v>
@@ -16413,7 +16413,7 @@
         <v>32</v>
       </c>
       <c r="E396" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F396" s="16" t="s">
         <v>65</v>
@@ -16447,7 +16447,7 @@
         <v>33</v>
       </c>
       <c r="E397" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F397" s="16" t="s">
         <v>66</v>
@@ -16481,7 +16481,7 @@
         <v>34</v>
       </c>
       <c r="E398" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F398" s="16" t="s">
         <v>67</v>
@@ -16515,7 +16515,7 @@
         <v>35</v>
       </c>
       <c r="E399" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F399" s="16" t="s">
         <v>68</v>
@@ -16549,7 +16549,7 @@
         <v>36</v>
       </c>
       <c r="E400" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F400" s="16" t="s">
         <v>69</v>
@@ -16583,7 +16583,7 @@
         <v>37</v>
       </c>
       <c r="E401" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F401" s="16" t="s">
         <v>70</v>
@@ -16617,7 +16617,7 @@
         <v>38</v>
       </c>
       <c r="E402" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F402" s="16" t="s">
         <v>71</v>
@@ -16651,7 +16651,7 @@
         <v>39</v>
       </c>
       <c r="E403" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F403" s="16" t="s">
         <v>72</v>
@@ -16685,7 +16685,7 @@
         <v>40</v>
       </c>
       <c r="E404" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F404" s="16" t="s">
         <v>73</v>
@@ -16719,7 +16719,7 @@
         <v>41</v>
       </c>
       <c r="E405" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F405" s="16" t="s">
         <v>74</v>
@@ -16753,7 +16753,7 @@
         <v>42</v>
       </c>
       <c r="E406" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F406" s="16" t="s">
         <v>75</v>
@@ -16787,7 +16787,7 @@
         <v>43</v>
       </c>
       <c r="E407" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F407" s="16" t="s">
         <v>76</v>
@@ -16821,7 +16821,7 @@
         <v>44</v>
       </c>
       <c r="E408" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F408" s="16" t="s">
         <v>77</v>
@@ -16855,7 +16855,7 @@
         <v>45</v>
       </c>
       <c r="E409" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F409" s="16" t="s">
         <v>78</v>
@@ -16889,7 +16889,7 @@
         <v>46</v>
       </c>
       <c r="E410" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F410" s="16" t="s">
         <v>79</v>
@@ -16923,7 +16923,7 @@
         <v>47</v>
       </c>
       <c r="E411" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F411" s="16" t="s">
         <v>80</v>
@@ -16957,7 +16957,7 @@
         <v>48</v>
       </c>
       <c r="E412" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F412" s="16" t="s">
         <v>81</v>
@@ -16991,7 +16991,7 @@
         <v>49</v>
       </c>
       <c r="E413" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F413" s="16" t="s">
         <v>82</v>
@@ -17025,7 +17025,7 @@
         <v>50</v>
       </c>
       <c r="E414" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F414" s="16" t="s">
         <v>83</v>
@@ -17059,7 +17059,7 @@
         <v>51</v>
       </c>
       <c r="E415" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F415" s="16" t="s">
         <v>84</v>
@@ -17093,7 +17093,7 @@
         <v>52</v>
       </c>
       <c r="E416" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F416" s="16" t="s">
         <v>85</v>
@@ -17127,7 +17127,7 @@
         <v>53</v>
       </c>
       <c r="E417" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F417" s="16" t="s">
         <v>86</v>
@@ -17161,7 +17161,7 @@
         <v>54</v>
       </c>
       <c r="E418" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F418" s="16" t="s">
         <v>87</v>
@@ -17195,7 +17195,7 @@
         <v>55</v>
       </c>
       <c r="E419" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F419" s="16" t="s">
         <v>88</v>
@@ -17229,7 +17229,7 @@
         <v>56</v>
       </c>
       <c r="E420" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F420" s="16" t="s">
         <v>89</v>
@@ -17263,7 +17263,7 @@
         <v>57</v>
       </c>
       <c r="E421" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F421" s="16" t="s">
         <v>90</v>
@@ -17297,7 +17297,7 @@
         <v>58</v>
       </c>
       <c r="E422" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F422" s="16" t="s">
         <v>91</v>
@@ -17331,7 +17331,7 @@
         <v>59</v>
       </c>
       <c r="E423" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F423" s="16" t="s">
         <v>92</v>
@@ -17365,7 +17365,7 @@
         <v>60</v>
       </c>
       <c r="E424" s="16">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F424" s="16" t="s">
         <v>93</v>
@@ -17397,7 +17397,7 @@
         <v>1</v>
       </c>
       <c r="E425" s="20">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F425" s="20" t="s">
         <v>31</v>
@@ -17437,7 +17437,7 @@
         <v>2</v>
       </c>
       <c r="E426" s="20">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F426" s="20" t="s">
         <v>34</v>
@@ -17477,7 +17477,7 @@
         <v>3</v>
       </c>
       <c r="E427" s="20">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F427" s="20" t="s">
         <v>35</v>
@@ -17517,7 +17517,7 @@
         <v>4</v>
       </c>
       <c r="E428" s="20">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F428" s="20" t="s">
         <v>36</v>
@@ -17557,7 +17557,7 @@
         <v>5</v>
       </c>
       <c r="E429" s="20">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F429" s="20" t="s">
         <v>37</v>
@@ -17597,7 +17597,7 @@
         <v>6</v>
       </c>
       <c r="E430" s="20">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F430" s="20" t="s">
         <v>38</v>
@@ -17637,7 +17637,7 @@
         <v>7</v>
       </c>
       <c r="E431" s="20">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F431" s="20" t="s">
         <v>39</v>
@@ -17677,7 +17677,7 @@
         <v>8</v>
       </c>
       <c r="E432" s="20">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F432" s="20" t="s">
         <v>40</v>
@@ -17717,7 +17717,7 @@
         <v>9</v>
       </c>
       <c r="E433" s="20">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F433" s="20" t="s">
         <v>41</v>
@@ -17757,7 +17757,7 @@
         <v>10</v>
       </c>
       <c r="E434" s="20">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F434" s="20" t="s">
         <v>42</v>
@@ -17797,7 +17797,7 @@
         <v>11</v>
       </c>
       <c r="E435" s="20">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F435" s="20" t="s">
         <v>43</v>
@@ -17837,7 +17837,7 @@
         <v>12</v>
       </c>
       <c r="E436" s="20">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F436" s="20" t="s">
         <v>44</v>
@@ -17877,7 +17877,7 @@
         <v>13</v>
       </c>
       <c r="E437" s="20">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F437" s="20" t="s">
         <v>45</v>
@@ -17917,7 +17917,7 @@
         <v>14</v>
       </c>
       <c r="E438" s="20">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F438" s="20" t="s">
         <v>46</v>
@@ -17957,7 +17957,7 @@
         <v>15</v>
       </c>
       <c r="E439" s="20">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F439" s="20" t="s">
         <v>47</v>
@@ -17997,7 +17997,7 @@
         <v>16</v>
       </c>
       <c r="E440" s="20">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F440" s="20" t="s">
         <v>48</v>
@@ -18034,7 +18034,7 @@
         <v>17</v>
       </c>
       <c r="E441" s="20">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F441" s="20" t="s">
         <v>49</v>
@@ -18071,7 +18071,7 @@
         <v>18</v>
       </c>
       <c r="E442" s="20">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F442" s="20" t="s">
         <v>50</v>
@@ -18108,7 +18108,7 @@
         <v>19</v>
       </c>
       <c r="E443" s="20">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F443" s="20" t="s">
         <v>51</v>
@@ -18148,7 +18148,7 @@
         <v>20</v>
       </c>
       <c r="E444" s="20">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F444" s="20" t="s">
         <v>52</v>
@@ -18188,7 +18188,7 @@
         <v>21</v>
       </c>
       <c r="E445" s="20">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F445" s="20" t="s">
         <v>53</v>
@@ -18228,7 +18228,7 @@
         <v>22</v>
       </c>
       <c r="E446" s="20">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F446" s="20" t="s">
         <v>54</v>
@@ -18268,7 +18268,7 @@
         <v>23</v>
       </c>
       <c r="E447" s="20">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F447" s="20" t="s">
         <v>55</v>
@@ -18308,7 +18308,7 @@
         <v>24</v>
       </c>
       <c r="E448" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F448" s="20" t="s">
         <v>56</v>
@@ -18348,7 +18348,7 @@
         <v>25</v>
       </c>
       <c r="E449" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F449" s="20" t="s">
         <v>57</v>
@@ -18384,7 +18384,7 @@
         <v>26</v>
       </c>
       <c r="E450" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F450" s="20" t="s">
         <v>58</v>
@@ -18420,7 +18420,7 @@
         <v>27</v>
       </c>
       <c r="E451" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F451" s="20" t="s">
         <v>59</v>
@@ -18456,7 +18456,7 @@
         <v>28</v>
       </c>
       <c r="E452" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F452" s="20" t="s">
         <v>60</v>
@@ -18492,7 +18492,7 @@
         <v>29</v>
       </c>
       <c r="E453" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F453" s="20" t="s">
         <v>61</v>
@@ -18528,7 +18528,7 @@
         <v>30</v>
       </c>
       <c r="E454" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F454" s="20" t="s">
         <v>62</v>
@@ -18564,7 +18564,7 @@
         <v>31</v>
       </c>
       <c r="E455" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F455" s="20" t="s">
         <v>64</v>
@@ -18600,7 +18600,7 @@
         <v>32</v>
       </c>
       <c r="E456" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F456" s="20" t="s">
         <v>65</v>
@@ -18636,7 +18636,7 @@
         <v>33</v>
       </c>
       <c r="E457" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F457" s="20" t="s">
         <v>66</v>
@@ -18672,7 +18672,7 @@
         <v>34</v>
       </c>
       <c r="E458" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F458" s="20" t="s">
         <v>67</v>
@@ -18708,7 +18708,7 @@
         <v>35</v>
       </c>
       <c r="E459" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F459" s="20" t="s">
         <v>68</v>
@@ -18744,7 +18744,7 @@
         <v>36</v>
       </c>
       <c r="E460" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F460" s="20" t="s">
         <v>69</v>
@@ -18780,7 +18780,7 @@
         <v>37</v>
       </c>
       <c r="E461" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F461" s="20" t="s">
         <v>70</v>
@@ -18816,7 +18816,7 @@
         <v>38</v>
       </c>
       <c r="E462" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F462" s="20" t="s">
         <v>71</v>
@@ -18852,7 +18852,7 @@
         <v>39</v>
       </c>
       <c r="E463" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F463" s="20" t="s">
         <v>72</v>
@@ -18888,7 +18888,7 @@
         <v>40</v>
       </c>
       <c r="E464" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F464" s="20" t="s">
         <v>73</v>
@@ -18924,7 +18924,7 @@
         <v>41</v>
       </c>
       <c r="E465" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F465" s="20" t="s">
         <v>74</v>
@@ -18960,7 +18960,7 @@
         <v>42</v>
       </c>
       <c r="E466" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F466" s="20" t="s">
         <v>75</v>
@@ -18996,7 +18996,7 @@
         <v>43</v>
       </c>
       <c r="E467" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F467" s="20" t="s">
         <v>76</v>
@@ -19032,7 +19032,7 @@
         <v>44</v>
       </c>
       <c r="E468" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F468" s="20" t="s">
         <v>77</v>
@@ -19068,7 +19068,7 @@
         <v>45</v>
       </c>
       <c r="E469" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F469" s="20" t="s">
         <v>78</v>
@@ -19104,7 +19104,7 @@
         <v>46</v>
       </c>
       <c r="E470" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F470" s="20" t="s">
         <v>79</v>
@@ -19140,7 +19140,7 @@
         <v>47</v>
       </c>
       <c r="E471" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F471" s="20" t="s">
         <v>80</v>
@@ -19176,7 +19176,7 @@
         <v>48</v>
       </c>
       <c r="E472" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F472" s="20" t="s">
         <v>81</v>
@@ -19212,7 +19212,7 @@
         <v>49</v>
       </c>
       <c r="E473" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F473" s="20" t="s">
         <v>82</v>
@@ -19248,7 +19248,7 @@
         <v>50</v>
       </c>
       <c r="E474" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F474" s="20" t="s">
         <v>83</v>
@@ -19284,7 +19284,7 @@
         <v>51</v>
       </c>
       <c r="E475" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F475" s="20" t="s">
         <v>84</v>
@@ -19320,7 +19320,7 @@
         <v>52</v>
       </c>
       <c r="E476" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F476" s="20" t="s">
         <v>85</v>
@@ -19356,7 +19356,7 @@
         <v>53</v>
       </c>
       <c r="E477" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F477" s="20" t="s">
         <v>86</v>
@@ -19392,7 +19392,7 @@
         <v>54</v>
       </c>
       <c r="E478" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F478" s="20" t="s">
         <v>87</v>
@@ -19428,7 +19428,7 @@
         <v>55</v>
       </c>
       <c r="E479" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F479" s="20" t="s">
         <v>88</v>
@@ -19464,7 +19464,7 @@
         <v>56</v>
       </c>
       <c r="E480" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F480" s="20" t="s">
         <v>89</v>
@@ -19500,7 +19500,7 @@
         <v>57</v>
       </c>
       <c r="E481" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F481" s="20" t="s">
         <v>90</v>
@@ -19536,7 +19536,7 @@
         <v>58</v>
       </c>
       <c r="E482" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F482" s="20" t="s">
         <v>91</v>
@@ -19572,7 +19572,7 @@
         <v>59</v>
       </c>
       <c r="E483" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F483" s="20" t="s">
         <v>92</v>
@@ -19608,7 +19608,7 @@
         <v>60</v>
       </c>
       <c r="E484" s="20">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F484" s="20" t="s">
         <v>93</v>
@@ -19642,7 +19642,7 @@
         <v>1</v>
       </c>
       <c r="E485" s="16">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F485" s="16" t="s">
         <v>31</v>
@@ -19682,7 +19682,7 @@
         <v>2</v>
       </c>
       <c r="E486" s="16">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F486" s="16" t="s">
         <v>34</v>
@@ -19722,7 +19722,7 @@
         <v>3</v>
       </c>
       <c r="E487" s="16">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F487" s="16" t="s">
         <v>35</v>
@@ -19762,7 +19762,7 @@
         <v>4</v>
       </c>
       <c r="E488" s="16">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F488" s="16" t="s">
         <v>36</v>
@@ -19802,7 +19802,7 @@
         <v>5</v>
       </c>
       <c r="E489" s="16">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F489" s="16" t="s">
         <v>37</v>
@@ -19842,7 +19842,7 @@
         <v>6</v>
       </c>
       <c r="E490" s="16">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F490" s="16" t="s">
         <v>38</v>
@@ -19882,7 +19882,7 @@
         <v>7</v>
       </c>
       <c r="E491" s="16">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F491" s="16" t="s">
         <v>39</v>
@@ -19922,7 +19922,7 @@
         <v>8</v>
       </c>
       <c r="E492" s="16">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F492" s="16" t="s">
         <v>40</v>
@@ -19962,7 +19962,7 @@
         <v>9</v>
       </c>
       <c r="E493" s="16">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F493" s="16" t="s">
         <v>41</v>
@@ -20002,7 +20002,7 @@
         <v>10</v>
       </c>
       <c r="E494" s="16">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F494" s="16" t="s">
         <v>42</v>
@@ -20042,7 +20042,7 @@
         <v>11</v>
       </c>
       <c r="E495" s="16">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F495" s="16" t="s">
         <v>43</v>
@@ -20082,7 +20082,7 @@
         <v>12</v>
       </c>
       <c r="E496" s="16">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F496" s="16" t="s">
         <v>44</v>
@@ -20122,7 +20122,7 @@
         <v>13</v>
       </c>
       <c r="E497" s="16">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F497" s="16" t="s">
         <v>45</v>
@@ -20162,7 +20162,7 @@
         <v>14</v>
       </c>
       <c r="E498" s="16">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F498" s="16" t="s">
         <v>46</v>
@@ -20202,7 +20202,7 @@
         <v>15</v>
       </c>
       <c r="E499" s="16">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F499" s="16" t="s">
         <v>47</v>
@@ -20242,7 +20242,7 @@
         <v>16</v>
       </c>
       <c r="E500" s="16">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F500" s="16" t="s">
         <v>48</v>
@@ -20282,7 +20282,7 @@
         <v>17</v>
       </c>
       <c r="E501" s="16">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F501" s="16" t="s">
         <v>49</v>
@@ -20322,7 +20322,7 @@
         <v>18</v>
       </c>
       <c r="E502" s="16">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F502" s="16" t="s">
         <v>50</v>
@@ -20362,7 +20362,7 @@
         <v>19</v>
       </c>
       <c r="E503" s="16">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F503" s="16" t="s">
         <v>51</v>
@@ -20402,7 +20402,7 @@
         <v>20</v>
       </c>
       <c r="E504" s="16">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F504" s="16" t="s">
         <v>52</v>
@@ -20439,7 +20439,7 @@
         <v>21</v>
       </c>
       <c r="E505" s="16">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F505" s="16" t="s">
         <v>53</v>
@@ -20479,7 +20479,7 @@
         <v>22</v>
       </c>
       <c r="E506" s="16">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F506" s="16" t="s">
         <v>54</v>
@@ -20519,7 +20519,7 @@
         <v>23</v>
       </c>
       <c r="E507" s="16">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F507" s="16" t="s">
         <v>55</v>
@@ -20559,7 +20559,7 @@
         <v>24</v>
       </c>
       <c r="E508" s="16">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F508" s="16" t="s">
         <v>56</v>
@@ -20599,7 +20599,7 @@
         <v>25</v>
       </c>
       <c r="E509" s="16">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F509" s="16" t="s">
         <v>57</v>
@@ -20633,7 +20633,7 @@
         <v>26</v>
       </c>
       <c r="E510" s="16">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F510" s="16" t="s">
         <v>58</v>
@@ -20667,7 +20667,7 @@
         <v>27</v>
       </c>
       <c r="E511" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F511" s="16" t="s">
         <v>59</v>
@@ -20701,7 +20701,7 @@
         <v>28</v>
       </c>
       <c r="E512" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F512" s="16" t="s">
         <v>60</v>
@@ -20735,7 +20735,7 @@
         <v>29</v>
       </c>
       <c r="E513" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F513" s="16" t="s">
         <v>61</v>
@@ -20769,7 +20769,7 @@
         <v>30</v>
       </c>
       <c r="E514" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F514" s="16" t="s">
         <v>62</v>
@@ -20803,7 +20803,7 @@
         <v>31</v>
       </c>
       <c r="E515" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F515" s="16" t="s">
         <v>64</v>
@@ -20837,7 +20837,7 @@
         <v>32</v>
       </c>
       <c r="E516" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F516" s="16" t="s">
         <v>65</v>
@@ -20871,7 +20871,7 @@
         <v>33</v>
       </c>
       <c r="E517" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F517" s="16" t="s">
         <v>66</v>
@@ -20905,7 +20905,7 @@
         <v>34</v>
       </c>
       <c r="E518" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F518" s="16" t="s">
         <v>67</v>
@@ -20939,7 +20939,7 @@
         <v>35</v>
       </c>
       <c r="E519" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F519" s="16" t="s">
         <v>68</v>
@@ -20973,7 +20973,7 @@
         <v>36</v>
       </c>
       <c r="E520" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F520" s="16" t="s">
         <v>69</v>
@@ -21007,7 +21007,7 @@
         <v>37</v>
       </c>
       <c r="E521" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F521" s="16" t="s">
         <v>70</v>
@@ -21041,7 +21041,7 @@
         <v>38</v>
       </c>
       <c r="E522" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F522" s="16" t="s">
         <v>71</v>
@@ -21075,7 +21075,7 @@
         <v>39</v>
       </c>
       <c r="E523" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F523" s="16" t="s">
         <v>72</v>
@@ -21109,7 +21109,7 @@
         <v>40</v>
       </c>
       <c r="E524" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F524" s="16" t="s">
         <v>73</v>
@@ -21143,7 +21143,7 @@
         <v>41</v>
       </c>
       <c r="E525" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F525" s="16" t="s">
         <v>74</v>
@@ -21177,7 +21177,7 @@
         <v>42</v>
       </c>
       <c r="E526" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F526" s="16" t="s">
         <v>75</v>
@@ -21211,7 +21211,7 @@
         <v>43</v>
       </c>
       <c r="E527" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F527" s="16" t="s">
         <v>76</v>
@@ -21245,7 +21245,7 @@
         <v>44</v>
       </c>
       <c r="E528" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F528" s="16" t="s">
         <v>77</v>
@@ -21279,7 +21279,7 @@
         <v>45</v>
       </c>
       <c r="E529" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F529" s="16" t="s">
         <v>78</v>
@@ -21313,7 +21313,7 @@
         <v>46</v>
       </c>
       <c r="E530" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F530" s="16" t="s">
         <v>79</v>
@@ -21347,7 +21347,7 @@
         <v>47</v>
       </c>
       <c r="E531" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F531" s="16" t="s">
         <v>80</v>
@@ -21381,7 +21381,7 @@
         <v>48</v>
       </c>
       <c r="E532" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F532" s="16" t="s">
         <v>81</v>
@@ -21415,7 +21415,7 @@
         <v>49</v>
       </c>
       <c r="E533" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F533" s="16" t="s">
         <v>82</v>
@@ -21449,7 +21449,7 @@
         <v>50</v>
       </c>
       <c r="E534" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F534" s="16" t="s">
         <v>83</v>
@@ -21483,7 +21483,7 @@
         <v>51</v>
       </c>
       <c r="E535" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F535" s="16" t="s">
         <v>84</v>
@@ -21517,7 +21517,7 @@
         <v>52</v>
       </c>
       <c r="E536" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F536" s="16" t="s">
         <v>85</v>
@@ -21551,7 +21551,7 @@
         <v>53</v>
       </c>
       <c r="E537" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F537" s="16" t="s">
         <v>86</v>
@@ -21585,7 +21585,7 @@
         <v>54</v>
       </c>
       <c r="E538" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F538" s="16" t="s">
         <v>87</v>
@@ -21619,7 +21619,7 @@
         <v>55</v>
       </c>
       <c r="E539" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F539" s="16" t="s">
         <v>88</v>
@@ -21653,7 +21653,7 @@
         <v>56</v>
       </c>
       <c r="E540" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F540" s="16" t="s">
         <v>89</v>
@@ -21687,7 +21687,7 @@
         <v>57</v>
       </c>
       <c r="E541" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F541" s="16" t="s">
         <v>90</v>
@@ -21721,7 +21721,7 @@
         <v>58</v>
       </c>
       <c r="E542" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F542" s="16" t="s">
         <v>91</v>
@@ -21755,7 +21755,7 @@
         <v>59</v>
       </c>
       <c r="E543" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F543" s="16" t="s">
         <v>92</v>
@@ -21789,7 +21789,7 @@
         <v>60</v>
       </c>
       <c r="E544" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F544" s="16" t="s">
         <v>93</v>
@@ -21821,7 +21821,7 @@
         <v>1</v>
       </c>
       <c r="E545" s="20">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F545" s="20" t="s">
         <v>31</v>
@@ -21861,7 +21861,7 @@
         <v>2</v>
       </c>
       <c r="E546" s="20">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F546" s="20" t="s">
         <v>34</v>
@@ -21901,7 +21901,7 @@
         <v>3</v>
       </c>
       <c r="E547" s="20">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F547" s="20" t="s">
         <v>35</v>
@@ -21941,7 +21941,7 @@
         <v>4</v>
       </c>
       <c r="E548" s="20">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F548" s="20" t="s">
         <v>36</v>
@@ -21981,7 +21981,7 @@
         <v>5</v>
       </c>
       <c r="E549" s="20">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F549" s="20" t="s">
         <v>37</v>
@@ -22021,7 +22021,7 @@
         <v>6</v>
       </c>
       <c r="E550" s="20">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F550" s="20" t="s">
         <v>38</v>
@@ -22061,7 +22061,7 @@
         <v>7</v>
       </c>
       <c r="E551" s="20">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F551" s="20" t="s">
         <v>39</v>
@@ -22101,7 +22101,7 @@
         <v>8</v>
       </c>
       <c r="E552" s="20">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F552" s="20" t="s">
         <v>40</v>
@@ -22141,7 +22141,7 @@
         <v>9</v>
       </c>
       <c r="E553" s="20">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F553" s="20" t="s">
         <v>41</v>
@@ -22181,7 +22181,7 @@
         <v>10</v>
       </c>
       <c r="E554" s="20">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F554" s="20" t="s">
         <v>42</v>
@@ -22221,7 +22221,7 @@
         <v>11</v>
       </c>
       <c r="E555" s="20">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F555" s="20" t="s">
         <v>43</v>
@@ -22261,7 +22261,7 @@
         <v>12</v>
       </c>
       <c r="E556" s="20">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F556" s="20" t="s">
         <v>44</v>
@@ -22301,7 +22301,7 @@
         <v>13</v>
       </c>
       <c r="E557" s="20">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F557" s="20" t="s">
         <v>45</v>
@@ -22341,7 +22341,7 @@
         <v>14</v>
       </c>
       <c r="E558" s="20">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F558" s="20" t="s">
         <v>46</v>
@@ -22381,7 +22381,7 @@
         <v>15</v>
       </c>
       <c r="E559" s="20">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="F559" s="20" t="s">
         <v>47</v>
@@ -22421,7 +22421,7 @@
         <v>16</v>
       </c>
       <c r="E560" s="20">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F560" s="20" t="s">
         <v>48</v>
@@ -22458,7 +22458,7 @@
         <v>17</v>
       </c>
       <c r="E561" s="20">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F561" s="20" t="s">
         <v>49</v>
@@ -22495,7 +22495,7 @@
         <v>18</v>
       </c>
       <c r="E562" s="20">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F562" s="20" t="s">
         <v>50</v>
@@ -22532,7 +22532,7 @@
         <v>19</v>
       </c>
       <c r="E563" s="20">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F563" s="20" t="s">
         <v>51</v>
@@ -22569,7 +22569,7 @@
         <v>20</v>
       </c>
       <c r="E564" s="20">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F564" s="20" t="s">
         <v>52</v>
@@ -22606,7 +22606,7 @@
         <v>21</v>
       </c>
       <c r="E565" s="20">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F565" s="20" t="s">
         <v>53</v>
@@ -22646,7 +22646,7 @@
         <v>22</v>
       </c>
       <c r="E566" s="20">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F566" s="20" t="s">
         <v>54</v>
@@ -22686,7 +22686,7 @@
         <v>23</v>
       </c>
       <c r="E567" s="20">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F567" s="20" t="s">
         <v>55</v>
@@ -22726,7 +22726,7 @@
         <v>24</v>
       </c>
       <c r="E568" s="20">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F568" s="20" t="s">
         <v>56</v>
@@ -22766,7 +22766,7 @@
         <v>25</v>
       </c>
       <c r="E569" s="20">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="F569" s="20" t="s">
         <v>57</v>
@@ -22802,7 +22802,7 @@
         <v>26</v>
       </c>
       <c r="E570" s="20">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F570" s="20" t="s">
         <v>58</v>
@@ -22838,7 +22838,7 @@
         <v>27</v>
       </c>
       <c r="E571" s="20">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="F571" s="20" t="s">
         <v>59</v>
@@ -22874,7 +22874,7 @@
         <v>28</v>
       </c>
       <c r="E572" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F572" s="20" t="s">
         <v>60</v>
@@ -22910,7 +22910,7 @@
         <v>29</v>
       </c>
       <c r="E573" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F573" s="20" t="s">
         <v>61</v>
@@ -22946,7 +22946,7 @@
         <v>30</v>
       </c>
       <c r="E574" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F574" s="20" t="s">
         <v>62</v>
@@ -22982,7 +22982,7 @@
         <v>31</v>
       </c>
       <c r="E575" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F575" s="20" t="s">
         <v>64</v>
@@ -23018,7 +23018,7 @@
         <v>32</v>
       </c>
       <c r="E576" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F576" s="20" t="s">
         <v>65</v>
@@ -23054,7 +23054,7 @@
         <v>33</v>
       </c>
       <c r="E577" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F577" s="20" t="s">
         <v>66</v>
@@ -23090,7 +23090,7 @@
         <v>34</v>
       </c>
       <c r="E578" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F578" s="20" t="s">
         <v>67</v>
@@ -23126,7 +23126,7 @@
         <v>35</v>
       </c>
       <c r="E579" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F579" s="20" t="s">
         <v>68</v>
@@ -23162,7 +23162,7 @@
         <v>36</v>
       </c>
       <c r="E580" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F580" s="20" t="s">
         <v>69</v>
@@ -23198,7 +23198,7 @@
         <v>37</v>
       </c>
       <c r="E581" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F581" s="20" t="s">
         <v>70</v>
@@ -23234,7 +23234,7 @@
         <v>38</v>
       </c>
       <c r="E582" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F582" s="20" t="s">
         <v>71</v>
@@ -23270,7 +23270,7 @@
         <v>39</v>
       </c>
       <c r="E583" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F583" s="20" t="s">
         <v>72</v>
@@ -23306,7 +23306,7 @@
         <v>40</v>
       </c>
       <c r="E584" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F584" s="20" t="s">
         <v>73</v>
@@ -23342,7 +23342,7 @@
         <v>41</v>
       </c>
       <c r="E585" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F585" s="20" t="s">
         <v>74</v>
@@ -23378,7 +23378,7 @@
         <v>42</v>
       </c>
       <c r="E586" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F586" s="20" t="s">
         <v>75</v>
@@ -23414,7 +23414,7 @@
         <v>43</v>
       </c>
       <c r="E587" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F587" s="20" t="s">
         <v>76</v>
@@ -23450,7 +23450,7 @@
         <v>44</v>
       </c>
       <c r="E588" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F588" s="20" t="s">
         <v>77</v>
@@ -23486,7 +23486,7 @@
         <v>45</v>
       </c>
       <c r="E589" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F589" s="20" t="s">
         <v>78</v>
@@ -23522,7 +23522,7 @@
         <v>46</v>
       </c>
       <c r="E590" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F590" s="20" t="s">
         <v>79</v>
@@ -23558,7 +23558,7 @@
         <v>47</v>
       </c>
       <c r="E591" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F591" s="20" t="s">
         <v>80</v>
@@ -23594,7 +23594,7 @@
         <v>48</v>
       </c>
       <c r="E592" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F592" s="20" t="s">
         <v>81</v>
@@ -23630,7 +23630,7 @@
         <v>49</v>
       </c>
       <c r="E593" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F593" s="20" t="s">
         <v>82</v>
@@ -23666,7 +23666,7 @@
         <v>50</v>
       </c>
       <c r="E594" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F594" s="20" t="s">
         <v>83</v>
@@ -23702,7 +23702,7 @@
         <v>51</v>
       </c>
       <c r="E595" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F595" s="20" t="s">
         <v>84</v>
@@ -23738,7 +23738,7 @@
         <v>52</v>
       </c>
       <c r="E596" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F596" s="20" t="s">
         <v>85</v>
@@ -23774,7 +23774,7 @@
         <v>53</v>
       </c>
       <c r="E597" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F597" s="20" t="s">
         <v>86</v>
@@ -23810,7 +23810,7 @@
         <v>54</v>
       </c>
       <c r="E598" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F598" s="20" t="s">
         <v>87</v>
@@ -23846,7 +23846,7 @@
         <v>55</v>
       </c>
       <c r="E599" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F599" s="20" t="s">
         <v>88</v>
@@ -23882,7 +23882,7 @@
         <v>56</v>
       </c>
       <c r="E600" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F600" s="20" t="s">
         <v>89</v>
@@ -23918,7 +23918,7 @@
         <v>57</v>
       </c>
       <c r="E601" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F601" s="20" t="s">
         <v>90</v>
@@ -23954,7 +23954,7 @@
         <v>58</v>
       </c>
       <c r="E602" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F602" s="20" t="s">
         <v>91</v>
@@ -23990,7 +23990,7 @@
         <v>59</v>
       </c>
       <c r="E603" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F603" s="20" t="s">
         <v>92</v>
@@ -24026,7 +24026,7 @@
         <v>60</v>
       </c>
       <c r="E604" s="20">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F604" s="20" t="s">
         <v>93</v>
@@ -24060,7 +24060,7 @@
         <v>1</v>
       </c>
       <c r="E605" s="16">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F605" s="16" t="s">
         <v>31</v>
@@ -24100,7 +24100,7 @@
         <v>2</v>
       </c>
       <c r="E606" s="16">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F606" s="16" t="s">
         <v>34</v>
@@ -24140,7 +24140,7 @@
         <v>3</v>
       </c>
       <c r="E607" s="16">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F607" s="16" t="s">
         <v>35</v>
@@ -24180,7 +24180,7 @@
         <v>4</v>
       </c>
       <c r="E608" s="16">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F608" s="16" t="s">
         <v>36</v>
@@ -24220,7 +24220,7 @@
         <v>5</v>
       </c>
       <c r="E609" s="16">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F609" s="16" t="s">
         <v>37</v>
@@ -24260,7 +24260,7 @@
         <v>6</v>
       </c>
       <c r="E610" s="16">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F610" s="16" t="s">
         <v>38</v>
@@ -24300,7 +24300,7 @@
         <v>7</v>
       </c>
       <c r="E611" s="16">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F611" s="16" t="s">
         <v>39</v>
@@ -24340,7 +24340,7 @@
         <v>8</v>
       </c>
       <c r="E612" s="16">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F612" s="16" t="s">
         <v>40</v>
@@ -24380,7 +24380,7 @@
         <v>9</v>
       </c>
       <c r="E613" s="16">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F613" s="16" t="s">
         <v>41</v>
@@ -24420,7 +24420,7 @@
         <v>10</v>
       </c>
       <c r="E614" s="16">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F614" s="16" t="s">
         <v>42</v>
@@ -24460,7 +24460,7 @@
         <v>11</v>
       </c>
       <c r="E615" s="16">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F615" s="16" t="s">
         <v>43</v>
@@ -24500,7 +24500,7 @@
         <v>12</v>
       </c>
       <c r="E616" s="16">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F616" s="16" t="s">
         <v>44</v>
@@ -24540,7 +24540,7 @@
         <v>13</v>
       </c>
       <c r="E617" s="16">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F617" s="16" t="s">
         <v>45</v>
@@ -24580,7 +24580,7 @@
         <v>14</v>
       </c>
       <c r="E618" s="16">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F618" s="16" t="s">
         <v>46</v>
@@ -24620,7 +24620,7 @@
         <v>15</v>
       </c>
       <c r="E619" s="16">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F619" s="16" t="s">
         <v>47</v>
@@ -24660,7 +24660,7 @@
         <v>16</v>
       </c>
       <c r="E620" s="16">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F620" s="16" t="s">
         <v>48</v>
@@ -24700,7 +24700,7 @@
         <v>17</v>
       </c>
       <c r="E621" s="16">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F621" s="16" t="s">
         <v>49</v>
@@ -24740,7 +24740,7 @@
         <v>18</v>
       </c>
       <c r="E622" s="16">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F622" s="16" t="s">
         <v>50</v>
@@ -24780,7 +24780,7 @@
         <v>19</v>
       </c>
       <c r="E623" s="16">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F623" s="16" t="s">
         <v>51</v>
@@ -24817,7 +24817,7 @@
         <v>20</v>
       </c>
       <c r="E624" s="16">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F624" s="16" t="s">
         <v>52</v>
@@ -24854,7 +24854,7 @@
         <v>21</v>
       </c>
       <c r="E625" s="16">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F625" s="16" t="s">
         <v>53</v>
@@ -24891,7 +24891,7 @@
         <v>22</v>
       </c>
       <c r="E626" s="16">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F626" s="16" t="s">
         <v>54</v>
@@ -24931,7 +24931,7 @@
         <v>23</v>
       </c>
       <c r="E627" s="16">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F627" s="16" t="s">
         <v>55</v>
@@ -24971,7 +24971,7 @@
         <v>24</v>
       </c>
       <c r="E628" s="16">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F628" s="16" t="s">
         <v>56</v>
@@ -25011,7 +25011,7 @@
         <v>25</v>
       </c>
       <c r="E629" s="16">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F629" s="16" t="s">
         <v>57</v>
@@ -25047,7 +25047,7 @@
         <v>26</v>
       </c>
       <c r="E630" s="16">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F630" s="16" t="s">
         <v>58</v>
@@ -25083,7 +25083,7 @@
         <v>27</v>
       </c>
       <c r="E631" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F631" s="16" t="s">
         <v>59</v>
@@ -25119,7 +25119,7 @@
         <v>28</v>
       </c>
       <c r="E632" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F632" s="16" t="s">
         <v>60</v>
@@ -25155,7 +25155,7 @@
         <v>29</v>
       </c>
       <c r="E633" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F633" s="16" t="s">
         <v>61</v>
@@ -25191,7 +25191,7 @@
         <v>30</v>
       </c>
       <c r="E634" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F634" s="16" t="s">
         <v>62</v>
@@ -25227,7 +25227,7 @@
         <v>31</v>
       </c>
       <c r="E635" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F635" s="16" t="s">
         <v>64</v>
@@ -25263,7 +25263,7 @@
         <v>32</v>
       </c>
       <c r="E636" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F636" s="16" t="s">
         <v>65</v>
@@ -25299,7 +25299,7 @@
         <v>33</v>
       </c>
       <c r="E637" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F637" s="16" t="s">
         <v>66</v>
@@ -25335,7 +25335,7 @@
         <v>34</v>
       </c>
       <c r="E638" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F638" s="16" t="s">
         <v>67</v>
@@ -25371,7 +25371,7 @@
         <v>35</v>
       </c>
       <c r="E639" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F639" s="16" t="s">
         <v>68</v>
@@ -25407,7 +25407,7 @@
         <v>36</v>
       </c>
       <c r="E640" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F640" s="16" t="s">
         <v>69</v>
@@ -25443,7 +25443,7 @@
         <v>37</v>
       </c>
       <c r="E641" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F641" s="16" t="s">
         <v>70</v>
@@ -25479,7 +25479,7 @@
         <v>38</v>
       </c>
       <c r="E642" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F642" s="16" t="s">
         <v>71</v>
@@ -25515,7 +25515,7 @@
         <v>39</v>
       </c>
       <c r="E643" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F643" s="16" t="s">
         <v>72</v>
@@ -25551,7 +25551,7 @@
         <v>40</v>
       </c>
       <c r="E644" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F644" s="16" t="s">
         <v>73</v>
@@ -25587,7 +25587,7 @@
         <v>41</v>
       </c>
       <c r="E645" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F645" s="16" t="s">
         <v>74</v>
@@ -25623,7 +25623,7 @@
         <v>42</v>
       </c>
       <c r="E646" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F646" s="16" t="s">
         <v>75</v>
@@ -25659,7 +25659,7 @@
         <v>43</v>
       </c>
       <c r="E647" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F647" s="16" t="s">
         <v>76</v>
@@ -25695,7 +25695,7 @@
         <v>44</v>
       </c>
       <c r="E648" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F648" s="16" t="s">
         <v>77</v>
@@ -25731,7 +25731,7 @@
         <v>45</v>
       </c>
       <c r="E649" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F649" s="16" t="s">
         <v>78</v>
@@ -25767,7 +25767,7 @@
         <v>46</v>
       </c>
       <c r="E650" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F650" s="16" t="s">
         <v>79</v>
@@ -25803,7 +25803,7 @@
         <v>47</v>
       </c>
       <c r="E651" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F651" s="16" t="s">
         <v>80</v>
@@ -25839,7 +25839,7 @@
         <v>48</v>
       </c>
       <c r="E652" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F652" s="16" t="s">
         <v>81</v>
@@ -25875,7 +25875,7 @@
         <v>49</v>
       </c>
       <c r="E653" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F653" s="16" t="s">
         <v>82</v>
@@ -25911,7 +25911,7 @@
         <v>50</v>
       </c>
       <c r="E654" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F654" s="16" t="s">
         <v>83</v>
@@ -25947,7 +25947,7 @@
         <v>51</v>
       </c>
       <c r="E655" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F655" s="16" t="s">
         <v>84</v>
@@ -25983,7 +25983,7 @@
         <v>52</v>
       </c>
       <c r="E656" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F656" s="16" t="s">
         <v>85</v>
@@ -26019,7 +26019,7 @@
         <v>53</v>
       </c>
       <c r="E657" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F657" s="16" t="s">
         <v>86</v>
@@ -26055,7 +26055,7 @@
         <v>54</v>
       </c>
       <c r="E658" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F658" s="16" t="s">
         <v>87</v>
@@ -26091,7 +26091,7 @@
         <v>55</v>
       </c>
       <c r="E659" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F659" s="16" t="s">
         <v>88</v>
@@ -26127,7 +26127,7 @@
         <v>56</v>
       </c>
       <c r="E660" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F660" s="16" t="s">
         <v>89</v>
@@ -26163,7 +26163,7 @@
         <v>57</v>
       </c>
       <c r="E661" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F661" s="16" t="s">
         <v>90</v>
@@ -26199,7 +26199,7 @@
         <v>58</v>
       </c>
       <c r="E662" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F662" s="16" t="s">
         <v>91</v>
@@ -26235,7 +26235,7 @@
         <v>59</v>
       </c>
       <c r="E663" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F663" s="16" t="s">
         <v>92</v>
@@ -26271,7 +26271,7 @@
         <v>60</v>
       </c>
       <c r="E664" s="16">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F664" s="16" t="s">
         <v>93</v>
@@ -26305,7 +26305,7 @@
         <v>1</v>
       </c>
       <c r="E665" s="20">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F665" s="20" t="s">
         <v>31</v>
@@ -26345,7 +26345,7 @@
         <v>2</v>
       </c>
       <c r="E666" s="20">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F666" s="20" t="s">
         <v>34</v>
@@ -26385,7 +26385,7 @@
         <v>3</v>
       </c>
       <c r="E667" s="20">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="F667" s="20" t="s">
         <v>35</v>
@@ -26425,7 +26425,7 @@
         <v>4</v>
       </c>
       <c r="E668" s="20">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F668" s="20" t="s">
         <v>36</v>
@@ -26465,7 +26465,7 @@
         <v>5</v>
       </c>
       <c r="E669" s="20">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F669" s="20" t="s">
         <v>37</v>
@@ -26505,7 +26505,7 @@
         <v>6</v>
       </c>
       <c r="E670" s="20">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F670" s="20" t="s">
         <v>38</v>
@@ -26545,7 +26545,7 @@
         <v>7</v>
       </c>
       <c r="E671" s="20">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F671" s="20" t="s">
         <v>39</v>
@@ -26585,7 +26585,7 @@
         <v>8</v>
       </c>
       <c r="E672" s="20">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F672" s="20" t="s">
         <v>40</v>
@@ -26625,7 +26625,7 @@
         <v>9</v>
       </c>
       <c r="E673" s="20">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="F673" s="20" t="s">
         <v>41</v>
@@ -26665,7 +26665,7 @@
         <v>10</v>
       </c>
       <c r="E674" s="20">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F674" s="20" t="s">
         <v>42</v>
@@ -26705,7 +26705,7 @@
         <v>11</v>
       </c>
       <c r="E675" s="20">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="F675" s="20" t="s">
         <v>43</v>
@@ -26745,7 +26745,7 @@
         <v>12</v>
       </c>
       <c r="E676" s="20">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F676" s="20" t="s">
         <v>44</v>
@@ -26785,7 +26785,7 @@
         <v>13</v>
       </c>
       <c r="E677" s="20">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="F677" s="20" t="s">
         <v>45</v>
@@ -26821,7 +26821,7 @@
         <v>14</v>
       </c>
       <c r="E678" s="20">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F678" s="20" t="s">
         <v>46</v>
@@ -26857,7 +26857,7 @@
         <v>15</v>
       </c>
       <c r="E679" s="20">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F679" s="20" t="s">
         <v>47</v>
@@ -26893,7 +26893,7 @@
         <v>16</v>
       </c>
       <c r="E680" s="20">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F680" s="20" t="s">
         <v>48</v>
@@ -26929,7 +26929,7 @@
         <v>17</v>
       </c>
       <c r="E681" s="20">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="F681" s="20" t="s">
         <v>49</v>
@@ -26965,7 +26965,7 @@
         <v>18</v>
       </c>
       <c r="E682" s="20">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F682" s="20" t="s">
         <v>50</v>
@@ -27001,7 +27001,7 @@
         <v>19</v>
       </c>
       <c r="E683" s="20">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F683" s="20" t="s">
         <v>51</v>
@@ -27037,7 +27037,7 @@
         <v>20</v>
       </c>
       <c r="E684" s="20">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="F684" s="20" t="s">
         <v>52</v>
@@ -27073,7 +27073,7 @@
         <v>21</v>
       </c>
       <c r="E685" s="20">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F685" s="20" t="s">
         <v>53</v>
@@ -27106,7 +27106,7 @@
         <v>22</v>
       </c>
       <c r="E686" s="20">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F686" s="20" t="s">
         <v>54</v>
@@ -27139,7 +27139,7 @@
         <v>23</v>
       </c>
       <c r="E687" s="20">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F687" s="20" t="s">
         <v>55</v>
@@ -27172,7 +27172,7 @@
         <v>24</v>
       </c>
       <c r="E688" s="20">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="F688" s="20" t="s">
         <v>56</v>
@@ -27205,7 +27205,7 @@
         <v>25</v>
       </c>
       <c r="E689" s="20">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F689" s="20" t="s">
         <v>57</v>
@@ -27238,7 +27238,7 @@
         <v>26</v>
       </c>
       <c r="E690" s="20">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F690" s="20" t="s">
         <v>58</v>
@@ -27274,7 +27274,7 @@
         <v>27</v>
       </c>
       <c r="E691" s="20">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F691" s="20" t="s">
         <v>59</v>
@@ -27310,7 +27310,7 @@
         <v>28</v>
       </c>
       <c r="E692" s="20">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F692" s="20" t="s">
         <v>60</v>
@@ -27346,7 +27346,7 @@
         <v>29</v>
       </c>
       <c r="E693" s="20">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F693" s="20" t="s">
         <v>61</v>
@@ -27382,7 +27382,7 @@
         <v>30</v>
       </c>
       <c r="E694" s="20">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F694" s="20" t="s">
         <v>62</v>
@@ -27418,7 +27418,7 @@
         <v>31</v>
       </c>
       <c r="E695" s="20">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="F695" s="20" t="s">
         <v>64</v>
@@ -27454,7 +27454,7 @@
         <v>32</v>
       </c>
       <c r="E696" s="20">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F696" s="20" t="s">
         <v>65</v>
@@ -27490,7 +27490,7 @@
         <v>33</v>
       </c>
       <c r="E697" s="20">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="F697" s="20" t="s">
         <v>66</v>
@@ -27526,7 +27526,7 @@
         <v>34</v>
       </c>
       <c r="E698" s="20">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="F698" s="20" t="s">
         <v>67</v>
@@ -27562,7 +27562,7 @@
         <v>35</v>
       </c>
       <c r="E699" s="20">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F699" s="20" t="s">
         <v>68</v>
@@ -27598,7 +27598,7 @@
         <v>36</v>
       </c>
       <c r="E700" s="20">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F700" s="20" t="s">
         <v>69</v>
@@ -27634,7 +27634,7 @@
         <v>37</v>
       </c>
       <c r="E701" s="20">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F701" s="20" t="s">
         <v>70</v>
@@ -27670,7 +27670,7 @@
         <v>38</v>
       </c>
       <c r="E702" s="20">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F702" s="20" t="s">
         <v>71</v>
@@ -27706,7 +27706,7 @@
         <v>39</v>
       </c>
       <c r="E703" s="20">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F703" s="20" t="s">
         <v>72</v>
@@ -27742,7 +27742,7 @@
         <v>40</v>
       </c>
       <c r="E704" s="20">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F704" s="20" t="s">
         <v>73</v>
@@ -27778,7 +27778,7 @@
         <v>41</v>
       </c>
       <c r="E705" s="20">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F705" s="20" t="s">
         <v>74</v>
@@ -27814,7 +27814,7 @@
         <v>42</v>
       </c>
       <c r="E706" s="20">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F706" s="20" t="s">
         <v>75</v>
@@ -27850,7 +27850,7 @@
         <v>43</v>
       </c>
       <c r="E707" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F707" s="20" t="s">
         <v>76</v>
@@ -27886,7 +27886,7 @@
         <v>44</v>
       </c>
       <c r="E708" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F708" s="20" t="s">
         <v>77</v>
@@ -27922,7 +27922,7 @@
         <v>45</v>
       </c>
       <c r="E709" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F709" s="20" t="s">
         <v>78</v>
@@ -27958,7 +27958,7 @@
         <v>46</v>
       </c>
       <c r="E710" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F710" s="20" t="s">
         <v>79</v>
@@ -27994,7 +27994,7 @@
         <v>47</v>
       </c>
       <c r="E711" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F711" s="20" t="s">
         <v>80</v>
@@ -28030,7 +28030,7 @@
         <v>48</v>
       </c>
       <c r="E712" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F712" s="20" t="s">
         <v>81</v>
@@ -28066,7 +28066,7 @@
         <v>49</v>
       </c>
       <c r="E713" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F713" s="20" t="s">
         <v>82</v>
@@ -28102,7 +28102,7 @@
         <v>50</v>
       </c>
       <c r="E714" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F714" s="20" t="s">
         <v>83</v>
@@ -28138,7 +28138,7 @@
         <v>51</v>
       </c>
       <c r="E715" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F715" s="20" t="s">
         <v>84</v>
@@ -28174,7 +28174,7 @@
         <v>52</v>
       </c>
       <c r="E716" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F716" s="20" t="s">
         <v>85</v>
@@ -28210,7 +28210,7 @@
         <v>53</v>
       </c>
       <c r="E717" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F717" s="20" t="s">
         <v>86</v>
@@ -28246,7 +28246,7 @@
         <v>54</v>
       </c>
       <c r="E718" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F718" s="20" t="s">
         <v>87</v>
@@ -28282,7 +28282,7 @@
         <v>55</v>
       </c>
       <c r="E719" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F719" s="20" t="s">
         <v>88</v>
@@ -28318,7 +28318,7 @@
         <v>56</v>
       </c>
       <c r="E720" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F720" s="20" t="s">
         <v>89</v>
@@ -28354,7 +28354,7 @@
         <v>57</v>
       </c>
       <c r="E721" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F721" s="20" t="s">
         <v>90</v>
@@ -28390,7 +28390,7 @@
         <v>58</v>
       </c>
       <c r="E722" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F722" s="20" t="s">
         <v>91</v>
@@ -28426,7 +28426,7 @@
         <v>59</v>
       </c>
       <c r="E723" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F723" s="20" t="s">
         <v>92</v>
@@ -28462,7 +28462,7 @@
         <v>60</v>
       </c>
       <c r="E724" s="20">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F724" s="20" t="s">
         <v>93</v>
@@ -28496,7 +28496,7 @@
         <v>1</v>
       </c>
       <c r="E725" s="16">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F725" s="16" t="s">
         <v>31</v>
@@ -28536,7 +28536,7 @@
         <v>2</v>
       </c>
       <c r="E726" s="16">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F726" s="16" t="s">
         <v>34</v>
@@ -28576,7 +28576,7 @@
         <v>3</v>
       </c>
       <c r="E727" s="16">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F727" s="16" t="s">
         <v>35</v>
@@ -28616,7 +28616,7 @@
         <v>4</v>
       </c>
       <c r="E728" s="16">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F728" s="16" t="s">
         <v>36</v>
@@ -28656,7 +28656,7 @@
         <v>5</v>
       </c>
       <c r="E729" s="16">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F729" s="16" t="s">
         <v>37</v>
@@ -28696,7 +28696,7 @@
         <v>6</v>
       </c>
       <c r="E730" s="16">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F730" s="16" t="s">
         <v>38</v>
@@ -28736,7 +28736,7 @@
         <v>7</v>
       </c>
       <c r="E731" s="16">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F731" s="16" t="s">
         <v>39</v>
@@ -28776,7 +28776,7 @@
         <v>8</v>
       </c>
       <c r="E732" s="16">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F732" s="16" t="s">
         <v>40</v>
@@ -28816,7 +28816,7 @@
         <v>9</v>
       </c>
       <c r="E733" s="16">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F733" s="16" t="s">
         <v>41</v>
@@ -28856,7 +28856,7 @@
         <v>10</v>
       </c>
       <c r="E734" s="16">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F734" s="16" t="s">
         <v>42</v>
@@ -28896,7 +28896,7 @@
         <v>11</v>
       </c>
       <c r="E735" s="16">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F735" s="16" t="s">
         <v>43</v>
@@ -28936,7 +28936,7 @@
         <v>12</v>
       </c>
       <c r="E736" s="16">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F736" s="16" t="s">
         <v>44</v>
@@ -28976,7 +28976,7 @@
         <v>13</v>
       </c>
       <c r="E737" s="16">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="F737" s="16" t="s">
         <v>45</v>
@@ -29010,7 +29010,7 @@
         <v>14</v>
       </c>
       <c r="E738" s="16">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F738" s="16" t="s">
         <v>46</v>
@@ -29044,7 +29044,7 @@
         <v>15</v>
       </c>
       <c r="E739" s="16">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F739" s="16" t="s">
         <v>47</v>
@@ -29078,7 +29078,7 @@
         <v>16</v>
       </c>
       <c r="E740" s="16">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F740" s="16" t="s">
         <v>48</v>
@@ -29112,7 +29112,7 @@
         <v>17</v>
       </c>
       <c r="E741" s="16">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F741" s="16" t="s">
         <v>49</v>
@@ -29146,7 +29146,7 @@
         <v>18</v>
       </c>
       <c r="E742" s="16">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F742" s="16" t="s">
         <v>50</v>
@@ -29180,7 +29180,7 @@
         <v>19</v>
       </c>
       <c r="E743" s="16">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F743" s="16" t="s">
         <v>51</v>
@@ -29214,7 +29214,7 @@
         <v>20</v>
       </c>
       <c r="E744" s="16">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F744" s="16" t="s">
         <v>52</v>
@@ -29248,7 +29248,7 @@
         <v>21</v>
       </c>
       <c r="E745" s="16">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F745" s="16" t="s">
         <v>53</v>
@@ -29282,7 +29282,7 @@
         <v>22</v>
       </c>
       <c r="E746" s="16">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F746" s="16" t="s">
         <v>54</v>
@@ -29316,7 +29316,7 @@
         <v>23</v>
       </c>
       <c r="E747" s="16">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F747" s="16" t="s">
         <v>55</v>
@@ -29350,7 +29350,7 @@
         <v>24</v>
       </c>
       <c r="E748" s="16">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F748" s="16" t="s">
         <v>56</v>
@@ -29384,7 +29384,7 @@
         <v>25</v>
       </c>
       <c r="E749" s="16">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F749" s="16" t="s">
         <v>57</v>
@@ -29418,7 +29418,7 @@
         <v>26</v>
       </c>
       <c r="E750" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F750" s="16" t="s">
         <v>58</v>
@@ -29452,7 +29452,7 @@
         <v>27</v>
       </c>
       <c r="E751" s="16">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F751" s="16" t="s">
         <v>59</v>
@@ -29486,7 +29486,7 @@
         <v>28</v>
       </c>
       <c r="E752" s="16">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F752" s="16" t="s">
         <v>60</v>
@@ -29520,7 +29520,7 @@
         <v>29</v>
       </c>
       <c r="E753" s="16">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F753" s="16" t="s">
         <v>61</v>
@@ -29554,7 +29554,7 @@
         <v>30</v>
       </c>
       <c r="E754" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F754" s="16" t="s">
         <v>62</v>
@@ -29588,7 +29588,7 @@
         <v>31</v>
       </c>
       <c r="E755" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F755" s="16" t="s">
         <v>64</v>
@@ -29622,7 +29622,7 @@
         <v>32</v>
       </c>
       <c r="E756" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F756" s="16" t="s">
         <v>65</v>
@@ -29656,7 +29656,7 @@
         <v>33</v>
       </c>
       <c r="E757" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F757" s="16" t="s">
         <v>66</v>
@@ -29690,7 +29690,7 @@
         <v>34</v>
       </c>
       <c r="E758" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F758" s="16" t="s">
         <v>67</v>
@@ -29724,7 +29724,7 @@
         <v>35</v>
       </c>
       <c r="E759" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F759" s="16" t="s">
         <v>68</v>
@@ -29758,7 +29758,7 @@
         <v>36</v>
       </c>
       <c r="E760" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F760" s="16" t="s">
         <v>69</v>
@@ -29792,7 +29792,7 @@
         <v>37</v>
       </c>
       <c r="E761" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F761" s="16" t="s">
         <v>70</v>
@@ -29826,7 +29826,7 @@
         <v>38</v>
       </c>
       <c r="E762" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F762" s="16" t="s">
         <v>71</v>
@@ -29860,7 +29860,7 @@
         <v>39</v>
       </c>
       <c r="E763" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F763" s="16" t="s">
         <v>72</v>
@@ -29894,7 +29894,7 @@
         <v>40</v>
       </c>
       <c r="E764" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F764" s="16" t="s">
         <v>73</v>
@@ -29925,7 +29925,7 @@
         <v>41</v>
       </c>
       <c r="E765" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F765" s="16" t="s">
         <v>74</v>
@@ -29956,7 +29956,7 @@
         <v>42</v>
       </c>
       <c r="E766" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F766" s="16" t="s">
         <v>75</v>
@@ -29987,7 +29987,7 @@
         <v>43</v>
       </c>
       <c r="E767" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F767" s="16" t="s">
         <v>76</v>
@@ -30018,7 +30018,7 @@
         <v>44</v>
       </c>
       <c r="E768" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F768" s="16" t="s">
         <v>77</v>
@@ -30049,7 +30049,7 @@
         <v>45</v>
       </c>
       <c r="E769" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F769" s="16" t="s">
         <v>78</v>
@@ -30080,7 +30080,7 @@
         <v>46</v>
       </c>
       <c r="E770" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F770" s="16" t="s">
         <v>79</v>
@@ -30111,7 +30111,7 @@
         <v>47</v>
       </c>
       <c r="E771" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F771" s="16" t="s">
         <v>80</v>
@@ -30142,7 +30142,7 @@
         <v>48</v>
       </c>
       <c r="E772" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F772" s="16" t="s">
         <v>81</v>
@@ -30176,7 +30176,7 @@
         <v>49</v>
       </c>
       <c r="E773" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F773" s="16" t="s">
         <v>82</v>
@@ -30210,7 +30210,7 @@
         <v>50</v>
       </c>
       <c r="E774" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F774" s="16" t="s">
         <v>83</v>
@@ -30244,7 +30244,7 @@
         <v>51</v>
       </c>
       <c r="E775" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F775" s="16" t="s">
         <v>84</v>
@@ -30278,7 +30278,7 @@
         <v>52</v>
       </c>
       <c r="E776" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F776" s="16" t="s">
         <v>85</v>
@@ -30312,7 +30312,7 @@
         <v>53</v>
       </c>
       <c r="E777" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F777" s="16" t="s">
         <v>86</v>
@@ -30346,7 +30346,7 @@
         <v>54</v>
       </c>
       <c r="E778" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F778" s="16" t="s">
         <v>87</v>
@@ -30380,7 +30380,7 @@
         <v>55</v>
       </c>
       <c r="E779" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F779" s="16" t="s">
         <v>88</v>
@@ -30414,7 +30414,7 @@
         <v>56</v>
       </c>
       <c r="E780" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F780" s="16" t="s">
         <v>89</v>
@@ -30448,7 +30448,7 @@
         <v>57</v>
       </c>
       <c r="E781" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F781" s="16" t="s">
         <v>90</v>
@@ -30482,7 +30482,7 @@
         <v>58</v>
       </c>
       <c r="E782" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F782" s="16" t="s">
         <v>91</v>
@@ -30516,7 +30516,7 @@
         <v>59</v>
       </c>
       <c r="E783" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F783" s="16" t="s">
         <v>92</v>
@@ -30550,7 +30550,7 @@
         <v>60</v>
       </c>
       <c r="E784" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F784" s="16" t="s">
         <v>93</v>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -934,12 +934,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -30756,7 +30756,7 @@
         <v>4030001</v>
       </c>
       <c r="I846" s="38">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="J846" s="38"/>
       <c r="K846" s="39"/>
@@ -30792,9 +30792,8 @@
         <v>4030001</v>
       </c>
       <c r="I847" s="38">
-        <v>100700</v>
-      </c>
-      <c r="J847" s="38"/>
+        <v>101200</v>
+      </c>
       <c r="K847" s="39"/>
       <c r="L847" s="40">
         <v>60</v>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -1214,12 +1214,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -25055,7 +25055,7 @@
         <v>31</v>
       </c>
       <c r="G665" s="24">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H665" s="24"/>
       <c r="I665" s="25" t="s">
@@ -25095,7 +25095,7 @@
         <v>36</v>
       </c>
       <c r="G666" s="24">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H666" s="24"/>
       <c r="I666" s="25"/>
@@ -25129,7 +25129,7 @@
         <v>38</v>
       </c>
       <c r="G667" s="24">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="H667" s="24"/>
       <c r="I667" s="25"/>
@@ -25163,7 +25163,7 @@
         <v>40</v>
       </c>
       <c r="G668" s="24">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="H668" s="24"/>
       <c r="I668" s="25"/>
@@ -25197,7 +25197,7 @@
         <v>42</v>
       </c>
       <c r="G669" s="24">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="H669" s="24"/>
       <c r="I669" s="25"/>
@@ -25231,7 +25231,7 @@
         <v>44</v>
       </c>
       <c r="G670" s="24">
-        <v>6</v>
+        <v>600</v>
       </c>
       <c r="H670" s="24"/>
       <c r="I670" s="25"/>
@@ -25265,7 +25265,7 @@
         <v>46</v>
       </c>
       <c r="G671" s="24">
-        <v>7</v>
+        <v>700</v>
       </c>
       <c r="H671" s="24"/>
       <c r="I671" s="25"/>
@@ -25299,7 +25299,7 @@
         <v>48</v>
       </c>
       <c r="G672" s="24">
-        <v>8</v>
+        <v>800</v>
       </c>
       <c r="H672" s="24"/>
       <c r="I672" s="25"/>
@@ -25333,7 +25333,7 @@
         <v>50</v>
       </c>
       <c r="G673" s="24">
-        <v>9</v>
+        <v>900</v>
       </c>
       <c r="H673" s="24"/>
       <c r="I673" s="25"/>
@@ -25367,7 +25367,7 @@
         <v>52</v>
       </c>
       <c r="G674" s="24">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="H674" s="24"/>
       <c r="I674" s="25"/>
@@ -25401,7 +25401,7 @@
         <v>54</v>
       </c>
       <c r="G675" s="24">
-        <v>11</v>
+        <v>1100</v>
       </c>
       <c r="H675" s="24"/>
       <c r="I675" s="25"/>
@@ -25435,7 +25435,7 @@
         <v>56</v>
       </c>
       <c r="G676" s="24">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="H676" s="24"/>
       <c r="I676" s="25"/>
@@ -25469,7 +25469,7 @@
         <v>58</v>
       </c>
       <c r="G677" s="24">
-        <v>13</v>
+        <v>1300</v>
       </c>
       <c r="H677" s="24"/>
       <c r="I677" s="25"/>
@@ -25503,7 +25503,7 @@
         <v>60</v>
       </c>
       <c r="G678" s="24">
-        <v>14</v>
+        <v>1400</v>
       </c>
       <c r="H678" s="24"/>
       <c r="I678" s="25"/>
@@ -25537,7 +25537,7 @@
         <v>62</v>
       </c>
       <c r="G679" s="24">
-        <v>15</v>
+        <v>1500</v>
       </c>
       <c r="H679" s="24"/>
       <c r="I679" s="25"/>
@@ -25571,7 +25571,7 @@
         <v>64</v>
       </c>
       <c r="G680" s="24">
-        <v>16</v>
+        <v>1600</v>
       </c>
       <c r="H680" s="24"/>
       <c r="I680" s="25"/>
@@ -25605,7 +25605,7 @@
         <v>66</v>
       </c>
       <c r="G681" s="24">
-        <v>17</v>
+        <v>1700</v>
       </c>
       <c r="H681" s="24"/>
       <c r="I681" s="25"/>
@@ -25639,7 +25639,7 @@
         <v>68</v>
       </c>
       <c r="G682" s="24">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="H682" s="24"/>
       <c r="I682" s="25"/>
@@ -25673,7 +25673,7 @@
         <v>70</v>
       </c>
       <c r="G683" s="24">
-        <v>19</v>
+        <v>1900</v>
       </c>
       <c r="H683" s="24"/>
       <c r="I683" s="25"/>
@@ -25707,7 +25707,7 @@
         <v>72</v>
       </c>
       <c r="G684" s="24">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="H684" s="24"/>
       <c r="I684" s="25"/>
@@ -25741,7 +25741,7 @@
         <v>74</v>
       </c>
       <c r="G685" s="24">
-        <v>21</v>
+        <v>2100</v>
       </c>
       <c r="H685" s="24"/>
       <c r="I685" s="25"/>
@@ -25775,7 +25775,7 @@
         <v>76</v>
       </c>
       <c r="G686" s="24">
-        <v>22</v>
+        <v>2200</v>
       </c>
       <c r="H686" s="24"/>
       <c r="I686" s="25"/>
@@ -25809,7 +25809,7 @@
         <v>78</v>
       </c>
       <c r="G687" s="24">
-        <v>23</v>
+        <v>2300</v>
       </c>
       <c r="H687" s="24"/>
       <c r="I687" s="25"/>
@@ -25843,7 +25843,7 @@
         <v>80</v>
       </c>
       <c r="G688" s="24">
-        <v>24</v>
+        <v>2400</v>
       </c>
       <c r="H688" s="24"/>
       <c r="I688" s="25"/>
@@ -25877,7 +25877,7 @@
         <v>82</v>
       </c>
       <c r="G689" s="24">
-        <v>25</v>
+        <v>2500</v>
       </c>
       <c r="H689" s="24"/>
       <c r="I689" s="25"/>
@@ -25911,7 +25911,7 @@
         <v>84</v>
       </c>
       <c r="G690" s="24">
-        <v>26</v>
+        <v>2600</v>
       </c>
       <c r="H690" s="24"/>
       <c r="I690" s="25"/>
@@ -25947,7 +25947,7 @@
         <v>86</v>
       </c>
       <c r="G691" s="24">
-        <v>27</v>
+        <v>2700</v>
       </c>
       <c r="H691" s="24"/>
       <c r="I691" s="25"/>
@@ -25983,7 +25983,7 @@
         <v>88</v>
       </c>
       <c r="G692" s="24">
-        <v>28</v>
+        <v>2800</v>
       </c>
       <c r="H692" s="24"/>
       <c r="I692" s="25"/>
@@ -26019,7 +26019,7 @@
         <v>90</v>
       </c>
       <c r="G693" s="24">
-        <v>29</v>
+        <v>2900</v>
       </c>
       <c r="H693" s="24"/>
       <c r="I693" s="25"/>
@@ -26055,7 +26055,7 @@
         <v>92</v>
       </c>
       <c r="G694" s="24">
-        <v>30</v>
+        <v>3000</v>
       </c>
       <c r="H694" s="24"/>
       <c r="I694" s="25"/>
@@ -26091,7 +26091,7 @@
         <v>95</v>
       </c>
       <c r="G695" s="24">
-        <v>31</v>
+        <v>3100</v>
       </c>
       <c r="H695" s="24"/>
       <c r="I695" s="25"/>
@@ -26127,7 +26127,7 @@
         <v>97</v>
       </c>
       <c r="G696" s="24">
-        <v>32</v>
+        <v>3200</v>
       </c>
       <c r="H696" s="24"/>
       <c r="I696" s="25"/>
@@ -26163,7 +26163,7 @@
         <v>99</v>
       </c>
       <c r="G697" s="24">
-        <v>33</v>
+        <v>3300</v>
       </c>
       <c r="H697" s="24"/>
       <c r="I697" s="25"/>
@@ -26199,7 +26199,7 @@
         <v>101</v>
       </c>
       <c r="G698" s="24">
-        <v>34</v>
+        <v>3400</v>
       </c>
       <c r="H698" s="24"/>
       <c r="I698" s="25"/>
@@ -26235,7 +26235,7 @@
         <v>103</v>
       </c>
       <c r="G699" s="24">
-        <v>35</v>
+        <v>3500</v>
       </c>
       <c r="H699" s="24"/>
       <c r="I699" s="25"/>
@@ -26271,7 +26271,7 @@
         <v>105</v>
       </c>
       <c r="G700" s="24">
-        <v>36</v>
+        <v>3600</v>
       </c>
       <c r="H700" s="24"/>
       <c r="I700" s="25"/>
@@ -26307,7 +26307,7 @@
         <v>107</v>
       </c>
       <c r="G701" s="24">
-        <v>37</v>
+        <v>3700</v>
       </c>
       <c r="H701" s="24"/>
       <c r="I701" s="25"/>
@@ -26343,7 +26343,7 @@
         <v>109</v>
       </c>
       <c r="G702" s="24">
-        <v>38</v>
+        <v>3800</v>
       </c>
       <c r="H702" s="24"/>
       <c r="I702" s="25"/>
@@ -26379,7 +26379,7 @@
         <v>111</v>
       </c>
       <c r="G703" s="24">
-        <v>39</v>
+        <v>3900</v>
       </c>
       <c r="H703" s="24"/>
       <c r="I703" s="25"/>
@@ -26415,7 +26415,7 @@
         <v>113</v>
       </c>
       <c r="G704" s="24">
-        <v>40</v>
+        <v>4000</v>
       </c>
       <c r="H704" s="24"/>
       <c r="I704" s="25"/>
@@ -26451,7 +26451,7 @@
         <v>115</v>
       </c>
       <c r="G705" s="24">
-        <v>41</v>
+        <v>4100</v>
       </c>
       <c r="H705" s="24"/>
       <c r="I705" s="25"/>
@@ -26487,7 +26487,7 @@
         <v>117</v>
       </c>
       <c r="G706" s="24">
-        <v>42</v>
+        <v>4200</v>
       </c>
       <c r="H706" s="24"/>
       <c r="I706" s="25"/>
@@ -26523,7 +26523,7 @@
         <v>119</v>
       </c>
       <c r="G707" s="24">
-        <v>43</v>
+        <v>4300</v>
       </c>
       <c r="H707" s="24"/>
       <c r="I707" s="25"/>
@@ -26559,7 +26559,7 @@
         <v>121</v>
       </c>
       <c r="G708" s="24">
-        <v>44</v>
+        <v>4400</v>
       </c>
       <c r="H708" s="24"/>
       <c r="I708" s="25"/>
@@ -26595,7 +26595,7 @@
         <v>123</v>
       </c>
       <c r="G709" s="24">
-        <v>45</v>
+        <v>4500</v>
       </c>
       <c r="H709" s="24"/>
       <c r="I709" s="25"/>
@@ -26631,7 +26631,7 @@
         <v>125</v>
       </c>
       <c r="G710" s="24">
-        <v>46</v>
+        <v>4600</v>
       </c>
       <c r="H710" s="24"/>
       <c r="I710" s="25"/>
@@ -26667,7 +26667,7 @@
         <v>127</v>
       </c>
       <c r="G711" s="24">
-        <v>47</v>
+        <v>4700</v>
       </c>
       <c r="H711" s="24"/>
       <c r="I711" s="25"/>
@@ -26703,7 +26703,7 @@
         <v>129</v>
       </c>
       <c r="G712" s="24">
-        <v>48</v>
+        <v>4800</v>
       </c>
       <c r="H712" s="24"/>
       <c r="I712" s="25"/>
@@ -26739,7 +26739,7 @@
         <v>131</v>
       </c>
       <c r="G713" s="24">
-        <v>49</v>
+        <v>4900</v>
       </c>
       <c r="H713" s="24"/>
       <c r="I713" s="25"/>
@@ -26775,7 +26775,7 @@
         <v>133</v>
       </c>
       <c r="G714" s="24">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="H714" s="24"/>
       <c r="I714" s="25"/>
@@ -26811,7 +26811,7 @@
         <v>135</v>
       </c>
       <c r="G715" s="24">
-        <v>51</v>
+        <v>5100</v>
       </c>
       <c r="H715" s="24"/>
       <c r="I715" s="25"/>
@@ -26847,7 +26847,7 @@
         <v>137</v>
       </c>
       <c r="G716" s="24">
-        <v>52</v>
+        <v>5200</v>
       </c>
       <c r="H716" s="24"/>
       <c r="I716" s="25"/>
@@ -26883,7 +26883,7 @@
         <v>139</v>
       </c>
       <c r="G717" s="24">
-        <v>53</v>
+        <v>5300</v>
       </c>
       <c r="H717" s="24"/>
       <c r="I717" s="25"/>
@@ -26919,7 +26919,7 @@
         <v>141</v>
       </c>
       <c r="G718" s="24">
-        <v>54</v>
+        <v>5400</v>
       </c>
       <c r="H718" s="24"/>
       <c r="I718" s="25"/>
@@ -26955,7 +26955,7 @@
         <v>143</v>
       </c>
       <c r="G719" s="24">
-        <v>55</v>
+        <v>5500</v>
       </c>
       <c r="H719" s="24"/>
       <c r="I719" s="25"/>
@@ -26991,7 +26991,7 @@
         <v>145</v>
       </c>
       <c r="G720" s="24">
-        <v>56</v>
+        <v>5600</v>
       </c>
       <c r="H720" s="24"/>
       <c r="I720" s="25"/>
@@ -27027,7 +27027,7 @@
         <v>147</v>
       </c>
       <c r="G721" s="24">
-        <v>57</v>
+        <v>5700</v>
       </c>
       <c r="H721" s="24"/>
       <c r="I721" s="25"/>
@@ -27063,7 +27063,7 @@
         <v>149</v>
       </c>
       <c r="G722" s="24">
-        <v>58</v>
+        <v>5800</v>
       </c>
       <c r="H722" s="24"/>
       <c r="I722" s="25"/>
@@ -27099,7 +27099,7 @@
         <v>151</v>
       </c>
       <c r="G723" s="24">
-        <v>59</v>
+        <v>5900</v>
       </c>
       <c r="H723" s="24"/>
       <c r="I723" s="25"/>
@@ -27135,7 +27135,7 @@
         <v>153</v>
       </c>
       <c r="G724" s="24">
-        <v>60</v>
+        <v>6000</v>
       </c>
       <c r="H724" s="24"/>
       <c r="I724" s="25"/>
@@ -27169,7 +27169,7 @@
         <v>31</v>
       </c>
       <c r="G725" s="9">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H725" s="9"/>
       <c r="I725" s="7" t="s">
@@ -27209,7 +27209,7 @@
         <v>36</v>
       </c>
       <c r="G726" s="9">
-        <v>4</v>
+        <v>400</v>
       </c>
       <c r="H726" s="9"/>
       <c r="K726" s="32"/>
@@ -27241,7 +27241,7 @@
         <v>38</v>
       </c>
       <c r="G727" s="9">
-        <v>6</v>
+        <v>600</v>
       </c>
       <c r="H727" s="9"/>
       <c r="L727" s="21">
@@ -27272,7 +27272,7 @@
         <v>40</v>
       </c>
       <c r="G728" s="9">
-        <v>8</v>
+        <v>800</v>
       </c>
       <c r="H728" s="9"/>
       <c r="L728" s="21">
@@ -27303,7 +27303,7 @@
         <v>42</v>
       </c>
       <c r="G729" s="9">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="H729" s="9"/>
       <c r="L729" s="21">
@@ -27334,7 +27334,7 @@
         <v>44</v>
       </c>
       <c r="G730" s="9">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="H730" s="9"/>
       <c r="L730" s="21">
@@ -27365,7 +27365,7 @@
         <v>46</v>
       </c>
       <c r="G731" s="9">
-        <v>14</v>
+        <v>1400</v>
       </c>
       <c r="H731" s="9"/>
       <c r="L731" s="21">
@@ -27396,7 +27396,7 @@
         <v>48</v>
       </c>
       <c r="G732" s="9">
-        <v>16</v>
+        <v>1600</v>
       </c>
       <c r="H732" s="9"/>
       <c r="L732" s="21">
@@ -27427,7 +27427,7 @@
         <v>50</v>
       </c>
       <c r="G733" s="9">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="H733" s="9"/>
       <c r="L733" s="21">
@@ -27458,7 +27458,7 @@
         <v>52</v>
       </c>
       <c r="G734" s="9">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="H734" s="9"/>
       <c r="L734" s="21">
@@ -27489,7 +27489,7 @@
         <v>54</v>
       </c>
       <c r="G735" s="9">
-        <v>22</v>
+        <v>2200</v>
       </c>
       <c r="H735" s="9"/>
       <c r="L735" s="21">
@@ -27520,7 +27520,7 @@
         <v>56</v>
       </c>
       <c r="G736" s="9">
-        <v>24</v>
+        <v>2400</v>
       </c>
       <c r="H736" s="9"/>
       <c r="L736" s="21">
@@ -27551,7 +27551,7 @@
         <v>58</v>
       </c>
       <c r="G737" s="9">
-        <v>26</v>
+        <v>2600</v>
       </c>
       <c r="H737" s="9"/>
       <c r="L737" s="21">
@@ -27582,7 +27582,7 @@
         <v>60</v>
       </c>
       <c r="G738" s="9">
-        <v>28</v>
+        <v>2800</v>
       </c>
       <c r="H738" s="9"/>
       <c r="L738" s="21">
@@ -27613,7 +27613,7 @@
         <v>62</v>
       </c>
       <c r="G739" s="9">
-        <v>30</v>
+        <v>3000</v>
       </c>
       <c r="H739" s="9"/>
       <c r="L739" s="21">
@@ -27644,7 +27644,7 @@
         <v>64</v>
       </c>
       <c r="G740" s="9">
-        <v>32</v>
+        <v>3200</v>
       </c>
       <c r="H740" s="9"/>
       <c r="L740" s="21">
@@ -27675,7 +27675,7 @@
         <v>66</v>
       </c>
       <c r="G741" s="9">
-        <v>34</v>
+        <v>3400</v>
       </c>
       <c r="H741" s="9"/>
       <c r="L741" s="21">
@@ -27706,7 +27706,7 @@
         <v>68</v>
       </c>
       <c r="G742" s="9">
-        <v>36</v>
+        <v>3600</v>
       </c>
       <c r="H742" s="9"/>
       <c r="L742" s="21">
@@ -27737,7 +27737,7 @@
         <v>70</v>
       </c>
       <c r="G743" s="9">
-        <v>38</v>
+        <v>3800</v>
       </c>
       <c r="H743" s="9"/>
       <c r="L743" s="21">
@@ -27768,7 +27768,7 @@
         <v>72</v>
       </c>
       <c r="G744" s="9">
-        <v>40</v>
+        <v>4000</v>
       </c>
       <c r="H744" s="9"/>
       <c r="L744" s="21">
@@ -27799,7 +27799,7 @@
         <v>74</v>
       </c>
       <c r="G745" s="9">
-        <v>42</v>
+        <v>4200</v>
       </c>
       <c r="H745" s="9"/>
       <c r="L745" s="21">
@@ -27830,7 +27830,7 @@
         <v>76</v>
       </c>
       <c r="G746" s="9">
-        <v>44</v>
+        <v>4400</v>
       </c>
       <c r="H746" s="9"/>
       <c r="L746" s="21">
@@ -27861,7 +27861,7 @@
         <v>78</v>
       </c>
       <c r="G747" s="9">
-        <v>46</v>
+        <v>4600</v>
       </c>
       <c r="H747" s="9"/>
       <c r="L747" s="21">
@@ -27892,7 +27892,7 @@
         <v>80</v>
       </c>
       <c r="G748" s="9">
-        <v>48</v>
+        <v>4800</v>
       </c>
       <c r="H748" s="9"/>
       <c r="L748" s="21">
@@ -27923,7 +27923,7 @@
         <v>82</v>
       </c>
       <c r="G749" s="9">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="H749" s="9"/>
       <c r="L749" s="21">
@@ -27954,7 +27954,7 @@
         <v>84</v>
       </c>
       <c r="G750" s="9">
-        <v>52</v>
+        <v>5200</v>
       </c>
       <c r="H750" s="9"/>
       <c r="L750" s="21">
@@ -27985,7 +27985,7 @@
         <v>86</v>
       </c>
       <c r="G751" s="9">
-        <v>54</v>
+        <v>5400</v>
       </c>
       <c r="H751" s="9"/>
       <c r="L751" s="21">
@@ -28016,7 +28016,7 @@
         <v>88</v>
       </c>
       <c r="G752" s="9">
-        <v>56</v>
+        <v>5600</v>
       </c>
       <c r="H752" s="9"/>
       <c r="L752" s="21">
@@ -28047,7 +28047,7 @@
         <v>90</v>
       </c>
       <c r="G753" s="9">
-        <v>58</v>
+        <v>5800</v>
       </c>
       <c r="H753" s="9"/>
       <c r="L753" s="21">
@@ -28078,7 +28078,7 @@
         <v>92</v>
       </c>
       <c r="G754" s="9">
-        <v>60</v>
+        <v>6000</v>
       </c>
       <c r="H754" s="9"/>
       <c r="L754" s="21">
@@ -28109,7 +28109,7 @@
         <v>95</v>
       </c>
       <c r="G755" s="9">
-        <v>62</v>
+        <v>6200</v>
       </c>
       <c r="H755" s="9"/>
       <c r="K755" s="32"/>
@@ -28141,7 +28141,7 @@
         <v>97</v>
       </c>
       <c r="G756" s="9">
-        <v>64</v>
+        <v>6400</v>
       </c>
       <c r="H756" s="9"/>
       <c r="L756" s="21">
@@ -28172,7 +28172,7 @@
         <v>99</v>
       </c>
       <c r="G757" s="9">
-        <v>66</v>
+        <v>6600</v>
       </c>
       <c r="H757" s="9"/>
       <c r="L757" s="21">
@@ -28203,7 +28203,7 @@
         <v>101</v>
       </c>
       <c r="G758" s="9">
-        <v>68</v>
+        <v>6800</v>
       </c>
       <c r="H758" s="9"/>
       <c r="L758" s="21">
@@ -28234,7 +28234,7 @@
         <v>103</v>
       </c>
       <c r="G759" s="9">
-        <v>70</v>
+        <v>7000</v>
       </c>
       <c r="H759" s="9"/>
       <c r="L759" s="21">
@@ -28265,7 +28265,7 @@
         <v>105</v>
       </c>
       <c r="G760" s="9">
-        <v>72</v>
+        <v>7200</v>
       </c>
       <c r="H760" s="9"/>
       <c r="L760" s="21">
@@ -28296,7 +28296,7 @@
         <v>107</v>
       </c>
       <c r="G761" s="9">
-        <v>74</v>
+        <v>7400</v>
       </c>
       <c r="H761" s="9"/>
       <c r="L761" s="21">
@@ -28327,7 +28327,7 @@
         <v>109</v>
       </c>
       <c r="G762" s="9">
-        <v>76</v>
+        <v>7600</v>
       </c>
       <c r="H762" s="9"/>
       <c r="L762" s="21">
@@ -28358,7 +28358,7 @@
         <v>111</v>
       </c>
       <c r="G763" s="9">
-        <v>78</v>
+        <v>7800</v>
       </c>
       <c r="H763" s="9"/>
       <c r="L763" s="21">
@@ -28389,7 +28389,7 @@
         <v>113</v>
       </c>
       <c r="G764" s="9">
-        <v>80</v>
+        <v>8000</v>
       </c>
       <c r="H764" s="9"/>
       <c r="L764" s="21">
@@ -28420,7 +28420,7 @@
         <v>115</v>
       </c>
       <c r="G765" s="9">
-        <v>82</v>
+        <v>8200</v>
       </c>
       <c r="H765" s="9"/>
       <c r="L765" s="21">
@@ -28451,7 +28451,7 @@
         <v>117</v>
       </c>
       <c r="G766" s="9">
-        <v>84</v>
+        <v>8400</v>
       </c>
       <c r="H766" s="9"/>
       <c r="L766" s="21">
@@ -28482,7 +28482,7 @@
         <v>119</v>
       </c>
       <c r="G767" s="9">
-        <v>86</v>
+        <v>8600</v>
       </c>
       <c r="H767" s="9"/>
       <c r="L767" s="21">
@@ -28513,7 +28513,7 @@
         <v>121</v>
       </c>
       <c r="G768" s="9">
-        <v>88</v>
+        <v>8800</v>
       </c>
       <c r="H768" s="9"/>
       <c r="L768" s="21">
@@ -28544,7 +28544,7 @@
         <v>123</v>
       </c>
       <c r="G769" s="9">
-        <v>90</v>
+        <v>9000</v>
       </c>
       <c r="H769" s="9"/>
       <c r="L769" s="21">
@@ -28575,7 +28575,7 @@
         <v>125</v>
       </c>
       <c r="G770" s="9">
-        <v>92</v>
+        <v>9200</v>
       </c>
       <c r="H770" s="9"/>
       <c r="L770" s="21">
@@ -28606,7 +28606,7 @@
         <v>127</v>
       </c>
       <c r="G771" s="9">
-        <v>94</v>
+        <v>9400</v>
       </c>
       <c r="H771" s="9"/>
       <c r="L771" s="21">
@@ -28637,7 +28637,7 @@
         <v>129</v>
       </c>
       <c r="G772" s="9">
-        <v>96</v>
+        <v>9600</v>
       </c>
       <c r="H772" s="9"/>
       <c r="K772" s="8" t="s">
@@ -28671,7 +28671,7 @@
         <v>131</v>
       </c>
       <c r="G773" s="9">
-        <v>98</v>
+        <v>9800</v>
       </c>
       <c r="H773" s="9"/>
       <c r="K773" s="8" t="s">
@@ -28705,7 +28705,7 @@
         <v>133</v>
       </c>
       <c r="G774" s="9">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="H774" s="9"/>
       <c r="K774" s="8" t="s">
@@ -28739,7 +28739,7 @@
         <v>135</v>
       </c>
       <c r="G775" s="9">
-        <v>102</v>
+        <v>10200</v>
       </c>
       <c r="H775" s="9"/>
       <c r="K775" s="8" t="s">
@@ -28773,7 +28773,7 @@
         <v>137</v>
       </c>
       <c r="G776" s="9">
-        <v>104</v>
+        <v>10400</v>
       </c>
       <c r="H776" s="9"/>
       <c r="K776" s="8" t="s">
@@ -28807,7 +28807,7 @@
         <v>139</v>
       </c>
       <c r="G777" s="9">
-        <v>106</v>
+        <v>10600</v>
       </c>
       <c r="H777" s="9"/>
       <c r="K777" s="8" t="s">
@@ -28841,7 +28841,7 @@
         <v>141</v>
       </c>
       <c r="G778" s="9">
-        <v>108</v>
+        <v>10800</v>
       </c>
       <c r="H778" s="9"/>
       <c r="K778" s="8" t="s">
@@ -28875,7 +28875,7 @@
         <v>143</v>
       </c>
       <c r="G779" s="9">
-        <v>110</v>
+        <v>11000</v>
       </c>
       <c r="H779" s="9"/>
       <c r="K779" s="8" t="s">
@@ -28909,7 +28909,7 @@
         <v>145</v>
       </c>
       <c r="G780" s="9">
-        <v>112</v>
+        <v>11200</v>
       </c>
       <c r="H780" s="9"/>
       <c r="K780" s="8" t="s">
@@ -28943,7 +28943,7 @@
         <v>147</v>
       </c>
       <c r="G781" s="9">
-        <v>114</v>
+        <v>11400</v>
       </c>
       <c r="H781" s="9"/>
       <c r="K781" s="8" t="s">
@@ -28977,7 +28977,7 @@
         <v>149</v>
       </c>
       <c r="G782" s="9">
-        <v>116</v>
+        <v>11600</v>
       </c>
       <c r="H782" s="9"/>
       <c r="K782" s="8" t="s">
@@ -29011,7 +29011,7 @@
         <v>151</v>
       </c>
       <c r="G783" s="9">
-        <v>118</v>
+        <v>11800</v>
       </c>
       <c r="H783" s="9"/>
       <c r="K783" s="8" t="s">
@@ -29045,7 +29045,7 @@
         <v>153</v>
       </c>
       <c r="G784" s="9">
-        <v>120</v>
+        <v>12000</v>
       </c>
       <c r="H784" s="9"/>
       <c r="K784" s="8" t="s">

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3631" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -378,7 +378,7 @@
     <t>11021011_11021021_11021031_11021041_11021051_11021061_11021071_11021081_11021091_11021101_11021111_11021121</t>
   </si>
   <si>
-    <t>1102251_1102252_1102253_1102254_1102255_1102256_1102257</t>
+    <t>1102251_1102252_1102253_1102254_1102255_1102256_1102257_1102258_1102259_1102260_1102261_1102262_1102263_1102264_1102265</t>
   </si>
   <si>
     <t>1990000_1000,1990000_1100,1990000_1200,1990000_1300,1990000_1400,1990000_1500,1990000_1600,1990000_1700,1990000_1800</t>
@@ -750,7 +750,7 @@
     <t>11031011_11031021_11031031_11031041_11031051_11031061_11031071_11031081_11031091_11031101</t>
   </si>
   <si>
-    <t>1103251_1103252</t>
+    <t>1103251_1103252_1103253_1103254_1103255_1103256_1103257_1103258_1103259_1103260_1103261_1103262_1103263_1103264_1103265</t>
   </si>
   <si>
     <t>1990000_62000,1990000_68200,1990000_74400,1990000_80600,1990000_86800,1990000_93000,1990000_99200,1990000_105400,1990000_111600</t>
@@ -852,7 +852,7 @@
     <t>11041011_11041021_11041031_11041041_11041051_11041061_11041071_11041081_11041091_11041101</t>
   </si>
   <si>
-    <t>1104251_1104252</t>
+    <t>1104251_1104252_1104253_1104254_1104255_1104256_1104257_1104258_1104259_1104260_1104261_1104262</t>
   </si>
   <si>
     <t>尊享厅</t>
@@ -864,7 +864,7 @@
     <t>11051011_11051021_11051031_11051041_11051051_11051061_11051071_11051081_11051091_11051101</t>
   </si>
   <si>
-    <t>1105251_1105252</t>
+    <t>1105251_1105252_1105253_1105254_1105255_1105256_1105257_1105258_1105259_1105260_1105261_1105262_1105263_1105264_1105265</t>
   </si>
   <si>
     <t>至尊厅</t>
@@ -876,7 +876,7 @@
     <t>11061021_11061031_11061041_11061051_11061061_11061071_11061081_11061091_11061101</t>
   </si>
   <si>
-    <t>1106251_1106252</t>
+    <t>1106252_1106253_1106254_1106255_1106256_1106257_1106258_1106259_1106260</t>
   </si>
   <si>
     <t>博弈扑克厅</t>
@@ -888,7 +888,7 @@
     <t>11071031_11071032_11071033_11071034_11071035_11071036_11071041_11071042_11071043_11071044_11071045_11071046</t>
   </si>
   <si>
-    <t>1107251_1107252_1107253</t>
+    <t>1107251_1107252_1107253_1107254_1107255_1107256_1107257_1107258</t>
   </si>
   <si>
     <t>1107101_1107101_1107101_1107101_1107101_1107101</t>
@@ -912,7 +912,7 @@
     <t>11081031_11081032_11081033_11081034_11081035_11081036_11081041_11081042_11081043_11081044_11081045_11081046</t>
   </si>
   <si>
-    <t>1108251_1108252_1108253_1108254</t>
+    <t>1108251_1108252_1108253_1108254_1108255_1108256_1108257_1108258_1108259_1108260</t>
   </si>
   <si>
     <t>1108101_1108101_1108101_1108101_1108101_1108101</t>
@@ -936,7 +936,7 @@
     <t>11091031_11091032_11091033_11091034_11091035_11091036_11091041_11091042_11091043_11091044_11091045_11091046</t>
   </si>
   <si>
-    <t>1109251_1109252_1109253_1109254</t>
+    <t>1109251_1109252_1109253_1109254_1109255_1109256_1109257_1109258_1109259_1109260</t>
   </si>
   <si>
     <t>1109101_1109101_1109101_1109101_1109101_1109101</t>
@@ -960,7 +960,7 @@
     <t>11101031_11101032_11101033_11101034_11101035_11101036_11101041_11101042_11101043_11101044_11101045_11101046</t>
   </si>
   <si>
-    <t>1110251_1110252_1110253_1110254</t>
+    <t>1110251_1110252_1110253_1110254_1110255_1110256_1110257_1110258_1110259_1110260</t>
   </si>
   <si>
     <t>1110101_1110101_1110101_1110101_1110101_1110101</t>
@@ -984,7 +984,7 @@
     <t>11111031_11111032_11111033_11111034_11111035_11111036_11111041_11111042_11111043_11111044_11111045_11111046</t>
   </si>
   <si>
-    <t>1111251_1111252_1111253_1111254</t>
+    <t>1111251_1111252_1111253_1111254_1111255_1111256_1111257_1111258_1111259_1111260</t>
   </si>
   <si>
     <t>1111101_1111101_1111101_1111101_1111101_1111101</t>
@@ -1008,7 +1008,7 @@
     <t>11121031_11121032_11121033_11121034_11121035_11121036_11121041_11121042_11121043_11121044_11121045_11121046</t>
   </si>
   <si>
-    <t>1112251_1112252_1112253_1112254</t>
+    <t>1112251_1112252_1112253_1112254_1112255_1112256_1112257_1112258_1112259_1112260</t>
   </si>
   <si>
     <t>1112101_1112101_1112101_1112101_1112101_1112101</t>
@@ -1032,7 +1032,7 @@
     <t>12011011_12011012_12011021_12011022_12011031_12011032_12011041_12011042_12011051_12011052_12011061_12011062_12011071_12011072_12011081_12011082_12011091_12011092_12011101_12011102_12011111_12011112_12011121_12011122</t>
   </si>
   <si>
-    <t>1201251_1201252_1201253</t>
+    <t>1201251_1201252_1201253_1201254_1201255</t>
   </si>
   <si>
     <t>VIP休息区</t>
@@ -1044,7 +1044,7 @@
     <t>12021011_12021012_12021021_12021022_12021031_12021032_12021041_12021042_12021051_12021052_12021061_12021062_12021071_12021072_12021081_12021082_12021091_12021092_12021101_12021102_12021111_12021112_12021121_12021122</t>
   </si>
   <si>
-    <t>1202251_1202252_1202261_1202262_1202263</t>
+    <t>1202251_1202252_1202253_1202254_1202255_1202256_1202257_1202258_1202259_1202260_1202261_1202262_1202263_1202264_1202265_1202266_1202267_1202268_1202269_1202270</t>
   </si>
   <si>
     <t>接待区</t>
@@ -1056,10 +1056,7 @@
     <t>研发部&amp;游戏厅</t>
   </si>
   <si>
-    <t>1302251_1302252_1302253_1302254_1302268_1302269_1302270_1302271_1302272_1302273_1302274_1302275_1302276_1302277_1302278_1302279_1302280_1302281_1302282_1302283_1302284_1302285</t>
-  </si>
-  <si>
-    <t>1302255_1302256</t>
+    <t>1302251_1302252_1302253_1302254_1302268_1302269_1302270_1302271_1302272_1302273_1302274_1302275_1302276_1302277_1302278_1302279_1302280_1302281_1302282_1302283_1302284_1302285_1302255_1302256</t>
   </si>
   <si>
     <t>1302257_1302258_1302259</t>
@@ -1086,7 +1083,7 @@
     <t>运营部</t>
   </si>
   <si>
-    <t>1303201_1303202_1303203_1303204</t>
+    <t>1303201_1303202_1303203_1303204_1303205_1303206</t>
   </si>
   <si>
     <t>营销部</t>
@@ -2658,7 +2655,7 @@
         <v>11021131</v>
       </c>
       <c r="K6" s="8">
-        <v>1102258</v>
+        <v>1102266</v>
       </c>
       <c r="L6" s="21">
         <v>2</v>
@@ -2699,7 +2696,7 @@
         <v>11021141</v>
       </c>
       <c r="K7" s="8">
-        <v>1102259</v>
+        <v>1102267</v>
       </c>
       <c r="L7" s="21">
         <v>4</v>
@@ -2740,7 +2737,7 @@
         <v>11021151</v>
       </c>
       <c r="K8" s="8">
-        <v>1102260</v>
+        <v>1102268</v>
       </c>
       <c r="L8" s="21">
         <v>6</v>
@@ -2781,7 +2778,7 @@
         <v>11021161</v>
       </c>
       <c r="K9" s="8">
-        <v>1102261</v>
+        <v>1102269</v>
       </c>
       <c r="L9" s="21">
         <v>8</v>
@@ -2822,7 +2819,7 @@
         <v>11021171</v>
       </c>
       <c r="K10" s="8">
-        <v>1102262</v>
+        <v>1102270</v>
       </c>
       <c r="L10" s="21">
         <v>10</v>
@@ -2863,7 +2860,7 @@
         <v>11021181</v>
       </c>
       <c r="K11" s="8">
-        <v>1102264</v>
+        <v>1102271</v>
       </c>
       <c r="L11" s="21">
         <v>12</v>
@@ -2897,7 +2894,7 @@
       </c>
       <c r="H12" s="9"/>
       <c r="K12" s="8">
-        <v>1102265</v>
+        <v>1102272</v>
       </c>
       <c r="L12" s="21">
         <v>14</v>
@@ -2931,7 +2928,7 @@
       </c>
       <c r="H13" s="9"/>
       <c r="K13" s="8">
-        <v>1102266</v>
+        <v>1102273</v>
       </c>
       <c r="L13" s="21">
         <v>16</v>
@@ -2965,7 +2962,7 @@
       </c>
       <c r="H14" s="9"/>
       <c r="K14" s="8">
-        <v>1102267</v>
+        <v>1102274</v>
       </c>
       <c r="L14" s="21">
         <v>18</v>
@@ -2999,7 +2996,7 @@
       </c>
       <c r="H15" s="9"/>
       <c r="K15" s="8">
-        <v>1102268</v>
+        <v>1102275</v>
       </c>
       <c r="L15" s="21">
         <v>20</v>
@@ -3033,7 +3030,7 @@
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="8">
-        <v>1102269</v>
+        <v>1102276</v>
       </c>
       <c r="L16" s="21">
         <v>22</v>
@@ -3067,7 +3064,7 @@
       </c>
       <c r="H17" s="9"/>
       <c r="K17" s="8">
-        <v>1102270</v>
+        <v>1102277</v>
       </c>
       <c r="L17" s="21">
         <v>24</v>
@@ -3101,7 +3098,7 @@
       </c>
       <c r="H18" s="9"/>
       <c r="K18" s="8">
-        <v>1102271</v>
+        <v>1102278</v>
       </c>
       <c r="L18" s="21">
         <v>26</v>
@@ -3135,7 +3132,7 @@
       </c>
       <c r="H19" s="9"/>
       <c r="K19" s="8">
-        <v>1102272</v>
+        <v>1102279</v>
       </c>
       <c r="L19" s="21">
         <v>28</v>
@@ -3168,9 +3165,6 @@
         <v>4000</v>
       </c>
       <c r="H20" s="9"/>
-      <c r="K20" s="8">
-        <v>1102273</v>
-      </c>
       <c r="L20" s="21">
         <v>30</v>
       </c>
@@ -3202,9 +3196,6 @@
         <v>4200</v>
       </c>
       <c r="H21" s="9"/>
-      <c r="K21" s="8">
-        <v>1102274</v>
-      </c>
       <c r="L21" s="21">
         <v>32</v>
       </c>
@@ -3236,9 +3227,6 @@
         <v>4400</v>
       </c>
       <c r="H22" s="9"/>
-      <c r="K22" s="8">
-        <v>1102275</v>
-      </c>
       <c r="L22" s="21">
         <v>34</v>
       </c>
@@ -3270,9 +3258,6 @@
         <v>4600</v>
       </c>
       <c r="H23" s="9"/>
-      <c r="K23" s="8">
-        <v>1102276</v>
-      </c>
       <c r="L23" s="21">
         <v>36</v>
       </c>
@@ -3304,9 +3289,6 @@
         <v>4800</v>
       </c>
       <c r="H24" s="9"/>
-      <c r="K24" s="8">
-        <v>1102277</v>
-      </c>
       <c r="L24" s="21">
         <v>38</v>
       </c>
@@ -3338,9 +3320,6 @@
         <v>5000</v>
       </c>
       <c r="H25" s="9"/>
-      <c r="K25" s="8">
-        <v>1102278</v>
-      </c>
       <c r="L25" s="21">
         <v>40</v>
       </c>
@@ -3372,9 +3351,6 @@
         <v>5200</v>
       </c>
       <c r="H26" s="9"/>
-      <c r="K26" s="8">
-        <v>1102279</v>
-      </c>
       <c r="L26" s="21">
         <v>42</v>
       </c>
@@ -4723,7 +4699,7 @@
         <v>11031111</v>
       </c>
       <c r="K66" s="26">
-        <v>1103253</v>
+        <v>1103266</v>
       </c>
       <c r="L66" s="27">
         <v>4</v>
@@ -4764,7 +4740,7 @@
         <v>11031121</v>
       </c>
       <c r="K67" s="26">
-        <v>1103254</v>
+        <v>1103267</v>
       </c>
       <c r="L67" s="27">
         <v>8</v>
@@ -4805,7 +4781,7 @@
         <v>11031131</v>
       </c>
       <c r="K68" s="26">
-        <v>1103255</v>
+        <v>1103268</v>
       </c>
       <c r="L68" s="27">
         <v>12</v>
@@ -4845,8 +4821,8 @@
         <f t="shared" si="4"/>
         <v>11031141</v>
       </c>
-      <c r="K69" s="26">
-        <v>1103256</v>
+      <c r="K69" s="29">
+        <v>1103269</v>
       </c>
       <c r="L69" s="27">
         <v>16</v>
@@ -4886,8 +4862,8 @@
         <f t="shared" si="4"/>
         <v>11031151</v>
       </c>
-      <c r="K70" s="26">
-        <v>1103257</v>
+      <c r="K70" s="29">
+        <v>1103270</v>
       </c>
       <c r="L70" s="27">
         <v>20</v>
@@ -4927,8 +4903,8 @@
         <f t="shared" si="4"/>
         <v>11031161</v>
       </c>
-      <c r="K71" s="26">
-        <v>1103258</v>
+      <c r="K71" s="29">
+        <v>1103271</v>
       </c>
       <c r="L71" s="27">
         <v>24</v>
@@ -4963,8 +4939,8 @@
       <c r="H72" s="24"/>
       <c r="I72" s="25"/>
       <c r="J72" s="25"/>
-      <c r="K72" s="26">
-        <v>1103259</v>
+      <c r="K72" s="29">
+        <v>1103272</v>
       </c>
       <c r="L72" s="27">
         <v>28</v>
@@ -4999,8 +4975,8 @@
       <c r="H73" s="24"/>
       <c r="I73" s="25"/>
       <c r="J73" s="25"/>
-      <c r="K73" s="26">
-        <v>1103260</v>
+      <c r="K73" s="29">
+        <v>1103273</v>
       </c>
       <c r="L73" s="27">
         <v>32</v>
@@ -5035,8 +5011,8 @@
       <c r="H74" s="24"/>
       <c r="I74" s="25"/>
       <c r="J74" s="25"/>
-      <c r="K74" s="26">
-        <v>1103261</v>
+      <c r="K74" s="29">
+        <v>1103274</v>
       </c>
       <c r="L74" s="27">
         <v>36</v>
@@ -5071,8 +5047,8 @@
       <c r="H75" s="24"/>
       <c r="I75" s="25"/>
       <c r="J75" s="25"/>
-      <c r="K75" s="26">
-        <v>1103262</v>
+      <c r="K75" s="29">
+        <v>1103275</v>
       </c>
       <c r="L75" s="27">
         <v>40</v>
@@ -5107,9 +5083,6 @@
       <c r="H76" s="24"/>
       <c r="I76" s="25"/>
       <c r="J76" s="25"/>
-      <c r="K76" s="26">
-        <v>1103263</v>
-      </c>
       <c r="L76" s="27">
         <v>44</v>
       </c>
@@ -5143,9 +5116,7 @@
       <c r="H77" s="24"/>
       <c r="I77" s="25"/>
       <c r="J77" s="25"/>
-      <c r="K77" s="26">
-        <v>1103264</v>
-      </c>
+      <c r="K77" s="26"/>
       <c r="L77" s="27">
         <v>48</v>
       </c>
@@ -5179,9 +5150,6 @@
       <c r="H78" s="24"/>
       <c r="I78" s="25"/>
       <c r="J78" s="25"/>
-      <c r="K78" s="26">
-        <v>1103265</v>
-      </c>
       <c r="L78" s="27">
         <v>52</v>
       </c>
@@ -5215,9 +5183,6 @@
       <c r="H79" s="24"/>
       <c r="I79" s="25"/>
       <c r="J79" s="25"/>
-      <c r="K79" s="26">
-        <v>1103266</v>
-      </c>
       <c r="L79" s="27">
         <v>56</v>
       </c>
@@ -5251,9 +5216,6 @@
       <c r="H80" s="24"/>
       <c r="I80" s="25"/>
       <c r="J80" s="25"/>
-      <c r="K80" s="26">
-        <v>1103267</v>
-      </c>
       <c r="L80" s="27">
         <v>60</v>
       </c>
@@ -5287,9 +5249,6 @@
       <c r="H81" s="24"/>
       <c r="I81" s="25"/>
       <c r="J81" s="25"/>
-      <c r="K81" s="26">
-        <v>1103268</v>
-      </c>
       <c r="L81" s="27">
         <v>64</v>
       </c>
@@ -5323,9 +5282,6 @@
       <c r="H82" s="24"/>
       <c r="I82" s="25"/>
       <c r="J82" s="25"/>
-      <c r="K82" s="29">
-        <v>1103269</v>
-      </c>
       <c r="L82" s="27">
         <v>68</v>
       </c>
@@ -5359,9 +5315,6 @@
       <c r="H83" s="24"/>
       <c r="I83" s="25"/>
       <c r="J83" s="25"/>
-      <c r="K83" s="29">
-        <v>1103270</v>
-      </c>
       <c r="L83" s="27">
         <v>72</v>
       </c>
@@ -5395,9 +5348,6 @@
       <c r="H84" s="24"/>
       <c r="I84" s="25"/>
       <c r="J84" s="25"/>
-      <c r="K84" s="29">
-        <v>1103271</v>
-      </c>
       <c r="L84" s="27">
         <v>76</v>
       </c>
@@ -5431,9 +5381,6 @@
       <c r="H85" s="24"/>
       <c r="I85" s="25"/>
       <c r="J85" s="25"/>
-      <c r="K85" s="29">
-        <v>1103272</v>
-      </c>
       <c r="L85" s="27">
         <v>80</v>
       </c>
@@ -5467,9 +5414,6 @@
       <c r="H86" s="24"/>
       <c r="I86" s="25"/>
       <c r="J86" s="25"/>
-      <c r="K86" s="29">
-        <v>1103273</v>
-      </c>
       <c r="L86" s="27">
         <v>84</v>
       </c>
@@ -5503,9 +5447,6 @@
       <c r="H87" s="24"/>
       <c r="I87" s="25"/>
       <c r="J87" s="25"/>
-      <c r="K87" s="29">
-        <v>1103274</v>
-      </c>
       <c r="L87" s="27">
         <v>88</v>
       </c>
@@ -5539,9 +5480,6 @@
       <c r="H88" s="24"/>
       <c r="I88" s="25"/>
       <c r="J88" s="25"/>
-      <c r="K88" s="29">
-        <v>1103275</v>
-      </c>
       <c r="L88" s="27">
         <v>92</v>
       </c>
@@ -6913,7 +6851,7 @@
         <v>11041111</v>
       </c>
       <c r="K126" s="8">
-        <v>1104253</v>
+        <v>1104263</v>
       </c>
       <c r="L126" s="21">
         <v>4</v>
@@ -6954,7 +6892,7 @@
         <v>11041121</v>
       </c>
       <c r="K127" s="8">
-        <v>1104254</v>
+        <v>1104264</v>
       </c>
       <c r="L127" s="21">
         <v>8</v>
@@ -6995,7 +6933,7 @@
         <v>11041131</v>
       </c>
       <c r="K128" s="8">
-        <v>1104255</v>
+        <v>1104265</v>
       </c>
       <c r="L128" s="21">
         <v>12</v>
@@ -7036,7 +6974,7 @@
         <v>11041141</v>
       </c>
       <c r="K129" s="8">
-        <v>1104256</v>
+        <v>1104266</v>
       </c>
       <c r="L129" s="21">
         <v>16</v>
@@ -7077,7 +7015,7 @@
         <v>11041151</v>
       </c>
       <c r="K130" s="8">
-        <v>1104257</v>
+        <v>1104267</v>
       </c>
       <c r="L130" s="21">
         <v>20</v>
@@ -7118,7 +7056,7 @@
         <v>11041161</v>
       </c>
       <c r="K131" s="8">
-        <v>1104258</v>
+        <v>1104268</v>
       </c>
       <c r="L131" s="21">
         <v>24</v>
@@ -7152,7 +7090,7 @@
       </c>
       <c r="H132" s="9"/>
       <c r="K132" s="8">
-        <v>1104259</v>
+        <v>1104269</v>
       </c>
       <c r="L132" s="21">
         <v>28</v>
@@ -7186,7 +7124,7 @@
       </c>
       <c r="H133" s="9"/>
       <c r="K133" s="8">
-        <v>1104260</v>
+        <v>1104270</v>
       </c>
       <c r="L133" s="21">
         <v>32</v>
@@ -7220,7 +7158,7 @@
       </c>
       <c r="H134" s="9"/>
       <c r="K134" s="8">
-        <v>1104261</v>
+        <v>1104271</v>
       </c>
       <c r="L134" s="21">
         <v>36</v>
@@ -7254,7 +7192,7 @@
       </c>
       <c r="H135" s="9"/>
       <c r="K135" s="8">
-        <v>1104262</v>
+        <v>1104272</v>
       </c>
       <c r="L135" s="21">
         <v>40</v>
@@ -7287,9 +7225,6 @@
         <v>13000</v>
       </c>
       <c r="H136" s="9"/>
-      <c r="K136" s="8">
-        <v>1104263</v>
-      </c>
       <c r="L136" s="21">
         <v>44</v>
       </c>
@@ -7321,9 +7256,6 @@
         <v>14000</v>
       </c>
       <c r="H137" s="9"/>
-      <c r="K137" s="8">
-        <v>1104264</v>
-      </c>
       <c r="L137" s="21">
         <v>48</v>
       </c>
@@ -7355,9 +7287,6 @@
         <v>15000</v>
       </c>
       <c r="H138" s="9"/>
-      <c r="K138" s="8">
-        <v>1104265</v>
-      </c>
       <c r="L138" s="21">
         <v>52</v>
       </c>
@@ -7389,9 +7318,6 @@
         <v>16000</v>
       </c>
       <c r="H139" s="9"/>
-      <c r="K139" s="8">
-        <v>1104266</v>
-      </c>
       <c r="L139" s="21">
         <v>56</v>
       </c>
@@ -7423,9 +7349,6 @@
         <v>17000</v>
       </c>
       <c r="H140" s="9"/>
-      <c r="K140" s="8">
-        <v>1104267</v>
-      </c>
       <c r="L140" s="21">
         <v>60</v>
       </c>
@@ -7457,9 +7380,6 @@
         <v>18000</v>
       </c>
       <c r="H141" s="9"/>
-      <c r="K141" s="8">
-        <v>1104268</v>
-      </c>
       <c r="L141" s="21">
         <v>64</v>
       </c>
@@ -7491,9 +7411,6 @@
         <v>19000</v>
       </c>
       <c r="H142" s="9"/>
-      <c r="K142" s="8">
-        <v>1104269</v>
-      </c>
       <c r="L142" s="21">
         <v>68</v>
       </c>
@@ -7525,9 +7442,6 @@
         <v>20000</v>
       </c>
       <c r="H143" s="9"/>
-      <c r="K143" s="8">
-        <v>1104270</v>
-      </c>
       <c r="L143" s="21">
         <v>72</v>
       </c>
@@ -7559,9 +7473,6 @@
         <v>21000</v>
       </c>
       <c r="H144" s="9"/>
-      <c r="K144" s="8">
-        <v>1104271</v>
-      </c>
       <c r="L144" s="21">
         <v>76</v>
       </c>
@@ -7593,9 +7504,6 @@
         <v>22000</v>
       </c>
       <c r="H145" s="9"/>
-      <c r="K145" s="8">
-        <v>1104272</v>
-      </c>
       <c r="L145" s="21">
         <v>80</v>
       </c>
@@ -8996,7 +8904,7 @@
         <v>11051111</v>
       </c>
       <c r="K186" s="26">
-        <v>1105253</v>
+        <v>1105266</v>
       </c>
       <c r="L186" s="27">
         <v>4</v>
@@ -9037,7 +8945,7 @@
         <v>11051121</v>
       </c>
       <c r="K187" s="26">
-        <v>1105254</v>
+        <v>1105267</v>
       </c>
       <c r="L187" s="27">
         <v>8</v>
@@ -9078,7 +8986,7 @@
         <v>11051131</v>
       </c>
       <c r="K188" s="26">
-        <v>1105255</v>
+        <v>1105268</v>
       </c>
       <c r="L188" s="27">
         <v>12</v>
@@ -9118,8 +9026,8 @@
         <f t="shared" si="10"/>
         <v>11051141</v>
       </c>
-      <c r="K189" s="26">
-        <v>1105256</v>
+      <c r="K189" s="29">
+        <v>1105269</v>
       </c>
       <c r="L189" s="27">
         <v>16</v>
@@ -9159,8 +9067,8 @@
         <f t="shared" si="10"/>
         <v>11051151</v>
       </c>
-      <c r="K190" s="26">
-        <v>1105257</v>
+      <c r="K190" s="29">
+        <v>1105270</v>
       </c>
       <c r="L190" s="27">
         <v>20</v>
@@ -9200,8 +9108,8 @@
         <f t="shared" si="10"/>
         <v>11051161</v>
       </c>
-      <c r="K191" s="26">
-        <v>1105258</v>
+      <c r="K191" s="29">
+        <v>1105271</v>
       </c>
       <c r="L191" s="27">
         <v>24</v>
@@ -9236,8 +9144,8 @@
       <c r="H192" s="24"/>
       <c r="I192" s="25"/>
       <c r="J192" s="31"/>
-      <c r="K192" s="26">
-        <v>1105259</v>
+      <c r="K192" s="29">
+        <v>1105272</v>
       </c>
       <c r="L192" s="27">
         <v>28</v>
@@ -9272,8 +9180,8 @@
       <c r="H193" s="24"/>
       <c r="I193" s="25"/>
       <c r="J193" s="31"/>
-      <c r="K193" s="26">
-        <v>1105260</v>
+      <c r="K193" s="29">
+        <v>1105273</v>
       </c>
       <c r="L193" s="27">
         <v>32</v>
@@ -9308,8 +9216,8 @@
       <c r="H194" s="24"/>
       <c r="I194" s="25"/>
       <c r="J194" s="31"/>
-      <c r="K194" s="26">
-        <v>1105261</v>
+      <c r="K194" s="29">
+        <v>1105274</v>
       </c>
       <c r="L194" s="27">
         <v>36</v>
@@ -9344,8 +9252,8 @@
       <c r="H195" s="24"/>
       <c r="I195" s="25"/>
       <c r="J195" s="31"/>
-      <c r="K195" s="26">
-        <v>1105262</v>
+      <c r="K195" s="29">
+        <v>1105275</v>
       </c>
       <c r="L195" s="27">
         <v>40</v>
@@ -9380,9 +9288,7 @@
       <c r="H196" s="24"/>
       <c r="I196" s="25"/>
       <c r="J196" s="31"/>
-      <c r="K196" s="26">
-        <v>1105263</v>
-      </c>
+      <c r="K196" s="26"/>
       <c r="L196" s="27">
         <v>44</v>
       </c>
@@ -9416,9 +9322,7 @@
       <c r="H197" s="24"/>
       <c r="I197" s="25"/>
       <c r="J197" s="31"/>
-      <c r="K197" s="26">
-        <v>1105264</v>
-      </c>
+      <c r="K197" s="26"/>
       <c r="L197" s="27">
         <v>48</v>
       </c>
@@ -9452,9 +9356,7 @@
       <c r="H198" s="24"/>
       <c r="I198" s="25"/>
       <c r="J198" s="31"/>
-      <c r="K198" s="26">
-        <v>1105265</v>
-      </c>
+      <c r="K198" s="26"/>
       <c r="L198" s="27">
         <v>52</v>
       </c>
@@ -9488,9 +9390,6 @@
       <c r="H199" s="24"/>
       <c r="I199" s="25"/>
       <c r="J199" s="31"/>
-      <c r="K199" s="26">
-        <v>1105266</v>
-      </c>
       <c r="L199" s="27">
         <v>56</v>
       </c>
@@ -9524,9 +9423,6 @@
       <c r="H200" s="24"/>
       <c r="I200" s="25"/>
       <c r="J200" s="31"/>
-      <c r="K200" s="26">
-        <v>1105267</v>
-      </c>
       <c r="L200" s="27">
         <v>60</v>
       </c>
@@ -9560,9 +9456,6 @@
       <c r="H201" s="24"/>
       <c r="I201" s="25"/>
       <c r="J201" s="25"/>
-      <c r="K201" s="26">
-        <v>1105268</v>
-      </c>
       <c r="L201" s="27">
         <v>64</v>
       </c>
@@ -9596,9 +9489,6 @@
       <c r="H202" s="24"/>
       <c r="I202" s="25"/>
       <c r="J202" s="25"/>
-      <c r="K202" s="29">
-        <v>1105269</v>
-      </c>
       <c r="L202" s="27">
         <v>68</v>
       </c>
@@ -9632,9 +9522,6 @@
       <c r="H203" s="24"/>
       <c r="I203" s="25"/>
       <c r="J203" s="25"/>
-      <c r="K203" s="29">
-        <v>1105270</v>
-      </c>
       <c r="L203" s="27">
         <v>72</v>
       </c>
@@ -9668,9 +9555,6 @@
       <c r="H204" s="24"/>
       <c r="I204" s="25"/>
       <c r="J204" s="25"/>
-      <c r="K204" s="29">
-        <v>1105271</v>
-      </c>
       <c r="L204" s="27">
         <v>76</v>
       </c>
@@ -9704,9 +9588,6 @@
       <c r="H205" s="24"/>
       <c r="I205" s="25"/>
       <c r="J205" s="25"/>
-      <c r="K205" s="29">
-        <v>1105272</v>
-      </c>
       <c r="L205" s="27">
         <v>80</v>
       </c>
@@ -9740,9 +9621,6 @@
       <c r="H206" s="24"/>
       <c r="I206" s="25"/>
       <c r="J206" s="25"/>
-      <c r="K206" s="29">
-        <v>1105273</v>
-      </c>
       <c r="L206" s="27">
         <v>84</v>
       </c>
@@ -9776,9 +9654,6 @@
       <c r="H207" s="24"/>
       <c r="I207" s="25"/>
       <c r="J207" s="25"/>
-      <c r="K207" s="29">
-        <v>1105274</v>
-      </c>
       <c r="L207" s="27">
         <v>88</v>
       </c>
@@ -9812,9 +9687,6 @@
       <c r="H208" s="24"/>
       <c r="I208" s="25"/>
       <c r="J208" s="25"/>
-      <c r="K208" s="29">
-        <v>1105275</v>
-      </c>
       <c r="L208" s="27">
         <v>92</v>
       </c>
@@ -11186,7 +11058,7 @@
         <v>11061111</v>
       </c>
       <c r="K246" s="8">
-        <v>1106253</v>
+        <v>1106261</v>
       </c>
       <c r="L246" s="21">
         <v>4</v>
@@ -11227,7 +11099,7 @@
         <v>11061121</v>
       </c>
       <c r="K247" s="8">
-        <v>1106254</v>
+        <v>1106262</v>
       </c>
       <c r="L247" s="21">
         <v>8</v>
@@ -11268,7 +11140,7 @@
         <v>11061131</v>
       </c>
       <c r="K248" s="8">
-        <v>1106255</v>
+        <v>1106263</v>
       </c>
       <c r="L248" s="21">
         <v>12</v>
@@ -11309,7 +11181,7 @@
         <v>11061141</v>
       </c>
       <c r="K249" s="8">
-        <v>1106256</v>
+        <v>1106264</v>
       </c>
       <c r="L249" s="21">
         <v>16</v>
@@ -11350,7 +11222,7 @@
         <v>11061151</v>
       </c>
       <c r="K250" s="8">
-        <v>1106257</v>
+        <v>1106265</v>
       </c>
       <c r="L250" s="21">
         <v>20</v>
@@ -11391,7 +11263,7 @@
         <v>11061161</v>
       </c>
       <c r="K251" s="8">
-        <v>1106258</v>
+        <v>1106266</v>
       </c>
       <c r="L251" s="21">
         <v>24</v>
@@ -11426,7 +11298,7 @@
       <c r="H252" s="9"/>
       <c r="J252" s="32"/>
       <c r="K252" s="8">
-        <v>1106259</v>
+        <v>1106267</v>
       </c>
       <c r="L252" s="21">
         <v>28</v>
@@ -11461,7 +11333,7 @@
       <c r="H253" s="9"/>
       <c r="J253" s="32"/>
       <c r="K253" s="8">
-        <v>1106260</v>
+        <v>1106268</v>
       </c>
       <c r="L253" s="21">
         <v>32</v>
@@ -11496,7 +11368,7 @@
       <c r="H254" s="9"/>
       <c r="J254" s="32"/>
       <c r="K254" s="8">
-        <v>1106261</v>
+        <v>1106269</v>
       </c>
       <c r="L254" s="21">
         <v>36</v>
@@ -11531,7 +11403,7 @@
       <c r="H255" s="9"/>
       <c r="J255" s="32"/>
       <c r="K255" s="8">
-        <v>1106262</v>
+        <v>1106270</v>
       </c>
       <c r="L255" s="21">
         <v>40</v>
@@ -11565,9 +11437,6 @@
       </c>
       <c r="H256" s="9"/>
       <c r="J256" s="32"/>
-      <c r="K256" s="8">
-        <v>1106263</v>
-      </c>
       <c r="L256" s="21">
         <v>44</v>
       </c>
@@ -11600,9 +11469,6 @@
       </c>
       <c r="H257" s="9"/>
       <c r="J257" s="32"/>
-      <c r="K257" s="8">
-        <v>1106264</v>
-      </c>
       <c r="L257" s="21">
         <v>48</v>
       </c>
@@ -11635,9 +11501,6 @@
       </c>
       <c r="H258" s="9"/>
       <c r="J258" s="32"/>
-      <c r="K258" s="8">
-        <v>1106265</v>
-      </c>
       <c r="L258" s="21">
         <v>52</v>
       </c>
@@ -11670,9 +11533,6 @@
       </c>
       <c r="H259" s="9"/>
       <c r="J259" s="32"/>
-      <c r="K259" s="8">
-        <v>1106266</v>
-      </c>
       <c r="L259" s="21">
         <v>56</v>
       </c>
@@ -11705,9 +11565,6 @@
       </c>
       <c r="H260" s="9"/>
       <c r="J260" s="32"/>
-      <c r="K260" s="8">
-        <v>1106267</v>
-      </c>
       <c r="L260" s="21">
         <v>60</v>
       </c>
@@ -11739,9 +11596,6 @@
         <v>18000</v>
       </c>
       <c r="H261" s="9"/>
-      <c r="K261" s="8">
-        <v>1106268</v>
-      </c>
       <c r="L261" s="21">
         <v>64</v>
       </c>
@@ -11773,9 +11627,6 @@
         <v>19000</v>
       </c>
       <c r="H262" s="9"/>
-      <c r="K262" s="8">
-        <v>1106269</v>
-      </c>
       <c r="L262" s="21">
         <v>68</v>
       </c>
@@ -11807,9 +11658,6 @@
         <v>20000</v>
       </c>
       <c r="H263" s="9"/>
-      <c r="K263" s="8">
-        <v>1106270</v>
-      </c>
       <c r="L263" s="21">
         <v>72</v>
       </c>
@@ -13277,7 +13125,7 @@
         <v>206</v>
       </c>
       <c r="K306" s="26">
-        <v>1107254</v>
+        <v>1107259</v>
       </c>
       <c r="L306" s="27">
         <v>2</v>
@@ -13317,7 +13165,7 @@
         <v>208</v>
       </c>
       <c r="K307" s="26">
-        <v>1107255</v>
+        <v>1107260</v>
       </c>
       <c r="L307" s="27">
         <v>4</v>
@@ -13351,7 +13199,7 @@
       </c>
       <c r="H308" s="24"/>
       <c r="K308" s="26">
-        <v>1107256</v>
+        <v>1107261</v>
       </c>
       <c r="L308" s="27">
         <v>6</v>
@@ -13387,7 +13235,7 @@
       <c r="I309" s="25"/>
       <c r="J309" s="25"/>
       <c r="K309" s="26">
-        <v>1107257</v>
+        <v>1107262</v>
       </c>
       <c r="L309" s="27">
         <v>8</v>
@@ -13423,7 +13271,7 @@
       <c r="I310" s="25"/>
       <c r="J310" s="25"/>
       <c r="K310" s="26">
-        <v>1107258</v>
+        <v>1107263</v>
       </c>
       <c r="L310" s="27">
         <v>10</v>
@@ -13459,7 +13307,7 @@
       <c r="I311" s="25"/>
       <c r="J311" s="31"/>
       <c r="K311" s="26">
-        <v>1107259</v>
+        <v>1107264</v>
       </c>
       <c r="L311" s="27">
         <v>12</v>
@@ -13495,7 +13343,7 @@
       <c r="I312" s="25"/>
       <c r="J312" s="31"/>
       <c r="K312" s="26">
-        <v>1107260</v>
+        <v>1107265</v>
       </c>
       <c r="L312" s="27">
         <v>14</v>
@@ -13531,7 +13379,7 @@
       <c r="I313" s="25"/>
       <c r="J313" s="31"/>
       <c r="K313" s="26">
-        <v>1107261</v>
+        <v>1107266</v>
       </c>
       <c r="L313" s="27">
         <v>16</v>
@@ -13567,7 +13415,7 @@
       <c r="I314" s="25"/>
       <c r="J314" s="31"/>
       <c r="K314" s="26">
-        <v>1107262</v>
+        <v>1107267</v>
       </c>
       <c r="L314" s="27">
         <v>18</v>
@@ -13602,9 +13450,6 @@
       <c r="H315" s="24"/>
       <c r="I315" s="25"/>
       <c r="J315" s="31"/>
-      <c r="K315" s="26">
-        <v>1107263</v>
-      </c>
       <c r="L315" s="27">
         <v>20</v>
       </c>
@@ -13638,9 +13483,6 @@
       <c r="H316" s="24"/>
       <c r="I316" s="25"/>
       <c r="J316" s="31"/>
-      <c r="K316" s="26">
-        <v>1107264</v>
-      </c>
       <c r="L316" s="27">
         <v>22</v>
       </c>
@@ -13674,9 +13516,6 @@
       <c r="H317" s="24"/>
       <c r="I317" s="25"/>
       <c r="J317" s="25"/>
-      <c r="K317" s="26">
-        <v>1107265</v>
-      </c>
       <c r="L317" s="27">
         <v>24</v>
       </c>
@@ -13710,9 +13549,6 @@
       <c r="H318" s="24"/>
       <c r="I318" s="25"/>
       <c r="J318" s="25"/>
-      <c r="K318" s="26">
-        <v>1107266</v>
-      </c>
       <c r="L318" s="27">
         <v>26</v>
       </c>
@@ -13746,9 +13582,6 @@
       <c r="H319" s="24"/>
       <c r="I319" s="25"/>
       <c r="J319" s="25"/>
-      <c r="K319" s="26">
-        <v>1107267</v>
-      </c>
       <c r="L319" s="27">
         <v>28</v>
       </c>
@@ -15423,7 +15256,7 @@
         <v>214</v>
       </c>
       <c r="K366" s="8">
-        <v>1108255</v>
+        <v>1108261</v>
       </c>
       <c r="L366" s="21">
         <v>4</v>
@@ -15463,7 +15296,7 @@
         <v>216</v>
       </c>
       <c r="K367" s="8">
-        <v>1108256</v>
+        <v>1108262</v>
       </c>
       <c r="L367" s="21">
         <v>8</v>
@@ -15497,7 +15330,7 @@
       </c>
       <c r="H368" s="9"/>
       <c r="K368" s="8">
-        <v>1108257</v>
+        <v>1108263</v>
       </c>
       <c r="L368" s="21">
         <v>12</v>
@@ -15531,7 +15364,7 @@
       </c>
       <c r="H369" s="9"/>
       <c r="K369" s="8">
-        <v>1108258</v>
+        <v>1108264</v>
       </c>
       <c r="L369" s="21">
         <v>16</v>
@@ -15565,7 +15398,7 @@
       </c>
       <c r="H370" s="9"/>
       <c r="K370" s="8">
-        <v>1108259</v>
+        <v>1108265</v>
       </c>
       <c r="L370" s="21">
         <v>20</v>
@@ -15599,7 +15432,7 @@
       </c>
       <c r="H371" s="9"/>
       <c r="K371" s="8">
-        <v>1108260</v>
+        <v>1108266</v>
       </c>
       <c r="L371" s="21">
         <v>24</v>
@@ -15633,7 +15466,7 @@
       </c>
       <c r="H372" s="9"/>
       <c r="K372" s="8">
-        <v>1108261</v>
+        <v>1108267</v>
       </c>
       <c r="L372" s="21">
         <v>28</v>
@@ -15667,7 +15500,7 @@
       </c>
       <c r="H373" s="9"/>
       <c r="K373" s="8">
-        <v>1108262</v>
+        <v>1108268</v>
       </c>
       <c r="L373" s="21">
         <v>32</v>
@@ -15700,9 +15533,6 @@
         <v>1900</v>
       </c>
       <c r="H374" s="9"/>
-      <c r="K374" s="8">
-        <v>1108263</v>
-      </c>
       <c r="L374" s="21">
         <v>36</v>
       </c>
@@ -15734,9 +15564,6 @@
         <v>2000</v>
       </c>
       <c r="H375" s="9"/>
-      <c r="K375" s="8">
-        <v>1108264</v>
-      </c>
       <c r="L375" s="21">
         <v>40</v>
       </c>
@@ -15768,9 +15595,6 @@
         <v>2100</v>
       </c>
       <c r="H376" s="9"/>
-      <c r="K376" s="8">
-        <v>1108265</v>
-      </c>
       <c r="L376" s="21">
         <v>44</v>
       </c>
@@ -15802,9 +15626,6 @@
         <v>2200</v>
       </c>
       <c r="H377" s="9"/>
-      <c r="K377" s="8">
-        <v>1108266</v>
-      </c>
       <c r="L377" s="21">
         <v>48</v>
       </c>
@@ -15836,9 +15657,6 @@
         <v>2300</v>
       </c>
       <c r="H378" s="9"/>
-      <c r="K378" s="8">
-        <v>1108267</v>
-      </c>
       <c r="L378" s="21">
         <v>52</v>
       </c>
@@ -15870,9 +15688,6 @@
         <v>2400</v>
       </c>
       <c r="H379" s="9"/>
-      <c r="K379" s="8">
-        <v>1108268</v>
-      </c>
       <c r="L379" s="21">
         <v>56</v>
       </c>
@@ -17449,7 +17264,7 @@
         <v>222</v>
       </c>
       <c r="K426" s="26">
-        <v>1109255</v>
+        <v>1109261</v>
       </c>
       <c r="L426" s="27">
         <v>4</v>
@@ -17489,7 +17304,7 @@
         <v>224</v>
       </c>
       <c r="K427" s="26">
-        <v>1109256</v>
+        <v>1109262</v>
       </c>
       <c r="L427" s="27">
         <v>8</v>
@@ -17525,7 +17340,7 @@
       <c r="I428" s="25"/>
       <c r="J428" s="25"/>
       <c r="K428" s="26">
-        <v>1109257</v>
+        <v>1109263</v>
       </c>
       <c r="L428" s="27">
         <v>12</v>
@@ -17559,7 +17374,7 @@
       </c>
       <c r="H429" s="24"/>
       <c r="K429" s="26">
-        <v>1109258</v>
+        <v>1109264</v>
       </c>
       <c r="L429" s="27">
         <v>16</v>
@@ -17595,7 +17410,7 @@
       <c r="I430" s="25"/>
       <c r="J430" s="25"/>
       <c r="K430" s="26">
-        <v>1109259</v>
+        <v>1109265</v>
       </c>
       <c r="L430" s="27">
         <v>20</v>
@@ -17631,7 +17446,7 @@
       <c r="I431" s="25"/>
       <c r="J431" s="25"/>
       <c r="K431" s="26">
-        <v>1109260</v>
+        <v>1109266</v>
       </c>
       <c r="L431" s="27">
         <v>24</v>
@@ -17667,7 +17482,7 @@
       <c r="I432" s="25"/>
       <c r="J432" s="25"/>
       <c r="K432" s="26">
-        <v>1109261</v>
+        <v>1109267</v>
       </c>
       <c r="L432" s="27">
         <v>28</v>
@@ -17703,7 +17518,7 @@
       <c r="I433" s="25"/>
       <c r="J433" s="25"/>
       <c r="K433" s="26">
-        <v>1109262</v>
+        <v>1109268</v>
       </c>
       <c r="L433" s="27">
         <v>32</v>
@@ -17738,9 +17553,6 @@
       <c r="H434" s="24"/>
       <c r="I434" s="25"/>
       <c r="J434" s="25"/>
-      <c r="K434" s="26">
-        <v>1109263</v>
-      </c>
       <c r="L434" s="27">
         <v>36</v>
       </c>
@@ -17774,9 +17586,6 @@
       <c r="H435" s="24"/>
       <c r="I435" s="25"/>
       <c r="J435" s="25"/>
-      <c r="K435" s="26">
-        <v>1109264</v>
-      </c>
       <c r="L435" s="27">
         <v>40</v>
       </c>
@@ -17810,9 +17619,6 @@
       <c r="H436" s="24"/>
       <c r="I436" s="25"/>
       <c r="J436" s="25"/>
-      <c r="K436" s="26">
-        <v>1109265</v>
-      </c>
       <c r="L436" s="27">
         <v>44</v>
       </c>
@@ -17846,9 +17652,6 @@
       <c r="H437" s="24"/>
       <c r="I437" s="25"/>
       <c r="J437" s="25"/>
-      <c r="K437" s="26">
-        <v>1109266</v>
-      </c>
       <c r="L437" s="27">
         <v>48</v>
       </c>
@@ -17882,9 +17685,6 @@
       <c r="H438" s="24"/>
       <c r="I438" s="25"/>
       <c r="J438" s="25"/>
-      <c r="K438" s="26">
-        <v>1109267</v>
-      </c>
       <c r="L438" s="27">
         <v>52</v>
       </c>
@@ -17918,9 +17718,6 @@
       <c r="H439" s="24"/>
       <c r="I439" s="25"/>
       <c r="J439" s="25"/>
-      <c r="K439" s="26">
-        <v>1109268</v>
-      </c>
       <c r="L439" s="27">
         <v>56</v>
       </c>
@@ -19597,7 +19394,7 @@
         <v>230</v>
       </c>
       <c r="K486" s="8">
-        <v>1110255</v>
+        <v>1110261</v>
       </c>
       <c r="L486" s="21">
         <v>2</v>
@@ -19637,7 +19434,7 @@
         <v>232</v>
       </c>
       <c r="K487" s="8">
-        <v>1110256</v>
+        <v>1110262</v>
       </c>
       <c r="L487" s="21">
         <v>4</v>
@@ -19671,7 +19468,7 @@
       </c>
       <c r="H488" s="9"/>
       <c r="K488" s="8">
-        <v>1110257</v>
+        <v>1110263</v>
       </c>
       <c r="L488" s="21">
         <v>6</v>
@@ -19705,7 +19502,7 @@
       </c>
       <c r="H489" s="9"/>
       <c r="K489" s="8">
-        <v>1110258</v>
+        <v>1110264</v>
       </c>
       <c r="L489" s="21">
         <v>8</v>
@@ -19739,7 +19536,7 @@
       </c>
       <c r="H490" s="9"/>
       <c r="K490" s="8">
-        <v>1110259</v>
+        <v>1110265</v>
       </c>
       <c r="L490" s="21">
         <v>10</v>
@@ -19773,7 +19570,7 @@
       </c>
       <c r="H491" s="9"/>
       <c r="K491" s="8">
-        <v>1110260</v>
+        <v>1110266</v>
       </c>
       <c r="L491" s="21">
         <v>12</v>
@@ -19807,7 +19604,7 @@
       </c>
       <c r="H492" s="9"/>
       <c r="K492" s="8">
-        <v>1110261</v>
+        <v>1110267</v>
       </c>
       <c r="L492" s="21">
         <v>14</v>
@@ -19841,7 +19638,7 @@
       </c>
       <c r="H493" s="9"/>
       <c r="K493" s="8">
-        <v>1110262</v>
+        <v>1110268</v>
       </c>
       <c r="L493" s="21">
         <v>16</v>
@@ -19875,7 +19672,7 @@
       </c>
       <c r="H494" s="9"/>
       <c r="K494" s="8">
-        <v>1110263</v>
+        <v>1110269</v>
       </c>
       <c r="L494" s="21">
         <v>18</v>
@@ -19909,7 +19706,7 @@
       </c>
       <c r="H495" s="9"/>
       <c r="K495" s="8">
-        <v>1110264</v>
+        <v>1110270</v>
       </c>
       <c r="L495" s="21">
         <v>20</v>
@@ -19942,9 +19739,6 @@
         <v>2100</v>
       </c>
       <c r="H496" s="9"/>
-      <c r="K496" s="8">
-        <v>1110265</v>
-      </c>
       <c r="L496" s="21">
         <v>22</v>
       </c>
@@ -19976,9 +19770,6 @@
         <v>2200</v>
       </c>
       <c r="H497" s="9"/>
-      <c r="K497" s="8">
-        <v>1110266</v>
-      </c>
       <c r="L497" s="21">
         <v>24</v>
       </c>
@@ -20010,9 +19801,6 @@
         <v>2300</v>
       </c>
       <c r="H498" s="9"/>
-      <c r="K498" s="8">
-        <v>1110267</v>
-      </c>
       <c r="L498" s="21">
         <v>26</v>
       </c>
@@ -20044,9 +19832,6 @@
         <v>2400</v>
       </c>
       <c r="H499" s="9"/>
-      <c r="K499" s="8">
-        <v>1110268</v>
-      </c>
       <c r="L499" s="21">
         <v>28</v>
       </c>
@@ -20078,9 +19863,6 @@
         <v>2500</v>
       </c>
       <c r="H500" s="9"/>
-      <c r="K500" s="8">
-        <v>1110269</v>
-      </c>
       <c r="L500" s="21">
         <v>30</v>
       </c>
@@ -20112,9 +19894,6 @@
         <v>2600</v>
       </c>
       <c r="H501" s="9"/>
-      <c r="K501" s="8">
-        <v>1110270</v>
-      </c>
       <c r="L501" s="21">
         <v>32</v>
       </c>
@@ -21628,8 +21407,8 @@
       <c r="J546" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="K546" s="31">
-        <v>1111255</v>
+      <c r="K546" s="26">
+        <v>1111261</v>
       </c>
       <c r="L546" s="27">
         <v>4</v>
@@ -21669,7 +21448,7 @@
         <v>240</v>
       </c>
       <c r="K547" s="26">
-        <v>1111256</v>
+        <v>1111262</v>
       </c>
       <c r="L547" s="27">
         <v>8</v>
@@ -21705,7 +21484,7 @@
       <c r="I548" s="25"/>
       <c r="J548" s="25"/>
       <c r="K548" s="26">
-        <v>1111257</v>
+        <v>1111263</v>
       </c>
       <c r="L548" s="27">
         <v>12</v>
@@ -21739,7 +21518,7 @@
       </c>
       <c r="H549" s="24"/>
       <c r="K549" s="26">
-        <v>1111258</v>
+        <v>1111264</v>
       </c>
       <c r="L549" s="27">
         <v>16</v>
@@ -21775,7 +21554,7 @@
       <c r="I550" s="25"/>
       <c r="J550" s="25"/>
       <c r="K550" s="26">
-        <v>1111259</v>
+        <v>1111265</v>
       </c>
       <c r="L550" s="27">
         <v>20</v>
@@ -21811,7 +21590,7 @@
       <c r="I551" s="25"/>
       <c r="J551" s="25"/>
       <c r="K551" s="26">
-        <v>1111260</v>
+        <v>1111266</v>
       </c>
       <c r="L551" s="27">
         <v>24</v>
@@ -21847,7 +21626,7 @@
       <c r="I552" s="25"/>
       <c r="J552" s="25"/>
       <c r="K552" s="26">
-        <v>1111261</v>
+        <v>1111267</v>
       </c>
       <c r="L552" s="27">
         <v>28</v>
@@ -21883,7 +21662,7 @@
       <c r="I553" s="25"/>
       <c r="J553" s="25"/>
       <c r="K553" s="26">
-        <v>1111262</v>
+        <v>1111268</v>
       </c>
       <c r="L553" s="27">
         <v>32</v>
@@ -21918,8 +21697,8 @@
       <c r="H554" s="24"/>
       <c r="I554" s="25"/>
       <c r="J554" s="25"/>
-      <c r="K554" s="26">
-        <v>1111263</v>
+      <c r="K554" s="29">
+        <v>1111269</v>
       </c>
       <c r="L554" s="27">
         <v>36</v>
@@ -21954,8 +21733,8 @@
       <c r="H555" s="24"/>
       <c r="I555" s="25"/>
       <c r="J555" s="25"/>
-      <c r="K555" s="26">
-        <v>1111264</v>
+      <c r="K555" s="29">
+        <v>1111270</v>
       </c>
       <c r="L555" s="27">
         <v>40</v>
@@ -21990,9 +21769,6 @@
       <c r="H556" s="24"/>
       <c r="I556" s="25"/>
       <c r="J556" s="25"/>
-      <c r="K556" s="26">
-        <v>1111265</v>
-      </c>
       <c r="L556" s="27">
         <v>44</v>
       </c>
@@ -22026,9 +21802,6 @@
       <c r="H557" s="24"/>
       <c r="I557" s="25"/>
       <c r="J557" s="25"/>
-      <c r="K557" s="26">
-        <v>1111266</v>
-      </c>
       <c r="L557" s="27">
         <v>48</v>
       </c>
@@ -22062,9 +21835,6 @@
       <c r="H558" s="24"/>
       <c r="I558" s="25"/>
       <c r="J558" s="25"/>
-      <c r="K558" s="26">
-        <v>1111267</v>
-      </c>
       <c r="L558" s="27">
         <v>52</v>
       </c>
@@ -22098,9 +21868,6 @@
       <c r="H559" s="24"/>
       <c r="I559" s="25"/>
       <c r="J559" s="25"/>
-      <c r="K559" s="26">
-        <v>1111268</v>
-      </c>
       <c r="L559" s="27">
         <v>56</v>
       </c>
@@ -22134,9 +21901,6 @@
       <c r="H560" s="24"/>
       <c r="I560" s="25"/>
       <c r="J560" s="25"/>
-      <c r="K560" s="29">
-        <v>1111269</v>
-      </c>
       <c r="L560" s="27">
         <v>60</v>
       </c>
@@ -22170,9 +21934,6 @@
       <c r="H561" s="24"/>
       <c r="I561" s="25"/>
       <c r="J561" s="25"/>
-      <c r="K561" s="29">
-        <v>1111270</v>
-      </c>
       <c r="L561" s="27">
         <v>64</v>
       </c>
@@ -23777,7 +23538,7 @@
         <v>246</v>
       </c>
       <c r="K606" s="8">
-        <v>1112255</v>
+        <v>1112261</v>
       </c>
       <c r="L606" s="21">
         <v>4</v>
@@ -23817,7 +23578,7 @@
         <v>248</v>
       </c>
       <c r="K607" s="8">
-        <v>1112256</v>
+        <v>1112262</v>
       </c>
       <c r="L607" s="21">
         <v>8</v>
@@ -23851,7 +23612,7 @@
       </c>
       <c r="H608" s="9"/>
       <c r="K608" s="8">
-        <v>1112257</v>
+        <v>1112263</v>
       </c>
       <c r="L608" s="21">
         <v>12</v>
@@ -23885,7 +23646,7 @@
       </c>
       <c r="H609" s="9"/>
       <c r="K609" s="8">
-        <v>1112258</v>
+        <v>1112264</v>
       </c>
       <c r="L609" s="21">
         <v>16</v>
@@ -23919,7 +23680,7 @@
       </c>
       <c r="H610" s="9"/>
       <c r="K610" s="8">
-        <v>1112259</v>
+        <v>1112265</v>
       </c>
       <c r="L610" s="21">
         <v>20</v>
@@ -23953,7 +23714,7 @@
       </c>
       <c r="H611" s="9"/>
       <c r="K611" s="8">
-        <v>1112260</v>
+        <v>1112266</v>
       </c>
       <c r="L611" s="21">
         <v>24</v>
@@ -23987,7 +23748,7 @@
       </c>
       <c r="H612" s="9"/>
       <c r="K612" s="8">
-        <v>1112261</v>
+        <v>1112267</v>
       </c>
       <c r="L612" s="21">
         <v>28</v>
@@ -24021,7 +23782,7 @@
       </c>
       <c r="H613" s="9"/>
       <c r="K613" s="8">
-        <v>1112262</v>
+        <v>1112268</v>
       </c>
       <c r="L613" s="21">
         <v>32</v>
@@ -24055,7 +23816,7 @@
       </c>
       <c r="H614" s="9"/>
       <c r="K614" s="8">
-        <v>1112263</v>
+        <v>1112269</v>
       </c>
       <c r="L614" s="21">
         <v>36</v>
@@ -24091,7 +23852,7 @@
       <c r="I615" s="7"/>
       <c r="J615" s="7"/>
       <c r="K615" s="8">
-        <v>1112264</v>
+        <v>1112270</v>
       </c>
       <c r="L615" s="21">
         <v>40</v>
@@ -24127,7 +23888,7 @@
       <c r="I616" s="7"/>
       <c r="J616" s="7"/>
       <c r="K616" s="8">
-        <v>1112265</v>
+        <v>1112271</v>
       </c>
       <c r="L616" s="21">
         <v>44</v>
@@ -24162,9 +23923,6 @@
       <c r="H617" s="9"/>
       <c r="I617" s="7"/>
       <c r="J617" s="7"/>
-      <c r="K617" s="8">
-        <v>1112266</v>
-      </c>
       <c r="L617" s="21">
         <v>48</v>
       </c>
@@ -24198,9 +23956,6 @@
       <c r="H618" s="9"/>
       <c r="I618" s="7"/>
       <c r="J618" s="7"/>
-      <c r="K618" s="8">
-        <v>1112267</v>
-      </c>
       <c r="L618" s="21">
         <v>52</v>
       </c>
@@ -24234,9 +23989,6 @@
       <c r="H619" s="9"/>
       <c r="I619" s="7"/>
       <c r="J619" s="7"/>
-      <c r="K619" s="8">
-        <v>1112268</v>
-      </c>
       <c r="L619" s="21">
         <v>56</v>
       </c>
@@ -24270,9 +24022,6 @@
       <c r="H620" s="9"/>
       <c r="I620" s="7"/>
       <c r="J620" s="7"/>
-      <c r="K620" s="8">
-        <v>1112269</v>
-      </c>
       <c r="L620" s="21">
         <v>60</v>
       </c>
@@ -24306,9 +24055,6 @@
       <c r="H621" s="9"/>
       <c r="I621" s="7"/>
       <c r="J621" s="7"/>
-      <c r="K621" s="8">
-        <v>1112270</v>
-      </c>
       <c r="L621" s="21">
         <v>64</v>
       </c>
@@ -24342,9 +24088,6 @@
       <c r="H622" s="9"/>
       <c r="I622" s="7"/>
       <c r="J622" s="7"/>
-      <c r="K622" s="8">
-        <v>1112271</v>
-      </c>
       <c r="L622" s="21">
         <v>68</v>
       </c>
@@ -25916,8 +25659,8 @@
       <c r="H666" s="24"/>
       <c r="I666" s="25"/>
       <c r="J666" s="25"/>
-      <c r="K666" s="25">
-        <v>1201254</v>
+      <c r="K666" s="26">
+        <v>1201256</v>
       </c>
       <c r="L666" s="27">
         <v>2</v>
@@ -25952,8 +25695,8 @@
       <c r="H667" s="24"/>
       <c r="I667" s="25"/>
       <c r="J667" s="25"/>
-      <c r="K667" s="26">
-        <v>1201255</v>
+      <c r="K667" s="25">
+        <v>1201257</v>
       </c>
       <c r="L667" s="27">
         <v>4</v>
@@ -25989,7 +25732,7 @@
       <c r="I668" s="25"/>
       <c r="J668" s="25"/>
       <c r="K668" s="26">
-        <v>1201256</v>
+        <v>1201258</v>
       </c>
       <c r="L668" s="27">
         <v>6</v>
@@ -26024,8 +25767,8 @@
       <c r="H669" s="24"/>
       <c r="I669" s="25"/>
       <c r="J669" s="25"/>
-      <c r="K669" s="25">
-        <v>1201257</v>
+      <c r="K669" s="26">
+        <v>1201259</v>
       </c>
       <c r="L669" s="27">
         <v>8</v>
@@ -26061,7 +25804,7 @@
       <c r="I670" s="25"/>
       <c r="J670" s="25"/>
       <c r="K670" s="26">
-        <v>1201258</v>
+        <v>1201260</v>
       </c>
       <c r="L670" s="27">
         <v>10</v>
@@ -26097,7 +25840,7 @@
       <c r="I671" s="25"/>
       <c r="J671" s="25"/>
       <c r="K671" s="26">
-        <v>1201259</v>
+        <v>1201261</v>
       </c>
       <c r="L671" s="27">
         <v>12</v>
@@ -26133,7 +25876,7 @@
       <c r="I672" s="25"/>
       <c r="J672" s="25"/>
       <c r="K672" s="26">
-        <v>1201260</v>
+        <v>1201262</v>
       </c>
       <c r="L672" s="27">
         <v>14</v>
@@ -26169,7 +25912,7 @@
       <c r="I673" s="25"/>
       <c r="J673" s="25"/>
       <c r="K673" s="26">
-        <v>1201261</v>
+        <v>1201263</v>
       </c>
       <c r="L673" s="27">
         <v>16</v>
@@ -26205,7 +25948,7 @@
       <c r="I674" s="25"/>
       <c r="J674" s="25"/>
       <c r="K674" s="26">
-        <v>1201262</v>
+        <v>1201264</v>
       </c>
       <c r="L674" s="27">
         <v>18</v>
@@ -26241,7 +25984,7 @@
       <c r="I675" s="25"/>
       <c r="J675" s="25"/>
       <c r="K675" s="26">
-        <v>1201263</v>
+        <v>1201265</v>
       </c>
       <c r="L675" s="27">
         <v>20</v>
@@ -26277,7 +26020,7 @@
       <c r="I676" s="25"/>
       <c r="J676" s="25"/>
       <c r="K676" s="26">
-        <v>1201264</v>
+        <v>1201266</v>
       </c>
       <c r="L676" s="27">
         <v>22</v>
@@ -26312,8 +26055,8 @@
       <c r="H677" s="24"/>
       <c r="I677" s="25"/>
       <c r="J677" s="25"/>
-      <c r="K677" s="26">
-        <v>1201265</v>
+      <c r="K677" s="31">
+        <v>1201267</v>
       </c>
       <c r="L677" s="27">
         <v>24</v>
@@ -26349,7 +26092,7 @@
       <c r="I678" s="25"/>
       <c r="J678" s="25"/>
       <c r="K678" s="26">
-        <v>1201266</v>
+        <v>1201268</v>
       </c>
       <c r="L678" s="27">
         <v>26</v>
@@ -26384,8 +26127,8 @@
       <c r="H679" s="24"/>
       <c r="I679" s="25"/>
       <c r="J679" s="25"/>
-      <c r="K679" s="31">
-        <v>1201267</v>
+      <c r="K679" s="26">
+        <v>1201269</v>
       </c>
       <c r="L679" s="27">
         <v>28</v>
@@ -26421,7 +26164,7 @@
       <c r="I680" s="25"/>
       <c r="J680" s="25"/>
       <c r="K680" s="26">
-        <v>1201268</v>
+        <v>1201270</v>
       </c>
       <c r="L680" s="27">
         <v>30</v>
@@ -26457,7 +26200,7 @@
       <c r="I681" s="25"/>
       <c r="J681" s="25"/>
       <c r="K681" s="26">
-        <v>1201269</v>
+        <v>1201271</v>
       </c>
       <c r="L681" s="27">
         <v>32</v>
@@ -26493,7 +26236,7 @@
       <c r="I682" s="25"/>
       <c r="J682" s="25"/>
       <c r="K682" s="26">
-        <v>1201270</v>
+        <v>1201272</v>
       </c>
       <c r="L682" s="27">
         <v>34</v>
@@ -26528,8 +26271,8 @@
       <c r="H683" s="24"/>
       <c r="I683" s="25"/>
       <c r="J683" s="25"/>
-      <c r="K683" s="26">
-        <v>1201271</v>
+      <c r="K683" s="25">
+        <v>1201273</v>
       </c>
       <c r="L683" s="27">
         <v>36</v>
@@ -26564,9 +26307,6 @@
       <c r="H684" s="24"/>
       <c r="I684" s="25"/>
       <c r="J684" s="25"/>
-      <c r="K684" s="26">
-        <v>1201272</v>
-      </c>
       <c r="L684" s="27">
         <v>38</v>
       </c>
@@ -26600,9 +26340,6 @@
       <c r="H685" s="24"/>
       <c r="I685" s="25"/>
       <c r="J685" s="25"/>
-      <c r="K685" s="25">
-        <v>1201273</v>
-      </c>
       <c r="L685" s="27">
         <v>40</v>
       </c>
@@ -28068,8 +27805,8 @@
         <v>400</v>
       </c>
       <c r="H726" s="9"/>
-      <c r="K726" s="32">
-        <v>1202253</v>
+      <c r="K726" s="8">
+        <v>1202271</v>
       </c>
       <c r="L726" s="21">
         <v>4</v>
@@ -28103,7 +27840,7 @@
       </c>
       <c r="H727" s="9"/>
       <c r="K727" s="8">
-        <v>1202254</v>
+        <v>1202272</v>
       </c>
       <c r="L727" s="21">
         <v>8</v>
@@ -28137,7 +27874,7 @@
       </c>
       <c r="H728" s="9"/>
       <c r="K728" s="8">
-        <v>1202255</v>
+        <v>1202273</v>
       </c>
       <c r="L728" s="21">
         <v>12</v>
@@ -28171,7 +27908,7 @@
       </c>
       <c r="H729" s="9"/>
       <c r="K729" s="8">
-        <v>1202256</v>
+        <v>1202274</v>
       </c>
       <c r="L729" s="21">
         <v>16</v>
@@ -28205,7 +27942,7 @@
       </c>
       <c r="H730" s="9"/>
       <c r="K730" s="8">
-        <v>1202257</v>
+        <v>1202275</v>
       </c>
       <c r="L730" s="21">
         <v>20</v>
@@ -28239,7 +27976,7 @@
       </c>
       <c r="H731" s="9"/>
       <c r="K731" s="8">
-        <v>1202258</v>
+        <v>1202276</v>
       </c>
       <c r="L731" s="21">
         <v>24</v>
@@ -28273,7 +28010,7 @@
       </c>
       <c r="H732" s="9"/>
       <c r="K732" s="8">
-        <v>1202259</v>
+        <v>1202277</v>
       </c>
       <c r="L732" s="21">
         <v>28</v>
@@ -28307,7 +28044,7 @@
       </c>
       <c r="H733" s="9"/>
       <c r="K733" s="8">
-        <v>1202260</v>
+        <v>1202278</v>
       </c>
       <c r="L733" s="21">
         <v>32</v>
@@ -28341,7 +28078,7 @@
       </c>
       <c r="H734" s="9"/>
       <c r="K734" s="8">
-        <v>1202264</v>
+        <v>1202279</v>
       </c>
       <c r="L734" s="21">
         <v>36</v>
@@ -28375,7 +28112,7 @@
       </c>
       <c r="H735" s="9"/>
       <c r="K735" s="8">
-        <v>1202265</v>
+        <v>1202280</v>
       </c>
       <c r="L735" s="21">
         <v>40</v>
@@ -28409,7 +28146,7 @@
       </c>
       <c r="H736" s="9"/>
       <c r="K736" s="8">
-        <v>1202266</v>
+        <v>1202282</v>
       </c>
       <c r="L736" s="21">
         <v>44</v>
@@ -28443,7 +28180,7 @@
       </c>
       <c r="H737" s="9"/>
       <c r="K737" s="8">
-        <v>1202267</v>
+        <v>1202283</v>
       </c>
       <c r="L737" s="21">
         <v>48</v>
@@ -28477,7 +28214,7 @@
       </c>
       <c r="H738" s="9"/>
       <c r="K738" s="8">
-        <v>1202268</v>
+        <v>1202284</v>
       </c>
       <c r="L738" s="21">
         <v>52</v>
@@ -28511,7 +28248,7 @@
       </c>
       <c r="H739" s="9"/>
       <c r="K739" s="8">
-        <v>1202269</v>
+        <v>1202285</v>
       </c>
       <c r="L739" s="21">
         <v>56</v>
@@ -28544,8 +28281,8 @@
         <v>3200</v>
       </c>
       <c r="H740" s="9"/>
-      <c r="K740" s="8">
-        <v>1202270</v>
+      <c r="K740" s="32">
+        <v>1202286</v>
       </c>
       <c r="L740" s="21">
         <v>60</v>
@@ -28579,7 +28316,7 @@
       </c>
       <c r="H741" s="9"/>
       <c r="K741" s="8">
-        <v>1202271</v>
+        <v>1202287</v>
       </c>
       <c r="L741" s="21">
         <v>64</v>
@@ -28613,7 +28350,7 @@
       </c>
       <c r="H742" s="9"/>
       <c r="K742" s="8">
-        <v>1202272</v>
+        <v>1202288</v>
       </c>
       <c r="L742" s="21">
         <v>68</v>
@@ -28647,7 +28384,7 @@
       </c>
       <c r="H743" s="9"/>
       <c r="K743" s="8">
-        <v>1202273</v>
+        <v>1202289</v>
       </c>
       <c r="L743" s="21">
         <v>72</v>
@@ -28681,7 +28418,7 @@
       </c>
       <c r="H744" s="9"/>
       <c r="K744" s="8">
-        <v>1202274</v>
+        <v>1202290</v>
       </c>
       <c r="L744" s="21">
         <v>76</v>
@@ -28715,7 +28452,7 @@
       </c>
       <c r="H745" s="9"/>
       <c r="K745" s="8">
-        <v>1202275</v>
+        <v>1202291</v>
       </c>
       <c r="L745" s="21">
         <v>80</v>
@@ -28749,7 +28486,7 @@
       </c>
       <c r="H746" s="9"/>
       <c r="K746" s="8">
-        <v>1202276</v>
+        <v>1202292</v>
       </c>
       <c r="L746" s="21">
         <v>84</v>
@@ -28783,7 +28520,7 @@
       </c>
       <c r="H747" s="9"/>
       <c r="K747" s="8">
-        <v>1202277</v>
+        <v>1202293</v>
       </c>
       <c r="L747" s="21">
         <v>88</v>
@@ -28817,7 +28554,7 @@
       </c>
       <c r="H748" s="9"/>
       <c r="K748" s="8">
-        <v>1202278</v>
+        <v>1202294</v>
       </c>
       <c r="L748" s="21">
         <v>92</v>
@@ -28851,7 +28588,7 @@
       </c>
       <c r="H749" s="9"/>
       <c r="K749" s="8">
-        <v>1202279</v>
+        <v>1202295</v>
       </c>
       <c r="L749" s="21">
         <v>96</v>
@@ -28885,7 +28622,7 @@
       </c>
       <c r="H750" s="9"/>
       <c r="K750" s="8">
-        <v>1202280</v>
+        <v>1202296</v>
       </c>
       <c r="L750" s="21">
         <v>100</v>
@@ -28919,7 +28656,7 @@
       </c>
       <c r="H751" s="9"/>
       <c r="K751" s="8">
-        <v>1202282</v>
+        <v>1202297</v>
       </c>
       <c r="L751" s="21">
         <v>104</v>
@@ -28953,7 +28690,7 @@
       </c>
       <c r="H752" s="9"/>
       <c r="K752" s="8">
-        <v>1202283</v>
+        <v>1202298</v>
       </c>
       <c r="L752" s="21">
         <v>108</v>
@@ -28986,9 +28723,6 @@
         <v>5800</v>
       </c>
       <c r="H753" s="9"/>
-      <c r="K753" s="8">
-        <v>1202284</v>
-      </c>
       <c r="L753" s="21">
         <v>112</v>
       </c>
@@ -29020,9 +28754,6 @@
         <v>6000</v>
       </c>
       <c r="H754" s="9"/>
-      <c r="K754" s="8">
-        <v>1202285</v>
-      </c>
       <c r="L754" s="21">
         <v>116</v>
       </c>
@@ -29054,9 +28785,6 @@
         <v>6200</v>
       </c>
       <c r="H755" s="9"/>
-      <c r="K755" s="32">
-        <v>1202286</v>
-      </c>
       <c r="L755" s="21">
         <v>120</v>
       </c>
@@ -29088,9 +28816,6 @@
         <v>6400</v>
       </c>
       <c r="H756" s="9"/>
-      <c r="K756" s="8">
-        <v>1202287</v>
-      </c>
       <c r="L756" s="21">
         <v>124</v>
       </c>
@@ -29122,9 +28847,6 @@
         <v>6600</v>
       </c>
       <c r="H757" s="9"/>
-      <c r="K757" s="8">
-        <v>1202288</v>
-      </c>
       <c r="L757" s="21">
         <v>128</v>
       </c>
@@ -29156,9 +28878,6 @@
         <v>6800</v>
       </c>
       <c r="H758" s="9"/>
-      <c r="K758" s="8">
-        <v>1202289</v>
-      </c>
       <c r="L758" s="21">
         <v>132</v>
       </c>
@@ -29190,9 +28909,6 @@
         <v>7000</v>
       </c>
       <c r="H759" s="9"/>
-      <c r="K759" s="8">
-        <v>1202290</v>
-      </c>
       <c r="L759" s="21">
         <v>136</v>
       </c>
@@ -29224,9 +28940,6 @@
         <v>7200</v>
       </c>
       <c r="H760" s="9"/>
-      <c r="K760" s="8">
-        <v>1202291</v>
-      </c>
       <c r="L760" s="21">
         <v>140</v>
       </c>
@@ -29258,9 +28971,6 @@
         <v>7400</v>
       </c>
       <c r="H761" s="9"/>
-      <c r="K761" s="8">
-        <v>1202292</v>
-      </c>
       <c r="L761" s="21">
         <v>144</v>
       </c>
@@ -29292,9 +29002,6 @@
         <v>7600</v>
       </c>
       <c r="H762" s="9"/>
-      <c r="K762" s="8">
-        <v>1202293</v>
-      </c>
       <c r="L762" s="21">
         <v>148</v>
       </c>
@@ -29326,9 +29033,6 @@
         <v>7800</v>
       </c>
       <c r="H763" s="9"/>
-      <c r="K763" s="8">
-        <v>1202294</v>
-      </c>
       <c r="L763" s="21">
         <v>152</v>
       </c>
@@ -29360,9 +29064,6 @@
         <v>8000</v>
       </c>
       <c r="H764" s="9"/>
-      <c r="K764" s="8">
-        <v>1202295</v>
-      </c>
       <c r="L764" s="21">
         <v>156</v>
       </c>
@@ -29394,9 +29095,6 @@
         <v>8200</v>
       </c>
       <c r="H765" s="9"/>
-      <c r="K765" s="8">
-        <v>1202296</v>
-      </c>
       <c r="L765" s="21">
         <v>160</v>
       </c>
@@ -29428,9 +29126,6 @@
         <v>8400</v>
       </c>
       <c r="H766" s="9"/>
-      <c r="K766" s="8">
-        <v>1202297</v>
-      </c>
       <c r="L766" s="21">
         <v>164</v>
       </c>
@@ -29462,9 +29157,6 @@
         <v>8600</v>
       </c>
       <c r="H767" s="9"/>
-      <c r="K767" s="8">
-        <v>1202298</v>
-      </c>
       <c r="L767" s="21">
         <v>168</v>
       </c>
@@ -32059,7 +31751,7 @@
       <c r="I847" s="37">
         <v>101200</v>
       </c>
-      <c r="K847" s="38" t="s">
+      <c r="K847" s="41" t="s">
         <v>262</v>
       </c>
       <c r="L847" s="39">
@@ -32173,9 +31865,6 @@
         <v>103100</v>
       </c>
       <c r="J850" s="37"/>
-      <c r="K850" s="41" t="s">
-        <v>265</v>
-      </c>
       <c r="L850" s="39">
         <v>10</v>
       </c>
@@ -32336,14 +32025,14 @@
         <v>1101</v>
       </c>
       <c r="C855" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D855" s="42">
         <v>1</v>
       </c>
       <c r="E855" s="5"/>
       <c r="F855" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G855" s="43">
         <v>100</v>
@@ -32356,7 +32045,7 @@
         <v>1</v>
       </c>
       <c r="M855" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="856" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32368,14 +32057,14 @@
         <v>1101</v>
       </c>
       <c r="C856" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D856" s="42">
         <v>2</v>
       </c>
       <c r="E856" s="5"/>
       <c r="F856" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G856" s="43">
         <v>200</v>
@@ -32388,7 +32077,7 @@
         <v>2</v>
       </c>
       <c r="M856" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="857" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32400,14 +32089,14 @@
         <v>1101</v>
       </c>
       <c r="C857" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D857" s="42">
         <v>3</v>
       </c>
       <c r="E857" s="5"/>
       <c r="F857" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G857" s="43">
         <v>300</v>
@@ -32420,7 +32109,7 @@
         <v>4</v>
       </c>
       <c r="M857" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="858" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32432,14 +32121,14 @@
         <v>1101</v>
       </c>
       <c r="C858" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D858" s="42">
         <v>4</v>
       </c>
       <c r="E858" s="5"/>
       <c r="F858" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G858" s="43">
         <v>400</v>
@@ -32452,7 +32141,7 @@
         <v>6</v>
       </c>
       <c r="M858" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="859" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32464,14 +32153,14 @@
         <v>1101</v>
       </c>
       <c r="C859" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D859" s="42">
         <v>5</v>
       </c>
       <c r="E859" s="5"/>
       <c r="F859" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G859" s="43">
         <v>500</v>
@@ -32484,7 +32173,7 @@
         <v>8</v>
       </c>
       <c r="M859" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="860" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32496,14 +32185,14 @@
         <v>1101</v>
       </c>
       <c r="C860" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D860" s="42">
         <v>6</v>
       </c>
       <c r="E860" s="5"/>
       <c r="F860" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G860" s="43">
         <v>600</v>
@@ -32516,7 +32205,7 @@
         <v>10</v>
       </c>
       <c r="M860" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="861" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32528,14 +32217,14 @@
         <v>1101</v>
       </c>
       <c r="C861" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D861" s="42">
         <v>7</v>
       </c>
       <c r="E861" s="5"/>
       <c r="F861" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G861" s="43">
         <v>700</v>
@@ -32548,7 +32237,7 @@
         <v>12</v>
       </c>
       <c r="M861" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="862" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32560,14 +32249,14 @@
         <v>1101</v>
       </c>
       <c r="C862" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D862" s="42">
         <v>8</v>
       </c>
       <c r="E862" s="5"/>
       <c r="F862" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G862" s="43">
         <v>800</v>
@@ -32580,7 +32269,7 @@
         <v>14</v>
       </c>
       <c r="M862" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="863" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32592,14 +32281,14 @@
         <v>1101</v>
       </c>
       <c r="C863" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D863" s="42">
         <v>9</v>
       </c>
       <c r="E863" s="5"/>
       <c r="F863" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G863" s="43">
         <v>900</v>
@@ -32612,7 +32301,7 @@
         <v>16</v>
       </c>
       <c r="M863" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="864" s="5" customFormat="1" customHeight="1" spans="1:13">
@@ -32624,14 +32313,14 @@
         <v>1101</v>
       </c>
       <c r="C864" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D864" s="42">
         <v>10</v>
       </c>
       <c r="E864" s="5"/>
       <c r="F864" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G864" s="43">
         <v>1000</v>
@@ -32644,7 +32333,7 @@
         <v>18</v>
       </c>
       <c r="M864" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="865" s="2" customFormat="1" customHeight="1" spans="1:13">
@@ -32656,7 +32345,7 @@
         <v>1303</v>
       </c>
       <c r="C865" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D865" s="23">
         <v>1</v>
@@ -32672,7 +32361,7 @@
       <c r="I865" s="25"/>
       <c r="J865" s="25"/>
       <c r="K865" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L865" s="27">
         <v>1</v>
@@ -32690,7 +32379,7 @@
         <v>1303</v>
       </c>
       <c r="C866" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D866" s="23">
         <v>2</v>
@@ -32706,7 +32395,7 @@
       <c r="I866" s="25"/>
       <c r="J866" s="25"/>
       <c r="K866" s="26">
-        <v>1303205</v>
+        <v>1303207</v>
       </c>
       <c r="L866" s="27">
         <v>2</v>
@@ -32724,7 +32413,7 @@
         <v>1303</v>
       </c>
       <c r="C867" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D867" s="23">
         <v>3</v>
@@ -32740,7 +32429,7 @@
       <c r="I867" s="25"/>
       <c r="J867" s="25"/>
       <c r="K867" s="26">
-        <v>1303206</v>
+        <v>1303208</v>
       </c>
       <c r="L867" s="27">
         <v>4</v>
@@ -32758,7 +32447,7 @@
         <v>1303</v>
       </c>
       <c r="C868" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D868" s="23">
         <v>4</v>
@@ -32774,7 +32463,7 @@
       <c r="I868" s="25"/>
       <c r="J868" s="25"/>
       <c r="K868" s="26">
-        <v>1303207</v>
+        <v>1303209</v>
       </c>
       <c r="L868" s="27">
         <v>6</v>
@@ -32792,7 +32481,7 @@
         <v>1303</v>
       </c>
       <c r="C869" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D869" s="23">
         <v>5</v>
@@ -32808,7 +32497,7 @@
       <c r="I869" s="25"/>
       <c r="J869" s="25"/>
       <c r="K869" s="26">
-        <v>1303208</v>
+        <v>1303210</v>
       </c>
       <c r="L869" s="27">
         <v>8</v>
@@ -32826,7 +32515,7 @@
         <v>1303</v>
       </c>
       <c r="C870" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D870" s="23">
         <v>6</v>
@@ -32842,7 +32531,7 @@
       <c r="I870" s="25"/>
       <c r="J870" s="25"/>
       <c r="K870" s="26">
-        <v>1303209</v>
+        <v>1303211</v>
       </c>
       <c r="L870" s="27">
         <v>10</v>
@@ -32860,7 +32549,7 @@
         <v>1303</v>
       </c>
       <c r="C871" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D871" s="23">
         <v>7</v>
@@ -32875,9 +32564,6 @@
       <c r="H871" s="2"/>
       <c r="I871" s="25"/>
       <c r="J871" s="25"/>
-      <c r="K871" s="26">
-        <v>1303210</v>
-      </c>
       <c r="L871" s="27">
         <v>12</v>
       </c>
@@ -32894,7 +32580,7 @@
         <v>1303</v>
       </c>
       <c r="C872" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D872" s="23">
         <v>8</v>
@@ -32909,9 +32595,6 @@
       <c r="H872" s="2"/>
       <c r="I872" s="25"/>
       <c r="J872" s="25"/>
-      <c r="K872" s="26">
-        <v>1303211</v>
-      </c>
       <c r="L872" s="27">
         <v>14</v>
       </c>
@@ -32928,7 +32611,7 @@
         <v>1303</v>
       </c>
       <c r="C873" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D873" s="23">
         <v>9</v>
@@ -32960,7 +32643,7 @@
         <v>1303</v>
       </c>
       <c r="C874" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D874" s="23">
         <v>10</v>
@@ -32992,7 +32675,7 @@
         <v>1303</v>
       </c>
       <c r="C875" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D875" s="23">
         <v>11</v>
@@ -33024,7 +32707,7 @@
         <v>1303</v>
       </c>
       <c r="C876" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D876" s="23">
         <v>12</v>
@@ -33056,7 +32739,7 @@
         <v>1303</v>
       </c>
       <c r="C877" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D877" s="23">
         <v>13</v>
@@ -33088,7 +32771,7 @@
         <v>1303</v>
       </c>
       <c r="C878" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D878" s="23">
         <v>14</v>
@@ -33120,7 +32803,7 @@
         <v>1303</v>
       </c>
       <c r="C879" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D879" s="23">
         <v>15</v>
@@ -33154,7 +32837,7 @@
         <v>1303</v>
       </c>
       <c r="C880" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D880" s="23">
         <v>16</v>
@@ -33188,7 +32871,7 @@
         <v>1303</v>
       </c>
       <c r="C881" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D881" s="23">
         <v>17</v>
@@ -33222,7 +32905,7 @@
         <v>1303</v>
       </c>
       <c r="C882" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D882" s="23">
         <v>18</v>
@@ -33256,7 +32939,7 @@
         <v>1303</v>
       </c>
       <c r="C883" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D883" s="23">
         <v>19</v>
@@ -33290,7 +32973,7 @@
         <v>1303</v>
       </c>
       <c r="C884" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D884" s="23">
         <v>20</v>
@@ -33324,7 +33007,7 @@
         <v>1303</v>
       </c>
       <c r="C885" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D885" s="23">
         <v>21</v>
@@ -33358,7 +33041,7 @@
         <v>1303</v>
       </c>
       <c r="C886" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D886" s="23">
         <v>22</v>
@@ -33392,7 +33075,7 @@
         <v>1303</v>
       </c>
       <c r="C887" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D887" s="23">
         <v>23</v>
@@ -33426,7 +33109,7 @@
         <v>1303</v>
       </c>
       <c r="C888" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D888" s="23">
         <v>24</v>
@@ -33460,7 +33143,7 @@
         <v>1303</v>
       </c>
       <c r="C889" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D889" s="23">
         <v>25</v>
@@ -33494,7 +33177,7 @@
         <v>1303</v>
       </c>
       <c r="C890" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D890" s="23">
         <v>26</v>
@@ -33528,7 +33211,7 @@
         <v>1303</v>
       </c>
       <c r="C891" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D891" s="23">
         <v>27</v>
@@ -33562,7 +33245,7 @@
         <v>1303</v>
       </c>
       <c r="C892" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D892" s="23">
         <v>28</v>
@@ -33596,7 +33279,7 @@
         <v>1303</v>
       </c>
       <c r="C893" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D893" s="23">
         <v>29</v>
@@ -33630,7 +33313,7 @@
         <v>1303</v>
       </c>
       <c r="C894" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D894" s="23">
         <v>30</v>
@@ -33664,7 +33347,7 @@
         <v>1303</v>
       </c>
       <c r="C895" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D895" s="23">
         <v>31</v>
@@ -33698,7 +33381,7 @@
         <v>1303</v>
       </c>
       <c r="C896" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D896" s="23">
         <v>32</v>
@@ -33732,7 +33415,7 @@
         <v>1303</v>
       </c>
       <c r="C897" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D897" s="23">
         <v>33</v>
@@ -33766,7 +33449,7 @@
         <v>1303</v>
       </c>
       <c r="C898" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D898" s="23">
         <v>34</v>
@@ -33800,7 +33483,7 @@
         <v>1303</v>
       </c>
       <c r="C899" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D899" s="23">
         <v>35</v>
@@ -33834,7 +33517,7 @@
         <v>1303</v>
       </c>
       <c r="C900" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D900" s="23">
         <v>36</v>
@@ -33868,7 +33551,7 @@
         <v>1303</v>
       </c>
       <c r="C901" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D901" s="23">
         <v>37</v>
@@ -33902,7 +33585,7 @@
         <v>1303</v>
       </c>
       <c r="C902" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D902" s="23">
         <v>38</v>
@@ -33936,7 +33619,7 @@
         <v>1303</v>
       </c>
       <c r="C903" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D903" s="23">
         <v>39</v>
@@ -33970,7 +33653,7 @@
         <v>1303</v>
       </c>
       <c r="C904" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D904" s="23">
         <v>40</v>
@@ -34004,7 +33687,7 @@
         <v>1303</v>
       </c>
       <c r="C905" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D905" s="23">
         <v>41</v>
@@ -34038,7 +33721,7 @@
         <v>1303</v>
       </c>
       <c r="C906" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D906" s="23">
         <v>42</v>
@@ -34072,7 +33755,7 @@
         <v>1303</v>
       </c>
       <c r="C907" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D907" s="23">
         <v>43</v>
@@ -34106,7 +33789,7 @@
         <v>1303</v>
       </c>
       <c r="C908" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D908" s="23">
         <v>44</v>
@@ -34140,7 +33823,7 @@
         <v>1303</v>
       </c>
       <c r="C909" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D909" s="23">
         <v>45</v>
@@ -34174,7 +33857,7 @@
         <v>1303</v>
       </c>
       <c r="C910" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D910" s="23">
         <v>46</v>
@@ -34208,7 +33891,7 @@
         <v>1303</v>
       </c>
       <c r="C911" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D911" s="23">
         <v>47</v>
@@ -34242,7 +33925,7 @@
         <v>1303</v>
       </c>
       <c r="C912" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D912" s="23">
         <v>48</v>
@@ -34276,7 +33959,7 @@
         <v>1303</v>
       </c>
       <c r="C913" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D913" s="23">
         <v>49</v>
@@ -34310,7 +33993,7 @@
         <v>1303</v>
       </c>
       <c r="C914" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D914" s="23">
         <v>50</v>
@@ -34344,7 +34027,7 @@
         <v>1303</v>
       </c>
       <c r="C915" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D915" s="23">
         <v>51</v>
@@ -34378,7 +34061,7 @@
         <v>1303</v>
       </c>
       <c r="C916" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D916" s="23">
         <v>52</v>
@@ -34412,7 +34095,7 @@
         <v>1303</v>
       </c>
       <c r="C917" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D917" s="23">
         <v>53</v>
@@ -34446,7 +34129,7 @@
         <v>1303</v>
       </c>
       <c r="C918" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D918" s="23">
         <v>54</v>
@@ -34480,7 +34163,7 @@
         <v>1303</v>
       </c>
       <c r="C919" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D919" s="23">
         <v>55</v>
@@ -34514,7 +34197,7 @@
         <v>1303</v>
       </c>
       <c r="C920" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D920" s="23">
         <v>56</v>
@@ -34548,7 +34231,7 @@
         <v>1303</v>
       </c>
       <c r="C921" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D921" s="23">
         <v>57</v>
@@ -34582,7 +34265,7 @@
         <v>1303</v>
       </c>
       <c r="C922" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D922" s="23">
         <v>58</v>
@@ -34616,7 +34299,7 @@
         <v>1303</v>
       </c>
       <c r="C923" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D923" s="23">
         <v>59</v>
@@ -34650,7 +34333,7 @@
         <v>1303</v>
       </c>
       <c r="C924" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D924" s="23">
         <v>60</v>
@@ -34682,7 +34365,7 @@
         <v>1304</v>
       </c>
       <c r="C925" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D925" s="19">
         <v>1</v>
@@ -34694,7 +34377,7 @@
         <v>100</v>
       </c>
       <c r="K925" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L925" s="21">
         <v>1</v>
@@ -34712,7 +34395,7 @@
         <v>1304</v>
       </c>
       <c r="C926" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D926" s="19">
         <v>2</v>
@@ -34742,7 +34425,7 @@
         <v>1304</v>
       </c>
       <c r="C927" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D927" s="19">
         <v>3</v>
@@ -34772,7 +34455,7 @@
         <v>1304</v>
       </c>
       <c r="C928" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D928" s="19">
         <v>4</v>
@@ -34802,7 +34485,7 @@
         <v>1304</v>
       </c>
       <c r="C929" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D929" s="19">
         <v>5</v>
@@ -34832,7 +34515,7 @@
         <v>1304</v>
       </c>
       <c r="C930" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D930" s="19">
         <v>6</v>
@@ -34862,7 +34545,7 @@
         <v>1304</v>
       </c>
       <c r="C931" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D931" s="19">
         <v>7</v>
@@ -34889,7 +34572,7 @@
         <v>1304</v>
       </c>
       <c r="C932" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D932" s="19">
         <v>8</v>
@@ -34916,7 +34599,7 @@
         <v>1304</v>
       </c>
       <c r="C933" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D933" s="19">
         <v>9</v>
@@ -34943,7 +34626,7 @@
         <v>1304</v>
       </c>
       <c r="C934" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D934" s="19">
         <v>10</v>
@@ -34970,7 +34653,7 @@
         <v>1304</v>
       </c>
       <c r="C935" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D935" s="19">
         <v>11</v>
@@ -35000,7 +34683,7 @@
         <v>1304</v>
       </c>
       <c r="C936" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D936" s="19">
         <v>12</v>
@@ -35030,7 +34713,7 @@
         <v>1304</v>
       </c>
       <c r="C937" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D937" s="19">
         <v>13</v>
@@ -35060,7 +34743,7 @@
         <v>1304</v>
       </c>
       <c r="C938" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D938" s="19">
         <v>14</v>
@@ -35090,7 +34773,7 @@
         <v>1304</v>
       </c>
       <c r="C939" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D939" s="19">
         <v>15</v>
@@ -35120,7 +34803,7 @@
         <v>1304</v>
       </c>
       <c r="C940" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D940" s="19">
         <v>16</v>
@@ -35150,7 +34833,7 @@
         <v>1304</v>
       </c>
       <c r="C941" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D941" s="19">
         <v>17</v>
@@ -35180,7 +34863,7 @@
         <v>1304</v>
       </c>
       <c r="C942" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D942" s="19">
         <v>18</v>
@@ -35210,7 +34893,7 @@
         <v>1304</v>
       </c>
       <c r="C943" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D943" s="19">
         <v>19</v>
@@ -35240,7 +34923,7 @@
         <v>1304</v>
       </c>
       <c r="C944" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D944" s="19">
         <v>20</v>
@@ -35270,7 +34953,7 @@
         <v>1304</v>
       </c>
       <c r="C945" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D945" s="19">
         <v>21</v>
@@ -35300,7 +34983,7 @@
         <v>1304</v>
       </c>
       <c r="C946" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D946" s="19">
         <v>22</v>
@@ -35330,7 +35013,7 @@
         <v>1304</v>
       </c>
       <c r="C947" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D947" s="19">
         <v>23</v>
@@ -35360,7 +35043,7 @@
         <v>1304</v>
       </c>
       <c r="C948" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D948" s="19">
         <v>24</v>
@@ -35390,7 +35073,7 @@
         <v>1304</v>
       </c>
       <c r="C949" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D949" s="19">
         <v>25</v>
@@ -35420,7 +35103,7 @@
         <v>1304</v>
       </c>
       <c r="C950" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D950" s="19">
         <v>26</v>
@@ -35450,7 +35133,7 @@
         <v>1304</v>
       </c>
       <c r="C951" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D951" s="19">
         <v>27</v>
@@ -35480,7 +35163,7 @@
         <v>1304</v>
       </c>
       <c r="C952" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D952" s="19">
         <v>28</v>
@@ -35510,7 +35193,7 @@
         <v>1304</v>
       </c>
       <c r="C953" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D953" s="19">
         <v>29</v>
@@ -35540,7 +35223,7 @@
         <v>1304</v>
       </c>
       <c r="C954" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D954" s="19">
         <v>30</v>
@@ -35570,7 +35253,7 @@
         <v>1304</v>
       </c>
       <c r="C955" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D955" s="19">
         <v>31</v>
@@ -35600,7 +35283,7 @@
         <v>1304</v>
       </c>
       <c r="C956" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D956" s="19">
         <v>32</v>
@@ -35630,7 +35313,7 @@
         <v>1304</v>
       </c>
       <c r="C957" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D957" s="19">
         <v>33</v>
@@ -35660,7 +35343,7 @@
         <v>1304</v>
       </c>
       <c r="C958" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D958" s="19">
         <v>34</v>
@@ -35690,7 +35373,7 @@
         <v>1304</v>
       </c>
       <c r="C959" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D959" s="19">
         <v>35</v>
@@ -35720,7 +35403,7 @@
         <v>1304</v>
       </c>
       <c r="C960" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D960" s="19">
         <v>36</v>
@@ -35750,7 +35433,7 @@
         <v>1304</v>
       </c>
       <c r="C961" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D961" s="19">
         <v>37</v>
@@ -35780,7 +35463,7 @@
         <v>1304</v>
       </c>
       <c r="C962" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D962" s="19">
         <v>38</v>
@@ -35810,7 +35493,7 @@
         <v>1304</v>
       </c>
       <c r="C963" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D963" s="19">
         <v>39</v>
@@ -35840,7 +35523,7 @@
         <v>1304</v>
       </c>
       <c r="C964" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D964" s="19">
         <v>40</v>
@@ -35870,7 +35553,7 @@
         <v>1304</v>
       </c>
       <c r="C965" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D965" s="19">
         <v>41</v>
@@ -35900,7 +35583,7 @@
         <v>1304</v>
       </c>
       <c r="C966" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D966" s="19">
         <v>42</v>
@@ -35930,7 +35613,7 @@
         <v>1304</v>
       </c>
       <c r="C967" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D967" s="19">
         <v>43</v>
@@ -35960,7 +35643,7 @@
         <v>1304</v>
       </c>
       <c r="C968" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D968" s="19">
         <v>44</v>
@@ -35990,7 +35673,7 @@
         <v>1304</v>
       </c>
       <c r="C969" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D969" s="19">
         <v>45</v>
@@ -36020,7 +35703,7 @@
         <v>1304</v>
       </c>
       <c r="C970" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D970" s="19">
         <v>46</v>
@@ -36050,7 +35733,7 @@
         <v>1304</v>
       </c>
       <c r="C971" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D971" s="19">
         <v>47</v>
@@ -36080,7 +35763,7 @@
         <v>1304</v>
       </c>
       <c r="C972" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D972" s="19">
         <v>48</v>
@@ -36110,7 +35793,7 @@
         <v>1304</v>
       </c>
       <c r="C973" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D973" s="19">
         <v>49</v>
@@ -36140,7 +35823,7 @@
         <v>1304</v>
       </c>
       <c r="C974" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D974" s="19">
         <v>50</v>
@@ -36170,7 +35853,7 @@
         <v>1304</v>
       </c>
       <c r="C975" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D975" s="19">
         <v>51</v>
@@ -36200,7 +35883,7 @@
         <v>1304</v>
       </c>
       <c r="C976" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D976" s="19">
         <v>52</v>
@@ -36230,7 +35913,7 @@
         <v>1304</v>
       </c>
       <c r="C977" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D977" s="19">
         <v>53</v>
@@ -36260,7 +35943,7 @@
         <v>1304</v>
       </c>
       <c r="C978" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D978" s="19">
         <v>54</v>
@@ -36290,7 +35973,7 @@
         <v>1304</v>
       </c>
       <c r="C979" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D979" s="19">
         <v>55</v>
@@ -36320,7 +36003,7 @@
         <v>1304</v>
       </c>
       <c r="C980" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D980" s="19">
         <v>56</v>
@@ -36350,7 +36033,7 @@
         <v>1304</v>
       </c>
       <c r="C981" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D981" s="19">
         <v>57</v>
@@ -36380,7 +36063,7 @@
         <v>1304</v>
       </c>
       <c r="C982" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D982" s="19">
         <v>58</v>
@@ -36410,7 +36093,7 @@
         <v>1304</v>
       </c>
       <c r="C983" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D983" s="19">
         <v>59</v>
@@ -36440,7 +36123,7 @@
         <v>1304</v>
       </c>
       <c r="C984" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D984" s="19">
         <v>60</v>
@@ -36476,10 +36159,10 @@
   <sheetData>
     <row r="1" spans="1:65">
       <c r="A1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" t="s">
         <v>273</v>
-      </c>
-      <c r="C1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:65">
@@ -38206,7 +37889,7 @@
     </row>
     <row r="11" spans="1:65">
       <c r="B11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C11">
         <f>SUM(C2:C10)</f>
@@ -40759,7 +40442,7 @@
     </row>
     <row r="27" spans="3:66">
       <c r="C27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="3:66">

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -3015,7 +3015,7 @@
         <v>37</v>
       </c>
       <c r="E5" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="22">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>37</v>
       </c>
       <c r="E6" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="22">
         <v>2</v>
@@ -3119,7 +3119,7 @@
         <v>37</v>
       </c>
       <c r="E7" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="22">
         <v>3</v>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E8" s="22">
         <f t="shared" ref="E8:E64" si="1">E5+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="22">
         <v>4</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="E9" s="22">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="22">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="E10" s="22">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="22">
         <v>6</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E11" s="22">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="22">
         <v>7</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="E12" s="22">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="22">
         <v>8</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E13" s="22">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="22">
         <v>9</v>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="E14" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="22">
         <v>10</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E15" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="22">
         <v>11</v>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E16" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="22">
         <v>12</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E17" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="22">
         <v>13</v>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E18" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="22">
         <v>14</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E19" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="22">
         <v>15</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E20" s="22">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="22">
         <v>16</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E21" s="22">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" s="22">
         <v>17</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E22" s="22">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="22">
         <v>18</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="E23" s="22">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="22">
         <v>19</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E24" s="22">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="22">
         <v>20</v>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="E25" s="22">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="22">
         <v>21</v>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="E26" s="22">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="22">
         <v>22</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="E27" s="22">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" s="22">
         <v>23</v>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="E28" s="22">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" s="22">
         <v>24</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="E29" s="22">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" s="22">
         <v>25</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E30" s="22">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" s="22">
         <v>26</v>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E31" s="22">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" s="22">
         <v>27</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="E32" s="22">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="22">
         <v>28</v>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E33" s="22">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" s="22">
         <v>29</v>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="E34" s="22">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="22">
         <v>30</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="E35" s="22">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="22">
         <v>31</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E36" s="22">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="22">
         <v>32</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E37" s="22">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="22">
         <v>33</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E38" s="22">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" s="22">
         <v>34</v>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E39" s="22">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F39" s="22">
         <v>35</v>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="E40" s="22">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F40" s="22">
         <v>36</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="E41" s="22">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F41" s="22">
         <v>37</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E42" s="22">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F42" s="22">
         <v>38</v>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E43" s="22">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F43" s="22">
         <v>39</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="E44" s="22">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F44" s="22">
         <v>40</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E45" s="22">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F45" s="22">
         <v>41</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="E46" s="22">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F46" s="22">
         <v>42</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="E47" s="22">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F47" s="22">
         <v>43</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="E48" s="22">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F48" s="22">
         <v>44</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E49" s="22">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F49" s="22">
         <v>45</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="E50" s="22">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F50" s="22">
         <v>46</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="E51" s="22">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F51" s="22">
         <v>47</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="E52" s="22">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F52" s="22">
         <v>48</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="E53" s="22">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53" s="22">
         <v>49</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="E54" s="22">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F54" s="22">
         <v>50</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="E55" s="22">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55" s="22">
         <v>51</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E56" s="22">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F56" s="22">
         <v>52</v>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="E57" s="22">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F57" s="22">
         <v>53</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="E58" s="22">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F58" s="22">
         <v>54</v>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="E59" s="22">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F59" s="22">
         <v>55</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="E60" s="22">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F60" s="22">
         <v>56</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="E61" s="22">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F61" s="22">
         <v>57</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="E62" s="22">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F62" s="22">
         <v>58</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="E63" s="22">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63" s="22">
         <v>59</v>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
     <t>1980000_10</t>
   </si>
   <si>
-    <t>1022505_200|1980000_50</t>
+    <t>1022505_200</t>
   </si>
   <si>
     <t>1101101_1101102_1101103_1101104_1101105_1101106</t>
@@ -416,7 +416,7 @@
     <t>1980000_15</t>
   </si>
   <si>
-    <t>1022505_300|1980000_50</t>
+    <t>1022505_300</t>
   </si>
   <si>
     <t>1101107_1101108_1101109</t>
@@ -431,7 +431,7 @@
     <t>1980000_20</t>
   </si>
   <si>
-    <t>1022505_400|1980000_50</t>
+    <t>1022505_400</t>
   </si>
   <si>
     <t>1101110_1101111_1101112</t>
@@ -446,7 +446,7 @@
     <t>1980000_25</t>
   </si>
   <si>
-    <t>1022505_500|1980000_50</t>
+    <t>1022505_500</t>
   </si>
   <si>
     <t>1990000_4000,1990000_4400,1990000_4800,1990000_5200,1990000_5600,1990000_6000,1990000_6400,1990000_6800,1990000_7200</t>
@@ -455,7 +455,7 @@
     <t>1980000_30</t>
   </si>
   <si>
-    <t>1022505_600|1980000_50</t>
+    <t>1022505_600</t>
   </si>
   <si>
     <t>1990000_5000,1990000_5500,1990000_6000,1990000_6500,1990000_7000,1990000_7500,1990000_8000,1990000_8500,1990000_9000</t>
@@ -464,7 +464,7 @@
     <t>1980000_35</t>
   </si>
   <si>
-    <t>1022505_700|1980000_50</t>
+    <t>1022505_700</t>
   </si>
   <si>
     <t>1990000_6000,1990000_6600,1990000_7200,1990000_7800,1990000_8400,1990000_9000,1990000_9600,1990000_10200,1990000_10800</t>
@@ -473,7 +473,7 @@
     <t>1980000_40</t>
   </si>
   <si>
-    <t>1022505_800|1980000_50</t>
+    <t>1022505_800</t>
   </si>
   <si>
     <t>1990000_7000,1990000_7700,1990000_8400,1990000_9100,1990000_9800,1990000_10500,1990000_11200,1990000_11900,1990000_12600</t>
@@ -482,7 +482,7 @@
     <t>1980000_45</t>
   </si>
   <si>
-    <t>1022505_900|1980000_50</t>
+    <t>1022505_900</t>
   </si>
   <si>
     <t>1990000_8000,1990000_8800,1990000_9600,1990000_10400,1990000_11200,1990000_12000,1990000_12800,1990000_13600,1990000_14400</t>
@@ -491,7 +491,7 @@
     <t>1980000_50</t>
   </si>
   <si>
-    <t>1022505_1000|1980000_50</t>
+    <t>1022505_1000</t>
   </si>
   <si>
     <t>1990000_9000,1990000_9900,1990000_10800,1990000_11700,1990000_12600,1990000_13500,1990000_14400,1990000_15300,1990000_16200</t>
@@ -500,7 +500,7 @@
     <t>1980000_55</t>
   </si>
   <si>
-    <t>1022505_1100|1980000_50</t>
+    <t>1022505_1100</t>
   </si>
   <si>
     <t>1990000_10000,1990000_11000,1990000_12000,1990000_13000,1990000_14000,1990000_15000,1990000_16000,1990000_17000,1990000_18000</t>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -407,7 +407,7 @@
     <t>11011011_11011021_11011031_11011041_11011051_11011061</t>
   </si>
   <si>
-    <t>1101274_1101275_1101276_1101256_1101261_1101263_1101266_1101269_1101257</t>
+    <t>1101270_1101274_1101275_1101276_1101256_1101261_1101263_1101266_1101269_1101257</t>
   </si>
   <si>
     <t>1990000_1000,1990000_1100,1990000_1200,1990000_1300,1990000_1400,1990000_1500,1990000_1600,1990000_1700,1990000_1800</t>
@@ -1175,7 +1175,7 @@
     <t>11071011_11071021_11071031_11071041_11071051</t>
   </si>
   <si>
-    <t>1107267_1107268_1107259_1107253_1107261</t>
+    <t>1107254_1107267_1107268_1107259_1107253_1107261</t>
   </si>
   <si>
     <t>1107106_1107107_1107108</t>
@@ -1202,7 +1202,7 @@
     <t>11081011_11081021_11081031_11081041_11081051</t>
   </si>
   <si>
-    <t>1108268_1108269_1108261_1108262</t>
+    <t>1108252_1108268_1108269_1108261_1108262</t>
   </si>
   <si>
     <t>1108106_1108107_1108108</t>
@@ -1259,7 +1259,7 @@
     <t>11091011_11091021_11091031_11091041_11091051</t>
   </si>
   <si>
-    <t>1109268_1109269_1109261_1109262</t>
+    <t>1109252_1109268_1109269_1109261_1109262</t>
   </si>
   <si>
     <t>1109106_1109107_1109108</t>
@@ -1286,7 +1286,7 @@
     <t>11101011_11101021_11101031_11101041_11101051</t>
   </si>
   <si>
-    <t>1110268_1110269_1110259_1110253_1110261</t>
+    <t>1110251_1110268_1110269_1110259_1110253_1110261</t>
   </si>
   <si>
     <t>1110106_1110107_1110108</t>
@@ -1313,7 +1313,7 @@
     <t>11111091_11111101_11111061_11111071_11111081</t>
   </si>
   <si>
-    <t>1111251_1111271_1111267_1111265_1111264_1111263_1111256_1111260</t>
+    <t>1111269_1111270_1111251_1111271_1111267_1111265_1111264_1111263_1111256_1111260</t>
   </si>
   <si>
     <t>1111103_1111104_1111105</t>
@@ -1364,7 +1364,7 @@
     <t>11121011_11121021_11121031_11121041_11121051</t>
   </si>
   <si>
-    <t>1112268_1112269_1112261_1112260_1112257</t>
+    <t>1112251_1112252_1112253_1112268_1112269_1112261_1112260_1112257</t>
   </si>
   <si>
     <t>1112106_1112107_1112108</t>
@@ -3889,9 +3889,7 @@
       <c r="L19" s="12"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="2">
-        <v>1101270</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" s="24">
         <v>28</v>
       </c>
@@ -20688,9 +20686,7 @@
       <c r="L372" s="27"/>
       <c r="M372" s="28"/>
       <c r="N372" s="31"/>
-      <c r="O372" s="3">
-        <v>1107254</v>
-      </c>
+      <c r="O372" s="3"/>
       <c r="P372" s="29">
         <v>14</v>
       </c>
@@ -23787,9 +23783,6 @@
         <v>248</v>
       </c>
       <c r="L436" s="12"/>
-      <c r="O436" s="2">
-        <v>1108252</v>
-      </c>
       <c r="P436" s="24">
         <v>44</v>
       </c>
@@ -26608,9 +26601,7 @@
       <c r="L496" s="27"/>
       <c r="M496" s="28"/>
       <c r="N496" s="28"/>
-      <c r="O496" s="3">
-        <v>1109252</v>
-      </c>
+      <c r="O496" s="3"/>
       <c r="P496" s="29">
         <v>44</v>
       </c>
@@ -29515,9 +29506,6 @@
         <v>109</v>
       </c>
       <c r="L556" s="12"/>
-      <c r="O556" s="2">
-        <v>1110251</v>
-      </c>
       <c r="P556" s="24">
         <v>22</v>
       </c>
@@ -32287,9 +32275,7 @@
       <c r="L615" s="27"/>
       <c r="M615" s="28"/>
       <c r="N615" s="28"/>
-      <c r="O615" s="3">
-        <v>1111270</v>
-      </c>
+      <c r="O615" s="3"/>
       <c r="P615" s="29">
         <v>40</v>
       </c>
@@ -32336,9 +32322,7 @@
       <c r="L616" s="27"/>
       <c r="M616" s="28"/>
       <c r="N616" s="28"/>
-      <c r="O616" s="3">
-        <v>1111269</v>
-      </c>
+      <c r="O616" s="3"/>
       <c r="P616" s="29">
         <v>44</v>
       </c>
@@ -35141,9 +35125,6 @@
         <v>252</v>
       </c>
       <c r="L674" s="12"/>
-      <c r="O674" s="2">
-        <v>1112253</v>
-      </c>
       <c r="P674" s="24">
         <v>36</v>
       </c>
@@ -35190,9 +35171,7 @@
       <c r="L675" s="12"/>
       <c r="M675" s="11"/>
       <c r="N675" s="11"/>
-      <c r="O675" s="2">
-        <v>1112252</v>
-      </c>
+      <c r="O675" s="2"/>
       <c r="P675" s="24">
         <v>40</v>
       </c>
@@ -35239,9 +35218,7 @@
       <c r="L676" s="12"/>
       <c r="M676" s="11"/>
       <c r="N676" s="11"/>
-      <c r="O676" s="2">
-        <v>1112251</v>
-      </c>
+      <c r="O676" s="2"/>
       <c r="P676" s="24">
         <v>44</v>
       </c>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -10549,7 +10549,7 @@
         <v>44</v>
       </c>
       <c r="E64" s="25">
-        <v>9999</v>
+        <v>20</v>
       </c>
       <c r="F64" s="25">
         <v>60</v>
@@ -13510,7 +13510,7 @@
         <v>199</v>
       </c>
       <c r="E124" s="25">
-        <v>9999</v>
+        <v>22</v>
       </c>
       <c r="F124" s="25">
         <v>60</v>
@@ -16654,7 +16654,7 @@
         <v>338</v>
       </c>
       <c r="E184" s="25">
-        <v>9999</v>
+        <v>46</v>
       </c>
       <c r="F184" s="29">
         <v>60</v>
@@ -19690,7 +19690,7 @@
         <v>496</v>
       </c>
       <c r="E244" s="25">
-        <v>9999</v>
+        <v>42</v>
       </c>
       <c r="F244" s="25">
         <v>60</v>
@@ -22831,7 +22831,7 @@
         <v>638</v>
       </c>
       <c r="E304" s="25">
-        <v>9999</v>
+        <v>38</v>
       </c>
       <c r="F304" s="29">
         <v>60</v>
@@ -25877,7 +25877,7 @@
         <v>776</v>
       </c>
       <c r="E364" s="25">
-        <v>9999</v>
+        <v>34</v>
       </c>
       <c r="F364" s="25">
         <v>60</v>
@@ -29010,7 +29010,7 @@
         <v>914</v>
       </c>
       <c r="E424" s="25">
-        <v>9999</v>
+        <v>30</v>
       </c>
       <c r="F424" s="29">
         <v>60</v>
@@ -32034,7 +32034,7 @@
         <v>1052</v>
       </c>
       <c r="E484" s="25">
-        <v>999</v>
+        <v>54</v>
       </c>
       <c r="F484" s="25">
         <v>60</v>
@@ -35176,7 +35176,7 @@
         <v>1198</v>
       </c>
       <c r="E544" s="25">
-        <v>9999</v>
+        <v>50</v>
       </c>
       <c r="F544" s="29">
         <v>60</v>
@@ -38191,7 +38191,7 @@
         <v>1336</v>
       </c>
       <c r="E604" s="25">
-        <v>9999</v>
+        <v>26</v>
       </c>
       <c r="F604" s="25">
         <v>60</v>
@@ -41320,7 +41320,7 @@
         <v>1473</v>
       </c>
       <c r="E664" s="25">
-        <v>9999</v>
+        <v>60</v>
       </c>
       <c r="F664" s="29">
         <v>60</v>
@@ -44442,7 +44442,7 @@
         <v>1617</v>
       </c>
       <c r="E724" s="25">
-        <v>9999</v>
+        <v>58</v>
       </c>
       <c r="F724" s="25">
         <v>60</v>
@@ -47154,7 +47154,7 @@
       </c>
       <c r="D784" s="25"/>
       <c r="E784" s="25">
-        <v>9999</v>
+        <v>23</v>
       </c>
       <c r="F784" s="25">
         <v>60</v>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="D844" s="29"/>
       <c r="E844" s="25">
-        <v>9999</v>
+        <v>20</v>
       </c>
       <c r="F844" s="29">
         <v>60</v>
@@ -52429,7 +52429,7 @@
       </c>
       <c r="D904" s="29"/>
       <c r="E904" s="25">
-        <v>9999</v>
+        <v>23</v>
       </c>
       <c r="F904" s="29">
         <v>60</v>
@@ -54758,7 +54758,7 @@
       </c>
       <c r="D964" s="25"/>
       <c r="E964" s="25">
-        <v>9999</v>
+        <v>23</v>
       </c>
       <c r="F964" s="25">
         <v>60</v>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -959,7 +959,7 @@
     <t>11021071_11021081_11021091_11021101</t>
   </si>
   <si>
-    <t>1102259_1102261_1102263_1102264_1102265_1102266_1102267_1102268_1102276_1102277_1102278_1102272_1102273_1102274_1102275_1102279</t>
+    <t>1102259_1102261_1102263_1102264_1102265_1102266_1102267_1102268_1102276_1102277_1102278_1102272_1102273_1102274_1102275_1102279_1102297</t>
   </si>
   <si>
     <t>1990000_7476,1990000_14952,1990000_22428,1990000_29904,1990000_37380,1990000_44856,1990000_52332,1990000_59808,1990000_67284</t>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgradeTable" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
     <t>1101270_1101274_1101275_1101276_1101256_1101261_1101263_1101266_1101269_1101257</t>
   </si>
   <si>
-    <t>1990000_1059,1990000_2118,1990000_3177,1990000_4236,1990000_5295,1990000_6354,1990000_7413,1990000_8472,1990000_9532</t>
+    <t>1990000_706,1990000_1412,1990000_2118,1990000_2824,1990000_3530,1990000_4236,1990000_4942,1990000_5648,1990000_6354</t>
   </si>
   <si>
     <t>1101407_1101408_1101409</t>
@@ -476,24 +476,24 @@
     <t>11011071_11011081_11011091</t>
   </si>
   <si>
+    <t>1990000_1412,1990000_2824,1990000_4236,1990000_5648,1990000_7060,1990000_8472,1990000_9885,1990000_11297,1990000_12709</t>
+  </si>
+  <si>
+    <t>1101410_1101411_1101412</t>
+  </si>
+  <si>
+    <t>1024081_15</t>
+  </si>
+  <si>
+    <t>1101110_1101111_1101112</t>
+  </si>
+  <si>
+    <t>11011101_11011111_11011121</t>
+  </si>
+  <si>
     <t>1990000_2118,1990000_4236,1990000_6354,1990000_8472,1990000_10591,1990000_12709,1990000_14827,1990000_16945,1990000_19064</t>
   </si>
   <si>
-    <t>1101410_1101411_1101412</t>
-  </si>
-  <si>
-    <t>1024081_15</t>
-  </si>
-  <si>
-    <t>1101110_1101111_1101112</t>
-  </si>
-  <si>
-    <t>11011101_11011111_11011121</t>
-  </si>
-  <si>
-    <t>1990000_3177,1990000_6354,1990000_9532,1990000_12709,1990000_15886,1990000_19064,1990000_22241,1990000_25418,1990000_28596</t>
-  </si>
-  <si>
     <t>1024081_20</t>
   </si>
   <si>
@@ -506,111 +506,111 @@
     <t>11011131_11011141_11011151_11011161</t>
   </si>
   <si>
+    <t>1990000_2824,1990000_5648,1990000_8472,1990000_11297,1990000_14121,1990000_16945,1990000_19770,1990000_22594,1990000_25418</t>
+  </si>
+  <si>
+    <t>1024081_25</t>
+  </si>
+  <si>
+    <t>1990000_3530,1990000_7060,1990000_10591,1990000_14121,1990000_17651,1990000_21182,1990000_24712,1990000_28243,1990000_31773</t>
+  </si>
+  <si>
+    <t>1024081_30</t>
+  </si>
+  <si>
     <t>1990000_4236,1990000_8472,1990000_12709,1990000_16945,1990000_21182,1990000_25418,1990000_29655,1990000_33891,1990000_38128</t>
   </si>
   <si>
-    <t>1024081_25</t>
-  </si>
-  <si>
-    <t>1990000_5295,1990000_10591,1990000_15886,1990000_21182,1990000_26477,1990000_31773,1990000_37069,1990000_42364,1990000_47660</t>
-  </si>
-  <si>
-    <t>1024081_30</t>
+    <t>1024081_35</t>
+  </si>
+  <si>
+    <t>1990000_4942,1990000_9885,1990000_14827,1990000_19770,1990000_24712,1990000_29655,1990000_34597,1990000_39540,1990000_44483</t>
+  </si>
+  <si>
+    <t>1024081_40</t>
+  </si>
+  <si>
+    <t>10390001_2</t>
+  </si>
+  <si>
+    <t>1990000_5648,1990000_11297,1990000_16945,1990000_22594,1990000_28243,1990000_33891,1990000_39540,1990000_45188,1990000_50837</t>
+  </si>
+  <si>
+    <t>1024081_45</t>
   </si>
   <si>
     <t>1990000_6354,1990000_12709,1990000_19064,1990000_25418,1990000_31773,1990000_38128,1990000_44482,1990000_50837,1990000_57192</t>
   </si>
   <si>
-    <t>1024081_35</t>
-  </si>
-  <si>
-    <t>1990000_7413,1990000_14827,1990000_22241,1990000_29655,1990000_37069,1990000_44482,1990000_51896,1990000_59310,1990000_66724</t>
-  </si>
-  <si>
-    <t>1024081_40</t>
-  </si>
-  <si>
-    <t>10390001_2</t>
+    <t>1024081_50</t>
+  </si>
+  <si>
+    <t>1990000_7060,1990000_14121,1990000_21182,1990000_28243,1990000_35303,1990000_42364,1990000_49425,1990000_56486,1990000_63547</t>
+  </si>
+  <si>
+    <t>1024081_55</t>
+  </si>
+  <si>
+    <t>10390001_3</t>
   </si>
   <si>
     <t>1990000_8472,1990000_16945,1990000_25418,1990000_33891,1990000_42364,1990000_50837,1990000_59310,1990000_67783,1990000_76256</t>
   </si>
   <si>
-    <t>1024081_45</t>
-  </si>
-  <si>
-    <t>1990000_9532,1990000_19064,1990000_28596,1990000_38128,1990000_47660,1990000_57192,1990000_66724,1990000_76256,1990000_85788</t>
-  </si>
-  <si>
-    <t>1024081_50</t>
-  </si>
-  <si>
-    <t>1990000_10591,1990000_21182,1990000_31773,1990000_42364,1990000_52955,1990000_63547,1990000_74138,1990000_84729,1990000_95320</t>
-  </si>
-  <si>
-    <t>1024081_55</t>
-  </si>
-  <si>
-    <t>10390001_3</t>
+    <t>1024081_60</t>
+  </si>
+  <si>
+    <t>1990000_9885,1990000_19770,1990000_29655,1990000_39540,1990000_49425,1990000_59310,1990000_69195,1990000_79080,1990000_88966</t>
+  </si>
+  <si>
+    <t>1024081_65</t>
+  </si>
+  <si>
+    <t>1990000_11297,1990000_22594,1990000_33891,1990000_45189,1990000_56486,1990000_67783,1990000_79080,1990000_90378,1990000_101675</t>
+  </si>
+  <si>
+    <t>1024081_70</t>
   </si>
   <si>
     <t>1990000_12709,1990000_25418,1990000_38128,1990000_50837,1990000_63547,1990000_76256,1990000_88965,1990000_101675,1990000_114384</t>
   </si>
   <si>
-    <t>1024081_60</t>
-  </si>
-  <si>
-    <t>1990000_14827,1990000_29655,1990000_44483,1990000_59310,1990000_74138,1990000_88966,1990000_103793,1990000_118621,1990000_133449</t>
-  </si>
-  <si>
-    <t>1024081_65</t>
+    <t>1024081_75</t>
+  </si>
+  <si>
+    <t>1990000_14121,1990000_28243,1990000_42364,1990000_56486,1990000_70607,1990000_84729,1990000_98851,1990000_112972,1990000_127094</t>
+  </si>
+  <si>
+    <t>1024081_80</t>
+  </si>
+  <si>
+    <t>1990000_15533,1990000_31067,1990000_46601,1990000_62134,1990000_77668,1990000_93202,1990000_108736,1990000_124269,1990000_139803</t>
+  </si>
+  <si>
+    <t>1024081_85</t>
   </si>
   <si>
     <t>1990000_16945,1990000_33891,1990000_50837,1990000_67783,1990000_84729,1990000_101675,1990000_118621,1990000_135567,1990000_152513</t>
   </si>
   <si>
-    <t>1024081_70</t>
-  </si>
-  <si>
-    <t>1990000_19064,1990000_38128,1990000_57192,1990000_76256,1990000_95320,1990000_114384,1990000_133448,1990000_152513,1990000_171577</t>
-  </si>
-  <si>
-    <t>1024081_75</t>
+    <t>1024081_90</t>
+  </si>
+  <si>
+    <t>1990000_18358,1990000_36716,1990000_55074,1990000_73432,1990000_91790,1990000_110148,1990000_128506,1990000_146864,1990000_165222</t>
+  </si>
+  <si>
+    <t>1024081_95</t>
+  </si>
+  <si>
+    <t>1990000_19770,1990000_39540,1990000_59310,1990000_79080,1990000_98851,1990000_118621,1990000_138391,1990000_158161,1990000_177932</t>
+  </si>
+  <si>
+    <t>1024081_100</t>
   </si>
   <si>
     <t>1990000_21182,1990000_42364,1990000_63547,1990000_84729,1990000_105911,1990000_127094,1990000_148276,1990000_169459,1990000_190641</t>
   </si>
   <si>
-    <t>1024081_80</t>
-  </si>
-  <si>
-    <t>1990000_23300,1990000_46601,1990000_69901,1990000_93202,1990000_116503,1990000_139803,1990000_163104,1990000_186404,1990000_209705</t>
-  </si>
-  <si>
-    <t>1024081_85</t>
-  </si>
-  <si>
-    <t>1990000_25418,1990000_50837,1990000_76256,1990000_101675,1990000_127094,1990000_152513,1990000_177932,1990000_203350,1990000_228769</t>
-  </si>
-  <si>
-    <t>1024081_90</t>
-  </si>
-  <si>
-    <t>1990000_27537,1990000_55074,1990000_82611,1990000_110148,1990000_137685,1990000_165222,1990000_192759,1990000_220296,1990000_247833</t>
-  </si>
-  <si>
-    <t>1024081_95</t>
-  </si>
-  <si>
-    <t>1990000_29655,1990000_59310,1990000_88966,1990000_118621,1990000_148276,1990000_177932,1990000_207587,1990000_237242,1990000_266898</t>
-  </si>
-  <si>
-    <t>1024081_100</t>
-  </si>
-  <si>
-    <t>1990000_31773,1990000_63547,1990000_95320,1990000_127094,1990000_158867,1990000_190641,1990000_222415,1990000_254188,1990000_285962</t>
-  </si>
-  <si>
     <t>贵宾厅</t>
   </si>
   <si>
@@ -635,7 +635,7 @@
     <t>1102251_1102252_1102253_1102254_1102255_1102256_1102257_1102258_1102296_1102280_1102269_1102270_1102271_1102260_1102262_1102286</t>
   </si>
   <si>
-    <t>1990000_2651,1990000_5303,1990000_7954,1990000_10606,1990000_13257,1990000_15909,1990000_18560,1990000_21212,1990000_23864</t>
+    <t>1990000_1767,1990000_3535,1990000_5303,1990000_7070,1990000_8838,1990000_10606,1990000_12373,1990000_14141,1990000_15909</t>
   </si>
   <si>
     <t>1102407_1102408_1102409</t>
@@ -653,139 +653,139 @@
     <t>1102259_1102261_1102263_1102264_1102265_1102266_1102267_1102268_1102276_1102277_1102278_1102272_1102273_1102274_1102275_1102279_1102297</t>
   </si>
   <si>
+    <t>1990000_3535,1990000_7070,1990000_10606,1990000_14141,1990000_17677,1990000_21212,1990000_24747,1990000_28283,1990000_31818</t>
+  </si>
+  <si>
+    <t>1102410_1102411_1102412</t>
+  </si>
+  <si>
+    <t>1024083_15</t>
+  </si>
+  <si>
+    <t>1102111_1102112</t>
+  </si>
+  <si>
+    <t>11021111_11021121</t>
+  </si>
+  <si>
+    <t>1102287_1102288_1102289_1102290_1102282_1102283_1102284_1102285_1102281_1102291_1102292_1102293_1102294_1102295</t>
+  </si>
+  <si>
     <t>1990000_5303,1990000_10606,1990000_15909,1990000_21212,1990000_26515,1990000_31818,1990000_37121,1990000_42425,1990000_47728</t>
   </si>
   <si>
-    <t>1102410_1102411_1102412</t>
-  </si>
-  <si>
-    <t>1024083_15</t>
-  </si>
-  <si>
-    <t>1102111_1102112</t>
-  </si>
-  <si>
-    <t>11021111_11021121</t>
-  </si>
-  <si>
-    <t>1102287_1102288_1102289_1102290_1102282_1102283_1102284_1102285_1102281_1102291_1102292_1102293_1102294_1102295</t>
-  </si>
-  <si>
-    <t>1990000_7954,1990000_15909,1990000_23864,1990000_31818,1990000_39773,1990000_47728,1990000_55682,1990000_63637,1990000_71592</t>
-  </si>
-  <si>
     <t>1024083_20</t>
   </si>
   <si>
     <t>10270001_1</t>
   </si>
   <si>
+    <t>1990000_7070,1990000_14141,1990000_21212,1990000_28283,1990000_35354,1990000_42425,1990000_49495,1990000_56566,1990000_63637</t>
+  </si>
+  <si>
+    <t>1024083_25</t>
+  </si>
+  <si>
+    <t>1990000_8838,1990000_17677,1990000_26515,1990000_35354,1990000_44192,1990000_53031,1990000_61869,1990000_70708,1990000_79547</t>
+  </si>
+  <si>
+    <t>1024083_30</t>
+  </si>
+  <si>
     <t>1990000_10606,1990000_21212,1990000_31818,1990000_42425,1990000_53031,1990000_63637,1990000_74244,1990000_84850,1990000_95456</t>
   </si>
   <si>
-    <t>1024083_25</t>
-  </si>
-  <si>
-    <t>1990000_13257,1990000_26515,1990000_39773,1990000_53031,1990000_66289,1990000_79547,1990000_92804,1990000_106062,1990000_119320</t>
-  </si>
-  <si>
-    <t>1024083_30</t>
+    <t>1024083_35</t>
+  </si>
+  <si>
+    <t>1990000_12374,1990000_24748,1990000_37122,1990000_49496,1990000_61870,1990000_74244,1990000_86618,1990000_98992,1990000_111366</t>
+  </si>
+  <si>
+    <t>1024083_40</t>
+  </si>
+  <si>
+    <t>10270001_2</t>
+  </si>
+  <si>
+    <t>1990000_14141,1990000_28283,1990000_42425,1990000_56566,1990000_70708,1990000_84850,1990000_98991,1990000_113133,1990000_127275</t>
+  </si>
+  <si>
+    <t>1024083_45</t>
   </si>
   <si>
     <t>1990000_15909,1990000_31818,1990000_47728,1990000_63637,1990000_79547,1990000_95456,1990000_111365,1990000_127275,1990000_143184</t>
   </si>
   <si>
-    <t>1024083_35</t>
-  </si>
-  <si>
-    <t>1990000_18561,1990000_37122,1990000_55683,1990000_74244,1990000_92805,1990000_111366,1990000_129927,1990000_148488,1990000_167049</t>
-  </si>
-  <si>
-    <t>1024083_40</t>
-  </si>
-  <si>
-    <t>10270001_2</t>
+    <t>1024083_50</t>
+  </si>
+  <si>
+    <t>1990000_17677,1990000_35354,1990000_53031,1990000_70708,1990000_88385,1990000_106062,1990000_123739,1990000_141417,1990000_159094</t>
+  </si>
+  <si>
+    <t>1024083_55</t>
+  </si>
+  <si>
+    <t>10270001_3</t>
   </si>
   <si>
     <t>1990000_21212,1990000_42425,1990000_63637,1990000_84850,1990000_106062,1990000_127275,1990000_148488,1990000_169700,1990000_190913</t>
   </si>
   <si>
-    <t>1024083_45</t>
-  </si>
-  <si>
-    <t>1990000_23864,1990000_47728,1990000_71592,1990000_95456,1990000_119320,1990000_143184,1990000_167048,1990000_190913,1990000_214777</t>
-  </si>
-  <si>
-    <t>1024083_50</t>
-  </si>
-  <si>
-    <t>1990000_26515,1990000_53031,1990000_79547,1990000_106062,1990000_132578,1990000_159094,1990000_185609,1990000_212125,1990000_238641</t>
-  </si>
-  <si>
-    <t>1024083_55</t>
-  </si>
-  <si>
-    <t>10270001_3</t>
+    <t>1024083_60</t>
+  </si>
+  <si>
+    <t>1990000_24748,1990000_49496,1990000_74244,1990000_98992,1990000_123740,1990000_148488,1990000_173236,1990000_197984,1990000_222732</t>
+  </si>
+  <si>
+    <t>1024083_65</t>
+  </si>
+  <si>
+    <t>1990000_28283,1990000_56566,1990000_84850,1990000_113133,1990000_141417,1990000_169700,1990000_197983,1990000_226267,1990000_254550</t>
+  </si>
+  <si>
+    <t>1024083_70</t>
+  </si>
+  <si>
+    <t>10270001_4</t>
   </si>
   <si>
     <t>1990000_31818,1990000_63637,1990000_95456,1990000_127275,1990000_159094,1990000_190913,1990000_222732,1990000_254550,1990000_286369</t>
   </si>
   <si>
-    <t>1024083_60</t>
-  </si>
-  <si>
-    <t>1990000_37122,1990000_74244,1990000_111366,1990000_148488,1990000_185610,1990000_222732,1990000_259854,1990000_296976,1990000_334098</t>
-  </si>
-  <si>
-    <t>1024083_65</t>
+    <t>1024083_75</t>
+  </si>
+  <si>
+    <t>1990000_35354,1990000_70708,1990000_106062,1990000_141417,1990000_176771,1990000_212125,1990000_247480,1990000_282834,1990000_318188</t>
+  </si>
+  <si>
+    <t>1024083_80</t>
+  </si>
+  <si>
+    <t>1990000_38889,1990000_77779,1990000_116669,1990000_155558,1990000_194448,1990000_233338,1990000_272227,1990000_311117,1990000_350007</t>
+  </si>
+  <si>
+    <t>1024083_85</t>
   </si>
   <si>
     <t>1990000_42425,1990000_84850,1990000_127275,1990000_169700,1990000_212125,1990000_254550,1990000_296976,1990000_339401,1990000_381826</t>
   </si>
   <si>
-    <t>1024083_70</t>
-  </si>
-  <si>
-    <t>10270001_4</t>
-  </si>
-  <si>
-    <t>1990000_47728,1990000_95456,1990000_143184,1990000_190913,1990000_238641,1990000_286369,1990000_334098,1990000_381826,1990000_429554</t>
-  </si>
-  <si>
-    <t>1024083_75</t>
+    <t>1024083_90</t>
+  </si>
+  <si>
+    <t>1990000_45960,1990000_91921,1990000_137881,1990000_183842,1990000_229802,1990000_275763,1990000_321724,1990000_367684,1990000_413645</t>
+  </si>
+  <si>
+    <t>1024083_95</t>
+  </si>
+  <si>
+    <t>1990000_49496,1990000_98992,1990000_148488,1990000_197984,1990000_247480,1990000_296976,1990000_346472,1990000_395968,1990000_445464</t>
+  </si>
+  <si>
+    <t>1024083_100</t>
   </si>
   <si>
     <t>1990000_53031,1990000_106062,1990000_159094,1990000_212125,1990000_265157,1990000_318188,1990000_371220,1990000_424251,1990000_477283</t>
-  </si>
-  <si>
-    <t>1024083_80</t>
-  </si>
-  <si>
-    <t>1990000_58334,1990000_116669,1990000_175003,1990000_233338,1990000_291672,1990000_350007,1990000_408342,1990000_466676,1990000_525011</t>
-  </si>
-  <si>
-    <t>1024083_85</t>
-  </si>
-  <si>
-    <t>1990000_63637,1990000_127275,1990000_190913,1990000_254550,1990000_318188,1990000_381826,1990000_445464,1990000_509101,1990000_572739</t>
-  </si>
-  <si>
-    <t>1024083_90</t>
-  </si>
-  <si>
-    <t>1990000_68940,1990000_137881,1990000_206822,1990000_275763,1990000_344704,1990000_413645,1990000_482586,1990000_551526,1990000_620467</t>
-  </si>
-  <si>
-    <t>1024083_95</t>
-  </si>
-  <si>
-    <t>1990000_74244,1990000_148488,1990000_222732,1990000_296976,1990000_371220,1990000_445464,1990000_519708,1990000_593952,1990000_668196</t>
-  </si>
-  <si>
-    <t>1024083_100</t>
-  </si>
-  <si>
-    <t>1990000_79547,1990000_159094,1990000_238641,1990000_318188,1990000_397735,1990000_477282,1990000_556830,1990000_636377,1990000_715924</t>
   </si>
   <si>
     <t>辉煌厅</t>
@@ -3072,12 +3072,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -17700,7 +17700,7 @@
         <v>751</v>
       </c>
       <c r="J265" s="30">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K265" s="30"/>
       <c r="L265" s="15" t="s">
@@ -17714,7 +17714,7 @@
       <c r="S265" s="32">
         <v>1</v>
       </c>
-      <c r="T265" s="34" t="s">
+      <c r="T265" s="28" t="s">
         <v>51</v>
       </c>
     </row>
@@ -17742,7 +17742,7 @@
         <v>756</v>
       </c>
       <c r="J266" s="30">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="K266" s="30"/>
       <c r="L266" s="15" t="s">
@@ -17756,7 +17756,7 @@
       <c r="S266" s="32">
         <v>2</v>
       </c>
-      <c r="T266" s="34" t="s">
+      <c r="T266" s="28" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
         <v>758</v>
       </c>
       <c r="J267" s="30">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="K267" s="30"/>
       <c r="L267" s="15" t="s">
@@ -17798,7 +17798,7 @@
       <c r="S267" s="32">
         <v>4</v>
       </c>
-      <c r="T267" s="34" t="s">
+      <c r="T267" s="28" t="s">
         <v>61</v>
       </c>
     </row>
@@ -17826,7 +17826,7 @@
         <v>759</v>
       </c>
       <c r="J268" s="30">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="K268" s="30"/>
       <c r="L268" s="15" t="s">
@@ -17840,7 +17840,7 @@
       <c r="S268" s="32">
         <v>6</v>
       </c>
-      <c r="T268" s="34" t="s">
+      <c r="T268" s="28" t="s">
         <v>66</v>
       </c>
     </row>
@@ -17868,7 +17868,7 @@
         <v>760</v>
       </c>
       <c r="J269" s="30">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="K269" s="30"/>
       <c r="L269" s="15" t="s">
@@ -17882,7 +17882,7 @@
       <c r="S269" s="32">
         <v>8</v>
       </c>
-      <c r="T269" s="34" t="s">
+      <c r="T269" s="28" t="s">
         <v>68</v>
       </c>
     </row>
@@ -17924,7 +17924,7 @@
       <c r="S270" s="32">
         <v>10</v>
       </c>
-      <c r="T270" s="34" t="s">
+      <c r="T270" s="28" t="s">
         <v>70</v>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
         <v>762</v>
       </c>
       <c r="J271" s="30">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="K271" s="30"/>
       <c r="L271" s="15" t="s">
@@ -17966,7 +17966,7 @@
       <c r="S271" s="32">
         <v>12</v>
       </c>
-      <c r="T271" s="34" t="s">
+      <c r="T271" s="28" t="s">
         <v>72</v>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
         <v>763</v>
       </c>
       <c r="J272" s="30">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="K272" s="30"/>
       <c r="L272" s="15" t="s">
@@ -18008,7 +18008,7 @@
       <c r="S272" s="32">
         <v>14</v>
       </c>
-      <c r="T272" s="34" t="s">
+      <c r="T272" s="28" t="s">
         <v>75</v>
       </c>
     </row>
@@ -18036,7 +18036,7 @@
         <v>765</v>
       </c>
       <c r="J273" s="30">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="K273" s="30"/>
       <c r="L273" s="15" t="s">
@@ -18050,7 +18050,7 @@
       <c r="S273" s="32">
         <v>16</v>
       </c>
-      <c r="T273" s="34" t="s">
+      <c r="T273" s="28" t="s">
         <v>77</v>
       </c>
     </row>
@@ -18078,7 +18078,7 @@
         <v>767</v>
       </c>
       <c r="J274" s="30">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="K274" s="30"/>
       <c r="L274" s="15" t="s">
@@ -18090,7 +18090,7 @@
       <c r="S274" s="32">
         <v>18</v>
       </c>
-      <c r="T274" s="34" t="s">
+      <c r="T274" s="28" t="s">
         <v>79</v>
       </c>
     </row>
@@ -18118,7 +18118,7 @@
         <v>769</v>
       </c>
       <c r="J275" s="30">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="K275" s="30"/>
       <c r="L275" s="15" t="s">
@@ -18130,7 +18130,7 @@
       <c r="S275" s="32">
         <v>20</v>
       </c>
-      <c r="T275" s="34" t="s">
+      <c r="T275" s="28" t="s">
         <v>82</v>
       </c>
     </row>
@@ -18158,7 +18158,7 @@
         <v>771</v>
       </c>
       <c r="J276" s="30">
-        <v>600</v>
+        <v>420</v>
       </c>
       <c r="K276" s="30"/>
       <c r="L276" s="15" t="s">
@@ -18170,7 +18170,7 @@
       <c r="S276" s="32">
         <v>22</v>
       </c>
-      <c r="T276" s="34" t="s">
+      <c r="T276" s="28" t="s">
         <v>84</v>
       </c>
     </row>
@@ -18198,7 +18198,7 @@
         <v>773</v>
       </c>
       <c r="J277" s="30">
-        <v>650</v>
+        <v>440</v>
       </c>
       <c r="K277" s="30"/>
       <c r="L277" s="15" t="s">
@@ -18212,7 +18212,7 @@
       <c r="S277" s="32">
         <v>24</v>
       </c>
-      <c r="T277" s="34" t="s">
+      <c r="T277" s="28" t="s">
         <v>86</v>
       </c>
     </row>
@@ -18240,7 +18240,7 @@
         <v>775</v>
       </c>
       <c r="J278" s="30">
-        <v>700</v>
+        <v>460</v>
       </c>
       <c r="K278" s="30"/>
       <c r="L278" s="15" t="s">
@@ -18254,7 +18254,7 @@
       <c r="S278" s="32">
         <v>26</v>
       </c>
-      <c r="T278" s="34" t="s">
+      <c r="T278" s="28" t="s">
         <v>88</v>
       </c>
     </row>
@@ -18282,7 +18282,7 @@
         <v>776</v>
       </c>
       <c r="J279" s="30">
-        <v>750</v>
+        <v>480</v>
       </c>
       <c r="K279" s="30"/>
       <c r="L279" s="15" t="s">
@@ -18296,7 +18296,7 @@
       <c r="S279" s="32">
         <v>28</v>
       </c>
-      <c r="T279" s="34" t="s">
+      <c r="T279" s="28" t="s">
         <v>90</v>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
         <v>777</v>
       </c>
       <c r="J280" s="30">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="K280" s="30"/>
       <c r="L280" s="15" t="s">
@@ -18338,7 +18338,7 @@
       <c r="S280" s="32">
         <v>30</v>
       </c>
-      <c r="T280" s="34" t="s">
+      <c r="T280" s="28" t="s">
         <v>92</v>
       </c>
     </row>
@@ -18366,7 +18366,7 @@
         <v>778</v>
       </c>
       <c r="J281" s="30">
-        <v>850</v>
+        <v>520</v>
       </c>
       <c r="K281" s="30"/>
       <c r="L281" s="15" t="s">
@@ -18380,7 +18380,7 @@
       <c r="S281" s="32">
         <v>32</v>
       </c>
-      <c r="T281" s="34" t="s">
+      <c r="T281" s="28" t="s">
         <v>94</v>
       </c>
     </row>
@@ -18408,7 +18408,7 @@
         <v>779</v>
       </c>
       <c r="J282" s="30">
-        <v>900</v>
+        <v>540</v>
       </c>
       <c r="K282" s="30"/>
       <c r="L282" s="15" t="s">
@@ -18422,7 +18422,7 @@
       <c r="S282" s="32">
         <v>34</v>
       </c>
-      <c r="T282" s="34" t="s">
+      <c r="T282" s="28" t="s">
         <v>96</v>
       </c>
     </row>
@@ -18450,7 +18450,7 @@
         <v>780</v>
       </c>
       <c r="J283" s="30">
-        <v>950</v>
+        <v>560</v>
       </c>
       <c r="K283" s="30"/>
       <c r="L283" s="15" t="s">
@@ -18464,7 +18464,7 @@
       <c r="S283" s="32">
         <v>36</v>
       </c>
-      <c r="T283" s="34" t="s">
+      <c r="T283" s="28" t="s">
         <v>98</v>
       </c>
     </row>
@@ -18492,7 +18492,7 @@
         <v>781</v>
       </c>
       <c r="J284" s="30">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="K284" s="30"/>
       <c r="L284" s="15" t="s">
@@ -18506,7 +18506,7 @@
       <c r="S284" s="32">
         <v>38</v>
       </c>
-      <c r="T284" s="34" t="s">
+      <c r="T284" s="28" t="s">
         <v>100</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="857">
   <si>
     <t>ID</t>
   </si>
@@ -2654,7 +2654,13 @@
     <t>接待区</t>
   </si>
   <si>
-    <t>1301260_1301258</t>
+    <t>1301251_1301252_1301253_1301254_1301257_1301259_1301260_1301263_1301264</t>
+  </si>
+  <si>
+    <t>1301258_1301261</t>
+  </si>
+  <si>
+    <t>1301262_1301255_1301256</t>
   </si>
   <si>
     <t/>
@@ -4425,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>45</v>
@@ -4482,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>52</v>
@@ -4539,7 +4545,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>58</v>
@@ -4595,7 +4601,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H8" s="14">
         <v>1101413</v>
@@ -4656,7 +4662,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H9" s="14">
         <v>1101414</v>
@@ -4712,7 +4718,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H10" s="14">
         <v>1101415</v>
@@ -4771,7 +4777,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="25" t="s">
@@ -4818,7 +4824,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="25" t="s">
@@ -4867,7 +4873,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="25" t="s">
@@ -4916,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="25" t="s">
@@ -4962,7 +4968,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="25" t="s">
@@ -5013,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="25" t="s">
@@ -5060,7 +5066,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="25" t="s">
@@ -5111,7 +5117,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="25" t="s">
@@ -5160,7 +5166,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="25" t="s">
@@ -5211,7 +5217,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="25" t="s">
@@ -5260,7 +5266,7 @@
         <v>17</v>
       </c>
       <c r="G21" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="25" t="s">
@@ -5311,7 +5317,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="25" t="s">
@@ -5360,7 +5366,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="25" t="s">
@@ -5411,7 +5417,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="25" t="s">
@@ -5460,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="10">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>102</v>
@@ -5517,7 +5523,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>109</v>
@@ -5574,7 +5580,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>115</v>
@@ -5633,7 +5639,7 @@
         <v>4</v>
       </c>
       <c r="G28" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H28" s="14">
         <v>1102413</v>
@@ -5692,7 +5698,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H29" s="14">
         <v>1102414</v>
@@ -5738,7 +5744,7 @@
         <v>6</v>
       </c>
       <c r="G30" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H30" s="14">
         <v>1102415</v>
@@ -5788,7 +5794,7 @@
         <v>7</v>
       </c>
       <c r="G31" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I31" s="25" t="s">
         <v>128</v>
@@ -5831,7 +5837,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I32" s="25" t="s">
         <v>130</v>
@@ -5878,7 +5884,7 @@
         <v>9</v>
       </c>
       <c r="G33" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I33" s="25" t="s">
         <v>133</v>
@@ -5925,7 +5931,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I34" s="25" t="s">
         <v>135</v>
@@ -5969,7 +5975,7 @@
         <v>11</v>
       </c>
       <c r="G35" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I35" s="25" t="s">
         <v>137</v>
@@ -6018,7 +6024,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I36" s="25" t="s">
         <v>140</v>
@@ -6063,7 +6069,7 @@
         <v>13</v>
       </c>
       <c r="G37" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I37" s="25" t="s">
         <v>142</v>
@@ -6109,7 +6115,7 @@
         <v>14</v>
       </c>
       <c r="G38" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I38" s="25" t="s">
         <v>144</v>
@@ -6156,7 +6162,7 @@
         <v>15</v>
       </c>
       <c r="G39" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I39" s="25" t="s">
         <v>147</v>
@@ -6202,7 +6208,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I40" s="25" t="s">
         <v>149</v>
@@ -6247,7 +6253,7 @@
         <v>17</v>
       </c>
       <c r="G41" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I41" s="25" t="s">
         <v>151</v>
@@ -6294,7 +6300,7 @@
         <v>18</v>
       </c>
       <c r="G42" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I42" s="25" t="s">
         <v>153</v>
@@ -6339,7 +6345,7 @@
         <v>19</v>
       </c>
       <c r="G43" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I43" s="25" t="s">
         <v>155</v>
@@ -6386,7 +6392,7 @@
         <v>20</v>
       </c>
       <c r="G44" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I44" s="25" t="s">
         <v>157</v>
@@ -16771,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="G245" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H245" s="25" t="s">
         <v>749</v>
@@ -16824,7 +16830,7 @@
         <v>2</v>
       </c>
       <c r="G246" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H246" s="25">
         <v>1202417</v>
@@ -16871,7 +16877,7 @@
         <v>3</v>
       </c>
       <c r="G247" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H247" s="25">
         <v>1202418</v>
@@ -16918,7 +16924,7 @@
         <v>4</v>
       </c>
       <c r="G248" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H248" s="25">
         <v>1202419</v>
@@ -16965,7 +16971,7 @@
         <v>5</v>
       </c>
       <c r="G249" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H249" s="25">
         <v>1202420</v>
@@ -17012,7 +17018,7 @@
         <v>6</v>
       </c>
       <c r="G250" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H250" s="25">
         <v>1202421</v>
@@ -17059,7 +17065,7 @@
         <v>7</v>
       </c>
       <c r="G251" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H251" s="25">
         <v>1202422</v>
@@ -17106,7 +17112,7 @@
         <v>8</v>
       </c>
       <c r="G252" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H252" s="25">
         <v>1202423</v>
@@ -17153,7 +17159,7 @@
         <v>9</v>
       </c>
       <c r="G253" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H253" s="25">
         <v>1202424</v>
@@ -17200,7 +17206,7 @@
         <v>10</v>
       </c>
       <c r="G254" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H254" s="25">
         <v>1202425</v>
@@ -17247,7 +17253,7 @@
         <v>11</v>
       </c>
       <c r="G255" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H255" s="25"/>
       <c r="I255" s="25" t="s">
@@ -17292,7 +17298,7 @@
         <v>12</v>
       </c>
       <c r="G256" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H256" s="25"/>
       <c r="I256" s="25" t="s">
@@ -17337,7 +17343,7 @@
         <v>13</v>
       </c>
       <c r="G257" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H257" s="25"/>
       <c r="I257" s="25" t="s">
@@ -17382,7 +17388,7 @@
         <v>14</v>
       </c>
       <c r="G258" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H258" s="25"/>
       <c r="I258" s="25" t="s">
@@ -17427,7 +17433,7 @@
         <v>15</v>
       </c>
       <c r="G259" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H259" s="25"/>
       <c r="I259" s="25" t="s">
@@ -17472,7 +17478,7 @@
         <v>16</v>
       </c>
       <c r="G260" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H260" s="25"/>
       <c r="I260" s="25" t="s">
@@ -17517,7 +17523,7 @@
         <v>17</v>
       </c>
       <c r="G261" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H261" s="25"/>
       <c r="I261" s="25" t="s">
@@ -17562,7 +17568,7 @@
         <v>18</v>
       </c>
       <c r="G262" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H262" s="25"/>
       <c r="I262" s="25" t="s">
@@ -17607,7 +17613,7 @@
         <v>19</v>
       </c>
       <c r="G263" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H263" s="25"/>
       <c r="I263" s="25" t="s">
@@ -17652,7 +17658,7 @@
         <v>20</v>
       </c>
       <c r="G264" s="25">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H264" s="25"/>
       <c r="I264" s="25" t="s">
@@ -17752,8 +17758,8 @@
       </c>
       <c r="P266" s="31"/>
       <c r="Q266" s="31"/>
-      <c r="R266" s="6">
-        <v>1301251</v>
+      <c r="R266" s="6" t="s">
+        <v>783</v>
       </c>
       <c r="S266" s="32">
         <v>2</v>
@@ -17794,8 +17800,8 @@
       </c>
       <c r="P267" s="31"/>
       <c r="Q267" s="31"/>
-      <c r="R267" s="6">
-        <v>1301252</v>
+      <c r="R267" s="6" t="s">
+        <v>784</v>
       </c>
       <c r="S267" s="32">
         <v>4</v>
@@ -17836,9 +17842,7 @@
       </c>
       <c r="P268" s="31"/>
       <c r="Q268" s="31"/>
-      <c r="R268" s="6">
-        <v>1301253</v>
-      </c>
+      <c r="R268" s="6"/>
       <c r="S268" s="32">
         <v>6</v>
       </c>
@@ -17878,9 +17882,7 @@
       </c>
       <c r="P269" s="31"/>
       <c r="Q269" s="31"/>
-      <c r="R269" s="6">
-        <v>1301254</v>
-      </c>
+      <c r="R269" s="6"/>
       <c r="S269" s="32">
         <v>8</v>
       </c>
@@ -17920,9 +17922,7 @@
       </c>
       <c r="P270" s="31"/>
       <c r="Q270" s="31"/>
-      <c r="R270" s="6">
-        <v>1301255</v>
-      </c>
+      <c r="R270" s="6"/>
       <c r="S270" s="32">
         <v>10</v>
       </c>
@@ -17962,9 +17962,7 @@
       </c>
       <c r="P271" s="31"/>
       <c r="Q271" s="31"/>
-      <c r="R271" s="6">
-        <v>1301256</v>
-      </c>
+      <c r="R271" s="6"/>
       <c r="S271" s="32">
         <v>12</v>
       </c>
@@ -18004,9 +18002,7 @@
       </c>
       <c r="P272" s="31"/>
       <c r="Q272" s="31"/>
-      <c r="R272" s="6">
-        <v>1301257</v>
-      </c>
+      <c r="R272" s="6"/>
       <c r="S272" s="32">
         <v>14</v>
       </c>
@@ -18046,9 +18042,7 @@
       </c>
       <c r="P273" s="31"/>
       <c r="Q273" s="31"/>
-      <c r="R273" s="6">
-        <v>1301259</v>
-      </c>
+      <c r="R273" s="6"/>
       <c r="S273" s="32">
         <v>16</v>
       </c>
@@ -18209,7 +18203,7 @@
       <c r="P277" s="31"/>
       <c r="Q277" s="31"/>
       <c r="R277" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S277" s="32">
         <v>24</v>
@@ -18251,7 +18245,7 @@
       <c r="P278" s="31"/>
       <c r="Q278" s="31"/>
       <c r="R278" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S278" s="32">
         <v>26</v>
@@ -18293,7 +18287,7 @@
       <c r="P279" s="31"/>
       <c r="Q279" s="31"/>
       <c r="R279" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S279" s="32">
         <v>28</v>
@@ -18335,7 +18329,7 @@
       <c r="P280" s="31"/>
       <c r="Q280" s="31"/>
       <c r="R280" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S280" s="32">
         <v>30</v>
@@ -18377,7 +18371,7 @@
       <c r="P281" s="31"/>
       <c r="Q281" s="31"/>
       <c r="R281" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S281" s="32">
         <v>32</v>
@@ -18419,7 +18413,7 @@
       <c r="P282" s="31"/>
       <c r="Q282" s="31"/>
       <c r="R282" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S282" s="32">
         <v>34</v>
@@ -18461,7 +18455,7 @@
       <c r="P283" s="31"/>
       <c r="Q283" s="31"/>
       <c r="R283" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S283" s="32">
         <v>36</v>
@@ -18503,7 +18497,7 @@
       <c r="P284" s="31"/>
       <c r="Q284" s="31"/>
       <c r="R284" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S284" s="32">
         <v>38</v>
@@ -18521,7 +18515,7 @@
         <v>1303</v>
       </c>
       <c r="C285" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D285" s="29"/>
       <c r="E285" s="25">
@@ -18545,7 +18539,7 @@
       <c r="P285" s="31"/>
       <c r="Q285" s="31"/>
       <c r="R285" s="6" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="S285" s="32">
         <v>1</v>
@@ -18563,7 +18557,7 @@
         <v>1303</v>
       </c>
       <c r="C286" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D286" s="29"/>
       <c r="E286" s="25">
@@ -18605,7 +18599,7 @@
         <v>1303</v>
       </c>
       <c r="C287" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D287" s="29"/>
       <c r="E287" s="25">
@@ -18647,7 +18641,7 @@
         <v>1303</v>
       </c>
       <c r="C288" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D288" s="29"/>
       <c r="E288" s="25">
@@ -18689,7 +18683,7 @@
         <v>1303</v>
       </c>
       <c r="C289" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D289" s="29"/>
       <c r="E289" s="25">
@@ -18731,7 +18725,7 @@
         <v>1303</v>
       </c>
       <c r="C290" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D290" s="29"/>
       <c r="E290" s="25">
@@ -18773,7 +18767,7 @@
         <v>1303</v>
       </c>
       <c r="C291" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D291" s="29"/>
       <c r="E291" s="25">
@@ -18815,7 +18809,7 @@
         <v>1303</v>
       </c>
       <c r="C292" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D292" s="29"/>
       <c r="E292" s="25">
@@ -18854,7 +18848,7 @@
         <v>1303</v>
       </c>
       <c r="C293" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D293" s="29"/>
       <c r="E293" s="25">
@@ -18894,7 +18888,7 @@
         <v>1303</v>
       </c>
       <c r="C294" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D294" s="29"/>
       <c r="E294" s="25">
@@ -18934,7 +18928,7 @@
         <v>1303</v>
       </c>
       <c r="C295" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D295" s="29"/>
       <c r="E295" s="25">
@@ -18977,7 +18971,7 @@
         <v>1303</v>
       </c>
       <c r="C296" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D296" s="29"/>
       <c r="E296" s="25">
@@ -19020,7 +19014,7 @@
         <v>1303</v>
       </c>
       <c r="C297" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D297" s="29"/>
       <c r="E297" s="25">
@@ -19063,7 +19057,7 @@
         <v>1303</v>
       </c>
       <c r="C298" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D298" s="29"/>
       <c r="E298" s="25">
@@ -19106,7 +19100,7 @@
         <v>1303</v>
       </c>
       <c r="C299" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D299" s="29"/>
       <c r="E299" s="25">
@@ -19133,7 +19127,7 @@
       <c r="P299" s="31"/>
       <c r="Q299" s="31"/>
       <c r="R299" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S299" s="32">
         <v>28</v>
@@ -19151,7 +19145,7 @@
         <v>1303</v>
       </c>
       <c r="C300" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D300" s="29"/>
       <c r="E300" s="25">
@@ -19178,7 +19172,7 @@
       <c r="P300" s="31"/>
       <c r="Q300" s="31"/>
       <c r="R300" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S300" s="32">
         <v>30</v>
@@ -19196,7 +19190,7 @@
         <v>1303</v>
       </c>
       <c r="C301" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D301" s="29"/>
       <c r="E301" s="25">
@@ -19223,7 +19217,7 @@
       <c r="P301" s="31"/>
       <c r="Q301" s="31"/>
       <c r="R301" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S301" s="32">
         <v>32</v>
@@ -19241,7 +19235,7 @@
         <v>1303</v>
       </c>
       <c r="C302" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D302" s="29"/>
       <c r="E302" s="25">
@@ -19268,7 +19262,7 @@
       <c r="P302" s="31"/>
       <c r="Q302" s="31"/>
       <c r="R302" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S302" s="32">
         <v>34</v>
@@ -19286,7 +19280,7 @@
         <v>1303</v>
       </c>
       <c r="C303" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D303" s="29"/>
       <c r="E303" s="25">
@@ -19313,7 +19307,7 @@
       <c r="P303" s="31"/>
       <c r="Q303" s="31"/>
       <c r="R303" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S303" s="32">
         <v>36</v>
@@ -19331,7 +19325,7 @@
         <v>1303</v>
       </c>
       <c r="C304" s="29" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D304" s="29"/>
       <c r="E304" s="25">
@@ -19358,7 +19352,7 @@
       <c r="P304" s="31"/>
       <c r="Q304" s="31"/>
       <c r="R304" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S304" s="32">
         <v>38</v>
@@ -19376,7 +19370,7 @@
         <v>1304</v>
       </c>
       <c r="C305" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D305" s="25"/>
       <c r="E305" s="25">
@@ -19396,7 +19390,7 @@
         <v>751</v>
       </c>
       <c r="R305" s="5" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="S305" s="27">
         <v>1</v>
@@ -19414,7 +19408,7 @@
         <v>1304</v>
       </c>
       <c r="C306" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D306" s="25"/>
       <c r="E306" s="25">
@@ -19452,7 +19446,7 @@
         <v>1304</v>
       </c>
       <c r="C307" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D307" s="25"/>
       <c r="E307" s="25">
@@ -19490,7 +19484,7 @@
         <v>1304</v>
       </c>
       <c r="C308" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D308" s="25"/>
       <c r="E308" s="25">
@@ -19528,7 +19522,7 @@
         <v>1304</v>
       </c>
       <c r="C309" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D309" s="25"/>
       <c r="E309" s="25">
@@ -19566,7 +19560,7 @@
         <v>1304</v>
       </c>
       <c r="C310" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D310" s="25"/>
       <c r="E310" s="25">
@@ -19604,7 +19598,7 @@
         <v>1304</v>
       </c>
       <c r="C311" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D311" s="25"/>
       <c r="E311" s="25">
@@ -19639,7 +19633,7 @@
         <v>1304</v>
       </c>
       <c r="C312" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D312" s="25"/>
       <c r="E312" s="25">
@@ -19674,7 +19668,7 @@
         <v>1304</v>
       </c>
       <c r="C313" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D313" s="25"/>
       <c r="E313" s="25">
@@ -19709,7 +19703,7 @@
         <v>1304</v>
       </c>
       <c r="C314" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D314" s="25"/>
       <c r="E314" s="25">
@@ -19744,7 +19738,7 @@
         <v>1304</v>
       </c>
       <c r="C315" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D315" s="25"/>
       <c r="E315" s="25">
@@ -19764,7 +19758,7 @@
         <v>751</v>
       </c>
       <c r="R315" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S315" s="27">
         <v>20</v>
@@ -19782,7 +19776,7 @@
         <v>1304</v>
       </c>
       <c r="C316" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D316" s="25"/>
       <c r="E316" s="25">
@@ -19802,7 +19796,7 @@
         <v>751</v>
       </c>
       <c r="R316" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S316" s="27">
         <v>22</v>
@@ -19820,7 +19814,7 @@
         <v>1304</v>
       </c>
       <c r="C317" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D317" s="25"/>
       <c r="E317" s="25">
@@ -19840,7 +19834,7 @@
         <v>751</v>
       </c>
       <c r="R317" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S317" s="27">
         <v>24</v>
@@ -19858,7 +19852,7 @@
         <v>1304</v>
       </c>
       <c r="C318" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D318" s="25"/>
       <c r="E318" s="25">
@@ -19878,7 +19872,7 @@
         <v>751</v>
       </c>
       <c r="R318" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S318" s="27">
         <v>26</v>
@@ -19896,7 +19890,7 @@
         <v>1304</v>
       </c>
       <c r="C319" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D319" s="25"/>
       <c r="E319" s="25">
@@ -19916,7 +19910,7 @@
         <v>751</v>
       </c>
       <c r="R319" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S319" s="27">
         <v>28</v>
@@ -19934,7 +19928,7 @@
         <v>1304</v>
       </c>
       <c r="C320" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D320" s="25"/>
       <c r="E320" s="25">
@@ -19954,7 +19948,7 @@
         <v>751</v>
       </c>
       <c r="R320" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S320" s="27">
         <v>30</v>
@@ -19972,7 +19966,7 @@
         <v>1304</v>
       </c>
       <c r="C321" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D321" s="25"/>
       <c r="E321" s="25">
@@ -19992,7 +19986,7 @@
         <v>751</v>
       </c>
       <c r="R321" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S321" s="27">
         <v>32</v>
@@ -20010,7 +20004,7 @@
         <v>1304</v>
       </c>
       <c r="C322" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D322" s="25"/>
       <c r="E322" s="25">
@@ -20030,7 +20024,7 @@
         <v>751</v>
       </c>
       <c r="R322" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S322" s="27">
         <v>34</v>
@@ -20048,7 +20042,7 @@
         <v>1304</v>
       </c>
       <c r="C323" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D323" s="25"/>
       <c r="E323" s="25">
@@ -20068,7 +20062,7 @@
         <v>751</v>
       </c>
       <c r="R323" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S323" s="27">
         <v>36</v>
@@ -20086,7 +20080,7 @@
         <v>1304</v>
       </c>
       <c r="C324" s="25" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D324" s="25"/>
       <c r="E324" s="25">
@@ -20106,7 +20100,7 @@
         <v>751</v>
       </c>
       <c r="R324" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S324" s="27">
         <v>38</v>
@@ -20134,10 +20128,10 @@
   <sheetData>
     <row r="1" spans="1:73">
       <c r="A1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="2" spans="1:73">
@@ -22080,7 +22074,7 @@
     </row>
     <row r="11" spans="1:73">
       <c r="B11" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C11">
         <f>SUM(C2:C10)</f>
@@ -24953,7 +24947,7 @@
     </row>
     <row r="27" spans="3:74">
       <c r="C27" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28" spans="3:74">
@@ -30797,7 +30791,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:V239"/>
+  <dimension ref="A2:V256"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="9.375"/>
@@ -33898,7 +33892,7 @@
         <v>1102103</v>
       </c>
       <c r="C179">
-        <f t="shared" ref="C179:C183" si="3">B179*10+1</f>
+        <f t="shared" ref="C179:C184" si="3">B179*10+1</f>
         <v>11021031</v>
       </c>
       <c r="E179">
@@ -33982,7 +33976,7 @@
         <v>1102108</v>
       </c>
       <c r="C184">
-        <f>B184*10+1</f>
+        <f t="shared" si="3"/>
         <v>11021081</v>
       </c>
       <c r="F184">
@@ -34137,7 +34131,7 @@
         <v>1101101</v>
       </c>
       <c r="C200">
-        <f t="shared" ref="C200:C206" si="4">B200*10+1</f>
+        <f t="shared" ref="C200:C207" si="4">B200*10+1</f>
         <v>11011011</v>
       </c>
       <c r="E200">
@@ -34287,7 +34281,7 @@
         <v>1101101</v>
       </c>
       <c r="C207">
-        <f>B207*10+1</f>
+        <f t="shared" si="4"/>
         <v>11011011</v>
       </c>
       <c r="E207">
@@ -34633,398 +34627,533 @@
         <v>1101297</v>
       </c>
     </row>
+    <row r="242" spans="5:10">
+      <c r="H242" t="str">
+        <f t="shared" ref="H242:J242" si="5">_xlfn.TEXTJOIN("_",TRUE,H243:H258)</f>
+        <v>1301251_1301252_1301253_1301254_1301257_1301259_1301260_1301263_1301264</v>
+      </c>
+      <c r="I242" t="str">
+        <f t="shared" si="5"/>
+        <v>1301258_1301261</v>
+      </c>
+      <c r="J242" t="str">
+        <f t="shared" si="5"/>
+        <v>1301262_1301255_1301256</v>
+      </c>
+    </row>
+    <row r="243" spans="5:10">
+      <c r="E243">
+        <v>1301251</v>
+      </c>
+      <c r="H243">
+        <v>1301251</v>
+      </c>
+      <c r="I243">
+        <v>1301258</v>
+      </c>
+      <c r="J243">
+        <v>1301262</v>
+      </c>
+    </row>
+    <row r="244" spans="5:10">
+      <c r="E244">
+        <v>1301252</v>
+      </c>
+      <c r="H244">
+        <v>1301252</v>
+      </c>
+      <c r="I244">
+        <v>1301261</v>
+      </c>
+      <c r="J244">
+        <v>1301255</v>
+      </c>
+    </row>
+    <row r="245" spans="5:10">
+      <c r="E245">
+        <v>1301253</v>
+      </c>
+      <c r="H245">
+        <v>1301253</v>
+      </c>
+      <c r="J245">
+        <v>1301256</v>
+      </c>
+    </row>
+    <row r="246" spans="5:10">
+      <c r="E246">
+        <v>1301254</v>
+      </c>
+      <c r="H246">
+        <v>1301254</v>
+      </c>
+    </row>
+    <row r="247" spans="5:10">
+      <c r="E247">
+        <v>1301255</v>
+      </c>
+      <c r="H247">
+        <v>1301257</v>
+      </c>
+    </row>
+    <row r="248" spans="5:10">
+      <c r="E248">
+        <v>1301256</v>
+      </c>
+      <c r="H248">
+        <v>1301259</v>
+      </c>
+    </row>
+    <row r="249" spans="5:10">
+      <c r="E249">
+        <v>1301257</v>
+      </c>
+      <c r="H249">
+        <v>1301260</v>
+      </c>
+    </row>
+    <row r="250" spans="5:10">
+      <c r="E250">
+        <v>1301258</v>
+      </c>
+      <c r="H250">
+        <v>1301263</v>
+      </c>
+    </row>
+    <row r="251" spans="5:10">
+      <c r="E251">
+        <v>1301259</v>
+      </c>
+      <c r="H251">
+        <v>1301264</v>
+      </c>
+    </row>
+    <row r="252" spans="5:10">
+      <c r="E252">
+        <v>1301260</v>
+      </c>
+    </row>
+    <row r="253" spans="5:10">
+      <c r="E253">
+        <v>1301261</v>
+      </c>
+    </row>
+    <row r="254" spans="5:10">
+      <c r="E254">
+        <v>1301262</v>
+      </c>
+    </row>
+    <row r="255" spans="5:10">
+      <c r="E255">
+        <v>1301263</v>
+      </c>
+    </row>
+    <row r="256" spans="5:10">
+      <c r="E256">
+        <v>1301264</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M2">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3">
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3">
+    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4">
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O4">
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N8">
+    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O8">
+    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N9">
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O9">
+    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V9">
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N10">
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O10">
+    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V10">
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U11">
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
+    <cfRule type="duplicateValues" dxfId="0" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
+    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V18">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V19">
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
     <cfRule type="duplicateValues" dxfId="0" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2">
+  <conditionalFormatting sqref="U24">
     <cfRule type="duplicateValues" dxfId="0" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3">
-    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3">
-    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O4">
-    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8">
-    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8">
-    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9">
-    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O9">
-    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V9">
-    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N10">
-    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O10">
-    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V10">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U11">
+  <conditionalFormatting sqref="F28">
     <cfRule type="duplicateValues" dxfId="0" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V18">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V19">
-    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M24">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U24">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
     <cfRule type="duplicateValues" dxfId="0" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N35">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N36">
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N40">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M45">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U45">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E64">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F64">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M64">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U64">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F65">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E85">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F85">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H85">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I85">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J85">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K85">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L85">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M85">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C111">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J111">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P111">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D129:F129">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B159">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C159">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H159">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J159">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K159">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L159">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B178:C178">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B182:C182">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C198">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H198">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J198:N198">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B212:C212">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B219:C219">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E13">
-    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F7">
-    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11">
-    <cfRule type="duplicateValues" dxfId="0" priority="136"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F14">
-    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:F27">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:F35">
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F35">
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F38">
     <cfRule type="duplicateValues" dxfId="0" priority="69"/>
     <cfRule type="duplicateValues" dxfId="0" priority="68"/>
     <cfRule type="duplicateValues" dxfId="0" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29:G34">
+  <conditionalFormatting sqref="N40">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M45">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U45">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F64">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U64">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F65">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E85">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F85">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H85">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I85">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J85">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K85">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L85">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M85">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C111">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J111">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P111">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D129:F129">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B159">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C159">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H159">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J159">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K159">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L159">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B178:C178">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B182:C182">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B198">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C198">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H198">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J198:N198">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B212:C212">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B219:C219">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H242">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I242:J242">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E13">
+    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F7">
+    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13:F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18:F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:F27">
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F35">
     <cfRule type="duplicateValues" dxfId="0" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G34">
+  <conditionalFormatting sqref="F31:F35">
     <cfRule type="duplicateValues" dxfId="0" priority="75"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F36:F38">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G34">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G34">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3:I7">
+    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8:I11">
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13:I14">
     <cfRule type="duplicateValues" dxfId="0" priority="145"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8:I11">
+  <conditionalFormatting sqref="I15:I16">
     <cfRule type="duplicateValues" dxfId="0" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13:I14">
+  <conditionalFormatting sqref="I18:I20">
     <cfRule type="duplicateValues" dxfId="0" priority="142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15:I16">
-    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18:I20">
-    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N5:N7">
-    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11:N12">
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:N17">
+    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N18:N19">
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25:N27">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N29:N31">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N32:N34">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N37:N39">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O7">
+    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O11:O12">
+    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O13:O17">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O18:O19">
+    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V3:V5">
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V6:V8">
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V11:V14">
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V15:V17">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V35:V37">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H2 A3:D13 G3:H13">
+    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:L2 N2 J3:N20">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:M16">
+    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:U10 R11:T11 R12:U16">
     <cfRule type="duplicateValues" dxfId="0" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N13:N17">
-    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+  <conditionalFormatting sqref="R3:V19">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:N19">
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+  <conditionalFormatting sqref="A25:E37">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N25:N27">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N29:N31">
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N32:N34">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N37:N39">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  <conditionalFormatting sqref="A25:F28 A29:E37">
     <cfRule type="duplicateValues" dxfId="0" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O5:O7">
-    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+  <conditionalFormatting sqref="A25:F35 A36:E37">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11:O12">
-    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+  <conditionalFormatting sqref="J25:M37">
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O13:O17">
-    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  <conditionalFormatting sqref="J25:N36">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O18:O19">
-    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
+  <conditionalFormatting sqref="R25:V34 R35:U36">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:V5">
-    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V8">
-    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V11:V14">
-    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V15:V17">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V35:V37">
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H2 A3:D13 G3:H13">
-    <cfRule type="duplicateValues" dxfId="0" priority="146"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:L2 N2 J3:N20">
+  <conditionalFormatting sqref="A46:F58">
     <cfRule type="duplicateValues" dxfId="0" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:F20">
+  <conditionalFormatting sqref="J46:N62">
     <cfRule type="duplicateValues" dxfId="0" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:M16">
-    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
+  <conditionalFormatting sqref="R46:V62">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:U10 R11:T11 R12:U16">
-    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R3:V19">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25:E37">
-    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25:F28 A29:E37">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25:F35 A36:E37">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25:M37">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25:N36">
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R25:V34 R35:U36">
-    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A46:F58">
+  <conditionalFormatting sqref="A65:E65 A66:F81">
     <cfRule type="duplicateValues" dxfId="0" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J46:N62">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R46:V62">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65:E65 A66:F81">
+  <conditionalFormatting sqref="A65:F80">
     <cfRule type="duplicateValues" dxfId="0" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A65:F80">
+  <conditionalFormatting sqref="J65:N81">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R65:V82">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A86:Q105">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A86:G110 A111:B111 D111:G111 A112:G125">
     <cfRule type="duplicateValues" dxfId="0" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J65:N81">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R65:V82">
+  <conditionalFormatting sqref="H112:K123">
     <cfRule type="duplicateValues" dxfId="0" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A86:Q105">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A86:G110 A111:B111 D111:G111 A112:G125">
+  <conditionalFormatting sqref="N112:Q122">
     <cfRule type="duplicateValues" dxfId="0" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H112:K123">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N112:Q122">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A130:I155">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A160:B177">
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E160:H196">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A199:B211 A212 A213:B214">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E199:H237 H238:H239">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E243:H255 E256">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40594,488 +40723,488 @@
   <sheetData>
     <row r="1" spans="1:27">
       <c r="A1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="I1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="J1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="K1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="L1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="M1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="N1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="O1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="P1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="Q1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="R1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="S1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="T1" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="U1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="V1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="W1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="X1" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="Y1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="Z1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AA1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="G2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="H2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="I2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="K2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="L2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="M2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="N2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="O2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="P2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="Q2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="R2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="S2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="T2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="U2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="V2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="W2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="X2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="Y2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="1:27">
       <c r="A3" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C3" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="G3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="H3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:27">
       <c r="I12" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="13" spans="1:27">
       <c r="I13" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:27">
       <c r="I14" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15" spans="1:27">
       <c r="I15" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:27">
       <c r="I16" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="17" spans="9:9">
       <c r="I17" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="18" spans="9:9">
       <c r="I18" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19" spans="9:9">
       <c r="I19" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="20" spans="9:9">
       <c r="I20" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" spans="9:9">
       <c r="I21" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="22" spans="9:9">
       <c r="I22" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="23" spans="9:9">
       <c r="I23" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="24" spans="9:9">
       <c r="I24" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="25" spans="9:9">
       <c r="I25" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="26" spans="9:9">
       <c r="I26" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="27" spans="9:9">
       <c r="I27" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="28" spans="9:9">
       <c r="I28" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="29" spans="9:9">
       <c r="I29" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="30" spans="9:9">
       <c r="I30" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="31" spans="9:9">
       <c r="I31" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="32" spans="9:9">
       <c r="I32" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="33" spans="9:9">
       <c r="I33" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="34" spans="9:9">
       <c r="I34" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="35" spans="9:9">
       <c r="I35" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="36" spans="9:9">
       <c r="I36" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="37" spans="9:9">
       <c r="I37" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="38" spans="9:9">
       <c r="I38" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="39" spans="9:9">
       <c r="I39" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="40" spans="9:9">
       <c r="I40" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="41" spans="9:9">
       <c r="I41" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="42" spans="9:9">
       <c r="I42" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="44" spans="9:9">
       <c r="I44" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="45" spans="9:9">
       <c r="I45" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="46" spans="9:9">
       <c r="I46" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="47" spans="9:9">
       <c r="I47" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="48" spans="9:9">
       <c r="I48" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="49" spans="9:9">
       <c r="I49" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50" spans="9:9">
       <c r="I50" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="51" spans="9:9">
       <c r="I51" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="52" spans="9:9">
       <c r="I52" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="53" spans="9:9">
       <c r="I53" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="54" spans="9:9">
       <c r="I54" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="55" spans="9:9">
       <c r="I55" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="56" spans="9:9">
       <c r="I56" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="57" spans="9:9">
       <c r="I57" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="58" spans="9:9">
       <c r="I58" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="59" spans="9:9">
       <c r="I59" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="60" spans="9:9">
       <c r="I60" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="61" spans="9:9">
       <c r="I61" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="62" spans="9:9">
       <c r="I62" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="63" spans="9:9">
       <c r="I63" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="64" spans="9:9">
       <c r="I64" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="65" spans="9:9">
       <c r="I65" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="66" spans="9:9">
       <c r="I66" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="67" spans="9:9">
       <c r="I67" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="68" spans="9:9">
       <c r="I68" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="69" spans="9:9">
       <c r="I69" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="70" spans="9:9">
       <c r="I70" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="71" spans="9:9">
       <c r="I71" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -41099,13 +41228,13 @@
         <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2" spans="2:5">

--- a/hall/resources/sample/BuildingUpgradeTable.xlsx
+++ b/hall/resources/sample/BuildingUpgradeTable.xlsx
@@ -3697,17 +3697,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3911,25 +3901,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4539,7 +4529,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="25">
         <v>3</v>
@@ -4595,7 +4585,7 @@
         <v>44</v>
       </c>
       <c r="E8" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="25">
         <v>4</v>
@@ -4656,7 +4646,7 @@
         <v>44</v>
       </c>
       <c r="E9" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="25">
         <v>5</v>
@@ -4712,7 +4702,7 @@
         <v>44</v>
       </c>
       <c r="E10" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="25">
         <v>6</v>
@@ -4771,7 +4761,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="25">
         <v>7</v>
@@ -4818,7 +4808,7 @@
         <v>44</v>
       </c>
       <c r="E12" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="25">
         <v>8</v>
@@ -4867,7 +4857,7 @@
         <v>44</v>
       </c>
       <c r="E13" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="25">
         <v>9</v>
@@ -4916,7 +4906,7 @@
         <v>44</v>
       </c>
       <c r="E14" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="25">
         <v>10</v>
@@ -4962,7 +4952,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="25">
         <v>11</v>
@@ -5013,7 +5003,7 @@
         <v>44</v>
       </c>
       <c r="E16" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="25">
         <v>12</v>
@@ -5060,7 +5050,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="25">
         <v>13</v>
@@ -5111,7 +5101,7 @@
         <v>44</v>
       </c>
       <c r="E18" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="25">
         <v>14</v>
@@ -5160,7 +5150,7 @@
         <v>44</v>
       </c>
       <c r="E19" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="25">
         <v>15</v>
@@ -5211,7 +5201,7 @@
         <v>44</v>
       </c>
       <c r="E20" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="25">
         <v>16</v>
@@ -5260,7 +5250,7 @@
         <v>44</v>
       </c>
       <c r="E21" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="25">
         <v>17</v>
@@ -5311,7 +5301,7 @@
         <v>44</v>
       </c>
       <c r="E22" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="25">
         <v>18</v>
@@ -5360,7 +5350,7 @@
         <v>44</v>
       </c>
       <c r="E23" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="25">
         <v>19</v>
@@ -5411,7 +5401,7 @@
         <v>44</v>
       </c>
       <c r="E24" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="25">
         <v>20</v>
@@ -35154,7 +35144,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243:H255 E256">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
